--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$1:$N$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$1:$AB$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,23 +452,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,50 +508,120 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>raison_sociale</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>forme_juridique</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>code_naf</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>libelle_naf</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>date_creation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>annee_ouverture</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>code_postal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>effectif</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>chiffre_affaires</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>annee_ca</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>site_web</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_nom</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_prenom</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_poste</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_adresse</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_code_postal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dirigeant_ville</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dirigeants</t>
         </is>
@@ -564,52 +648,66 @@
           <t>LES FRERES DE BAKEL</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>04/03/2019</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>18 RUE DE L'ABREUVOIR</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -632,52 +730,66 @@
           <t>ARLANMETZ</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>03/05/2024</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>26 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -700,52 +812,66 @@
           <t>SORRENTO</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>19/11/1992</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>73 RUE AUX ARENES</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -768,52 +894,66 @@
           <t>SARL JULES ADRIEN</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>20/12/2010</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2 RUE HAUTE</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>55000</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>LES HAUTS-DE-CHEE</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -836,52 +976,66 @@
           <t>STAGNA57</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>13/05/2019</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -904,52 +1058,66 @@
           <t>MAISON MOITRIER-BRASSERIE ABC</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>01/01/1968</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2 PLACE DU GENERAL DE GAULLE</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -972,52 +1140,66 @@
           <t>CITY'REST</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>07/05/2019</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14 RUE MARGUERITE PUHL-DEMANGE</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1040,52 +1222,66 @@
           <t>ALTHEROM</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>02/12/2024</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1 RUE DE LA PIERRE HARDIE</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1108,52 +1304,66 @@
           <t>RESTAURANT OSAKA</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>15/03/2001</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32 B RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1176,52 +1386,66 @@
           <t>ISAYA</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>25/01/2024</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17 B RUE DE PELTRE</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>57245</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>CHESNY</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1244,52 +1468,66 @@
           <t>ALPHAM</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>06/06/2005</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>83 RUE MAZELLE</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1316,52 +1554,66 @@
           <t>MRC</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>20/01/2020</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1388,52 +1640,66 @@
           <t>JUVIC</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>21/12/2021</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>81 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1460,52 +1726,66 @@
           <t>MARTINA SAULCY</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>10/12/2024</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2 PLACE JEAN MOULIN</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1532,52 +1812,66 @@
           <t>AN</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>19/10/2022</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>31 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1604,52 +1898,66 @@
           <t>LA JEEP</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Société en nom collectif</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>02/01/2005</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>3 B RUE VAUBAN</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1676,52 +1984,66 @@
           <t>ISLAMABAD</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>09/03/2001</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>92 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1748,52 +2070,66 @@
           <t>SARL LA TORCHE</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>27/11/1986</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>10 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1820,52 +2156,66 @@
           <t>HERBAUX</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>22/06/2017</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>30 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1892,52 +2242,66 @@
           <t>MACOVA</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>01/10/2007</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>11 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -1964,52 +2328,66 @@
           <t>CAPPAERT PHILIPPE</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>02/01/1991</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>33 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>PHILIPPE JEAN ALBERT CAPPAERT | Chef d'entreprise</t>
         </is>
@@ -2036,52 +2414,66 @@
           <t>LE CAFE DU PORT</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>32 PLACE SAINT-THIEBAULT</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2108,52 +2500,66 @@
           <t>SAVEURS DU TIBET</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>15/10/2024</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>3 RUE DU CHAMPE</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2180,52 +2586,66 @@
           <t>GUARA</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
           <t>16/09/2020</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>14 RUE DE L'ABREUVOIR</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2252,52 +2672,66 @@
           <t>AMPIRE</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>SA à conseil d'administration (s.a.i.)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>01/11/1995</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>MARCHE DE LA CHEVRE</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2324,52 +2758,66 @@
           <t>BIERSTUB</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
           <t>11/10/2019</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>44 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2396,52 +2844,66 @@
           <t>C.D.F.P.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>07/07/2008</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>29 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2468,52 +2930,66 @@
           <t>VERDURA CATHEDRALE</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
           <t>18/09/2021</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>7 PLACE JEAN-PAUL II</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2540,52 +3016,66 @@
           <t>MAXIM'E</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>08/04/1997</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>2 B RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2612,52 +3102,66 @@
           <t>AJ2M</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
           <t>30/09/2022</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>56 RUE DE LA CHAPELLE</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2684,52 +3188,66 @@
           <t>ALGHERO</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
           <t>10/07/2015</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>68 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2756,52 +3274,66 @@
           <t>LES BISTROTS DE METZ</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
           <t>16/10/2019</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>12 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2828,52 +3360,66 @@
           <t>OPPA EONNI</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
           <t>18/09/2025</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>3 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2900,52 +3446,66 @@
           <t>RDJ</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
           <t>11/07/2025</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>35 QUAI FELIX MARECHAL</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -2972,52 +3532,66 @@
           <t>RS GOURMET</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>22/03/2012</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>3 RUE DES PARMENTIERS</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3044,52 +3618,66 @@
           <t>FUKUOKA</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
           <t>01/06/2021</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>11 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3116,52 +3704,66 @@
           <t>VILLA PREZIOSA</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
           <t>03/01/2022</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>32 RUE DU COETLOSQUET</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3188,52 +3790,66 @@
           <t>JOULEAR</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
           <t>19/11/2015</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>65 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3260,52 +3876,66 @@
           <t>LA RIPAILLE</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
           <t>14/11/2022</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>40 RUE DE LA TETE D'OR</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3332,52 +3962,66 @@
           <t>SAS PIEROZEK</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
           <t>01/06/2022</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>2 RUE DE LA PIERRE HARDIE</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3404,52 +4048,66 @@
           <t>REPUBLIQUE</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
           <t>30/05/2005</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>1 AVENUE NEY</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3476,52 +4134,66 @@
           <t>PALAIS BANH BAO</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
           <t>02/01/2012</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>15 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3548,52 +4220,66 @@
           <t>STEACK HOUSE</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
           <t>13/10/2016</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>43 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3620,52 +4306,66 @@
           <t>OISIF</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>27 RUE TAISON</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3692,52 +4392,66 @@
           <t>HD MUSE</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
           <t>01/04/2022</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3764,52 +4478,66 @@
           <t>C.R METZ</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
           <t>15/04/2024</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>1 PARVIS DES DROITS DE L'HOMME</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3836,52 +4564,66 @@
           <t>LA TERRASSE</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
           <t>15/05/1985</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>27 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3908,52 +4650,66 @@
           <t>LE BROOK</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
           <t>03/01/2023</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>25 RUE DES ROCHES</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -3980,52 +4736,66 @@
           <t>L'EVIDENCE II</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
           <t>25/02/2010</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>10 RUE DES PARMENTIERS</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4052,52 +4822,66 @@
           <t>DARUL AMAN</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
           <t>06/07/2020</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>41 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4124,52 +4908,66 @@
           <t>J2S</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
           <t>07/02/2020</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>10 RUE DES TROIS EVECHES</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4196,52 +4994,66 @@
           <t>OBJECTIF 53</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
           <t>18/04/2011</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>38 RUE DE LA TETE D'OR</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr"/>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4268,52 +5080,66 @@
           <t>PIETRAPAOLI</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
           <t>18/12/2003</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>7 AVENUE FRANCOIS MITTERRAND</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4340,52 +5166,66 @@
           <t>LOUBNAN</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
           <t>27/08/2025</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>20 B RUE DES JARDINS</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale pour les industries de produits alimentaires élaborés</t>
         </is>
@@ -4412,52 +5252,66 @@
           <t>NEWCO</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
           <t>06/12/2016</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>8 RUE DE LADOUCETTE</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4484,52 +5338,66 @@
           <t>C.A.T.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
           <t>14/10/2020</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>30 RUE SAINT-JEAN</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4556,52 +5424,66 @@
           <t>RACCOON</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
           <t>01/03/2022</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>11 AVENUE ROBERT SCHUMAN</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4628,52 +5510,66 @@
           <t>LCR RESTAURATION</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
           <t>01/10/2023</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>20 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4700,52 +5596,66 @@
           <t>ALFANO CLAUDE</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
           <t>04/11/1985</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>18 RUE DE L'ABREUVOIR</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>CLAUDE ALFANO | Chef d'entreprise</t>
         </is>
@@ -4772,52 +5682,66 @@
           <t>IK FOOD</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
           <t>01/06/2023</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>1 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale de la restauration rapide (restauration livrée)</t>
         </is>
@@ -4844,52 +5768,66 @@
           <t>NR4 - LE ROMARIN</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
           <t>10/08/2020</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>18 RUE DES AUGUSTINS</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr"/>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>Convention collective nationale des hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4916,52 +5854,66 @@
           <t>L'EMPIRE DE CHINE</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
           <t>27/12/1991</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>12 RUE DU NEUFBOURG</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr"/>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
@@ -4988,419 +5940,1089 @@
           <t>LE PEPE ROSSO RESTAURANT</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Restauration traditionnelle</t>
+          <t>56.10A</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
           <t>01/01/1978</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>81 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>Hôtels, cafés, restaurants (HCR)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>929975167</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>92997516700016</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Amb</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>Restauration traditionnelle</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>24/05/2024</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>8 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>Mathieu BERTOLONI | Président</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>993479617</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>99347961700017</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>HOPESUN</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>Restauration traditionnelle</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>30/10/2025</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>2 RUE HENRY MARET</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr"/>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>Jianmin ZHOU | Gérant ; Xiaoyi ZHOU | Gérant</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>799964572</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>79996457200017</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>LA FABRIQUE</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Restauration traditionnelle</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>01/02/2014</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>11 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr"/>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>Mitra MAROUF | Gérant</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>518661715</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>51866171500012</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>O PARADIS ETHIOPIEN</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Restauration traditionnelle</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>07/12/2009</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>14 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr"/>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>Genet ABEBE NEGA | Gérant</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>490402641</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>49040264100024</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>SARL CARISSIMI PIZZA</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>56.10A</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Restauration traditionnelle</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>01/06/2006</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>72 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>METZ</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr"/>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>Rosa SAVIO | Gérant</t>
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>848508156</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>84850815600025</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>RIZO</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>RIZO</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2019</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>7 RUE LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="5" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V70" s="4" t="inlineStr">
+        <is>
+          <t>SCHIPANI</t>
+        </is>
+      </c>
+      <c r="W70" s="4" t="inlineStr">
+        <is>
+          <t>Ricky, Giuseppe, Dominique</t>
+        </is>
+      </c>
+      <c r="X70" s="4" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y70" s="4" t="inlineStr">
+        <is>
+          <t>23 rue d'Auché</t>
+        </is>
+      </c>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>57680</t>
+        </is>
+      </c>
+      <c r="AA70" s="4" t="inlineStr">
+        <is>
+          <t>Corny-sur-Moselle</t>
+        </is>
+      </c>
+      <c r="AB70" s="4" t="inlineStr">
+        <is>
+          <t>Ricky Giuseppe Dominique SCHIPANI | Président</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>940159940</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>94015994000011</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>BS COMPAGNIE</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>BS COMPAGNIE</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>01/12/2024</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>3 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
+      <c r="Q71" s="4" t="inlineStr"/>
+      <c r="R71" s="4" t="inlineStr"/>
+      <c r="S71" s="5" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr"/>
+      <c r="U71" s="4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V71" s="4" t="inlineStr">
+        <is>
+          <t>BENAOUICHA</t>
+        </is>
+      </c>
+      <c r="W71" s="4" t="inlineStr">
+        <is>
+          <t>Samir</t>
+        </is>
+      </c>
+      <c r="X71" s="4" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y71" s="4" t="inlineStr">
+        <is>
+          <t>25 rue marc seguin</t>
+        </is>
+      </c>
+      <c r="Z71" s="4" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="AA71" s="4" t="inlineStr">
+        <is>
+          <t>Montigny-lès-Metz</t>
+        </is>
+      </c>
+      <c r="AB71" s="4" t="inlineStr">
+        <is>
+          <t>Samir BENAOUICHA | Président</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>819532219</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>81953221900022</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>AUX GLACES DE LA FERME</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>AUX GLACES DE LA FERME</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>30/03/2016</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>20 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
+      <c r="Q72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="5" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr"/>
+      <c r="U72" s="4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>HORY</t>
+        </is>
+      </c>
+      <c r="W72" s="4" t="inlineStr">
+        <is>
+          <t>Vincent, Roland</t>
+        </is>
+      </c>
+      <c r="X72" s="4" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y72" s="4" t="inlineStr">
+        <is>
+          <t>75 rue Principale</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="inlineStr">
+        <is>
+          <t>57580</t>
+        </is>
+      </c>
+      <c r="AA72" s="4" t="inlineStr">
+        <is>
+          <t>Vittoncourt</t>
+        </is>
+      </c>
+      <c r="AB72" s="4" t="inlineStr">
+        <is>
+          <t>Vincent Roland HORY | Gérant ; Estelle SAR | Gérant</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>839551389</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>83955138900035</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>AHMED AMER</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>AHMED AMER</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>01/05/2018</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>29 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr"/>
+      <c r="Q73" s="4" t="inlineStr"/>
+      <c r="R73" s="4" t="inlineStr"/>
+      <c r="S73" s="5" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V73" s="4" t="inlineStr">
+        <is>
+          <t>AHMED</t>
+        </is>
+      </c>
+      <c r="W73" s="4" t="inlineStr">
+        <is>
+          <t>Amer</t>
+        </is>
+      </c>
+      <c r="X73" s="4" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="Y73" s="4" t="inlineStr"/>
+      <c r="Z73" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA73" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="AB73" s="4" t="inlineStr">
+        <is>
+          <t>Amer AHMED | Chef d'entreprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>850375502</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>85037550200018</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>25/04/2019</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>26 AVENUE FOCH</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr"/>
+      <c r="Q74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="inlineStr"/>
+      <c r="S74" s="5" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr"/>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V74" s="4" t="inlineStr">
+        <is>
+          <t>MARCHAL</t>
+        </is>
+      </c>
+      <c r="W74" s="4" t="inlineStr">
+        <is>
+          <t>Valentin</t>
+        </is>
+      </c>
+      <c r="X74" s="4" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y74" s="4" t="inlineStr">
+        <is>
+          <t>26 avenue foch</t>
+        </is>
+      </c>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>57680</t>
+        </is>
+      </c>
+      <c r="AA74" s="4" t="inlineStr">
+        <is>
+          <t>Novéant-sur-Moselle</t>
+        </is>
+      </c>
+      <c r="AB74" s="4" t="inlineStr">
+        <is>
+          <t>Valentin MARCHAL | Gérant</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N69"/>
+  <autoFilter ref="A1:AB74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$AA$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$AA$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -164,8 +164,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -207,6 +208,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -579,12 +586,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="1" min="2" max="2"/>
+    <col width="16" customWidth="1" style="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
@@ -600,2461 +607,3054 @@
     <col width="8" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" style="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" style="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ENTREPRISE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>ACTIVITE</t>
         </is>
       </c>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LOCALISATION</t>
         </is>
       </c>
-      <c r="L1" s="6" t="n"/>
-      <c r="M1" s="6" t="n"/>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>FINANCES</t>
         </is>
       </c>
-      <c r="O1" s="8" t="n"/>
-      <c r="P1" s="8" t="n"/>
-      <c r="Q1" s="8" t="n"/>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>CONTACT</t>
         </is>
       </c>
-      <c r="S1" s="10" t="n"/>
-      <c r="T1" s="10" t="n"/>
-      <c r="U1" s="10" t="n"/>
-      <c r="V1" s="11" t="inlineStr">
+      <c r="S1" s="11" t="n"/>
+      <c r="T1" s="11" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>DIRIGEANTS</t>
         </is>
       </c>
-      <c r="W1" s="12" t="n"/>
-      <c r="X1" s="12" t="n"/>
-      <c r="Y1" s="12" t="n"/>
-      <c r="Z1" s="12" t="n"/>
-      <c r="AA1" s="12" t="n"/>
+      <c r="W1" s="13" t="n"/>
+      <c r="X1" s="13" t="n"/>
+      <c r="Y1" s="13" t="n"/>
+      <c r="Z1" s="13" t="n"/>
+      <c r="AA1" s="13" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>date_ajout</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>siren</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>siret_siege</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>raison_sociale</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>forme_juridique</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>code_naf</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>libelle_naf</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>date_creation</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t>annee_ouverture</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>code_postal</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>effectif</t>
         </is>
       </c>
-      <c r="O2" s="16" t="inlineStr">
+      <c r="O2" s="17" t="inlineStr">
         <is>
           <t>chiffre_affaires</t>
         </is>
       </c>
-      <c r="P2" s="16" t="inlineStr">
+      <c r="P2" s="17" t="inlineStr">
         <is>
           <t>annee_ca</t>
         </is>
       </c>
-      <c r="Q2" s="16" t="inlineStr">
+      <c r="Q2" s="17" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="R2" s="17" t="inlineStr">
+      <c r="R2" s="18" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="S2" s="17" t="inlineStr">
+      <c r="S2" s="18" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="T2" s="17" t="inlineStr">
+      <c r="T2" s="18" t="inlineStr">
         <is>
           <t>site_web</t>
         </is>
       </c>
-      <c r="U2" s="17" t="inlineStr">
+      <c r="U2" s="18" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="V2" s="18" t="inlineStr">
+      <c r="V2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_nom</t>
         </is>
       </c>
-      <c r="W2" s="18" t="inlineStr">
+      <c r="W2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_prenom</t>
         </is>
       </c>
-      <c r="X2" s="18" t="inlineStr">
+      <c r="X2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_poste</t>
         </is>
       </c>
-      <c r="Y2" s="18" t="inlineStr">
+      <c r="Y2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_adresse</t>
         </is>
       </c>
-      <c r="Z2" s="18" t="inlineStr">
+      <c r="Z2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_code_postal</t>
         </is>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
+      <c r="AA2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_ville</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>929975167</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>92997516700016</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Amb</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Amb</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>24/05/2024</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>8 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr"/>
-      <c r="P3" s="19" t="inlineStr"/>
-      <c r="Q3" s="19" t="inlineStr"/>
-      <c r="R3" s="19" t="inlineStr"/>
-      <c r="S3" s="20" t="inlineStr"/>
-      <c r="T3" s="19" t="inlineStr"/>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr"/>
+      <c r="P3" s="20" t="inlineStr"/>
+      <c r="Q3" s="20" t="inlineStr"/>
+      <c r="R3" s="20" t="inlineStr"/>
+      <c r="S3" s="21" t="inlineStr"/>
+      <c r="T3" s="20" t="inlineStr"/>
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V3" s="19" t="inlineStr">
+      <c r="V3" s="20" t="inlineStr">
         <is>
           <t>BERTOLONI</t>
         </is>
       </c>
-      <c r="W3" s="19" t="inlineStr">
+      <c r="W3" s="20" t="inlineStr">
         <is>
           <t>Mathieu</t>
         </is>
       </c>
-      <c r="X3" s="19" t="inlineStr">
+      <c r="X3" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y3" s="19" t="inlineStr">
+      <c r="Y3" s="20" t="inlineStr">
         <is>
           <t>2 rue de tanière</t>
         </is>
       </c>
-      <c r="Z3" s="20" t="inlineStr">
+      <c r="Z3" s="21" t="inlineStr">
         <is>
           <t>57680</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr">
+      <c r="AA3" s="20" t="inlineStr">
         <is>
           <t>Corny-sur-Moselle</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>993479617</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>99347961700017</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>HOPESUN</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>HOPESUN</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>30/10/2025</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K4" s="19" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>2 RUE HENRY MARET</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M4" s="19" t="inlineStr">
+      <c r="M4" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N4" s="19" t="inlineStr">
+      <c r="N4" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O4" s="19" t="inlineStr"/>
-      <c r="P4" s="19" t="inlineStr"/>
-      <c r="Q4" s="19" t="inlineStr"/>
-      <c r="R4" s="19" t="inlineStr"/>
-      <c r="S4" s="20" t="inlineStr"/>
-      <c r="T4" s="19" t="inlineStr"/>
-      <c r="U4" s="19" t="inlineStr">
+      <c r="O4" s="20" t="inlineStr"/>
+      <c r="P4" s="20" t="inlineStr"/>
+      <c r="Q4" s="20" t="inlineStr"/>
+      <c r="R4" s="20" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr"/>
+      <c r="T4" s="20" t="inlineStr"/>
+      <c r="U4" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V4" s="19" t="inlineStr">
+      <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ZHOU</t>
         </is>
       </c>
-      <c r="W4" s="19" t="inlineStr">
+      <c r="W4" s="20" t="inlineStr">
         <is>
           <t>Jianmin</t>
         </is>
       </c>
-      <c r="X4" s="19" t="inlineStr">
+      <c r="X4" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y4" s="19" t="inlineStr">
+      <c r="Y4" s="20" t="inlineStr">
         <is>
           <t>20 bis avenue robert schuman</t>
         </is>
       </c>
-      <c r="Z4" s="20" t="inlineStr">
+      <c r="Z4" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA4" s="19" t="inlineStr">
+      <c r="AA4" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>799964572</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>79996457200017</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>LA FABRIQUE</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>LA FABRIQUE</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>01/02/2014</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>11 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O5" s="19" t="n">
-        <v>61910</v>
-      </c>
-      <c r="P5" s="19" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q5" s="19" t="n">
-        <v>-644</v>
-      </c>
-      <c r="R5" s="19" t="inlineStr"/>
-      <c r="S5" s="20" t="inlineStr"/>
-      <c r="T5" s="19" t="inlineStr"/>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>61910</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
+        <is>
+          <t>-644</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr"/>
+      <c r="S5" s="21" t="inlineStr"/>
+      <c r="T5" s="20" t="inlineStr"/>
+      <c r="U5" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V5" s="19" t="inlineStr">
+      <c r="V5" s="20" t="inlineStr">
         <is>
           <t>MAROUF</t>
         </is>
       </c>
-      <c r="W5" s="19" t="inlineStr">
+      <c r="W5" s="20" t="inlineStr">
         <is>
           <t>Mitra</t>
         </is>
       </c>
-      <c r="X5" s="19" t="inlineStr">
+      <c r="X5" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y5" s="19" t="inlineStr">
+      <c r="Y5" s="20" t="inlineStr">
         <is>
           <t>Cité Universitaire du Saulcy</t>
         </is>
       </c>
-      <c r="Z5" s="20" t="inlineStr">
+      <c r="Z5" s="21" t="inlineStr">
         <is>
           <t>57010</t>
         </is>
       </c>
-      <c r="AA5" s="19" t="inlineStr">
+      <c r="AA5" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>518661715</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>51866171500012</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>O PARADIS ETHIOPIEN</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>O PARADIS ETHIOPIEN</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>07/12/2009</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="K6" s="19" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>14 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N6" s="19" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O6" s="19" t="n">
-        <v>17498</v>
-      </c>
-      <c r="P6" s="19" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Q6" s="19" t="n">
-        <v>13528</v>
-      </c>
-      <c r="R6" s="19" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="19" t="inlineStr"/>
-      <c r="U6" s="19" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>17498</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q6" s="20" t="inlineStr">
+        <is>
+          <t>13528</t>
+        </is>
+      </c>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="21" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V6" s="19" t="inlineStr">
+      <c r="V6" s="20" t="inlineStr">
         <is>
           <t>ABEBE NEGA</t>
         </is>
       </c>
-      <c r="W6" s="19" t="inlineStr">
+      <c r="W6" s="20" t="inlineStr">
         <is>
           <t>Genet</t>
         </is>
       </c>
-      <c r="X6" s="19" t="inlineStr">
+      <c r="X6" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y6" s="19" t="inlineStr">
+      <c r="Y6" s="20" t="inlineStr">
         <is>
           <t>48 rue Sente à My</t>
         </is>
       </c>
-      <c r="Z6" s="20" t="inlineStr">
+      <c r="Z6" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA6" s="19" t="inlineStr">
+      <c r="AA6" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>490402641</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>49040264100024</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>SARL CARISSIMI PIZZA</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>SARL CARISSIMI PIZZA</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>01/06/2006</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>72 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N7" s="19" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O7" s="19" t="inlineStr"/>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="19" t="inlineStr"/>
-      <c r="R7" s="19" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="19" t="inlineStr"/>
-      <c r="U7" s="19" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="21" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V7" s="19" t="inlineStr">
+      <c r="V7" s="20" t="inlineStr">
         <is>
           <t>SAVIO</t>
         </is>
       </c>
-      <c r="W7" s="19" t="inlineStr">
+      <c r="W7" s="20" t="inlineStr">
         <is>
           <t>Rosa</t>
         </is>
       </c>
-      <c r="X7" s="19" t="inlineStr">
+      <c r="X7" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y7" s="19" t="inlineStr">
+      <c r="Y7" s="20" t="inlineStr">
         <is>
           <t>6 rue de Brest</t>
         </is>
       </c>
-      <c r="Z7" s="20" t="inlineStr">
+      <c r="Z7" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="AA7" s="19" t="inlineStr">
+      <c r="AA7" s="20" t="inlineStr">
         <is>
           <t>Woippy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>850708405</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>85070840500012</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>STAGNA57</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>STAGNA57</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>13/05/2019</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K8" s="19" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>5 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M8" s="19" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N8" s="19" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O8" s="19" t="inlineStr"/>
-      <c r="P8" s="19" t="inlineStr"/>
-      <c r="Q8" s="19" t="inlineStr"/>
-      <c r="R8" s="19" t="inlineStr"/>
-      <c r="S8" s="20" t="inlineStr"/>
-      <c r="T8" s="19" t="inlineStr"/>
-      <c r="U8" s="19" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="21" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V8" s="19" t="inlineStr">
+      <c r="V8" s="20" t="inlineStr">
         <is>
           <t>KOLOGRECKI</t>
         </is>
       </c>
-      <c r="W8" s="19" t="inlineStr">
+      <c r="W8" s="20" t="inlineStr">
         <is>
           <t>Steve, Jean, Baptiste, Sylvain</t>
         </is>
       </c>
-      <c r="X8" s="19" t="inlineStr">
+      <c r="X8" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y8" s="19" t="inlineStr">
+      <c r="Y8" s="20" t="inlineStr">
         <is>
           <t>19 rue du Grand Wad</t>
         </is>
       </c>
-      <c r="Z8" s="20" t="inlineStr">
+      <c r="Z8" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA8" s="19" t="inlineStr">
+      <c r="AA8" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>848508156</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>84850815600025</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>RIZO</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>RIZO</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>19/02/2019</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>7 RUE LAFAYETTE</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N9" s="19" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O9" s="19" t="inlineStr"/>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="19" t="inlineStr"/>
-      <c r="R9" s="19" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="19" t="inlineStr"/>
-      <c r="U9" s="19" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="21" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V9" s="19" t="inlineStr">
+      <c r="V9" s="20" t="inlineStr">
         <is>
           <t>SCHIPANI</t>
         </is>
       </c>
-      <c r="W9" s="19" t="inlineStr">
+      <c r="W9" s="20" t="inlineStr">
         <is>
           <t>Ricky, Giuseppe, Dominique</t>
         </is>
       </c>
-      <c r="X9" s="19" t="inlineStr">
+      <c r="X9" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y9" s="19" t="inlineStr">
+      <c r="Y9" s="20" t="inlineStr">
         <is>
           <t>23 rue d'Auché</t>
         </is>
       </c>
-      <c r="Z9" s="20" t="inlineStr">
+      <c r="Z9" s="21" t="inlineStr">
         <is>
           <t>57680</t>
         </is>
       </c>
-      <c r="AA9" s="19" t="inlineStr">
+      <c r="AA9" s="20" t="inlineStr">
         <is>
           <t>Corny-sur-Moselle</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>940159940</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>94015994000011</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>BS COMPAGNIE</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>BS COMPAGNIE</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>01/12/2024</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>3 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L10" s="19" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N10" s="19" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O10" s="19" t="inlineStr"/>
-      <c r="P10" s="19" t="inlineStr"/>
-      <c r="Q10" s="19" t="inlineStr"/>
-      <c r="R10" s="19" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="19" t="inlineStr"/>
-      <c r="U10" s="19" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="21" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V10" s="19" t="inlineStr">
+      <c r="V10" s="20" t="inlineStr">
         <is>
           <t>BENAOUICHA</t>
         </is>
       </c>
-      <c r="W10" s="19" t="inlineStr">
+      <c r="W10" s="20" t="inlineStr">
         <is>
           <t>Samir</t>
         </is>
       </c>
-      <c r="X10" s="19" t="inlineStr">
+      <c r="X10" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y10" s="19" t="inlineStr">
+      <c r="Y10" s="20" t="inlineStr">
         <is>
           <t>25 rue marc seguin</t>
         </is>
       </c>
-      <c r="Z10" s="20" t="inlineStr">
+      <c r="Z10" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA10" s="19" t="inlineStr">
+      <c r="AA10" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>819532219</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>81953221900022</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>AUX GLACES DE LA FERME</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>AUX GLACES DE LA FERME</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>30/03/2016</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K11" s="19" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>20 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N11" s="19" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O11" s="19" t="inlineStr"/>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="19" t="inlineStr"/>
-      <c r="R11" s="19" t="inlineStr"/>
-      <c r="S11" s="20" t="inlineStr"/>
-      <c r="T11" s="19" t="inlineStr"/>
-      <c r="U11" s="19" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="21" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V11" s="19" t="inlineStr">
+      <c r="V11" s="20" t="inlineStr">
         <is>
           <t>HORY</t>
         </is>
       </c>
-      <c r="W11" s="19" t="inlineStr">
+      <c r="W11" s="20" t="inlineStr">
         <is>
           <t>Vincent, Roland</t>
         </is>
       </c>
-      <c r="X11" s="19" t="inlineStr">
+      <c r="X11" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y11" s="19" t="inlineStr">
+      <c r="Y11" s="20" t="inlineStr">
         <is>
           <t>75 rue Principale</t>
         </is>
       </c>
-      <c r="Z11" s="20" t="inlineStr">
+      <c r="Z11" s="21" t="inlineStr">
         <is>
           <t>57580</t>
         </is>
       </c>
-      <c r="AA11" s="19" t="inlineStr">
+      <c r="AA11" s="20" t="inlineStr">
         <is>
           <t>Vittoncourt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>905387262</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>90538726200025</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>VERDURA CATHEDRALE</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>VERDURA CATHEDRALE</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>18/09/2021</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K12" s="19" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>7 PLACE JEAN-PAUL II</t>
         </is>
       </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N12" s="19" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O12" s="19" t="inlineStr"/>
-      <c r="P12" s="19" t="inlineStr"/>
-      <c r="Q12" s="19" t="inlineStr"/>
-      <c r="R12" s="19" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="19" t="inlineStr"/>
-      <c r="U12" s="19" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="21" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V12" s="19" t="inlineStr">
+      <c r="V12" s="20" t="inlineStr">
         <is>
           <t>MINET</t>
         </is>
       </c>
-      <c r="W12" s="19" t="inlineStr">
+      <c r="W12" s="20" t="inlineStr">
         <is>
           <t>Stéphanie, Cécile</t>
         </is>
       </c>
-      <c r="X12" s="19" t="inlineStr">
+      <c r="X12" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y12" s="19" t="inlineStr">
+      <c r="Y12" s="20" t="inlineStr">
         <is>
           <t>16 Allée du Fort</t>
         </is>
       </c>
-      <c r="Z12" s="20" t="inlineStr">
+      <c r="Z12" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA12" s="19" t="inlineStr">
+      <c r="AA12" s="20" t="inlineStr">
         <is>
           <t>Saint-Julien-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>928441047</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>92844104700018</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>ARLANMETZ</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>ARLANMETZ</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>03/05/2024</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K13" s="19" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>26 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O13" s="19" t="inlineStr"/>
-      <c r="P13" s="19" t="inlineStr"/>
-      <c r="Q13" s="19" t="inlineStr"/>
-      <c r="R13" s="19" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="19" t="inlineStr"/>
-      <c r="U13" s="19" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="21" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V13" s="19" t="inlineStr">
+      <c r="V13" s="20" t="inlineStr">
         <is>
           <t>HUMBERT</t>
         </is>
       </c>
-      <c r="W13" s="19" t="inlineStr">
+      <c r="W13" s="20" t="inlineStr">
         <is>
           <t>Arthur, Victor</t>
         </is>
       </c>
-      <c r="X13" s="19" t="inlineStr">
+      <c r="X13" s="20" t="inlineStr">
         <is>
           <t>Gérant, Associé indéfiniment responsable</t>
         </is>
       </c>
-      <c r="Y13" s="19" t="inlineStr"/>
-      <c r="Z13" s="20" t="inlineStr">
+      <c r="Y13" s="20" t="inlineStr"/>
+      <c r="Z13" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="AA13" s="19" t="inlineStr">
+      <c r="AA13" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>389546284</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>38954628400032</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>SORRENTO</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>SORRENTO</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>19/11/1992</t>
         </is>
       </c>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
       </c>
-      <c r="K14" s="19" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>73 RUE AUX ARENES</t>
         </is>
       </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M14" s="19" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N14" s="19" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O14" s="19" t="n">
-        <v>233394</v>
-      </c>
-      <c r="P14" s="19" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q14" s="19" t="n">
-        <v>-12144</v>
-      </c>
-      <c r="R14" s="19" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
-      <c r="T14" s="19" t="inlineStr"/>
-      <c r="U14" s="19" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>233394</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
+        <is>
+          <t>-12144</t>
+        </is>
+      </c>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr"/>
+      <c r="T14" s="20" t="inlineStr"/>
+      <c r="U14" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V14" s="19" t="inlineStr">
+      <c r="V14" s="20" t="inlineStr">
         <is>
           <t>DAVADANT</t>
         </is>
       </c>
-      <c r="W14" s="19" t="inlineStr">
+      <c r="W14" s="20" t="inlineStr">
         <is>
           <t>Serge</t>
         </is>
       </c>
-      <c r="X14" s="19" t="inlineStr">
+      <c r="X14" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y14" s="19" t="inlineStr">
+      <c r="Y14" s="20" t="inlineStr">
         <is>
           <t>1 rue aux Ossons</t>
         </is>
       </c>
-      <c r="Z14" s="20" t="inlineStr">
+      <c r="Z14" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA14" s="19" t="inlineStr">
+      <c r="AA14" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>852655083</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>85265508300016</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C.SULI</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>C.SULI</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K15" s="19" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>30 RUE DU COETLOSQUET</t>
         </is>
       </c>
-      <c r="L15" s="19" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N15" s="19" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr"/>
-      <c r="P15" s="19" t="inlineStr"/>
-      <c r="Q15" s="19" t="inlineStr"/>
-      <c r="R15" s="19" t="inlineStr"/>
-      <c r="S15" s="20" t="inlineStr"/>
-      <c r="T15" s="19" t="inlineStr"/>
-      <c r="U15" s="19" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr"/>
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr"/>
+      <c r="T15" s="20" t="inlineStr"/>
+      <c r="U15" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V15" s="19" t="inlineStr">
+      <c r="V15" s="20" t="inlineStr">
         <is>
           <t>CHEN</t>
         </is>
       </c>
-      <c r="W15" s="19" t="inlineStr">
+      <c r="W15" s="20" t="inlineStr">
         <is>
           <t>Suli</t>
         </is>
       </c>
-      <c r="X15" s="19" t="inlineStr">
+      <c r="X15" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y15" s="19" t="inlineStr">
+      <c r="Y15" s="20" t="inlineStr">
         <is>
           <t>34 rue du Coetlosquet</t>
         </is>
       </c>
-      <c r="Z15" s="20" t="inlineStr">
+      <c r="Z15" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA15" s="19" t="inlineStr">
+      <c r="AA15" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>322398173</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>32239817300029</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>SODIPARE SOCIETE DE DIFFUSION DE PRODUITS ALIMENTAIRES ET RESTAURATION</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>SODIPARE SOCIETE DE DIFFUSION DE PRODUITS ALIMENTAIRES ET RESTAURATION</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>SA à conseil d'administration (s.a.i.)</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>01/09/1981</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>14 RUE MARGUERITE PUHL-DEMANGE</t>
         </is>
       </c>
-      <c r="L16" s="19" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M16" s="19" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N16" s="19" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O16" s="19" t="inlineStr"/>
-      <c r="P16" s="19" t="inlineStr"/>
-      <c r="Q16" s="19" t="inlineStr"/>
-      <c r="R16" s="19" t="inlineStr"/>
-      <c r="S16" s="20" t="inlineStr"/>
-      <c r="T16" s="19" t="inlineStr"/>
-      <c r="U16" s="19" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr"/>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr"/>
+      <c r="T16" s="20" t="inlineStr"/>
+      <c r="U16" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V16" s="19" t="inlineStr">
+      <c r="V16" s="20" t="inlineStr">
         <is>
           <t>COULBAUX</t>
         </is>
       </c>
-      <c r="W16" s="19" t="inlineStr">
+      <c r="W16" s="20" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
-      <c r="X16" s="19" t="inlineStr">
+      <c r="X16" s="20" t="inlineStr">
         <is>
           <t>Liquidateur</t>
         </is>
       </c>
-      <c r="Y16" s="19" t="inlineStr">
+      <c r="Y16" s="20" t="inlineStr">
         <is>
           <t>8 RUE DE VILLIERS</t>
         </is>
       </c>
-      <c r="Z16" s="20" t="inlineStr">
+      <c r="Z16" s="21" t="inlineStr">
         <is>
           <t>78710</t>
         </is>
       </c>
-      <c r="AA16" s="19" t="inlineStr">
+      <c r="AA16" s="20" t="inlineStr">
         <is>
           <t>ROSNY SUR SEINE</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>392789632</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>39278963200016</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>L'ITALIANO</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>L'ITALIANO</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>01/10/1993</t>
         </is>
       </c>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="K17" s="19" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>16 PLACE ALEXANDRE MONPEURT</t>
         </is>
       </c>
-      <c r="L17" s="19" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M17" s="19" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N17" s="19" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O17" s="19" t="inlineStr"/>
-      <c r="P17" s="19" t="inlineStr"/>
-      <c r="Q17" s="19" t="inlineStr"/>
-      <c r="R17" s="19" t="inlineStr"/>
-      <c r="S17" s="20" t="inlineStr"/>
-      <c r="T17" s="19" t="inlineStr"/>
-      <c r="U17" s="19" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr"/>
+      <c r="P17" s="20" t="inlineStr"/>
+      <c r="Q17" s="20" t="inlineStr"/>
+      <c r="R17" s="20" t="inlineStr"/>
+      <c r="S17" s="21" t="inlineStr"/>
+      <c r="T17" s="20" t="inlineStr"/>
+      <c r="U17" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V17" s="19" t="inlineStr">
+      <c r="V17" s="20" t="inlineStr">
         <is>
           <t>ZANETTI</t>
         </is>
       </c>
-      <c r="W17" s="19" t="inlineStr">
+      <c r="W17" s="20" t="inlineStr">
         <is>
           <t>Michele</t>
         </is>
       </c>
-      <c r="X17" s="19" t="inlineStr">
+      <c r="X17" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y17" s="19" t="inlineStr">
+      <c r="Y17" s="20" t="inlineStr">
         <is>
           <t>29 rue de la Source</t>
         </is>
       </c>
-      <c r="Z17" s="20" t="inlineStr">
+      <c r="Z17" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA17" s="19" t="inlineStr">
+      <c r="AA17" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>524897345</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>52489734500020</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>SYRESSENCE BE SYRESSENCE BIEN ETRE</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>SYRESSENCE BIEN ETRE</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>15/09/2010</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>7 RUE DU NEUFBOURG</t>
         </is>
       </c>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N18" s="19" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O18" s="19" t="n">
-        <v>47714</v>
-      </c>
-      <c r="P18" s="19" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q18" s="19" t="n">
-        <v>-2268</v>
-      </c>
-      <c r="R18" s="19" t="inlineStr"/>
-      <c r="S18" s="20" t="inlineStr"/>
-      <c r="T18" s="19" t="inlineStr"/>
-      <c r="U18" s="19" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
+        <is>
+          <t>47714</t>
+        </is>
+      </c>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q18" s="20" t="inlineStr">
+        <is>
+          <t>-2268</t>
+        </is>
+      </c>
+      <c r="R18" s="20" t="inlineStr"/>
+      <c r="S18" s="21" t="inlineStr"/>
+      <c r="T18" s="20" t="inlineStr"/>
+      <c r="U18" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V18" s="19" t="inlineStr">
+      <c r="V18" s="20" t="inlineStr">
         <is>
           <t>AL- ATRASH</t>
         </is>
       </c>
-      <c r="W18" s="19" t="inlineStr">
+      <c r="W18" s="20" t="inlineStr">
         <is>
           <t>Abel</t>
         </is>
       </c>
-      <c r="X18" s="19" t="inlineStr">
+      <c r="X18" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y18" s="19" t="inlineStr">
+      <c r="Y18" s="20" t="inlineStr">
         <is>
           <t>67 rue de Neuves Maisons</t>
         </is>
       </c>
-      <c r="Z18" s="20" t="inlineStr">
+      <c r="Z18" s="21" t="inlineStr">
         <is>
           <t>54230</t>
         </is>
       </c>
-      <c r="AA18" s="19" t="inlineStr">
+      <c r="AA18" s="20" t="inlineStr">
         <is>
           <t>Chavigny</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>980862981</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>98086298100019</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>NOUVELLE ERE</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>NOUVELLE ERE</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>24/10/2023</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>3 RUE CHARLES PETRE</t>
         </is>
       </c>
-      <c r="L19" s="19" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M19" s="19" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N19" s="19" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr"/>
-      <c r="P19" s="19" t="inlineStr"/>
-      <c r="Q19" s="19" t="inlineStr"/>
-      <c r="R19" s="19" t="inlineStr"/>
-      <c r="S19" s="20" t="inlineStr"/>
-      <c r="T19" s="19" t="inlineStr"/>
-      <c r="U19" s="19" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr"/>
+      <c r="P19" s="20" t="inlineStr"/>
+      <c r="Q19" s="20" t="inlineStr"/>
+      <c r="R19" s="20" t="inlineStr"/>
+      <c r="S19" s="21" t="inlineStr"/>
+      <c r="T19" s="20" t="inlineStr"/>
+      <c r="U19" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V19" s="19" t="inlineStr">
+      <c r="V19" s="20" t="inlineStr">
         <is>
           <t>BERLOGER</t>
         </is>
       </c>
-      <c r="W19" s="19" t="inlineStr">
+      <c r="W19" s="20" t="inlineStr">
         <is>
           <t>Yoan</t>
         </is>
       </c>
-      <c r="X19" s="19" t="inlineStr">
+      <c r="X19" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y19" s="19" t="inlineStr"/>
-      <c r="Z19" s="20" t="inlineStr">
+      <c r="Y19" s="20" t="inlineStr"/>
+      <c r="Z19" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA19" s="19" t="inlineStr">
+      <c r="AA19" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>479579070</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>47957907000018</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>HERAVI</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>HERAVI</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>22/11/2004</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>12 RUE DES ROCHES</t>
         </is>
       </c>
-      <c r="L20" s="19" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M20" s="19" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N20" s="19" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O20" s="19" t="inlineStr"/>
-      <c r="P20" s="19" t="inlineStr"/>
-      <c r="Q20" s="19" t="inlineStr"/>
-      <c r="R20" s="19" t="inlineStr"/>
-      <c r="S20" s="20" t="inlineStr"/>
-      <c r="T20" s="19" t="inlineStr"/>
-      <c r="U20" s="19" t="inlineStr">
+      <c r="O20" s="20" t="inlineStr"/>
+      <c r="P20" s="20" t="inlineStr"/>
+      <c r="Q20" s="20" t="inlineStr"/>
+      <c r="R20" s="20" t="inlineStr"/>
+      <c r="S20" s="21" t="inlineStr"/>
+      <c r="T20" s="20" t="inlineStr"/>
+      <c r="U20" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V20" s="19" t="inlineStr">
+      <c r="V20" s="20" t="inlineStr">
         <is>
           <t>HERTZOG</t>
         </is>
       </c>
-      <c r="W20" s="19" t="inlineStr">
+      <c r="W20" s="20" t="inlineStr">
         <is>
           <t>Gerald</t>
         </is>
       </c>
-      <c r="X20" s="19" t="inlineStr">
+      <c r="X20" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y20" s="19" t="inlineStr">
+      <c r="Y20" s="20" t="inlineStr">
         <is>
           <t>19 rue des Pépinières</t>
         </is>
       </c>
-      <c r="Z20" s="20" t="inlineStr">
+      <c r="Z20" s="21" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="AA20" s="19" t="inlineStr">
+      <c r="AA20" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>401299417</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>40129941700014</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>SARL KASSAN</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>SARL KASSAN</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>28/11/1994</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>3 RUE CHARLES PETRE</t>
         </is>
       </c>
-      <c r="L21" s="19" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N21" s="19" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O21" s="19" t="inlineStr"/>
-      <c r="P21" s="19" t="inlineStr"/>
-      <c r="Q21" s="19" t="inlineStr"/>
-      <c r="R21" s="19" t="inlineStr"/>
-      <c r="S21" s="20" t="inlineStr"/>
-      <c r="T21" s="19" t="inlineStr"/>
-      <c r="U21" s="19" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr"/>
+      <c r="P21" s="20" t="inlineStr"/>
+      <c r="Q21" s="20" t="inlineStr"/>
+      <c r="R21" s="20" t="inlineStr"/>
+      <c r="S21" s="21" t="inlineStr"/>
+      <c r="T21" s="20" t="inlineStr"/>
+      <c r="U21" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V21" s="19" t="inlineStr"/>
-      <c r="W21" s="19" t="inlineStr"/>
-      <c r="X21" s="19" t="inlineStr"/>
-      <c r="Y21" s="19" t="inlineStr"/>
-      <c r="Z21" s="20" t="inlineStr"/>
-      <c r="AA21" s="19" t="inlineStr"/>
+      <c r="V21" s="20" t="inlineStr"/>
+      <c r="W21" s="20" t="inlineStr"/>
+      <c r="X21" s="20" t="inlineStr"/>
+      <c r="Y21" s="20" t="inlineStr"/>
+      <c r="Z21" s="21" t="inlineStr"/>
+      <c r="AA21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>843893066</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>84389306600012</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>SUSHI SOLEIL</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>SUSHI SOLEIL</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>15/11/2018</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>4 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L22" s="19" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N22" s="19" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr"/>
-      <c r="P22" s="19" t="inlineStr"/>
-      <c r="Q22" s="19" t="inlineStr"/>
-      <c r="R22" s="19" t="inlineStr"/>
-      <c r="S22" s="20" t="inlineStr"/>
-      <c r="T22" s="19" t="inlineStr"/>
-      <c r="U22" s="19" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr"/>
+      <c r="P22" s="20" t="inlineStr"/>
+      <c r="Q22" s="20" t="inlineStr"/>
+      <c r="R22" s="20" t="inlineStr"/>
+      <c r="S22" s="21" t="inlineStr"/>
+      <c r="T22" s="20" t="inlineStr"/>
+      <c r="U22" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V22" s="19" t="inlineStr">
+      <c r="V22" s="20" t="inlineStr">
         <is>
           <t>HUANG</t>
         </is>
       </c>
-      <c r="W22" s="19" t="inlineStr">
+      <c r="W22" s="20" t="inlineStr">
         <is>
           <t>Aizhen</t>
         </is>
       </c>
-      <c r="X22" s="19" t="inlineStr">
+      <c r="X22" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y22" s="19" t="inlineStr">
+      <c r="Y22" s="20" t="inlineStr">
         <is>
           <t>8 avenue Karl Marx</t>
         </is>
       </c>
-      <c r="Z22" s="20" t="inlineStr">
+      <c r="Z22" s="21" t="inlineStr">
         <is>
           <t>93000</t>
         </is>
       </c>
-      <c r="AA22" s="19" t="inlineStr">
+      <c r="AA22" s="20" t="inlineStr">
         <is>
           <t>Bobigny</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>835303769</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>83530376900011</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>RHS 50</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>RHS 50</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>09/02/2018</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>50 RUE HAUTE SEILLE</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr"/>
+      <c r="P23" s="22" t="inlineStr"/>
+      <c r="Q23" s="22" t="inlineStr"/>
+      <c r="R23" s="22" t="inlineStr"/>
+      <c r="S23" s="23" t="inlineStr"/>
+      <c r="T23" s="22" t="inlineStr"/>
+      <c r="U23" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V23" s="22" t="inlineStr">
+        <is>
+          <t>BEAUX</t>
+        </is>
+      </c>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>Bernard, Francois</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y23" s="22" t="inlineStr">
+        <is>
+          <t>2, rue du Stade</t>
+        </is>
+      </c>
+      <c r="Z23" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="AA23" s="22" t="inlineStr">
+        <is>
+          <t>Longeville-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>834808651</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>83480865100014</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>LINE SUSHI METZ</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>LINE SUSHI METZ</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>27/11/2017</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr"/>
+      <c r="P24" s="22" t="inlineStr"/>
+      <c r="Q24" s="22" t="inlineStr"/>
+      <c r="R24" s="22" t="inlineStr"/>
+      <c r="S24" s="23" t="inlineStr"/>
+      <c r="T24" s="22" t="inlineStr"/>
+      <c r="U24" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V24" s="22" t="inlineStr">
+        <is>
+          <t>LIAO</t>
+        </is>
+      </c>
+      <c r="W24" s="22" t="inlineStr">
+        <is>
+          <t>Xuemei</t>
+        </is>
+      </c>
+      <c r="X24" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y24" s="22" t="inlineStr">
+        <is>
+          <t>29 rue Aristide Briand Chez Mme Bu Jiangli</t>
+        </is>
+      </c>
+      <c r="Z24" s="23" t="inlineStr">
+        <is>
+          <t>54510</t>
+        </is>
+      </c>
+      <c r="AA24" s="22" t="inlineStr">
+        <is>
+          <t>Tomblaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>492309059</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>49230905900011</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>EURL PHAM</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>EURL PHAM</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>11/11/2006</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>32 RUE DU COETLOSQUET</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O25" s="22" t="inlineStr"/>
+      <c r="P25" s="22" t="inlineStr"/>
+      <c r="Q25" s="22" t="inlineStr"/>
+      <c r="R25" s="22" t="inlineStr"/>
+      <c r="S25" s="23" t="inlineStr"/>
+      <c r="T25" s="22" t="inlineStr"/>
+      <c r="U25" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V25" s="22" t="inlineStr">
+        <is>
+          <t>THAMMAVONG</t>
+        </is>
+      </c>
+      <c r="W25" s="22" t="inlineStr">
+        <is>
+          <t>Bounlay</t>
+        </is>
+      </c>
+      <c r="X25" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y25" s="22" t="inlineStr">
+        <is>
+          <t>15 rue Virginie du Verger</t>
+        </is>
+      </c>
+      <c r="Z25" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA25" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>920324530</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>92032453000012</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>BATIGNOLLES INVEST</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>BATIGNOLLES INVEST</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>13/10/2022</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE WINSTON CHURCHILL</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr"/>
+      <c r="P26" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>162363</v>
+      </c>
+      <c r="R26" s="22" t="inlineStr"/>
+      <c r="S26" s="23" t="inlineStr"/>
+      <c r="T26" s="22" t="inlineStr"/>
+      <c r="U26" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V26" s="22" t="inlineStr">
+        <is>
+          <t>MICHEL</t>
+        </is>
+      </c>
+      <c r="W26" s="22" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="X26" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y26" s="22" t="inlineStr">
+        <is>
+          <t>2 Rue des Marronniers</t>
+        </is>
+      </c>
+      <c r="Z26" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA26" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>853118255</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>85311825500027</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>CLOE</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>CLOE</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>12/08/2019</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>3 AVENUE DE LATTRE DE TASSIGNY</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="inlineStr"/>
+      <c r="P27" s="22" t="inlineStr"/>
+      <c r="Q27" s="22" t="inlineStr"/>
+      <c r="R27" s="22" t="inlineStr"/>
+      <c r="S27" s="23" t="inlineStr"/>
+      <c r="T27" s="22" t="inlineStr"/>
+      <c r="U27" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V27" s="22" t="inlineStr">
+        <is>
+          <t>SIDOT</t>
+        </is>
+      </c>
+      <c r="W27" s="22" t="inlineStr">
+        <is>
+          <t>Clément, Victor</t>
+        </is>
+      </c>
+      <c r="X27" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y27" s="22" t="inlineStr">
+        <is>
+          <t>1 rue André Malraux</t>
+        </is>
+      </c>
+      <c r="Z27" s="23" t="inlineStr">
+        <is>
+          <t>57155</t>
+        </is>
+      </c>
+      <c r="AA27" s="22" t="inlineStr">
+        <is>
+          <t>Marly</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AA22"/>
+  <autoFilter ref="A2:AA27"/>
   <mergeCells count="6">
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="R1:U1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$AA$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$AA$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3085,576 +3085,2850 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>835303769</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>83530376900011</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>RHS 50</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>RHS 50</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>09/02/2018</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>50 RUE HAUTE SEILLE</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N23" s="22" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O23" s="22" t="inlineStr"/>
-      <c r="P23" s="22" t="inlineStr"/>
-      <c r="Q23" s="22" t="inlineStr"/>
-      <c r="R23" s="22" t="inlineStr"/>
-      <c r="S23" s="23" t="inlineStr"/>
-      <c r="T23" s="22" t="inlineStr"/>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr"/>
+      <c r="P23" s="20" t="inlineStr"/>
+      <c r="Q23" s="20" t="inlineStr"/>
+      <c r="R23" s="20" t="inlineStr"/>
+      <c r="S23" s="21" t="inlineStr"/>
+      <c r="T23" s="20" t="inlineStr"/>
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V23" s="22" t="inlineStr">
+      <c r="V23" s="20" t="inlineStr">
         <is>
           <t>BEAUX</t>
         </is>
       </c>
-      <c r="W23" s="22" t="inlineStr">
+      <c r="W23" s="20" t="inlineStr">
         <is>
           <t>Bernard, Francois</t>
         </is>
       </c>
-      <c r="X23" s="22" t="inlineStr">
+      <c r="X23" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y23" s="22" t="inlineStr">
+      <c r="Y23" s="20" t="inlineStr">
         <is>
           <t>2, rue du Stade</t>
         </is>
       </c>
-      <c r="Z23" s="23" t="inlineStr">
+      <c r="Z23" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="AA23" s="22" t="inlineStr">
+      <c r="AA23" s="20" t="inlineStr">
         <is>
           <t>Longeville-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>834808651</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>83480865100014</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>LINE SUSHI METZ</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>LINE SUSHI METZ</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>27/11/2017</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>1 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N24" s="22" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O24" s="22" t="inlineStr"/>
-      <c r="P24" s="22" t="inlineStr"/>
-      <c r="Q24" s="22" t="inlineStr"/>
-      <c r="R24" s="22" t="inlineStr"/>
-      <c r="S24" s="23" t="inlineStr"/>
-      <c r="T24" s="22" t="inlineStr"/>
-      <c r="U24" s="22" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr"/>
+      <c r="P24" s="20" t="inlineStr"/>
+      <c r="Q24" s="20" t="inlineStr"/>
+      <c r="R24" s="20" t="inlineStr"/>
+      <c r="S24" s="21" t="inlineStr"/>
+      <c r="T24" s="20" t="inlineStr"/>
+      <c r="U24" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V24" s="22" t="inlineStr">
+      <c r="V24" s="20" t="inlineStr">
         <is>
           <t>LIAO</t>
         </is>
       </c>
-      <c r="W24" s="22" t="inlineStr">
+      <c r="W24" s="20" t="inlineStr">
         <is>
           <t>Xuemei</t>
         </is>
       </c>
-      <c r="X24" s="22" t="inlineStr">
+      <c r="X24" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y24" s="22" t="inlineStr">
+      <c r="Y24" s="20" t="inlineStr">
         <is>
           <t>29 rue Aristide Briand Chez Mme Bu Jiangli</t>
         </is>
       </c>
-      <c r="Z24" s="23" t="inlineStr">
+      <c r="Z24" s="21" t="inlineStr">
         <is>
           <t>54510</t>
         </is>
       </c>
-      <c r="AA24" s="22" t="inlineStr">
+      <c r="AA24" s="20" t="inlineStr">
         <is>
           <t>Tomblaine</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>492309059</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>49230905900011</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>EURL PHAM</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>EURL PHAM</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>11/11/2006</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>32 RUE DU COETLOSQUET</t>
         </is>
       </c>
-      <c r="L25" s="22" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N25" s="22" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O25" s="22" t="inlineStr"/>
-      <c r="P25" s="22" t="inlineStr"/>
-      <c r="Q25" s="22" t="inlineStr"/>
-      <c r="R25" s="22" t="inlineStr"/>
-      <c r="S25" s="23" t="inlineStr"/>
-      <c r="T25" s="22" t="inlineStr"/>
-      <c r="U25" s="22" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr"/>
+      <c r="P25" s="20" t="inlineStr"/>
+      <c r="Q25" s="20" t="inlineStr"/>
+      <c r="R25" s="20" t="inlineStr"/>
+      <c r="S25" s="21" t="inlineStr"/>
+      <c r="T25" s="20" t="inlineStr"/>
+      <c r="U25" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V25" s="22" t="inlineStr">
+      <c r="V25" s="20" t="inlineStr">
         <is>
           <t>THAMMAVONG</t>
         </is>
       </c>
-      <c r="W25" s="22" t="inlineStr">
+      <c r="W25" s="20" t="inlineStr">
         <is>
           <t>Bounlay</t>
         </is>
       </c>
-      <c r="X25" s="22" t="inlineStr">
+      <c r="X25" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y25" s="22" t="inlineStr">
+      <c r="Y25" s="20" t="inlineStr">
         <is>
           <t>15 rue Virginie du Verger</t>
         </is>
       </c>
-      <c r="Z25" s="23" t="inlineStr">
+      <c r="Z25" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA25" s="22" t="inlineStr">
+      <c r="AA25" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>920324530</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>92032453000012</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>BATIGNOLLES INVEST</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>BATIGNOLLES INVEST</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>13/10/2022</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>10 RUE WINSTON CHURCHILL</t>
         </is>
       </c>
-      <c r="L26" s="22" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N26" s="22" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O26" s="22" t="inlineStr"/>
-      <c r="P26" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q26" s="22" t="n">
-        <v>162363</v>
-      </c>
-      <c r="R26" s="22" t="inlineStr"/>
-      <c r="S26" s="23" t="inlineStr"/>
-      <c r="T26" s="22" t="inlineStr"/>
-      <c r="U26" s="22" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr"/>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
+        <is>
+          <t>162363</t>
+        </is>
+      </c>
+      <c r="R26" s="20" t="inlineStr"/>
+      <c r="S26" s="21" t="inlineStr"/>
+      <c r="T26" s="20" t="inlineStr"/>
+      <c r="U26" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V26" s="22" t="inlineStr">
+      <c r="V26" s="20" t="inlineStr">
         <is>
           <t>MICHEL</t>
         </is>
       </c>
-      <c r="W26" s="22" t="inlineStr">
+      <c r="W26" s="20" t="inlineStr">
         <is>
           <t>David</t>
         </is>
       </c>
-      <c r="X26" s="22" t="inlineStr">
+      <c r="X26" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y26" s="22" t="inlineStr">
+      <c r="Y26" s="20" t="inlineStr">
         <is>
           <t>2 Rue des Marronniers</t>
         </is>
       </c>
-      <c r="Z26" s="23" t="inlineStr">
+      <c r="Z26" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA26" s="22" t="inlineStr">
+      <c r="AA26" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>853118255</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>85311825500027</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>CLOE</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>CLOE</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>12/08/2019</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>3 AVENUE DE LATTRE DE TASSIGNY</t>
         </is>
       </c>
-      <c r="L27" s="22" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
       </c>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N27" s="22" t="inlineStr">
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O27" s="22" t="inlineStr"/>
-      <c r="P27" s="22" t="inlineStr"/>
-      <c r="Q27" s="22" t="inlineStr"/>
-      <c r="R27" s="22" t="inlineStr"/>
-      <c r="S27" s="23" t="inlineStr"/>
-      <c r="T27" s="22" t="inlineStr"/>
-      <c r="U27" s="22" t="inlineStr">
+      <c r="O27" s="20" t="inlineStr"/>
+      <c r="P27" s="20" t="inlineStr"/>
+      <c r="Q27" s="20" t="inlineStr"/>
+      <c r="R27" s="20" t="inlineStr"/>
+      <c r="S27" s="21" t="inlineStr"/>
+      <c r="T27" s="20" t="inlineStr"/>
+      <c r="U27" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V27" s="22" t="inlineStr">
+      <c r="V27" s="20" t="inlineStr">
         <is>
           <t>SIDOT</t>
         </is>
       </c>
-      <c r="W27" s="22" t="inlineStr">
+      <c r="W27" s="20" t="inlineStr">
         <is>
           <t>Clément, Victor</t>
         </is>
       </c>
-      <c r="X27" s="22" t="inlineStr">
+      <c r="X27" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y27" s="22" t="inlineStr">
+      <c r="Y27" s="20" t="inlineStr">
         <is>
           <t>1 rue André Malraux</t>
         </is>
       </c>
-      <c r="Z27" s="23" t="inlineStr">
+      <c r="Z27" s="21" t="inlineStr">
         <is>
           <t>57155</t>
         </is>
       </c>
-      <c r="AA27" s="22" t="inlineStr">
+      <c r="AA27" s="20" t="inlineStr">
         <is>
           <t>Marly</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>348588617</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>34858861700012</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>LA JONQUE D'OR</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>LA JONQUE D'OR</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>01/11/1988</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>45 EN FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>564988</v>
+      </c>
+      <c r="P28" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>26750</v>
+      </c>
+      <c r="R28" s="22" t="inlineStr"/>
+      <c r="S28" s="23" t="inlineStr"/>
+      <c r="T28" s="22" t="inlineStr"/>
+      <c r="U28" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V28" s="22" t="inlineStr">
+        <is>
+          <t>GAO</t>
+        </is>
+      </c>
+      <c r="W28" s="22" t="inlineStr">
+        <is>
+          <t>Ning</t>
+        </is>
+      </c>
+      <c r="X28" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y28" s="22" t="inlineStr"/>
+      <c r="Z28" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA28" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>848949103</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>84894910300024</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>LES FRERES DE BAKEL</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>LES FRERES DE BAKEL</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>04/03/2019</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE DE L'ABREUVOIR</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M29" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N29" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O29" s="22" t="inlineStr"/>
+      <c r="P29" s="22" t="inlineStr"/>
+      <c r="Q29" s="22" t="inlineStr"/>
+      <c r="R29" s="22" t="inlineStr"/>
+      <c r="S29" s="23" t="inlineStr"/>
+      <c r="T29" s="22" t="inlineStr"/>
+      <c r="U29" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V29" s="22" t="inlineStr">
+        <is>
+          <t>TRAORE</t>
+        </is>
+      </c>
+      <c r="W29" s="22" t="inlineStr">
+        <is>
+          <t>Daumbe</t>
+        </is>
+      </c>
+      <c r="X29" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y29" s="22" t="inlineStr">
+        <is>
+          <t>7 Rue de Peltre</t>
+        </is>
+      </c>
+      <c r="Z29" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA29" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>482693744</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>48269374400013</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>ALPHAM</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>ALPHAM</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>06/06/2005</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>83 RUE MAZELLE</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O30" s="22" t="inlineStr"/>
+      <c r="P30" s="22" t="inlineStr"/>
+      <c r="Q30" s="22" t="inlineStr"/>
+      <c r="R30" s="22" t="inlineStr"/>
+      <c r="S30" s="23" t="inlineStr"/>
+      <c r="T30" s="22" t="inlineStr"/>
+      <c r="U30" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V30" s="22" t="inlineStr">
+        <is>
+          <t>CRISTOFARO</t>
+        </is>
+      </c>
+      <c r="W30" s="22" t="inlineStr">
+        <is>
+          <t>Girolamo</t>
+        </is>
+      </c>
+      <c r="X30" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y30" s="22" t="inlineStr">
+        <is>
+          <t>17 route de Borny</t>
+        </is>
+      </c>
+      <c r="Z30" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA30" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>908199466</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>90819946600024</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>AJFM SAINT LOUIS</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>AJFM SAINT LOUIS</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>14/12/2021</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L31" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M31" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N31" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O31" s="22" t="n">
+        <v>677283</v>
+      </c>
+      <c r="P31" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>-614</v>
+      </c>
+      <c r="R31" s="22" t="inlineStr"/>
+      <c r="S31" s="23" t="inlineStr"/>
+      <c r="T31" s="22" t="inlineStr"/>
+      <c r="U31" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V31" s="22" t="inlineStr">
+        <is>
+          <t>CHR INVEST</t>
+        </is>
+      </c>
+      <c r="W31" s="22" t="inlineStr"/>
+      <c r="X31" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y31" s="22" t="inlineStr">
+        <is>
+          <t>41 Place de la Carrière</t>
+        </is>
+      </c>
+      <c r="Z31" s="23" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="AA31" s="22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>929820710</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>92982071000010</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>CASA FRIDA</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>CASA FRIDA</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>10/07/2024</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>59 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="inlineStr"/>
+      <c r="P32" s="22" t="inlineStr"/>
+      <c r="Q32" s="22" t="inlineStr"/>
+      <c r="R32" s="22" t="inlineStr"/>
+      <c r="S32" s="23" t="inlineStr"/>
+      <c r="T32" s="22" t="inlineStr"/>
+      <c r="U32" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V32" s="22" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="W32" s="22" t="inlineStr">
+        <is>
+          <t>Raimundo, Andres</t>
+        </is>
+      </c>
+      <c r="X32" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y32" s="22" t="inlineStr">
+        <is>
+          <t>68 rue vallières</t>
+        </is>
+      </c>
+      <c r="Z32" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA32" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>793604141</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>79360414100028</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>MONSIEUR JEAN</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>MONSIEUR JEAN</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>12/06/2013</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>23 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N33" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O33" s="22" t="n">
+        <v>582282</v>
+      </c>
+      <c r="P33" s="22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="Q33" s="22" t="n">
+        <v>20308</v>
+      </c>
+      <c r="R33" s="22" t="inlineStr"/>
+      <c r="S33" s="23" t="inlineStr"/>
+      <c r="T33" s="22" t="inlineStr"/>
+      <c r="U33" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V33" s="22" t="inlineStr">
+        <is>
+          <t>PANZA</t>
+        </is>
+      </c>
+      <c r="W33" s="22" t="inlineStr">
+        <is>
+          <t>Jean-pierre</t>
+        </is>
+      </c>
+      <c r="X33" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y33" s="22" t="inlineStr">
+        <is>
+          <t>8 rue des Parmentiers</t>
+        </is>
+      </c>
+      <c r="Z33" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA33" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>881725642</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>88172564200014</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>RIMINI</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>RIMINI</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>13/02/2020</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DE LA PIERRE HARDIE</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="inlineStr"/>
+      <c r="P34" s="22" t="inlineStr"/>
+      <c r="Q34" s="22" t="inlineStr"/>
+      <c r="R34" s="22" t="inlineStr"/>
+      <c r="S34" s="23" t="inlineStr"/>
+      <c r="T34" s="22" t="inlineStr"/>
+      <c r="U34" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V34" s="22" t="inlineStr">
+        <is>
+          <t>PRZYBYLSKI</t>
+        </is>
+      </c>
+      <c r="W34" s="22" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="X34" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y34" s="22" t="inlineStr">
+        <is>
+          <t>13 Rue Georges de la Tour</t>
+        </is>
+      </c>
+      <c r="Z34" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="AA34" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>877808931</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>87780893100019</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>ROYAL BAO</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>ROYAL BAO</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2019</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>24 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N35" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O35" s="22" t="inlineStr"/>
+      <c r="P35" s="22" t="inlineStr"/>
+      <c r="Q35" s="22" t="inlineStr"/>
+      <c r="R35" s="22" t="inlineStr"/>
+      <c r="S35" s="23" t="inlineStr"/>
+      <c r="T35" s="22" t="inlineStr"/>
+      <c r="U35" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V35" s="22" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="W35" s="22" t="inlineStr">
+        <is>
+          <t>Hao</t>
+        </is>
+      </c>
+      <c r="X35" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y35" s="22" t="inlineStr">
+        <is>
+          <t>62 avenue de Fontainebleau</t>
+        </is>
+      </c>
+      <c r="Z35" s="23" t="inlineStr">
+        <is>
+          <t>94270</t>
+        </is>
+      </c>
+      <c r="AA35" s="22" t="inlineStr">
+        <is>
+          <t>Le Kremlin-Bicêtre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>845332154</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>84533215400010</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>15/01/2019</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>34 RUE PASTEUR</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O36" s="22" t="inlineStr"/>
+      <c r="P36" s="22" t="inlineStr"/>
+      <c r="Q36" s="22" t="inlineStr"/>
+      <c r="R36" s="22" t="inlineStr"/>
+      <c r="S36" s="23" t="inlineStr"/>
+      <c r="T36" s="22" t="inlineStr"/>
+      <c r="U36" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V36" s="22" t="inlineStr">
+        <is>
+          <t>SAINOUX</t>
+        </is>
+      </c>
+      <c r="W36" s="22" t="inlineStr">
+        <is>
+          <t>Laurent, Pascal, Eugène</t>
+        </is>
+      </c>
+      <c r="X36" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y36" s="22" t="inlineStr">
+        <is>
+          <t>80 rue du Général de Gaulle</t>
+        </is>
+      </c>
+      <c r="Z36" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="AA36" s="22" t="inlineStr">
+        <is>
+          <t>Longeville-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>483597050</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>48359705000010</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>LA JEEP</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>LA JEEP</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Société en nom collectif</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>02/01/2005</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>3 B RUE VAUBAN</t>
+        </is>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N37" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O37" s="22" t="inlineStr"/>
+      <c r="P37" s="22" t="inlineStr"/>
+      <c r="Q37" s="22" t="inlineStr"/>
+      <c r="R37" s="22" t="inlineStr"/>
+      <c r="S37" s="23" t="inlineStr"/>
+      <c r="T37" s="22" t="inlineStr"/>
+      <c r="U37" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V37" s="22" t="inlineStr">
+        <is>
+          <t>OBRANIAK</t>
+        </is>
+      </c>
+      <c r="W37" s="22" t="inlineStr">
+        <is>
+          <t>Gerard</t>
+        </is>
+      </c>
+      <c r="X37" s="22" t="inlineStr">
+        <is>
+          <t>Gérant, Associé indéfiniment responsable</t>
+        </is>
+      </c>
+      <c r="Y37" s="22" t="inlineStr">
+        <is>
+          <t>13 rue de la Carochiere</t>
+        </is>
+      </c>
+      <c r="Z37" s="23" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="AA37" s="22" t="inlineStr">
+        <is>
+          <t>Pange</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>435082797</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>43508279700018</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>ISLAMABAD</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>ISLAMABAD</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>09/03/2001</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>92 RUE DU XXEME CORPS AMERICAIN</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O38" s="22" t="n">
+        <v>145217</v>
+      </c>
+      <c r="P38" s="22" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Q38" s="22" t="n">
+        <v>19490</v>
+      </c>
+      <c r="R38" s="22" t="inlineStr"/>
+      <c r="S38" s="23" t="inlineStr"/>
+      <c r="T38" s="22" t="inlineStr"/>
+      <c r="U38" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V38" s="22" t="inlineStr">
+        <is>
+          <t>BHATTI</t>
+        </is>
+      </c>
+      <c r="W38" s="22" t="inlineStr">
+        <is>
+          <t>Mohammad, Javed</t>
+        </is>
+      </c>
+      <c r="X38" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y38" s="22" t="inlineStr">
+        <is>
+          <t>9 rue Gauthey</t>
+        </is>
+      </c>
+      <c r="Z38" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="AA38" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>428958516</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>42895851600026</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>L'ASSIETTE DU BISTROT</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>L'ASSIETTE DU BISTROT</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>12/01/2000</t>
+        </is>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M39" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N39" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O39" s="22" t="inlineStr"/>
+      <c r="P39" s="22" t="n">
+        <v>2018</v>
+      </c>
+      <c r="Q39" s="22" t="n">
+        <v>33773</v>
+      </c>
+      <c r="R39" s="22" t="inlineStr"/>
+      <c r="S39" s="23" t="inlineStr"/>
+      <c r="T39" s="22" t="inlineStr"/>
+      <c r="U39" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V39" s="22" t="inlineStr">
+        <is>
+          <t>ENGEL</t>
+        </is>
+      </c>
+      <c r="W39" s="22" t="inlineStr">
+        <is>
+          <t>Gérald</t>
+        </is>
+      </c>
+      <c r="X39" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y39" s="22" t="inlineStr">
+        <is>
+          <t>45 rue de France</t>
+        </is>
+      </c>
+      <c r="Z39" s="23" t="inlineStr">
+        <is>
+          <t>57280</t>
+        </is>
+      </c>
+      <c r="AA39" s="22" t="inlineStr">
+        <is>
+          <t>Maizières-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>908885643</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>90888564300027</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>VILLA PREZIOSA</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>VILLA PREZIOSA</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I40" s="22" t="inlineStr">
+        <is>
+          <t>03/01/2022</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>32 RUE DU COETLOSQUET</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M40" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N40" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O40" s="22" t="inlineStr"/>
+      <c r="P40" s="22" t="inlineStr"/>
+      <c r="Q40" s="22" t="inlineStr"/>
+      <c r="R40" s="22" t="inlineStr"/>
+      <c r="S40" s="23" t="inlineStr"/>
+      <c r="T40" s="22" t="inlineStr"/>
+      <c r="U40" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V40" s="22" t="inlineStr">
+        <is>
+          <t>PREZIOSA</t>
+        </is>
+      </c>
+      <c r="W40" s="22" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="X40" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y40" s="22" t="inlineStr"/>
+      <c r="Z40" s="23" t="inlineStr">
+        <is>
+          <t>57180</t>
+        </is>
+      </c>
+      <c r="AA40" s="22" t="inlineStr">
+        <is>
+          <t>Terville</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>814544425</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>81454442500030</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>JOULEAR</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>JOULEAR</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>19/11/2015</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>65 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M41" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N41" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O41" s="22" t="inlineStr"/>
+      <c r="P41" s="22" t="inlineStr"/>
+      <c r="Q41" s="22" t="inlineStr"/>
+      <c r="R41" s="22" t="inlineStr"/>
+      <c r="S41" s="23" t="inlineStr"/>
+      <c r="T41" s="22" t="inlineStr"/>
+      <c r="U41" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V41" s="22" t="inlineStr">
+        <is>
+          <t>CARDI</t>
+        </is>
+      </c>
+      <c r="W41" s="22" t="inlineStr">
+        <is>
+          <t>Antoine</t>
+        </is>
+      </c>
+      <c r="X41" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y41" s="22" t="inlineStr">
+        <is>
+          <t>149 rue saint ladre</t>
+        </is>
+      </c>
+      <c r="Z41" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="AA41" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>902893064</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>90289306400011</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>O PETIT JAPON</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>O PETIT JAPON</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I42" s="22" t="inlineStr">
+        <is>
+          <t>06/08/2021</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE HARELLE</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M42" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N42" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O42" s="22" t="inlineStr"/>
+      <c r="P42" s="22" t="inlineStr"/>
+      <c r="Q42" s="22" t="inlineStr"/>
+      <c r="R42" s="22" t="inlineStr"/>
+      <c r="S42" s="23" t="inlineStr"/>
+      <c r="T42" s="22" t="inlineStr"/>
+      <c r="U42" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V42" s="22" t="inlineStr">
+        <is>
+          <t>VITTECOQ</t>
+        </is>
+      </c>
+      <c r="W42" s="22" t="inlineStr">
+        <is>
+          <t>Carole</t>
+        </is>
+      </c>
+      <c r="X42" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y42" s="22" t="inlineStr">
+        <is>
+          <t>2 Rue de Metz</t>
+        </is>
+      </c>
+      <c r="Z42" s="23" t="inlineStr">
+        <is>
+          <t>57300</t>
+        </is>
+      </c>
+      <c r="AA42" s="22" t="inlineStr">
+        <is>
+          <t>Ay-sur-Moselle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>830269734</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>83026973400018</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>BOCK RESTAURATION</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>BOCK RESTAURATION</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>01/08/2017</t>
+        </is>
+      </c>
+      <c r="J43" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K43" s="22" t="inlineStr">
+        <is>
+          <t>RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L43" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M43" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N43" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O43" s="22" t="n">
+        <v>987035</v>
+      </c>
+      <c r="P43" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q43" s="22" t="n">
+        <v>5943</v>
+      </c>
+      <c r="R43" s="22" t="inlineStr"/>
+      <c r="S43" s="23" t="inlineStr"/>
+      <c r="T43" s="22" t="inlineStr"/>
+      <c r="U43" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V43" s="22" t="inlineStr">
+        <is>
+          <t>NI-NO BOCK INVESTISSEMENT</t>
+        </is>
+      </c>
+      <c r="W43" s="22" t="inlineStr"/>
+      <c r="X43" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y43" s="22" t="inlineStr">
+        <is>
+          <t>7 rue Marie Laurencin</t>
+        </is>
+      </c>
+      <c r="Z43" s="23" t="inlineStr">
+        <is>
+          <t>54510</t>
+        </is>
+      </c>
+      <c r="AA43" s="22" t="inlineStr">
+        <is>
+          <t>Tomblaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>380617886</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>38061788600060</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>CAPPAERT Philippe</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>CAPPAERT Philippe</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>02/01/1991</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>33 RUE SAINT-PIERRE</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O44" s="22" t="inlineStr"/>
+      <c r="P44" s="22" t="inlineStr"/>
+      <c r="Q44" s="22" t="inlineStr"/>
+      <c r="R44" s="22" t="inlineStr"/>
+      <c r="S44" s="23" t="inlineStr"/>
+      <c r="T44" s="22" t="inlineStr"/>
+      <c r="U44" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V44" s="22" t="inlineStr">
+        <is>
+          <t>CAPPAERT</t>
+        </is>
+      </c>
+      <c r="W44" s="22" t="inlineStr">
+        <is>
+          <t>Philippe, Jean, Albert</t>
+        </is>
+      </c>
+      <c r="X44" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="Y44" s="22" t="inlineStr"/>
+      <c r="Z44" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA44" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>500056858</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>50005685800011</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>MACOVA</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>MACOVA</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2007</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>11 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L45" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M45" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N45" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O45" s="22" t="inlineStr"/>
+      <c r="P45" s="22" t="inlineStr"/>
+      <c r="Q45" s="22" t="inlineStr"/>
+      <c r="R45" s="22" t="inlineStr"/>
+      <c r="S45" s="23" t="inlineStr"/>
+      <c r="T45" s="22" t="inlineStr"/>
+      <c r="U45" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V45" s="22" t="inlineStr">
+        <is>
+          <t>MARQUET</t>
+        </is>
+      </c>
+      <c r="W45" s="22" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="X45" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="Y45" s="22" t="inlineStr">
+        <is>
+          <t>4 rue Montplaisir</t>
+        </is>
+      </c>
+      <c r="Z45" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="AA45" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>820527968</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>82052796800011</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>PASTA MERY BAR</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>PASTA MERY BAR</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>26/05/2016</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K46" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M46" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N46" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O46" s="22" t="inlineStr"/>
+      <c r="P46" s="22" t="inlineStr"/>
+      <c r="Q46" s="22" t="inlineStr"/>
+      <c r="R46" s="22" t="inlineStr"/>
+      <c r="S46" s="23" t="inlineStr"/>
+      <c r="T46" s="22" t="inlineStr"/>
+      <c r="U46" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V46" s="22" t="inlineStr">
+        <is>
+          <t>EL ALAMI</t>
+        </is>
+      </c>
+      <c r="W46" s="22" t="inlineStr">
+        <is>
+          <t>Youness</t>
+        </is>
+      </c>
+      <c r="X46" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="Y46" s="22" t="inlineStr">
+        <is>
+          <t>69 rue des Allemands</t>
+        </is>
+      </c>
+      <c r="Z46" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA46" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>451081251</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>45108125100014</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>HORODNYJ Thierry</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>HORODNYJ Thierry</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>24/09/2003</t>
+        </is>
+      </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K47" s="22" t="inlineStr">
+        <is>
+          <t>33 RUE VIGNE SAINT-AVOLD</t>
+        </is>
+      </c>
+      <c r="L47" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M47" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N47" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O47" s="22" t="inlineStr"/>
+      <c r="P47" s="22" t="inlineStr"/>
+      <c r="Q47" s="22" t="inlineStr"/>
+      <c r="R47" s="22" t="inlineStr"/>
+      <c r="S47" s="23" t="inlineStr"/>
+      <c r="T47" s="22" t="inlineStr"/>
+      <c r="U47" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="V47" s="22" t="inlineStr">
+        <is>
+          <t>HORODNYJ</t>
+        </is>
+      </c>
+      <c r="W47" s="22" t="inlineStr">
+        <is>
+          <t>Thierry, Bernard</t>
+        </is>
+      </c>
+      <c r="X47" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="Y47" s="22" t="inlineStr"/>
+      <c r="Z47" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="AA47" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AA27"/>
+  <autoFilter ref="A2:AA47"/>
   <mergeCells count="6">
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="R1:U1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$AA$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -605,17 +605,16 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" style="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" style="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" style="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" style="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -651,25 +650,24 @@
       </c>
       <c r="O1" s="9" t="n"/>
       <c r="P1" s="9" t="n"/>
-      <c r="Q1" s="9" t="n"/>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>CONTACT</t>
         </is>
       </c>
+      <c r="R1" s="11" t="n"/>
       <c r="S1" s="11" t="n"/>
       <c r="T1" s="11" t="n"/>
-      <c r="U1" s="11" t="n"/>
-      <c r="V1" s="12" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>DIRIGEANTS</t>
         </is>
       </c>
+      <c r="V1" s="13" t="n"/>
       <c r="W1" s="13" t="n"/>
       <c r="X1" s="13" t="n"/>
       <c r="Y1" s="13" t="n"/>
       <c r="Z1" s="13" t="n"/>
-      <c r="AA1" s="13" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
@@ -752,57 +750,52 @@
           <t>annee_ca</t>
         </is>
       </c>
-      <c r="Q2" s="17" t="inlineStr">
-        <is>
-          <t>resultat</t>
+      <c r="Q2" s="18" t="inlineStr">
+        <is>
+          <t>email</t>
         </is>
       </c>
       <c r="R2" s="18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>telephone</t>
         </is>
       </c>
       <c r="S2" s="18" t="inlineStr">
         <is>
-          <t>telephone</t>
+          <t>site_web</t>
         </is>
       </c>
       <c r="T2" s="18" t="inlineStr">
         <is>
-          <t>site_web</t>
-        </is>
-      </c>
-      <c r="U2" s="18" t="inlineStr">
-        <is>
           <t>statut</t>
         </is>
       </c>
+      <c r="U2" s="19" t="inlineStr">
+        <is>
+          <t>dirigeant_nom</t>
+        </is>
+      </c>
       <c r="V2" s="19" t="inlineStr">
         <is>
-          <t>dirigeant_nom</t>
+          <t>dirigeant_prenom</t>
         </is>
       </c>
       <c r="W2" s="19" t="inlineStr">
         <is>
-          <t>dirigeant_prenom</t>
+          <t>dirigeant_poste</t>
         </is>
       </c>
       <c r="X2" s="19" t="inlineStr">
         <is>
-          <t>dirigeant_poste</t>
+          <t>dirigeant_adresse</t>
         </is>
       </c>
       <c r="Y2" s="19" t="inlineStr">
         <is>
-          <t>dirigeant_adresse</t>
+          <t>dirigeant_code_postal</t>
         </is>
       </c>
       <c r="Z2" s="19" t="inlineStr">
-        <is>
-          <t>dirigeant_code_postal</t>
-        </is>
-      </c>
-      <c r="AA2" s="19" t="inlineStr">
         <is>
           <t>dirigeant_ville</t>
         </is>
@@ -882,40 +875,39 @@
       <c r="O3" s="20" t="inlineStr"/>
       <c r="P3" s="20" t="inlineStr"/>
       <c r="Q3" s="20" t="inlineStr"/>
-      <c r="R3" s="20" t="inlineStr"/>
-      <c r="S3" s="21" t="inlineStr"/>
-      <c r="T3" s="20" t="inlineStr"/>
+      <c r="R3" s="21" t="inlineStr"/>
+      <c r="S3" s="20" t="inlineStr"/>
+      <c r="T3" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U3" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>BERTOLONI</t>
         </is>
       </c>
       <c r="V3" s="20" t="inlineStr">
         <is>
-          <t>BERTOLONI</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="W3" s="20" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X3" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y3" s="20" t="inlineStr">
-        <is>
           <t>2 rue de tanière</t>
         </is>
       </c>
-      <c r="Z3" s="21" t="inlineStr">
+      <c r="Y3" s="21" t="inlineStr">
         <is>
           <t>57680</t>
         </is>
       </c>
-      <c r="AA3" s="20" t="inlineStr">
+      <c r="Z3" s="20" t="inlineStr">
         <is>
           <t>Corny-sur-Moselle</t>
         </is>
@@ -995,40 +987,39 @@
       <c r="O4" s="20" t="inlineStr"/>
       <c r="P4" s="20" t="inlineStr"/>
       <c r="Q4" s="20" t="inlineStr"/>
-      <c r="R4" s="20" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
-      <c r="T4" s="20" t="inlineStr"/>
+      <c r="R4" s="21" t="inlineStr"/>
+      <c r="S4" s="20" t="inlineStr"/>
+      <c r="T4" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U4" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="V4" s="20" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>Jianmin</t>
         </is>
       </c>
       <c r="W4" s="20" t="inlineStr">
         <is>
-          <t>Jianmin</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X4" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y4" s="20" t="inlineStr">
-        <is>
           <t>20 bis avenue robert schuman</t>
         </is>
       </c>
-      <c r="Z4" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA4" s="20" t="inlineStr">
+      <c r="Y4" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z4" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -1115,45 +1106,40 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="Q5" s="20" t="inlineStr">
-        <is>
-          <t>-644</t>
-        </is>
-      </c>
-      <c r="R5" s="20" t="inlineStr"/>
-      <c r="S5" s="21" t="inlineStr"/>
-      <c r="T5" s="20" t="inlineStr"/>
+      <c r="Q5" s="20" t="inlineStr"/>
+      <c r="R5" s="21" t="inlineStr"/>
+      <c r="S5" s="20" t="inlineStr"/>
+      <c r="T5" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U5" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>MAROUF</t>
         </is>
       </c>
       <c r="V5" s="20" t="inlineStr">
         <is>
-          <t>MAROUF</t>
+          <t>Mitra</t>
         </is>
       </c>
       <c r="W5" s="20" t="inlineStr">
         <is>
-          <t>Mitra</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X5" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y5" s="20" t="inlineStr">
-        <is>
           <t>Cité Universitaire du Saulcy</t>
         </is>
       </c>
-      <c r="Z5" s="21" t="inlineStr">
+      <c r="Y5" s="21" t="inlineStr">
         <is>
           <t>57010</t>
         </is>
       </c>
-      <c r="AA5" s="20" t="inlineStr">
+      <c r="Z5" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -1240,45 +1226,40 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="Q6" s="20" t="inlineStr">
-        <is>
-          <t>13528</t>
-        </is>
-      </c>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="21" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U6" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>ABEBE NEGA</t>
         </is>
       </c>
       <c r="V6" s="20" t="inlineStr">
         <is>
-          <t>ABEBE NEGA</t>
+          <t>Genet</t>
         </is>
       </c>
       <c r="W6" s="20" t="inlineStr">
         <is>
-          <t>Genet</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X6" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y6" s="20" t="inlineStr">
-        <is>
           <t>48 rue Sente à My</t>
         </is>
       </c>
-      <c r="Z6" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA6" s="20" t="inlineStr">
+      <c r="Y6" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z6" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -1358,40 +1339,39 @@
       <c r="O7" s="20" t="inlineStr"/>
       <c r="P7" s="20" t="inlineStr"/>
       <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="21" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
+      <c r="R7" s="21" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U7" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>SAVIO</t>
         </is>
       </c>
       <c r="V7" s="20" t="inlineStr">
         <is>
-          <t>SAVIO</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="W7" s="20" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X7" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y7" s="20" t="inlineStr">
-        <is>
           <t>6 rue de Brest</t>
         </is>
       </c>
-      <c r="Z7" s="21" t="inlineStr">
+      <c r="Y7" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="AA7" s="20" t="inlineStr">
+      <c r="Z7" s="20" t="inlineStr">
         <is>
           <t>Woippy</t>
         </is>
@@ -1471,40 +1451,39 @@
       <c r="O8" s="20" t="inlineStr"/>
       <c r="P8" s="20" t="inlineStr"/>
       <c r="Q8" s="20" t="inlineStr"/>
-      <c r="R8" s="20" t="inlineStr"/>
-      <c r="S8" s="21" t="inlineStr"/>
-      <c r="T8" s="20" t="inlineStr"/>
+      <c r="R8" s="21" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U8" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>KOLOGRECKI</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr">
         <is>
-          <t>KOLOGRECKI</t>
+          <t>Steve, Jean, Baptiste, Sylvain</t>
         </is>
       </c>
       <c r="W8" s="20" t="inlineStr">
         <is>
-          <t>Steve, Jean, Baptiste, Sylvain</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X8" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y8" s="20" t="inlineStr">
-        <is>
           <t>19 rue du Grand Wad</t>
         </is>
       </c>
-      <c r="Z8" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA8" s="20" t="inlineStr">
+      <c r="Y8" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z8" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -1584,40 +1563,39 @@
       <c r="O9" s="20" t="inlineStr"/>
       <c r="P9" s="20" t="inlineStr"/>
       <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="21" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
+      <c r="R9" s="21" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U9" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>SCHIPANI</t>
         </is>
       </c>
       <c r="V9" s="20" t="inlineStr">
         <is>
-          <t>SCHIPANI</t>
+          <t>Ricky, Giuseppe, Dominique</t>
         </is>
       </c>
       <c r="W9" s="20" t="inlineStr">
         <is>
-          <t>Ricky, Giuseppe, Dominique</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X9" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y9" s="20" t="inlineStr">
-        <is>
           <t>23 rue d'Auché</t>
         </is>
       </c>
-      <c r="Z9" s="21" t="inlineStr">
+      <c r="Y9" s="21" t="inlineStr">
         <is>
           <t>57680</t>
         </is>
       </c>
-      <c r="AA9" s="20" t="inlineStr">
+      <c r="Z9" s="20" t="inlineStr">
         <is>
           <t>Corny-sur-Moselle</t>
         </is>
@@ -1697,40 +1675,39 @@
       <c r="O10" s="20" t="inlineStr"/>
       <c r="P10" s="20" t="inlineStr"/>
       <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="21" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
+      <c r="R10" s="21" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U10" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>BENAOUICHA</t>
         </is>
       </c>
       <c r="V10" s="20" t="inlineStr">
         <is>
-          <t>BENAOUICHA</t>
+          <t>Samir</t>
         </is>
       </c>
       <c r="W10" s="20" t="inlineStr">
         <is>
-          <t>Samir</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X10" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y10" s="20" t="inlineStr">
-        <is>
           <t>25 rue marc seguin</t>
         </is>
       </c>
-      <c r="Z10" s="21" t="inlineStr">
+      <c r="Y10" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA10" s="20" t="inlineStr">
+      <c r="Z10" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
@@ -1810,40 +1787,39 @@
       <c r="O11" s="20" t="inlineStr"/>
       <c r="P11" s="20" t="inlineStr"/>
       <c r="Q11" s="20" t="inlineStr"/>
-      <c r="R11" s="20" t="inlineStr"/>
-      <c r="S11" s="21" t="inlineStr"/>
-      <c r="T11" s="20" t="inlineStr"/>
+      <c r="R11" s="21" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U11" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>HORY</t>
         </is>
       </c>
       <c r="V11" s="20" t="inlineStr">
         <is>
-          <t>HORY</t>
+          <t>Vincent, Roland</t>
         </is>
       </c>
       <c r="W11" s="20" t="inlineStr">
         <is>
-          <t>Vincent, Roland</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X11" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y11" s="20" t="inlineStr">
-        <is>
           <t>75 rue Principale</t>
         </is>
       </c>
-      <c r="Z11" s="21" t="inlineStr">
+      <c r="Y11" s="21" t="inlineStr">
         <is>
           <t>57580</t>
         </is>
       </c>
-      <c r="AA11" s="20" t="inlineStr">
+      <c r="Z11" s="20" t="inlineStr">
         <is>
           <t>Vittoncourt</t>
         </is>
@@ -1923,40 +1899,39 @@
       <c r="O12" s="20" t="inlineStr"/>
       <c r="P12" s="20" t="inlineStr"/>
       <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="21" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
+      <c r="R12" s="21" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U12" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>MINET</t>
         </is>
       </c>
       <c r="V12" s="20" t="inlineStr">
         <is>
-          <t>MINET</t>
+          <t>Stéphanie, Cécile</t>
         </is>
       </c>
       <c r="W12" s="20" t="inlineStr">
         <is>
-          <t>Stéphanie, Cécile</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X12" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y12" s="20" t="inlineStr">
-        <is>
           <t>16 Allée du Fort</t>
         </is>
       </c>
-      <c r="Z12" s="21" t="inlineStr">
+      <c r="Y12" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA12" s="20" t="inlineStr">
+      <c r="Z12" s="20" t="inlineStr">
         <is>
           <t>Saint-Julien-lès-Metz</t>
         </is>
@@ -2036,36 +2011,35 @@
       <c r="O13" s="20" t="inlineStr"/>
       <c r="P13" s="20" t="inlineStr"/>
       <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="21" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
+      <c r="R13" s="21" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U13" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>HUMBERT</t>
         </is>
       </c>
       <c r="V13" s="20" t="inlineStr">
         <is>
-          <t>HUMBERT</t>
+          <t>Arthur, Victor</t>
         </is>
       </c>
       <c r="W13" s="20" t="inlineStr">
         <is>
-          <t>Arthur, Victor</t>
-        </is>
-      </c>
-      <c r="X13" s="20" t="inlineStr">
-        <is>
           <t>Gérant, Associé indéfiniment responsable</t>
         </is>
       </c>
-      <c r="Y13" s="20" t="inlineStr"/>
-      <c r="Z13" s="21" t="inlineStr">
+      <c r="X13" s="20" t="inlineStr"/>
+      <c r="Y13" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="AA13" s="20" t="inlineStr">
+      <c r="Z13" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
@@ -2152,45 +2126,40 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="Q14" s="20" t="inlineStr">
-        <is>
-          <t>-12144</t>
-        </is>
-      </c>
-      <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr"/>
-      <c r="T14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="21" t="inlineStr"/>
+      <c r="S14" s="20" t="inlineStr"/>
+      <c r="T14" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U14" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>DAVADANT</t>
         </is>
       </c>
       <c r="V14" s="20" t="inlineStr">
         <is>
-          <t>DAVADANT</t>
+          <t>Serge</t>
         </is>
       </c>
       <c r="W14" s="20" t="inlineStr">
         <is>
-          <t>Serge</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X14" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y14" s="20" t="inlineStr">
-        <is>
           <t>1 rue aux Ossons</t>
         </is>
       </c>
-      <c r="Z14" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA14" s="20" t="inlineStr">
+      <c r="Y14" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z14" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -2270,40 +2239,39 @@
       <c r="O15" s="20" t="inlineStr"/>
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr"/>
-      <c r="T15" s="20" t="inlineStr"/>
+      <c r="R15" s="21" t="inlineStr"/>
+      <c r="S15" s="20" t="inlineStr"/>
+      <c r="T15" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U15" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>CHEN</t>
         </is>
       </c>
       <c r="V15" s="20" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>Suli</t>
         </is>
       </c>
       <c r="W15" s="20" t="inlineStr">
         <is>
-          <t>Suli</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X15" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y15" s="20" t="inlineStr">
-        <is>
           <t>34 rue du Coetlosquet</t>
         </is>
       </c>
-      <c r="Z15" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA15" s="20" t="inlineStr">
+      <c r="Y15" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z15" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -2383,40 +2351,39 @@
       <c r="O16" s="20" t="inlineStr"/>
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr"/>
-      <c r="T16" s="20" t="inlineStr"/>
+      <c r="R16" s="21" t="inlineStr"/>
+      <c r="S16" s="20" t="inlineStr"/>
+      <c r="T16" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U16" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>COULBAUX</t>
         </is>
       </c>
       <c r="V16" s="20" t="inlineStr">
         <is>
-          <t>COULBAUX</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="W16" s="20" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Liquidateur</t>
         </is>
       </c>
       <c r="X16" s="20" t="inlineStr">
         <is>
-          <t>Liquidateur</t>
-        </is>
-      </c>
-      <c r="Y16" s="20" t="inlineStr">
-        <is>
           <t>8 RUE DE VILLIERS</t>
         </is>
       </c>
-      <c r="Z16" s="21" t="inlineStr">
+      <c r="Y16" s="21" t="inlineStr">
         <is>
           <t>78710</t>
         </is>
       </c>
-      <c r="AA16" s="20" t="inlineStr">
+      <c r="Z16" s="20" t="inlineStr">
         <is>
           <t>ROSNY SUR SEINE</t>
         </is>
@@ -2496,40 +2463,39 @@
       <c r="O17" s="20" t="inlineStr"/>
       <c r="P17" s="20" t="inlineStr"/>
       <c r="Q17" s="20" t="inlineStr"/>
-      <c r="R17" s="20" t="inlineStr"/>
-      <c r="S17" s="21" t="inlineStr"/>
-      <c r="T17" s="20" t="inlineStr"/>
+      <c r="R17" s="21" t="inlineStr"/>
+      <c r="S17" s="20" t="inlineStr"/>
+      <c r="T17" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U17" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>ZANETTI</t>
         </is>
       </c>
       <c r="V17" s="20" t="inlineStr">
         <is>
-          <t>ZANETTI</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="W17" s="20" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X17" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y17" s="20" t="inlineStr">
-        <is>
           <t>29 rue de la Source</t>
         </is>
       </c>
-      <c r="Z17" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA17" s="20" t="inlineStr">
+      <c r="Y17" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z17" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -2616,45 +2582,40 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="Q18" s="20" t="inlineStr">
-        <is>
-          <t>-2268</t>
-        </is>
-      </c>
-      <c r="R18" s="20" t="inlineStr"/>
-      <c r="S18" s="21" t="inlineStr"/>
-      <c r="T18" s="20" t="inlineStr"/>
+      <c r="Q18" s="20" t="inlineStr"/>
+      <c r="R18" s="21" t="inlineStr"/>
+      <c r="S18" s="20" t="inlineStr"/>
+      <c r="T18" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U18" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>AL- ATRASH</t>
         </is>
       </c>
       <c r="V18" s="20" t="inlineStr">
         <is>
-          <t>AL- ATRASH</t>
+          <t>Abel</t>
         </is>
       </c>
       <c r="W18" s="20" t="inlineStr">
         <is>
-          <t>Abel</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X18" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y18" s="20" t="inlineStr">
-        <is>
           <t>67 rue de Neuves Maisons</t>
         </is>
       </c>
-      <c r="Z18" s="21" t="inlineStr">
+      <c r="Y18" s="21" t="inlineStr">
         <is>
           <t>54230</t>
         </is>
       </c>
-      <c r="AA18" s="20" t="inlineStr">
+      <c r="Z18" s="20" t="inlineStr">
         <is>
           <t>Chavigny</t>
         </is>
@@ -2734,36 +2695,35 @@
       <c r="O19" s="20" t="inlineStr"/>
       <c r="P19" s="20" t="inlineStr"/>
       <c r="Q19" s="20" t="inlineStr"/>
-      <c r="R19" s="20" t="inlineStr"/>
-      <c r="S19" s="21" t="inlineStr"/>
-      <c r="T19" s="20" t="inlineStr"/>
+      <c r="R19" s="21" t="inlineStr"/>
+      <c r="S19" s="20" t="inlineStr"/>
+      <c r="T19" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U19" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>BERLOGER</t>
         </is>
       </c>
       <c r="V19" s="20" t="inlineStr">
         <is>
-          <t>BERLOGER</t>
+          <t>Yoan</t>
         </is>
       </c>
       <c r="W19" s="20" t="inlineStr">
         <is>
-          <t>Yoan</t>
-        </is>
-      </c>
-      <c r="X19" s="20" t="inlineStr">
-        <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y19" s="20" t="inlineStr"/>
-      <c r="Z19" s="21" t="inlineStr">
+      <c r="X19" s="20" t="inlineStr"/>
+      <c r="Y19" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA19" s="20" t="inlineStr">
+      <c r="Z19" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
@@ -2843,40 +2803,39 @@
       <c r="O20" s="20" t="inlineStr"/>
       <c r="P20" s="20" t="inlineStr"/>
       <c r="Q20" s="20" t="inlineStr"/>
-      <c r="R20" s="20" t="inlineStr"/>
-      <c r="S20" s="21" t="inlineStr"/>
-      <c r="T20" s="20" t="inlineStr"/>
+      <c r="R20" s="21" t="inlineStr"/>
+      <c r="S20" s="20" t="inlineStr"/>
+      <c r="T20" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U20" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>HERTZOG</t>
         </is>
       </c>
       <c r="V20" s="20" t="inlineStr">
         <is>
-          <t>HERTZOG</t>
+          <t>Gerald</t>
         </is>
       </c>
       <c r="W20" s="20" t="inlineStr">
         <is>
-          <t>Gerald</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X20" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y20" s="20" t="inlineStr">
-        <is>
           <t>19 rue des Pépinières</t>
         </is>
       </c>
-      <c r="Z20" s="21" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA20" s="20" t="inlineStr">
+      <c r="Y20" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z20" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -2956,20 +2915,19 @@
       <c r="O21" s="20" t="inlineStr"/>
       <c r="P21" s="20" t="inlineStr"/>
       <c r="Q21" s="20" t="inlineStr"/>
-      <c r="R21" s="20" t="inlineStr"/>
-      <c r="S21" s="21" t="inlineStr"/>
-      <c r="T21" s="20" t="inlineStr"/>
-      <c r="U21" s="20" t="inlineStr">
+      <c r="R21" s="21" t="inlineStr"/>
+      <c r="S21" s="20" t="inlineStr"/>
+      <c r="T21" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
+      <c r="U21" s="20" t="inlineStr"/>
       <c r="V21" s="20" t="inlineStr"/>
       <c r="W21" s="20" t="inlineStr"/>
       <c r="X21" s="20" t="inlineStr"/>
-      <c r="Y21" s="20" t="inlineStr"/>
-      <c r="Z21" s="21" t="inlineStr"/>
-      <c r="AA21" s="20" t="inlineStr"/>
+      <c r="Y21" s="21" t="inlineStr"/>
+      <c r="Z21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
@@ -3045,40 +3003,39 @@
       <c r="O22" s="20" t="inlineStr"/>
       <c r="P22" s="20" t="inlineStr"/>
       <c r="Q22" s="20" t="inlineStr"/>
-      <c r="R22" s="20" t="inlineStr"/>
-      <c r="S22" s="21" t="inlineStr"/>
-      <c r="T22" s="20" t="inlineStr"/>
+      <c r="R22" s="21" t="inlineStr"/>
+      <c r="S22" s="20" t="inlineStr"/>
+      <c r="T22" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U22" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="V22" s="20" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>Aizhen</t>
         </is>
       </c>
       <c r="W22" s="20" t="inlineStr">
         <is>
-          <t>Aizhen</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X22" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y22" s="20" t="inlineStr">
-        <is>
           <t>8 avenue Karl Marx</t>
         </is>
       </c>
-      <c r="Z22" s="21" t="inlineStr">
+      <c r="Y22" s="21" t="inlineStr">
         <is>
           <t>93000</t>
         </is>
       </c>
-      <c r="AA22" s="20" t="inlineStr">
+      <c r="Z22" s="20" t="inlineStr">
         <is>
           <t>Bobigny</t>
         </is>
@@ -3158,40 +3115,39 @@
       <c r="O23" s="20" t="inlineStr"/>
       <c r="P23" s="20" t="inlineStr"/>
       <c r="Q23" s="20" t="inlineStr"/>
-      <c r="R23" s="20" t="inlineStr"/>
-      <c r="S23" s="21" t="inlineStr"/>
-      <c r="T23" s="20" t="inlineStr"/>
+      <c r="R23" s="21" t="inlineStr"/>
+      <c r="S23" s="20" t="inlineStr"/>
+      <c r="T23" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U23" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>BEAUX</t>
         </is>
       </c>
       <c r="V23" s="20" t="inlineStr">
         <is>
-          <t>BEAUX</t>
+          <t>Bernard, Francois</t>
         </is>
       </c>
       <c r="W23" s="20" t="inlineStr">
         <is>
-          <t>Bernard, Francois</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="X23" s="20" t="inlineStr">
         <is>
-          <t>Président</t>
-        </is>
-      </c>
-      <c r="Y23" s="20" t="inlineStr">
-        <is>
           <t>2, rue du Stade</t>
         </is>
       </c>
-      <c r="Z23" s="21" t="inlineStr">
+      <c r="Y23" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="AA23" s="20" t="inlineStr">
+      <c r="Z23" s="20" t="inlineStr">
         <is>
           <t>Longeville-lès-Metz</t>
         </is>
@@ -3271,40 +3227,39 @@
       <c r="O24" s="20" t="inlineStr"/>
       <c r="P24" s="20" t="inlineStr"/>
       <c r="Q24" s="20" t="inlineStr"/>
-      <c r="R24" s="20" t="inlineStr"/>
-      <c r="S24" s="21" t="inlineStr"/>
-      <c r="T24" s="20" t="inlineStr"/>
+      <c r="R24" s="21" t="inlineStr"/>
+      <c r="S24" s="20" t="inlineStr"/>
+      <c r="T24" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U24" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>LIAO</t>
         </is>
       </c>
       <c r="V24" s="20" t="inlineStr">
         <is>
-          <t>LIAO</t>
+          <t>Xuemei</t>
         </is>
       </c>
       <c r="W24" s="20" t="inlineStr">
         <is>
-          <t>Xuemei</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X24" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y24" s="20" t="inlineStr">
-        <is>
           <t>29 rue Aristide Briand Chez Mme Bu Jiangli</t>
         </is>
       </c>
-      <c r="Z24" s="21" t="inlineStr">
+      <c r="Y24" s="21" t="inlineStr">
         <is>
           <t>54510</t>
         </is>
       </c>
-      <c r="AA24" s="20" t="inlineStr">
+      <c r="Z24" s="20" t="inlineStr">
         <is>
           <t>Tomblaine</t>
         </is>
@@ -3384,40 +3339,39 @@
       <c r="O25" s="20" t="inlineStr"/>
       <c r="P25" s="20" t="inlineStr"/>
       <c r="Q25" s="20" t="inlineStr"/>
-      <c r="R25" s="20" t="inlineStr"/>
-      <c r="S25" s="21" t="inlineStr"/>
-      <c r="T25" s="20" t="inlineStr"/>
+      <c r="R25" s="21" t="inlineStr"/>
+      <c r="S25" s="20" t="inlineStr"/>
+      <c r="T25" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U25" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>THAMMAVONG</t>
         </is>
       </c>
       <c r="V25" s="20" t="inlineStr">
         <is>
-          <t>THAMMAVONG</t>
+          <t>Bounlay</t>
         </is>
       </c>
       <c r="W25" s="20" t="inlineStr">
         <is>
-          <t>Bounlay</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X25" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y25" s="20" t="inlineStr">
-        <is>
           <t>15 rue Virginie du Verger</t>
         </is>
       </c>
-      <c r="Z25" s="21" t="inlineStr">
+      <c r="Y25" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA25" s="20" t="inlineStr">
+      <c r="Z25" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -3500,45 +3454,40 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="Q26" s="20" t="inlineStr">
-        <is>
-          <t>162363</t>
-        </is>
-      </c>
-      <c r="R26" s="20" t="inlineStr"/>
-      <c r="S26" s="21" t="inlineStr"/>
-      <c r="T26" s="20" t="inlineStr"/>
+      <c r="Q26" s="20" t="inlineStr"/>
+      <c r="R26" s="21" t="inlineStr"/>
+      <c r="S26" s="20" t="inlineStr"/>
+      <c r="T26" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U26" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>MICHEL</t>
         </is>
       </c>
       <c r="V26" s="20" t="inlineStr">
         <is>
-          <t>MICHEL</t>
+          <t>David</t>
         </is>
       </c>
       <c r="W26" s="20" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X26" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y26" s="20" t="inlineStr">
-        <is>
           <t>2 Rue des Marronniers</t>
         </is>
       </c>
-      <c r="Z26" s="21" t="inlineStr">
+      <c r="Y26" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA26" s="20" t="inlineStr">
+      <c r="Z26" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -3618,2322 +3567,4527 @@
       <c r="O27" s="20" t="inlineStr"/>
       <c r="P27" s="20" t="inlineStr"/>
       <c r="Q27" s="20" t="inlineStr"/>
-      <c r="R27" s="20" t="inlineStr"/>
-      <c r="S27" s="21" t="inlineStr"/>
-      <c r="T27" s="20" t="inlineStr"/>
+      <c r="R27" s="21" t="inlineStr"/>
+      <c r="S27" s="20" t="inlineStr"/>
+      <c r="T27" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
       <c r="U27" s="20" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>SIDOT</t>
         </is>
       </c>
       <c r="V27" s="20" t="inlineStr">
         <is>
-          <t>SIDOT</t>
+          <t>Clément, Victor</t>
         </is>
       </c>
       <c r="W27" s="20" t="inlineStr">
         <is>
-          <t>Clément, Victor</t>
+          <t>Gérant</t>
         </is>
       </c>
       <c r="X27" s="20" t="inlineStr">
         <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="Y27" s="20" t="inlineStr">
-        <is>
           <t>1 rue André Malraux</t>
         </is>
       </c>
-      <c r="Z27" s="21" t="inlineStr">
+      <c r="Y27" s="21" t="inlineStr">
         <is>
           <t>57155</t>
         </is>
       </c>
-      <c r="AA27" s="20" t="inlineStr">
+      <c r="Z27" s="20" t="inlineStr">
         <is>
           <t>Marly</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>348588617</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>34858861700012</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>LA JONQUE D'OR</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>LA JONQUE D'OR</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>01/11/1988</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>1988</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>45 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L28" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M28" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N28" s="22" t="inlineStr">
+      <c r="N28" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O28" s="22" t="n">
-        <v>564988</v>
-      </c>
-      <c r="P28" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q28" s="22" t="n">
-        <v>26750</v>
-      </c>
-      <c r="R28" s="22" t="inlineStr"/>
-      <c r="S28" s="23" t="inlineStr"/>
-      <c r="T28" s="22" t="inlineStr"/>
-      <c r="U28" s="22" t="inlineStr">
+      <c r="O28" s="20" t="inlineStr">
+        <is>
+          <t>564988</t>
+        </is>
+      </c>
+      <c r="P28" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q28" s="20" t="inlineStr"/>
+      <c r="R28" s="21" t="inlineStr"/>
+      <c r="S28" s="20" t="inlineStr"/>
+      <c r="T28" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V28" s="22" t="inlineStr">
+      <c r="U28" s="20" t="inlineStr">
         <is>
           <t>GAO</t>
         </is>
       </c>
-      <c r="W28" s="22" t="inlineStr">
+      <c r="V28" s="20" t="inlineStr">
         <is>
           <t>Ning</t>
         </is>
       </c>
-      <c r="X28" s="22" t="inlineStr">
+      <c r="W28" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y28" s="22" t="inlineStr"/>
-      <c r="Z28" s="23" t="inlineStr">
+      <c r="X28" s="20" t="inlineStr"/>
+      <c r="Y28" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA28" s="22" t="inlineStr">
+      <c r="Z28" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>848949103</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>84894910300024</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>LES FRERES DE BAKEL</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>LES FRERES DE BAKEL</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>04/03/2019</t>
         </is>
       </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>18 RUE DE L'ABREUVOIR</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N29" s="22" t="inlineStr">
+      <c r="N29" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O29" s="22" t="inlineStr"/>
-      <c r="P29" s="22" t="inlineStr"/>
-      <c r="Q29" s="22" t="inlineStr"/>
-      <c r="R29" s="22" t="inlineStr"/>
-      <c r="S29" s="23" t="inlineStr"/>
-      <c r="T29" s="22" t="inlineStr"/>
-      <c r="U29" s="22" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr"/>
+      <c r="P29" s="20" t="inlineStr"/>
+      <c r="Q29" s="20" t="inlineStr"/>
+      <c r="R29" s="21" t="inlineStr"/>
+      <c r="S29" s="20" t="inlineStr"/>
+      <c r="T29" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V29" s="22" t="inlineStr">
+      <c r="U29" s="20" t="inlineStr">
         <is>
           <t>TRAORE</t>
         </is>
       </c>
-      <c r="W29" s="22" t="inlineStr">
+      <c r="V29" s="20" t="inlineStr">
         <is>
           <t>Daumbe</t>
         </is>
       </c>
-      <c r="X29" s="22" t="inlineStr">
+      <c r="W29" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y29" s="22" t="inlineStr">
+      <c r="X29" s="20" t="inlineStr">
         <is>
           <t>7 Rue de Peltre</t>
         </is>
       </c>
-      <c r="Z29" s="23" t="inlineStr">
+      <c r="Y29" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA29" s="22" t="inlineStr">
+      <c r="Z29" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>482693744</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>48269374400013</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>ALPHAM</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>ALPHAM</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>06/06/2005</t>
         </is>
       </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>83 RUE MAZELLE</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M30" s="22" t="inlineStr">
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N30" s="22" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O30" s="22" t="inlineStr"/>
-      <c r="P30" s="22" t="inlineStr"/>
-      <c r="Q30" s="22" t="inlineStr"/>
-      <c r="R30" s="22" t="inlineStr"/>
-      <c r="S30" s="23" t="inlineStr"/>
-      <c r="T30" s="22" t="inlineStr"/>
-      <c r="U30" s="22" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr"/>
+      <c r="P30" s="20" t="inlineStr"/>
+      <c r="Q30" s="20" t="inlineStr"/>
+      <c r="R30" s="21" t="inlineStr"/>
+      <c r="S30" s="20" t="inlineStr"/>
+      <c r="T30" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V30" s="22" t="inlineStr">
+      <c r="U30" s="20" t="inlineStr">
         <is>
           <t>CRISTOFARO</t>
         </is>
       </c>
-      <c r="W30" s="22" t="inlineStr">
+      <c r="V30" s="20" t="inlineStr">
         <is>
           <t>Girolamo</t>
         </is>
       </c>
-      <c r="X30" s="22" t="inlineStr">
+      <c r="W30" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y30" s="22" t="inlineStr">
+      <c r="X30" s="20" t="inlineStr">
         <is>
           <t>17 route de Borny</t>
         </is>
       </c>
-      <c r="Z30" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA30" s="22" t="inlineStr">
+      <c r="Y30" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z30" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>908199466</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>90819946600024</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>AJFM SAINT LOUIS</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>AJFM SAINT LOUIS</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>14/12/2021</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L31" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M31" s="22" t="inlineStr">
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M31" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N31" s="22" t="inlineStr">
+      <c r="N31" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O31" s="22" t="n">
-        <v>677283</v>
-      </c>
-      <c r="P31" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q31" s="22" t="n">
-        <v>-614</v>
-      </c>
-      <c r="R31" s="22" t="inlineStr"/>
-      <c r="S31" s="23" t="inlineStr"/>
-      <c r="T31" s="22" t="inlineStr"/>
-      <c r="U31" s="22" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>677283</t>
+        </is>
+      </c>
+      <c r="P31" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q31" s="20" t="inlineStr"/>
+      <c r="R31" s="21" t="inlineStr"/>
+      <c r="S31" s="20" t="inlineStr"/>
+      <c r="T31" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V31" s="22" t="inlineStr">
+      <c r="U31" s="20" t="inlineStr">
         <is>
           <t>CHR INVEST</t>
         </is>
       </c>
-      <c r="W31" s="22" t="inlineStr"/>
-      <c r="X31" s="22" t="inlineStr">
+      <c r="V31" s="20" t="inlineStr"/>
+      <c r="W31" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y31" s="22" t="inlineStr">
+      <c r="X31" s="20" t="inlineStr">
         <is>
           <t>41 Place de la Carrière</t>
         </is>
       </c>
-      <c r="Z31" s="23" t="inlineStr">
+      <c r="Y31" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="AA31" s="22" t="inlineStr">
+      <c r="Z31" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>929820710</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>92982071000010</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>CASA FRIDA</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>CASA FRIDA</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>10/07/2024</t>
         </is>
       </c>
-      <c r="J32" s="22" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K32" s="22" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>59 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M32" s="22" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N32" s="22" t="inlineStr">
+      <c r="N32" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O32" s="22" t="inlineStr"/>
-      <c r="P32" s="22" t="inlineStr"/>
-      <c r="Q32" s="22" t="inlineStr"/>
-      <c r="R32" s="22" t="inlineStr"/>
-      <c r="S32" s="23" t="inlineStr"/>
-      <c r="T32" s="22" t="inlineStr"/>
-      <c r="U32" s="22" t="inlineStr">
+      <c r="O32" s="20" t="inlineStr"/>
+      <c r="P32" s="20" t="inlineStr"/>
+      <c r="Q32" s="20" t="inlineStr"/>
+      <c r="R32" s="21" t="inlineStr"/>
+      <c r="S32" s="20" t="inlineStr"/>
+      <c r="T32" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V32" s="22" t="inlineStr">
+      <c r="U32" s="20" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="W32" s="22" t="inlineStr">
+      <c r="V32" s="20" t="inlineStr">
         <is>
           <t>Raimundo, Andres</t>
         </is>
       </c>
-      <c r="X32" s="22" t="inlineStr">
+      <c r="W32" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y32" s="22" t="inlineStr">
+      <c r="X32" s="20" t="inlineStr">
         <is>
           <t>68 rue vallières</t>
         </is>
       </c>
-      <c r="Z32" s="23" t="inlineStr">
+      <c r="Y32" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA32" s="22" t="inlineStr">
+      <c r="Z32" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>793604141</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>79360414100028</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>MONSIEUR JEAN</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>MONSIEUR JEAN</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>12/06/2013</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>23 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L33" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M33" s="22" t="inlineStr">
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N33" s="22" t="inlineStr">
+      <c r="N33" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O33" s="22" t="n">
-        <v>582282</v>
-      </c>
-      <c r="P33" s="22" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Q33" s="22" t="n">
-        <v>20308</v>
-      </c>
-      <c r="R33" s="22" t="inlineStr"/>
-      <c r="S33" s="23" t="inlineStr"/>
-      <c r="T33" s="22" t="inlineStr"/>
-      <c r="U33" s="22" t="inlineStr">
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>582282</t>
+        </is>
+      </c>
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q33" s="20" t="inlineStr"/>
+      <c r="R33" s="21" t="inlineStr"/>
+      <c r="S33" s="20" t="inlineStr"/>
+      <c r="T33" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V33" s="22" t="inlineStr">
+      <c r="U33" s="20" t="inlineStr">
         <is>
           <t>PANZA</t>
         </is>
       </c>
-      <c r="W33" s="22" t="inlineStr">
+      <c r="V33" s="20" t="inlineStr">
         <is>
           <t>Jean-pierre</t>
         </is>
       </c>
-      <c r="X33" s="22" t="inlineStr">
+      <c r="W33" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y33" s="22" t="inlineStr">
+      <c r="X33" s="20" t="inlineStr">
         <is>
           <t>8 rue des Parmentiers</t>
         </is>
       </c>
-      <c r="Z33" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA33" s="22" t="inlineStr">
+      <c r="Y33" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z33" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>881725642</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>88172564200014</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>RIMINI</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>RIMINI</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>13/02/2020</t>
         </is>
       </c>
-      <c r="J34" s="22" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K34" s="22" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>1 RUE DE LA PIERRE HARDIE</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M34" s="22" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N34" s="22" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O34" s="22" t="inlineStr"/>
-      <c r="P34" s="22" t="inlineStr"/>
-      <c r="Q34" s="22" t="inlineStr"/>
-      <c r="R34" s="22" t="inlineStr"/>
-      <c r="S34" s="23" t="inlineStr"/>
-      <c r="T34" s="22" t="inlineStr"/>
-      <c r="U34" s="22" t="inlineStr">
+      <c r="O34" s="20" t="inlineStr"/>
+      <c r="P34" s="20" t="inlineStr"/>
+      <c r="Q34" s="20" t="inlineStr"/>
+      <c r="R34" s="21" t="inlineStr"/>
+      <c r="S34" s="20" t="inlineStr"/>
+      <c r="T34" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V34" s="22" t="inlineStr">
+      <c r="U34" s="20" t="inlineStr">
         <is>
           <t>PRZYBYLSKI</t>
         </is>
       </c>
-      <c r="W34" s="22" t="inlineStr">
+      <c r="V34" s="20" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="X34" s="22" t="inlineStr">
+      <c r="W34" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y34" s="22" t="inlineStr">
+      <c r="X34" s="20" t="inlineStr">
         <is>
           <t>13 Rue Georges de la Tour</t>
         </is>
       </c>
-      <c r="Z34" s="23" t="inlineStr">
+      <c r="Y34" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="AA34" s="22" t="inlineStr">
+      <c r="Z34" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>877808931</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>87780893100019</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>ROYAL BAO</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>ROYAL BAO</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>01/10/2019</t>
         </is>
       </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K35" s="20" t="inlineStr">
         <is>
           <t>24 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M35" s="22" t="inlineStr">
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M35" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N35" s="22" t="inlineStr">
+      <c r="N35" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O35" s="22" t="inlineStr"/>
-      <c r="P35" s="22" t="inlineStr"/>
-      <c r="Q35" s="22" t="inlineStr"/>
-      <c r="R35" s="22" t="inlineStr"/>
-      <c r="S35" s="23" t="inlineStr"/>
-      <c r="T35" s="22" t="inlineStr"/>
-      <c r="U35" s="22" t="inlineStr">
+      <c r="O35" s="20" t="inlineStr"/>
+      <c r="P35" s="20" t="inlineStr"/>
+      <c r="Q35" s="20" t="inlineStr"/>
+      <c r="R35" s="21" t="inlineStr"/>
+      <c r="S35" s="20" t="inlineStr"/>
+      <c r="T35" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V35" s="22" t="inlineStr">
+      <c r="U35" s="20" t="inlineStr">
         <is>
           <t>WANG</t>
         </is>
       </c>
-      <c r="W35" s="22" t="inlineStr">
+      <c r="V35" s="20" t="inlineStr">
         <is>
           <t>Hao</t>
         </is>
       </c>
-      <c r="X35" s="22" t="inlineStr">
+      <c r="W35" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y35" s="22" t="inlineStr">
+      <c r="X35" s="20" t="inlineStr">
         <is>
           <t>62 avenue de Fontainebleau</t>
         </is>
       </c>
-      <c r="Z35" s="23" t="inlineStr">
+      <c r="Y35" s="21" t="inlineStr">
         <is>
           <t>94270</t>
         </is>
       </c>
-      <c r="AA35" s="22" t="inlineStr">
+      <c r="Z35" s="20" t="inlineStr">
         <is>
           <t>Le Kremlin-Bicêtre</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>845332154</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>84533215400010</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>15/01/2019</t>
         </is>
       </c>
-      <c r="J36" s="22" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K36" s="22" t="inlineStr">
+      <c r="K36" s="20" t="inlineStr">
         <is>
           <t>34 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M36" s="22" t="inlineStr">
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M36" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N36" s="22" t="inlineStr">
+      <c r="N36" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O36" s="22" t="inlineStr"/>
-      <c r="P36" s="22" t="inlineStr"/>
-      <c r="Q36" s="22" t="inlineStr"/>
-      <c r="R36" s="22" t="inlineStr"/>
-      <c r="S36" s="23" t="inlineStr"/>
-      <c r="T36" s="22" t="inlineStr"/>
-      <c r="U36" s="22" t="inlineStr">
+      <c r="O36" s="20" t="inlineStr"/>
+      <c r="P36" s="20" t="inlineStr"/>
+      <c r="Q36" s="20" t="inlineStr"/>
+      <c r="R36" s="21" t="inlineStr"/>
+      <c r="S36" s="20" t="inlineStr"/>
+      <c r="T36" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V36" s="22" t="inlineStr">
+      <c r="U36" s="20" t="inlineStr">
         <is>
           <t>SAINOUX</t>
         </is>
       </c>
-      <c r="W36" s="22" t="inlineStr">
+      <c r="V36" s="20" t="inlineStr">
         <is>
           <t>Laurent, Pascal, Eugène</t>
         </is>
       </c>
-      <c r="X36" s="22" t="inlineStr">
+      <c r="W36" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y36" s="22" t="inlineStr">
+      <c r="X36" s="20" t="inlineStr">
         <is>
           <t>80 rue du Général de Gaulle</t>
         </is>
       </c>
-      <c r="Z36" s="23" t="inlineStr">
+      <c r="Y36" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="AA36" s="22" t="inlineStr">
+      <c r="Z36" s="20" t="inlineStr">
         <is>
           <t>Longeville-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>483597050</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>48359705000010</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>LA JEEP</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>LA JEEP</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>Société en nom collectif</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>02/01/2005</t>
         </is>
       </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="K37" s="22" t="inlineStr">
+      <c r="K37" s="20" t="inlineStr">
         <is>
           <t>3 B RUE VAUBAN</t>
         </is>
       </c>
-      <c r="L37" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M37" s="22" t="inlineStr">
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N37" s="22" t="inlineStr">
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O37" s="22" t="inlineStr"/>
-      <c r="P37" s="22" t="inlineStr"/>
-      <c r="Q37" s="22" t="inlineStr"/>
-      <c r="R37" s="22" t="inlineStr"/>
-      <c r="S37" s="23" t="inlineStr"/>
-      <c r="T37" s="22" t="inlineStr"/>
-      <c r="U37" s="22" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr"/>
+      <c r="P37" s="20" t="inlineStr"/>
+      <c r="Q37" s="20" t="inlineStr"/>
+      <c r="R37" s="21" t="inlineStr"/>
+      <c r="S37" s="20" t="inlineStr"/>
+      <c r="T37" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V37" s="22" t="inlineStr">
+      <c r="U37" s="20" t="inlineStr">
         <is>
           <t>OBRANIAK</t>
         </is>
       </c>
-      <c r="W37" s="22" t="inlineStr">
+      <c r="V37" s="20" t="inlineStr">
         <is>
           <t>Gerard</t>
         </is>
       </c>
-      <c r="X37" s="22" t="inlineStr">
+      <c r="W37" s="20" t="inlineStr">
         <is>
           <t>Gérant, Associé indéfiniment responsable</t>
         </is>
       </c>
-      <c r="Y37" s="22" t="inlineStr">
+      <c r="X37" s="20" t="inlineStr">
         <is>
           <t>13 rue de la Carochiere</t>
         </is>
       </c>
-      <c r="Z37" s="23" t="inlineStr">
+      <c r="Y37" s="21" t="inlineStr">
         <is>
           <t>57530</t>
         </is>
       </c>
-      <c r="AA37" s="22" t="inlineStr">
+      <c r="Z37" s="20" t="inlineStr">
         <is>
           <t>Pange</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>435082797</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>43508279700018</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>ISLAMABAD</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>ISLAMABAD</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>09/03/2001</t>
         </is>
       </c>
-      <c r="J38" s="22" t="inlineStr">
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="K38" s="22" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>92 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M38" s="22" t="inlineStr">
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N38" s="22" t="inlineStr">
+      <c r="N38" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O38" s="22" t="n">
-        <v>145217</v>
-      </c>
-      <c r="P38" s="22" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q38" s="22" t="n">
-        <v>19490</v>
-      </c>
-      <c r="R38" s="22" t="inlineStr"/>
-      <c r="S38" s="23" t="inlineStr"/>
-      <c r="T38" s="22" t="inlineStr"/>
-      <c r="U38" s="22" t="inlineStr">
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>145217</t>
+        </is>
+      </c>
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q38" s="20" t="inlineStr"/>
+      <c r="R38" s="21" t="inlineStr"/>
+      <c r="S38" s="20" t="inlineStr"/>
+      <c r="T38" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V38" s="22" t="inlineStr">
+      <c r="U38" s="20" t="inlineStr">
         <is>
           <t>BHATTI</t>
         </is>
       </c>
-      <c r="W38" s="22" t="inlineStr">
+      <c r="V38" s="20" t="inlineStr">
         <is>
           <t>Mohammad, Javed</t>
         </is>
       </c>
-      <c r="X38" s="22" t="inlineStr">
+      <c r="W38" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y38" s="22" t="inlineStr">
+      <c r="X38" s="20" t="inlineStr">
         <is>
           <t>9 rue Gauthey</t>
         </is>
       </c>
-      <c r="Z38" s="23" t="inlineStr">
+      <c r="Y38" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA38" s="22" t="inlineStr">
+      <c r="Z38" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>428958516</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>42895851600026</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>L'ASSIETTE DU BISTROT</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>L'ASSIETTE DU BISTROT</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>12/01/2000</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="J39" s="20" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="K39" s="22" t="inlineStr">
+      <c r="K39" s="20" t="inlineStr">
         <is>
           <t>9 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L39" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M39" s="22" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N39" s="22" t="inlineStr">
+      <c r="N39" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O39" s="22" t="inlineStr"/>
-      <c r="P39" s="22" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Q39" s="22" t="n">
-        <v>33773</v>
-      </c>
-      <c r="R39" s="22" t="inlineStr"/>
-      <c r="S39" s="23" t="inlineStr"/>
-      <c r="T39" s="22" t="inlineStr"/>
-      <c r="U39" s="22" t="inlineStr">
+      <c r="O39" s="20" t="inlineStr"/>
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q39" s="20" t="inlineStr"/>
+      <c r="R39" s="21" t="inlineStr"/>
+      <c r="S39" s="20" t="inlineStr"/>
+      <c r="T39" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V39" s="22" t="inlineStr">
+      <c r="U39" s="20" t="inlineStr">
         <is>
           <t>ENGEL</t>
         </is>
       </c>
-      <c r="W39" s="22" t="inlineStr">
+      <c r="V39" s="20" t="inlineStr">
         <is>
           <t>Gérald</t>
         </is>
       </c>
-      <c r="X39" s="22" t="inlineStr">
+      <c r="W39" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y39" s="22" t="inlineStr">
+      <c r="X39" s="20" t="inlineStr">
         <is>
           <t>45 rue de France</t>
         </is>
       </c>
-      <c r="Z39" s="23" t="inlineStr">
+      <c r="Y39" s="21" t="inlineStr">
         <is>
           <t>57280</t>
         </is>
       </c>
-      <c r="AA39" s="22" t="inlineStr">
+      <c r="Z39" s="20" t="inlineStr">
         <is>
           <t>Maizières-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>908885643</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>90888564300027</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>VILLA PREZIOSA</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>VILLA PREZIOSA</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I40" s="22" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
         <is>
           <t>03/01/2022</t>
         </is>
       </c>
-      <c r="J40" s="22" t="inlineStr">
+      <c r="J40" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K40" s="22" t="inlineStr">
+      <c r="K40" s="20" t="inlineStr">
         <is>
           <t>32 RUE DU COETLOSQUET</t>
         </is>
       </c>
-      <c r="L40" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M40" s="22" t="inlineStr">
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M40" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N40" s="22" t="inlineStr">
+      <c r="N40" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O40" s="22" t="inlineStr"/>
-      <c r="P40" s="22" t="inlineStr"/>
-      <c r="Q40" s="22" t="inlineStr"/>
-      <c r="R40" s="22" t="inlineStr"/>
-      <c r="S40" s="23" t="inlineStr"/>
-      <c r="T40" s="22" t="inlineStr"/>
-      <c r="U40" s="22" t="inlineStr">
+      <c r="O40" s="20" t="inlineStr"/>
+      <c r="P40" s="20" t="inlineStr"/>
+      <c r="Q40" s="20" t="inlineStr"/>
+      <c r="R40" s="21" t="inlineStr"/>
+      <c r="S40" s="20" t="inlineStr"/>
+      <c r="T40" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V40" s="22" t="inlineStr">
+      <c r="U40" s="20" t="inlineStr">
         <is>
           <t>PREZIOSA</t>
         </is>
       </c>
-      <c r="W40" s="22" t="inlineStr">
+      <c r="V40" s="20" t="inlineStr">
         <is>
           <t>Lucas</t>
         </is>
       </c>
-      <c r="X40" s="22" t="inlineStr">
+      <c r="W40" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y40" s="22" t="inlineStr"/>
-      <c r="Z40" s="23" t="inlineStr">
+      <c r="X40" s="20" t="inlineStr"/>
+      <c r="Y40" s="21" t="inlineStr">
         <is>
           <t>57180</t>
         </is>
       </c>
-      <c r="AA40" s="22" t="inlineStr">
+      <c r="Z40" s="20" t="inlineStr">
         <is>
           <t>Terville</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>814544425</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>81454442500030</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>JOULEAR</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>JOULEAR</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>19/11/2015</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K41" s="22" t="inlineStr">
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>65 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M41" s="22" t="inlineStr">
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M41" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N41" s="22" t="inlineStr">
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O41" s="22" t="inlineStr"/>
-      <c r="P41" s="22" t="inlineStr"/>
-      <c r="Q41" s="22" t="inlineStr"/>
-      <c r="R41" s="22" t="inlineStr"/>
-      <c r="S41" s="23" t="inlineStr"/>
-      <c r="T41" s="22" t="inlineStr"/>
-      <c r="U41" s="22" t="inlineStr">
+      <c r="O41" s="20" t="inlineStr"/>
+      <c r="P41" s="20" t="inlineStr"/>
+      <c r="Q41" s="20" t="inlineStr"/>
+      <c r="R41" s="21" t="inlineStr"/>
+      <c r="S41" s="20" t="inlineStr"/>
+      <c r="T41" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V41" s="22" t="inlineStr">
+      <c r="U41" s="20" t="inlineStr">
         <is>
           <t>CARDI</t>
         </is>
       </c>
-      <c r="W41" s="22" t="inlineStr">
+      <c r="V41" s="20" t="inlineStr">
         <is>
           <t>Antoine</t>
         </is>
       </c>
-      <c r="X41" s="22" t="inlineStr">
+      <c r="W41" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y41" s="22" t="inlineStr">
+      <c r="X41" s="20" t="inlineStr">
         <is>
           <t>149 rue saint ladre</t>
         </is>
       </c>
-      <c r="Z41" s="23" t="inlineStr">
+      <c r="Y41" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="AA41" s="22" t="inlineStr">
+      <c r="Z41" s="20" t="inlineStr">
         <is>
           <t>Montigny-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>902893064</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>90289306400011</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>O PETIT JAPON</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>O PETIT JAPON</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>06/08/2021</t>
         </is>
       </c>
-      <c r="J42" s="22" t="inlineStr">
+      <c r="J42" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K42" s="22" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>2 RUE HARELLE</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M42" s="22" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M42" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N42" s="22" t="inlineStr">
+      <c r="N42" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O42" s="22" t="inlineStr"/>
-      <c r="P42" s="22" t="inlineStr"/>
-      <c r="Q42" s="22" t="inlineStr"/>
-      <c r="R42" s="22" t="inlineStr"/>
-      <c r="S42" s="23" t="inlineStr"/>
-      <c r="T42" s="22" t="inlineStr"/>
-      <c r="U42" s="22" t="inlineStr">
+      <c r="O42" s="20" t="inlineStr"/>
+      <c r="P42" s="20" t="inlineStr"/>
+      <c r="Q42" s="20" t="inlineStr"/>
+      <c r="R42" s="21" t="inlineStr"/>
+      <c r="S42" s="20" t="inlineStr"/>
+      <c r="T42" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V42" s="22" t="inlineStr">
+      <c r="U42" s="20" t="inlineStr">
         <is>
           <t>VITTECOQ</t>
         </is>
       </c>
-      <c r="W42" s="22" t="inlineStr">
+      <c r="V42" s="20" t="inlineStr">
         <is>
           <t>Carole</t>
         </is>
       </c>
-      <c r="X42" s="22" t="inlineStr">
+      <c r="W42" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y42" s="22" t="inlineStr">
+      <c r="X42" s="20" t="inlineStr">
         <is>
           <t>2 Rue de Metz</t>
         </is>
       </c>
-      <c r="Z42" s="23" t="inlineStr">
+      <c r="Y42" s="21" t="inlineStr">
         <is>
           <t>57300</t>
         </is>
       </c>
-      <c r="AA42" s="22" t="inlineStr">
+      <c r="Z42" s="20" t="inlineStr">
         <is>
           <t>Ay-sur-Moselle</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>830269734</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>83026973400018</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>BOCK RESTAURATION</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>BOCK RESTAURATION</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t>01/08/2017</t>
         </is>
       </c>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="J43" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K43" s="22" t="inlineStr">
+      <c r="K43" s="20" t="inlineStr">
         <is>
           <t>RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L43" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M43" s="22" t="inlineStr">
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M43" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N43" s="22" t="inlineStr">
+      <c r="N43" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O43" s="22" t="n">
-        <v>987035</v>
-      </c>
-      <c r="P43" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q43" s="22" t="n">
-        <v>5943</v>
-      </c>
-      <c r="R43" s="22" t="inlineStr"/>
-      <c r="S43" s="23" t="inlineStr"/>
-      <c r="T43" s="22" t="inlineStr"/>
-      <c r="U43" s="22" t="inlineStr">
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>987035</t>
+        </is>
+      </c>
+      <c r="P43" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q43" s="20" t="inlineStr"/>
+      <c r="R43" s="21" t="inlineStr"/>
+      <c r="S43" s="20" t="inlineStr"/>
+      <c r="T43" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V43" s="22" t="inlineStr">
+      <c r="U43" s="20" t="inlineStr">
         <is>
           <t>NI-NO BOCK INVESTISSEMENT</t>
         </is>
       </c>
-      <c r="W43" s="22" t="inlineStr"/>
-      <c r="X43" s="22" t="inlineStr">
+      <c r="V43" s="20" t="inlineStr"/>
+      <c r="W43" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y43" s="22" t="inlineStr">
+      <c r="X43" s="20" t="inlineStr">
         <is>
           <t>7 rue Marie Laurencin</t>
         </is>
       </c>
-      <c r="Z43" s="23" t="inlineStr">
+      <c r="Y43" s="21" t="inlineStr">
         <is>
           <t>54510</t>
         </is>
       </c>
-      <c r="AA43" s="22" t="inlineStr">
+      <c r="Z43" s="20" t="inlineStr">
         <is>
           <t>Tomblaine</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>380617886</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>38061788600060</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>CAPPAERT Philippe</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>CAPPAERT Philippe</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I44" s="20" t="inlineStr">
         <is>
           <t>02/01/1991</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="J44" s="20" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr">
+      <c r="K44" s="20" t="inlineStr">
         <is>
           <t>33 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="L44" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M44" s="22" t="inlineStr">
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M44" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N44" s="22" t="inlineStr">
+      <c r="N44" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O44" s="22" t="inlineStr"/>
-      <c r="P44" s="22" t="inlineStr"/>
-      <c r="Q44" s="22" t="inlineStr"/>
-      <c r="R44" s="22" t="inlineStr"/>
-      <c r="S44" s="23" t="inlineStr"/>
-      <c r="T44" s="22" t="inlineStr"/>
-      <c r="U44" s="22" t="inlineStr">
+      <c r="O44" s="20" t="inlineStr"/>
+      <c r="P44" s="20" t="inlineStr"/>
+      <c r="Q44" s="20" t="inlineStr"/>
+      <c r="R44" s="21" t="inlineStr"/>
+      <c r="S44" s="20" t="inlineStr"/>
+      <c r="T44" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V44" s="22" t="inlineStr">
+      <c r="U44" s="20" t="inlineStr">
         <is>
           <t>CAPPAERT</t>
         </is>
       </c>
-      <c r="W44" s="22" t="inlineStr">
+      <c r="V44" s="20" t="inlineStr">
         <is>
           <t>Philippe, Jean, Albert</t>
         </is>
       </c>
-      <c r="X44" s="22" t="inlineStr">
+      <c r="W44" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="Y44" s="22" t="inlineStr"/>
-      <c r="Z44" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA44" s="22" t="inlineStr">
+      <c r="X44" s="20" t="inlineStr"/>
+      <c r="Y44" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z44" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>500056858</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>50005685800011</t>
         </is>
       </c>
-      <c r="D45" s="22" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>MACOVA</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>MACOVA</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I45" s="22" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>01/10/2007</t>
         </is>
       </c>
-      <c r="J45" s="22" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="K45" s="22" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>11 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L45" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M45" s="22" t="inlineStr">
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N45" s="22" t="inlineStr">
+      <c r="N45" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O45" s="22" t="inlineStr"/>
-      <c r="P45" s="22" t="inlineStr"/>
-      <c r="Q45" s="22" t="inlineStr"/>
-      <c r="R45" s="22" t="inlineStr"/>
-      <c r="S45" s="23" t="inlineStr"/>
-      <c r="T45" s="22" t="inlineStr"/>
-      <c r="U45" s="22" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr"/>
+      <c r="P45" s="20" t="inlineStr"/>
+      <c r="Q45" s="20" t="inlineStr"/>
+      <c r="R45" s="21" t="inlineStr"/>
+      <c r="S45" s="20" t="inlineStr"/>
+      <c r="T45" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V45" s="22" t="inlineStr">
+      <c r="U45" s="20" t="inlineStr">
         <is>
           <t>MARQUET</t>
         </is>
       </c>
-      <c r="W45" s="22" t="inlineStr">
+      <c r="V45" s="20" t="inlineStr">
         <is>
           <t>Cynthia</t>
         </is>
       </c>
-      <c r="X45" s="22" t="inlineStr">
+      <c r="W45" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="Y45" s="22" t="inlineStr">
+      <c r="X45" s="20" t="inlineStr">
         <is>
           <t>4 rue Montplaisir</t>
         </is>
       </c>
-      <c r="Z45" s="23" t="inlineStr">
+      <c r="Y45" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="AA45" s="22" t="inlineStr">
+      <c r="Z45" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>820527968</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>82052796800011</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>PASTA MERY BAR</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>PASTA MERY BAR</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I46" s="22" t="inlineStr">
+      <c r="I46" s="20" t="inlineStr">
         <is>
           <t>26/05/2016</t>
         </is>
       </c>
-      <c r="J46" s="22" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K46" s="22" t="inlineStr">
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>3 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L46" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M46" s="22" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M46" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N46" s="22" t="inlineStr">
+      <c r="N46" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O46" s="22" t="inlineStr"/>
-      <c r="P46" s="22" t="inlineStr"/>
-      <c r="Q46" s="22" t="inlineStr"/>
-      <c r="R46" s="22" t="inlineStr"/>
-      <c r="S46" s="23" t="inlineStr"/>
-      <c r="T46" s="22" t="inlineStr"/>
-      <c r="U46" s="22" t="inlineStr">
+      <c r="O46" s="20" t="inlineStr"/>
+      <c r="P46" s="20" t="inlineStr"/>
+      <c r="Q46" s="20" t="inlineStr"/>
+      <c r="R46" s="21" t="inlineStr"/>
+      <c r="S46" s="20" t="inlineStr"/>
+      <c r="T46" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V46" s="22" t="inlineStr">
+      <c r="U46" s="20" t="inlineStr">
         <is>
           <t>EL ALAMI</t>
         </is>
       </c>
-      <c r="W46" s="22" t="inlineStr">
+      <c r="V46" s="20" t="inlineStr">
         <is>
           <t>Youness</t>
         </is>
       </c>
-      <c r="X46" s="22" t="inlineStr">
+      <c r="W46" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="Y46" s="22" t="inlineStr">
+      <c r="X46" s="20" t="inlineStr">
         <is>
           <t>69 rue des Allemands</t>
         </is>
       </c>
-      <c r="Z46" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA46" s="22" t="inlineStr">
+      <c r="Y46" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z46" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>451081251</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>45108125100014</t>
         </is>
       </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>HORODNYJ Thierry</t>
         </is>
       </c>
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>HORODNYJ Thierry</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I47" s="22" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>24/09/2003</t>
         </is>
       </c>
-      <c r="J47" s="22" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K47" s="22" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>33 RUE VIGNE SAINT-AVOLD</t>
         </is>
       </c>
-      <c r="L47" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M47" s="22" t="inlineStr">
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N47" s="22" t="inlineStr">
+      <c r="N47" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O47" s="22" t="inlineStr"/>
-      <c r="P47" s="22" t="inlineStr"/>
-      <c r="Q47" s="22" t="inlineStr"/>
-      <c r="R47" s="22" t="inlineStr"/>
-      <c r="S47" s="23" t="inlineStr"/>
-      <c r="T47" s="22" t="inlineStr"/>
-      <c r="U47" s="22" t="inlineStr">
+      <c r="O47" s="20" t="inlineStr"/>
+      <c r="P47" s="20" t="inlineStr"/>
+      <c r="Q47" s="20" t="inlineStr"/>
+      <c r="R47" s="21" t="inlineStr"/>
+      <c r="S47" s="20" t="inlineStr"/>
+      <c r="T47" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="V47" s="22" t="inlineStr">
+      <c r="U47" s="20" t="inlineStr">
         <is>
           <t>HORODNYJ</t>
         </is>
       </c>
-      <c r="W47" s="22" t="inlineStr">
+      <c r="V47" s="20" t="inlineStr">
         <is>
           <t>Thierry, Bernard</t>
         </is>
       </c>
-      <c r="X47" s="22" t="inlineStr">
+      <c r="W47" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="Y47" s="22" t="inlineStr"/>
-      <c r="Z47" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="AA47" s="22" t="inlineStr">
+      <c r="X47" s="20" t="inlineStr"/>
+      <c r="Y47" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z47" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>839551389</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>83955138900035</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>AHMED AMER</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>AHMED AMER</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>01/05/2018</t>
+        </is>
+      </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K48" s="22" t="inlineStr">
+        <is>
+          <t>29 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L48" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M48" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N48" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O48" s="22" t="inlineStr"/>
+      <c r="P48" s="22" t="inlineStr"/>
+      <c r="Q48" s="22" t="inlineStr"/>
+      <c r="R48" s="23" t="inlineStr"/>
+      <c r="S48" s="22" t="inlineStr"/>
+      <c r="T48" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U48" s="22" t="inlineStr">
+        <is>
+          <t>AHMED</t>
+        </is>
+      </c>
+      <c r="V48" s="22" t="inlineStr">
+        <is>
+          <t>Amer</t>
+        </is>
+      </c>
+      <c r="W48" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X48" s="22" t="inlineStr"/>
+      <c r="Y48" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z48" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>850375502</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>85037550200018</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I49" s="22" t="inlineStr">
+        <is>
+          <t>25/04/2019</t>
+        </is>
+      </c>
+      <c r="J49" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K49" s="22" t="inlineStr">
+        <is>
+          <t>26 AVENUE FOCH</t>
+        </is>
+      </c>
+      <c r="L49" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M49" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N49" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O49" s="22" t="inlineStr"/>
+      <c r="P49" s="22" t="inlineStr"/>
+      <c r="Q49" s="22" t="inlineStr"/>
+      <c r="R49" s="23" t="inlineStr"/>
+      <c r="S49" s="22" t="inlineStr"/>
+      <c r="T49" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U49" s="22" t="inlineStr">
+        <is>
+          <t>MARCHAL</t>
+        </is>
+      </c>
+      <c r="V49" s="22" t="inlineStr">
+        <is>
+          <t>Valentin</t>
+        </is>
+      </c>
+      <c r="W49" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X49" s="22" t="inlineStr">
+        <is>
+          <t>26 avenue foch</t>
+        </is>
+      </c>
+      <c r="Y49" s="23" t="inlineStr">
+        <is>
+          <t>57680</t>
+        </is>
+      </c>
+      <c r="Z49" s="22" t="inlineStr">
+        <is>
+          <t>Novéant-sur-Moselle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>799995865</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>79999586500026</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>QYMEL</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>QYMEL</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>29/01/2014</t>
+        </is>
+      </c>
+      <c r="J50" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K50" s="22" t="inlineStr">
+        <is>
+          <t>77 RUE AUX ARENES</t>
+        </is>
+      </c>
+      <c r="L50" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M50" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N50" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O50" s="22" t="inlineStr"/>
+      <c r="P50" s="22" t="inlineStr"/>
+      <c r="Q50" s="22" t="inlineStr"/>
+      <c r="R50" s="23" t="inlineStr"/>
+      <c r="S50" s="22" t="inlineStr"/>
+      <c r="T50" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U50" s="22" t="inlineStr">
+        <is>
+          <t>QUIGNIOT</t>
+        </is>
+      </c>
+      <c r="V50" s="22" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="W50" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X50" s="22" t="inlineStr">
+        <is>
+          <t>44 rue Saint-André</t>
+        </is>
+      </c>
+      <c r="Y50" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z50" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>830443933</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>83044393300015</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>HERBAUX</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>HERBAUX</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="inlineStr">
+        <is>
+          <t>22/06/2017</t>
+        </is>
+      </c>
+      <c r="J51" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K51" s="22" t="inlineStr">
+        <is>
+          <t>30 RUE CLOVIS</t>
+        </is>
+      </c>
+      <c r="L51" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M51" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N51" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O51" s="22" t="inlineStr"/>
+      <c r="P51" s="22" t="inlineStr"/>
+      <c r="Q51" s="22" t="inlineStr"/>
+      <c r="R51" s="23" t="inlineStr"/>
+      <c r="S51" s="22" t="inlineStr"/>
+      <c r="T51" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U51" s="22" t="inlineStr">
+        <is>
+          <t>CAILLARD</t>
+        </is>
+      </c>
+      <c r="V51" s="22" t="inlineStr">
+        <is>
+          <t>Stéphane, Jacques, Franck, Raymond</t>
+        </is>
+      </c>
+      <c r="W51" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X51" s="22" t="inlineStr">
+        <is>
+          <t>33 chemin de la Noue</t>
+        </is>
+      </c>
+      <c r="Y51" s="23" t="inlineStr">
+        <is>
+          <t>57130</t>
+        </is>
+      </c>
+      <c r="Z51" s="22" t="inlineStr">
+        <is>
+          <t>Vaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>921382453</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>92138245300014</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I52" s="22" t="inlineStr">
+        <is>
+          <t>07/11/2022</t>
+        </is>
+      </c>
+      <c r="J52" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K52" s="22" t="inlineStr">
+        <is>
+          <t>7 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L52" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M52" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N52" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O52" s="22" t="inlineStr"/>
+      <c r="P52" s="22" t="inlineStr"/>
+      <c r="Q52" s="22" t="inlineStr"/>
+      <c r="R52" s="23" t="inlineStr"/>
+      <c r="S52" s="22" t="inlineStr"/>
+      <c r="T52" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U52" s="22" t="inlineStr">
+        <is>
+          <t>BASIN</t>
+        </is>
+      </c>
+      <c r="V52" s="22" t="inlineStr">
+        <is>
+          <t>Billy, Gérard, Denis</t>
+        </is>
+      </c>
+      <c r="W52" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X52" s="22" t="inlineStr"/>
+      <c r="Y52" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z52" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>414294116</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>41429411600036</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>SOJADEX</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>SOJADEX</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I53" s="22" t="inlineStr">
+        <is>
+          <t>01/11/1997</t>
+        </is>
+      </c>
+      <c r="J53" s="22" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="K53" s="22" t="inlineStr">
+        <is>
+          <t>1 AVENUE NEY</t>
+        </is>
+      </c>
+      <c r="L53" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M53" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N53" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O53" s="22" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P53" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q53" s="22" t="inlineStr"/>
+      <c r="R53" s="23" t="inlineStr"/>
+      <c r="S53" s="22" t="inlineStr"/>
+      <c r="T53" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U53" s="22" t="inlineStr">
+        <is>
+          <t>JARDINE</t>
+        </is>
+      </c>
+      <c r="V53" s="22" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="W53" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X53" s="22" t="inlineStr">
+        <is>
+          <t>4 rue des Bergeronnettes</t>
+        </is>
+      </c>
+      <c r="Y53" s="23" t="inlineStr">
+        <is>
+          <t>57120</t>
+        </is>
+      </c>
+      <c r="Z53" s="22" t="inlineStr">
+        <is>
+          <t>Rombas</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>106340490</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>10634049000015</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>YASAF</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>YASAF</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I54" s="22" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="J54" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K54" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L54" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M54" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N54" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O54" s="22" t="inlineStr"/>
+      <c r="P54" s="22" t="inlineStr"/>
+      <c r="Q54" s="22" t="inlineStr"/>
+      <c r="R54" s="23" t="inlineStr"/>
+      <c r="S54" s="22" t="inlineStr"/>
+      <c r="T54" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U54" s="22" t="inlineStr">
+        <is>
+          <t>AIOUN</t>
+        </is>
+      </c>
+      <c r="V54" s="22" t="inlineStr">
+        <is>
+          <t>Younes</t>
+        </is>
+      </c>
+      <c r="W54" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X54" s="22" t="inlineStr"/>
+      <c r="Y54" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z54" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>982266702</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>98226670200017</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>STAGNO WASANA</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>STAGNO WASANA</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="inlineStr">
+        <is>
+          <t>04/01/2024</t>
+        </is>
+      </c>
+      <c r="J55" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K55" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE PIERRE MAURICE MASSON</t>
+        </is>
+      </c>
+      <c r="L55" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M55" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N55" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O55" s="22" t="inlineStr"/>
+      <c r="P55" s="22" t="inlineStr"/>
+      <c r="Q55" s="22" t="inlineStr"/>
+      <c r="R55" s="23" t="inlineStr"/>
+      <c r="S55" s="22" t="inlineStr"/>
+      <c r="T55" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U55" s="22" t="inlineStr">
+        <is>
+          <t>TUNKONG</t>
+        </is>
+      </c>
+      <c r="V55" s="22" t="inlineStr">
+        <is>
+          <t>Wasana</t>
+        </is>
+      </c>
+      <c r="W55" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X55" s="22" t="inlineStr"/>
+      <c r="Y55" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z55" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>934358284</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>93435828400016</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>LONGHI-WELFRINGER Elisa</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>LONGHI-WELFRINGER Elisa</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I56" s="22" t="inlineStr">
+        <is>
+          <t>17/10/2024</t>
+        </is>
+      </c>
+      <c r="J56" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K56" s="22" t="inlineStr">
+        <is>
+          <t>15 RUE DE LA TETE D'OR</t>
+        </is>
+      </c>
+      <c r="L56" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M56" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N56" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O56" s="22" t="inlineStr"/>
+      <c r="P56" s="22" t="inlineStr"/>
+      <c r="Q56" s="22" t="inlineStr"/>
+      <c r="R56" s="23" t="inlineStr"/>
+      <c r="S56" s="22" t="inlineStr"/>
+      <c r="T56" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U56" s="22" t="inlineStr">
+        <is>
+          <t>LONGHI</t>
+        </is>
+      </c>
+      <c r="V56" s="22" t="inlineStr">
+        <is>
+          <t>Elisa</t>
+        </is>
+      </c>
+      <c r="W56" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X56" s="22" t="inlineStr"/>
+      <c r="Y56" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z56" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>812163772</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>81216377200013</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>SNACK FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>SNACK FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I57" s="22" t="inlineStr">
+        <is>
+          <t>17/06/2015</t>
+        </is>
+      </c>
+      <c r="J57" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K57" s="22" t="inlineStr">
+        <is>
+          <t>7 EN FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="L57" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M57" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N57" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O57" s="22" t="inlineStr"/>
+      <c r="P57" s="22" t="inlineStr"/>
+      <c r="Q57" s="22" t="inlineStr"/>
+      <c r="R57" s="23" t="inlineStr"/>
+      <c r="S57" s="22" t="inlineStr"/>
+      <c r="T57" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U57" s="22" t="inlineStr">
+        <is>
+          <t>REZAOUI</t>
+        </is>
+      </c>
+      <c r="V57" s="22" t="inlineStr">
+        <is>
+          <t>Tarik</t>
+        </is>
+      </c>
+      <c r="W57" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X57" s="22" t="inlineStr">
+        <is>
+          <t>10 rue Nicolas Jung</t>
+        </is>
+      </c>
+      <c r="Y57" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z57" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>993730621</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>99373062100014</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>MISTER CHICKEN</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>MISTER CHICKEN</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I58" s="22" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="J58" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K58" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L58" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M58" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N58" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O58" s="22" t="inlineStr"/>
+      <c r="P58" s="22" t="inlineStr"/>
+      <c r="Q58" s="22" t="inlineStr"/>
+      <c r="R58" s="23" t="inlineStr"/>
+      <c r="S58" s="22" t="inlineStr"/>
+      <c r="T58" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U58" s="22" t="inlineStr">
+        <is>
+          <t>HOLDING MB</t>
+        </is>
+      </c>
+      <c r="V58" s="22" t="inlineStr"/>
+      <c r="W58" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X58" s="22" t="inlineStr">
+        <is>
+          <t>79 RUE Saint Georges</t>
+        </is>
+      </c>
+      <c r="Y58" s="23" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="Z58" s="22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>914736202</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>91473620200021</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>ZINE</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>ZINE</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I59" s="22" t="inlineStr">
+        <is>
+          <t>21/06/2022</t>
+        </is>
+      </c>
+      <c r="J59" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K59" s="22" t="inlineStr">
+        <is>
+          <t>10 B RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L59" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M59" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N59" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O59" s="22" t="n">
+        <v>882795</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q59" s="22" t="inlineStr"/>
+      <c r="R59" s="23" t="inlineStr"/>
+      <c r="S59" s="22" t="inlineStr"/>
+      <c r="T59" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U59" s="22" t="inlineStr">
+        <is>
+          <t>GERARD</t>
+        </is>
+      </c>
+      <c r="V59" s="22" t="inlineStr">
+        <is>
+          <t>Alexis, Serge, Henri, Marcel</t>
+        </is>
+      </c>
+      <c r="W59" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X59" s="22" t="inlineStr">
+        <is>
+          <t>12 Rue Charlemagne</t>
+        </is>
+      </c>
+      <c r="Y59" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z59" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>848149449</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>84814944900011</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>DELICE PIZZA</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>DELICE PIZZA</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>04/02/2019</t>
+        </is>
+      </c>
+      <c r="J60" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K60" s="22" t="inlineStr">
+        <is>
+          <t>19 PLACE DES CHARRONS</t>
+        </is>
+      </c>
+      <c r="L60" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M60" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N60" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O60" s="22" t="inlineStr"/>
+      <c r="P60" s="22" t="inlineStr"/>
+      <c r="Q60" s="22" t="inlineStr"/>
+      <c r="R60" s="23" t="inlineStr"/>
+      <c r="S60" s="22" t="inlineStr"/>
+      <c r="T60" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U60" s="22" t="inlineStr">
+        <is>
+          <t>MSADEK</t>
+        </is>
+      </c>
+      <c r="V60" s="22" t="inlineStr">
+        <is>
+          <t>Amine</t>
+        </is>
+      </c>
+      <c r="W60" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X60" s="22" t="inlineStr">
+        <is>
+          <t>1 Ruelle Saint-michel</t>
+        </is>
+      </c>
+      <c r="Y60" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z60" s="22" t="inlineStr">
+        <is>
+          <t>Plappeville</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>942018656</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>94201865600028</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr">
+        <is>
+          <t>MADAME JEAN</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>MADAME JEAN</t>
+        </is>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I61" s="22" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="J61" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K61" s="22" t="inlineStr">
+        <is>
+          <t>7 RUE DUPONT DES LOGES</t>
+        </is>
+      </c>
+      <c r="L61" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M61" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N61" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O61" s="22" t="inlineStr"/>
+      <c r="P61" s="22" t="inlineStr"/>
+      <c r="Q61" s="22" t="inlineStr"/>
+      <c r="R61" s="23" t="inlineStr"/>
+      <c r="S61" s="22" t="inlineStr"/>
+      <c r="T61" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U61" s="22" t="inlineStr">
+        <is>
+          <t>RENOUARD</t>
+        </is>
+      </c>
+      <c r="V61" s="22" t="inlineStr">
+        <is>
+          <t>Adeline</t>
+        </is>
+      </c>
+      <c r="W61" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X61" s="22" t="inlineStr">
+        <is>
+          <t>8 rue des Parmentiers</t>
+        </is>
+      </c>
+      <c r="Y61" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z61" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>833114796</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>83311479600026</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>VI &amp; VI</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>VI &amp; VI</t>
+        </is>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2017</t>
+        </is>
+      </c>
+      <c r="J62" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K62" s="22" t="inlineStr">
+        <is>
+          <t>CTRE COMMERCIAL ST JACQUES</t>
+        </is>
+      </c>
+      <c r="L62" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M62" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N62" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O62" s="22" t="inlineStr"/>
+      <c r="P62" s="22" t="inlineStr"/>
+      <c r="Q62" s="22" t="inlineStr"/>
+      <c r="R62" s="23" t="inlineStr"/>
+      <c r="S62" s="22" t="inlineStr"/>
+      <c r="T62" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U62" s="22" t="inlineStr">
+        <is>
+          <t>TRAN</t>
+        </is>
+      </c>
+      <c r="V62" s="22" t="inlineStr">
+        <is>
+          <t>Thanh, Thu, Ha</t>
+        </is>
+      </c>
+      <c r="W62" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X62" s="22" t="inlineStr">
+        <is>
+          <t>2 boulevard Robert Schuman</t>
+        </is>
+      </c>
+      <c r="Y62" s="23" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="Z62" s="22" t="inlineStr">
+        <is>
+          <t>Thionville</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>939927034</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>93992703400016</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>PETRALITO EDUARDO</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>PETRALITO EDUARDO</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>22/01/2025</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K63" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE GOUVY</t>
+        </is>
+      </c>
+      <c r="L63" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M63" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N63" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O63" s="22" t="inlineStr"/>
+      <c r="P63" s="22" t="inlineStr"/>
+      <c r="Q63" s="22" t="inlineStr"/>
+      <c r="R63" s="23" t="inlineStr"/>
+      <c r="S63" s="22" t="inlineStr"/>
+      <c r="T63" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U63" s="22" t="inlineStr">
+        <is>
+          <t>PETRALITO</t>
+        </is>
+      </c>
+      <c r="V63" s="22" t="inlineStr">
+        <is>
+          <t>Eduardo, Salvatore, Antonio</t>
+        </is>
+      </c>
+      <c r="W63" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X63" s="22" t="inlineStr"/>
+      <c r="Y63" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z63" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>879005932</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>87900593200014</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>SCHMIT Sylvie</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>SCHMIT Sylvie</t>
+        </is>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>01/11/2019</t>
+        </is>
+      </c>
+      <c r="J64" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K64" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DU PAS DU LOUP</t>
+        </is>
+      </c>
+      <c r="L64" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M64" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N64" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O64" s="22" t="inlineStr"/>
+      <c r="P64" s="22" t="inlineStr"/>
+      <c r="Q64" s="22" t="inlineStr"/>
+      <c r="R64" s="23" t="inlineStr"/>
+      <c r="S64" s="22" t="inlineStr"/>
+      <c r="T64" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U64" s="22" t="inlineStr">
+        <is>
+          <t>SCHMIT</t>
+        </is>
+      </c>
+      <c r="V64" s="22" t="inlineStr">
+        <is>
+          <t>Sylvie, Marie, Andree</t>
+        </is>
+      </c>
+      <c r="W64" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X64" s="22" t="inlineStr"/>
+      <c r="Y64" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z64" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>851264903</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>85126490300010</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr">
+        <is>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>03/06/2019</t>
+        </is>
+      </c>
+      <c r="J65" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K65" s="22" t="inlineStr">
+        <is>
+          <t>1 AVENUE NEY</t>
+        </is>
+      </c>
+      <c r="L65" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M65" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N65" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O65" s="22" t="inlineStr"/>
+      <c r="P65" s="22" t="inlineStr"/>
+      <c r="Q65" s="22" t="inlineStr"/>
+      <c r="R65" s="23" t="inlineStr"/>
+      <c r="S65" s="22" t="inlineStr"/>
+      <c r="T65" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U65" s="22" t="inlineStr">
+        <is>
+          <t>HOANG</t>
+        </is>
+      </c>
+      <c r="V65" s="22" t="inlineStr">
+        <is>
+          <t>Thi, Anh, Thu</t>
+        </is>
+      </c>
+      <c r="W65" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X65" s="22" t="inlineStr">
+        <is>
+          <t>36 rue des Framboises</t>
+        </is>
+      </c>
+      <c r="Y65" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z65" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>830488037</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>83048803700011</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>MD DIFFUSION</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>MD DIFFUSION</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>15/05/2017</t>
+        </is>
+      </c>
+      <c r="J66" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="inlineStr">
+        <is>
+          <t>43 RUE DE POUILLY</t>
+        </is>
+      </c>
+      <c r="L66" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N66" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O66" s="22" t="inlineStr"/>
+      <c r="P66" s="22" t="inlineStr"/>
+      <c r="Q66" s="22" t="inlineStr"/>
+      <c r="R66" s="23" t="inlineStr"/>
+      <c r="S66" s="22" t="inlineStr"/>
+      <c r="T66" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U66" s="22" t="inlineStr">
+        <is>
+          <t>CAPIZZI</t>
+        </is>
+      </c>
+      <c r="V66" s="22" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="W66" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X66" s="22" t="inlineStr">
+        <is>
+          <t>43 rue de Pouilly</t>
+        </is>
+      </c>
+      <c r="Y66" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z66" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>952396885</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>95239688500024</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>SAS MAGIRA</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>SAS MAGIRA</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>05/05/2023</t>
+        </is>
+      </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K67" s="22" t="inlineStr">
+        <is>
+          <t>32 RUE DE LA TETE D'OR</t>
+        </is>
+      </c>
+      <c r="L67" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M67" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N67" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O67" s="22" t="inlineStr"/>
+      <c r="P67" s="22" t="inlineStr"/>
+      <c r="Q67" s="22" t="inlineStr"/>
+      <c r="R67" s="23" t="inlineStr"/>
+      <c r="S67" s="22" t="inlineStr"/>
+      <c r="T67" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U67" s="22" t="inlineStr">
+        <is>
+          <t>ETIENNE</t>
+        </is>
+      </c>
+      <c r="V67" s="22" t="inlineStr">
+        <is>
+          <t>Alexandre, Marcel, Jean-pierre</t>
+        </is>
+      </c>
+      <c r="W67" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X67" s="22" t="inlineStr">
+        <is>
+          <t>10 Rue des Fauvettes</t>
+        </is>
+      </c>
+      <c r="Y67" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z67" s="22" t="inlineStr">
+        <is>
+          <t>Lorry-lès-Metz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AA47"/>
+  <autoFilter ref="A2:Z67"/>
   <mergeCells count="6">
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="R1:U1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5866,2223 +5866,4449 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>839551389</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>83955138900035</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>AHMED AMER</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>AHMED AMER</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G48" s="22" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H48" s="22" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I48" s="22" t="inlineStr">
+      <c r="I48" s="20" t="inlineStr">
         <is>
           <t>01/05/2018</t>
         </is>
       </c>
-      <c r="J48" s="22" t="inlineStr">
+      <c r="J48" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K48" s="22" t="inlineStr">
+      <c r="K48" s="20" t="inlineStr">
         <is>
           <t>29 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L48" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M48" s="22" t="inlineStr">
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M48" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N48" s="22" t="inlineStr">
+      <c r="N48" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O48" s="22" t="inlineStr"/>
-      <c r="P48" s="22" t="inlineStr"/>
-      <c r="Q48" s="22" t="inlineStr"/>
-      <c r="R48" s="23" t="inlineStr"/>
-      <c r="S48" s="22" t="inlineStr"/>
-      <c r="T48" s="22" t="inlineStr">
+      <c r="O48" s="20" t="inlineStr"/>
+      <c r="P48" s="20" t="inlineStr"/>
+      <c r="Q48" s="20" t="inlineStr"/>
+      <c r="R48" s="21" t="inlineStr"/>
+      <c r="S48" s="20" t="inlineStr"/>
+      <c r="T48" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U48" s="22" t="inlineStr">
+      <c r="U48" s="20" t="inlineStr">
         <is>
           <t>AHMED</t>
         </is>
       </c>
-      <c r="V48" s="22" t="inlineStr">
+      <c r="V48" s="20" t="inlineStr">
         <is>
           <t>Amer</t>
         </is>
       </c>
-      <c r="W48" s="22" t="inlineStr">
+      <c r="W48" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X48" s="22" t="inlineStr"/>
-      <c r="Y48" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z48" s="22" t="inlineStr">
+      <c r="X48" s="20" t="inlineStr"/>
+      <c r="Y48" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z48" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>850375502</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>85037550200018</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I49" s="22" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
         <is>
           <t>25/04/2019</t>
         </is>
       </c>
-      <c r="J49" s="22" t="inlineStr">
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K49" s="22" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>26 AVENUE FOCH</t>
         </is>
       </c>
-      <c r="L49" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M49" s="22" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N49" s="22" t="inlineStr">
+      <c r="N49" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O49" s="22" t="inlineStr"/>
-      <c r="P49" s="22" t="inlineStr"/>
-      <c r="Q49" s="22" t="inlineStr"/>
-      <c r="R49" s="23" t="inlineStr"/>
-      <c r="S49" s="22" t="inlineStr"/>
-      <c r="T49" s="22" t="inlineStr">
+      <c r="O49" s="20" t="inlineStr"/>
+      <c r="P49" s="20" t="inlineStr"/>
+      <c r="Q49" s="20" t="inlineStr"/>
+      <c r="R49" s="21" t="inlineStr"/>
+      <c r="S49" s="20" t="inlineStr"/>
+      <c r="T49" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U49" s="22" t="inlineStr">
+      <c r="U49" s="20" t="inlineStr">
         <is>
           <t>MARCHAL</t>
         </is>
       </c>
-      <c r="V49" s="22" t="inlineStr">
+      <c r="V49" s="20" t="inlineStr">
         <is>
           <t>Valentin</t>
         </is>
       </c>
-      <c r="W49" s="22" t="inlineStr">
+      <c r="W49" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X49" s="22" t="inlineStr">
+      <c r="X49" s="20" t="inlineStr">
         <is>
           <t>26 avenue foch</t>
         </is>
       </c>
-      <c r="Y49" s="23" t="inlineStr">
+      <c r="Y49" s="21" t="inlineStr">
         <is>
           <t>57680</t>
         </is>
       </c>
-      <c r="Z49" s="22" t="inlineStr">
+      <c r="Z49" s="20" t="inlineStr">
         <is>
           <t>Novéant-sur-Moselle</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>799995865</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>79999586500026</t>
         </is>
       </c>
-      <c r="D50" s="22" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>QYMEL</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>QYMEL</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H50" s="22" t="inlineStr">
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I50" s="22" t="inlineStr">
+      <c r="I50" s="20" t="inlineStr">
         <is>
           <t>29/01/2014</t>
         </is>
       </c>
-      <c r="J50" s="22" t="inlineStr">
+      <c r="J50" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K50" s="22" t="inlineStr">
+      <c r="K50" s="20" t="inlineStr">
         <is>
           <t>77 RUE AUX ARENES</t>
         </is>
       </c>
-      <c r="L50" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M50" s="22" t="inlineStr">
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M50" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N50" s="22" t="inlineStr">
+      <c r="N50" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O50" s="22" t="inlineStr"/>
-      <c r="P50" s="22" t="inlineStr"/>
-      <c r="Q50" s="22" t="inlineStr"/>
-      <c r="R50" s="23" t="inlineStr"/>
-      <c r="S50" s="22" t="inlineStr"/>
-      <c r="T50" s="22" t="inlineStr">
+      <c r="O50" s="20" t="inlineStr"/>
+      <c r="P50" s="20" t="inlineStr"/>
+      <c r="Q50" s="20" t="inlineStr"/>
+      <c r="R50" s="21" t="inlineStr"/>
+      <c r="S50" s="20" t="inlineStr"/>
+      <c r="T50" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U50" s="22" t="inlineStr">
+      <c r="U50" s="20" t="inlineStr">
         <is>
           <t>QUIGNIOT</t>
         </is>
       </c>
-      <c r="V50" s="22" t="inlineStr">
+      <c r="V50" s="20" t="inlineStr">
         <is>
           <t>Erwan</t>
         </is>
       </c>
-      <c r="W50" s="22" t="inlineStr">
+      <c r="W50" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X50" s="22" t="inlineStr">
+      <c r="X50" s="20" t="inlineStr">
         <is>
           <t>44 rue Saint-André</t>
         </is>
       </c>
-      <c r="Y50" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z50" s="22" t="inlineStr">
+      <c r="Y50" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z50" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>830443933</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>83044393300015</t>
         </is>
       </c>
-      <c r="D51" s="22" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>HERBAUX</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>HERBAUX</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G51" s="22" t="inlineStr">
+      <c r="G51" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I51" s="22" t="inlineStr">
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>22/06/2017</t>
         </is>
       </c>
-      <c r="J51" s="22" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K51" s="22" t="inlineStr">
+      <c r="K51" s="20" t="inlineStr">
         <is>
           <t>30 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="L51" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M51" s="22" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N51" s="22" t="inlineStr">
+      <c r="N51" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O51" s="22" t="inlineStr"/>
-      <c r="P51" s="22" t="inlineStr"/>
-      <c r="Q51" s="22" t="inlineStr"/>
-      <c r="R51" s="23" t="inlineStr"/>
-      <c r="S51" s="22" t="inlineStr"/>
-      <c r="T51" s="22" t="inlineStr">
+      <c r="O51" s="20" t="inlineStr"/>
+      <c r="P51" s="20" t="inlineStr"/>
+      <c r="Q51" s="20" t="inlineStr"/>
+      <c r="R51" s="21" t="inlineStr"/>
+      <c r="S51" s="20" t="inlineStr"/>
+      <c r="T51" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U51" s="22" t="inlineStr">
+      <c r="U51" s="20" t="inlineStr">
         <is>
           <t>CAILLARD</t>
         </is>
       </c>
-      <c r="V51" s="22" t="inlineStr">
+      <c r="V51" s="20" t="inlineStr">
         <is>
           <t>Stéphane, Jacques, Franck, Raymond</t>
         </is>
       </c>
-      <c r="W51" s="22" t="inlineStr">
+      <c r="W51" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X51" s="22" t="inlineStr">
+      <c r="X51" s="20" t="inlineStr">
         <is>
           <t>33 chemin de la Noue</t>
         </is>
       </c>
-      <c r="Y51" s="23" t="inlineStr">
+      <c r="Y51" s="21" t="inlineStr">
         <is>
           <t>57130</t>
         </is>
       </c>
-      <c r="Z51" s="22" t="inlineStr">
+      <c r="Z51" s="20" t="inlineStr">
         <is>
           <t>Vaux</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>921382453</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>92138245300014</t>
         </is>
       </c>
-      <c r="D52" s="22" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>LA FONTAINE</t>
         </is>
       </c>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>LA FONTAINE</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G52" s="22" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H52" s="22" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I52" s="22" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>07/11/2022</t>
         </is>
       </c>
-      <c r="J52" s="22" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K52" s="22" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>7 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L52" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M52" s="22" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M52" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N52" s="22" t="inlineStr">
+      <c r="N52" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O52" s="22" t="inlineStr"/>
-      <c r="P52" s="22" t="inlineStr"/>
-      <c r="Q52" s="22" t="inlineStr"/>
-      <c r="R52" s="23" t="inlineStr"/>
-      <c r="S52" s="22" t="inlineStr"/>
-      <c r="T52" s="22" t="inlineStr">
+      <c r="O52" s="20" t="inlineStr"/>
+      <c r="P52" s="20" t="inlineStr"/>
+      <c r="Q52" s="20" t="inlineStr"/>
+      <c r="R52" s="21" t="inlineStr"/>
+      <c r="S52" s="20" t="inlineStr"/>
+      <c r="T52" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U52" s="22" t="inlineStr">
+      <c r="U52" s="20" t="inlineStr">
         <is>
           <t>BASIN</t>
         </is>
       </c>
-      <c r="V52" s="22" t="inlineStr">
+      <c r="V52" s="20" t="inlineStr">
         <is>
           <t>Billy, Gérard, Denis</t>
         </is>
       </c>
-      <c r="W52" s="22" t="inlineStr">
+      <c r="W52" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X52" s="22" t="inlineStr"/>
-      <c r="Y52" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z52" s="22" t="inlineStr">
+      <c r="X52" s="20" t="inlineStr"/>
+      <c r="Y52" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z52" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>414294116</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>41429411600036</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr">
+      <c r="D53" s="20" t="inlineStr">
         <is>
           <t>SOJADEX</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>SOJADEX</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G53" s="22" t="inlineStr">
+      <c r="G53" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H53" s="22" t="inlineStr">
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I53" s="22" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>01/11/1997</t>
         </is>
       </c>
-      <c r="J53" s="22" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="K53" s="22" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
         <is>
           <t>1 AVENUE NEY</t>
         </is>
       </c>
-      <c r="L53" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M53" s="22" t="inlineStr">
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M53" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N53" s="22" t="inlineStr">
+      <c r="N53" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O53" s="22" t="n">
-        <v>19000</v>
-      </c>
-      <c r="P53" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q53" s="22" t="inlineStr"/>
-      <c r="R53" s="23" t="inlineStr"/>
-      <c r="S53" s="22" t="inlineStr"/>
-      <c r="T53" s="22" t="inlineStr">
+      <c r="O53" s="20" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="P53" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q53" s="20" t="inlineStr"/>
+      <c r="R53" s="21" t="inlineStr"/>
+      <c r="S53" s="20" t="inlineStr"/>
+      <c r="T53" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U53" s="22" t="inlineStr">
+      <c r="U53" s="20" t="inlineStr">
         <is>
           <t>JARDINE</t>
         </is>
       </c>
-      <c r="V53" s="22" t="inlineStr">
+      <c r="V53" s="20" t="inlineStr">
         <is>
           <t>Sophie</t>
         </is>
       </c>
-      <c r="W53" s="22" t="inlineStr">
+      <c r="W53" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X53" s="22" t="inlineStr">
+      <c r="X53" s="20" t="inlineStr">
         <is>
           <t>4 rue des Bergeronnettes</t>
         </is>
       </c>
-      <c r="Y53" s="23" t="inlineStr">
+      <c r="Y53" s="21" t="inlineStr">
         <is>
           <t>57120</t>
         </is>
       </c>
-      <c r="Z53" s="22" t="inlineStr">
+      <c r="Z53" s="20" t="inlineStr">
         <is>
           <t>Rombas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>106340490</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>10634049000015</t>
         </is>
       </c>
-      <c r="D54" s="22" t="inlineStr">
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>YASAF</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>YASAF</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="G54" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H54" s="22" t="inlineStr">
+      <c r="H54" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I54" s="22" t="inlineStr">
+      <c r="I54" s="20" t="inlineStr">
         <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="J54" s="22" t="inlineStr">
+      <c r="J54" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K54" s="22" t="inlineStr">
+      <c r="K54" s="20" t="inlineStr">
         <is>
           <t>9 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L54" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M54" s="22" t="inlineStr">
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M54" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N54" s="22" t="inlineStr">
+      <c r="N54" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O54" s="22" t="inlineStr"/>
-      <c r="P54" s="22" t="inlineStr"/>
-      <c r="Q54" s="22" t="inlineStr"/>
-      <c r="R54" s="23" t="inlineStr"/>
-      <c r="S54" s="22" t="inlineStr"/>
-      <c r="T54" s="22" t="inlineStr">
+      <c r="O54" s="20" t="inlineStr"/>
+      <c r="P54" s="20" t="inlineStr"/>
+      <c r="Q54" s="20" t="inlineStr"/>
+      <c r="R54" s="21" t="inlineStr"/>
+      <c r="S54" s="20" t="inlineStr"/>
+      <c r="T54" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U54" s="22" t="inlineStr">
+      <c r="U54" s="20" t="inlineStr">
         <is>
           <t>AIOUN</t>
         </is>
       </c>
-      <c r="V54" s="22" t="inlineStr">
+      <c r="V54" s="20" t="inlineStr">
         <is>
           <t>Younes</t>
         </is>
       </c>
-      <c r="W54" s="22" t="inlineStr">
+      <c r="W54" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X54" s="22" t="inlineStr"/>
-      <c r="Y54" s="23" t="inlineStr">
+      <c r="X54" s="20" t="inlineStr"/>
+      <c r="Y54" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z54" s="22" t="inlineStr">
+      <c r="Z54" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>982266702</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>98226670200017</t>
         </is>
       </c>
-      <c r="D55" s="22" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>STAGNO WASANA</t>
         </is>
       </c>
-      <c r="E55" s="22" t="inlineStr">
+      <c r="E55" s="20" t="inlineStr">
         <is>
           <t>STAGNO WASANA</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G55" s="22" t="inlineStr">
+      <c r="G55" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I55" s="22" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>04/01/2024</t>
         </is>
       </c>
-      <c r="J55" s="22" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K55" s="22" t="inlineStr">
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>9 RUE PIERRE MAURICE MASSON</t>
         </is>
       </c>
-      <c r="L55" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M55" s="22" t="inlineStr">
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M55" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N55" s="22" t="inlineStr">
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O55" s="22" t="inlineStr"/>
-      <c r="P55" s="22" t="inlineStr"/>
-      <c r="Q55" s="22" t="inlineStr"/>
-      <c r="R55" s="23" t="inlineStr"/>
-      <c r="S55" s="22" t="inlineStr"/>
-      <c r="T55" s="22" t="inlineStr">
+      <c r="O55" s="20" t="inlineStr"/>
+      <c r="P55" s="20" t="inlineStr"/>
+      <c r="Q55" s="20" t="inlineStr"/>
+      <c r="R55" s="21" t="inlineStr"/>
+      <c r="S55" s="20" t="inlineStr"/>
+      <c r="T55" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U55" s="22" t="inlineStr">
+      <c r="U55" s="20" t="inlineStr">
         <is>
           <t>TUNKONG</t>
         </is>
       </c>
-      <c r="V55" s="22" t="inlineStr">
+      <c r="V55" s="20" t="inlineStr">
         <is>
           <t>Wasana</t>
         </is>
       </c>
-      <c r="W55" s="22" t="inlineStr">
+      <c r="W55" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X55" s="22" t="inlineStr"/>
-      <c r="Y55" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z55" s="22" t="inlineStr">
+      <c r="X55" s="20" t="inlineStr"/>
+      <c r="Y55" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z55" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>934358284</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>93435828400016</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr">
         <is>
           <t>LONGHI-WELFRINGER Elisa</t>
         </is>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E56" s="20" t="inlineStr">
         <is>
           <t>LONGHI-WELFRINGER Elisa</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
+      <c r="F56" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G56" s="22" t="inlineStr">
+      <c r="G56" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H56" s="22" t="inlineStr">
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I56" s="22" t="inlineStr">
+      <c r="I56" s="20" t="inlineStr">
         <is>
           <t>17/10/2024</t>
         </is>
       </c>
-      <c r="J56" s="22" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K56" s="22" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>15 RUE DE LA TETE D'OR</t>
         </is>
       </c>
-      <c r="L56" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M56" s="22" t="inlineStr">
+      <c r="L56" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M56" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N56" s="22" t="inlineStr">
+      <c r="N56" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O56" s="22" t="inlineStr"/>
-      <c r="P56" s="22" t="inlineStr"/>
-      <c r="Q56" s="22" t="inlineStr"/>
-      <c r="R56" s="23" t="inlineStr"/>
-      <c r="S56" s="22" t="inlineStr"/>
-      <c r="T56" s="22" t="inlineStr">
+      <c r="O56" s="20" t="inlineStr"/>
+      <c r="P56" s="20" t="inlineStr"/>
+      <c r="Q56" s="20" t="inlineStr"/>
+      <c r="R56" s="21" t="inlineStr"/>
+      <c r="S56" s="20" t="inlineStr"/>
+      <c r="T56" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U56" s="22" t="inlineStr">
+      <c r="U56" s="20" t="inlineStr">
         <is>
           <t>LONGHI</t>
         </is>
       </c>
-      <c r="V56" s="22" t="inlineStr">
+      <c r="V56" s="20" t="inlineStr">
         <is>
           <t>Elisa</t>
         </is>
       </c>
-      <c r="W56" s="22" t="inlineStr">
+      <c r="W56" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X56" s="22" t="inlineStr"/>
-      <c r="Y56" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z56" s="22" t="inlineStr">
+      <c r="X56" s="20" t="inlineStr"/>
+      <c r="Y56" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z56" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>812163772</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
+      <c r="C57" s="21" t="inlineStr">
         <is>
           <t>81216377200013</t>
         </is>
       </c>
-      <c r="D57" s="22" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr">
         <is>
           <t>SNACK FOURNIRUE</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E57" s="20" t="inlineStr">
         <is>
           <t>SNACK FOURNIRUE</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr">
+      <c r="G57" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H57" s="22" t="inlineStr">
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I57" s="22" t="inlineStr">
+      <c r="I57" s="20" t="inlineStr">
         <is>
           <t>17/06/2015</t>
         </is>
       </c>
-      <c r="J57" s="22" t="inlineStr">
+      <c r="J57" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K57" s="22" t="inlineStr">
+      <c r="K57" s="20" t="inlineStr">
         <is>
           <t>7 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L57" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M57" s="22" t="inlineStr">
+      <c r="L57" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M57" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N57" s="22" t="inlineStr">
+      <c r="N57" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O57" s="22" t="inlineStr"/>
-      <c r="P57" s="22" t="inlineStr"/>
-      <c r="Q57" s="22" t="inlineStr"/>
-      <c r="R57" s="23" t="inlineStr"/>
-      <c r="S57" s="22" t="inlineStr"/>
-      <c r="T57" s="22" t="inlineStr">
+      <c r="O57" s="20" t="inlineStr"/>
+      <c r="P57" s="20" t="inlineStr"/>
+      <c r="Q57" s="20" t="inlineStr"/>
+      <c r="R57" s="21" t="inlineStr"/>
+      <c r="S57" s="20" t="inlineStr"/>
+      <c r="T57" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U57" s="22" t="inlineStr">
+      <c r="U57" s="20" t="inlineStr">
         <is>
           <t>REZAOUI</t>
         </is>
       </c>
-      <c r="V57" s="22" t="inlineStr">
+      <c r="V57" s="20" t="inlineStr">
         <is>
           <t>Tarik</t>
         </is>
       </c>
-      <c r="W57" s="22" t="inlineStr">
+      <c r="W57" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X57" s="22" t="inlineStr">
+      <c r="X57" s="20" t="inlineStr">
         <is>
           <t>10 rue Nicolas Jung</t>
         </is>
       </c>
-      <c r="Y57" s="23" t="inlineStr">
+      <c r="Y57" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z57" s="22" t="inlineStr">
+      <c r="Z57" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="21" t="inlineStr">
         <is>
           <t>993730621</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
+      <c r="C58" s="21" t="inlineStr">
         <is>
           <t>99373062100014</t>
         </is>
       </c>
-      <c r="D58" s="22" t="inlineStr">
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>MISTER CHICKEN</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E58" s="20" t="inlineStr">
         <is>
           <t>MISTER CHICKEN</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
+      <c r="G58" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H58" s="22" t="inlineStr">
+      <c r="H58" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I58" s="22" t="inlineStr">
+      <c r="I58" s="20" t="inlineStr">
         <is>
           <t>07/11/2025</t>
         </is>
       </c>
-      <c r="J58" s="22" t="inlineStr">
+      <c r="J58" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K58" s="22" t="inlineStr">
+      <c r="K58" s="20" t="inlineStr">
         <is>
           <t>12 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L58" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M58" s="22" t="inlineStr">
+      <c r="L58" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M58" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N58" s="22" t="inlineStr">
+      <c r="N58" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O58" s="22" t="inlineStr"/>
-      <c r="P58" s="22" t="inlineStr"/>
-      <c r="Q58" s="22" t="inlineStr"/>
-      <c r="R58" s="23" t="inlineStr"/>
-      <c r="S58" s="22" t="inlineStr"/>
-      <c r="T58" s="22" t="inlineStr">
+      <c r="O58" s="20" t="inlineStr"/>
+      <c r="P58" s="20" t="inlineStr"/>
+      <c r="Q58" s="20" t="inlineStr"/>
+      <c r="R58" s="21" t="inlineStr"/>
+      <c r="S58" s="20" t="inlineStr"/>
+      <c r="T58" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U58" s="22" t="inlineStr">
+      <c r="U58" s="20" t="inlineStr">
         <is>
           <t>HOLDING MB</t>
         </is>
       </c>
-      <c r="V58" s="22" t="inlineStr"/>
-      <c r="W58" s="22" t="inlineStr">
+      <c r="V58" s="20" t="inlineStr"/>
+      <c r="W58" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X58" s="22" t="inlineStr">
+      <c r="X58" s="20" t="inlineStr">
         <is>
           <t>79 RUE Saint Georges</t>
         </is>
       </c>
-      <c r="Y58" s="23" t="inlineStr">
+      <c r="Y58" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="Z58" s="22" t="inlineStr">
+      <c r="Z58" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>914736202</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
+      <c r="C59" s="21" t="inlineStr">
         <is>
           <t>91473620200021</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>ZINE</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>ZINE</t>
         </is>
       </c>
-      <c r="F59" s="22" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G59" s="22" t="inlineStr">
+      <c r="G59" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H59" s="22" t="inlineStr">
+      <c r="H59" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I59" s="22" t="inlineStr">
+      <c r="I59" s="20" t="inlineStr">
         <is>
           <t>21/06/2022</t>
         </is>
       </c>
-      <c r="J59" s="22" t="inlineStr">
+      <c r="J59" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K59" s="22" t="inlineStr">
+      <c r="K59" s="20" t="inlineStr">
         <is>
           <t>10 B RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L59" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M59" s="22" t="inlineStr">
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M59" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N59" s="22" t="inlineStr">
+      <c r="N59" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O59" s="22" t="n">
-        <v>882795</v>
-      </c>
-      <c r="P59" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q59" s="22" t="inlineStr"/>
-      <c r="R59" s="23" t="inlineStr"/>
-      <c r="S59" s="22" t="inlineStr"/>
-      <c r="T59" s="22" t="inlineStr">
+      <c r="O59" s="20" t="inlineStr">
+        <is>
+          <t>882795</t>
+        </is>
+      </c>
+      <c r="P59" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q59" s="20" t="inlineStr"/>
+      <c r="R59" s="21" t="inlineStr"/>
+      <c r="S59" s="20" t="inlineStr"/>
+      <c r="T59" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U59" s="22" t="inlineStr">
+      <c r="U59" s="20" t="inlineStr">
         <is>
           <t>GERARD</t>
         </is>
       </c>
-      <c r="V59" s="22" t="inlineStr">
+      <c r="V59" s="20" t="inlineStr">
         <is>
           <t>Alexis, Serge, Henri, Marcel</t>
         </is>
       </c>
-      <c r="W59" s="22" t="inlineStr">
+      <c r="W59" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X59" s="22" t="inlineStr">
+      <c r="X59" s="20" t="inlineStr">
         <is>
           <t>12 Rue Charlemagne</t>
         </is>
       </c>
-      <c r="Y59" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z59" s="22" t="inlineStr">
+      <c r="Y59" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z59" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="21" t="inlineStr">
         <is>
           <t>848149449</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
+      <c r="C60" s="21" t="inlineStr">
         <is>
           <t>84814944900011</t>
         </is>
       </c>
-      <c r="D60" s="22" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>DELICE PIZZA</t>
         </is>
       </c>
-      <c r="E60" s="22" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>DELICE PIZZA</t>
         </is>
       </c>
-      <c r="F60" s="22" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G60" s="22" t="inlineStr">
+      <c r="G60" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H60" s="22" t="inlineStr">
+      <c r="H60" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I60" s="22" t="inlineStr">
+      <c r="I60" s="20" t="inlineStr">
         <is>
           <t>04/02/2019</t>
         </is>
       </c>
-      <c r="J60" s="22" t="inlineStr">
+      <c r="J60" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K60" s="22" t="inlineStr">
+      <c r="K60" s="20" t="inlineStr">
         <is>
           <t>19 PLACE DES CHARRONS</t>
         </is>
       </c>
-      <c r="L60" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M60" s="22" t="inlineStr">
+      <c r="L60" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M60" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N60" s="22" t="inlineStr">
+      <c r="N60" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O60" s="22" t="inlineStr"/>
-      <c r="P60" s="22" t="inlineStr"/>
-      <c r="Q60" s="22" t="inlineStr"/>
-      <c r="R60" s="23" t="inlineStr"/>
-      <c r="S60" s="22" t="inlineStr"/>
-      <c r="T60" s="22" t="inlineStr">
+      <c r="O60" s="20" t="inlineStr"/>
+      <c r="P60" s="20" t="inlineStr"/>
+      <c r="Q60" s="20" t="inlineStr"/>
+      <c r="R60" s="21" t="inlineStr"/>
+      <c r="S60" s="20" t="inlineStr"/>
+      <c r="T60" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U60" s="22" t="inlineStr">
+      <c r="U60" s="20" t="inlineStr">
         <is>
           <t>MSADEK</t>
         </is>
       </c>
-      <c r="V60" s="22" t="inlineStr">
+      <c r="V60" s="20" t="inlineStr">
         <is>
           <t>Amine</t>
         </is>
       </c>
-      <c r="W60" s="22" t="inlineStr">
+      <c r="W60" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X60" s="22" t="inlineStr">
+      <c r="X60" s="20" t="inlineStr">
         <is>
           <t>1 Ruelle Saint-michel</t>
         </is>
       </c>
-      <c r="Y60" s="23" t="inlineStr">
+      <c r="Y60" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z60" s="22" t="inlineStr">
+      <c r="Z60" s="20" t="inlineStr">
         <is>
           <t>Plappeville</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="21" t="inlineStr">
         <is>
           <t>942018656</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="C61" s="21" t="inlineStr">
         <is>
           <t>94201865600028</t>
         </is>
       </c>
-      <c r="D61" s="22" t="inlineStr">
+      <c r="D61" s="20" t="inlineStr">
         <is>
           <t>MADAME JEAN</t>
         </is>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>MADAME JEAN</t>
         </is>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F61" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G61" s="22" t="inlineStr">
+      <c r="G61" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H61" s="22" t="inlineStr">
+      <c r="H61" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I61" s="22" t="inlineStr">
+      <c r="I61" s="20" t="inlineStr">
         <is>
           <t>05/05/2025</t>
         </is>
       </c>
-      <c r="J61" s="22" t="inlineStr">
+      <c r="J61" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K61" s="22" t="inlineStr">
+      <c r="K61" s="20" t="inlineStr">
         <is>
           <t>7 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="L61" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M61" s="22" t="inlineStr">
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M61" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N61" s="22" t="inlineStr">
+      <c r="N61" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O61" s="22" t="inlineStr"/>
-      <c r="P61" s="22" t="inlineStr"/>
-      <c r="Q61" s="22" t="inlineStr"/>
-      <c r="R61" s="23" t="inlineStr"/>
-      <c r="S61" s="22" t="inlineStr"/>
-      <c r="T61" s="22" t="inlineStr">
+      <c r="O61" s="20" t="inlineStr"/>
+      <c r="P61" s="20" t="inlineStr"/>
+      <c r="Q61" s="20" t="inlineStr"/>
+      <c r="R61" s="21" t="inlineStr"/>
+      <c r="S61" s="20" t="inlineStr"/>
+      <c r="T61" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U61" s="22" t="inlineStr">
+      <c r="U61" s="20" t="inlineStr">
         <is>
           <t>RENOUARD</t>
         </is>
       </c>
-      <c r="V61" s="22" t="inlineStr">
+      <c r="V61" s="20" t="inlineStr">
         <is>
           <t>Adeline</t>
         </is>
       </c>
-      <c r="W61" s="22" t="inlineStr">
+      <c r="W61" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X61" s="22" t="inlineStr">
+      <c r="X61" s="20" t="inlineStr">
         <is>
           <t>8 rue des Parmentiers</t>
         </is>
       </c>
-      <c r="Y61" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z61" s="22" t="inlineStr">
+      <c r="Y61" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z61" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="21" t="inlineStr">
         <is>
           <t>833114796</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
+      <c r="C62" s="21" t="inlineStr">
         <is>
           <t>83311479600026</t>
         </is>
       </c>
-      <c r="D62" s="22" t="inlineStr">
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>VI &amp; VI</t>
         </is>
       </c>
-      <c r="E62" s="22" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
         <is>
           <t>VI &amp; VI</t>
         </is>
       </c>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="F62" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G62" s="22" t="inlineStr">
+      <c r="G62" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H62" s="22" t="inlineStr">
+      <c r="H62" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I62" s="22" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
-      <c r="J62" s="22" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K62" s="22" t="inlineStr">
+      <c r="K62" s="20" t="inlineStr">
         <is>
           <t>CTRE COMMERCIAL ST JACQUES</t>
         </is>
       </c>
-      <c r="L62" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M62" s="22" t="inlineStr">
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M62" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N62" s="22" t="inlineStr">
+      <c r="N62" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O62" s="22" t="inlineStr"/>
-      <c r="P62" s="22" t="inlineStr"/>
-      <c r="Q62" s="22" t="inlineStr"/>
-      <c r="R62" s="23" t="inlineStr"/>
-      <c r="S62" s="22" t="inlineStr"/>
-      <c r="T62" s="22" t="inlineStr">
+      <c r="O62" s="20" t="inlineStr"/>
+      <c r="P62" s="20" t="inlineStr"/>
+      <c r="Q62" s="20" t="inlineStr"/>
+      <c r="R62" s="21" t="inlineStr"/>
+      <c r="S62" s="20" t="inlineStr"/>
+      <c r="T62" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U62" s="22" t="inlineStr">
+      <c r="U62" s="20" t="inlineStr">
         <is>
           <t>TRAN</t>
         </is>
       </c>
-      <c r="V62" s="22" t="inlineStr">
+      <c r="V62" s="20" t="inlineStr">
         <is>
           <t>Thanh, Thu, Ha</t>
         </is>
       </c>
-      <c r="W62" s="22" t="inlineStr">
+      <c r="W62" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X62" s="22" t="inlineStr">
+      <c r="X62" s="20" t="inlineStr">
         <is>
           <t>2 boulevard Robert Schuman</t>
         </is>
       </c>
-      <c r="Y62" s="23" t="inlineStr">
+      <c r="Y62" s="21" t="inlineStr">
         <is>
           <t>57100</t>
         </is>
       </c>
-      <c r="Z62" s="22" t="inlineStr">
+      <c r="Z62" s="20" t="inlineStr">
         <is>
           <t>Thionville</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>939927034</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
+      <c r="C63" s="21" t="inlineStr">
         <is>
           <t>93992703400016</t>
         </is>
       </c>
-      <c r="D63" s="22" t="inlineStr">
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>PETRALITO EDUARDO</t>
         </is>
       </c>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>PETRALITO EDUARDO</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G63" s="22" t="inlineStr">
+      <c r="G63" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H63" s="22" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I63" s="22" t="inlineStr">
+      <c r="I63" s="20" t="inlineStr">
         <is>
           <t>22/01/2025</t>
         </is>
       </c>
-      <c r="J63" s="22" t="inlineStr">
+      <c r="J63" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K63" s="22" t="inlineStr">
+      <c r="K63" s="20" t="inlineStr">
         <is>
           <t>9 RUE GOUVY</t>
         </is>
       </c>
-      <c r="L63" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M63" s="22" t="inlineStr">
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M63" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N63" s="22" t="inlineStr">
+      <c r="N63" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O63" s="22" t="inlineStr"/>
-      <c r="P63" s="22" t="inlineStr"/>
-      <c r="Q63" s="22" t="inlineStr"/>
-      <c r="R63" s="23" t="inlineStr"/>
-      <c r="S63" s="22" t="inlineStr"/>
-      <c r="T63" s="22" t="inlineStr">
+      <c r="O63" s="20" t="inlineStr"/>
+      <c r="P63" s="20" t="inlineStr"/>
+      <c r="Q63" s="20" t="inlineStr"/>
+      <c r="R63" s="21" t="inlineStr"/>
+      <c r="S63" s="20" t="inlineStr"/>
+      <c r="T63" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U63" s="22" t="inlineStr">
+      <c r="U63" s="20" t="inlineStr">
         <is>
           <t>PETRALITO</t>
         </is>
       </c>
-      <c r="V63" s="22" t="inlineStr">
+      <c r="V63" s="20" t="inlineStr">
         <is>
           <t>Eduardo, Salvatore, Antonio</t>
         </is>
       </c>
-      <c r="W63" s="22" t="inlineStr">
+      <c r="W63" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X63" s="22" t="inlineStr"/>
-      <c r="Y63" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z63" s="22" t="inlineStr">
+      <c r="X63" s="20" t="inlineStr"/>
+      <c r="Y63" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z63" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="21" t="inlineStr">
         <is>
           <t>879005932</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
+      <c r="C64" s="21" t="inlineStr">
         <is>
           <t>87900593200014</t>
         </is>
       </c>
-      <c r="D64" s="22" t="inlineStr">
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>SCHMIT Sylvie</t>
         </is>
       </c>
-      <c r="E64" s="22" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>SCHMIT Sylvie</t>
         </is>
       </c>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
+      <c r="G64" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H64" s="22" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I64" s="22" t="inlineStr">
+      <c r="I64" s="20" t="inlineStr">
         <is>
           <t>01/11/2019</t>
         </is>
       </c>
-      <c r="J64" s="22" t="inlineStr">
+      <c r="J64" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K64" s="22" t="inlineStr">
+      <c r="K64" s="20" t="inlineStr">
         <is>
           <t>2 RUE DU PAS DU LOUP</t>
         </is>
       </c>
-      <c r="L64" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M64" s="22" t="inlineStr">
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M64" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N64" s="22" t="inlineStr">
+      <c r="N64" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O64" s="22" t="inlineStr"/>
-      <c r="P64" s="22" t="inlineStr"/>
-      <c r="Q64" s="22" t="inlineStr"/>
-      <c r="R64" s="23" t="inlineStr"/>
-      <c r="S64" s="22" t="inlineStr"/>
-      <c r="T64" s="22" t="inlineStr">
+      <c r="O64" s="20" t="inlineStr"/>
+      <c r="P64" s="20" t="inlineStr"/>
+      <c r="Q64" s="20" t="inlineStr"/>
+      <c r="R64" s="21" t="inlineStr"/>
+      <c r="S64" s="20" t="inlineStr"/>
+      <c r="T64" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U64" s="22" t="inlineStr">
+      <c r="U64" s="20" t="inlineStr">
         <is>
           <t>SCHMIT</t>
         </is>
       </c>
-      <c r="V64" s="22" t="inlineStr">
+      <c r="V64" s="20" t="inlineStr">
         <is>
           <t>Sylvie, Marie, Andree</t>
         </is>
       </c>
-      <c r="W64" s="22" t="inlineStr">
+      <c r="W64" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X64" s="22" t="inlineStr"/>
-      <c r="Y64" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z64" s="22" t="inlineStr">
+      <c r="X64" s="20" t="inlineStr"/>
+      <c r="Y64" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z64" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" s="21" t="inlineStr">
         <is>
           <t>851264903</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
+      <c r="C65" s="21" t="inlineStr">
         <is>
           <t>85126490300010</t>
         </is>
       </c>
-      <c r="D65" s="22" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>LCA</t>
         </is>
       </c>
-      <c r="E65" s="22" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>LCA</t>
         </is>
       </c>
-      <c r="F65" s="22" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G65" s="22" t="inlineStr">
+      <c r="G65" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H65" s="22" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I65" s="22" t="inlineStr">
+      <c r="I65" s="20" t="inlineStr">
         <is>
           <t>03/06/2019</t>
         </is>
       </c>
-      <c r="J65" s="22" t="inlineStr">
+      <c r="J65" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K65" s="22" t="inlineStr">
+      <c r="K65" s="20" t="inlineStr">
         <is>
           <t>1 AVENUE NEY</t>
         </is>
       </c>
-      <c r="L65" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M65" s="22" t="inlineStr">
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M65" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N65" s="22" t="inlineStr">
+      <c r="N65" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O65" s="22" t="inlineStr"/>
-      <c r="P65" s="22" t="inlineStr"/>
-      <c r="Q65" s="22" t="inlineStr"/>
-      <c r="R65" s="23" t="inlineStr"/>
-      <c r="S65" s="22" t="inlineStr"/>
-      <c r="T65" s="22" t="inlineStr">
+      <c r="O65" s="20" t="inlineStr"/>
+      <c r="P65" s="20" t="inlineStr"/>
+      <c r="Q65" s="20" t="inlineStr"/>
+      <c r="R65" s="21" t="inlineStr"/>
+      <c r="S65" s="20" t="inlineStr"/>
+      <c r="T65" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U65" s="22" t="inlineStr">
+      <c r="U65" s="20" t="inlineStr">
         <is>
           <t>HOANG</t>
         </is>
       </c>
-      <c r="V65" s="22" t="inlineStr">
+      <c r="V65" s="20" t="inlineStr">
         <is>
           <t>Thi, Anh, Thu</t>
         </is>
       </c>
-      <c r="W65" s="22" t="inlineStr">
+      <c r="W65" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X65" s="22" t="inlineStr">
+      <c r="X65" s="20" t="inlineStr">
         <is>
           <t>36 rue des Framboises</t>
         </is>
       </c>
-      <c r="Y65" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z65" s="22" t="inlineStr">
+      <c r="Y65" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z65" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B66" s="23" t="inlineStr">
+      <c r="B66" s="21" t="inlineStr">
         <is>
           <t>830488037</t>
         </is>
       </c>
-      <c r="C66" s="23" t="inlineStr">
+      <c r="C66" s="21" t="inlineStr">
         <is>
           <t>83048803700011</t>
         </is>
       </c>
-      <c r="D66" s="22" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>MD DIFFUSION</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>MD DIFFUSION</t>
         </is>
       </c>
-      <c r="F66" s="22" t="inlineStr">
+      <c r="F66" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G66" s="22" t="inlineStr">
+      <c r="G66" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H66" s="22" t="inlineStr">
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I66" s="22" t="inlineStr">
+      <c r="I66" s="20" t="inlineStr">
         <is>
           <t>15/05/2017</t>
         </is>
       </c>
-      <c r="J66" s="22" t="inlineStr">
+      <c r="J66" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K66" s="22" t="inlineStr">
+      <c r="K66" s="20" t="inlineStr">
         <is>
           <t>43 RUE DE POUILLY</t>
         </is>
       </c>
-      <c r="L66" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M66" s="22" t="inlineStr">
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M66" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N66" s="22" t="inlineStr">
+      <c r="N66" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O66" s="22" t="inlineStr"/>
-      <c r="P66" s="22" t="inlineStr"/>
-      <c r="Q66" s="22" t="inlineStr"/>
-      <c r="R66" s="23" t="inlineStr"/>
-      <c r="S66" s="22" t="inlineStr"/>
-      <c r="T66" s="22" t="inlineStr">
+      <c r="O66" s="20" t="inlineStr"/>
+      <c r="P66" s="20" t="inlineStr"/>
+      <c r="Q66" s="20" t="inlineStr"/>
+      <c r="R66" s="21" t="inlineStr"/>
+      <c r="S66" s="20" t="inlineStr"/>
+      <c r="T66" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U66" s="22" t="inlineStr">
+      <c r="U66" s="20" t="inlineStr">
         <is>
           <t>CAPIZZI</t>
         </is>
       </c>
-      <c r="V66" s="22" t="inlineStr">
+      <c r="V66" s="20" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="W66" s="22" t="inlineStr">
+      <c r="W66" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X66" s="22" t="inlineStr">
+      <c r="X66" s="20" t="inlineStr">
         <is>
           <t>43 rue de Pouilly</t>
         </is>
       </c>
-      <c r="Y66" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z66" s="22" t="inlineStr">
+      <c r="Y66" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z66" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" s="21" t="inlineStr">
         <is>
           <t>952396885</t>
         </is>
       </c>
-      <c r="C67" s="23" t="inlineStr">
+      <c r="C67" s="21" t="inlineStr">
         <is>
           <t>95239688500024</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>SAS MAGIRA</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>SAS MAGIRA</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G67" s="22" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I67" s="22" t="inlineStr">
+      <c r="I67" s="20" t="inlineStr">
         <is>
           <t>05/05/2023</t>
         </is>
       </c>
-      <c r="J67" s="22" t="inlineStr">
+      <c r="J67" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K67" s="22" t="inlineStr">
+      <c r="K67" s="20" t="inlineStr">
         <is>
           <t>32 RUE DE LA TETE D'OR</t>
         </is>
       </c>
-      <c r="L67" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M67" s="22" t="inlineStr">
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M67" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N67" s="22" t="inlineStr">
+      <c r="N67" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O67" s="22" t="inlineStr"/>
-      <c r="P67" s="22" t="inlineStr"/>
-      <c r="Q67" s="22" t="inlineStr"/>
-      <c r="R67" s="23" t="inlineStr"/>
-      <c r="S67" s="22" t="inlineStr"/>
-      <c r="T67" s="22" t="inlineStr">
+      <c r="O67" s="20" t="inlineStr"/>
+      <c r="P67" s="20" t="inlineStr"/>
+      <c r="Q67" s="20" t="inlineStr"/>
+      <c r="R67" s="21" t="inlineStr"/>
+      <c r="S67" s="20" t="inlineStr"/>
+      <c r="T67" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U67" s="22" t="inlineStr">
+      <c r="U67" s="20" t="inlineStr">
         <is>
           <t>ETIENNE</t>
         </is>
       </c>
-      <c r="V67" s="22" t="inlineStr">
+      <c r="V67" s="20" t="inlineStr">
         <is>
           <t>Alexandre, Marcel, Jean-pierre</t>
         </is>
       </c>
-      <c r="W67" s="22" t="inlineStr">
+      <c r="W67" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X67" s="22" t="inlineStr">
+      <c r="X67" s="20" t="inlineStr">
         <is>
           <t>10 Rue des Fauvettes</t>
         </is>
       </c>
-      <c r="Y67" s="23" t="inlineStr">
+      <c r="Y67" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z67" s="22" t="inlineStr">
+      <c r="Z67" s="20" t="inlineStr">
         <is>
           <t>Lorry-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>837619626</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>83761962600026</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>LDF</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>LDF</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>20/11/2017</t>
+        </is>
+      </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K68" s="22" t="inlineStr">
+        <is>
+          <t>11 RUE DES AUGUSTINS</t>
+        </is>
+      </c>
+      <c r="L68" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M68" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N68" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O68" s="22" t="inlineStr"/>
+      <c r="P68" s="22" t="inlineStr"/>
+      <c r="Q68" s="22" t="inlineStr"/>
+      <c r="R68" s="23" t="inlineStr"/>
+      <c r="S68" s="22" t="inlineStr"/>
+      <c r="T68" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U68" s="22" t="inlineStr">
+        <is>
+          <t>GOTHUEY</t>
+        </is>
+      </c>
+      <c r="V68" s="22" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="W68" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X68" s="22" t="inlineStr">
+        <is>
+          <t>6 rue de la Fontaine</t>
+        </is>
+      </c>
+      <c r="Y68" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z68" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>805245974</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>80524597400011</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>PINHO DE CASTRO Maria</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>PINHO DE CASTRO Maria</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2014</t>
+        </is>
+      </c>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="inlineStr">
+        <is>
+          <t>60 RUE DE LA CHAPELLE</t>
+        </is>
+      </c>
+      <c r="L69" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M69" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N69" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O69" s="22" t="inlineStr"/>
+      <c r="P69" s="22" t="inlineStr"/>
+      <c r="Q69" s="22" t="inlineStr"/>
+      <c r="R69" s="23" t="inlineStr"/>
+      <c r="S69" s="22" t="inlineStr"/>
+      <c r="T69" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U69" s="22" t="inlineStr">
+        <is>
+          <t>PINHO DE CASTRO</t>
+        </is>
+      </c>
+      <c r="V69" s="22" t="inlineStr">
+        <is>
+          <t>Maria goreti</t>
+        </is>
+      </c>
+      <c r="W69" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X69" s="22" t="inlineStr"/>
+      <c r="Y69" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z69" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>878082627</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>87808262700018</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>THIMOSO</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>THIMOSO</t>
+        </is>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I70" s="22" t="inlineStr">
+        <is>
+          <t>14/10/2019</t>
+        </is>
+      </c>
+      <c r="J70" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K70" s="22" t="inlineStr">
+        <is>
+          <t>6 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L70" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M70" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N70" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O70" s="22" t="inlineStr"/>
+      <c r="P70" s="22" t="inlineStr"/>
+      <c r="Q70" s="22" t="inlineStr"/>
+      <c r="R70" s="23" t="inlineStr"/>
+      <c r="S70" s="22" t="inlineStr"/>
+      <c r="T70" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U70" s="22" t="inlineStr">
+        <is>
+          <t>GURY</t>
+        </is>
+      </c>
+      <c r="V70" s="22" t="inlineStr">
+        <is>
+          <t>Thierry</t>
+        </is>
+      </c>
+      <c r="W70" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X70" s="22" t="inlineStr">
+        <is>
+          <t>9 lotissement les Jardins</t>
+        </is>
+      </c>
+      <c r="Y70" s="23" t="inlineStr">
+        <is>
+          <t>57940</t>
+        </is>
+      </c>
+      <c r="Z70" s="22" t="inlineStr">
+        <is>
+          <t>Volstroff</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>449015296</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>44901529600022</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>LE CROCODILE</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>LE CROCODILE</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>15/09/2003</t>
+        </is>
+      </c>
+      <c r="J71" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K71" s="22" t="inlineStr">
+        <is>
+          <t>25 RUE SAINT-PIERRE</t>
+        </is>
+      </c>
+      <c r="L71" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M71" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N71" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O71" s="22" t="inlineStr"/>
+      <c r="P71" s="22" t="inlineStr"/>
+      <c r="Q71" s="22" t="inlineStr"/>
+      <c r="R71" s="23" t="inlineStr"/>
+      <c r="S71" s="22" t="inlineStr"/>
+      <c r="T71" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U71" s="22" t="inlineStr">
+        <is>
+          <t>LORRAIN</t>
+        </is>
+      </c>
+      <c r="V71" s="22" t="inlineStr">
+        <is>
+          <t>Sophie, Marie, Bernadette</t>
+        </is>
+      </c>
+      <c r="W71" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X71" s="22" t="inlineStr">
+        <is>
+          <t>5 ALLEE DES MESANGES</t>
+        </is>
+      </c>
+      <c r="Y71" s="23" t="inlineStr">
+        <is>
+          <t>57640</t>
+        </is>
+      </c>
+      <c r="Z71" s="22" t="inlineStr">
+        <is>
+          <t>VIGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>819204660</t>
+        </is>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>81920466000016</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>L'ANCIENNE GARE</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>L'ANCIENNE GARE</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>21/03/2016</t>
+        </is>
+      </c>
+      <c r="J72" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K72" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE ANTOINE</t>
+        </is>
+      </c>
+      <c r="L72" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M72" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N72" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O72" s="22" t="inlineStr"/>
+      <c r="P72" s="22" t="inlineStr"/>
+      <c r="Q72" s="22" t="inlineStr"/>
+      <c r="R72" s="23" t="inlineStr"/>
+      <c r="S72" s="22" t="inlineStr"/>
+      <c r="T72" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U72" s="22" t="inlineStr">
+        <is>
+          <t>VALENTIC</t>
+        </is>
+      </c>
+      <c r="V72" s="22" t="inlineStr">
+        <is>
+          <t>Joséphine</t>
+        </is>
+      </c>
+      <c r="W72" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X72" s="22" t="inlineStr">
+        <is>
+          <t>18 rue de la Croix Saint-Joseph</t>
+        </is>
+      </c>
+      <c r="Y72" s="23" t="inlineStr">
+        <is>
+          <t>57155</t>
+        </is>
+      </c>
+      <c r="Z72" s="22" t="inlineStr">
+        <is>
+          <t>Marly</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>484259767</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>48425976700024</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr">
+        <is>
+          <t>L'OPERA</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>L'OPERA</t>
+        </is>
+      </c>
+      <c r="F73" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>23/09/2005</t>
+        </is>
+      </c>
+      <c r="J73" s="22" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K73" s="22" t="inlineStr">
+        <is>
+          <t>39 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L73" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M73" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N73" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O73" s="22" t="inlineStr"/>
+      <c r="P73" s="22" t="inlineStr"/>
+      <c r="Q73" s="22" t="inlineStr"/>
+      <c r="R73" s="23" t="inlineStr"/>
+      <c r="S73" s="22" t="inlineStr"/>
+      <c r="T73" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U73" s="22" t="inlineStr">
+        <is>
+          <t>CAZAUDEBAT</t>
+        </is>
+      </c>
+      <c r="V73" s="22" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="W73" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X73" s="22" t="inlineStr">
+        <is>
+          <t>99 rue des Frênes</t>
+        </is>
+      </c>
+      <c r="Y73" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z73" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Julien-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="inlineStr">
+        <is>
+          <t>442445383</t>
+        </is>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>44244538300031</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>BEKIARIS GERASINOS</t>
+        </is>
+      </c>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>BEKIARIS GERASINOS</t>
+        </is>
+      </c>
+      <c r="F74" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2001</t>
+        </is>
+      </c>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="K74" s="22" t="inlineStr">
+        <is>
+          <t>34 EN CHAPLERUE</t>
+        </is>
+      </c>
+      <c r="L74" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N74" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O74" s="22" t="inlineStr"/>
+      <c r="P74" s="22" t="inlineStr"/>
+      <c r="Q74" s="22" t="inlineStr"/>
+      <c r="R74" s="23" t="inlineStr"/>
+      <c r="S74" s="22" t="inlineStr"/>
+      <c r="T74" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U74" s="22" t="inlineStr">
+        <is>
+          <t>BEKIARIS</t>
+        </is>
+      </c>
+      <c r="V74" s="22" t="inlineStr">
+        <is>
+          <t>Gerasinos</t>
+        </is>
+      </c>
+      <c r="W74" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X74" s="22" t="inlineStr"/>
+      <c r="Y74" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z74" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>851396275</t>
+        </is>
+      </c>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>85139627500022</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>LAVISION</t>
+        </is>
+      </c>
+      <c r="E75" s="22" t="inlineStr">
+        <is>
+          <t>LAVISION</t>
+        </is>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr">
+        <is>
+          <t>06/06/2019</t>
+        </is>
+      </c>
+      <c r="J75" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K75" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L75" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M75" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N75" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O75" s="22" t="inlineStr"/>
+      <c r="P75" s="22" t="inlineStr"/>
+      <c r="Q75" s="22" t="inlineStr"/>
+      <c r="R75" s="23" t="inlineStr"/>
+      <c r="S75" s="22" t="inlineStr"/>
+      <c r="T75" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U75" s="22" t="inlineStr">
+        <is>
+          <t>NZELO</t>
+        </is>
+      </c>
+      <c r="V75" s="22" t="inlineStr">
+        <is>
+          <t>Mbuta</t>
+        </is>
+      </c>
+      <c r="W75" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X75" s="22" t="inlineStr">
+        <is>
+          <t>9 Rue du Neufbourg</t>
+        </is>
+      </c>
+      <c r="Y75" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z75" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B76" s="23" t="inlineStr">
+        <is>
+          <t>484955711</t>
+        </is>
+      </c>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>48495571100011</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>SARL MAJU</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>SARL MAJU</t>
+        </is>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>05/10/2005</t>
+        </is>
+      </c>
+      <c r="J76" s="22" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K76" s="22" t="inlineStr">
+        <is>
+          <t>34 RUE TAISON</t>
+        </is>
+      </c>
+      <c r="L76" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N76" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O76" s="22" t="inlineStr"/>
+      <c r="P76" s="22" t="inlineStr"/>
+      <c r="Q76" s="22" t="inlineStr"/>
+      <c r="R76" s="23" t="inlineStr"/>
+      <c r="S76" s="22" t="inlineStr"/>
+      <c r="T76" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U76" s="22" t="inlineStr">
+        <is>
+          <t>HENNEQUIN</t>
+        </is>
+      </c>
+      <c r="V76" s="22" t="inlineStr">
+        <is>
+          <t>Patrice</t>
+        </is>
+      </c>
+      <c r="W76" s="22" t="inlineStr">
+        <is>
+          <t>Liquidateur</t>
+        </is>
+      </c>
+      <c r="X76" s="22" t="inlineStr">
+        <is>
+          <t>15 rue du Four du Cloître</t>
+        </is>
+      </c>
+      <c r="Y76" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z76" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>911732923</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>91173292300014</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>B.H RESTAURATION</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>B.H RESTAURATION</t>
+        </is>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>22/03/2022</t>
+        </is>
+      </c>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K77" s="22" t="inlineStr">
+        <is>
+          <t>15 RUE FABERT</t>
+        </is>
+      </c>
+      <c r="L77" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M77" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N77" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O77" s="22" t="inlineStr"/>
+      <c r="P77" s="22" t="inlineStr"/>
+      <c r="Q77" s="22" t="inlineStr"/>
+      <c r="R77" s="23" t="inlineStr"/>
+      <c r="S77" s="22" t="inlineStr"/>
+      <c r="T77" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U77" s="22" t="inlineStr">
+        <is>
+          <t>BENTAHA</t>
+        </is>
+      </c>
+      <c r="V77" s="22" t="inlineStr">
+        <is>
+          <t>Hacene</t>
+        </is>
+      </c>
+      <c r="W77" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X77" s="22" t="inlineStr">
+        <is>
+          <t>50 Boulevard de l'Evasion</t>
+        </is>
+      </c>
+      <c r="Y77" s="23" t="inlineStr">
+        <is>
+          <t>95800</t>
+        </is>
+      </c>
+      <c r="Z77" s="22" t="inlineStr">
+        <is>
+          <t>Cergy</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B78" s="23" t="inlineStr">
+        <is>
+          <t>989368493</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>98936849300015</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>BERKANE MARKET</t>
+        </is>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>BERKANE MARKET</t>
+        </is>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K78" s="22" t="inlineStr">
+        <is>
+          <t>13 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L78" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N78" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O78" s="22" t="inlineStr"/>
+      <c r="P78" s="22" t="inlineStr"/>
+      <c r="Q78" s="22" t="inlineStr"/>
+      <c r="R78" s="23" t="inlineStr"/>
+      <c r="S78" s="22" t="inlineStr"/>
+      <c r="T78" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U78" s="22" t="inlineStr">
+        <is>
+          <t>REGGAD</t>
+        </is>
+      </c>
+      <c r="V78" s="22" t="inlineStr">
+        <is>
+          <t>Adnane</t>
+        </is>
+      </c>
+      <c r="W78" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X78" s="22" t="inlineStr">
+        <is>
+          <t>20 rue du languedoc</t>
+        </is>
+      </c>
+      <c r="Y78" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z78" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="inlineStr">
+        <is>
+          <t>929224020</t>
+        </is>
+      </c>
+      <c r="C79" s="23" t="inlineStr">
+        <is>
+          <t>92922402000016</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>KYODAÏ IZAKAYA</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>KYODAÏ IZAKAYA</t>
+        </is>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>23/05/2024</t>
+        </is>
+      </c>
+      <c r="J79" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K79" s="22" t="inlineStr">
+        <is>
+          <t>22 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L79" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N79" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O79" s="22" t="inlineStr"/>
+      <c r="P79" s="22" t="inlineStr"/>
+      <c r="Q79" s="22" t="inlineStr"/>
+      <c r="R79" s="23" t="inlineStr"/>
+      <c r="S79" s="22" t="inlineStr"/>
+      <c r="T79" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U79" s="22" t="inlineStr">
+        <is>
+          <t>SUK</t>
+        </is>
+      </c>
+      <c r="V79" s="22" t="inlineStr">
+        <is>
+          <t>Laurent, Sébastien</t>
+        </is>
+      </c>
+      <c r="W79" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X79" s="22" t="inlineStr"/>
+      <c r="Y79" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z79" s="22" t="inlineStr">
+        <is>
+          <t>Norroy-le-Veneur</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="inlineStr">
+        <is>
+          <t>531462257</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>53146225700027</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>AYACHI JONATHAN</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>AYACHI JONATHAN</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>17/03/2011</t>
+        </is>
+      </c>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="K80" s="22" t="inlineStr">
+        <is>
+          <t>17 BOULEVARD ANDRE MAGINOT</t>
+        </is>
+      </c>
+      <c r="L80" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N80" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O80" s="22" t="inlineStr"/>
+      <c r="P80" s="22" t="inlineStr"/>
+      <c r="Q80" s="22" t="inlineStr"/>
+      <c r="R80" s="23" t="inlineStr"/>
+      <c r="S80" s="22" t="inlineStr"/>
+      <c r="T80" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U80" s="22" t="inlineStr">
+        <is>
+          <t>AYACHI</t>
+        </is>
+      </c>
+      <c r="V80" s="22" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="W80" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X80" s="22" t="inlineStr"/>
+      <c r="Y80" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z80" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>927863464</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>92786346400016</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr">
+        <is>
+          <t>CROQ'Ô'PIZZAS 04</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>CROQ'Ô'PIZZAS 04</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>18/04/2024</t>
+        </is>
+      </c>
+      <c r="J81" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K81" s="22" t="inlineStr">
+        <is>
+          <t>28 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L81" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N81" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O81" s="22" t="inlineStr"/>
+      <c r="P81" s="22" t="inlineStr"/>
+      <c r="Q81" s="22" t="inlineStr"/>
+      <c r="R81" s="23" t="inlineStr"/>
+      <c r="S81" s="22" t="inlineStr"/>
+      <c r="T81" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U81" s="22" t="inlineStr">
+        <is>
+          <t>RABHI</t>
+        </is>
+      </c>
+      <c r="V81" s="22" t="inlineStr">
+        <is>
+          <t>Sofiane</t>
+        </is>
+      </c>
+      <c r="W81" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X81" s="22" t="inlineStr">
+        <is>
+          <t>33 rue sainte anne</t>
+        </is>
+      </c>
+      <c r="Y81" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z81" s="22" t="inlineStr">
+        <is>
+          <t>Norroy-le-Veneur</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>991405655</t>
+        </is>
+      </c>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>99140565500010</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>BHM FOOD</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>BHM FOOD</t>
+        </is>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="J82" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K82" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L82" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N82" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O82" s="22" t="inlineStr"/>
+      <c r="P82" s="22" t="inlineStr"/>
+      <c r="Q82" s="22" t="inlineStr"/>
+      <c r="R82" s="23" t="inlineStr"/>
+      <c r="S82" s="22" t="inlineStr"/>
+      <c r="T82" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U82" s="22" t="inlineStr">
+        <is>
+          <t>BENTAHA</t>
+        </is>
+      </c>
+      <c r="V82" s="22" t="inlineStr">
+        <is>
+          <t>Hacene</t>
+        </is>
+      </c>
+      <c r="W82" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X82" s="22" t="inlineStr">
+        <is>
+          <t>50 boulevard de l'évasion</t>
+        </is>
+      </c>
+      <c r="Y82" s="23" t="inlineStr">
+        <is>
+          <t>95800</t>
+        </is>
+      </c>
+      <c r="Z82" s="22" t="inlineStr">
+        <is>
+          <t>Cergy</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>104939418</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>10493941800018</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>LE COMPTOIR GOURMAND DU SABLON</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>LE COMPTOIR GOURMAND DU SABLON</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="J83" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K83" s="22" t="inlineStr">
+        <is>
+          <t>RUE DES JARDINIERS</t>
+        </is>
+      </c>
+      <c r="L83" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O83" s="22" t="inlineStr"/>
+      <c r="P83" s="22" t="inlineStr"/>
+      <c r="Q83" s="22" t="inlineStr"/>
+      <c r="R83" s="23" t="inlineStr"/>
+      <c r="S83" s="22" t="inlineStr"/>
+      <c r="T83" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U83" s="22" t="inlineStr">
+        <is>
+          <t>CHELLI</t>
+        </is>
+      </c>
+      <c r="V83" s="22" t="inlineStr">
+        <is>
+          <t>Kahina</t>
+        </is>
+      </c>
+      <c r="W83" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X83" s="22" t="inlineStr">
+        <is>
+          <t>29 grand rue</t>
+        </is>
+      </c>
+      <c r="Y83" s="23" t="inlineStr">
+        <is>
+          <t>57190</t>
+        </is>
+      </c>
+      <c r="Z83" s="22" t="inlineStr">
+        <is>
+          <t>Florange</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>528504160</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>52850416000011</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>KAPAN Marc</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>KAPAN Marc</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>24/11/2010</t>
+        </is>
+      </c>
+      <c r="J84" s="22" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K84" s="22" t="inlineStr">
+        <is>
+          <t>5 PLACE BOUCHOTTE</t>
+        </is>
+      </c>
+      <c r="L84" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O84" s="22" t="inlineStr"/>
+      <c r="P84" s="22" t="inlineStr"/>
+      <c r="Q84" s="22" t="inlineStr"/>
+      <c r="R84" s="23" t="inlineStr"/>
+      <c r="S84" s="22" t="inlineStr"/>
+      <c r="T84" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U84" s="22" t="inlineStr">
+        <is>
+          <t>KAPAN</t>
+        </is>
+      </c>
+      <c r="V84" s="22" t="inlineStr">
+        <is>
+          <t>Marc</t>
+        </is>
+      </c>
+      <c r="W84" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X84" s="22" t="inlineStr"/>
+      <c r="Y84" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z84" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>901363978</t>
+        </is>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>90136397800015</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>WOKO METZ MUSE</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>WOKO METZ MUSE</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>07/07/2021</t>
+        </is>
+      </c>
+      <c r="J85" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K85" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L85" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M85" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O85" s="22" t="inlineStr"/>
+      <c r="P85" s="22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q85" s="22" t="inlineStr"/>
+      <c r="R85" s="23" t="inlineStr"/>
+      <c r="S85" s="22" t="inlineStr"/>
+      <c r="T85" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U85" s="22" t="inlineStr">
+        <is>
+          <t>WOKO HOLDING</t>
+        </is>
+      </c>
+      <c r="V85" s="22" t="inlineStr"/>
+      <c r="W85" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X85" s="22" t="inlineStr">
+        <is>
+          <t>17 Rue Hector Berlioz</t>
+        </is>
+      </c>
+      <c r="Y85" s="23" t="inlineStr">
+        <is>
+          <t>69100</t>
+        </is>
+      </c>
+      <c r="Z85" s="22" t="inlineStr">
+        <is>
+          <t>Villeurbanne</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>948354865</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>94835486500024</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>ALLO TACOS 57</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>ALLO TACOS 57</t>
+        </is>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I86" s="22" t="inlineStr">
+        <is>
+          <t>19/01/2023</t>
+        </is>
+      </c>
+      <c r="J86" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K86" s="22" t="inlineStr">
+        <is>
+          <t>65 B RUE AUX ARENES</t>
+        </is>
+      </c>
+      <c r="L86" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M86" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N86" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O86" s="22" t="inlineStr"/>
+      <c r="P86" s="22" t="inlineStr"/>
+      <c r="Q86" s="22" t="inlineStr"/>
+      <c r="R86" s="23" t="inlineStr"/>
+      <c r="S86" s="22" t="inlineStr"/>
+      <c r="T86" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U86" s="22" t="inlineStr">
+        <is>
+          <t>NAIB</t>
+        </is>
+      </c>
+      <c r="V86" s="22" t="inlineStr">
+        <is>
+          <t>Tarik</t>
+        </is>
+      </c>
+      <c r="W86" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X86" s="22" t="inlineStr">
+        <is>
+          <t>63 Avenue de Lattre de Tassigny</t>
+        </is>
+      </c>
+      <c r="Y86" s="23" t="inlineStr">
+        <is>
+          <t>57280</t>
+        </is>
+      </c>
+      <c r="Z86" s="22" t="inlineStr">
+        <is>
+          <t>Maizières-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>897824421</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>89782442100019</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>FOOD STREET 57</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>FOOD STREET 57</t>
+        </is>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="J87" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K87" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE COISLIN</t>
+        </is>
+      </c>
+      <c r="L87" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O87" s="22" t="inlineStr"/>
+      <c r="P87" s="22" t="inlineStr"/>
+      <c r="Q87" s="22" t="inlineStr"/>
+      <c r="R87" s="23" t="inlineStr"/>
+      <c r="S87" s="22" t="inlineStr"/>
+      <c r="T87" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U87" s="22" t="inlineStr">
+        <is>
+          <t>BEAUCHET</t>
+        </is>
+      </c>
+      <c r="V87" s="22" t="inlineStr">
+        <is>
+          <t>Pierre-françois</t>
+        </is>
+      </c>
+      <c r="W87" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X87" s="22" t="inlineStr">
+        <is>
+          <t>65 Avenue Georges Clémenceau</t>
+        </is>
+      </c>
+      <c r="Y87" s="23" t="inlineStr">
+        <is>
+          <t>57500</t>
+        </is>
+      </c>
+      <c r="Z87" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Avold</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z67"/>
+  <autoFilter ref="A2:Z87"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z87"/>
+  <dimension ref="A1:Z107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8090,2225 +8090,4427 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" s="21" t="inlineStr">
         <is>
           <t>837619626</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
+      <c r="C68" s="21" t="inlineStr">
         <is>
           <t>83761962600026</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>LDF</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>LDF</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F68" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
+      <c r="G68" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H68" s="22" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I68" s="22" t="inlineStr">
+      <c r="I68" s="20" t="inlineStr">
         <is>
           <t>20/11/2017</t>
         </is>
       </c>
-      <c r="J68" s="22" t="inlineStr">
+      <c r="J68" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K68" s="22" t="inlineStr">
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>11 RUE DES AUGUSTINS</t>
         </is>
       </c>
-      <c r="L68" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M68" s="22" t="inlineStr">
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M68" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N68" s="22" t="inlineStr">
+      <c r="N68" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O68" s="22" t="inlineStr"/>
-      <c r="P68" s="22" t="inlineStr"/>
-      <c r="Q68" s="22" t="inlineStr"/>
-      <c r="R68" s="23" t="inlineStr"/>
-      <c r="S68" s="22" t="inlineStr"/>
-      <c r="T68" s="22" t="inlineStr">
+      <c r="O68" s="20" t="inlineStr"/>
+      <c r="P68" s="20" t="inlineStr"/>
+      <c r="Q68" s="20" t="inlineStr"/>
+      <c r="R68" s="21" t="inlineStr"/>
+      <c r="S68" s="20" t="inlineStr"/>
+      <c r="T68" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U68" s="22" t="inlineStr">
+      <c r="U68" s="20" t="inlineStr">
         <is>
           <t>GOTHUEY</t>
         </is>
       </c>
-      <c r="V68" s="22" t="inlineStr">
+      <c r="V68" s="20" t="inlineStr">
         <is>
           <t>Vincent</t>
         </is>
       </c>
-      <c r="W68" s="22" t="inlineStr">
+      <c r="W68" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X68" s="22" t="inlineStr">
+      <c r="X68" s="20" t="inlineStr">
         <is>
           <t>6 rue de la Fontaine</t>
         </is>
       </c>
-      <c r="Y68" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z68" s="22" t="inlineStr">
+      <c r="Y68" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z68" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t>805245974</t>
         </is>
       </c>
-      <c r="C69" s="23" t="inlineStr">
+      <c r="C69" s="21" t="inlineStr">
         <is>
           <t>80524597400011</t>
         </is>
       </c>
-      <c r="D69" s="22" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>PINHO DE CASTRO Maria</t>
         </is>
       </c>
-      <c r="E69" s="22" t="inlineStr">
+      <c r="E69" s="20" t="inlineStr">
         <is>
           <t>PINHO DE CASTRO Maria</t>
         </is>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G69" s="22" t="inlineStr">
+      <c r="G69" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H69" s="22" t="inlineStr">
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I69" s="22" t="inlineStr">
+      <c r="I69" s="20" t="inlineStr">
         <is>
           <t>01/10/2014</t>
         </is>
       </c>
-      <c r="J69" s="22" t="inlineStr">
+      <c r="J69" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K69" s="22" t="inlineStr">
+      <c r="K69" s="20" t="inlineStr">
         <is>
           <t>60 RUE DE LA CHAPELLE</t>
         </is>
       </c>
-      <c r="L69" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M69" s="22" t="inlineStr">
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M69" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N69" s="22" t="inlineStr">
+      <c r="N69" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O69" s="22" t="inlineStr"/>
-      <c r="P69" s="22" t="inlineStr"/>
-      <c r="Q69" s="22" t="inlineStr"/>
-      <c r="R69" s="23" t="inlineStr"/>
-      <c r="S69" s="22" t="inlineStr"/>
-      <c r="T69" s="22" t="inlineStr">
+      <c r="O69" s="20" t="inlineStr"/>
+      <c r="P69" s="20" t="inlineStr"/>
+      <c r="Q69" s="20" t="inlineStr"/>
+      <c r="R69" s="21" t="inlineStr"/>
+      <c r="S69" s="20" t="inlineStr"/>
+      <c r="T69" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U69" s="22" t="inlineStr">
+      <c r="U69" s="20" t="inlineStr">
         <is>
           <t>PINHO DE CASTRO</t>
         </is>
       </c>
-      <c r="V69" s="22" t="inlineStr">
+      <c r="V69" s="20" t="inlineStr">
         <is>
           <t>Maria goreti</t>
         </is>
       </c>
-      <c r="W69" s="22" t="inlineStr">
+      <c r="W69" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X69" s="22" t="inlineStr"/>
-      <c r="Y69" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z69" s="22" t="inlineStr">
+      <c r="X69" s="20" t="inlineStr"/>
+      <c r="Y69" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z69" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B70" s="23" t="inlineStr">
+      <c r="B70" s="21" t="inlineStr">
         <is>
           <t>878082627</t>
         </is>
       </c>
-      <c r="C70" s="23" t="inlineStr">
+      <c r="C70" s="21" t="inlineStr">
         <is>
           <t>87808262700018</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>THIMOSO</t>
         </is>
       </c>
-      <c r="E70" s="22" t="inlineStr">
+      <c r="E70" s="20" t="inlineStr">
         <is>
           <t>THIMOSO</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F70" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H70" s="22" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I70" s="22" t="inlineStr">
+      <c r="I70" s="20" t="inlineStr">
         <is>
           <t>14/10/2019</t>
         </is>
       </c>
-      <c r="J70" s="22" t="inlineStr">
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K70" s="22" t="inlineStr">
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>6 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L70" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M70" s="22" t="inlineStr">
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M70" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N70" s="22" t="inlineStr">
+      <c r="N70" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O70" s="22" t="inlineStr"/>
-      <c r="P70" s="22" t="inlineStr"/>
-      <c r="Q70" s="22" t="inlineStr"/>
-      <c r="R70" s="23" t="inlineStr"/>
-      <c r="S70" s="22" t="inlineStr"/>
-      <c r="T70" s="22" t="inlineStr">
+      <c r="O70" s="20" t="inlineStr"/>
+      <c r="P70" s="20" t="inlineStr"/>
+      <c r="Q70" s="20" t="inlineStr"/>
+      <c r="R70" s="21" t="inlineStr"/>
+      <c r="S70" s="20" t="inlineStr"/>
+      <c r="T70" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U70" s="22" t="inlineStr">
+      <c r="U70" s="20" t="inlineStr">
         <is>
           <t>GURY</t>
         </is>
       </c>
-      <c r="V70" s="22" t="inlineStr">
+      <c r="V70" s="20" t="inlineStr">
         <is>
           <t>Thierry</t>
         </is>
       </c>
-      <c r="W70" s="22" t="inlineStr">
+      <c r="W70" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X70" s="22" t="inlineStr">
+      <c r="X70" s="20" t="inlineStr">
         <is>
           <t>9 lotissement les Jardins</t>
         </is>
       </c>
-      <c r="Y70" s="23" t="inlineStr">
+      <c r="Y70" s="21" t="inlineStr">
         <is>
           <t>57940</t>
         </is>
       </c>
-      <c r="Z70" s="22" t="inlineStr">
+      <c r="Z70" s="20" t="inlineStr">
         <is>
           <t>Volstroff</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B71" s="23" t="inlineStr">
+      <c r="B71" s="21" t="inlineStr">
         <is>
           <t>449015296</t>
         </is>
       </c>
-      <c r="C71" s="23" t="inlineStr">
+      <c r="C71" s="21" t="inlineStr">
         <is>
           <t>44901529600022</t>
         </is>
       </c>
-      <c r="D71" s="22" t="inlineStr">
+      <c r="D71" s="20" t="inlineStr">
         <is>
           <t>LE CROCODILE</t>
         </is>
       </c>
-      <c r="E71" s="22" t="inlineStr">
+      <c r="E71" s="20" t="inlineStr">
         <is>
           <t>LE CROCODILE</t>
         </is>
       </c>
-      <c r="F71" s="22" t="inlineStr">
+      <c r="F71" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G71" s="22" t="inlineStr">
+      <c r="G71" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="H71" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I71" s="22" t="inlineStr">
+      <c r="I71" s="20" t="inlineStr">
         <is>
           <t>15/09/2003</t>
         </is>
       </c>
-      <c r="J71" s="22" t="inlineStr">
+      <c r="J71" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K71" s="22" t="inlineStr">
+      <c r="K71" s="20" t="inlineStr">
         <is>
           <t>25 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M71" s="22" t="inlineStr">
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M71" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N71" s="22" t="inlineStr">
+      <c r="N71" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O71" s="22" t="inlineStr"/>
-      <c r="P71" s="22" t="inlineStr"/>
-      <c r="Q71" s="22" t="inlineStr"/>
-      <c r="R71" s="23" t="inlineStr"/>
-      <c r="S71" s="22" t="inlineStr"/>
-      <c r="T71" s="22" t="inlineStr">
+      <c r="O71" s="20" t="inlineStr"/>
+      <c r="P71" s="20" t="inlineStr"/>
+      <c r="Q71" s="20" t="inlineStr"/>
+      <c r="R71" s="21" t="inlineStr"/>
+      <c r="S71" s="20" t="inlineStr"/>
+      <c r="T71" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U71" s="22" t="inlineStr">
+      <c r="U71" s="20" t="inlineStr">
         <is>
           <t>LORRAIN</t>
         </is>
       </c>
-      <c r="V71" s="22" t="inlineStr">
+      <c r="V71" s="20" t="inlineStr">
         <is>
           <t>Sophie, Marie, Bernadette</t>
         </is>
       </c>
-      <c r="W71" s="22" t="inlineStr">
+      <c r="W71" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X71" s="22" t="inlineStr">
+      <c r="X71" s="20" t="inlineStr">
         <is>
           <t>5 ALLEE DES MESANGES</t>
         </is>
       </c>
-      <c r="Y71" s="23" t="inlineStr">
+      <c r="Y71" s="21" t="inlineStr">
         <is>
           <t>57640</t>
         </is>
       </c>
-      <c r="Z71" s="22" t="inlineStr">
+      <c r="Z71" s="20" t="inlineStr">
         <is>
           <t>VIGY</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="inlineStr">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B72" s="23" t="inlineStr">
+      <c r="B72" s="21" t="inlineStr">
         <is>
           <t>819204660</t>
         </is>
       </c>
-      <c r="C72" s="23" t="inlineStr">
+      <c r="C72" s="21" t="inlineStr">
         <is>
           <t>81920466000016</t>
         </is>
       </c>
-      <c r="D72" s="22" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>L'ANCIENNE GARE</t>
         </is>
       </c>
-      <c r="E72" s="22" t="inlineStr">
+      <c r="E72" s="20" t="inlineStr">
         <is>
           <t>L'ANCIENNE GARE</t>
         </is>
       </c>
-      <c r="F72" s="22" t="inlineStr">
+      <c r="F72" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G72" s="22" t="inlineStr">
+      <c r="G72" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H72" s="22" t="inlineStr">
+      <c r="H72" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I72" s="22" t="inlineStr">
+      <c r="I72" s="20" t="inlineStr">
         <is>
           <t>21/03/2016</t>
         </is>
       </c>
-      <c r="J72" s="22" t="inlineStr">
+      <c r="J72" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K72" s="22" t="inlineStr">
+      <c r="K72" s="20" t="inlineStr">
         <is>
           <t>2 RUE ANTOINE</t>
         </is>
       </c>
-      <c r="L72" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M72" s="22" t="inlineStr">
+      <c r="L72" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M72" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N72" s="22" t="inlineStr">
+      <c r="N72" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O72" s="22" t="inlineStr"/>
-      <c r="P72" s="22" t="inlineStr"/>
-      <c r="Q72" s="22" t="inlineStr"/>
-      <c r="R72" s="23" t="inlineStr"/>
-      <c r="S72" s="22" t="inlineStr"/>
-      <c r="T72" s="22" t="inlineStr">
+      <c r="O72" s="20" t="inlineStr"/>
+      <c r="P72" s="20" t="inlineStr"/>
+      <c r="Q72" s="20" t="inlineStr"/>
+      <c r="R72" s="21" t="inlineStr"/>
+      <c r="S72" s="20" t="inlineStr"/>
+      <c r="T72" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U72" s="22" t="inlineStr">
+      <c r="U72" s="20" t="inlineStr">
         <is>
           <t>VALENTIC</t>
         </is>
       </c>
-      <c r="V72" s="22" t="inlineStr">
+      <c r="V72" s="20" t="inlineStr">
         <is>
           <t>Joséphine</t>
         </is>
       </c>
-      <c r="W72" s="22" t="inlineStr">
+      <c r="W72" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X72" s="22" t="inlineStr">
+      <c r="X72" s="20" t="inlineStr">
         <is>
           <t>18 rue de la Croix Saint-Joseph</t>
         </is>
       </c>
-      <c r="Y72" s="23" t="inlineStr">
+      <c r="Y72" s="21" t="inlineStr">
         <is>
           <t>57155</t>
         </is>
       </c>
-      <c r="Z72" s="22" t="inlineStr">
+      <c r="Z72" s="20" t="inlineStr">
         <is>
           <t>Marly</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="inlineStr">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B73" s="23" t="inlineStr">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>484259767</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="C73" s="21" t="inlineStr">
         <is>
           <t>48425976700024</t>
         </is>
       </c>
-      <c r="D73" s="22" t="inlineStr">
+      <c r="D73" s="20" t="inlineStr">
         <is>
           <t>L'OPERA</t>
         </is>
       </c>
-      <c r="E73" s="22" t="inlineStr">
+      <c r="E73" s="20" t="inlineStr">
         <is>
           <t>L'OPERA</t>
         </is>
       </c>
-      <c r="F73" s="22" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G73" s="22" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H73" s="22" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I73" s="22" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>23/09/2005</t>
         </is>
       </c>
-      <c r="J73" s="22" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="K73" s="22" t="inlineStr">
+      <c r="K73" s="20" t="inlineStr">
         <is>
           <t>39 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L73" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M73" s="22" t="inlineStr">
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M73" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N73" s="22" t="inlineStr">
+      <c r="N73" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O73" s="22" t="inlineStr"/>
-      <c r="P73" s="22" t="inlineStr"/>
-      <c r="Q73" s="22" t="inlineStr"/>
-      <c r="R73" s="23" t="inlineStr"/>
-      <c r="S73" s="22" t="inlineStr"/>
-      <c r="T73" s="22" t="inlineStr">
+      <c r="O73" s="20" t="inlineStr"/>
+      <c r="P73" s="20" t="inlineStr"/>
+      <c r="Q73" s="20" t="inlineStr"/>
+      <c r="R73" s="21" t="inlineStr"/>
+      <c r="S73" s="20" t="inlineStr"/>
+      <c r="T73" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U73" s="22" t="inlineStr">
+      <c r="U73" s="20" t="inlineStr">
         <is>
           <t>CAZAUDEBAT</t>
         </is>
       </c>
-      <c r="V73" s="22" t="inlineStr">
+      <c r="V73" s="20" t="inlineStr">
         <is>
           <t>Emilie</t>
         </is>
       </c>
-      <c r="W73" s="22" t="inlineStr">
+      <c r="W73" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X73" s="22" t="inlineStr">
+      <c r="X73" s="20" t="inlineStr">
         <is>
           <t>99 rue des Frênes</t>
         </is>
       </c>
-      <c r="Y73" s="23" t="inlineStr">
+      <c r="Y73" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z73" s="22" t="inlineStr">
+      <c r="Z73" s="20" t="inlineStr">
         <is>
           <t>Saint-Julien-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="inlineStr">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B74" s="23" t="inlineStr">
+      <c r="B74" s="21" t="inlineStr">
         <is>
           <t>442445383</t>
         </is>
       </c>
-      <c r="C74" s="23" t="inlineStr">
+      <c r="C74" s="21" t="inlineStr">
         <is>
           <t>44244538300031</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="D74" s="20" t="inlineStr">
         <is>
           <t>BEKIARIS GERASINOS</t>
         </is>
       </c>
-      <c r="E74" s="22" t="inlineStr">
+      <c r="E74" s="20" t="inlineStr">
         <is>
           <t>BEKIARIS GERASINOS</t>
         </is>
       </c>
-      <c r="F74" s="22" t="inlineStr">
+      <c r="F74" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G74" s="22" t="inlineStr">
+      <c r="G74" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H74" s="22" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I74" s="22" t="inlineStr">
+      <c r="I74" s="20" t="inlineStr">
         <is>
           <t>01/12/2001</t>
         </is>
       </c>
-      <c r="J74" s="22" t="inlineStr">
+      <c r="J74" s="20" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="K74" s="22" t="inlineStr">
+      <c r="K74" s="20" t="inlineStr">
         <is>
           <t>34 EN CHAPLERUE</t>
         </is>
       </c>
-      <c r="L74" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M74" s="22" t="inlineStr">
+      <c r="L74" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M74" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N74" s="22" t="inlineStr">
+      <c r="N74" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O74" s="22" t="inlineStr"/>
-      <c r="P74" s="22" t="inlineStr"/>
-      <c r="Q74" s="22" t="inlineStr"/>
-      <c r="R74" s="23" t="inlineStr"/>
-      <c r="S74" s="22" t="inlineStr"/>
-      <c r="T74" s="22" t="inlineStr">
+      <c r="O74" s="20" t="inlineStr"/>
+      <c r="P74" s="20" t="inlineStr"/>
+      <c r="Q74" s="20" t="inlineStr"/>
+      <c r="R74" s="21" t="inlineStr"/>
+      <c r="S74" s="20" t="inlineStr"/>
+      <c r="T74" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U74" s="22" t="inlineStr">
+      <c r="U74" s="20" t="inlineStr">
         <is>
           <t>BEKIARIS</t>
         </is>
       </c>
-      <c r="V74" s="22" t="inlineStr">
+      <c r="V74" s="20" t="inlineStr">
         <is>
           <t>Gerasinos</t>
         </is>
       </c>
-      <c r="W74" s="22" t="inlineStr">
+      <c r="W74" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X74" s="22" t="inlineStr"/>
-      <c r="Y74" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z74" s="22" t="inlineStr">
+      <c r="X74" s="20" t="inlineStr"/>
+      <c r="Y74" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z74" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="inlineStr">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B75" s="23" t="inlineStr">
+      <c r="B75" s="21" t="inlineStr">
         <is>
           <t>851396275</t>
         </is>
       </c>
-      <c r="C75" s="23" t="inlineStr">
+      <c r="C75" s="21" t="inlineStr">
         <is>
           <t>85139627500022</t>
         </is>
       </c>
-      <c r="D75" s="22" t="inlineStr">
+      <c r="D75" s="20" t="inlineStr">
         <is>
           <t>LAVISION</t>
         </is>
       </c>
-      <c r="E75" s="22" t="inlineStr">
+      <c r="E75" s="20" t="inlineStr">
         <is>
           <t>LAVISION</t>
         </is>
       </c>
-      <c r="F75" s="22" t="inlineStr">
+      <c r="F75" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G75" s="22" t="inlineStr">
+      <c r="G75" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H75" s="22" t="inlineStr">
+      <c r="H75" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I75" s="22" t="inlineStr">
+      <c r="I75" s="20" t="inlineStr">
         <is>
           <t>06/06/2019</t>
         </is>
       </c>
-      <c r="J75" s="22" t="inlineStr">
+      <c r="J75" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K75" s="22" t="inlineStr">
+      <c r="K75" s="20" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L75" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M75" s="22" t="inlineStr">
+      <c r="L75" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M75" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N75" s="22" t="inlineStr">
+      <c r="N75" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O75" s="22" t="inlineStr"/>
-      <c r="P75" s="22" t="inlineStr"/>
-      <c r="Q75" s="22" t="inlineStr"/>
-      <c r="R75" s="23" t="inlineStr"/>
-      <c r="S75" s="22" t="inlineStr"/>
-      <c r="T75" s="22" t="inlineStr">
+      <c r="O75" s="20" t="inlineStr"/>
+      <c r="P75" s="20" t="inlineStr"/>
+      <c r="Q75" s="20" t="inlineStr"/>
+      <c r="R75" s="21" t="inlineStr"/>
+      <c r="S75" s="20" t="inlineStr"/>
+      <c r="T75" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U75" s="22" t="inlineStr">
+      <c r="U75" s="20" t="inlineStr">
         <is>
           <t>NZELO</t>
         </is>
       </c>
-      <c r="V75" s="22" t="inlineStr">
+      <c r="V75" s="20" t="inlineStr">
         <is>
           <t>Mbuta</t>
         </is>
       </c>
-      <c r="W75" s="22" t="inlineStr">
+      <c r="W75" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X75" s="22" t="inlineStr">
+      <c r="X75" s="20" t="inlineStr">
         <is>
           <t>9 Rue du Neufbourg</t>
         </is>
       </c>
-      <c r="Y75" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z75" s="22" t="inlineStr">
+      <c r="Y75" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z75" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="B76" s="21" t="inlineStr">
         <is>
           <t>484955711</t>
         </is>
       </c>
-      <c r="C76" s="23" t="inlineStr">
+      <c r="C76" s="21" t="inlineStr">
         <is>
           <t>48495571100011</t>
         </is>
       </c>
-      <c r="D76" s="22" t="inlineStr">
+      <c r="D76" s="20" t="inlineStr">
         <is>
           <t>SARL MAJU</t>
         </is>
       </c>
-      <c r="E76" s="22" t="inlineStr">
+      <c r="E76" s="20" t="inlineStr">
         <is>
           <t>SARL MAJU</t>
         </is>
       </c>
-      <c r="F76" s="22" t="inlineStr">
+      <c r="F76" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
+      <c r="G76" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H76" s="22" t="inlineStr">
+      <c r="H76" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I76" s="22" t="inlineStr">
+      <c r="I76" s="20" t="inlineStr">
         <is>
           <t>05/10/2005</t>
         </is>
       </c>
-      <c r="J76" s="22" t="inlineStr">
+      <c r="J76" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="K76" s="22" t="inlineStr">
+      <c r="K76" s="20" t="inlineStr">
         <is>
           <t>34 RUE TAISON</t>
         </is>
       </c>
-      <c r="L76" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M76" s="22" t="inlineStr">
+      <c r="L76" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M76" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N76" s="22" t="inlineStr">
+      <c r="N76" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O76" s="22" t="inlineStr"/>
-      <c r="P76" s="22" t="inlineStr"/>
-      <c r="Q76" s="22" t="inlineStr"/>
-      <c r="R76" s="23" t="inlineStr"/>
-      <c r="S76" s="22" t="inlineStr"/>
-      <c r="T76" s="22" t="inlineStr">
+      <c r="O76" s="20" t="inlineStr"/>
+      <c r="P76" s="20" t="inlineStr"/>
+      <c r="Q76" s="20" t="inlineStr"/>
+      <c r="R76" s="21" t="inlineStr"/>
+      <c r="S76" s="20" t="inlineStr"/>
+      <c r="T76" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U76" s="22" t="inlineStr">
+      <c r="U76" s="20" t="inlineStr">
         <is>
           <t>HENNEQUIN</t>
         </is>
       </c>
-      <c r="V76" s="22" t="inlineStr">
+      <c r="V76" s="20" t="inlineStr">
         <is>
           <t>Patrice</t>
         </is>
       </c>
-      <c r="W76" s="22" t="inlineStr">
+      <c r="W76" s="20" t="inlineStr">
         <is>
           <t>Liquidateur</t>
         </is>
       </c>
-      <c r="X76" s="22" t="inlineStr">
+      <c r="X76" s="20" t="inlineStr">
         <is>
           <t>15 rue du Four du Cloître</t>
         </is>
       </c>
-      <c r="Y76" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z76" s="22" t="inlineStr">
+      <c r="Y76" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z76" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B77" s="23" t="inlineStr">
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>911732923</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
+      <c r="C77" s="21" t="inlineStr">
         <is>
           <t>91173292300014</t>
         </is>
       </c>
-      <c r="D77" s="22" t="inlineStr">
+      <c r="D77" s="20" t="inlineStr">
         <is>
           <t>B.H RESTAURATION</t>
         </is>
       </c>
-      <c r="E77" s="22" t="inlineStr">
+      <c r="E77" s="20" t="inlineStr">
         <is>
           <t>B.H RESTAURATION</t>
         </is>
       </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="F77" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G77" s="22" t="inlineStr">
+      <c r="G77" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H77" s="22" t="inlineStr">
+      <c r="H77" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I77" s="22" t="inlineStr">
+      <c r="I77" s="20" t="inlineStr">
         <is>
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="J77" s="22" t="inlineStr">
+      <c r="J77" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K77" s="22" t="inlineStr">
+      <c r="K77" s="20" t="inlineStr">
         <is>
           <t>15 RUE FABERT</t>
         </is>
       </c>
-      <c r="L77" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M77" s="22" t="inlineStr">
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M77" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N77" s="22" t="inlineStr">
+      <c r="N77" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O77" s="22" t="inlineStr"/>
-      <c r="P77" s="22" t="inlineStr"/>
-      <c r="Q77" s="22" t="inlineStr"/>
-      <c r="R77" s="23" t="inlineStr"/>
-      <c r="S77" s="22" t="inlineStr"/>
-      <c r="T77" s="22" t="inlineStr">
+      <c r="O77" s="20" t="inlineStr"/>
+      <c r="P77" s="20" t="inlineStr"/>
+      <c r="Q77" s="20" t="inlineStr"/>
+      <c r="R77" s="21" t="inlineStr"/>
+      <c r="S77" s="20" t="inlineStr"/>
+      <c r="T77" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U77" s="22" t="inlineStr">
+      <c r="U77" s="20" t="inlineStr">
         <is>
           <t>BENTAHA</t>
         </is>
       </c>
-      <c r="V77" s="22" t="inlineStr">
+      <c r="V77" s="20" t="inlineStr">
         <is>
           <t>Hacene</t>
         </is>
       </c>
-      <c r="W77" s="22" t="inlineStr">
+      <c r="W77" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X77" s="22" t="inlineStr">
+      <c r="X77" s="20" t="inlineStr">
         <is>
           <t>50 Boulevard de l'Evasion</t>
         </is>
       </c>
-      <c r="Y77" s="23" t="inlineStr">
+      <c r="Y77" s="21" t="inlineStr">
         <is>
           <t>95800</t>
         </is>
       </c>
-      <c r="Z77" s="22" t="inlineStr">
+      <c r="Z77" s="20" t="inlineStr">
         <is>
           <t>Cergy</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="inlineStr">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B78" s="23" t="inlineStr">
+      <c r="B78" s="21" t="inlineStr">
         <is>
           <t>989368493</t>
         </is>
       </c>
-      <c r="C78" s="23" t="inlineStr">
+      <c r="C78" s="21" t="inlineStr">
         <is>
           <t>98936849300015</t>
         </is>
       </c>
-      <c r="D78" s="22" t="inlineStr">
+      <c r="D78" s="20" t="inlineStr">
         <is>
           <t>BERKANE MARKET</t>
         </is>
       </c>
-      <c r="E78" s="22" t="inlineStr">
+      <c r="E78" s="20" t="inlineStr">
         <is>
           <t>BERKANE MARKET</t>
         </is>
       </c>
-      <c r="F78" s="22" t="inlineStr">
+      <c r="F78" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
+      <c r="G78" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H78" s="22" t="inlineStr">
+      <c r="H78" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I78" s="22" t="inlineStr">
+      <c r="I78" s="20" t="inlineStr">
         <is>
           <t>15/07/2025</t>
         </is>
       </c>
-      <c r="J78" s="22" t="inlineStr">
+      <c r="J78" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K78" s="22" t="inlineStr">
+      <c r="K78" s="20" t="inlineStr">
         <is>
           <t>13 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L78" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M78" s="22" t="inlineStr">
+      <c r="L78" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M78" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N78" s="22" t="inlineStr">
+      <c r="N78" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O78" s="22" t="inlineStr"/>
-      <c r="P78" s="22" t="inlineStr"/>
-      <c r="Q78" s="22" t="inlineStr"/>
-      <c r="R78" s="23" t="inlineStr"/>
-      <c r="S78" s="22" t="inlineStr"/>
-      <c r="T78" s="22" t="inlineStr">
+      <c r="O78" s="20" t="inlineStr"/>
+      <c r="P78" s="20" t="inlineStr"/>
+      <c r="Q78" s="20" t="inlineStr"/>
+      <c r="R78" s="21" t="inlineStr"/>
+      <c r="S78" s="20" t="inlineStr"/>
+      <c r="T78" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U78" s="22" t="inlineStr">
+      <c r="U78" s="20" t="inlineStr">
         <is>
           <t>REGGAD</t>
         </is>
       </c>
-      <c r="V78" s="22" t="inlineStr">
+      <c r="V78" s="20" t="inlineStr">
         <is>
           <t>Adnane</t>
         </is>
       </c>
-      <c r="W78" s="22" t="inlineStr">
+      <c r="W78" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X78" s="22" t="inlineStr">
+      <c r="X78" s="20" t="inlineStr">
         <is>
           <t>20 rue du languedoc</t>
         </is>
       </c>
-      <c r="Y78" s="23" t="inlineStr">
+      <c r="Y78" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z78" s="22" t="inlineStr">
+      <c r="Z78" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="inlineStr">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B79" s="23" t="inlineStr">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>929224020</t>
         </is>
       </c>
-      <c r="C79" s="23" t="inlineStr">
+      <c r="C79" s="21" t="inlineStr">
         <is>
           <t>92922402000016</t>
         </is>
       </c>
-      <c r="D79" s="22" t="inlineStr">
+      <c r="D79" s="20" t="inlineStr">
         <is>
           <t>KYODAÏ IZAKAYA</t>
         </is>
       </c>
-      <c r="E79" s="22" t="inlineStr">
+      <c r="E79" s="20" t="inlineStr">
         <is>
           <t>KYODAÏ IZAKAYA</t>
         </is>
       </c>
-      <c r="F79" s="22" t="inlineStr">
+      <c r="F79" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G79" s="22" t="inlineStr">
+      <c r="G79" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H79" s="22" t="inlineStr">
+      <c r="H79" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I79" s="22" t="inlineStr">
+      <c r="I79" s="20" t="inlineStr">
         <is>
           <t>23/05/2024</t>
         </is>
       </c>
-      <c r="J79" s="22" t="inlineStr">
+      <c r="J79" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K79" s="22" t="inlineStr">
+      <c r="K79" s="20" t="inlineStr">
         <is>
           <t>22 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L79" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M79" s="22" t="inlineStr">
+      <c r="L79" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M79" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N79" s="22" t="inlineStr">
+      <c r="N79" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O79" s="22" t="inlineStr"/>
-      <c r="P79" s="22" t="inlineStr"/>
-      <c r="Q79" s="22" t="inlineStr"/>
-      <c r="R79" s="23" t="inlineStr"/>
-      <c r="S79" s="22" t="inlineStr"/>
-      <c r="T79" s="22" t="inlineStr">
+      <c r="O79" s="20" t="inlineStr"/>
+      <c r="P79" s="20" t="inlineStr"/>
+      <c r="Q79" s="20" t="inlineStr"/>
+      <c r="R79" s="21" t="inlineStr"/>
+      <c r="S79" s="20" t="inlineStr"/>
+      <c r="T79" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U79" s="22" t="inlineStr">
+      <c r="U79" s="20" t="inlineStr">
         <is>
           <t>SUK</t>
         </is>
       </c>
-      <c r="V79" s="22" t="inlineStr">
+      <c r="V79" s="20" t="inlineStr">
         <is>
           <t>Laurent, Sébastien</t>
         </is>
       </c>
-      <c r="W79" s="22" t="inlineStr">
+      <c r="W79" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X79" s="22" t="inlineStr"/>
-      <c r="Y79" s="23" t="inlineStr">
+      <c r="X79" s="20" t="inlineStr"/>
+      <c r="Y79" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z79" s="22" t="inlineStr">
+      <c r="Z79" s="20" t="inlineStr">
         <is>
           <t>Norroy-le-Veneur</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="inlineStr">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B80" s="23" t="inlineStr">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>531462257</t>
         </is>
       </c>
-      <c r="C80" s="23" t="inlineStr">
+      <c r="C80" s="21" t="inlineStr">
         <is>
           <t>53146225700027</t>
         </is>
       </c>
-      <c r="D80" s="22" t="inlineStr">
+      <c r="D80" s="20" t="inlineStr">
         <is>
           <t>AYACHI JONATHAN</t>
         </is>
       </c>
-      <c r="E80" s="22" t="inlineStr">
+      <c r="E80" s="20" t="inlineStr">
         <is>
           <t>AYACHI JONATHAN</t>
         </is>
       </c>
-      <c r="F80" s="22" t="inlineStr">
+      <c r="F80" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
+      <c r="G80" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H80" s="22" t="inlineStr">
+      <c r="H80" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I80" s="22" t="inlineStr">
+      <c r="I80" s="20" t="inlineStr">
         <is>
           <t>17/03/2011</t>
         </is>
       </c>
-      <c r="J80" s="22" t="inlineStr">
+      <c r="J80" s="20" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="K80" s="22" t="inlineStr">
+      <c r="K80" s="20" t="inlineStr">
         <is>
           <t>17 BOULEVARD ANDRE MAGINOT</t>
         </is>
       </c>
-      <c r="L80" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M80" s="22" t="inlineStr">
+      <c r="L80" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M80" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N80" s="22" t="inlineStr">
+      <c r="N80" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O80" s="22" t="inlineStr"/>
-      <c r="P80" s="22" t="inlineStr"/>
-      <c r="Q80" s="22" t="inlineStr"/>
-      <c r="R80" s="23" t="inlineStr"/>
-      <c r="S80" s="22" t="inlineStr"/>
-      <c r="T80" s="22" t="inlineStr">
+      <c r="O80" s="20" t="inlineStr"/>
+      <c r="P80" s="20" t="inlineStr"/>
+      <c r="Q80" s="20" t="inlineStr"/>
+      <c r="R80" s="21" t="inlineStr"/>
+      <c r="S80" s="20" t="inlineStr"/>
+      <c r="T80" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U80" s="22" t="inlineStr">
+      <c r="U80" s="20" t="inlineStr">
         <is>
           <t>AYACHI</t>
         </is>
       </c>
-      <c r="V80" s="22" t="inlineStr">
+      <c r="V80" s="20" t="inlineStr">
         <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="W80" s="22" t="inlineStr">
+      <c r="W80" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X80" s="22" t="inlineStr"/>
-      <c r="Y80" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z80" s="22" t="inlineStr">
+      <c r="X80" s="20" t="inlineStr"/>
+      <c r="Y80" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z80" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="inlineStr">
+      <c r="A81" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B81" s="23" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>927863464</t>
         </is>
       </c>
-      <c r="C81" s="23" t="inlineStr">
+      <c r="C81" s="21" t="inlineStr">
         <is>
           <t>92786346400016</t>
         </is>
       </c>
-      <c r="D81" s="22" t="inlineStr">
+      <c r="D81" s="20" t="inlineStr">
         <is>
           <t>CROQ'Ô'PIZZAS 04</t>
         </is>
       </c>
-      <c r="E81" s="22" t="inlineStr">
+      <c r="E81" s="20" t="inlineStr">
         <is>
           <t>CROQ'Ô'PIZZAS 04</t>
         </is>
       </c>
-      <c r="F81" s="22" t="inlineStr">
+      <c r="F81" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G81" s="22" t="inlineStr">
+      <c r="G81" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H81" s="22" t="inlineStr">
+      <c r="H81" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I81" s="22" t="inlineStr">
+      <c r="I81" s="20" t="inlineStr">
         <is>
           <t>18/04/2024</t>
         </is>
       </c>
-      <c r="J81" s="22" t="inlineStr">
+      <c r="J81" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K81" s="22" t="inlineStr">
+      <c r="K81" s="20" t="inlineStr">
         <is>
           <t>28 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L81" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M81" s="22" t="inlineStr">
+      <c r="L81" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M81" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N81" s="22" t="inlineStr">
+      <c r="N81" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O81" s="22" t="inlineStr"/>
-      <c r="P81" s="22" t="inlineStr"/>
-      <c r="Q81" s="22" t="inlineStr"/>
-      <c r="R81" s="23" t="inlineStr"/>
-      <c r="S81" s="22" t="inlineStr"/>
-      <c r="T81" s="22" t="inlineStr">
+      <c r="O81" s="20" t="inlineStr"/>
+      <c r="P81" s="20" t="inlineStr"/>
+      <c r="Q81" s="20" t="inlineStr"/>
+      <c r="R81" s="21" t="inlineStr"/>
+      <c r="S81" s="20" t="inlineStr"/>
+      <c r="T81" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U81" s="22" t="inlineStr">
+      <c r="U81" s="20" t="inlineStr">
         <is>
           <t>RABHI</t>
         </is>
       </c>
-      <c r="V81" s="22" t="inlineStr">
+      <c r="V81" s="20" t="inlineStr">
         <is>
           <t>Sofiane</t>
         </is>
       </c>
-      <c r="W81" s="22" t="inlineStr">
+      <c r="W81" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X81" s="22" t="inlineStr">
+      <c r="X81" s="20" t="inlineStr">
         <is>
           <t>33 rue sainte anne</t>
         </is>
       </c>
-      <c r="Y81" s="23" t="inlineStr">
+      <c r="Y81" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z81" s="22" t="inlineStr">
+      <c r="Z81" s="20" t="inlineStr">
         <is>
           <t>Norroy-le-Veneur</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="inlineStr">
+      <c r="A82" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B82" s="23" t="inlineStr">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>991405655</t>
         </is>
       </c>
-      <c r="C82" s="23" t="inlineStr">
+      <c r="C82" s="21" t="inlineStr">
         <is>
           <t>99140565500010</t>
         </is>
       </c>
-      <c r="D82" s="22" t="inlineStr">
+      <c r="D82" s="20" t="inlineStr">
         <is>
           <t>BHM FOOD</t>
         </is>
       </c>
-      <c r="E82" s="22" t="inlineStr">
+      <c r="E82" s="20" t="inlineStr">
         <is>
           <t>BHM FOOD</t>
         </is>
       </c>
-      <c r="F82" s="22" t="inlineStr">
+      <c r="F82" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
+      <c r="G82" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H82" s="22" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I82" s="22" t="inlineStr">
+      <c r="I82" s="20" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="J82" s="22" t="inlineStr">
+      <c r="J82" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K82" s="22" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L82" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M82" s="22" t="inlineStr">
+      <c r="L82" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M82" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N82" s="22" t="inlineStr">
+      <c r="N82" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O82" s="22" t="inlineStr"/>
-      <c r="P82" s="22" t="inlineStr"/>
-      <c r="Q82" s="22" t="inlineStr"/>
-      <c r="R82" s="23" t="inlineStr"/>
-      <c r="S82" s="22" t="inlineStr"/>
-      <c r="T82" s="22" t="inlineStr">
+      <c r="O82" s="20" t="inlineStr"/>
+      <c r="P82" s="20" t="inlineStr"/>
+      <c r="Q82" s="20" t="inlineStr"/>
+      <c r="R82" s="21" t="inlineStr"/>
+      <c r="S82" s="20" t="inlineStr"/>
+      <c r="T82" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U82" s="22" t="inlineStr">
+      <c r="U82" s="20" t="inlineStr">
         <is>
           <t>BENTAHA</t>
         </is>
       </c>
-      <c r="V82" s="22" t="inlineStr">
+      <c r="V82" s="20" t="inlineStr">
         <is>
           <t>Hacene</t>
         </is>
       </c>
-      <c r="W82" s="22" t="inlineStr">
+      <c r="W82" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X82" s="22" t="inlineStr">
+      <c r="X82" s="20" t="inlineStr">
         <is>
           <t>50 boulevard de l'évasion</t>
         </is>
       </c>
-      <c r="Y82" s="23" t="inlineStr">
+      <c r="Y82" s="21" t="inlineStr">
         <is>
           <t>95800</t>
         </is>
       </c>
-      <c r="Z82" s="22" t="inlineStr">
+      <c r="Z82" s="20" t="inlineStr">
         <is>
           <t>Cergy</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+      <c r="A83" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B83" s="23" t="inlineStr">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>104939418</t>
         </is>
       </c>
-      <c r="C83" s="23" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
         <is>
           <t>10493941800018</t>
         </is>
       </c>
-      <c r="D83" s="22" t="inlineStr">
+      <c r="D83" s="20" t="inlineStr">
         <is>
           <t>LE COMPTOIR GOURMAND DU SABLON</t>
         </is>
       </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="E83" s="20" t="inlineStr">
         <is>
           <t>LE COMPTOIR GOURMAND DU SABLON</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
+      <c r="F83" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G83" s="22" t="inlineStr">
+      <c r="G83" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H83" s="22" t="inlineStr">
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I83" s="22" t="inlineStr">
+      <c r="I83" s="20" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="J83" s="22" t="inlineStr">
+      <c r="J83" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K83" s="22" t="inlineStr">
+      <c r="K83" s="20" t="inlineStr">
         <is>
           <t>RUE DES JARDINIERS</t>
         </is>
       </c>
-      <c r="L83" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M83" s="22" t="inlineStr">
+      <c r="L83" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M83" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N83" s="22" t="inlineStr">
+      <c r="N83" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O83" s="22" t="inlineStr"/>
-      <c r="P83" s="22" t="inlineStr"/>
-      <c r="Q83" s="22" t="inlineStr"/>
-      <c r="R83" s="23" t="inlineStr"/>
-      <c r="S83" s="22" t="inlineStr"/>
-      <c r="T83" s="22" t="inlineStr">
+      <c r="O83" s="20" t="inlineStr"/>
+      <c r="P83" s="20" t="inlineStr"/>
+      <c r="Q83" s="20" t="inlineStr"/>
+      <c r="R83" s="21" t="inlineStr"/>
+      <c r="S83" s="20" t="inlineStr"/>
+      <c r="T83" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U83" s="22" t="inlineStr">
+      <c r="U83" s="20" t="inlineStr">
         <is>
           <t>CHELLI</t>
         </is>
       </c>
-      <c r="V83" s="22" t="inlineStr">
+      <c r="V83" s="20" t="inlineStr">
         <is>
           <t>Kahina</t>
         </is>
       </c>
-      <c r="W83" s="22" t="inlineStr">
+      <c r="W83" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X83" s="22" t="inlineStr">
+      <c r="X83" s="20" t="inlineStr">
         <is>
           <t>29 grand rue</t>
         </is>
       </c>
-      <c r="Y83" s="23" t="inlineStr">
+      <c r="Y83" s="21" t="inlineStr">
         <is>
           <t>57190</t>
         </is>
       </c>
-      <c r="Z83" s="22" t="inlineStr">
+      <c r="Z83" s="20" t="inlineStr">
         <is>
           <t>Florange</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B84" s="23" t="inlineStr">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>528504160</t>
         </is>
       </c>
-      <c r="C84" s="23" t="inlineStr">
+      <c r="C84" s="21" t="inlineStr">
         <is>
           <t>52850416000011</t>
         </is>
       </c>
-      <c r="D84" s="22" t="inlineStr">
+      <c r="D84" s="20" t="inlineStr">
         <is>
           <t>KAPAN Marc</t>
         </is>
       </c>
-      <c r="E84" s="22" t="inlineStr">
+      <c r="E84" s="20" t="inlineStr">
         <is>
           <t>KAPAN Marc</t>
         </is>
       </c>
-      <c r="F84" s="22" t="inlineStr">
+      <c r="F84" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
+      <c r="G84" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H84" s="22" t="inlineStr">
+      <c r="H84" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I84" s="22" t="inlineStr">
+      <c r="I84" s="20" t="inlineStr">
         <is>
           <t>24/11/2010</t>
         </is>
       </c>
-      <c r="J84" s="22" t="inlineStr">
+      <c r="J84" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K84" s="22" t="inlineStr">
+      <c r="K84" s="20" t="inlineStr">
         <is>
           <t>5 PLACE BOUCHOTTE</t>
         </is>
       </c>
-      <c r="L84" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M84" s="22" t="inlineStr">
+      <c r="L84" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M84" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N84" s="22" t="inlineStr">
+      <c r="N84" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O84" s="22" t="inlineStr"/>
-      <c r="P84" s="22" t="inlineStr"/>
-      <c r="Q84" s="22" t="inlineStr"/>
-      <c r="R84" s="23" t="inlineStr"/>
-      <c r="S84" s="22" t="inlineStr"/>
-      <c r="T84" s="22" t="inlineStr">
+      <c r="O84" s="20" t="inlineStr"/>
+      <c r="P84" s="20" t="inlineStr"/>
+      <c r="Q84" s="20" t="inlineStr"/>
+      <c r="R84" s="21" t="inlineStr"/>
+      <c r="S84" s="20" t="inlineStr"/>
+      <c r="T84" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U84" s="22" t="inlineStr">
+      <c r="U84" s="20" t="inlineStr">
         <is>
           <t>KAPAN</t>
         </is>
       </c>
-      <c r="V84" s="22" t="inlineStr">
+      <c r="V84" s="20" t="inlineStr">
         <is>
           <t>Marc</t>
         </is>
       </c>
-      <c r="W84" s="22" t="inlineStr">
+      <c r="W84" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X84" s="22" t="inlineStr"/>
-      <c r="Y84" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z84" s="22" t="inlineStr">
+      <c r="X84" s="20" t="inlineStr"/>
+      <c r="Y84" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z84" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="inlineStr">
+      <c r="A85" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B85" s="23" t="inlineStr">
+      <c r="B85" s="21" t="inlineStr">
         <is>
           <t>901363978</t>
         </is>
       </c>
-      <c r="C85" s="23" t="inlineStr">
+      <c r="C85" s="21" t="inlineStr">
         <is>
           <t>90136397800015</t>
         </is>
       </c>
-      <c r="D85" s="22" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>WOKO METZ MUSE</t>
         </is>
       </c>
-      <c r="E85" s="22" t="inlineStr">
+      <c r="E85" s="20" t="inlineStr">
         <is>
           <t>WOKO METZ MUSE</t>
         </is>
       </c>
-      <c r="F85" s="22" t="inlineStr">
+      <c r="F85" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G85" s="22" t="inlineStr">
+      <c r="G85" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr">
+      <c r="H85" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I85" s="22" t="inlineStr">
+      <c r="I85" s="20" t="inlineStr">
         <is>
           <t>07/07/2021</t>
         </is>
       </c>
-      <c r="J85" s="22" t="inlineStr">
+      <c r="J85" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K85" s="22" t="inlineStr">
+      <c r="K85" s="20" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L85" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M85" s="22" t="inlineStr">
+      <c r="L85" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M85" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N85" s="22" t="inlineStr">
+      <c r="N85" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O85" s="22" t="inlineStr"/>
-      <c r="P85" s="22" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q85" s="22" t="inlineStr"/>
-      <c r="R85" s="23" t="inlineStr"/>
-      <c r="S85" s="22" t="inlineStr"/>
-      <c r="T85" s="22" t="inlineStr">
+      <c r="O85" s="20" t="inlineStr"/>
+      <c r="P85" s="20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q85" s="20" t="inlineStr"/>
+      <c r="R85" s="21" t="inlineStr"/>
+      <c r="S85" s="20" t="inlineStr"/>
+      <c r="T85" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U85" s="22" t="inlineStr">
+      <c r="U85" s="20" t="inlineStr">
         <is>
           <t>WOKO HOLDING</t>
         </is>
       </c>
-      <c r="V85" s="22" t="inlineStr"/>
-      <c r="W85" s="22" t="inlineStr">
+      <c r="V85" s="20" t="inlineStr"/>
+      <c r="W85" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X85" s="22" t="inlineStr">
+      <c r="X85" s="20" t="inlineStr">
         <is>
           <t>17 Rue Hector Berlioz</t>
         </is>
       </c>
-      <c r="Y85" s="23" t="inlineStr">
+      <c r="Y85" s="21" t="inlineStr">
         <is>
           <t>69100</t>
         </is>
       </c>
-      <c r="Z85" s="22" t="inlineStr">
+      <c r="Z85" s="20" t="inlineStr">
         <is>
           <t>Villeurbanne</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="inlineStr">
+      <c r="A86" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B86" s="23" t="inlineStr">
+      <c r="B86" s="21" t="inlineStr">
         <is>
           <t>948354865</t>
         </is>
       </c>
-      <c r="C86" s="23" t="inlineStr">
+      <c r="C86" s="21" t="inlineStr">
         <is>
           <t>94835486500024</t>
         </is>
       </c>
-      <c r="D86" s="22" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
         <is>
           <t>ALLO TACOS 57</t>
         </is>
       </c>
-      <c r="E86" s="22" t="inlineStr">
+      <c r="E86" s="20" t="inlineStr">
         <is>
           <t>ALLO TACOS 57</t>
         </is>
       </c>
-      <c r="F86" s="22" t="inlineStr">
+      <c r="F86" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
+      <c r="G86" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H86" s="22" t="inlineStr">
+      <c r="H86" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I86" s="22" t="inlineStr">
+      <c r="I86" s="20" t="inlineStr">
         <is>
           <t>19/01/2023</t>
         </is>
       </c>
-      <c r="J86" s="22" t="inlineStr">
+      <c r="J86" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K86" s="22" t="inlineStr">
+      <c r="K86" s="20" t="inlineStr">
         <is>
           <t>65 B RUE AUX ARENES</t>
         </is>
       </c>
-      <c r="L86" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M86" s="22" t="inlineStr">
+      <c r="L86" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M86" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N86" s="22" t="inlineStr">
+      <c r="N86" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O86" s="22" t="inlineStr"/>
-      <c r="P86" s="22" t="inlineStr"/>
-      <c r="Q86" s="22" t="inlineStr"/>
-      <c r="R86" s="23" t="inlineStr"/>
-      <c r="S86" s="22" t="inlineStr"/>
-      <c r="T86" s="22" t="inlineStr">
+      <c r="O86" s="20" t="inlineStr"/>
+      <c r="P86" s="20" t="inlineStr"/>
+      <c r="Q86" s="20" t="inlineStr"/>
+      <c r="R86" s="21" t="inlineStr"/>
+      <c r="S86" s="20" t="inlineStr"/>
+      <c r="T86" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U86" s="22" t="inlineStr">
+      <c r="U86" s="20" t="inlineStr">
         <is>
           <t>NAIB</t>
         </is>
       </c>
-      <c r="V86" s="22" t="inlineStr">
+      <c r="V86" s="20" t="inlineStr">
         <is>
           <t>Tarik</t>
         </is>
       </c>
-      <c r="W86" s="22" t="inlineStr">
+      <c r="W86" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X86" s="22" t="inlineStr">
+      <c r="X86" s="20" t="inlineStr">
         <is>
           <t>63 Avenue de Lattre de Tassigny</t>
         </is>
       </c>
-      <c r="Y86" s="23" t="inlineStr">
+      <c r="Y86" s="21" t="inlineStr">
         <is>
           <t>57280</t>
         </is>
       </c>
-      <c r="Z86" s="22" t="inlineStr">
+      <c r="Z86" s="20" t="inlineStr">
         <is>
           <t>Maizières-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="inlineStr">
+      <c r="A87" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B87" s="23" t="inlineStr">
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>897824421</t>
         </is>
       </c>
-      <c r="C87" s="23" t="inlineStr">
+      <c r="C87" s="21" t="inlineStr">
         <is>
           <t>89782442100019</t>
         </is>
       </c>
-      <c r="D87" s="22" t="inlineStr">
+      <c r="D87" s="20" t="inlineStr">
         <is>
           <t>FOOD STREET 57</t>
         </is>
       </c>
-      <c r="E87" s="22" t="inlineStr">
+      <c r="E87" s="20" t="inlineStr">
         <is>
           <t>FOOD STREET 57</t>
         </is>
       </c>
-      <c r="F87" s="22" t="inlineStr">
+      <c r="F87" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G87" s="22" t="inlineStr">
+      <c r="G87" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H87" s="22" t="inlineStr">
+      <c r="H87" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I87" s="22" t="inlineStr">
+      <c r="I87" s="20" t="inlineStr">
         <is>
           <t>01/04/2021</t>
         </is>
       </c>
-      <c r="J87" s="22" t="inlineStr">
+      <c r="J87" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K87" s="22" t="inlineStr">
+      <c r="K87" s="20" t="inlineStr">
         <is>
           <t>5 RUE COISLIN</t>
         </is>
       </c>
-      <c r="L87" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M87" s="22" t="inlineStr">
+      <c r="L87" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M87" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N87" s="22" t="inlineStr">
+      <c r="N87" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O87" s="22" t="inlineStr"/>
-      <c r="P87" s="22" t="inlineStr"/>
-      <c r="Q87" s="22" t="inlineStr"/>
-      <c r="R87" s="23" t="inlineStr"/>
-      <c r="S87" s="22" t="inlineStr"/>
-      <c r="T87" s="22" t="inlineStr">
+      <c r="O87" s="20" t="inlineStr"/>
+      <c r="P87" s="20" t="inlineStr"/>
+      <c r="Q87" s="20" t="inlineStr"/>
+      <c r="R87" s="21" t="inlineStr"/>
+      <c r="S87" s="20" t="inlineStr"/>
+      <c r="T87" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U87" s="22" t="inlineStr">
+      <c r="U87" s="20" t="inlineStr">
         <is>
           <t>BEAUCHET</t>
         </is>
       </c>
-      <c r="V87" s="22" t="inlineStr">
+      <c r="V87" s="20" t="inlineStr">
         <is>
           <t>Pierre-françois</t>
         </is>
       </c>
-      <c r="W87" s="22" t="inlineStr">
+      <c r="W87" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X87" s="22" t="inlineStr">
+      <c r="X87" s="20" t="inlineStr">
         <is>
           <t>65 Avenue Georges Clémenceau</t>
         </is>
       </c>
-      <c r="Y87" s="23" t="inlineStr">
+      <c r="Y87" s="21" t="inlineStr">
         <is>
           <t>57500</t>
         </is>
       </c>
-      <c r="Z87" s="22" t="inlineStr">
+      <c r="Z87" s="20" t="inlineStr">
         <is>
           <t>Saint-Avold</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="inlineStr">
+        <is>
+          <t>829049824</t>
+        </is>
+      </c>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>82904982400016</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>SARL COFFEE 2 M</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>SARL COFFEE 2 M</t>
+        </is>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>28/03/2017</t>
+        </is>
+      </c>
+      <c r="J88" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K88" s="22" t="inlineStr">
+        <is>
+          <t>RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L88" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M88" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O88" s="22" t="inlineStr"/>
+      <c r="P88" s="22" t="inlineStr"/>
+      <c r="Q88" s="22" t="inlineStr"/>
+      <c r="R88" s="23" t="inlineStr"/>
+      <c r="S88" s="22" t="inlineStr"/>
+      <c r="T88" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U88" s="22" t="inlineStr">
+        <is>
+          <t>MENIRI</t>
+        </is>
+      </c>
+      <c r="V88" s="22" t="inlineStr">
+        <is>
+          <t>Mehdi</t>
+        </is>
+      </c>
+      <c r="W88" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X88" s="22" t="inlineStr">
+        <is>
+          <t>34 rue du Chazeau</t>
+        </is>
+      </c>
+      <c r="Y88" s="23" t="inlineStr">
+        <is>
+          <t>54220</t>
+        </is>
+      </c>
+      <c r="Z88" s="22" t="inlineStr">
+        <is>
+          <t>Malzéville</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>103017752</t>
+        </is>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>10301775200017</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>NAAN</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>NAAN</t>
+        </is>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="J89" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K89" s="22" t="inlineStr">
+        <is>
+          <t>26 RUE CLOVIS</t>
+        </is>
+      </c>
+      <c r="L89" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M89" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N89" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O89" s="22" t="inlineStr"/>
+      <c r="P89" s="22" t="inlineStr"/>
+      <c r="Q89" s="22" t="inlineStr"/>
+      <c r="R89" s="23" t="inlineStr"/>
+      <c r="S89" s="22" t="inlineStr"/>
+      <c r="T89" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U89" s="22" t="inlineStr">
+        <is>
+          <t>HOTAK</t>
+        </is>
+      </c>
+      <c r="V89" s="22" t="inlineStr">
+        <is>
+          <t>Tariq</t>
+        </is>
+      </c>
+      <c r="W89" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X89" s="22" t="inlineStr">
+        <is>
+          <t>32 rue de la marne</t>
+        </is>
+      </c>
+      <c r="Y89" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z89" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B90" s="23" t="inlineStr">
+        <is>
+          <t>507384352</t>
+        </is>
+      </c>
+      <c r="C90" s="23" t="inlineStr">
+        <is>
+          <t>50738435200013</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>MB SARL</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>MB SARL</t>
+        </is>
+      </c>
+      <c r="F90" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>21/06/2008</t>
+        </is>
+      </c>
+      <c r="J90" s="22" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K90" s="22" t="inlineStr">
+        <is>
+          <t>8 PLACE DES CHARRONS</t>
+        </is>
+      </c>
+      <c r="L90" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M90" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O90" s="22" t="inlineStr"/>
+      <c r="P90" s="22" t="inlineStr"/>
+      <c r="Q90" s="22" t="inlineStr"/>
+      <c r="R90" s="23" t="inlineStr"/>
+      <c r="S90" s="22" t="inlineStr"/>
+      <c r="T90" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U90" s="22" t="inlineStr">
+        <is>
+          <t>MOKHTAR</t>
+        </is>
+      </c>
+      <c r="V90" s="22" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="W90" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X90" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE DE SAULXURES</t>
+        </is>
+      </c>
+      <c r="Y90" s="23" t="inlineStr">
+        <is>
+          <t>54700</t>
+        </is>
+      </c>
+      <c r="Z90" s="22" t="inlineStr">
+        <is>
+          <t>VITTONVILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>842873879</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>84287387900014</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>EVE</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>EVE</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2018</t>
+        </is>
+      </c>
+      <c r="J91" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K91" s="22" t="inlineStr">
+        <is>
+          <t>22 RUE TAISON</t>
+        </is>
+      </c>
+      <c r="L91" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M91" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N91" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O91" s="22" t="inlineStr"/>
+      <c r="P91" s="22" t="inlineStr"/>
+      <c r="Q91" s="22" t="inlineStr"/>
+      <c r="R91" s="23" t="inlineStr"/>
+      <c r="S91" s="22" t="inlineStr"/>
+      <c r="T91" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U91" s="22" t="inlineStr">
+        <is>
+          <t>CLOUET</t>
+        </is>
+      </c>
+      <c r="V91" s="22" t="inlineStr">
+        <is>
+          <t>Florane, Cannelle, Pauline</t>
+        </is>
+      </c>
+      <c r="W91" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X91" s="22" t="inlineStr">
+        <is>
+          <t>27 rue de la Princerie</t>
+        </is>
+      </c>
+      <c r="Y91" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z91" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B92" s="23" t="inlineStr">
+        <is>
+          <t>983359928</t>
+        </is>
+      </c>
+      <c r="C92" s="23" t="inlineStr">
+        <is>
+          <t>98335992800014</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>DIHA MOHAMED</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>DIHA MOHAMED</t>
+        </is>
+      </c>
+      <c r="F92" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>31/01/2024</t>
+        </is>
+      </c>
+      <c r="J92" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K92" s="22" t="inlineStr">
+        <is>
+          <t>225 AVENUE ANDRE MALRAUX</t>
+        </is>
+      </c>
+      <c r="L92" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M92" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N92" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O92" s="22" t="inlineStr"/>
+      <c r="P92" s="22" t="inlineStr"/>
+      <c r="Q92" s="22" t="inlineStr"/>
+      <c r="R92" s="23" t="inlineStr"/>
+      <c r="S92" s="22" t="inlineStr"/>
+      <c r="T92" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U92" s="22" t="inlineStr">
+        <is>
+          <t>DIHA</t>
+        </is>
+      </c>
+      <c r="V92" s="22" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="W92" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X92" s="22" t="inlineStr"/>
+      <c r="Y92" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z92" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>105834188</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>10583418800010</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr">
+        <is>
+          <t>BONFOH ABLAN</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>BONFOH ABLAN</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="J93" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K93" s="22" t="inlineStr">
+        <is>
+          <t>7 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L93" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M93" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O93" s="22" t="inlineStr"/>
+      <c r="P93" s="22" t="inlineStr"/>
+      <c r="Q93" s="22" t="inlineStr"/>
+      <c r="R93" s="23" t="inlineStr"/>
+      <c r="S93" s="22" t="inlineStr"/>
+      <c r="T93" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U93" s="22" t="inlineStr">
+        <is>
+          <t>MANOU</t>
+        </is>
+      </c>
+      <c r="V93" s="22" t="inlineStr">
+        <is>
+          <t>Ablan, Rebecca</t>
+        </is>
+      </c>
+      <c r="W93" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X93" s="22" t="inlineStr"/>
+      <c r="Y93" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z93" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B94" s="23" t="inlineStr">
+        <is>
+          <t>500317250</t>
+        </is>
+      </c>
+      <c r="C94" s="23" t="inlineStr">
+        <is>
+          <t>50031725000024</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>PARM'S</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>PARM'S</t>
+        </is>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>03/10/2007</t>
+        </is>
+      </c>
+      <c r="J94" s="22" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K94" s="22" t="inlineStr">
+        <is>
+          <t>70 RUE DE LA CHAPELLE</t>
+        </is>
+      </c>
+      <c r="L94" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M94" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N94" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O94" s="22" t="inlineStr"/>
+      <c r="P94" s="22" t="inlineStr"/>
+      <c r="Q94" s="22" t="inlineStr"/>
+      <c r="R94" s="23" t="inlineStr"/>
+      <c r="S94" s="22" t="inlineStr"/>
+      <c r="T94" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U94" s="22" t="inlineStr">
+        <is>
+          <t>PARMENTIER</t>
+        </is>
+      </c>
+      <c r="V94" s="22" t="inlineStr">
+        <is>
+          <t>Yann, Fernand, Raimond</t>
+        </is>
+      </c>
+      <c r="W94" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X94" s="22" t="inlineStr">
+        <is>
+          <t>70 Rue de la Chapelle</t>
+        </is>
+      </c>
+      <c r="Y94" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z94" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B95" s="23" t="inlineStr">
+        <is>
+          <t>450737424</t>
+        </is>
+      </c>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>45073742400017</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>LEXSIS</t>
+        </is>
+      </c>
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>LEXSIS</t>
+        </is>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>03/11/2003</t>
+        </is>
+      </c>
+      <c r="J95" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K95" s="22" t="inlineStr">
+        <is>
+          <t>7 RUE PAUL BEZANSON</t>
+        </is>
+      </c>
+      <c r="L95" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M95" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O95" s="22" t="n">
+        <v>667840</v>
+      </c>
+      <c r="P95" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q95" s="22" t="inlineStr"/>
+      <c r="R95" s="23" t="inlineStr"/>
+      <c r="S95" s="22" t="inlineStr"/>
+      <c r="T95" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U95" s="22" t="inlineStr">
+        <is>
+          <t>OZCELIK</t>
+        </is>
+      </c>
+      <c r="V95" s="22" t="inlineStr">
+        <is>
+          <t>Cem</t>
+        </is>
+      </c>
+      <c r="W95" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X95" s="22" t="inlineStr">
+        <is>
+          <t>25 RUE DE LA PLANCHETTE</t>
+        </is>
+      </c>
+      <c r="Y95" s="23" t="inlineStr">
+        <is>
+          <t>57645</t>
+        </is>
+      </c>
+      <c r="Z95" s="22" t="inlineStr">
+        <is>
+          <t>MONTOY FLANVILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B96" s="23" t="inlineStr">
+        <is>
+          <t>752026872</t>
+        </is>
+      </c>
+      <c r="C96" s="23" t="inlineStr">
+        <is>
+          <t>75202687200024</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="inlineStr">
+        <is>
+          <t>ALOUANE RABAH</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>ALOUANE RABAH</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>02/06/2012</t>
+        </is>
+      </c>
+      <c r="J96" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K96" s="22" t="inlineStr">
+        <is>
+          <t>5 AVENUE DE LATTRE DE TASSIGNY</t>
+        </is>
+      </c>
+      <c r="L96" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N96" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O96" s="22" t="inlineStr"/>
+      <c r="P96" s="22" t="inlineStr"/>
+      <c r="Q96" s="22" t="inlineStr"/>
+      <c r="R96" s="23" t="inlineStr"/>
+      <c r="S96" s="22" t="inlineStr"/>
+      <c r="T96" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U96" s="22" t="inlineStr">
+        <is>
+          <t>ALOUANE</t>
+        </is>
+      </c>
+      <c r="V96" s="22" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="W96" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X96" s="22" t="inlineStr"/>
+      <c r="Y96" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z96" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="inlineStr">
+        <is>
+          <t>949144307</t>
+        </is>
+      </c>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>94914430700012</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>LES SAVEURS</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>LES SAVEURS</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>07/02/2023</t>
+        </is>
+      </c>
+      <c r="J97" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K97" s="22" t="inlineStr">
+        <is>
+          <t>26 AVENUE FOCH</t>
+        </is>
+      </c>
+      <c r="L97" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M97" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N97" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O97" s="22" t="inlineStr"/>
+      <c r="P97" s="22" t="inlineStr"/>
+      <c r="Q97" s="22" t="inlineStr"/>
+      <c r="R97" s="23" t="inlineStr"/>
+      <c r="S97" s="22" t="inlineStr"/>
+      <c r="T97" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U97" s="22" t="inlineStr">
+        <is>
+          <t>REMY</t>
+        </is>
+      </c>
+      <c r="V97" s="22" t="inlineStr">
+        <is>
+          <t>Emmanuelle, Pascale, Bernadette</t>
+        </is>
+      </c>
+      <c r="W97" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X97" s="22" t="inlineStr">
+        <is>
+          <t>33 Rue Robert Darnery</t>
+        </is>
+      </c>
+      <c r="Y97" s="23" t="inlineStr">
+        <is>
+          <t>54410</t>
+        </is>
+      </c>
+      <c r="Z97" s="22" t="inlineStr">
+        <is>
+          <t>Laneuveville-devant-Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B98" s="23" t="inlineStr">
+        <is>
+          <t>899033450</t>
+        </is>
+      </c>
+      <c r="C98" s="23" t="inlineStr">
+        <is>
+          <t>89903345000011</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>SAS MGROUP ENTREPRISES</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>SAS MGROUP ENTREPRISES</t>
+        </is>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I98" s="22" t="inlineStr">
+        <is>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="J98" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K98" s="22" t="inlineStr">
+        <is>
+          <t>120 RUE DES ALLEMANDS</t>
+        </is>
+      </c>
+      <c r="L98" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M98" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N98" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O98" s="22" t="inlineStr"/>
+      <c r="P98" s="22" t="inlineStr"/>
+      <c r="Q98" s="22" t="inlineStr"/>
+      <c r="R98" s="23" t="inlineStr"/>
+      <c r="S98" s="22" t="inlineStr"/>
+      <c r="T98" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U98" s="22" t="inlineStr">
+        <is>
+          <t>MUNCH</t>
+        </is>
+      </c>
+      <c r="V98" s="22" t="inlineStr">
+        <is>
+          <t>Olivier, Roger</t>
+        </is>
+      </c>
+      <c r="W98" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X98" s="22" t="inlineStr">
+        <is>
+          <t>Lieu-Dit Pfisterquelle</t>
+        </is>
+      </c>
+      <c r="Y98" s="23" t="inlineStr">
+        <is>
+          <t>57460</t>
+        </is>
+      </c>
+      <c r="Z98" s="22" t="inlineStr">
+        <is>
+          <t>Behren-lès-Forbach</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B99" s="23" t="inlineStr">
+        <is>
+          <t>822068110</t>
+        </is>
+      </c>
+      <c r="C99" s="23" t="inlineStr">
+        <is>
+          <t>82206811000011</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>TRESSON TRAITEUR</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>TRESSON TRAITEUR</t>
+        </is>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I99" s="22" t="inlineStr">
+        <is>
+          <t>15/07/2016</t>
+        </is>
+      </c>
+      <c r="J99" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K99" s="22" t="inlineStr">
+        <is>
+          <t>RUE DE PONT-A-MOUSSON</t>
+        </is>
+      </c>
+      <c r="L99" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M99" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N99" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O99" s="22" t="inlineStr"/>
+      <c r="P99" s="22" t="inlineStr"/>
+      <c r="Q99" s="22" t="inlineStr"/>
+      <c r="R99" s="23" t="inlineStr"/>
+      <c r="S99" s="22" t="inlineStr"/>
+      <c r="T99" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U99" s="22" t="inlineStr">
+        <is>
+          <t>TRESSON</t>
+        </is>
+      </c>
+      <c r="V99" s="22" t="inlineStr">
+        <is>
+          <t>Sébastien</t>
+        </is>
+      </c>
+      <c r="W99" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X99" s="22" t="inlineStr">
+        <is>
+          <t>2 rue des Pruniers</t>
+        </is>
+      </c>
+      <c r="Y99" s="23" t="inlineStr">
+        <is>
+          <t>57420</t>
+        </is>
+      </c>
+      <c r="Z99" s="22" t="inlineStr">
+        <is>
+          <t>Pournoy-la-Chétive</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="inlineStr">
+        <is>
+          <t>451060693</t>
+        </is>
+      </c>
+      <c r="C100" s="23" t="inlineStr">
+        <is>
+          <t>45106069300012</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>ASSOCIATION CONSISTORIALE REFOUEL</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>ASSOCIATION CONSISTORIALE REFOUEL</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>Association de droit local (Bas-Rhin, Haut-Rhin et Moselle)</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="J100" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K100" s="22" t="inlineStr">
+        <is>
+          <t>7 PLACE VALLADIER</t>
+        </is>
+      </c>
+      <c r="L100" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M100" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N100" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O100" s="22" t="inlineStr"/>
+      <c r="P100" s="22" t="inlineStr"/>
+      <c r="Q100" s="22" t="inlineStr"/>
+      <c r="R100" s="23" t="inlineStr"/>
+      <c r="S100" s="22" t="inlineStr"/>
+      <c r="T100" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U100" s="22" t="inlineStr"/>
+      <c r="V100" s="22" t="inlineStr"/>
+      <c r="W100" s="22" t="inlineStr"/>
+      <c r="X100" s="22" t="inlineStr"/>
+      <c r="Y100" s="23" t="inlineStr"/>
+      <c r="Z100" s="22" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="inlineStr">
+        <is>
+          <t>821808672</t>
+        </is>
+      </c>
+      <c r="C101" s="23" t="inlineStr">
+        <is>
+          <t>82180867200017</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr">
+        <is>
+          <t>BROOKLYN CAFE</t>
+        </is>
+      </c>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>BROOKLYN CAFE</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>29/07/2016</t>
+        </is>
+      </c>
+      <c r="J101" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K101" s="22" t="inlineStr">
+        <is>
+          <t>27 RUE DES ROCHES</t>
+        </is>
+      </c>
+      <c r="L101" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M101" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N101" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O101" s="22" t="inlineStr"/>
+      <c r="P101" s="22" t="inlineStr"/>
+      <c r="Q101" s="22" t="inlineStr"/>
+      <c r="R101" s="23" t="inlineStr"/>
+      <c r="S101" s="22" t="inlineStr"/>
+      <c r="T101" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U101" s="22" t="inlineStr">
+        <is>
+          <t>DI CARLO</t>
+        </is>
+      </c>
+      <c r="V101" s="22" t="inlineStr">
+        <is>
+          <t>Olivier, Claude</t>
+        </is>
+      </c>
+      <c r="W101" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X101" s="22" t="inlineStr">
+        <is>
+          <t>26 rue Pasteur</t>
+        </is>
+      </c>
+      <c r="Y101" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z101" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>910224096</t>
+        </is>
+      </c>
+      <c r="C102" s="23" t="inlineStr">
+        <is>
+          <t>91022409600016</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>LE CELESTE</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
+        <is>
+          <t>LE CELESTE</t>
+        </is>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>26/01/2022</t>
+        </is>
+      </c>
+      <c r="J102" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K102" s="22" t="inlineStr">
+        <is>
+          <t>49 IMPASSE DES ALLEMANDS</t>
+        </is>
+      </c>
+      <c r="L102" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M102" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N102" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O102" s="22" t="inlineStr"/>
+      <c r="P102" s="22" t="inlineStr"/>
+      <c r="Q102" s="22" t="inlineStr"/>
+      <c r="R102" s="23" t="inlineStr"/>
+      <c r="S102" s="22" t="inlineStr"/>
+      <c r="T102" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U102" s="22" t="inlineStr">
+        <is>
+          <t>PREKA</t>
+        </is>
+      </c>
+      <c r="V102" s="22" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="W102" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X102" s="22" t="inlineStr">
+        <is>
+          <t>8 Rue de Budange</t>
+        </is>
+      </c>
+      <c r="Y102" s="23" t="inlineStr">
+        <is>
+          <t>57270</t>
+        </is>
+      </c>
+      <c r="Z102" s="22" t="inlineStr">
+        <is>
+          <t>Uckange</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>829499235</t>
+        </is>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
+        <is>
+          <t>82949923500028</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>AU COUTEAU LORRAIN</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="inlineStr">
+        <is>
+          <t>AU COUTEAU LORRAIN</t>
+        </is>
+      </c>
+      <c r="F103" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I103" s="22" t="inlineStr">
+        <is>
+          <t>09/05/2017</t>
+        </is>
+      </c>
+      <c r="J103" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K103" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L103" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M103" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N103" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O103" s="22" t="inlineStr"/>
+      <c r="P103" s="22" t="inlineStr"/>
+      <c r="Q103" s="22" t="inlineStr"/>
+      <c r="R103" s="23" t="inlineStr"/>
+      <c r="S103" s="22" t="inlineStr"/>
+      <c r="T103" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U103" s="22" t="inlineStr">
+        <is>
+          <t>BAUDINOT</t>
+        </is>
+      </c>
+      <c r="V103" s="22" t="inlineStr">
+        <is>
+          <t>Cédric, Damien</t>
+        </is>
+      </c>
+      <c r="W103" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X103" s="22" t="inlineStr">
+        <is>
+          <t>2B rue au Blé</t>
+        </is>
+      </c>
+      <c r="Y103" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z103" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>830552865</t>
+        </is>
+      </c>
+      <c r="C104" s="23" t="inlineStr">
+        <is>
+          <t>83055286500016</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>WINSTON</t>
+        </is>
+      </c>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>WINSTON</t>
+        </is>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>28/06/2017</t>
+        </is>
+      </c>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K104" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE WINSTON CHURCHILL</t>
+        </is>
+      </c>
+      <c r="L104" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M104" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N104" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O104" s="22" t="inlineStr"/>
+      <c r="P104" s="22" t="inlineStr"/>
+      <c r="Q104" s="22" t="inlineStr"/>
+      <c r="R104" s="23" t="inlineStr"/>
+      <c r="S104" s="22" t="inlineStr"/>
+      <c r="T104" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U104" s="22" t="inlineStr">
+        <is>
+          <t>WALLERICH</t>
+        </is>
+      </c>
+      <c r="V104" s="22" t="inlineStr">
+        <is>
+          <t>Michel, Ernest</t>
+        </is>
+      </c>
+      <c r="W104" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X104" s="22" t="inlineStr">
+        <is>
+          <t>40 rue Saint-Gengoulf</t>
+        </is>
+      </c>
+      <c r="Y104" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z104" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr">
+        <is>
+          <t>401402995</t>
+        </is>
+      </c>
+      <c r="C105" s="23" t="inlineStr">
+        <is>
+          <t>40140299500021</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>KOCH Sandrine</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>KOCH Sandrine</t>
+        </is>
+      </c>
+      <c r="F105" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>16/06/1995</t>
+        </is>
+      </c>
+      <c r="J105" s="22" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="K105" s="22" t="inlineStr">
+        <is>
+          <t>37 A RUE DU XXEME CORPS AMERICAIN</t>
+        </is>
+      </c>
+      <c r="L105" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M105" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N105" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O105" s="22" t="inlineStr"/>
+      <c r="P105" s="22" t="inlineStr"/>
+      <c r="Q105" s="22" t="inlineStr"/>
+      <c r="R105" s="23" t="inlineStr"/>
+      <c r="S105" s="22" t="inlineStr"/>
+      <c r="T105" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U105" s="22" t="inlineStr">
+        <is>
+          <t>KOCH</t>
+        </is>
+      </c>
+      <c r="V105" s="22" t="inlineStr">
+        <is>
+          <t>Sandrine</t>
+        </is>
+      </c>
+      <c r="W105" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X105" s="22" t="inlineStr"/>
+      <c r="Y105" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z105" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="inlineStr">
+        <is>
+          <t>491003075</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
+        <is>
+          <t>49100307500018</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>SARL LA TASSE AMOS</t>
+        </is>
+      </c>
+      <c r="E106" s="22" t="inlineStr">
+        <is>
+          <t>SARL LA TASSE AMOS</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>10/07/2006</t>
+        </is>
+      </c>
+      <c r="J106" s="22" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="K106" s="22" t="inlineStr">
+        <is>
+          <t>6 PLACE JEAN SPINGA</t>
+        </is>
+      </c>
+      <c r="L106" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M106" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O106" s="22" t="inlineStr"/>
+      <c r="P106" s="22" t="inlineStr"/>
+      <c r="Q106" s="22" t="inlineStr"/>
+      <c r="R106" s="23" t="inlineStr"/>
+      <c r="S106" s="22" t="inlineStr"/>
+      <c r="T106" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U106" s="22" t="inlineStr">
+        <is>
+          <t>CINAR</t>
+        </is>
+      </c>
+      <c r="V106" s="22" t="inlineStr">
+        <is>
+          <t>Sabri</t>
+        </is>
+      </c>
+      <c r="W106" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X106" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE ROCHEMBEAU</t>
+        </is>
+      </c>
+      <c r="Y106" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z106" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>838437283</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>83843728300016</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="inlineStr">
+        <is>
+          <t>FRIEDERICH Jordane</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="inlineStr">
+        <is>
+          <t>FRIEDERICH Jordane</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>13/03/2018</t>
+        </is>
+      </c>
+      <c r="J107" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K107" s="22" t="inlineStr">
+        <is>
+          <t>36 RUE DES JARDINS</t>
+        </is>
+      </c>
+      <c r="L107" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O107" s="22" t="inlineStr"/>
+      <c r="P107" s="22" t="inlineStr"/>
+      <c r="Q107" s="22" t="inlineStr"/>
+      <c r="R107" s="23" t="inlineStr"/>
+      <c r="S107" s="22" t="inlineStr"/>
+      <c r="T107" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U107" s="22" t="inlineStr">
+        <is>
+          <t>FRIEDERICH</t>
+        </is>
+      </c>
+      <c r="V107" s="22" t="inlineStr">
+        <is>
+          <t>Jordane</t>
+        </is>
+      </c>
+      <c r="W107" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X107" s="22" t="inlineStr"/>
+      <c r="Y107" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z107" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z87"/>
+  <autoFilter ref="A2:Z107"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z107"/>
+  <dimension ref="A1:Z127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10310,2207 +10310,4439 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B88" s="23" t="inlineStr">
+      <c r="B88" s="21" t="inlineStr">
         <is>
           <t>829049824</t>
         </is>
       </c>
-      <c r="C88" s="23" t="inlineStr">
+      <c r="C88" s="21" t="inlineStr">
         <is>
           <t>82904982400016</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr">
+      <c r="D88" s="20" t="inlineStr">
         <is>
           <t>SARL COFFEE 2 M</t>
         </is>
       </c>
-      <c r="E88" s="22" t="inlineStr">
+      <c r="E88" s="20" t="inlineStr">
         <is>
           <t>SARL COFFEE 2 M</t>
         </is>
       </c>
-      <c r="F88" s="22" t="inlineStr">
+      <c r="F88" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
+      <c r="G88" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H88" s="22" t="inlineStr">
+      <c r="H88" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I88" s="22" t="inlineStr">
+      <c r="I88" s="20" t="inlineStr">
         <is>
           <t>28/03/2017</t>
         </is>
       </c>
-      <c r="J88" s="22" t="inlineStr">
+      <c r="J88" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K88" s="22" t="inlineStr">
+      <c r="K88" s="20" t="inlineStr">
         <is>
           <t>RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L88" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M88" s="22" t="inlineStr">
+      <c r="L88" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M88" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N88" s="22" t="inlineStr">
+      <c r="N88" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O88" s="22" t="inlineStr"/>
-      <c r="P88" s="22" t="inlineStr"/>
-      <c r="Q88" s="22" t="inlineStr"/>
-      <c r="R88" s="23" t="inlineStr"/>
-      <c r="S88" s="22" t="inlineStr"/>
-      <c r="T88" s="22" t="inlineStr">
+      <c r="O88" s="20" t="inlineStr"/>
+      <c r="P88" s="20" t="inlineStr"/>
+      <c r="Q88" s="20" t="inlineStr"/>
+      <c r="R88" s="21" t="inlineStr"/>
+      <c r="S88" s="20" t="inlineStr"/>
+      <c r="T88" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U88" s="22" t="inlineStr">
+      <c r="U88" s="20" t="inlineStr">
         <is>
           <t>MENIRI</t>
         </is>
       </c>
-      <c r="V88" s="22" t="inlineStr">
+      <c r="V88" s="20" t="inlineStr">
         <is>
           <t>Mehdi</t>
         </is>
       </c>
-      <c r="W88" s="22" t="inlineStr">
+      <c r="W88" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X88" s="22" t="inlineStr">
+      <c r="X88" s="20" t="inlineStr">
         <is>
           <t>34 rue du Chazeau</t>
         </is>
       </c>
-      <c r="Y88" s="23" t="inlineStr">
+      <c r="Y88" s="21" t="inlineStr">
         <is>
           <t>54220</t>
         </is>
       </c>
-      <c r="Z88" s="22" t="inlineStr">
+      <c r="Z88" s="20" t="inlineStr">
         <is>
           <t>Malzéville</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="inlineStr">
+      <c r="A89" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B89" s="23" t="inlineStr">
+      <c r="B89" s="21" t="inlineStr">
         <is>
           <t>103017752</t>
         </is>
       </c>
-      <c r="C89" s="23" t="inlineStr">
+      <c r="C89" s="21" t="inlineStr">
         <is>
           <t>10301775200017</t>
         </is>
       </c>
-      <c r="D89" s="22" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
         <is>
           <t>NAAN</t>
         </is>
       </c>
-      <c r="E89" s="22" t="inlineStr">
+      <c r="E89" s="20" t="inlineStr">
         <is>
           <t>NAAN</t>
         </is>
       </c>
-      <c r="F89" s="22" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G89" s="22" t="inlineStr">
+      <c r="G89" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H89" s="22" t="inlineStr">
+      <c r="H89" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I89" s="22" t="inlineStr">
+      <c r="I89" s="20" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="J89" s="22" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K89" s="22" t="inlineStr">
+      <c r="K89" s="20" t="inlineStr">
         <is>
           <t>26 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="L89" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M89" s="22" t="inlineStr">
+      <c r="L89" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M89" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N89" s="22" t="inlineStr">
+      <c r="N89" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O89" s="22" t="inlineStr"/>
-      <c r="P89" s="22" t="inlineStr"/>
-      <c r="Q89" s="22" t="inlineStr"/>
-      <c r="R89" s="23" t="inlineStr"/>
-      <c r="S89" s="22" t="inlineStr"/>
-      <c r="T89" s="22" t="inlineStr">
+      <c r="O89" s="20" t="inlineStr"/>
+      <c r="P89" s="20" t="inlineStr"/>
+      <c r="Q89" s="20" t="inlineStr"/>
+      <c r="R89" s="21" t="inlineStr"/>
+      <c r="S89" s="20" t="inlineStr"/>
+      <c r="T89" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U89" s="22" t="inlineStr">
+      <c r="U89" s="20" t="inlineStr">
         <is>
           <t>HOTAK</t>
         </is>
       </c>
-      <c r="V89" s="22" t="inlineStr">
+      <c r="V89" s="20" t="inlineStr">
         <is>
           <t>Tariq</t>
         </is>
       </c>
-      <c r="W89" s="22" t="inlineStr">
+      <c r="W89" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X89" s="22" t="inlineStr">
+      <c r="X89" s="20" t="inlineStr">
         <is>
           <t>32 rue de la marne</t>
         </is>
       </c>
-      <c r="Y89" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z89" s="22" t="inlineStr">
+      <c r="Y89" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z89" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="inlineStr">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B90" s="23" t="inlineStr">
+      <c r="B90" s="21" t="inlineStr">
         <is>
           <t>507384352</t>
         </is>
       </c>
-      <c r="C90" s="23" t="inlineStr">
+      <c r="C90" s="21" t="inlineStr">
         <is>
           <t>50738435200013</t>
         </is>
       </c>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="20" t="inlineStr">
         <is>
           <t>MB SARL</t>
         </is>
       </c>
-      <c r="E90" s="22" t="inlineStr">
+      <c r="E90" s="20" t="inlineStr">
         <is>
           <t>MB SARL</t>
         </is>
       </c>
-      <c r="F90" s="22" t="inlineStr">
+      <c r="F90" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
+      <c r="G90" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H90" s="22" t="inlineStr">
+      <c r="H90" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I90" s="22" t="inlineStr">
+      <c r="I90" s="20" t="inlineStr">
         <is>
           <t>21/06/2008</t>
         </is>
       </c>
-      <c r="J90" s="22" t="inlineStr">
+      <c r="J90" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K90" s="22" t="inlineStr">
+      <c r="K90" s="20" t="inlineStr">
         <is>
           <t>8 PLACE DES CHARRONS</t>
         </is>
       </c>
-      <c r="L90" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M90" s="22" t="inlineStr">
+      <c r="L90" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M90" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N90" s="22" t="inlineStr">
+      <c r="N90" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O90" s="22" t="inlineStr"/>
-      <c r="P90" s="22" t="inlineStr"/>
-      <c r="Q90" s="22" t="inlineStr"/>
-      <c r="R90" s="23" t="inlineStr"/>
-      <c r="S90" s="22" t="inlineStr"/>
-      <c r="T90" s="22" t="inlineStr">
+      <c r="O90" s="20" t="inlineStr"/>
+      <c r="P90" s="20" t="inlineStr"/>
+      <c r="Q90" s="20" t="inlineStr"/>
+      <c r="R90" s="21" t="inlineStr"/>
+      <c r="S90" s="20" t="inlineStr"/>
+      <c r="T90" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U90" s="22" t="inlineStr">
+      <c r="U90" s="20" t="inlineStr">
         <is>
           <t>MOKHTAR</t>
         </is>
       </c>
-      <c r="V90" s="22" t="inlineStr">
+      <c r="V90" s="20" t="inlineStr">
         <is>
           <t>Ali</t>
         </is>
       </c>
-      <c r="W90" s="22" t="inlineStr">
+      <c r="W90" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X90" s="22" t="inlineStr">
+      <c r="X90" s="20" t="inlineStr">
         <is>
           <t>18 RUE DE SAULXURES</t>
         </is>
       </c>
-      <c r="Y90" s="23" t="inlineStr">
+      <c r="Y90" s="21" t="inlineStr">
         <is>
           <t>54700</t>
         </is>
       </c>
-      <c r="Z90" s="22" t="inlineStr">
+      <c r="Z90" s="20" t="inlineStr">
         <is>
           <t>VITTONVILLE</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="inlineStr">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B91" s="23" t="inlineStr">
+      <c r="B91" s="21" t="inlineStr">
         <is>
           <t>842873879</t>
         </is>
       </c>
-      <c r="C91" s="23" t="inlineStr">
+      <c r="C91" s="21" t="inlineStr">
         <is>
           <t>84287387900014</t>
         </is>
       </c>
-      <c r="D91" s="22" t="inlineStr">
+      <c r="D91" s="20" t="inlineStr">
         <is>
           <t>EVE</t>
         </is>
       </c>
-      <c r="E91" s="22" t="inlineStr">
+      <c r="E91" s="20" t="inlineStr">
         <is>
           <t>EVE</t>
         </is>
       </c>
-      <c r="F91" s="22" t="inlineStr">
+      <c r="F91" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G91" s="22" t="inlineStr">
+      <c r="G91" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H91" s="22" t="inlineStr">
+      <c r="H91" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I91" s="22" t="inlineStr">
+      <c r="I91" s="20" t="inlineStr">
         <is>
           <t>01/10/2018</t>
         </is>
       </c>
-      <c r="J91" s="22" t="inlineStr">
+      <c r="J91" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K91" s="22" t="inlineStr">
+      <c r="K91" s="20" t="inlineStr">
         <is>
           <t>22 RUE TAISON</t>
         </is>
       </c>
-      <c r="L91" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M91" s="22" t="inlineStr">
+      <c r="L91" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M91" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N91" s="22" t="inlineStr">
+      <c r="N91" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O91" s="22" t="inlineStr"/>
-      <c r="P91" s="22" t="inlineStr"/>
-      <c r="Q91" s="22" t="inlineStr"/>
-      <c r="R91" s="23" t="inlineStr"/>
-      <c r="S91" s="22" t="inlineStr"/>
-      <c r="T91" s="22" t="inlineStr">
+      <c r="O91" s="20" t="inlineStr"/>
+      <c r="P91" s="20" t="inlineStr"/>
+      <c r="Q91" s="20" t="inlineStr"/>
+      <c r="R91" s="21" t="inlineStr"/>
+      <c r="S91" s="20" t="inlineStr"/>
+      <c r="T91" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U91" s="22" t="inlineStr">
+      <c r="U91" s="20" t="inlineStr">
         <is>
           <t>CLOUET</t>
         </is>
       </c>
-      <c r="V91" s="22" t="inlineStr">
+      <c r="V91" s="20" t="inlineStr">
         <is>
           <t>Florane, Cannelle, Pauline</t>
         </is>
       </c>
-      <c r="W91" s="22" t="inlineStr">
+      <c r="W91" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X91" s="22" t="inlineStr">
+      <c r="X91" s="20" t="inlineStr">
         <is>
           <t>27 rue de la Princerie</t>
         </is>
       </c>
-      <c r="Y91" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z91" s="22" t="inlineStr">
+      <c r="Y91" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z91" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+      <c r="A92" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B92" s="23" t="inlineStr">
+      <c r="B92" s="21" t="inlineStr">
         <is>
           <t>983359928</t>
         </is>
       </c>
-      <c r="C92" s="23" t="inlineStr">
+      <c r="C92" s="21" t="inlineStr">
         <is>
           <t>98335992800014</t>
         </is>
       </c>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="20" t="inlineStr">
         <is>
           <t>DIHA MOHAMED</t>
         </is>
       </c>
-      <c r="E92" s="22" t="inlineStr">
+      <c r="E92" s="20" t="inlineStr">
         <is>
           <t>DIHA MOHAMED</t>
         </is>
       </c>
-      <c r="F92" s="22" t="inlineStr">
+      <c r="F92" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
+      <c r="G92" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H92" s="22" t="inlineStr">
+      <c r="H92" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I92" s="22" t="inlineStr">
+      <c r="I92" s="20" t="inlineStr">
         <is>
           <t>31/01/2024</t>
         </is>
       </c>
-      <c r="J92" s="22" t="inlineStr">
+      <c r="J92" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K92" s="22" t="inlineStr">
+      <c r="K92" s="20" t="inlineStr">
         <is>
           <t>225 AVENUE ANDRE MALRAUX</t>
         </is>
       </c>
-      <c r="L92" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M92" s="22" t="inlineStr">
+      <c r="L92" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M92" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N92" s="22" t="inlineStr">
+      <c r="N92" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O92" s="22" t="inlineStr"/>
-      <c r="P92" s="22" t="inlineStr"/>
-      <c r="Q92" s="22" t="inlineStr"/>
-      <c r="R92" s="23" t="inlineStr"/>
-      <c r="S92" s="22" t="inlineStr"/>
-      <c r="T92" s="22" t="inlineStr">
+      <c r="O92" s="20" t="inlineStr"/>
+      <c r="P92" s="20" t="inlineStr"/>
+      <c r="Q92" s="20" t="inlineStr"/>
+      <c r="R92" s="21" t="inlineStr"/>
+      <c r="S92" s="20" t="inlineStr"/>
+      <c r="T92" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U92" s="22" t="inlineStr">
+      <c r="U92" s="20" t="inlineStr">
         <is>
           <t>DIHA</t>
         </is>
       </c>
-      <c r="V92" s="22" t="inlineStr">
+      <c r="V92" s="20" t="inlineStr">
         <is>
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="W92" s="22" t="inlineStr">
+      <c r="W92" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X92" s="22" t="inlineStr"/>
-      <c r="Y92" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z92" s="22" t="inlineStr">
+      <c r="X92" s="20" t="inlineStr"/>
+      <c r="Y92" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z92" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B93" s="23" t="inlineStr">
+      <c r="B93" s="21" t="inlineStr">
         <is>
           <t>105834188</t>
         </is>
       </c>
-      <c r="C93" s="23" t="inlineStr">
+      <c r="C93" s="21" t="inlineStr">
         <is>
           <t>10583418800010</t>
         </is>
       </c>
-      <c r="D93" s="22" t="inlineStr">
+      <c r="D93" s="20" t="inlineStr">
         <is>
           <t>BONFOH ABLAN</t>
         </is>
       </c>
-      <c r="E93" s="22" t="inlineStr">
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>BONFOH ABLAN</t>
         </is>
       </c>
-      <c r="F93" s="22" t="inlineStr">
+      <c r="F93" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G93" s="22" t="inlineStr">
+      <c r="G93" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H93" s="22" t="inlineStr">
+      <c r="H93" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I93" s="22" t="inlineStr">
+      <c r="I93" s="20" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="J93" s="22" t="inlineStr">
+      <c r="J93" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K93" s="22" t="inlineStr">
+      <c r="K93" s="20" t="inlineStr">
         <is>
           <t>7 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L93" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M93" s="22" t="inlineStr">
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M93" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N93" s="22" t="inlineStr">
+      <c r="N93" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O93" s="22" t="inlineStr"/>
-      <c r="P93" s="22" t="inlineStr"/>
-      <c r="Q93" s="22" t="inlineStr"/>
-      <c r="R93" s="23" t="inlineStr"/>
-      <c r="S93" s="22" t="inlineStr"/>
-      <c r="T93" s="22" t="inlineStr">
+      <c r="O93" s="20" t="inlineStr"/>
+      <c r="P93" s="20" t="inlineStr"/>
+      <c r="Q93" s="20" t="inlineStr"/>
+      <c r="R93" s="21" t="inlineStr"/>
+      <c r="S93" s="20" t="inlineStr"/>
+      <c r="T93" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U93" s="22" t="inlineStr">
+      <c r="U93" s="20" t="inlineStr">
         <is>
           <t>MANOU</t>
         </is>
       </c>
-      <c r="V93" s="22" t="inlineStr">
+      <c r="V93" s="20" t="inlineStr">
         <is>
           <t>Ablan, Rebecca</t>
         </is>
       </c>
-      <c r="W93" s="22" t="inlineStr">
+      <c r="W93" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X93" s="22" t="inlineStr"/>
-      <c r="Y93" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z93" s="22" t="inlineStr">
+      <c r="X93" s="20" t="inlineStr"/>
+      <c r="Y93" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z93" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="inlineStr">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B94" s="23" t="inlineStr">
+      <c r="B94" s="21" t="inlineStr">
         <is>
           <t>500317250</t>
         </is>
       </c>
-      <c r="C94" s="23" t="inlineStr">
+      <c r="C94" s="21" t="inlineStr">
         <is>
           <t>50031725000024</t>
         </is>
       </c>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="20" t="inlineStr">
         <is>
           <t>PARM'S</t>
         </is>
       </c>
-      <c r="E94" s="22" t="inlineStr">
+      <c r="E94" s="20" t="inlineStr">
         <is>
           <t>PARM'S</t>
         </is>
       </c>
-      <c r="F94" s="22" t="inlineStr">
+      <c r="F94" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
+      <c r="G94" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H94" s="22" t="inlineStr">
+      <c r="H94" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I94" s="22" t="inlineStr">
+      <c r="I94" s="20" t="inlineStr">
         <is>
           <t>03/10/2007</t>
         </is>
       </c>
-      <c r="J94" s="22" t="inlineStr">
+      <c r="J94" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="K94" s="22" t="inlineStr">
+      <c r="K94" s="20" t="inlineStr">
         <is>
           <t>70 RUE DE LA CHAPELLE</t>
         </is>
       </c>
-      <c r="L94" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M94" s="22" t="inlineStr">
+      <c r="L94" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M94" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N94" s="22" t="inlineStr">
+      <c r="N94" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O94" s="22" t="inlineStr"/>
-      <c r="P94" s="22" t="inlineStr"/>
-      <c r="Q94" s="22" t="inlineStr"/>
-      <c r="R94" s="23" t="inlineStr"/>
-      <c r="S94" s="22" t="inlineStr"/>
-      <c r="T94" s="22" t="inlineStr">
+      <c r="O94" s="20" t="inlineStr"/>
+      <c r="P94" s="20" t="inlineStr"/>
+      <c r="Q94" s="20" t="inlineStr"/>
+      <c r="R94" s="21" t="inlineStr"/>
+      <c r="S94" s="20" t="inlineStr"/>
+      <c r="T94" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U94" s="22" t="inlineStr">
+      <c r="U94" s="20" t="inlineStr">
         <is>
           <t>PARMENTIER</t>
         </is>
       </c>
-      <c r="V94" s="22" t="inlineStr">
+      <c r="V94" s="20" t="inlineStr">
         <is>
           <t>Yann, Fernand, Raimond</t>
         </is>
       </c>
-      <c r="W94" s="22" t="inlineStr">
+      <c r="W94" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X94" s="22" t="inlineStr">
+      <c r="X94" s="20" t="inlineStr">
         <is>
           <t>70 Rue de la Chapelle</t>
         </is>
       </c>
-      <c r="Y94" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z94" s="22" t="inlineStr">
+      <c r="Y94" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z94" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="inlineStr">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B95" s="23" t="inlineStr">
+      <c r="B95" s="21" t="inlineStr">
         <is>
           <t>450737424</t>
         </is>
       </c>
-      <c r="C95" s="23" t="inlineStr">
+      <c r="C95" s="21" t="inlineStr">
         <is>
           <t>45073742400017</t>
         </is>
       </c>
-      <c r="D95" s="22" t="inlineStr">
+      <c r="D95" s="20" t="inlineStr">
         <is>
           <t>LEXSIS</t>
         </is>
       </c>
-      <c r="E95" s="22" t="inlineStr">
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>LEXSIS</t>
         </is>
       </c>
-      <c r="F95" s="22" t="inlineStr">
+      <c r="F95" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G95" s="22" t="inlineStr">
+      <c r="G95" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H95" s="22" t="inlineStr">
+      <c r="H95" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I95" s="22" t="inlineStr">
+      <c r="I95" s="20" t="inlineStr">
         <is>
           <t>03/11/2003</t>
         </is>
       </c>
-      <c r="J95" s="22" t="inlineStr">
+      <c r="J95" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K95" s="22" t="inlineStr">
+      <c r="K95" s="20" t="inlineStr">
         <is>
           <t>7 RUE PAUL BEZANSON</t>
         </is>
       </c>
-      <c r="L95" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M95" s="22" t="inlineStr">
+      <c r="L95" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M95" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N95" s="22" t="inlineStr">
+      <c r="N95" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O95" s="22" t="n">
-        <v>667840</v>
-      </c>
-      <c r="P95" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q95" s="22" t="inlineStr"/>
-      <c r="R95" s="23" t="inlineStr"/>
-      <c r="S95" s="22" t="inlineStr"/>
-      <c r="T95" s="22" t="inlineStr">
+      <c r="O95" s="20" t="inlineStr">
+        <is>
+          <t>667840</t>
+        </is>
+      </c>
+      <c r="P95" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q95" s="20" t="inlineStr"/>
+      <c r="R95" s="21" t="inlineStr"/>
+      <c r="S95" s="20" t="inlineStr"/>
+      <c r="T95" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U95" s="22" t="inlineStr">
+      <c r="U95" s="20" t="inlineStr">
         <is>
           <t>OZCELIK</t>
         </is>
       </c>
-      <c r="V95" s="22" t="inlineStr">
+      <c r="V95" s="20" t="inlineStr">
         <is>
           <t>Cem</t>
         </is>
       </c>
-      <c r="W95" s="22" t="inlineStr">
+      <c r="W95" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X95" s="22" t="inlineStr">
+      <c r="X95" s="20" t="inlineStr">
         <is>
           <t>25 RUE DE LA PLANCHETTE</t>
         </is>
       </c>
-      <c r="Y95" s="23" t="inlineStr">
+      <c r="Y95" s="21" t="inlineStr">
         <is>
           <t>57645</t>
         </is>
       </c>
-      <c r="Z95" s="22" t="inlineStr">
+      <c r="Z95" s="20" t="inlineStr">
         <is>
           <t>MONTOY FLANVILLE</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="inlineStr">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B96" s="23" t="inlineStr">
+      <c r="B96" s="21" t="inlineStr">
         <is>
           <t>752026872</t>
         </is>
       </c>
-      <c r="C96" s="23" t="inlineStr">
+      <c r="C96" s="21" t="inlineStr">
         <is>
           <t>75202687200024</t>
         </is>
       </c>
-      <c r="D96" s="22" t="inlineStr">
+      <c r="D96" s="20" t="inlineStr">
         <is>
           <t>ALOUANE RABAH</t>
         </is>
       </c>
-      <c r="E96" s="22" t="inlineStr">
+      <c r="E96" s="20" t="inlineStr">
         <is>
           <t>ALOUANE RABAH</t>
         </is>
       </c>
-      <c r="F96" s="22" t="inlineStr">
+      <c r="F96" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G96" s="22" t="inlineStr">
+      <c r="G96" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H96" s="22" t="inlineStr">
+      <c r="H96" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I96" s="22" t="inlineStr">
+      <c r="I96" s="20" t="inlineStr">
         <is>
           <t>02/06/2012</t>
         </is>
       </c>
-      <c r="J96" s="22" t="inlineStr">
+      <c r="J96" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K96" s="22" t="inlineStr">
+      <c r="K96" s="20" t="inlineStr">
         <is>
           <t>5 AVENUE DE LATTRE DE TASSIGNY</t>
         </is>
       </c>
-      <c r="L96" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M96" s="22" t="inlineStr">
+      <c r="L96" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M96" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N96" s="22" t="inlineStr">
+      <c r="N96" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O96" s="22" t="inlineStr"/>
-      <c r="P96" s="22" t="inlineStr"/>
-      <c r="Q96" s="22" t="inlineStr"/>
-      <c r="R96" s="23" t="inlineStr"/>
-      <c r="S96" s="22" t="inlineStr"/>
-      <c r="T96" s="22" t="inlineStr">
+      <c r="O96" s="20" t="inlineStr"/>
+      <c r="P96" s="20" t="inlineStr"/>
+      <c r="Q96" s="20" t="inlineStr"/>
+      <c r="R96" s="21" t="inlineStr"/>
+      <c r="S96" s="20" t="inlineStr"/>
+      <c r="T96" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U96" s="22" t="inlineStr">
+      <c r="U96" s="20" t="inlineStr">
         <is>
           <t>ALOUANE</t>
         </is>
       </c>
-      <c r="V96" s="22" t="inlineStr">
+      <c r="V96" s="20" t="inlineStr">
         <is>
           <t>Rabah</t>
         </is>
       </c>
-      <c r="W96" s="22" t="inlineStr">
+      <c r="W96" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X96" s="22" t="inlineStr"/>
-      <c r="Y96" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z96" s="22" t="inlineStr">
+      <c r="X96" s="20" t="inlineStr"/>
+      <c r="Y96" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z96" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="inlineStr">
+      <c r="A97" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B97" s="23" t="inlineStr">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>949144307</t>
         </is>
       </c>
-      <c r="C97" s="23" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
         <is>
           <t>94914430700012</t>
         </is>
       </c>
-      <c r="D97" s="22" t="inlineStr">
+      <c r="D97" s="20" t="inlineStr">
         <is>
           <t>LES SAVEURS</t>
         </is>
       </c>
-      <c r="E97" s="22" t="inlineStr">
+      <c r="E97" s="20" t="inlineStr">
         <is>
           <t>LES SAVEURS</t>
         </is>
       </c>
-      <c r="F97" s="22" t="inlineStr">
+      <c r="F97" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G97" s="22" t="inlineStr">
+      <c r="G97" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H97" s="22" t="inlineStr">
+      <c r="H97" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I97" s="22" t="inlineStr">
+      <c r="I97" s="20" t="inlineStr">
         <is>
           <t>07/02/2023</t>
         </is>
       </c>
-      <c r="J97" s="22" t="inlineStr">
+      <c r="J97" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K97" s="22" t="inlineStr">
+      <c r="K97" s="20" t="inlineStr">
         <is>
           <t>26 AVENUE FOCH</t>
         </is>
       </c>
-      <c r="L97" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M97" s="22" t="inlineStr">
+      <c r="L97" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M97" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N97" s="22" t="inlineStr">
+      <c r="N97" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O97" s="22" t="inlineStr"/>
-      <c r="P97" s="22" t="inlineStr"/>
-      <c r="Q97" s="22" t="inlineStr"/>
-      <c r="R97" s="23" t="inlineStr"/>
-      <c r="S97" s="22" t="inlineStr"/>
-      <c r="T97" s="22" t="inlineStr">
+      <c r="O97" s="20" t="inlineStr"/>
+      <c r="P97" s="20" t="inlineStr"/>
+      <c r="Q97" s="20" t="inlineStr"/>
+      <c r="R97" s="21" t="inlineStr"/>
+      <c r="S97" s="20" t="inlineStr"/>
+      <c r="T97" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U97" s="22" t="inlineStr">
+      <c r="U97" s="20" t="inlineStr">
         <is>
           <t>REMY</t>
         </is>
       </c>
-      <c r="V97" s="22" t="inlineStr">
+      <c r="V97" s="20" t="inlineStr">
         <is>
           <t>Emmanuelle, Pascale, Bernadette</t>
         </is>
       </c>
-      <c r="W97" s="22" t="inlineStr">
+      <c r="W97" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X97" s="22" t="inlineStr">
+      <c r="X97" s="20" t="inlineStr">
         <is>
           <t>33 Rue Robert Darnery</t>
         </is>
       </c>
-      <c r="Y97" s="23" t="inlineStr">
+      <c r="Y97" s="21" t="inlineStr">
         <is>
           <t>54410</t>
         </is>
       </c>
-      <c r="Z97" s="22" t="inlineStr">
+      <c r="Z97" s="20" t="inlineStr">
         <is>
           <t>Laneuveville-devant-Nancy</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="inlineStr">
+      <c r="A98" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B98" s="23" t="inlineStr">
+      <c r="B98" s="21" t="inlineStr">
         <is>
           <t>899033450</t>
         </is>
       </c>
-      <c r="C98" s="23" t="inlineStr">
+      <c r="C98" s="21" t="inlineStr">
         <is>
           <t>89903345000011</t>
         </is>
       </c>
-      <c r="D98" s="22" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
         <is>
           <t>SAS MGROUP ENTREPRISES</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
+      <c r="E98" s="20" t="inlineStr">
         <is>
           <t>SAS MGROUP ENTREPRISES</t>
         </is>
       </c>
-      <c r="F98" s="22" t="inlineStr">
+      <c r="F98" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
+      <c r="G98" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H98" s="22" t="inlineStr">
+      <c r="H98" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I98" s="22" t="inlineStr">
+      <c r="I98" s="20" t="inlineStr">
         <is>
           <t>01/04/2021</t>
         </is>
       </c>
-      <c r="J98" s="22" t="inlineStr">
+      <c r="J98" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K98" s="22" t="inlineStr">
+      <c r="K98" s="20" t="inlineStr">
         <is>
           <t>120 RUE DES ALLEMANDS</t>
         </is>
       </c>
-      <c r="L98" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M98" s="22" t="inlineStr">
+      <c r="L98" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M98" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N98" s="22" t="inlineStr">
+      <c r="N98" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O98" s="22" t="inlineStr"/>
-      <c r="P98" s="22" t="inlineStr"/>
-      <c r="Q98" s="22" t="inlineStr"/>
-      <c r="R98" s="23" t="inlineStr"/>
-      <c r="S98" s="22" t="inlineStr"/>
-      <c r="T98" s="22" t="inlineStr">
+      <c r="O98" s="20" t="inlineStr"/>
+      <c r="P98" s="20" t="inlineStr"/>
+      <c r="Q98" s="20" t="inlineStr"/>
+      <c r="R98" s="21" t="inlineStr"/>
+      <c r="S98" s="20" t="inlineStr"/>
+      <c r="T98" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U98" s="22" t="inlineStr">
+      <c r="U98" s="20" t="inlineStr">
         <is>
           <t>MUNCH</t>
         </is>
       </c>
-      <c r="V98" s="22" t="inlineStr">
+      <c r="V98" s="20" t="inlineStr">
         <is>
           <t>Olivier, Roger</t>
         </is>
       </c>
-      <c r="W98" s="22" t="inlineStr">
+      <c r="W98" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X98" s="22" t="inlineStr">
+      <c r="X98" s="20" t="inlineStr">
         <is>
           <t>Lieu-Dit Pfisterquelle</t>
         </is>
       </c>
-      <c r="Y98" s="23" t="inlineStr">
+      <c r="Y98" s="21" t="inlineStr">
         <is>
           <t>57460</t>
         </is>
       </c>
-      <c r="Z98" s="22" t="inlineStr">
+      <c r="Z98" s="20" t="inlineStr">
         <is>
           <t>Behren-lès-Forbach</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="inlineStr">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B99" s="23" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>822068110</t>
         </is>
       </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="C99" s="21" t="inlineStr">
         <is>
           <t>82206811000011</t>
         </is>
       </c>
-      <c r="D99" s="22" t="inlineStr">
+      <c r="D99" s="20" t="inlineStr">
         <is>
           <t>TRESSON TRAITEUR</t>
         </is>
       </c>
-      <c r="E99" s="22" t="inlineStr">
+      <c r="E99" s="20" t="inlineStr">
         <is>
           <t>TRESSON TRAITEUR</t>
         </is>
       </c>
-      <c r="F99" s="22" t="inlineStr">
+      <c r="F99" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G99" s="22" t="inlineStr">
+      <c r="G99" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H99" s="22" t="inlineStr">
+      <c r="H99" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I99" s="22" t="inlineStr">
+      <c r="I99" s="20" t="inlineStr">
         <is>
           <t>15/07/2016</t>
         </is>
       </c>
-      <c r="J99" s="22" t="inlineStr">
+      <c r="J99" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K99" s="22" t="inlineStr">
+      <c r="K99" s="20" t="inlineStr">
         <is>
           <t>RUE DE PONT-A-MOUSSON</t>
         </is>
       </c>
-      <c r="L99" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M99" s="22" t="inlineStr">
+      <c r="L99" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M99" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N99" s="22" t="inlineStr">
+      <c r="N99" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O99" s="22" t="inlineStr"/>
-      <c r="P99" s="22" t="inlineStr"/>
-      <c r="Q99" s="22" t="inlineStr"/>
-      <c r="R99" s="23" t="inlineStr"/>
-      <c r="S99" s="22" t="inlineStr"/>
-      <c r="T99" s="22" t="inlineStr">
+      <c r="O99" s="20" t="inlineStr"/>
+      <c r="P99" s="20" t="inlineStr"/>
+      <c r="Q99" s="20" t="inlineStr"/>
+      <c r="R99" s="21" t="inlineStr"/>
+      <c r="S99" s="20" t="inlineStr"/>
+      <c r="T99" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U99" s="22" t="inlineStr">
+      <c r="U99" s="20" t="inlineStr">
         <is>
           <t>TRESSON</t>
         </is>
       </c>
-      <c r="V99" s="22" t="inlineStr">
+      <c r="V99" s="20" t="inlineStr">
         <is>
           <t>Sébastien</t>
         </is>
       </c>
-      <c r="W99" s="22" t="inlineStr">
+      <c r="W99" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X99" s="22" t="inlineStr">
+      <c r="X99" s="20" t="inlineStr">
         <is>
           <t>2 rue des Pruniers</t>
         </is>
       </c>
-      <c r="Y99" s="23" t="inlineStr">
+      <c r="Y99" s="21" t="inlineStr">
         <is>
           <t>57420</t>
         </is>
       </c>
-      <c r="Z99" s="22" t="inlineStr">
+      <c r="Z99" s="20" t="inlineStr">
         <is>
           <t>Pournoy-la-Chétive</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B100" s="23" t="inlineStr">
+      <c r="B100" s="21" t="inlineStr">
         <is>
           <t>451060693</t>
         </is>
       </c>
-      <c r="C100" s="23" t="inlineStr">
+      <c r="C100" s="21" t="inlineStr">
         <is>
           <t>45106069300012</t>
         </is>
       </c>
-      <c r="D100" s="22" t="inlineStr">
+      <c r="D100" s="20" t="inlineStr">
         <is>
           <t>ASSOCIATION CONSISTORIALE REFOUEL</t>
         </is>
       </c>
-      <c r="E100" s="22" t="inlineStr">
+      <c r="E100" s="20" t="inlineStr">
         <is>
           <t>ASSOCIATION CONSISTORIALE REFOUEL</t>
         </is>
       </c>
-      <c r="F100" s="22" t="inlineStr">
+      <c r="F100" s="20" t="inlineStr">
         <is>
           <t>Association de droit local (Bas-Rhin, Haut-Rhin et Moselle)</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
+      <c r="G100" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H100" s="22" t="inlineStr">
+      <c r="H100" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I100" s="22" t="inlineStr">
+      <c r="I100" s="20" t="inlineStr">
         <is>
           <t>01/01/2003</t>
         </is>
       </c>
-      <c r="J100" s="22" t="inlineStr">
+      <c r="J100" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K100" s="22" t="inlineStr">
+      <c r="K100" s="20" t="inlineStr">
         <is>
           <t>7 PLACE VALLADIER</t>
         </is>
       </c>
-      <c r="L100" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M100" s="22" t="inlineStr">
+      <c r="L100" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M100" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N100" s="22" t="inlineStr">
+      <c r="N100" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O100" s="22" t="inlineStr"/>
-      <c r="P100" s="22" t="inlineStr"/>
-      <c r="Q100" s="22" t="inlineStr"/>
-      <c r="R100" s="23" t="inlineStr"/>
-      <c r="S100" s="22" t="inlineStr"/>
-      <c r="T100" s="22" t="inlineStr">
+      <c r="O100" s="20" t="inlineStr"/>
+      <c r="P100" s="20" t="inlineStr"/>
+      <c r="Q100" s="20" t="inlineStr"/>
+      <c r="R100" s="21" t="inlineStr"/>
+      <c r="S100" s="20" t="inlineStr"/>
+      <c r="T100" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U100" s="22" t="inlineStr"/>
-      <c r="V100" s="22" t="inlineStr"/>
-      <c r="W100" s="22" t="inlineStr"/>
-      <c r="X100" s="22" t="inlineStr"/>
-      <c r="Y100" s="23" t="inlineStr"/>
-      <c r="Z100" s="22" t="inlineStr"/>
+      <c r="U100" s="20" t="inlineStr"/>
+      <c r="V100" s="20" t="inlineStr"/>
+      <c r="W100" s="20" t="inlineStr"/>
+      <c r="X100" s="20" t="inlineStr"/>
+      <c r="Y100" s="21" t="inlineStr"/>
+      <c r="Z100" s="20" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="inlineStr">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B101" s="23" t="inlineStr">
+      <c r="B101" s="21" t="inlineStr">
         <is>
           <t>821808672</t>
         </is>
       </c>
-      <c r="C101" s="23" t="inlineStr">
+      <c r="C101" s="21" t="inlineStr">
         <is>
           <t>82180867200017</t>
         </is>
       </c>
-      <c r="D101" s="22" t="inlineStr">
+      <c r="D101" s="20" t="inlineStr">
         <is>
           <t>BROOKLYN CAFE</t>
         </is>
       </c>
-      <c r="E101" s="22" t="inlineStr">
+      <c r="E101" s="20" t="inlineStr">
         <is>
           <t>BROOKLYN CAFE</t>
         </is>
       </c>
-      <c r="F101" s="22" t="inlineStr">
+      <c r="F101" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G101" s="22" t="inlineStr">
+      <c r="G101" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H101" s="22" t="inlineStr">
+      <c r="H101" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I101" s="22" t="inlineStr">
+      <c r="I101" s="20" t="inlineStr">
         <is>
           <t>29/07/2016</t>
         </is>
       </c>
-      <c r="J101" s="22" t="inlineStr">
+      <c r="J101" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K101" s="22" t="inlineStr">
+      <c r="K101" s="20" t="inlineStr">
         <is>
           <t>27 RUE DES ROCHES</t>
         </is>
       </c>
-      <c r="L101" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M101" s="22" t="inlineStr">
+      <c r="L101" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M101" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N101" s="22" t="inlineStr">
+      <c r="N101" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O101" s="22" t="inlineStr"/>
-      <c r="P101" s="22" t="inlineStr"/>
-      <c r="Q101" s="22" t="inlineStr"/>
-      <c r="R101" s="23" t="inlineStr"/>
-      <c r="S101" s="22" t="inlineStr"/>
-      <c r="T101" s="22" t="inlineStr">
+      <c r="O101" s="20" t="inlineStr"/>
+      <c r="P101" s="20" t="inlineStr"/>
+      <c r="Q101" s="20" t="inlineStr"/>
+      <c r="R101" s="21" t="inlineStr"/>
+      <c r="S101" s="20" t="inlineStr"/>
+      <c r="T101" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U101" s="22" t="inlineStr">
+      <c r="U101" s="20" t="inlineStr">
         <is>
           <t>DI CARLO</t>
         </is>
       </c>
-      <c r="V101" s="22" t="inlineStr">
+      <c r="V101" s="20" t="inlineStr">
         <is>
           <t>Olivier, Claude</t>
         </is>
       </c>
-      <c r="W101" s="22" t="inlineStr">
+      <c r="W101" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X101" s="22" t="inlineStr">
+      <c r="X101" s="20" t="inlineStr">
         <is>
           <t>26 rue Pasteur</t>
         </is>
       </c>
-      <c r="Y101" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z101" s="22" t="inlineStr">
+      <c r="Y101" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z101" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="inlineStr">
+      <c r="A102" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B102" s="23" t="inlineStr">
+      <c r="B102" s="21" t="inlineStr">
         <is>
           <t>910224096</t>
         </is>
       </c>
-      <c r="C102" s="23" t="inlineStr">
+      <c r="C102" s="21" t="inlineStr">
         <is>
           <t>91022409600016</t>
         </is>
       </c>
-      <c r="D102" s="22" t="inlineStr">
+      <c r="D102" s="20" t="inlineStr">
         <is>
           <t>LE CELESTE</t>
         </is>
       </c>
-      <c r="E102" s="22" t="inlineStr">
+      <c r="E102" s="20" t="inlineStr">
         <is>
           <t>LE CELESTE</t>
         </is>
       </c>
-      <c r="F102" s="22" t="inlineStr">
+      <c r="F102" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
+      <c r="G102" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H102" s="22" t="inlineStr">
+      <c r="H102" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I102" s="22" t="inlineStr">
+      <c r="I102" s="20" t="inlineStr">
         <is>
           <t>26/01/2022</t>
         </is>
       </c>
-      <c r="J102" s="22" t="inlineStr">
+      <c r="J102" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K102" s="22" t="inlineStr">
+      <c r="K102" s="20" t="inlineStr">
         <is>
           <t>49 IMPASSE DES ALLEMANDS</t>
         </is>
       </c>
-      <c r="L102" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M102" s="22" t="inlineStr">
+      <c r="L102" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M102" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N102" s="22" t="inlineStr">
+      <c r="N102" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O102" s="22" t="inlineStr"/>
-      <c r="P102" s="22" t="inlineStr"/>
-      <c r="Q102" s="22" t="inlineStr"/>
-      <c r="R102" s="23" t="inlineStr"/>
-      <c r="S102" s="22" t="inlineStr"/>
-      <c r="T102" s="22" t="inlineStr">
+      <c r="O102" s="20" t="inlineStr"/>
+      <c r="P102" s="20" t="inlineStr"/>
+      <c r="Q102" s="20" t="inlineStr"/>
+      <c r="R102" s="21" t="inlineStr"/>
+      <c r="S102" s="20" t="inlineStr"/>
+      <c r="T102" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U102" s="22" t="inlineStr">
+      <c r="U102" s="20" t="inlineStr">
         <is>
           <t>PREKA</t>
         </is>
       </c>
-      <c r="V102" s="22" t="inlineStr">
+      <c r="V102" s="20" t="inlineStr">
         <is>
           <t>Julien</t>
         </is>
       </c>
-      <c r="W102" s="22" t="inlineStr">
+      <c r="W102" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X102" s="22" t="inlineStr">
+      <c r="X102" s="20" t="inlineStr">
         <is>
           <t>8 Rue de Budange</t>
         </is>
       </c>
-      <c r="Y102" s="23" t="inlineStr">
+      <c r="Y102" s="21" t="inlineStr">
         <is>
           <t>57270</t>
         </is>
       </c>
-      <c r="Z102" s="22" t="inlineStr">
+      <c r="Z102" s="20" t="inlineStr">
         <is>
           <t>Uckange</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="22" t="inlineStr">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B103" s="23" t="inlineStr">
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>829499235</t>
         </is>
       </c>
-      <c r="C103" s="23" t="inlineStr">
+      <c r="C103" s="21" t="inlineStr">
         <is>
           <t>82949923500028</t>
         </is>
       </c>
-      <c r="D103" s="22" t="inlineStr">
+      <c r="D103" s="20" t="inlineStr">
         <is>
           <t>AU COUTEAU LORRAIN</t>
         </is>
       </c>
-      <c r="E103" s="22" t="inlineStr">
+      <c r="E103" s="20" t="inlineStr">
         <is>
           <t>AU COUTEAU LORRAIN</t>
         </is>
       </c>
-      <c r="F103" s="22" t="inlineStr">
+      <c r="F103" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G103" s="22" t="inlineStr">
+      <c r="G103" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H103" s="22" t="inlineStr">
+      <c r="H103" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I103" s="22" t="inlineStr">
+      <c r="I103" s="20" t="inlineStr">
         <is>
           <t>09/05/2017</t>
         </is>
       </c>
-      <c r="J103" s="22" t="inlineStr">
+      <c r="J103" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K103" s="22" t="inlineStr">
+      <c r="K103" s="20" t="inlineStr">
         <is>
           <t>12 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L103" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M103" s="22" t="inlineStr">
+      <c r="L103" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M103" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N103" s="22" t="inlineStr">
+      <c r="N103" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O103" s="22" t="inlineStr"/>
-      <c r="P103" s="22" t="inlineStr"/>
-      <c r="Q103" s="22" t="inlineStr"/>
-      <c r="R103" s="23" t="inlineStr"/>
-      <c r="S103" s="22" t="inlineStr"/>
-      <c r="T103" s="22" t="inlineStr">
+      <c r="O103" s="20" t="inlineStr"/>
+      <c r="P103" s="20" t="inlineStr"/>
+      <c r="Q103" s="20" t="inlineStr"/>
+      <c r="R103" s="21" t="inlineStr"/>
+      <c r="S103" s="20" t="inlineStr"/>
+      <c r="T103" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U103" s="22" t="inlineStr">
+      <c r="U103" s="20" t="inlineStr">
         <is>
           <t>BAUDINOT</t>
         </is>
       </c>
-      <c r="V103" s="22" t="inlineStr">
+      <c r="V103" s="20" t="inlineStr">
         <is>
           <t>Cédric, Damien</t>
         </is>
       </c>
-      <c r="W103" s="22" t="inlineStr">
+      <c r="W103" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X103" s="22" t="inlineStr">
+      <c r="X103" s="20" t="inlineStr">
         <is>
           <t>2B rue au Blé</t>
         </is>
       </c>
-      <c r="Y103" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z103" s="22" t="inlineStr">
+      <c r="Y103" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z103" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="22" t="inlineStr">
+      <c r="A104" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B104" s="23" t="inlineStr">
+      <c r="B104" s="21" t="inlineStr">
         <is>
           <t>830552865</t>
         </is>
       </c>
-      <c r="C104" s="23" t="inlineStr">
+      <c r="C104" s="21" t="inlineStr">
         <is>
           <t>83055286500016</t>
         </is>
       </c>
-      <c r="D104" s="22" t="inlineStr">
+      <c r="D104" s="20" t="inlineStr">
         <is>
           <t>WINSTON</t>
         </is>
       </c>
-      <c r="E104" s="22" t="inlineStr">
+      <c r="E104" s="20" t="inlineStr">
         <is>
           <t>WINSTON</t>
         </is>
       </c>
-      <c r="F104" s="22" t="inlineStr">
+      <c r="F104" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G104" s="22" t="inlineStr">
+      <c r="G104" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H104" s="22" t="inlineStr">
+      <c r="H104" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I104" s="22" t="inlineStr">
+      <c r="I104" s="20" t="inlineStr">
         <is>
           <t>28/06/2017</t>
         </is>
       </c>
-      <c r="J104" s="22" t="inlineStr">
+      <c r="J104" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K104" s="22" t="inlineStr">
+      <c r="K104" s="20" t="inlineStr">
         <is>
           <t>10 RUE WINSTON CHURCHILL</t>
         </is>
       </c>
-      <c r="L104" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M104" s="22" t="inlineStr">
+      <c r="L104" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M104" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N104" s="22" t="inlineStr">
+      <c r="N104" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O104" s="22" t="inlineStr"/>
-      <c r="P104" s="22" t="inlineStr"/>
-      <c r="Q104" s="22" t="inlineStr"/>
-      <c r="R104" s="23" t="inlineStr"/>
-      <c r="S104" s="22" t="inlineStr"/>
-      <c r="T104" s="22" t="inlineStr">
+      <c r="O104" s="20" t="inlineStr"/>
+      <c r="P104" s="20" t="inlineStr"/>
+      <c r="Q104" s="20" t="inlineStr"/>
+      <c r="R104" s="21" t="inlineStr"/>
+      <c r="S104" s="20" t="inlineStr"/>
+      <c r="T104" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U104" s="22" t="inlineStr">
+      <c r="U104" s="20" t="inlineStr">
         <is>
           <t>WALLERICH</t>
         </is>
       </c>
-      <c r="V104" s="22" t="inlineStr">
+      <c r="V104" s="20" t="inlineStr">
         <is>
           <t>Michel, Ernest</t>
         </is>
       </c>
-      <c r="W104" s="22" t="inlineStr">
+      <c r="W104" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X104" s="22" t="inlineStr">
+      <c r="X104" s="20" t="inlineStr">
         <is>
           <t>40 rue Saint-Gengoulf</t>
         </is>
       </c>
-      <c r="Y104" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z104" s="22" t="inlineStr">
+      <c r="Y104" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z104" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="22" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B105" s="23" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>401402995</t>
         </is>
       </c>
-      <c r="C105" s="23" t="inlineStr">
+      <c r="C105" s="21" t="inlineStr">
         <is>
           <t>40140299500021</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D105" s="20" t="inlineStr">
         <is>
           <t>KOCH Sandrine</t>
         </is>
       </c>
-      <c r="E105" s="22" t="inlineStr">
+      <c r="E105" s="20" t="inlineStr">
         <is>
           <t>KOCH Sandrine</t>
         </is>
       </c>
-      <c r="F105" s="22" t="inlineStr">
+      <c r="F105" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G105" s="22" t="inlineStr">
+      <c r="G105" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H105" s="22" t="inlineStr">
+      <c r="H105" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I105" s="22" t="inlineStr">
+      <c r="I105" s="20" t="inlineStr">
         <is>
           <t>16/06/1995</t>
         </is>
       </c>
-      <c r="J105" s="22" t="inlineStr">
+      <c r="J105" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="K105" s="22" t="inlineStr">
+      <c r="K105" s="20" t="inlineStr">
         <is>
           <t>37 A RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="L105" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M105" s="22" t="inlineStr">
+      <c r="L105" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M105" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N105" s="22" t="inlineStr">
+      <c r="N105" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O105" s="22" t="inlineStr"/>
-      <c r="P105" s="22" t="inlineStr"/>
-      <c r="Q105" s="22" t="inlineStr"/>
-      <c r="R105" s="23" t="inlineStr"/>
-      <c r="S105" s="22" t="inlineStr"/>
-      <c r="T105" s="22" t="inlineStr">
+      <c r="O105" s="20" t="inlineStr"/>
+      <c r="P105" s="20" t="inlineStr"/>
+      <c r="Q105" s="20" t="inlineStr"/>
+      <c r="R105" s="21" t="inlineStr"/>
+      <c r="S105" s="20" t="inlineStr"/>
+      <c r="T105" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U105" s="22" t="inlineStr">
+      <c r="U105" s="20" t="inlineStr">
         <is>
           <t>KOCH</t>
         </is>
       </c>
-      <c r="V105" s="22" t="inlineStr">
+      <c r="V105" s="20" t="inlineStr">
         <is>
           <t>Sandrine</t>
         </is>
       </c>
-      <c r="W105" s="22" t="inlineStr">
+      <c r="W105" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X105" s="22" t="inlineStr"/>
-      <c r="Y105" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z105" s="22" t="inlineStr">
+      <c r="X105" s="20" t="inlineStr"/>
+      <c r="Y105" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z105" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="22" t="inlineStr">
+      <c r="A106" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B106" s="23" t="inlineStr">
+      <c r="B106" s="21" t="inlineStr">
         <is>
           <t>491003075</t>
         </is>
       </c>
-      <c r="C106" s="23" t="inlineStr">
+      <c r="C106" s="21" t="inlineStr">
         <is>
           <t>49100307500018</t>
         </is>
       </c>
-      <c r="D106" s="22" t="inlineStr">
+      <c r="D106" s="20" t="inlineStr">
         <is>
           <t>SARL LA TASSE AMOS</t>
         </is>
       </c>
-      <c r="E106" s="22" t="inlineStr">
+      <c r="E106" s="20" t="inlineStr">
         <is>
           <t>SARL LA TASSE AMOS</t>
         </is>
       </c>
-      <c r="F106" s="22" t="inlineStr">
+      <c r="F106" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G106" s="22" t="inlineStr">
+      <c r="G106" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H106" s="22" t="inlineStr">
+      <c r="H106" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I106" s="22" t="inlineStr">
+      <c r="I106" s="20" t="inlineStr">
         <is>
           <t>10/07/2006</t>
         </is>
       </c>
-      <c r="J106" s="22" t="inlineStr">
+      <c r="J106" s="20" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="K106" s="22" t="inlineStr">
+      <c r="K106" s="20" t="inlineStr">
         <is>
           <t>6 PLACE JEAN SPINGA</t>
         </is>
       </c>
-      <c r="L106" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M106" s="22" t="inlineStr">
+      <c r="L106" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M106" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N106" s="22" t="inlineStr">
+      <c r="N106" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O106" s="22" t="inlineStr"/>
-      <c r="P106" s="22" t="inlineStr"/>
-      <c r="Q106" s="22" t="inlineStr"/>
-      <c r="R106" s="23" t="inlineStr"/>
-      <c r="S106" s="22" t="inlineStr"/>
-      <c r="T106" s="22" t="inlineStr">
+      <c r="O106" s="20" t="inlineStr"/>
+      <c r="P106" s="20" t="inlineStr"/>
+      <c r="Q106" s="20" t="inlineStr"/>
+      <c r="R106" s="21" t="inlineStr"/>
+      <c r="S106" s="20" t="inlineStr"/>
+      <c r="T106" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U106" s="22" t="inlineStr">
+      <c r="U106" s="20" t="inlineStr">
         <is>
           <t>CINAR</t>
         </is>
       </c>
-      <c r="V106" s="22" t="inlineStr">
+      <c r="V106" s="20" t="inlineStr">
         <is>
           <t>Sabri</t>
         </is>
       </c>
-      <c r="W106" s="22" t="inlineStr">
+      <c r="W106" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X106" s="22" t="inlineStr">
+      <c r="X106" s="20" t="inlineStr">
         <is>
           <t>1 RUE ROCHEMBEAU</t>
         </is>
       </c>
-      <c r="Y106" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z106" s="22" t="inlineStr">
+      <c r="Y106" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z106" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="22" t="inlineStr">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B107" s="23" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>838437283</t>
         </is>
       </c>
-      <c r="C107" s="23" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>83843728300016</t>
         </is>
       </c>
-      <c r="D107" s="22" t="inlineStr">
+      <c r="D107" s="20" t="inlineStr">
         <is>
           <t>FRIEDERICH Jordane</t>
         </is>
       </c>
-      <c r="E107" s="22" t="inlineStr">
+      <c r="E107" s="20" t="inlineStr">
         <is>
           <t>FRIEDERICH Jordane</t>
         </is>
       </c>
-      <c r="F107" s="22" t="inlineStr">
+      <c r="F107" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G107" s="22" t="inlineStr">
+      <c r="G107" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H107" s="22" t="inlineStr">
+      <c r="H107" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I107" s="22" t="inlineStr">
+      <c r="I107" s="20" t="inlineStr">
         <is>
           <t>13/03/2018</t>
         </is>
       </c>
-      <c r="J107" s="22" t="inlineStr">
+      <c r="J107" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K107" s="22" t="inlineStr">
+      <c r="K107" s="20" t="inlineStr">
         <is>
           <t>36 RUE DES JARDINS</t>
         </is>
       </c>
-      <c r="L107" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M107" s="22" t="inlineStr">
+      <c r="L107" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M107" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N107" s="22" t="inlineStr">
+      <c r="N107" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O107" s="22" t="inlineStr"/>
-      <c r="P107" s="22" t="inlineStr"/>
-      <c r="Q107" s="22" t="inlineStr"/>
-      <c r="R107" s="23" t="inlineStr"/>
-      <c r="S107" s="22" t="inlineStr"/>
-      <c r="T107" s="22" t="inlineStr">
+      <c r="O107" s="20" t="inlineStr"/>
+      <c r="P107" s="20" t="inlineStr"/>
+      <c r="Q107" s="20" t="inlineStr"/>
+      <c r="R107" s="21" t="inlineStr"/>
+      <c r="S107" s="20" t="inlineStr"/>
+      <c r="T107" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U107" s="22" t="inlineStr">
+      <c r="U107" s="20" t="inlineStr">
         <is>
           <t>FRIEDERICH</t>
         </is>
       </c>
-      <c r="V107" s="22" t="inlineStr">
+      <c r="V107" s="20" t="inlineStr">
         <is>
           <t>Jordane</t>
         </is>
       </c>
-      <c r="W107" s="22" t="inlineStr">
+      <c r="W107" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X107" s="22" t="inlineStr"/>
-      <c r="Y107" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z107" s="22" t="inlineStr">
+      <c r="X107" s="20" t="inlineStr"/>
+      <c r="Y107" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z107" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="inlineStr">
+        <is>
+          <t>995019544</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>99501954400015</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>RGB</t>
+        </is>
+      </c>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>RGB</t>
+        </is>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>09/12/2025</t>
+        </is>
+      </c>
+      <c r="J108" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K108" s="22" t="inlineStr">
+        <is>
+          <t>7 B RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L108" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N108" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O108" s="22" t="inlineStr"/>
+      <c r="P108" s="22" t="inlineStr"/>
+      <c r="Q108" s="22" t="inlineStr"/>
+      <c r="R108" s="23" t="inlineStr"/>
+      <c r="S108" s="22" t="inlineStr"/>
+      <c r="T108" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U108" s="22" t="inlineStr">
+        <is>
+          <t>POTIER</t>
+        </is>
+      </c>
+      <c r="V108" s="22" t="inlineStr">
+        <is>
+          <t>Yannis</t>
+        </is>
+      </c>
+      <c r="W108" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X108" s="22" t="inlineStr">
+        <is>
+          <t>8 rue du Faisan</t>
+        </is>
+      </c>
+      <c r="Y108" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z108" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>849498654</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>84949865400011</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>BLANC &amp; NOIR LOUNGE</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>BLANC &amp; NOIR LOUNGE</t>
+        </is>
+      </c>
+      <c r="F109" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>27/03/2019</t>
+        </is>
+      </c>
+      <c r="J109" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K109" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE HAUTE PIERRE</t>
+        </is>
+      </c>
+      <c r="L109" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M109" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N109" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O109" s="22" t="inlineStr"/>
+      <c r="P109" s="22" t="inlineStr"/>
+      <c r="Q109" s="22" t="inlineStr"/>
+      <c r="R109" s="23" t="inlineStr"/>
+      <c r="S109" s="22" t="inlineStr"/>
+      <c r="T109" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U109" s="22" t="inlineStr">
+        <is>
+          <t>KOUADIO</t>
+        </is>
+      </c>
+      <c r="V109" s="22" t="inlineStr">
+        <is>
+          <t>Kotokoun, Amoin, Charlotte</t>
+        </is>
+      </c>
+      <c r="W109" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X109" s="22" t="inlineStr">
+        <is>
+          <t>15 rue Lothaire</t>
+        </is>
+      </c>
+      <c r="Y109" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z109" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>807703418</t>
+        </is>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>80770341800010</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>LE PIAF</t>
+        </is>
+      </c>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>LE PIAF</t>
+        </is>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>05/11/2014</t>
+        </is>
+      </c>
+      <c r="J110" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K110" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE DU GRAND CERF</t>
+        </is>
+      </c>
+      <c r="L110" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M110" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N110" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O110" s="22" t="inlineStr"/>
+      <c r="P110" s="22" t="inlineStr"/>
+      <c r="Q110" s="22" t="inlineStr"/>
+      <c r="R110" s="23" t="inlineStr"/>
+      <c r="S110" s="22" t="inlineStr"/>
+      <c r="T110" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U110" s="22" t="inlineStr">
+        <is>
+          <t>GRIMONPON</t>
+        </is>
+      </c>
+      <c r="V110" s="22" t="inlineStr">
+        <is>
+          <t>Muriel</t>
+        </is>
+      </c>
+      <c r="W110" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X110" s="22" t="inlineStr">
+        <is>
+          <t>28 rue Saint-Eucaire</t>
+        </is>
+      </c>
+      <c r="Y110" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z110" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>880546924</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>88054692400015</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="E111" s="22" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="F111" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>20/12/2019</t>
+        </is>
+      </c>
+      <c r="J111" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K111" s="22" t="inlineStr">
+        <is>
+          <t>19 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L111" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M111" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N111" s="22" t="inlineStr">
+        <is>
+          <t>Entre 20 et 49 salariés</t>
+        </is>
+      </c>
+      <c r="O111" s="22" t="inlineStr"/>
+      <c r="P111" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q111" s="22" t="inlineStr"/>
+      <c r="R111" s="23" t="inlineStr"/>
+      <c r="S111" s="22" t="inlineStr"/>
+      <c r="T111" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U111" s="22" t="inlineStr">
+        <is>
+          <t>CLEMENTE</t>
+        </is>
+      </c>
+      <c r="V111" s="22" t="inlineStr">
+        <is>
+          <t>Virgile, Pierre, Joseph</t>
+        </is>
+      </c>
+      <c r="W111" s="22" t="inlineStr">
+        <is>
+          <t>Directeur général</t>
+        </is>
+      </c>
+      <c r="X111" s="22" t="inlineStr">
+        <is>
+          <t>83 rue Principale</t>
+        </is>
+      </c>
+      <c r="Y111" s="23" t="inlineStr">
+        <is>
+          <t>57640</t>
+        </is>
+      </c>
+      <c r="Z111" s="22" t="inlineStr">
+        <is>
+          <t>Servigny-les-Sainte-barbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>948268602</t>
+        </is>
+      </c>
+      <c r="C112" s="23" t="inlineStr">
+        <is>
+          <t>94826860200026</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>APOCALYPSE</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
+        <is>
+          <t>APOCALYPSE</t>
+        </is>
+      </c>
+      <c r="F112" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>03/01/2023</t>
+        </is>
+      </c>
+      <c r="J112" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K112" s="22" t="inlineStr">
+        <is>
+          <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
+        </is>
+      </c>
+      <c r="L112" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M112" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N112" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O112" s="22" t="inlineStr"/>
+      <c r="P112" s="22" t="inlineStr"/>
+      <c r="Q112" s="22" t="inlineStr"/>
+      <c r="R112" s="23" t="inlineStr"/>
+      <c r="S112" s="22" t="inlineStr"/>
+      <c r="T112" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U112" s="22" t="inlineStr">
+        <is>
+          <t>RRETHI</t>
+        </is>
+      </c>
+      <c r="V112" s="22" t="inlineStr">
+        <is>
+          <t>Marjan</t>
+        </is>
+      </c>
+      <c r="W112" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X112" s="22" t="inlineStr">
+        <is>
+          <t>22 Boulevard André Maginot</t>
+        </is>
+      </c>
+      <c r="Y112" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z112" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>844714626</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>84471462600018</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr">
+        <is>
+          <t>LE SAINT MARCEL - BISTROT DU PONT</t>
+        </is>
+      </c>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>LE SAINT MARCEL - BISTROT DU PONT</t>
+        </is>
+      </c>
+      <c r="F113" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G113" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I113" s="22" t="inlineStr">
+        <is>
+          <t>31/12/2018</t>
+        </is>
+      </c>
+      <c r="J113" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K113" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DU PONT SAINT-MARCEL</t>
+        </is>
+      </c>
+      <c r="L113" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M113" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N113" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O113" s="22" t="inlineStr"/>
+      <c r="P113" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q113" s="22" t="inlineStr"/>
+      <c r="R113" s="23" t="inlineStr"/>
+      <c r="S113" s="22" t="inlineStr"/>
+      <c r="T113" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U113" s="22" t="inlineStr">
+        <is>
+          <t>ZIMMERMANN</t>
+        </is>
+      </c>
+      <c r="V113" s="22" t="inlineStr">
+        <is>
+          <t>Bruno, Claude</t>
+        </is>
+      </c>
+      <c r="W113" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X113" s="22" t="inlineStr">
+        <is>
+          <t>8 rue de la Garde</t>
+        </is>
+      </c>
+      <c r="Y113" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z113" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>832526297</t>
+        </is>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>83252629700011</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="inlineStr">
+        <is>
+          <t>SAHAN HALIL</t>
+        </is>
+      </c>
+      <c r="E114" s="22" t="inlineStr">
+        <is>
+          <t>SAHAN HALIL</t>
+        </is>
+      </c>
+      <c r="F114" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I114" s="22" t="inlineStr">
+        <is>
+          <t>11/10/2017</t>
+        </is>
+      </c>
+      <c r="J114" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K114" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DU MOULIN</t>
+        </is>
+      </c>
+      <c r="L114" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M114" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N114" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O114" s="22" t="inlineStr"/>
+      <c r="P114" s="22" t="inlineStr"/>
+      <c r="Q114" s="22" t="inlineStr"/>
+      <c r="R114" s="23" t="inlineStr"/>
+      <c r="S114" s="22" t="inlineStr"/>
+      <c r="T114" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U114" s="22" t="inlineStr">
+        <is>
+          <t>SAHAN</t>
+        </is>
+      </c>
+      <c r="V114" s="22" t="inlineStr">
+        <is>
+          <t>Halil</t>
+        </is>
+      </c>
+      <c r="W114" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X114" s="22" t="inlineStr"/>
+      <c r="Y114" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z114" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>844523316</t>
+        </is>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>84452331600017</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="inlineStr">
+        <is>
+          <t>MC WIN</t>
+        </is>
+      </c>
+      <c r="E115" s="22" t="inlineStr">
+        <is>
+          <t>MC WIN</t>
+        </is>
+      </c>
+      <c r="F115" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G115" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I115" s="22" t="inlineStr">
+        <is>
+          <t>04/12/2018</t>
+        </is>
+      </c>
+      <c r="J115" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K115" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L115" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O115" s="22" t="inlineStr"/>
+      <c r="P115" s="22" t="inlineStr"/>
+      <c r="Q115" s="22" t="inlineStr"/>
+      <c r="R115" s="23" t="inlineStr"/>
+      <c r="S115" s="22" t="inlineStr"/>
+      <c r="T115" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U115" s="22" t="inlineStr">
+        <is>
+          <t>BENHAFED</t>
+        </is>
+      </c>
+      <c r="V115" s="22" t="inlineStr">
+        <is>
+          <t>Adel</t>
+        </is>
+      </c>
+      <c r="W115" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X115" s="22" t="inlineStr">
+        <is>
+          <t>3 Rue de Normandie</t>
+        </is>
+      </c>
+      <c r="Y115" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z115" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B116" s="23" t="inlineStr">
+        <is>
+          <t>853101905</t>
+        </is>
+      </c>
+      <c r="C116" s="23" t="inlineStr">
+        <is>
+          <t>85310190500018</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>LES BURGERS MESSINS</t>
+        </is>
+      </c>
+      <c r="E116" s="22" t="inlineStr">
+        <is>
+          <t>LES BURGERS MESSINS</t>
+        </is>
+      </c>
+      <c r="F116" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>01/07/2019</t>
+        </is>
+      </c>
+      <c r="J116" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K116" s="22" t="inlineStr">
+        <is>
+          <t>42 RUE DES CLERCS</t>
+        </is>
+      </c>
+      <c r="L116" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M116" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N116" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O116" s="22" t="inlineStr"/>
+      <c r="P116" s="22" t="inlineStr"/>
+      <c r="Q116" s="22" t="inlineStr"/>
+      <c r="R116" s="23" t="inlineStr"/>
+      <c r="S116" s="22" t="inlineStr"/>
+      <c r="T116" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U116" s="22" t="inlineStr">
+        <is>
+          <t>ZHU</t>
+        </is>
+      </c>
+      <c r="V116" s="22" t="inlineStr">
+        <is>
+          <t>Noël, Pierre</t>
+        </is>
+      </c>
+      <c r="W116" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X116" s="22" t="inlineStr">
+        <is>
+          <t>50 Avenue de l'Ile d'Amour</t>
+        </is>
+      </c>
+      <c r="Y116" s="23" t="inlineStr">
+        <is>
+          <t>94170</t>
+        </is>
+      </c>
+      <c r="Z116" s="22" t="inlineStr">
+        <is>
+          <t>Le Perreux-sur-Marne</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="inlineStr">
+        <is>
+          <t>988252888</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>98825288800017</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>LE TRUCK BON</t>
+        </is>
+      </c>
+      <c r="E117" s="22" t="inlineStr">
+        <is>
+          <t>LE TRUCK BON</t>
+        </is>
+      </c>
+      <c r="F117" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G117" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H117" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I117" s="22" t="inlineStr">
+        <is>
+          <t>16/06/2025</t>
+        </is>
+      </c>
+      <c r="J117" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K117" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE DES LUPINS</t>
+        </is>
+      </c>
+      <c r="L117" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M117" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N117" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O117" s="22" t="inlineStr"/>
+      <c r="P117" s="22" t="inlineStr"/>
+      <c r="Q117" s="22" t="inlineStr"/>
+      <c r="R117" s="23" t="inlineStr"/>
+      <c r="S117" s="22" t="inlineStr"/>
+      <c r="T117" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U117" s="22" t="inlineStr">
+        <is>
+          <t>HARPALICE</t>
+        </is>
+      </c>
+      <c r="V117" s="22" t="inlineStr">
+        <is>
+          <t>Béatrice, Jocelyne, Eugénie</t>
+        </is>
+      </c>
+      <c r="W117" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X117" s="22" t="inlineStr">
+        <is>
+          <t>5, rue de la Marne</t>
+        </is>
+      </c>
+      <c r="Y117" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z117" s="22" t="inlineStr">
+        <is>
+          <t>Le Ban-Saint-Martin</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>953441490</t>
+        </is>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>95344149000018</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>Manna</t>
+        </is>
+      </c>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
+          <t>Manna</t>
+        </is>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I118" s="22" t="inlineStr">
+        <is>
+          <t>13/06/2023</t>
+        </is>
+      </c>
+      <c r="J118" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K118" s="22" t="inlineStr">
+        <is>
+          <t>19 PLACE DES CHARRONS</t>
+        </is>
+      </c>
+      <c r="L118" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M118" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N118" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O118" s="22" t="inlineStr"/>
+      <c r="P118" s="22" t="inlineStr"/>
+      <c r="Q118" s="22" t="inlineStr"/>
+      <c r="R118" s="23" t="inlineStr"/>
+      <c r="S118" s="22" t="inlineStr"/>
+      <c r="T118" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U118" s="22" t="inlineStr">
+        <is>
+          <t>EMHAMED MAHAMUD</t>
+        </is>
+      </c>
+      <c r="V118" s="22" t="inlineStr">
+        <is>
+          <t>Kamel</t>
+        </is>
+      </c>
+      <c r="W118" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X118" s="22" t="inlineStr">
+        <is>
+          <t>1 Rue de la Champagne</t>
+        </is>
+      </c>
+      <c r="Y118" s="23" t="inlineStr">
+        <is>
+          <t>79200</t>
+        </is>
+      </c>
+      <c r="Z118" s="22" t="inlineStr">
+        <is>
+          <t>Parthenay</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="inlineStr">
+        <is>
+          <t>925318701</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>92531870100032</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="inlineStr">
+        <is>
+          <t>FONDER</t>
+        </is>
+      </c>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>FONDER</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G119" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I119" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2023</t>
+        </is>
+      </c>
+      <c r="J119" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K119" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE SERPENOISE</t>
+        </is>
+      </c>
+      <c r="L119" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M119" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N119" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O119" s="22" t="inlineStr"/>
+      <c r="P119" s="22" t="inlineStr"/>
+      <c r="Q119" s="22" t="inlineStr"/>
+      <c r="R119" s="23" t="inlineStr"/>
+      <c r="S119" s="22" t="inlineStr"/>
+      <c r="T119" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U119" s="22" t="inlineStr">
+        <is>
+          <t>BEGUM</t>
+        </is>
+      </c>
+      <c r="V119" s="22" t="inlineStr">
+        <is>
+          <t>Fathma</t>
+        </is>
+      </c>
+      <c r="W119" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X119" s="22" t="inlineStr"/>
+      <c r="Y119" s="23" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="Z119" s="22" t="inlineStr">
+        <is>
+          <t>Nanterre</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>990366023</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>99036602300010</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>DIAMOND BURGER</t>
+        </is>
+      </c>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>DIAMOND BURGER</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I120" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="J120" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K120" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE COISLIN</t>
+        </is>
+      </c>
+      <c r="L120" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M120" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N120" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O120" s="22" t="inlineStr"/>
+      <c r="P120" s="22" t="inlineStr"/>
+      <c r="Q120" s="22" t="inlineStr"/>
+      <c r="R120" s="23" t="inlineStr"/>
+      <c r="S120" s="22" t="inlineStr"/>
+      <c r="T120" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U120" s="22" t="inlineStr">
+        <is>
+          <t>SALIH</t>
+        </is>
+      </c>
+      <c r="V120" s="22" t="inlineStr">
+        <is>
+          <t>Amir</t>
+        </is>
+      </c>
+      <c r="W120" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X120" s="22" t="inlineStr">
+        <is>
+          <t>24 rue du wad billy</t>
+        </is>
+      </c>
+      <c r="Y120" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z120" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>941815169</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>94181516900011</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="inlineStr">
+        <is>
+          <t>RD GROUPES</t>
+        </is>
+      </c>
+      <c r="E121" s="22" t="inlineStr">
+        <is>
+          <t>RD GROUPES</t>
+        </is>
+      </c>
+      <c r="F121" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G121" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I121" s="22" t="inlineStr">
+        <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="J121" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K121" s="22" t="inlineStr">
+        <is>
+          <t>105 AVENUE ANDRE MALRAUX</t>
+        </is>
+      </c>
+      <c r="L121" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M121" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N121" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O121" s="22" t="inlineStr"/>
+      <c r="P121" s="22" t="inlineStr"/>
+      <c r="Q121" s="22" t="inlineStr"/>
+      <c r="R121" s="23" t="inlineStr"/>
+      <c r="S121" s="22" t="inlineStr"/>
+      <c r="T121" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U121" s="22" t="inlineStr">
+        <is>
+          <t>APREYAN</t>
+        </is>
+      </c>
+      <c r="V121" s="22" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="W121" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X121" s="22" t="inlineStr">
+        <is>
+          <t>27b rue principale</t>
+        </is>
+      </c>
+      <c r="Y121" s="23" t="inlineStr">
+        <is>
+          <t>57245</t>
+        </is>
+      </c>
+      <c r="Z121" s="22" t="inlineStr">
+        <is>
+          <t>Jury</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t>790606255</t>
+        </is>
+      </c>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>79060625500053</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="inlineStr">
+        <is>
+          <t>DAUSSE WELKER</t>
+        </is>
+      </c>
+      <c r="E122" s="22" t="inlineStr">
+        <is>
+          <t>DAUSSE WELKER</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I122" s="22" t="inlineStr">
+        <is>
+          <t>01/01/2013</t>
+        </is>
+      </c>
+      <c r="J122" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K122" s="22" t="inlineStr">
+        <is>
+          <t>20 RUE PASTEUR</t>
+        </is>
+      </c>
+      <c r="L122" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M122" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N122" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O122" s="22" t="inlineStr"/>
+      <c r="P122" s="22" t="inlineStr"/>
+      <c r="Q122" s="22" t="inlineStr"/>
+      <c r="R122" s="23" t="inlineStr"/>
+      <c r="S122" s="22" t="inlineStr"/>
+      <c r="T122" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U122" s="22" t="inlineStr">
+        <is>
+          <t>HUBERTY</t>
+        </is>
+      </c>
+      <c r="V122" s="22" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="W122" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X122" s="22" t="inlineStr">
+        <is>
+          <t>26 Boulevard Saint-Symphorien</t>
+        </is>
+      </c>
+      <c r="Y122" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z122" s="22" t="inlineStr">
+        <is>
+          <t>Longeville-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>750091183</t>
+        </is>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>75009118300012</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="inlineStr">
+        <is>
+          <t>AIT BAYAHYA MOHAMED</t>
+        </is>
+      </c>
+      <c r="E123" s="22" t="inlineStr">
+        <is>
+          <t>AIT BAYAHYA MOHAMED</t>
+        </is>
+      </c>
+      <c r="F123" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G123" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H123" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="inlineStr">
+        <is>
+          <t>06/03/2012</t>
+        </is>
+      </c>
+      <c r="J123" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K123" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DES JACINTHES</t>
+        </is>
+      </c>
+      <c r="L123" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M123" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N123" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O123" s="22" t="inlineStr"/>
+      <c r="P123" s="22" t="inlineStr"/>
+      <c r="Q123" s="22" t="inlineStr"/>
+      <c r="R123" s="23" t="inlineStr"/>
+      <c r="S123" s="22" t="inlineStr"/>
+      <c r="T123" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U123" s="22" t="inlineStr">
+        <is>
+          <t>AIT BAYAHYA</t>
+        </is>
+      </c>
+      <c r="V123" s="22" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="W123" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X123" s="22" t="inlineStr"/>
+      <c r="Y123" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z123" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>499812774</t>
+        </is>
+      </c>
+      <c r="C124" s="23" t="inlineStr">
+        <is>
+          <t>49981277400044</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="inlineStr">
+        <is>
+          <t>EVENT COOK</t>
+        </is>
+      </c>
+      <c r="E124" s="22" t="inlineStr">
+        <is>
+          <t>EVENT COOK</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I124" s="22" t="inlineStr">
+        <is>
+          <t>01/07/2007</t>
+        </is>
+      </c>
+      <c r="J124" s="22" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K124" s="22" t="inlineStr">
+        <is>
+          <t>26 RUE SAINT-MARCEL</t>
+        </is>
+      </c>
+      <c r="L124" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M124" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N124" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O124" s="22" t="n">
+        <v>280269</v>
+      </c>
+      <c r="P124" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Q124" s="22" t="inlineStr"/>
+      <c r="R124" s="23" t="inlineStr"/>
+      <c r="S124" s="22" t="inlineStr"/>
+      <c r="T124" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U124" s="22" t="inlineStr">
+        <is>
+          <t>MAURICE</t>
+        </is>
+      </c>
+      <c r="V124" s="22" t="inlineStr">
+        <is>
+          <t>Philippe, Armand</t>
+        </is>
+      </c>
+      <c r="W124" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X124" s="22" t="inlineStr">
+        <is>
+          <t>26 Rue Saint-Marcel</t>
+        </is>
+      </c>
+      <c r="Y124" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z124" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="inlineStr">
+        <is>
+          <t>999059066</t>
+        </is>
+      </c>
+      <c r="C125" s="23" t="inlineStr">
+        <is>
+          <t>99905906600012</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="inlineStr">
+        <is>
+          <t>MILADI MAHER</t>
+        </is>
+      </c>
+      <c r="E125" s="22" t="inlineStr">
+        <is>
+          <t>MILADI MAHER</t>
+        </is>
+      </c>
+      <c r="F125" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G125" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H125" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I125" s="22" t="inlineStr">
+        <is>
+          <t>25/12/2025</t>
+        </is>
+      </c>
+      <c r="J125" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K125" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE AIME DE LEMUD</t>
+        </is>
+      </c>
+      <c r="L125" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M125" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N125" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O125" s="22" t="inlineStr"/>
+      <c r="P125" s="22" t="inlineStr"/>
+      <c r="Q125" s="22" t="inlineStr"/>
+      <c r="R125" s="23" t="inlineStr"/>
+      <c r="S125" s="22" t="inlineStr"/>
+      <c r="T125" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U125" s="22" t="inlineStr">
+        <is>
+          <t>MILADI</t>
+        </is>
+      </c>
+      <c r="V125" s="22" t="inlineStr">
+        <is>
+          <t>Maher</t>
+        </is>
+      </c>
+      <c r="W125" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X125" s="22" t="inlineStr"/>
+      <c r="Y125" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z125" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="inlineStr">
+        <is>
+          <t>533671160</t>
+        </is>
+      </c>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>53367116000018</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>ZAHAF MANEL</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="inlineStr">
+        <is>
+          <t>ZAHAF MANEL</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I126" s="22" t="inlineStr">
+        <is>
+          <t>05/07/2011</t>
+        </is>
+      </c>
+      <c r="J126" s="22" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="K126" s="22" t="inlineStr">
+        <is>
+          <t>8 EN NEXIRUE</t>
+        </is>
+      </c>
+      <c r="L126" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M126" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N126" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O126" s="22" t="inlineStr"/>
+      <c r="P126" s="22" t="inlineStr"/>
+      <c r="Q126" s="22" t="inlineStr"/>
+      <c r="R126" s="23" t="inlineStr"/>
+      <c r="S126" s="22" t="inlineStr"/>
+      <c r="T126" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U126" s="22" t="inlineStr">
+        <is>
+          <t>ZAHAF</t>
+        </is>
+      </c>
+      <c r="V126" s="22" t="inlineStr">
+        <is>
+          <t>Manel</t>
+        </is>
+      </c>
+      <c r="W126" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X126" s="22" t="inlineStr"/>
+      <c r="Y126" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z126" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>792179749</t>
+        </is>
+      </c>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>79217974900017</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="inlineStr">
+        <is>
+          <t>SAVOURER L'INSTANT</t>
+        </is>
+      </c>
+      <c r="E127" s="22" t="inlineStr">
+        <is>
+          <t>SAVOURER L'INSTANT</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G127" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H127" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I127" s="22" t="inlineStr">
+        <is>
+          <t>02/04/2013</t>
+        </is>
+      </c>
+      <c r="J127" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K127" s="22" t="inlineStr">
+        <is>
+          <t>46 RUE DE PONT-A-MOUSSON</t>
+        </is>
+      </c>
+      <c r="L127" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M127" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N127" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O127" s="22" t="inlineStr"/>
+      <c r="P127" s="22" t="inlineStr"/>
+      <c r="Q127" s="22" t="inlineStr"/>
+      <c r="R127" s="23" t="inlineStr"/>
+      <c r="S127" s="22" t="inlineStr"/>
+      <c r="T127" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U127" s="22" t="inlineStr">
+        <is>
+          <t>FOLNY</t>
+        </is>
+      </c>
+      <c r="V127" s="22" t="inlineStr">
+        <is>
+          <t>Flavien</t>
+        </is>
+      </c>
+      <c r="W127" s="22" t="inlineStr">
+        <is>
+          <t>Liquidateur</t>
+        </is>
+      </c>
+      <c r="X127" s="22" t="inlineStr">
+        <is>
+          <t>6 rue Raymond Mondon</t>
+        </is>
+      </c>
+      <c r="Y127" s="23" t="inlineStr">
+        <is>
+          <t>57130</t>
+        </is>
+      </c>
+      <c r="Z127" s="22" t="inlineStr">
+        <is>
+          <t>ANCY SUR MOSELLE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z107"/>
+  <autoFilter ref="A2:Z127"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z127"/>
+  <dimension ref="A1:Z147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12514,2235 +12514,4477 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="22" t="inlineStr">
+      <c r="A108" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B108" s="23" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>995019544</t>
         </is>
       </c>
-      <c r="C108" s="23" t="inlineStr">
+      <c r="C108" s="21" t="inlineStr">
         <is>
           <t>99501954400015</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="D108" s="20" t="inlineStr">
         <is>
           <t>RGB</t>
         </is>
       </c>
-      <c r="E108" s="22" t="inlineStr">
+      <c r="E108" s="20" t="inlineStr">
         <is>
           <t>RGB</t>
         </is>
       </c>
-      <c r="F108" s="22" t="inlineStr">
+      <c r="F108" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G108" s="22" t="inlineStr">
+      <c r="G108" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H108" s="22" t="inlineStr">
+      <c r="H108" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I108" s="22" t="inlineStr">
+      <c r="I108" s="20" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="J108" s="22" t="inlineStr">
+      <c r="J108" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K108" s="22" t="inlineStr">
+      <c r="K108" s="20" t="inlineStr">
         <is>
           <t>7 B RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L108" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M108" s="22" t="inlineStr">
+      <c r="L108" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M108" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N108" s="22" t="inlineStr">
+      <c r="N108" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O108" s="22" t="inlineStr"/>
-      <c r="P108" s="22" t="inlineStr"/>
-      <c r="Q108" s="22" t="inlineStr"/>
-      <c r="R108" s="23" t="inlineStr"/>
-      <c r="S108" s="22" t="inlineStr"/>
-      <c r="T108" s="22" t="inlineStr">
+      <c r="O108" s="20" t="inlineStr"/>
+      <c r="P108" s="20" t="inlineStr"/>
+      <c r="Q108" s="20" t="inlineStr"/>
+      <c r="R108" s="21" t="inlineStr"/>
+      <c r="S108" s="20" t="inlineStr"/>
+      <c r="T108" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U108" s="22" t="inlineStr">
+      <c r="U108" s="20" t="inlineStr">
         <is>
           <t>POTIER</t>
         </is>
       </c>
-      <c r="V108" s="22" t="inlineStr">
+      <c r="V108" s="20" t="inlineStr">
         <is>
           <t>Yannis</t>
         </is>
       </c>
-      <c r="W108" s="22" t="inlineStr">
+      <c r="W108" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X108" s="22" t="inlineStr">
+      <c r="X108" s="20" t="inlineStr">
         <is>
           <t>8 rue du Faisan</t>
         </is>
       </c>
-      <c r="Y108" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z108" s="22" t="inlineStr">
+      <c r="Y108" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z108" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="22" t="inlineStr">
+      <c r="A109" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B109" s="23" t="inlineStr">
+      <c r="B109" s="21" t="inlineStr">
         <is>
           <t>849498654</t>
         </is>
       </c>
-      <c r="C109" s="23" t="inlineStr">
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>84949865400011</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
+      <c r="D109" s="20" t="inlineStr">
         <is>
           <t>BLANC &amp; NOIR LOUNGE</t>
         </is>
       </c>
-      <c r="E109" s="22" t="inlineStr">
+      <c r="E109" s="20" t="inlineStr">
         <is>
           <t>BLANC &amp; NOIR LOUNGE</t>
         </is>
       </c>
-      <c r="F109" s="22" t="inlineStr">
+      <c r="F109" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G109" s="22" t="inlineStr">
+      <c r="G109" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H109" s="22" t="inlineStr">
+      <c r="H109" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I109" s="22" t="inlineStr">
+      <c r="I109" s="20" t="inlineStr">
         <is>
           <t>27/03/2019</t>
         </is>
       </c>
-      <c r="J109" s="22" t="inlineStr">
+      <c r="J109" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K109" s="22" t="inlineStr">
+      <c r="K109" s="20" t="inlineStr">
         <is>
           <t>2 RUE HAUTE PIERRE</t>
         </is>
       </c>
-      <c r="L109" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M109" s="22" t="inlineStr">
+      <c r="L109" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M109" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N109" s="22" t="inlineStr">
+      <c r="N109" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O109" s="22" t="inlineStr"/>
-      <c r="P109" s="22" t="inlineStr"/>
-      <c r="Q109" s="22" t="inlineStr"/>
-      <c r="R109" s="23" t="inlineStr"/>
-      <c r="S109" s="22" t="inlineStr"/>
-      <c r="T109" s="22" t="inlineStr">
+      <c r="O109" s="20" t="inlineStr"/>
+      <c r="P109" s="20" t="inlineStr"/>
+      <c r="Q109" s="20" t="inlineStr"/>
+      <c r="R109" s="21" t="inlineStr"/>
+      <c r="S109" s="20" t="inlineStr"/>
+      <c r="T109" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U109" s="22" t="inlineStr">
+      <c r="U109" s="20" t="inlineStr">
         <is>
           <t>KOUADIO</t>
         </is>
       </c>
-      <c r="V109" s="22" t="inlineStr">
+      <c r="V109" s="20" t="inlineStr">
         <is>
           <t>Kotokoun, Amoin, Charlotte</t>
         </is>
       </c>
-      <c r="W109" s="22" t="inlineStr">
+      <c r="W109" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X109" s="22" t="inlineStr">
+      <c r="X109" s="20" t="inlineStr">
         <is>
           <t>15 rue Lothaire</t>
         </is>
       </c>
-      <c r="Y109" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z109" s="22" t="inlineStr">
+      <c r="Y109" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z109" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="22" t="inlineStr">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B110" s="23" t="inlineStr">
+      <c r="B110" s="21" t="inlineStr">
         <is>
           <t>807703418</t>
         </is>
       </c>
-      <c r="C110" s="23" t="inlineStr">
+      <c r="C110" s="21" t="inlineStr">
         <is>
           <t>80770341800010</t>
         </is>
       </c>
-      <c r="D110" s="22" t="inlineStr">
+      <c r="D110" s="20" t="inlineStr">
         <is>
           <t>LE PIAF</t>
         </is>
       </c>
-      <c r="E110" s="22" t="inlineStr">
+      <c r="E110" s="20" t="inlineStr">
         <is>
           <t>LE PIAF</t>
         </is>
       </c>
-      <c r="F110" s="22" t="inlineStr">
+      <c r="F110" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G110" s="22" t="inlineStr">
+      <c r="G110" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H110" s="22" t="inlineStr">
+      <c r="H110" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I110" s="22" t="inlineStr">
+      <c r="I110" s="20" t="inlineStr">
         <is>
           <t>05/11/2014</t>
         </is>
       </c>
-      <c r="J110" s="22" t="inlineStr">
+      <c r="J110" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K110" s="22" t="inlineStr">
+      <c r="K110" s="20" t="inlineStr">
         <is>
           <t>3 RUE DU GRAND CERF</t>
         </is>
       </c>
-      <c r="L110" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M110" s="22" t="inlineStr">
+      <c r="L110" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M110" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N110" s="22" t="inlineStr">
+      <c r="N110" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O110" s="22" t="inlineStr"/>
-      <c r="P110" s="22" t="inlineStr"/>
-      <c r="Q110" s="22" t="inlineStr"/>
-      <c r="R110" s="23" t="inlineStr"/>
-      <c r="S110" s="22" t="inlineStr"/>
-      <c r="T110" s="22" t="inlineStr">
+      <c r="O110" s="20" t="inlineStr"/>
+      <c r="P110" s="20" t="inlineStr"/>
+      <c r="Q110" s="20" t="inlineStr"/>
+      <c r="R110" s="21" t="inlineStr"/>
+      <c r="S110" s="20" t="inlineStr"/>
+      <c r="T110" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U110" s="22" t="inlineStr">
+      <c r="U110" s="20" t="inlineStr">
         <is>
           <t>GRIMONPON</t>
         </is>
       </c>
-      <c r="V110" s="22" t="inlineStr">
+      <c r="V110" s="20" t="inlineStr">
         <is>
           <t>Muriel</t>
         </is>
       </c>
-      <c r="W110" s="22" t="inlineStr">
+      <c r="W110" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X110" s="22" t="inlineStr">
+      <c r="X110" s="20" t="inlineStr">
         <is>
           <t>28 rue Saint-Eucaire</t>
         </is>
       </c>
-      <c r="Y110" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z110" s="22" t="inlineStr">
+      <c r="Y110" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z110" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="22" t="inlineStr">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B111" s="23" t="inlineStr">
+      <c r="B111" s="21" t="inlineStr">
         <is>
           <t>880546924</t>
         </is>
       </c>
-      <c r="C111" s="23" t="inlineStr">
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>88054692400015</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr">
+      <c r="D111" s="20" t="inlineStr">
         <is>
           <t>CTC</t>
         </is>
       </c>
-      <c r="E111" s="22" t="inlineStr">
+      <c r="E111" s="20" t="inlineStr">
         <is>
           <t>CTC</t>
         </is>
       </c>
-      <c r="F111" s="22" t="inlineStr">
+      <c r="F111" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G111" s="22" t="inlineStr">
+      <c r="G111" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H111" s="22" t="inlineStr">
+      <c r="H111" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I111" s="22" t="inlineStr">
+      <c r="I111" s="20" t="inlineStr">
         <is>
           <t>20/12/2019</t>
         </is>
       </c>
-      <c r="J111" s="22" t="inlineStr">
+      <c r="J111" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K111" s="22" t="inlineStr">
+      <c r="K111" s="20" t="inlineStr">
         <is>
           <t>19 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L111" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M111" s="22" t="inlineStr">
+      <c r="L111" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M111" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N111" s="22" t="inlineStr">
+      <c r="N111" s="20" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="O111" s="22" t="inlineStr"/>
-      <c r="P111" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q111" s="22" t="inlineStr"/>
-      <c r="R111" s="23" t="inlineStr"/>
-      <c r="S111" s="22" t="inlineStr"/>
-      <c r="T111" s="22" t="inlineStr">
+      <c r="O111" s="20" t="inlineStr"/>
+      <c r="P111" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q111" s="20" t="inlineStr"/>
+      <c r="R111" s="21" t="inlineStr"/>
+      <c r="S111" s="20" t="inlineStr"/>
+      <c r="T111" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U111" s="22" t="inlineStr">
+      <c r="U111" s="20" t="inlineStr">
         <is>
           <t>CLEMENTE</t>
         </is>
       </c>
-      <c r="V111" s="22" t="inlineStr">
+      <c r="V111" s="20" t="inlineStr">
         <is>
           <t>Virgile, Pierre, Joseph</t>
         </is>
       </c>
-      <c r="W111" s="22" t="inlineStr">
+      <c r="W111" s="20" t="inlineStr">
         <is>
           <t>Directeur général</t>
         </is>
       </c>
-      <c r="X111" s="22" t="inlineStr">
+      <c r="X111" s="20" t="inlineStr">
         <is>
           <t>83 rue Principale</t>
         </is>
       </c>
-      <c r="Y111" s="23" t="inlineStr">
+      <c r="Y111" s="21" t="inlineStr">
         <is>
           <t>57640</t>
         </is>
       </c>
-      <c r="Z111" s="22" t="inlineStr">
+      <c r="Z111" s="20" t="inlineStr">
         <is>
           <t>Servigny-les-Sainte-barbe</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="22" t="inlineStr">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B112" s="23" t="inlineStr">
+      <c r="B112" s="21" t="inlineStr">
         <is>
           <t>948268602</t>
         </is>
       </c>
-      <c r="C112" s="23" t="inlineStr">
+      <c r="C112" s="21" t="inlineStr">
         <is>
           <t>94826860200026</t>
         </is>
       </c>
-      <c r="D112" s="22" t="inlineStr">
+      <c r="D112" s="20" t="inlineStr">
         <is>
           <t>APOCALYPSE</t>
         </is>
       </c>
-      <c r="E112" s="22" t="inlineStr">
+      <c r="E112" s="20" t="inlineStr">
         <is>
           <t>APOCALYPSE</t>
         </is>
       </c>
-      <c r="F112" s="22" t="inlineStr">
+      <c r="F112" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G112" s="22" t="inlineStr">
+      <c r="G112" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H112" s="22" t="inlineStr">
+      <c r="H112" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I112" s="22" t="inlineStr">
+      <c r="I112" s="20" t="inlineStr">
         <is>
           <t>03/01/2023</t>
         </is>
       </c>
-      <c r="J112" s="22" t="inlineStr">
+      <c r="J112" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K112" s="22" t="inlineStr">
+      <c r="K112" s="20" t="inlineStr">
         <is>
           <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
         </is>
       </c>
-      <c r="L112" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M112" s="22" t="inlineStr">
+      <c r="L112" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M112" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N112" s="22" t="inlineStr">
+      <c r="N112" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O112" s="22" t="inlineStr"/>
-      <c r="P112" s="22" t="inlineStr"/>
-      <c r="Q112" s="22" t="inlineStr"/>
-      <c r="R112" s="23" t="inlineStr"/>
-      <c r="S112" s="22" t="inlineStr"/>
-      <c r="T112" s="22" t="inlineStr">
+      <c r="O112" s="20" t="inlineStr"/>
+      <c r="P112" s="20" t="inlineStr"/>
+      <c r="Q112" s="20" t="inlineStr"/>
+      <c r="R112" s="21" t="inlineStr"/>
+      <c r="S112" s="20" t="inlineStr"/>
+      <c r="T112" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U112" s="22" t="inlineStr">
+      <c r="U112" s="20" t="inlineStr">
         <is>
           <t>RRETHI</t>
         </is>
       </c>
-      <c r="V112" s="22" t="inlineStr">
+      <c r="V112" s="20" t="inlineStr">
         <is>
           <t>Marjan</t>
         </is>
       </c>
-      <c r="W112" s="22" t="inlineStr">
+      <c r="W112" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X112" s="22" t="inlineStr">
+      <c r="X112" s="20" t="inlineStr">
         <is>
           <t>22 Boulevard André Maginot</t>
         </is>
       </c>
-      <c r="Y112" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z112" s="22" t="inlineStr">
+      <c r="Y112" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z112" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="22" t="inlineStr">
+      <c r="A113" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B113" s="23" t="inlineStr">
+      <c r="B113" s="21" t="inlineStr">
         <is>
           <t>844714626</t>
         </is>
       </c>
-      <c r="C113" s="23" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>84471462600018</t>
         </is>
       </c>
-      <c r="D113" s="22" t="inlineStr">
+      <c r="D113" s="20" t="inlineStr">
         <is>
           <t>LE SAINT MARCEL - BISTROT DU PONT</t>
         </is>
       </c>
-      <c r="E113" s="22" t="inlineStr">
+      <c r="E113" s="20" t="inlineStr">
         <is>
           <t>LE SAINT MARCEL - BISTROT DU PONT</t>
         </is>
       </c>
-      <c r="F113" s="22" t="inlineStr">
+      <c r="F113" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G113" s="22" t="inlineStr">
+      <c r="G113" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H113" s="22" t="inlineStr">
+      <c r="H113" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I113" s="22" t="inlineStr">
+      <c r="I113" s="20" t="inlineStr">
         <is>
           <t>31/12/2018</t>
         </is>
       </c>
-      <c r="J113" s="22" t="inlineStr">
+      <c r="J113" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K113" s="22" t="inlineStr">
+      <c r="K113" s="20" t="inlineStr">
         <is>
           <t>1 RUE DU PONT SAINT-MARCEL</t>
         </is>
       </c>
-      <c r="L113" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M113" s="22" t="inlineStr">
+      <c r="L113" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M113" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N113" s="22" t="inlineStr">
+      <c r="N113" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O113" s="22" t="inlineStr"/>
-      <c r="P113" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q113" s="22" t="inlineStr"/>
-      <c r="R113" s="23" t="inlineStr"/>
-      <c r="S113" s="22" t="inlineStr"/>
-      <c r="T113" s="22" t="inlineStr">
+      <c r="O113" s="20" t="inlineStr"/>
+      <c r="P113" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q113" s="20" t="inlineStr"/>
+      <c r="R113" s="21" t="inlineStr"/>
+      <c r="S113" s="20" t="inlineStr"/>
+      <c r="T113" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U113" s="22" t="inlineStr">
+      <c r="U113" s="20" t="inlineStr">
         <is>
           <t>ZIMMERMANN</t>
         </is>
       </c>
-      <c r="V113" s="22" t="inlineStr">
+      <c r="V113" s="20" t="inlineStr">
         <is>
           <t>Bruno, Claude</t>
         </is>
       </c>
-      <c r="W113" s="22" t="inlineStr">
+      <c r="W113" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X113" s="22" t="inlineStr">
+      <c r="X113" s="20" t="inlineStr">
         <is>
           <t>8 rue de la Garde</t>
         </is>
       </c>
-      <c r="Y113" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z113" s="22" t="inlineStr">
+      <c r="Y113" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z113" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="inlineStr">
+      <c r="A114" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B114" s="23" t="inlineStr">
+      <c r="B114" s="21" t="inlineStr">
         <is>
           <t>832526297</t>
         </is>
       </c>
-      <c r="C114" s="23" t="inlineStr">
+      <c r="C114" s="21" t="inlineStr">
         <is>
           <t>83252629700011</t>
         </is>
       </c>
-      <c r="D114" s="22" t="inlineStr">
+      <c r="D114" s="20" t="inlineStr">
         <is>
           <t>SAHAN HALIL</t>
         </is>
       </c>
-      <c r="E114" s="22" t="inlineStr">
+      <c r="E114" s="20" t="inlineStr">
         <is>
           <t>SAHAN HALIL</t>
         </is>
       </c>
-      <c r="F114" s="22" t="inlineStr">
+      <c r="F114" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G114" s="22" t="inlineStr">
+      <c r="G114" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H114" s="22" t="inlineStr">
+      <c r="H114" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I114" s="22" t="inlineStr">
+      <c r="I114" s="20" t="inlineStr">
         <is>
           <t>11/10/2017</t>
         </is>
       </c>
-      <c r="J114" s="22" t="inlineStr">
+      <c r="J114" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K114" s="22" t="inlineStr">
+      <c r="K114" s="20" t="inlineStr">
         <is>
           <t>5 RUE DU MOULIN</t>
         </is>
       </c>
-      <c r="L114" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M114" s="22" t="inlineStr">
+      <c r="L114" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M114" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N114" s="22" t="inlineStr">
+      <c r="N114" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O114" s="22" t="inlineStr"/>
-      <c r="P114" s="22" t="inlineStr"/>
-      <c r="Q114" s="22" t="inlineStr"/>
-      <c r="R114" s="23" t="inlineStr"/>
-      <c r="S114" s="22" t="inlineStr"/>
-      <c r="T114" s="22" t="inlineStr">
+      <c r="O114" s="20" t="inlineStr"/>
+      <c r="P114" s="20" t="inlineStr"/>
+      <c r="Q114" s="20" t="inlineStr"/>
+      <c r="R114" s="21" t="inlineStr"/>
+      <c r="S114" s="20" t="inlineStr"/>
+      <c r="T114" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U114" s="22" t="inlineStr">
+      <c r="U114" s="20" t="inlineStr">
         <is>
           <t>SAHAN</t>
         </is>
       </c>
-      <c r="V114" s="22" t="inlineStr">
+      <c r="V114" s="20" t="inlineStr">
         <is>
           <t>Halil</t>
         </is>
       </c>
-      <c r="W114" s="22" t="inlineStr">
+      <c r="W114" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X114" s="22" t="inlineStr"/>
-      <c r="Y114" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z114" s="22" t="inlineStr">
+      <c r="X114" s="20" t="inlineStr"/>
+      <c r="Y114" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z114" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="22" t="inlineStr">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B115" s="23" t="inlineStr">
+      <c r="B115" s="21" t="inlineStr">
         <is>
           <t>844523316</t>
         </is>
       </c>
-      <c r="C115" s="23" t="inlineStr">
+      <c r="C115" s="21" t="inlineStr">
         <is>
           <t>84452331600017</t>
         </is>
       </c>
-      <c r="D115" s="22" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
         <is>
           <t>MC WIN</t>
         </is>
       </c>
-      <c r="E115" s="22" t="inlineStr">
+      <c r="E115" s="20" t="inlineStr">
         <is>
           <t>MC WIN</t>
         </is>
       </c>
-      <c r="F115" s="22" t="inlineStr">
+      <c r="F115" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G115" s="22" t="inlineStr">
+      <c r="G115" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H115" s="22" t="inlineStr">
+      <c r="H115" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I115" s="22" t="inlineStr">
+      <c r="I115" s="20" t="inlineStr">
         <is>
           <t>04/12/2018</t>
         </is>
       </c>
-      <c r="J115" s="22" t="inlineStr">
+      <c r="J115" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K115" s="22" t="inlineStr">
+      <c r="K115" s="20" t="inlineStr">
         <is>
           <t>10 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L115" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M115" s="22" t="inlineStr">
+      <c r="L115" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M115" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N115" s="22" t="inlineStr">
+      <c r="N115" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O115" s="22" t="inlineStr"/>
-      <c r="P115" s="22" t="inlineStr"/>
-      <c r="Q115" s="22" t="inlineStr"/>
-      <c r="R115" s="23" t="inlineStr"/>
-      <c r="S115" s="22" t="inlineStr"/>
-      <c r="T115" s="22" t="inlineStr">
+      <c r="O115" s="20" t="inlineStr"/>
+      <c r="P115" s="20" t="inlineStr"/>
+      <c r="Q115" s="20" t="inlineStr"/>
+      <c r="R115" s="21" t="inlineStr"/>
+      <c r="S115" s="20" t="inlineStr"/>
+      <c r="T115" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U115" s="22" t="inlineStr">
+      <c r="U115" s="20" t="inlineStr">
         <is>
           <t>BENHAFED</t>
         </is>
       </c>
-      <c r="V115" s="22" t="inlineStr">
+      <c r="V115" s="20" t="inlineStr">
         <is>
           <t>Adel</t>
         </is>
       </c>
-      <c r="W115" s="22" t="inlineStr">
+      <c r="W115" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X115" s="22" t="inlineStr">
+      <c r="X115" s="20" t="inlineStr">
         <is>
           <t>3 Rue de Normandie</t>
         </is>
       </c>
-      <c r="Y115" s="23" t="inlineStr">
+      <c r="Y115" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z115" s="22" t="inlineStr">
+      <c r="Z115" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="22" t="inlineStr">
+      <c r="A116" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B116" s="23" t="inlineStr">
+      <c r="B116" s="21" t="inlineStr">
         <is>
           <t>853101905</t>
         </is>
       </c>
-      <c r="C116" s="23" t="inlineStr">
+      <c r="C116" s="21" t="inlineStr">
         <is>
           <t>85310190500018</t>
         </is>
       </c>
-      <c r="D116" s="22" t="inlineStr">
+      <c r="D116" s="20" t="inlineStr">
         <is>
           <t>LES BURGERS MESSINS</t>
         </is>
       </c>
-      <c r="E116" s="22" t="inlineStr">
+      <c r="E116" s="20" t="inlineStr">
         <is>
           <t>LES BURGERS MESSINS</t>
         </is>
       </c>
-      <c r="F116" s="22" t="inlineStr">
+      <c r="F116" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G116" s="22" t="inlineStr">
+      <c r="G116" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H116" s="22" t="inlineStr">
+      <c r="H116" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I116" s="22" t="inlineStr">
+      <c r="I116" s="20" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
-      <c r="J116" s="22" t="inlineStr">
+      <c r="J116" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K116" s="22" t="inlineStr">
+      <c r="K116" s="20" t="inlineStr">
         <is>
           <t>42 RUE DES CLERCS</t>
         </is>
       </c>
-      <c r="L116" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M116" s="22" t="inlineStr">
+      <c r="L116" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M116" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N116" s="22" t="inlineStr">
+      <c r="N116" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O116" s="22" t="inlineStr"/>
-      <c r="P116" s="22" t="inlineStr"/>
-      <c r="Q116" s="22" t="inlineStr"/>
-      <c r="R116" s="23" t="inlineStr"/>
-      <c r="S116" s="22" t="inlineStr"/>
-      <c r="T116" s="22" t="inlineStr">
+      <c r="O116" s="20" t="inlineStr"/>
+      <c r="P116" s="20" t="inlineStr"/>
+      <c r="Q116" s="20" t="inlineStr"/>
+      <c r="R116" s="21" t="inlineStr"/>
+      <c r="S116" s="20" t="inlineStr"/>
+      <c r="T116" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U116" s="22" t="inlineStr">
+      <c r="U116" s="20" t="inlineStr">
         <is>
           <t>ZHU</t>
         </is>
       </c>
-      <c r="V116" s="22" t="inlineStr">
+      <c r="V116" s="20" t="inlineStr">
         <is>
           <t>Noël, Pierre</t>
         </is>
       </c>
-      <c r="W116" s="22" t="inlineStr">
+      <c r="W116" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X116" s="22" t="inlineStr">
+      <c r="X116" s="20" t="inlineStr">
         <is>
           <t>50 Avenue de l'Ile d'Amour</t>
         </is>
       </c>
-      <c r="Y116" s="23" t="inlineStr">
+      <c r="Y116" s="21" t="inlineStr">
         <is>
           <t>94170</t>
         </is>
       </c>
-      <c r="Z116" s="22" t="inlineStr">
+      <c r="Z116" s="20" t="inlineStr">
         <is>
           <t>Le Perreux-sur-Marne</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="22" t="inlineStr">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B117" s="23" t="inlineStr">
+      <c r="B117" s="21" t="inlineStr">
         <is>
           <t>988252888</t>
         </is>
       </c>
-      <c r="C117" s="23" t="inlineStr">
+      <c r="C117" s="21" t="inlineStr">
         <is>
           <t>98825288800017</t>
         </is>
       </c>
-      <c r="D117" s="22" t="inlineStr">
+      <c r="D117" s="20" t="inlineStr">
         <is>
           <t>LE TRUCK BON</t>
         </is>
       </c>
-      <c r="E117" s="22" t="inlineStr">
+      <c r="E117" s="20" t="inlineStr">
         <is>
           <t>LE TRUCK BON</t>
         </is>
       </c>
-      <c r="F117" s="22" t="inlineStr">
+      <c r="F117" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G117" s="22" t="inlineStr">
+      <c r="G117" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H117" s="22" t="inlineStr">
+      <c r="H117" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I117" s="22" t="inlineStr">
+      <c r="I117" s="20" t="inlineStr">
         <is>
           <t>16/06/2025</t>
         </is>
       </c>
-      <c r="J117" s="22" t="inlineStr">
+      <c r="J117" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K117" s="22" t="inlineStr">
+      <c r="K117" s="20" t="inlineStr">
         <is>
           <t>10 RUE DES LUPINS</t>
         </is>
       </c>
-      <c r="L117" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M117" s="22" t="inlineStr">
+      <c r="L117" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M117" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N117" s="22" t="inlineStr">
+      <c r="N117" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O117" s="22" t="inlineStr"/>
-      <c r="P117" s="22" t="inlineStr"/>
-      <c r="Q117" s="22" t="inlineStr"/>
-      <c r="R117" s="23" t="inlineStr"/>
-      <c r="S117" s="22" t="inlineStr"/>
-      <c r="T117" s="22" t="inlineStr">
+      <c r="O117" s="20" t="inlineStr"/>
+      <c r="P117" s="20" t="inlineStr"/>
+      <c r="Q117" s="20" t="inlineStr"/>
+      <c r="R117" s="21" t="inlineStr"/>
+      <c r="S117" s="20" t="inlineStr"/>
+      <c r="T117" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U117" s="22" t="inlineStr">
+      <c r="U117" s="20" t="inlineStr">
         <is>
           <t>HARPALICE</t>
         </is>
       </c>
-      <c r="V117" s="22" t="inlineStr">
+      <c r="V117" s="20" t="inlineStr">
         <is>
           <t>Béatrice, Jocelyne, Eugénie</t>
         </is>
       </c>
-      <c r="W117" s="22" t="inlineStr">
+      <c r="W117" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X117" s="22" t="inlineStr">
+      <c r="X117" s="20" t="inlineStr">
         <is>
           <t>5, rue de la Marne</t>
         </is>
       </c>
-      <c r="Y117" s="23" t="inlineStr">
+      <c r="Y117" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z117" s="22" t="inlineStr">
+      <c r="Z117" s="20" t="inlineStr">
         <is>
           <t>Le Ban-Saint-Martin</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="22" t="inlineStr">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B118" s="23" t="inlineStr">
+      <c r="B118" s="21" t="inlineStr">
         <is>
           <t>953441490</t>
         </is>
       </c>
-      <c r="C118" s="23" t="inlineStr">
+      <c r="C118" s="21" t="inlineStr">
         <is>
           <t>95344149000018</t>
         </is>
       </c>
-      <c r="D118" s="22" t="inlineStr">
+      <c r="D118" s="20" t="inlineStr">
         <is>
           <t>Manna</t>
         </is>
       </c>
-      <c r="E118" s="22" t="inlineStr">
+      <c r="E118" s="20" t="inlineStr">
         <is>
           <t>Manna</t>
         </is>
       </c>
-      <c r="F118" s="22" t="inlineStr">
+      <c r="F118" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
+      <c r="G118" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H118" s="22" t="inlineStr">
+      <c r="H118" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I118" s="22" t="inlineStr">
+      <c r="I118" s="20" t="inlineStr">
         <is>
           <t>13/06/2023</t>
         </is>
       </c>
-      <c r="J118" s="22" t="inlineStr">
+      <c r="J118" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K118" s="22" t="inlineStr">
+      <c r="K118" s="20" t="inlineStr">
         <is>
           <t>19 PLACE DES CHARRONS</t>
         </is>
       </c>
-      <c r="L118" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M118" s="22" t="inlineStr">
+      <c r="L118" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M118" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N118" s="22" t="inlineStr">
+      <c r="N118" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O118" s="22" t="inlineStr"/>
-      <c r="P118" s="22" t="inlineStr"/>
-      <c r="Q118" s="22" t="inlineStr"/>
-      <c r="R118" s="23" t="inlineStr"/>
-      <c r="S118" s="22" t="inlineStr"/>
-      <c r="T118" s="22" t="inlineStr">
+      <c r="O118" s="20" t="inlineStr"/>
+      <c r="P118" s="20" t="inlineStr"/>
+      <c r="Q118" s="20" t="inlineStr"/>
+      <c r="R118" s="21" t="inlineStr"/>
+      <c r="S118" s="20" t="inlineStr"/>
+      <c r="T118" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U118" s="22" t="inlineStr">
+      <c r="U118" s="20" t="inlineStr">
         <is>
           <t>EMHAMED MAHAMUD</t>
         </is>
       </c>
-      <c r="V118" s="22" t="inlineStr">
+      <c r="V118" s="20" t="inlineStr">
         <is>
           <t>Kamel</t>
         </is>
       </c>
-      <c r="W118" s="22" t="inlineStr">
+      <c r="W118" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X118" s="22" t="inlineStr">
+      <c r="X118" s="20" t="inlineStr">
         <is>
           <t>1 Rue de la Champagne</t>
         </is>
       </c>
-      <c r="Y118" s="23" t="inlineStr">
+      <c r="Y118" s="21" t="inlineStr">
         <is>
           <t>79200</t>
         </is>
       </c>
-      <c r="Z118" s="22" t="inlineStr">
+      <c r="Z118" s="20" t="inlineStr">
         <is>
           <t>Parthenay</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="inlineStr">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B119" s="23" t="inlineStr">
+      <c r="B119" s="21" t="inlineStr">
         <is>
           <t>925318701</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
+      <c r="C119" s="21" t="inlineStr">
         <is>
           <t>92531870100032</t>
         </is>
       </c>
-      <c r="D119" s="22" t="inlineStr">
+      <c r="D119" s="20" t="inlineStr">
         <is>
           <t>FONDER</t>
         </is>
       </c>
-      <c r="E119" s="22" t="inlineStr">
+      <c r="E119" s="20" t="inlineStr">
         <is>
           <t>FONDER</t>
         </is>
       </c>
-      <c r="F119" s="22" t="inlineStr">
+      <c r="F119" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G119" s="22" t="inlineStr">
+      <c r="G119" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H119" s="22" t="inlineStr">
+      <c r="H119" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I119" s="22" t="inlineStr">
+      <c r="I119" s="20" t="inlineStr">
         <is>
           <t>01/09/2023</t>
         </is>
       </c>
-      <c r="J119" s="22" t="inlineStr">
+      <c r="J119" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K119" s="22" t="inlineStr">
+      <c r="K119" s="20" t="inlineStr">
         <is>
           <t>4 RUE SERPENOISE</t>
         </is>
       </c>
-      <c r="L119" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M119" s="22" t="inlineStr">
+      <c r="L119" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M119" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N119" s="22" t="inlineStr">
+      <c r="N119" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O119" s="22" t="inlineStr"/>
-      <c r="P119" s="22" t="inlineStr"/>
-      <c r="Q119" s="22" t="inlineStr"/>
-      <c r="R119" s="23" t="inlineStr"/>
-      <c r="S119" s="22" t="inlineStr"/>
-      <c r="T119" s="22" t="inlineStr">
+      <c r="O119" s="20" t="inlineStr"/>
+      <c r="P119" s="20" t="inlineStr"/>
+      <c r="Q119" s="20" t="inlineStr"/>
+      <c r="R119" s="21" t="inlineStr"/>
+      <c r="S119" s="20" t="inlineStr"/>
+      <c r="T119" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U119" s="22" t="inlineStr">
+      <c r="U119" s="20" t="inlineStr">
         <is>
           <t>BEGUM</t>
         </is>
       </c>
-      <c r="V119" s="22" t="inlineStr">
+      <c r="V119" s="20" t="inlineStr">
         <is>
           <t>Fathma</t>
         </is>
       </c>
-      <c r="W119" s="22" t="inlineStr">
+      <c r="W119" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X119" s="22" t="inlineStr"/>
-      <c r="Y119" s="23" t="inlineStr">
+      <c r="X119" s="20" t="inlineStr"/>
+      <c r="Y119" s="21" t="inlineStr">
         <is>
           <t>92000</t>
         </is>
       </c>
-      <c r="Z119" s="22" t="inlineStr">
+      <c r="Z119" s="20" t="inlineStr">
         <is>
           <t>Nanterre</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="22" t="inlineStr">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B120" s="23" t="inlineStr">
+      <c r="B120" s="21" t="inlineStr">
         <is>
           <t>990366023</t>
         </is>
       </c>
-      <c r="C120" s="23" t="inlineStr">
+      <c r="C120" s="21" t="inlineStr">
         <is>
           <t>99036602300010</t>
         </is>
       </c>
-      <c r="D120" s="22" t="inlineStr">
+      <c r="D120" s="20" t="inlineStr">
         <is>
           <t>DIAMOND BURGER</t>
         </is>
       </c>
-      <c r="E120" s="22" t="inlineStr">
+      <c r="E120" s="20" t="inlineStr">
         <is>
           <t>DIAMOND BURGER</t>
         </is>
       </c>
-      <c r="F120" s="22" t="inlineStr">
+      <c r="F120" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G120" s="22" t="inlineStr">
+      <c r="G120" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H120" s="22" t="inlineStr">
+      <c r="H120" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I120" s="22" t="inlineStr">
+      <c r="I120" s="20" t="inlineStr">
         <is>
           <t>01/09/2025</t>
         </is>
       </c>
-      <c r="J120" s="22" t="inlineStr">
+      <c r="J120" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K120" s="22" t="inlineStr">
+      <c r="K120" s="20" t="inlineStr">
         <is>
           <t>5 RUE COISLIN</t>
         </is>
       </c>
-      <c r="L120" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M120" s="22" t="inlineStr">
+      <c r="L120" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M120" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N120" s="22" t="inlineStr">
+      <c r="N120" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O120" s="22" t="inlineStr"/>
-      <c r="P120" s="22" t="inlineStr"/>
-      <c r="Q120" s="22" t="inlineStr"/>
-      <c r="R120" s="23" t="inlineStr"/>
-      <c r="S120" s="22" t="inlineStr"/>
-      <c r="T120" s="22" t="inlineStr">
+      <c r="O120" s="20" t="inlineStr"/>
+      <c r="P120" s="20" t="inlineStr"/>
+      <c r="Q120" s="20" t="inlineStr"/>
+      <c r="R120" s="21" t="inlineStr"/>
+      <c r="S120" s="20" t="inlineStr"/>
+      <c r="T120" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U120" s="22" t="inlineStr">
+      <c r="U120" s="20" t="inlineStr">
         <is>
           <t>SALIH</t>
         </is>
       </c>
-      <c r="V120" s="22" t="inlineStr">
+      <c r="V120" s="20" t="inlineStr">
         <is>
           <t>Amir</t>
         </is>
       </c>
-      <c r="W120" s="22" t="inlineStr">
+      <c r="W120" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X120" s="22" t="inlineStr">
+      <c r="X120" s="20" t="inlineStr">
         <is>
           <t>24 rue du wad billy</t>
         </is>
       </c>
-      <c r="Y120" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z120" s="22" t="inlineStr">
+      <c r="Y120" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z120" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="22" t="inlineStr">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B121" s="23" t="inlineStr">
+      <c r="B121" s="21" t="inlineStr">
         <is>
           <t>941815169</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
+      <c r="C121" s="21" t="inlineStr">
         <is>
           <t>94181516900011</t>
         </is>
       </c>
-      <c r="D121" s="22" t="inlineStr">
+      <c r="D121" s="20" t="inlineStr">
         <is>
           <t>RD GROUPES</t>
         </is>
       </c>
-      <c r="E121" s="22" t="inlineStr">
+      <c r="E121" s="20" t="inlineStr">
         <is>
           <t>RD GROUPES</t>
         </is>
       </c>
-      <c r="F121" s="22" t="inlineStr">
+      <c r="F121" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G121" s="22" t="inlineStr">
+      <c r="G121" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H121" s="22" t="inlineStr">
+      <c r="H121" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I121" s="22" t="inlineStr">
+      <c r="I121" s="20" t="inlineStr">
         <is>
           <t>05/03/2025</t>
         </is>
       </c>
-      <c r="J121" s="22" t="inlineStr">
+      <c r="J121" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K121" s="22" t="inlineStr">
+      <c r="K121" s="20" t="inlineStr">
         <is>
           <t>105 AVENUE ANDRE MALRAUX</t>
         </is>
       </c>
-      <c r="L121" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M121" s="22" t="inlineStr">
+      <c r="L121" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M121" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N121" s="22" t="inlineStr">
+      <c r="N121" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O121" s="22" t="inlineStr"/>
-      <c r="P121" s="22" t="inlineStr"/>
-      <c r="Q121" s="22" t="inlineStr"/>
-      <c r="R121" s="23" t="inlineStr"/>
-      <c r="S121" s="22" t="inlineStr"/>
-      <c r="T121" s="22" t="inlineStr">
+      <c r="O121" s="20" t="inlineStr"/>
+      <c r="P121" s="20" t="inlineStr"/>
+      <c r="Q121" s="20" t="inlineStr"/>
+      <c r="R121" s="21" t="inlineStr"/>
+      <c r="S121" s="20" t="inlineStr"/>
+      <c r="T121" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U121" s="22" t="inlineStr">
+      <c r="U121" s="20" t="inlineStr">
         <is>
           <t>APREYAN</t>
         </is>
       </c>
-      <c r="V121" s="22" t="inlineStr">
+      <c r="V121" s="20" t="inlineStr">
         <is>
           <t>David</t>
         </is>
       </c>
-      <c r="W121" s="22" t="inlineStr">
+      <c r="W121" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X121" s="22" t="inlineStr">
+      <c r="X121" s="20" t="inlineStr">
         <is>
           <t>27b rue principale</t>
         </is>
       </c>
-      <c r="Y121" s="23" t="inlineStr">
+      <c r="Y121" s="21" t="inlineStr">
         <is>
           <t>57245</t>
         </is>
       </c>
-      <c r="Z121" s="22" t="inlineStr">
+      <c r="Z121" s="20" t="inlineStr">
         <is>
           <t>Jury</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B122" s="23" t="inlineStr">
+      <c r="B122" s="21" t="inlineStr">
         <is>
           <t>790606255</t>
         </is>
       </c>
-      <c r="C122" s="23" t="inlineStr">
+      <c r="C122" s="21" t="inlineStr">
         <is>
           <t>79060625500053</t>
         </is>
       </c>
-      <c r="D122" s="22" t="inlineStr">
+      <c r="D122" s="20" t="inlineStr">
         <is>
           <t>DAUSSE WELKER</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E122" s="20" t="inlineStr">
         <is>
           <t>DAUSSE WELKER</t>
         </is>
       </c>
-      <c r="F122" s="22" t="inlineStr">
+      <c r="F122" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
+      <c r="G122" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H122" s="22" t="inlineStr">
+      <c r="H122" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I122" s="22" t="inlineStr">
+      <c r="I122" s="20" t="inlineStr">
         <is>
           <t>01/01/2013</t>
         </is>
       </c>
-      <c r="J122" s="22" t="inlineStr">
+      <c r="J122" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K122" s="22" t="inlineStr">
+      <c r="K122" s="20" t="inlineStr">
         <is>
           <t>20 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="L122" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M122" s="22" t="inlineStr">
+      <c r="L122" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M122" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N122" s="22" t="inlineStr">
+      <c r="N122" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O122" s="22" t="inlineStr"/>
-      <c r="P122" s="22" t="inlineStr"/>
-      <c r="Q122" s="22" t="inlineStr"/>
-      <c r="R122" s="23" t="inlineStr"/>
-      <c r="S122" s="22" t="inlineStr"/>
-      <c r="T122" s="22" t="inlineStr">
+      <c r="O122" s="20" t="inlineStr"/>
+      <c r="P122" s="20" t="inlineStr"/>
+      <c r="Q122" s="20" t="inlineStr"/>
+      <c r="R122" s="21" t="inlineStr"/>
+      <c r="S122" s="20" t="inlineStr"/>
+      <c r="T122" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U122" s="22" t="inlineStr">
+      <c r="U122" s="20" t="inlineStr">
         <is>
           <t>HUBERTY</t>
         </is>
       </c>
-      <c r="V122" s="22" t="inlineStr">
+      <c r="V122" s="20" t="inlineStr">
         <is>
           <t>Pierre</t>
         </is>
       </c>
-      <c r="W122" s="22" t="inlineStr">
+      <c r="W122" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X122" s="22" t="inlineStr">
+      <c r="X122" s="20" t="inlineStr">
         <is>
           <t>26 Boulevard Saint-Symphorien</t>
         </is>
       </c>
-      <c r="Y122" s="23" t="inlineStr">
+      <c r="Y122" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z122" s="22" t="inlineStr">
+      <c r="Z122" s="20" t="inlineStr">
         <is>
           <t>Longeville-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="inlineStr">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B123" s="23" t="inlineStr">
+      <c r="B123" s="21" t="inlineStr">
         <is>
           <t>750091183</t>
         </is>
       </c>
-      <c r="C123" s="23" t="inlineStr">
+      <c r="C123" s="21" t="inlineStr">
         <is>
           <t>75009118300012</t>
         </is>
       </c>
-      <c r="D123" s="22" t="inlineStr">
+      <c r="D123" s="20" t="inlineStr">
         <is>
           <t>AIT BAYAHYA MOHAMED</t>
         </is>
       </c>
-      <c r="E123" s="22" t="inlineStr">
+      <c r="E123" s="20" t="inlineStr">
         <is>
           <t>AIT BAYAHYA MOHAMED</t>
         </is>
       </c>
-      <c r="F123" s="22" t="inlineStr">
+      <c r="F123" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G123" s="22" t="inlineStr">
+      <c r="G123" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H123" s="22" t="inlineStr">
+      <c r="H123" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I123" s="22" t="inlineStr">
+      <c r="I123" s="20" t="inlineStr">
         <is>
           <t>06/03/2012</t>
         </is>
       </c>
-      <c r="J123" s="22" t="inlineStr">
+      <c r="J123" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K123" s="22" t="inlineStr">
+      <c r="K123" s="20" t="inlineStr">
         <is>
           <t>1 RUE DES JACINTHES</t>
         </is>
       </c>
-      <c r="L123" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M123" s="22" t="inlineStr">
+      <c r="L123" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M123" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N123" s="22" t="inlineStr">
+      <c r="N123" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O123" s="22" t="inlineStr"/>
-      <c r="P123" s="22" t="inlineStr"/>
-      <c r="Q123" s="22" t="inlineStr"/>
-      <c r="R123" s="23" t="inlineStr"/>
-      <c r="S123" s="22" t="inlineStr"/>
-      <c r="T123" s="22" t="inlineStr">
+      <c r="O123" s="20" t="inlineStr"/>
+      <c r="P123" s="20" t="inlineStr"/>
+      <c r="Q123" s="20" t="inlineStr"/>
+      <c r="R123" s="21" t="inlineStr"/>
+      <c r="S123" s="20" t="inlineStr"/>
+      <c r="T123" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U123" s="22" t="inlineStr">
+      <c r="U123" s="20" t="inlineStr">
         <is>
           <t>AIT BAYAHYA</t>
         </is>
       </c>
-      <c r="V123" s="22" t="inlineStr">
+      <c r="V123" s="20" t="inlineStr">
         <is>
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="W123" s="22" t="inlineStr">
+      <c r="W123" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X123" s="22" t="inlineStr"/>
-      <c r="Y123" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z123" s="22" t="inlineStr">
+      <c r="X123" s="20" t="inlineStr"/>
+      <c r="Y123" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z123" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="22" t="inlineStr">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B124" s="23" t="inlineStr">
+      <c r="B124" s="21" t="inlineStr">
         <is>
           <t>499812774</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
+      <c r="C124" s="21" t="inlineStr">
         <is>
           <t>49981277400044</t>
         </is>
       </c>
-      <c r="D124" s="22" t="inlineStr">
+      <c r="D124" s="20" t="inlineStr">
         <is>
           <t>EVENT COOK</t>
         </is>
       </c>
-      <c r="E124" s="22" t="inlineStr">
+      <c r="E124" s="20" t="inlineStr">
         <is>
           <t>EVENT COOK</t>
         </is>
       </c>
-      <c r="F124" s="22" t="inlineStr">
+      <c r="F124" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G124" s="22" t="inlineStr">
+      <c r="G124" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H124" s="22" t="inlineStr">
+      <c r="H124" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I124" s="22" t="inlineStr">
+      <c r="I124" s="20" t="inlineStr">
         <is>
           <t>01/07/2007</t>
         </is>
       </c>
-      <c r="J124" s="22" t="inlineStr">
+      <c r="J124" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="K124" s="22" t="inlineStr">
+      <c r="K124" s="20" t="inlineStr">
         <is>
           <t>26 RUE SAINT-MARCEL</t>
         </is>
       </c>
-      <c r="L124" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M124" s="22" t="inlineStr">
+      <c r="L124" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M124" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N124" s="22" t="inlineStr">
+      <c r="N124" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O124" s="22" t="n">
-        <v>280269</v>
-      </c>
-      <c r="P124" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q124" s="22" t="inlineStr"/>
-      <c r="R124" s="23" t="inlineStr"/>
-      <c r="S124" s="22" t="inlineStr"/>
-      <c r="T124" s="22" t="inlineStr">
+      <c r="O124" s="20" t="inlineStr">
+        <is>
+          <t>280269</t>
+        </is>
+      </c>
+      <c r="P124" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q124" s="20" t="inlineStr"/>
+      <c r="R124" s="21" t="inlineStr"/>
+      <c r="S124" s="20" t="inlineStr"/>
+      <c r="T124" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U124" s="22" t="inlineStr">
+      <c r="U124" s="20" t="inlineStr">
         <is>
           <t>MAURICE</t>
         </is>
       </c>
-      <c r="V124" s="22" t="inlineStr">
+      <c r="V124" s="20" t="inlineStr">
         <is>
           <t>Philippe, Armand</t>
         </is>
       </c>
-      <c r="W124" s="22" t="inlineStr">
+      <c r="W124" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X124" s="22" t="inlineStr">
+      <c r="X124" s="20" t="inlineStr">
         <is>
           <t>26 Rue Saint-Marcel</t>
         </is>
       </c>
-      <c r="Y124" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z124" s="22" t="inlineStr">
+      <c r="Y124" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z124" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="22" t="inlineStr">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" s="21" t="inlineStr">
         <is>
           <t>999059066</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
+      <c r="C125" s="21" t="inlineStr">
         <is>
           <t>99905906600012</t>
         </is>
       </c>
-      <c r="D125" s="22" t="inlineStr">
+      <c r="D125" s="20" t="inlineStr">
         <is>
           <t>MILADI MAHER</t>
         </is>
       </c>
-      <c r="E125" s="22" t="inlineStr">
+      <c r="E125" s="20" t="inlineStr">
         <is>
           <t>MILADI MAHER</t>
         </is>
       </c>
-      <c r="F125" s="22" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G125" s="22" t="inlineStr">
+      <c r="G125" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H125" s="22" t="inlineStr">
+      <c r="H125" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I125" s="22" t="inlineStr">
+      <c r="I125" s="20" t="inlineStr">
         <is>
           <t>25/12/2025</t>
         </is>
       </c>
-      <c r="J125" s="22" t="inlineStr">
+      <c r="J125" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K125" s="22" t="inlineStr">
+      <c r="K125" s="20" t="inlineStr">
         <is>
           <t>16 RUE AIME DE LEMUD</t>
         </is>
       </c>
-      <c r="L125" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M125" s="22" t="inlineStr">
+      <c r="L125" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M125" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N125" s="22" t="inlineStr">
+      <c r="N125" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O125" s="22" t="inlineStr"/>
-      <c r="P125" s="22" t="inlineStr"/>
-      <c r="Q125" s="22" t="inlineStr"/>
-      <c r="R125" s="23" t="inlineStr"/>
-      <c r="S125" s="22" t="inlineStr"/>
-      <c r="T125" s="22" t="inlineStr">
+      <c r="O125" s="20" t="inlineStr"/>
+      <c r="P125" s="20" t="inlineStr"/>
+      <c r="Q125" s="20" t="inlineStr"/>
+      <c r="R125" s="21" t="inlineStr"/>
+      <c r="S125" s="20" t="inlineStr"/>
+      <c r="T125" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U125" s="22" t="inlineStr">
+      <c r="U125" s="20" t="inlineStr">
         <is>
           <t>MILADI</t>
         </is>
       </c>
-      <c r="V125" s="22" t="inlineStr">
+      <c r="V125" s="20" t="inlineStr">
         <is>
           <t>Maher</t>
         </is>
       </c>
-      <c r="W125" s="22" t="inlineStr">
+      <c r="W125" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X125" s="22" t="inlineStr"/>
-      <c r="Y125" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z125" s="22" t="inlineStr">
+      <c r="X125" s="20" t="inlineStr"/>
+      <c r="Y125" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z125" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="22" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B126" s="23" t="inlineStr">
+      <c r="B126" s="21" t="inlineStr">
         <is>
           <t>533671160</t>
         </is>
       </c>
-      <c r="C126" s="23" t="inlineStr">
+      <c r="C126" s="21" t="inlineStr">
         <is>
           <t>53367116000018</t>
         </is>
       </c>
-      <c r="D126" s="22" t="inlineStr">
+      <c r="D126" s="20" t="inlineStr">
         <is>
           <t>ZAHAF MANEL</t>
         </is>
       </c>
-      <c r="E126" s="22" t="inlineStr">
+      <c r="E126" s="20" t="inlineStr">
         <is>
           <t>ZAHAF MANEL</t>
         </is>
       </c>
-      <c r="F126" s="22" t="inlineStr">
+      <c r="F126" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
+      <c r="G126" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H126" s="22" t="inlineStr">
+      <c r="H126" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I126" s="22" t="inlineStr">
+      <c r="I126" s="20" t="inlineStr">
         <is>
           <t>05/07/2011</t>
         </is>
       </c>
-      <c r="J126" s="22" t="inlineStr">
+      <c r="J126" s="20" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="K126" s="22" t="inlineStr">
+      <c r="K126" s="20" t="inlineStr">
         <is>
           <t>8 EN NEXIRUE</t>
         </is>
       </c>
-      <c r="L126" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M126" s="22" t="inlineStr">
+      <c r="L126" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M126" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N126" s="22" t="inlineStr">
+      <c r="N126" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O126" s="22" t="inlineStr"/>
-      <c r="P126" s="22" t="inlineStr"/>
-      <c r="Q126" s="22" t="inlineStr"/>
-      <c r="R126" s="23" t="inlineStr"/>
-      <c r="S126" s="22" t="inlineStr"/>
-      <c r="T126" s="22" t="inlineStr">
+      <c r="O126" s="20" t="inlineStr"/>
+      <c r="P126" s="20" t="inlineStr"/>
+      <c r="Q126" s="20" t="inlineStr"/>
+      <c r="R126" s="21" t="inlineStr"/>
+      <c r="S126" s="20" t="inlineStr"/>
+      <c r="T126" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U126" s="22" t="inlineStr">
+      <c r="U126" s="20" t="inlineStr">
         <is>
           <t>ZAHAF</t>
         </is>
       </c>
-      <c r="V126" s="22" t="inlineStr">
+      <c r="V126" s="20" t="inlineStr">
         <is>
           <t>Manel</t>
         </is>
       </c>
-      <c r="W126" s="22" t="inlineStr">
+      <c r="W126" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X126" s="22" t="inlineStr"/>
-      <c r="Y126" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z126" s="22" t="inlineStr">
+      <c r="X126" s="20" t="inlineStr"/>
+      <c r="Y126" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z126" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="22" t="inlineStr">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B127" s="23" t="inlineStr">
+      <c r="B127" s="21" t="inlineStr">
         <is>
           <t>792179749</t>
         </is>
       </c>
-      <c r="C127" s="23" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>79217974900017</t>
         </is>
       </c>
-      <c r="D127" s="22" t="inlineStr">
+      <c r="D127" s="20" t="inlineStr">
         <is>
           <t>SAVOURER L'INSTANT</t>
         </is>
       </c>
-      <c r="E127" s="22" t="inlineStr">
+      <c r="E127" s="20" t="inlineStr">
         <is>
           <t>SAVOURER L'INSTANT</t>
         </is>
       </c>
-      <c r="F127" s="22" t="inlineStr">
+      <c r="F127" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G127" s="22" t="inlineStr">
+      <c r="G127" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H127" s="22" t="inlineStr">
+      <c r="H127" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I127" s="22" t="inlineStr">
+      <c r="I127" s="20" t="inlineStr">
         <is>
           <t>02/04/2013</t>
         </is>
       </c>
-      <c r="J127" s="22" t="inlineStr">
+      <c r="J127" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K127" s="22" t="inlineStr">
+      <c r="K127" s="20" t="inlineStr">
         <is>
           <t>46 RUE DE PONT-A-MOUSSON</t>
         </is>
       </c>
-      <c r="L127" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M127" s="22" t="inlineStr">
+      <c r="L127" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M127" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N127" s="22" t="inlineStr">
+      <c r="N127" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O127" s="22" t="inlineStr"/>
-      <c r="P127" s="22" t="inlineStr"/>
-      <c r="Q127" s="22" t="inlineStr"/>
-      <c r="R127" s="23" t="inlineStr"/>
-      <c r="S127" s="22" t="inlineStr"/>
-      <c r="T127" s="22" t="inlineStr">
+      <c r="O127" s="20" t="inlineStr"/>
+      <c r="P127" s="20" t="inlineStr"/>
+      <c r="Q127" s="20" t="inlineStr"/>
+      <c r="R127" s="21" t="inlineStr"/>
+      <c r="S127" s="20" t="inlineStr"/>
+      <c r="T127" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U127" s="22" t="inlineStr">
+      <c r="U127" s="20" t="inlineStr">
         <is>
           <t>FOLNY</t>
         </is>
       </c>
-      <c r="V127" s="22" t="inlineStr">
+      <c r="V127" s="20" t="inlineStr">
         <is>
           <t>Flavien</t>
         </is>
       </c>
-      <c r="W127" s="22" t="inlineStr">
+      <c r="W127" s="20" t="inlineStr">
         <is>
           <t>Liquidateur</t>
         </is>
       </c>
-      <c r="X127" s="22" t="inlineStr">
+      <c r="X127" s="20" t="inlineStr">
         <is>
           <t>6 rue Raymond Mondon</t>
         </is>
       </c>
-      <c r="Y127" s="23" t="inlineStr">
+      <c r="Y127" s="21" t="inlineStr">
         <is>
           <t>57130</t>
         </is>
       </c>
-      <c r="Z127" s="22" t="inlineStr">
+      <c r="Z127" s="20" t="inlineStr">
         <is>
           <t>ANCY SUR MOSELLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr">
+        <is>
+          <t>953197209</t>
+        </is>
+      </c>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>95319720900018</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="inlineStr">
+        <is>
+          <t>DELICES HOME</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>DELICES HOME</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I128" s="22" t="inlineStr">
+        <is>
+          <t>01/06/2023</t>
+        </is>
+      </c>
+      <c r="J128" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K128" s="22" t="inlineStr">
+        <is>
+          <t>3 BOULEVARD ANDRE MAGINOT</t>
+        </is>
+      </c>
+      <c r="L128" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M128" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N128" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O128" s="22" t="inlineStr"/>
+      <c r="P128" s="22" t="inlineStr"/>
+      <c r="Q128" s="22" t="inlineStr"/>
+      <c r="R128" s="23" t="inlineStr"/>
+      <c r="S128" s="22" t="inlineStr"/>
+      <c r="T128" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U128" s="22" t="inlineStr">
+        <is>
+          <t>CAMARA</t>
+        </is>
+      </c>
+      <c r="V128" s="22" t="inlineStr">
+        <is>
+          <t>Bertrand, Arthur, Hugues</t>
+        </is>
+      </c>
+      <c r="W128" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X128" s="22" t="inlineStr">
+        <is>
+          <t>3 boulevard andre maginot</t>
+        </is>
+      </c>
+      <c r="Y128" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z128" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr">
+        <is>
+          <t>921954004</t>
+        </is>
+      </c>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>92195400400013</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="inlineStr">
+        <is>
+          <t>C COOK</t>
+        </is>
+      </c>
+      <c r="E129" s="22" t="inlineStr">
+        <is>
+          <t>C COOK</t>
+        </is>
+      </c>
+      <c r="F129" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G129" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H129" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I129" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2022</t>
+        </is>
+      </c>
+      <c r="J129" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K129" s="22" t="inlineStr">
+        <is>
+          <t>15 RUE CLOVIS</t>
+        </is>
+      </c>
+      <c r="L129" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M129" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N129" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O129" s="22" t="inlineStr"/>
+      <c r="P129" s="22" t="inlineStr"/>
+      <c r="Q129" s="22" t="inlineStr"/>
+      <c r="R129" s="23" t="inlineStr"/>
+      <c r="S129" s="22" t="inlineStr"/>
+      <c r="T129" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U129" s="22" t="inlineStr">
+        <is>
+          <t>CUERONI</t>
+        </is>
+      </c>
+      <c r="V129" s="22" t="inlineStr">
+        <is>
+          <t>Cyril</t>
+        </is>
+      </c>
+      <c r="W129" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X129" s="22" t="inlineStr">
+        <is>
+          <t>15 Rue Clovis</t>
+        </is>
+      </c>
+      <c r="Y129" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z129" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="inlineStr">
+        <is>
+          <t>812240604</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>81224060400015</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>NOEL Stéphane</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>NOEL Stéphane</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I130" s="22" t="inlineStr">
+        <is>
+          <t>04/07/2015</t>
+        </is>
+      </c>
+      <c r="J130" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K130" s="22" t="inlineStr">
+        <is>
+          <t>26 RUE DE CASTELNAU</t>
+        </is>
+      </c>
+      <c r="L130" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M130" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N130" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O130" s="22" t="inlineStr"/>
+      <c r="P130" s="22" t="inlineStr"/>
+      <c r="Q130" s="22" t="inlineStr"/>
+      <c r="R130" s="23" t="inlineStr"/>
+      <c r="S130" s="22" t="inlineStr"/>
+      <c r="T130" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U130" s="22" t="inlineStr">
+        <is>
+          <t>NOEL</t>
+        </is>
+      </c>
+      <c r="V130" s="22" t="inlineStr">
+        <is>
+          <t>Stephane</t>
+        </is>
+      </c>
+      <c r="W130" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X130" s="22" t="inlineStr"/>
+      <c r="Y130" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z130" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>990408163</t>
+        </is>
+      </c>
+      <c r="C131" s="23" t="inlineStr">
+        <is>
+          <t>99040816300014</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="inlineStr">
+        <is>
+          <t>KORNE D'OR</t>
+        </is>
+      </c>
+      <c r="E131" s="22" t="inlineStr">
+        <is>
+          <t>KORNE D'OR</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G131" s="22" t="inlineStr">
+        <is>
+          <t>56.21Z</t>
+        </is>
+      </c>
+      <c r="H131" s="22" t="inlineStr">
+        <is>
+          <t>Services des traiteurs</t>
+        </is>
+      </c>
+      <c r="I131" s="22" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="J131" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K131" s="22" t="inlineStr">
+        <is>
+          <t>57 RUE AU BOIS</t>
+        </is>
+      </c>
+      <c r="L131" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M131" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N131" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O131" s="22" t="inlineStr"/>
+      <c r="P131" s="22" t="inlineStr"/>
+      <c r="Q131" s="22" t="inlineStr"/>
+      <c r="R131" s="23" t="inlineStr"/>
+      <c r="S131" s="22" t="inlineStr"/>
+      <c r="T131" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U131" s="22" t="inlineStr">
+        <is>
+          <t>BOUKHETOUTA</t>
+        </is>
+      </c>
+      <c r="V131" s="22" t="inlineStr">
+        <is>
+          <t>Fouzia</t>
+        </is>
+      </c>
+      <c r="W131" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X131" s="22" t="inlineStr">
+        <is>
+          <t>57/1 rue au bois</t>
+        </is>
+      </c>
+      <c r="Y131" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z131" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>350865697</t>
+        </is>
+      </c>
+      <c r="C132" s="23" t="inlineStr">
+        <is>
+          <t>35086569700022</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="inlineStr">
+        <is>
+          <t>STANBURY CLUB</t>
+        </is>
+      </c>
+      <c r="E132" s="22" t="inlineStr">
+        <is>
+          <t>STANBURY CLUB</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I132" s="22" t="inlineStr">
+        <is>
+          <t>30/05/1989</t>
+        </is>
+      </c>
+      <c r="J132" s="22" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="K132" s="22" t="inlineStr">
+        <is>
+          <t>22 RUE DUPONT DES LOGES</t>
+        </is>
+      </c>
+      <c r="L132" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M132" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N132" s="22" t="inlineStr">
+        <is>
+          <t>Entre 20 et 49 salariés</t>
+        </is>
+      </c>
+      <c r="O132" s="22" t="inlineStr"/>
+      <c r="P132" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q132" s="22" t="inlineStr"/>
+      <c r="R132" s="23" t="inlineStr"/>
+      <c r="S132" s="22" t="inlineStr"/>
+      <c r="T132" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U132" s="22" t="inlineStr">
+        <is>
+          <t>PAPALIA</t>
+        </is>
+      </c>
+      <c r="V132" s="22" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="W132" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X132" s="22" t="inlineStr">
+        <is>
+          <t>14 rue Marchant</t>
+        </is>
+      </c>
+      <c r="Y132" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z132" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="inlineStr">
+        <is>
+          <t>819787698</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>81978769800011</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="inlineStr">
+        <is>
+          <t>APOLLON</t>
+        </is>
+      </c>
+      <c r="E133" s="22" t="inlineStr">
+        <is>
+          <t>APOLLON</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G133" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H133" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I133" s="22" t="inlineStr">
+        <is>
+          <t>19/04/2016</t>
+        </is>
+      </c>
+      <c r="J133" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K133" s="22" t="inlineStr">
+        <is>
+          <t>2 B PLACE JEANNE D'ARC</t>
+        </is>
+      </c>
+      <c r="L133" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M133" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N133" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O133" s="22" t="inlineStr"/>
+      <c r="P133" s="22" t="inlineStr"/>
+      <c r="Q133" s="22" t="inlineStr"/>
+      <c r="R133" s="23" t="inlineStr"/>
+      <c r="S133" s="22" t="inlineStr"/>
+      <c r="T133" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U133" s="22" t="inlineStr">
+        <is>
+          <t>ANSALONE</t>
+        </is>
+      </c>
+      <c r="V133" s="22" t="inlineStr">
+        <is>
+          <t>Franck, Sabino</t>
+        </is>
+      </c>
+      <c r="W133" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X133" s="22" t="inlineStr">
+        <is>
+          <t>2 rue Glatigny</t>
+        </is>
+      </c>
+      <c r="Y133" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z133" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="inlineStr">
+        <is>
+          <t>994446359</t>
+        </is>
+      </c>
+      <c r="C134" s="23" t="inlineStr">
+        <is>
+          <t>99444635900014</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="inlineStr">
+        <is>
+          <t>MBL SOCIETY</t>
+        </is>
+      </c>
+      <c r="E134" s="22" t="inlineStr">
+        <is>
+          <t>MBL SOCIETY</t>
+        </is>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I134" s="22" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="J134" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K134" s="22" t="inlineStr">
+        <is>
+          <t>39 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L134" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M134" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N134" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O134" s="22" t="inlineStr"/>
+      <c r="P134" s="22" t="inlineStr"/>
+      <c r="Q134" s="22" t="inlineStr"/>
+      <c r="R134" s="23" t="inlineStr"/>
+      <c r="S134" s="22" t="inlineStr"/>
+      <c r="T134" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U134" s="22" t="inlineStr">
+        <is>
+          <t>USAI</t>
+        </is>
+      </c>
+      <c r="V134" s="22" t="inlineStr">
+        <is>
+          <t>Lennie</t>
+        </is>
+      </c>
+      <c r="W134" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X134" s="22" t="inlineStr">
+        <is>
+          <t>39, place de chambre</t>
+        </is>
+      </c>
+      <c r="Y134" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z134" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="inlineStr">
+        <is>
+          <t>932948748</t>
+        </is>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>93294874800011</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="inlineStr">
+        <is>
+          <t>LIL' &amp; GO'</t>
+        </is>
+      </c>
+      <c r="E135" s="22" t="inlineStr">
+        <is>
+          <t>LIL' &amp; GO'</t>
+        </is>
+      </c>
+      <c r="F135" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G135" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H135" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I135" s="22" t="inlineStr">
+        <is>
+          <t>06/09/2024</t>
+        </is>
+      </c>
+      <c r="J135" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K135" s="22" t="inlineStr">
+        <is>
+          <t>34 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L135" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M135" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N135" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O135" s="22" t="inlineStr"/>
+      <c r="P135" s="22" t="inlineStr"/>
+      <c r="Q135" s="22" t="inlineStr"/>
+      <c r="R135" s="23" t="inlineStr"/>
+      <c r="S135" s="22" t="inlineStr"/>
+      <c r="T135" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U135" s="22" t="inlineStr">
+        <is>
+          <t>MUNKA</t>
+        </is>
+      </c>
+      <c r="V135" s="22" t="inlineStr">
+        <is>
+          <t>Elise, Adeline, Marie</t>
+        </is>
+      </c>
+      <c r="W135" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X135" s="22" t="inlineStr">
+        <is>
+          <t>18, rue de bouteiller</t>
+        </is>
+      </c>
+      <c r="Y135" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z135" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="inlineStr">
+        <is>
+          <t>400782892</t>
+        </is>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>40078289200048</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>DU PALAIS</t>
+        </is>
+      </c>
+      <c r="E136" s="22" t="inlineStr">
+        <is>
+          <t>DU PALAIS</t>
+        </is>
+      </c>
+      <c r="F136" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G136" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I136" s="22" t="inlineStr">
+        <is>
+          <t>01/05/1995</t>
+        </is>
+      </c>
+      <c r="J136" s="22" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="K136" s="22" t="inlineStr">
+        <is>
+          <t>24 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L136" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M136" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N136" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O136" s="22" t="n">
+        <v>822074</v>
+      </c>
+      <c r="P136" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q136" s="22" t="inlineStr"/>
+      <c r="R136" s="23" t="inlineStr"/>
+      <c r="S136" s="22" t="inlineStr"/>
+      <c r="T136" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U136" s="22" t="inlineStr">
+        <is>
+          <t>PJEVCEVIC</t>
+        </is>
+      </c>
+      <c r="V136" s="22" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="W136" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X136" s="22" t="inlineStr">
+        <is>
+          <t>5 place du général de gaulle</t>
+        </is>
+      </c>
+      <c r="Y136" s="23" t="inlineStr">
+        <is>
+          <t>57155</t>
+        </is>
+      </c>
+      <c r="Z136" s="22" t="inlineStr">
+        <is>
+          <t>Marly</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B137" s="23" t="inlineStr">
+        <is>
+          <t>981166085</t>
+        </is>
+      </c>
+      <c r="C137" s="23" t="inlineStr">
+        <is>
+          <t>98116608500010</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="inlineStr">
+        <is>
+          <t>RED BARREL</t>
+        </is>
+      </c>
+      <c r="E137" s="22" t="inlineStr">
+        <is>
+          <t>RED BARREL</t>
+        </is>
+      </c>
+      <c r="F137" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G137" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H137" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I137" s="22" t="inlineStr">
+        <is>
+          <t>31/08/2023</t>
+        </is>
+      </c>
+      <c r="J137" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K137" s="22" t="inlineStr">
+        <is>
+          <t>19 AVENUE ROBERT SCHUMAN</t>
+        </is>
+      </c>
+      <c r="L137" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M137" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N137" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O137" s="22" t="inlineStr"/>
+      <c r="P137" s="22" t="inlineStr"/>
+      <c r="Q137" s="22" t="inlineStr"/>
+      <c r="R137" s="23" t="inlineStr"/>
+      <c r="S137" s="22" t="inlineStr"/>
+      <c r="T137" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U137" s="22" t="inlineStr">
+        <is>
+          <t>BAUDE</t>
+        </is>
+      </c>
+      <c r="V137" s="22" t="inlineStr">
+        <is>
+          <t>Jérémy, Marc, Georges</t>
+        </is>
+      </c>
+      <c r="W137" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X137" s="22" t="inlineStr">
+        <is>
+          <t>4 rue du maitre échevin</t>
+        </is>
+      </c>
+      <c r="Y137" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z137" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>881776280</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>88177628000011</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>MUPI</t>
+        </is>
+      </c>
+      <c r="E138" s="22" t="inlineStr">
+        <is>
+          <t>MUPI</t>
+        </is>
+      </c>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G138" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H138" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I138" s="22" t="inlineStr">
+        <is>
+          <t>19/02/2020</t>
+        </is>
+      </c>
+      <c r="J138" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K138" s="22" t="inlineStr">
+        <is>
+          <t>53 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L138" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M138" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N138" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O138" s="22" t="inlineStr"/>
+      <c r="P138" s="22" t="inlineStr"/>
+      <c r="Q138" s="22" t="inlineStr"/>
+      <c r="R138" s="23" t="inlineStr"/>
+      <c r="S138" s="22" t="inlineStr"/>
+      <c r="T138" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U138" s="22" t="inlineStr">
+        <is>
+          <t>MULLER</t>
+        </is>
+      </c>
+      <c r="V138" s="22" t="inlineStr">
+        <is>
+          <t>Stéphane</t>
+        </is>
+      </c>
+      <c r="W138" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X138" s="22" t="inlineStr">
+        <is>
+          <t>13 rue des Huiliers</t>
+        </is>
+      </c>
+      <c r="Y138" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z138" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B139" s="23" t="inlineStr">
+        <is>
+          <t>800477713</t>
+        </is>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>80047771300013</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="inlineStr">
+        <is>
+          <t>LE PETIT BISTROT</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="inlineStr">
+        <is>
+          <t>LE PETIT BISTROT</t>
+        </is>
+      </c>
+      <c r="F139" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G139" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H139" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I139" s="22" t="inlineStr">
+        <is>
+          <t>15/02/2014</t>
+        </is>
+      </c>
+      <c r="J139" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K139" s="22" t="inlineStr">
+        <is>
+          <t>22 BOULEVARD ANDRE MAGINOT</t>
+        </is>
+      </c>
+      <c r="L139" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M139" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N139" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O139" s="22" t="inlineStr"/>
+      <c r="P139" s="22" t="inlineStr"/>
+      <c r="Q139" s="22" t="inlineStr"/>
+      <c r="R139" s="23" t="inlineStr"/>
+      <c r="S139" s="22" t="inlineStr"/>
+      <c r="T139" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U139" s="22" t="inlineStr">
+        <is>
+          <t>ALLALI</t>
+        </is>
+      </c>
+      <c r="V139" s="22" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="W139" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X139" s="22" t="inlineStr">
+        <is>
+          <t>10 rue Dupont des Loges</t>
+        </is>
+      </c>
+      <c r="Y139" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z139" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>979036894</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>97903689400017</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="inlineStr">
+        <is>
+          <t>THE PARTING GLASS</t>
+        </is>
+      </c>
+      <c r="E140" s="22" t="inlineStr">
+        <is>
+          <t>THE PARTING GLASS</t>
+        </is>
+      </c>
+      <c r="F140" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H140" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I140" s="22" t="inlineStr">
+        <is>
+          <t>31/08/2023</t>
+        </is>
+      </c>
+      <c r="J140" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K140" s="22" t="inlineStr">
+        <is>
+          <t>27 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L140" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M140" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N140" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O140" s="22" t="inlineStr"/>
+      <c r="P140" s="22" t="inlineStr"/>
+      <c r="Q140" s="22" t="inlineStr"/>
+      <c r="R140" s="23" t="inlineStr"/>
+      <c r="S140" s="22" t="inlineStr"/>
+      <c r="T140" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U140" s="22" t="inlineStr">
+        <is>
+          <t>LANG</t>
+        </is>
+      </c>
+      <c r="V140" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas, Ewen, Guillaume</t>
+        </is>
+      </c>
+      <c r="W140" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X140" s="22" t="inlineStr"/>
+      <c r="Y140" s="23" t="inlineStr"/>
+      <c r="Z140" s="22" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B141" s="23" t="inlineStr">
+        <is>
+          <t>431215516</t>
+        </is>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t>43121551600011</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="inlineStr">
+        <is>
+          <t>LA VILLE DE CASA</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>LA VILLE DE CASA</t>
+        </is>
+      </c>
+      <c r="F141" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G141" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I141" s="22" t="inlineStr">
+        <is>
+          <t>06/04/2000</t>
+        </is>
+      </c>
+      <c r="J141" s="22" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="K141" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE MAZELLE</t>
+        </is>
+      </c>
+      <c r="L141" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M141" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N141" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O141" s="22" t="inlineStr"/>
+      <c r="P141" s="22" t="inlineStr"/>
+      <c r="Q141" s="22" t="inlineStr"/>
+      <c r="R141" s="23" t="inlineStr"/>
+      <c r="S141" s="22" t="inlineStr"/>
+      <c r="T141" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U141" s="22" t="inlineStr">
+        <is>
+          <t>EL AMRI</t>
+        </is>
+      </c>
+      <c r="V141" s="22" t="inlineStr">
+        <is>
+          <t>Abdallah</t>
+        </is>
+      </c>
+      <c r="W141" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X141" s="22" t="inlineStr">
+        <is>
+          <t>8 boulevard Serot</t>
+        </is>
+      </c>
+      <c r="Y141" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z141" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B142" s="23" t="inlineStr">
+        <is>
+          <t>944744200</t>
+        </is>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>94474420000014</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>METZZARELLA</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>METZZARELLA</t>
+        </is>
+      </c>
+      <c r="F142" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G142" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H142" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I142" s="22" t="inlineStr">
+        <is>
+          <t>02/05/2025</t>
+        </is>
+      </c>
+      <c r="J142" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K142" s="22" t="inlineStr">
+        <is>
+          <t>41 RUE DES ALLEMANDS</t>
+        </is>
+      </c>
+      <c r="L142" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M142" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N142" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O142" s="22" t="inlineStr"/>
+      <c r="P142" s="22" t="inlineStr"/>
+      <c r="Q142" s="22" t="inlineStr"/>
+      <c r="R142" s="23" t="inlineStr"/>
+      <c r="S142" s="22" t="inlineStr"/>
+      <c r="T142" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U142" s="22" t="inlineStr">
+        <is>
+          <t>LHIOUI</t>
+        </is>
+      </c>
+      <c r="V142" s="22" t="inlineStr">
+        <is>
+          <t>Ramzi</t>
+        </is>
+      </c>
+      <c r="W142" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X142" s="22" t="inlineStr">
+        <is>
+          <t>02 rue du wad billy</t>
+        </is>
+      </c>
+      <c r="Y142" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z142" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B143" s="23" t="inlineStr">
+        <is>
+          <t>351052949</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>35105294900010</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="inlineStr">
+        <is>
+          <t>ITALREST</t>
+        </is>
+      </c>
+      <c r="E143" s="22" t="inlineStr">
+        <is>
+          <t>ITALREST</t>
+        </is>
+      </c>
+      <c r="F143" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G143" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H143" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I143" s="22" t="inlineStr">
+        <is>
+          <t>30/05/1989</t>
+        </is>
+      </c>
+      <c r="J143" s="22" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="K143" s="22" t="inlineStr">
+        <is>
+          <t>18 PLACE SAINT-JACQUES</t>
+        </is>
+      </c>
+      <c r="L143" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M143" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N143" s="22" t="inlineStr">
+        <is>
+          <t>Entre 20 et 49 salariés</t>
+        </is>
+      </c>
+      <c r="O143" s="22" t="n">
+        <v>1704665</v>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q143" s="22" t="inlineStr"/>
+      <c r="R143" s="23" t="inlineStr"/>
+      <c r="S143" s="22" t="inlineStr"/>
+      <c r="T143" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U143" s="22" t="inlineStr">
+        <is>
+          <t>SCIGLIANO</t>
+        </is>
+      </c>
+      <c r="V143" s="22" t="inlineStr">
+        <is>
+          <t>Marcello</t>
+        </is>
+      </c>
+      <c r="W143" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X143" s="22" t="inlineStr">
+        <is>
+          <t>38 rue Dupont des Loges</t>
+        </is>
+      </c>
+      <c r="Y143" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z143" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>930385398</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>93038539800019</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>L'HEDONISTE</t>
+        </is>
+      </c>
+      <c r="E144" s="22" t="inlineStr">
+        <is>
+          <t>L'HEDONISTE</t>
+        </is>
+      </c>
+      <c r="F144" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G144" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H144" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I144" s="22" t="inlineStr">
+        <is>
+          <t>14/06/2024</t>
+        </is>
+      </c>
+      <c r="J144" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K144" s="22" t="inlineStr">
+        <is>
+          <t>23 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L144" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M144" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N144" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O144" s="22" t="inlineStr"/>
+      <c r="P144" s="22" t="inlineStr"/>
+      <c r="Q144" s="22" t="inlineStr"/>
+      <c r="R144" s="23" t="inlineStr"/>
+      <c r="S144" s="22" t="inlineStr"/>
+      <c r="T144" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U144" s="22" t="inlineStr">
+        <is>
+          <t>SIMON</t>
+        </is>
+      </c>
+      <c r="V144" s="22" t="inlineStr">
+        <is>
+          <t>Bastien, Cris, Ian</t>
+        </is>
+      </c>
+      <c r="W144" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X144" s="22" t="inlineStr">
+        <is>
+          <t>43, rue Maurice Ravel</t>
+        </is>
+      </c>
+      <c r="Y144" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z144" s="22" t="inlineStr">
+        <is>
+          <t>Woippy</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B145" s="23" t="inlineStr">
+        <is>
+          <t>979422748</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>97942274800025</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="inlineStr">
+        <is>
+          <t>Petit bamboo</t>
+        </is>
+      </c>
+      <c r="E145" s="22" t="inlineStr">
+        <is>
+          <t>Petit bamboo</t>
+        </is>
+      </c>
+      <c r="F145" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G145" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H145" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I145" s="22" t="inlineStr">
+        <is>
+          <t>25/08/2023</t>
+        </is>
+      </c>
+      <c r="J145" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K145" s="22" t="inlineStr">
+        <is>
+          <t>11 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L145" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M145" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N145" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O145" s="22" t="inlineStr"/>
+      <c r="P145" s="22" t="inlineStr"/>
+      <c r="Q145" s="22" t="inlineStr"/>
+      <c r="R145" s="23" t="inlineStr"/>
+      <c r="S145" s="22" t="inlineStr"/>
+      <c r="T145" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U145" s="22" t="inlineStr">
+        <is>
+          <t>BAI</t>
+        </is>
+      </c>
+      <c r="V145" s="22" t="inlineStr">
+        <is>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="W145" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X145" s="22" t="inlineStr">
+        <is>
+          <t>72 cours de la libération et du général de gaulle</t>
+        </is>
+      </c>
+      <c r="Y145" s="23" t="inlineStr">
+        <is>
+          <t>38100</t>
+        </is>
+      </c>
+      <c r="Z145" s="22" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>810501825</t>
+        </is>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>81050182500022</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="inlineStr">
+        <is>
+          <t>JDC 33 QFX</t>
+        </is>
+      </c>
+      <c r="E146" s="22" t="inlineStr">
+        <is>
+          <t>JDC 33 QFX</t>
+        </is>
+      </c>
+      <c r="F146" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G146" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H146" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I146" s="22" t="inlineStr">
+        <is>
+          <t>27/03/2015</t>
+        </is>
+      </c>
+      <c r="J146" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K146" s="22" t="inlineStr">
+        <is>
+          <t>33 QUAI FELIX MARECHAL</t>
+        </is>
+      </c>
+      <c r="L146" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M146" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N146" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O146" s="22" t="inlineStr"/>
+      <c r="P146" s="22" t="inlineStr"/>
+      <c r="Q146" s="22" t="inlineStr"/>
+      <c r="R146" s="23" t="inlineStr"/>
+      <c r="S146" s="22" t="inlineStr"/>
+      <c r="T146" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U146" s="22" t="inlineStr">
+        <is>
+          <t>NEVEU</t>
+        </is>
+      </c>
+      <c r="V146" s="22" t="inlineStr">
+        <is>
+          <t>Alexandre, Hervé, Fabien</t>
+        </is>
+      </c>
+      <c r="W146" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X146" s="22" t="inlineStr">
+        <is>
+          <t>8 rue Amiral Varney</t>
+        </is>
+      </c>
+      <c r="Y146" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z146" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B147" s="23" t="inlineStr">
+        <is>
+          <t>431503341</t>
+        </is>
+      </c>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>43150334100015</t>
+        </is>
+      </c>
+      <c r="D147" s="22" t="inlineStr">
+        <is>
+          <t>MAHAL</t>
+        </is>
+      </c>
+      <c r="E147" s="22" t="inlineStr">
+        <is>
+          <t>MAHAL</t>
+        </is>
+      </c>
+      <c r="F147" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G147" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H147" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I147" s="22" t="inlineStr">
+        <is>
+          <t>30/04/2000</t>
+        </is>
+      </c>
+      <c r="J147" s="22" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="K147" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE DES JARDINS</t>
+        </is>
+      </c>
+      <c r="L147" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M147" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N147" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O147" s="22" t="inlineStr"/>
+      <c r="P147" s="22" t="inlineStr"/>
+      <c r="Q147" s="22" t="inlineStr"/>
+      <c r="R147" s="23" t="inlineStr"/>
+      <c r="S147" s="22" t="inlineStr"/>
+      <c r="T147" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U147" s="22" t="inlineStr">
+        <is>
+          <t>RAVIKUMAR</t>
+        </is>
+      </c>
+      <c r="V147" s="22" t="inlineStr">
+        <is>
+          <t>Kanapathipillah</t>
+        </is>
+      </c>
+      <c r="W147" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X147" s="22" t="inlineStr">
+        <is>
+          <t>60 rue Madame Carre de Malberg</t>
+        </is>
+      </c>
+      <c r="Y147" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z147" s="22" t="inlineStr">
+        <is>
+          <t>Lorry-les-Metz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z127"/>
+  <autoFilter ref="A2:Z147"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z147"/>
+  <dimension ref="A1:Z167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14750,2241 +14750,4485 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="22" t="inlineStr">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B128" s="23" t="inlineStr">
+      <c r="B128" s="21" t="inlineStr">
         <is>
           <t>953197209</t>
         </is>
       </c>
-      <c r="C128" s="23" t="inlineStr">
+      <c r="C128" s="21" t="inlineStr">
         <is>
           <t>95319720900018</t>
         </is>
       </c>
-      <c r="D128" s="22" t="inlineStr">
+      <c r="D128" s="20" t="inlineStr">
         <is>
           <t>DELICES HOME</t>
         </is>
       </c>
-      <c r="E128" s="22" t="inlineStr">
+      <c r="E128" s="20" t="inlineStr">
         <is>
           <t>DELICES HOME</t>
         </is>
       </c>
-      <c r="F128" s="22" t="inlineStr">
+      <c r="F128" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G128" s="22" t="inlineStr">
+      <c r="G128" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H128" s="22" t="inlineStr">
+      <c r="H128" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I128" s="22" t="inlineStr">
+      <c r="I128" s="20" t="inlineStr">
         <is>
           <t>01/06/2023</t>
         </is>
       </c>
-      <c r="J128" s="22" t="inlineStr">
+      <c r="J128" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K128" s="22" t="inlineStr">
+      <c r="K128" s="20" t="inlineStr">
         <is>
           <t>3 BOULEVARD ANDRE MAGINOT</t>
         </is>
       </c>
-      <c r="L128" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M128" s="22" t="inlineStr">
+      <c r="L128" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M128" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N128" s="22" t="inlineStr">
+      <c r="N128" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O128" s="22" t="inlineStr"/>
-      <c r="P128" s="22" t="inlineStr"/>
-      <c r="Q128" s="22" t="inlineStr"/>
-      <c r="R128" s="23" t="inlineStr"/>
-      <c r="S128" s="22" t="inlineStr"/>
-      <c r="T128" s="22" t="inlineStr">
+      <c r="O128" s="20" t="inlineStr"/>
+      <c r="P128" s="20" t="inlineStr"/>
+      <c r="Q128" s="20" t="inlineStr"/>
+      <c r="R128" s="21" t="inlineStr"/>
+      <c r="S128" s="20" t="inlineStr"/>
+      <c r="T128" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U128" s="22" t="inlineStr">
+      <c r="U128" s="20" t="inlineStr">
         <is>
           <t>CAMARA</t>
         </is>
       </c>
-      <c r="V128" s="22" t="inlineStr">
+      <c r="V128" s="20" t="inlineStr">
         <is>
           <t>Bertrand, Arthur, Hugues</t>
         </is>
       </c>
-      <c r="W128" s="22" t="inlineStr">
+      <c r="W128" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X128" s="22" t="inlineStr">
+      <c r="X128" s="20" t="inlineStr">
         <is>
           <t>3 boulevard andre maginot</t>
         </is>
       </c>
-      <c r="Y128" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z128" s="22" t="inlineStr">
+      <c r="Y128" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z128" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="22" t="inlineStr">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B129" s="23" t="inlineStr">
+      <c r="B129" s="21" t="inlineStr">
         <is>
           <t>921954004</t>
         </is>
       </c>
-      <c r="C129" s="23" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>92195400400013</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr">
+      <c r="D129" s="20" t="inlineStr">
         <is>
           <t>C COOK</t>
         </is>
       </c>
-      <c r="E129" s="22" t="inlineStr">
+      <c r="E129" s="20" t="inlineStr">
         <is>
           <t>C COOK</t>
         </is>
       </c>
-      <c r="F129" s="22" t="inlineStr">
+      <c r="F129" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G129" s="22" t="inlineStr">
+      <c r="G129" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H129" s="22" t="inlineStr">
+      <c r="H129" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I129" s="22" t="inlineStr">
+      <c r="I129" s="20" t="inlineStr">
         <is>
           <t>01/12/2022</t>
         </is>
       </c>
-      <c r="J129" s="22" t="inlineStr">
+      <c r="J129" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K129" s="22" t="inlineStr">
+      <c r="K129" s="20" t="inlineStr">
         <is>
           <t>15 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="L129" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M129" s="22" t="inlineStr">
+      <c r="L129" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M129" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N129" s="22" t="inlineStr">
+      <c r="N129" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O129" s="22" t="inlineStr"/>
-      <c r="P129" s="22" t="inlineStr"/>
-      <c r="Q129" s="22" t="inlineStr"/>
-      <c r="R129" s="23" t="inlineStr"/>
-      <c r="S129" s="22" t="inlineStr"/>
-      <c r="T129" s="22" t="inlineStr">
+      <c r="O129" s="20" t="inlineStr"/>
+      <c r="P129" s="20" t="inlineStr"/>
+      <c r="Q129" s="20" t="inlineStr"/>
+      <c r="R129" s="21" t="inlineStr"/>
+      <c r="S129" s="20" t="inlineStr"/>
+      <c r="T129" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U129" s="22" t="inlineStr">
+      <c r="U129" s="20" t="inlineStr">
         <is>
           <t>CUERONI</t>
         </is>
       </c>
-      <c r="V129" s="22" t="inlineStr">
+      <c r="V129" s="20" t="inlineStr">
         <is>
           <t>Cyril</t>
         </is>
       </c>
-      <c r="W129" s="22" t="inlineStr">
+      <c r="W129" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X129" s="22" t="inlineStr">
+      <c r="X129" s="20" t="inlineStr">
         <is>
           <t>15 Rue Clovis</t>
         </is>
       </c>
-      <c r="Y129" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z129" s="22" t="inlineStr">
+      <c r="Y129" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z129" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="22" t="inlineStr">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B130" s="23" t="inlineStr">
+      <c r="B130" s="21" t="inlineStr">
         <is>
           <t>812240604</t>
         </is>
       </c>
-      <c r="C130" s="23" t="inlineStr">
+      <c r="C130" s="21" t="inlineStr">
         <is>
           <t>81224060400015</t>
         </is>
       </c>
-      <c r="D130" s="22" t="inlineStr">
+      <c r="D130" s="20" t="inlineStr">
         <is>
           <t>NOEL Stéphane</t>
         </is>
       </c>
-      <c r="E130" s="22" t="inlineStr">
+      <c r="E130" s="20" t="inlineStr">
         <is>
           <t>NOEL Stéphane</t>
         </is>
       </c>
-      <c r="F130" s="22" t="inlineStr">
+      <c r="F130" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G130" s="22" t="inlineStr">
+      <c r="G130" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H130" s="22" t="inlineStr">
+      <c r="H130" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I130" s="22" t="inlineStr">
+      <c r="I130" s="20" t="inlineStr">
         <is>
           <t>04/07/2015</t>
         </is>
       </c>
-      <c r="J130" s="22" t="inlineStr">
+      <c r="J130" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K130" s="22" t="inlineStr">
+      <c r="K130" s="20" t="inlineStr">
         <is>
           <t>26 RUE DE CASTELNAU</t>
         </is>
       </c>
-      <c r="L130" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M130" s="22" t="inlineStr">
+      <c r="L130" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M130" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N130" s="22" t="inlineStr">
+      <c r="N130" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O130" s="22" t="inlineStr"/>
-      <c r="P130" s="22" t="inlineStr"/>
-      <c r="Q130" s="22" t="inlineStr"/>
-      <c r="R130" s="23" t="inlineStr"/>
-      <c r="S130" s="22" t="inlineStr"/>
-      <c r="T130" s="22" t="inlineStr">
+      <c r="O130" s="20" t="inlineStr"/>
+      <c r="P130" s="20" t="inlineStr"/>
+      <c r="Q130" s="20" t="inlineStr"/>
+      <c r="R130" s="21" t="inlineStr"/>
+      <c r="S130" s="20" t="inlineStr"/>
+      <c r="T130" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U130" s="22" t="inlineStr">
+      <c r="U130" s="20" t="inlineStr">
         <is>
           <t>NOEL</t>
         </is>
       </c>
-      <c r="V130" s="22" t="inlineStr">
+      <c r="V130" s="20" t="inlineStr">
         <is>
           <t>Stephane</t>
         </is>
       </c>
-      <c r="W130" s="22" t="inlineStr">
+      <c r="W130" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X130" s="22" t="inlineStr"/>
-      <c r="Y130" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z130" s="22" t="inlineStr">
+      <c r="X130" s="20" t="inlineStr"/>
+      <c r="Y130" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z130" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="22" t="inlineStr">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B131" s="23" t="inlineStr">
+      <c r="B131" s="21" t="inlineStr">
         <is>
           <t>990408163</t>
         </is>
       </c>
-      <c r="C131" s="23" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>99040816300014</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr">
+      <c r="D131" s="20" t="inlineStr">
         <is>
           <t>KORNE D'OR</t>
         </is>
       </c>
-      <c r="E131" s="22" t="inlineStr">
+      <c r="E131" s="20" t="inlineStr">
         <is>
           <t>KORNE D'OR</t>
         </is>
       </c>
-      <c r="F131" s="22" t="inlineStr">
+      <c r="F131" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G131" s="22" t="inlineStr">
+      <c r="G131" s="20" t="inlineStr">
         <is>
           <t>56.21Z</t>
         </is>
       </c>
-      <c r="H131" s="22" t="inlineStr">
+      <c r="H131" s="20" t="inlineStr">
         <is>
           <t>Services des traiteurs</t>
         </is>
       </c>
-      <c r="I131" s="22" t="inlineStr">
+      <c r="I131" s="20" t="inlineStr">
         <is>
           <t>22/07/2025</t>
         </is>
       </c>
-      <c r="J131" s="22" t="inlineStr">
+      <c r="J131" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K131" s="22" t="inlineStr">
+      <c r="K131" s="20" t="inlineStr">
         <is>
           <t>57 RUE AU BOIS</t>
         </is>
       </c>
-      <c r="L131" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M131" s="22" t="inlineStr">
+      <c r="L131" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M131" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N131" s="22" t="inlineStr">
+      <c r="N131" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O131" s="22" t="inlineStr"/>
-      <c r="P131" s="22" t="inlineStr"/>
-      <c r="Q131" s="22" t="inlineStr"/>
-      <c r="R131" s="23" t="inlineStr"/>
-      <c r="S131" s="22" t="inlineStr"/>
-      <c r="T131" s="22" t="inlineStr">
+      <c r="O131" s="20" t="inlineStr"/>
+      <c r="P131" s="20" t="inlineStr"/>
+      <c r="Q131" s="20" t="inlineStr"/>
+      <c r="R131" s="21" t="inlineStr"/>
+      <c r="S131" s="20" t="inlineStr"/>
+      <c r="T131" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U131" s="22" t="inlineStr">
+      <c r="U131" s="20" t="inlineStr">
         <is>
           <t>BOUKHETOUTA</t>
         </is>
       </c>
-      <c r="V131" s="22" t="inlineStr">
+      <c r="V131" s="20" t="inlineStr">
         <is>
           <t>Fouzia</t>
         </is>
       </c>
-      <c r="W131" s="22" t="inlineStr">
+      <c r="W131" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X131" s="22" t="inlineStr">
+      <c r="X131" s="20" t="inlineStr">
         <is>
           <t>57/1 rue au bois</t>
         </is>
       </c>
-      <c r="Y131" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z131" s="22" t="inlineStr">
+      <c r="Y131" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z131" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="22" t="inlineStr">
+      <c r="A132" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B132" s="23" t="inlineStr">
+      <c r="B132" s="21" t="inlineStr">
         <is>
           <t>350865697</t>
         </is>
       </c>
-      <c r="C132" s="23" t="inlineStr">
+      <c r="C132" s="21" t="inlineStr">
         <is>
           <t>35086569700022</t>
         </is>
       </c>
-      <c r="D132" s="22" t="inlineStr">
+      <c r="D132" s="20" t="inlineStr">
         <is>
           <t>STANBURY CLUB</t>
         </is>
       </c>
-      <c r="E132" s="22" t="inlineStr">
+      <c r="E132" s="20" t="inlineStr">
         <is>
           <t>STANBURY CLUB</t>
         </is>
       </c>
-      <c r="F132" s="22" t="inlineStr">
+      <c r="F132" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G132" s="22" t="inlineStr">
+      <c r="G132" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H132" s="22" t="inlineStr">
+      <c r="H132" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I132" s="22" t="inlineStr">
+      <c r="I132" s="20" t="inlineStr">
         <is>
           <t>30/05/1989</t>
         </is>
       </c>
-      <c r="J132" s="22" t="inlineStr">
+      <c r="J132" s="20" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="K132" s="22" t="inlineStr">
+      <c r="K132" s="20" t="inlineStr">
         <is>
           <t>22 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="L132" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M132" s="22" t="inlineStr">
+      <c r="L132" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M132" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N132" s="22" t="inlineStr">
+      <c r="N132" s="20" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="O132" s="22" t="inlineStr"/>
-      <c r="P132" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q132" s="22" t="inlineStr"/>
-      <c r="R132" s="23" t="inlineStr"/>
-      <c r="S132" s="22" t="inlineStr"/>
-      <c r="T132" s="22" t="inlineStr">
+      <c r="O132" s="20" t="inlineStr"/>
+      <c r="P132" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q132" s="20" t="inlineStr"/>
+      <c r="R132" s="21" t="inlineStr"/>
+      <c r="S132" s="20" t="inlineStr"/>
+      <c r="T132" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U132" s="22" t="inlineStr">
+      <c r="U132" s="20" t="inlineStr">
         <is>
           <t>PAPALIA</t>
         </is>
       </c>
-      <c r="V132" s="22" t="inlineStr">
+      <c r="V132" s="20" t="inlineStr">
         <is>
           <t>Pierre</t>
         </is>
       </c>
-      <c r="W132" s="22" t="inlineStr">
+      <c r="W132" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X132" s="22" t="inlineStr">
+      <c r="X132" s="20" t="inlineStr">
         <is>
           <t>14 rue Marchant</t>
         </is>
       </c>
-      <c r="Y132" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z132" s="22" t="inlineStr">
+      <c r="Y132" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z132" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="22" t="inlineStr">
+      <c r="A133" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B133" s="23" t="inlineStr">
+      <c r="B133" s="21" t="inlineStr">
         <is>
           <t>819787698</t>
         </is>
       </c>
-      <c r="C133" s="23" t="inlineStr">
+      <c r="C133" s="21" t="inlineStr">
         <is>
           <t>81978769800011</t>
         </is>
       </c>
-      <c r="D133" s="22" t="inlineStr">
+      <c r="D133" s="20" t="inlineStr">
         <is>
           <t>APOLLON</t>
         </is>
       </c>
-      <c r="E133" s="22" t="inlineStr">
+      <c r="E133" s="20" t="inlineStr">
         <is>
           <t>APOLLON</t>
         </is>
       </c>
-      <c r="F133" s="22" t="inlineStr">
+      <c r="F133" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G133" s="22" t="inlineStr">
+      <c r="G133" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H133" s="22" t="inlineStr">
+      <c r="H133" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I133" s="22" t="inlineStr">
+      <c r="I133" s="20" t="inlineStr">
         <is>
           <t>19/04/2016</t>
         </is>
       </c>
-      <c r="J133" s="22" t="inlineStr">
+      <c r="J133" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K133" s="22" t="inlineStr">
+      <c r="K133" s="20" t="inlineStr">
         <is>
           <t>2 B PLACE JEANNE D'ARC</t>
         </is>
       </c>
-      <c r="L133" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M133" s="22" t="inlineStr">
+      <c r="L133" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M133" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N133" s="22" t="inlineStr">
+      <c r="N133" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O133" s="22" t="inlineStr"/>
-      <c r="P133" s="22" t="inlineStr"/>
-      <c r="Q133" s="22" t="inlineStr"/>
-      <c r="R133" s="23" t="inlineStr"/>
-      <c r="S133" s="22" t="inlineStr"/>
-      <c r="T133" s="22" t="inlineStr">
+      <c r="O133" s="20" t="inlineStr"/>
+      <c r="P133" s="20" t="inlineStr"/>
+      <c r="Q133" s="20" t="inlineStr"/>
+      <c r="R133" s="21" t="inlineStr"/>
+      <c r="S133" s="20" t="inlineStr"/>
+      <c r="T133" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U133" s="22" t="inlineStr">
+      <c r="U133" s="20" t="inlineStr">
         <is>
           <t>ANSALONE</t>
         </is>
       </c>
-      <c r="V133" s="22" t="inlineStr">
+      <c r="V133" s="20" t="inlineStr">
         <is>
           <t>Franck, Sabino</t>
         </is>
       </c>
-      <c r="W133" s="22" t="inlineStr">
+      <c r="W133" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X133" s="22" t="inlineStr">
+      <c r="X133" s="20" t="inlineStr">
         <is>
           <t>2 rue Glatigny</t>
         </is>
       </c>
-      <c r="Y133" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z133" s="22" t="inlineStr">
+      <c r="Y133" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z133" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="22" t="inlineStr">
+      <c r="A134" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B134" s="23" t="inlineStr">
+      <c r="B134" s="21" t="inlineStr">
         <is>
           <t>994446359</t>
         </is>
       </c>
-      <c r="C134" s="23" t="inlineStr">
+      <c r="C134" s="21" t="inlineStr">
         <is>
           <t>99444635900014</t>
         </is>
       </c>
-      <c r="D134" s="22" t="inlineStr">
+      <c r="D134" s="20" t="inlineStr">
         <is>
           <t>MBL SOCIETY</t>
         </is>
       </c>
-      <c r="E134" s="22" t="inlineStr">
+      <c r="E134" s="20" t="inlineStr">
         <is>
           <t>MBL SOCIETY</t>
         </is>
       </c>
-      <c r="F134" s="22" t="inlineStr">
+      <c r="F134" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G134" s="22" t="inlineStr">
+      <c r="G134" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H134" s="22" t="inlineStr">
+      <c r="H134" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I134" s="22" t="inlineStr">
+      <c r="I134" s="20" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="J134" s="22" t="inlineStr">
+      <c r="J134" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K134" s="22" t="inlineStr">
+      <c r="K134" s="20" t="inlineStr">
         <is>
           <t>39 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L134" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M134" s="22" t="inlineStr">
+      <c r="L134" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M134" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N134" s="22" t="inlineStr">
+      <c r="N134" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O134" s="22" t="inlineStr"/>
-      <c r="P134" s="22" t="inlineStr"/>
-      <c r="Q134" s="22" t="inlineStr"/>
-      <c r="R134" s="23" t="inlineStr"/>
-      <c r="S134" s="22" t="inlineStr"/>
-      <c r="T134" s="22" t="inlineStr">
+      <c r="O134" s="20" t="inlineStr"/>
+      <c r="P134" s="20" t="inlineStr"/>
+      <c r="Q134" s="20" t="inlineStr"/>
+      <c r="R134" s="21" t="inlineStr"/>
+      <c r="S134" s="20" t="inlineStr"/>
+      <c r="T134" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U134" s="22" t="inlineStr">
+      <c r="U134" s="20" t="inlineStr">
         <is>
           <t>USAI</t>
         </is>
       </c>
-      <c r="V134" s="22" t="inlineStr">
+      <c r="V134" s="20" t="inlineStr">
         <is>
           <t>Lennie</t>
         </is>
       </c>
-      <c r="W134" s="22" t="inlineStr">
+      <c r="W134" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X134" s="22" t="inlineStr">
+      <c r="X134" s="20" t="inlineStr">
         <is>
           <t>39, place de chambre</t>
         </is>
       </c>
-      <c r="Y134" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z134" s="22" t="inlineStr">
+      <c r="Y134" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z134" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="22" t="inlineStr">
+      <c r="A135" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B135" s="23" t="inlineStr">
+      <c r="B135" s="21" t="inlineStr">
         <is>
           <t>932948748</t>
         </is>
       </c>
-      <c r="C135" s="23" t="inlineStr">
+      <c r="C135" s="21" t="inlineStr">
         <is>
           <t>93294874800011</t>
         </is>
       </c>
-      <c r="D135" s="22" t="inlineStr">
+      <c r="D135" s="20" t="inlineStr">
         <is>
           <t>LIL' &amp; GO'</t>
         </is>
       </c>
-      <c r="E135" s="22" t="inlineStr">
+      <c r="E135" s="20" t="inlineStr">
         <is>
           <t>LIL' &amp; GO'</t>
         </is>
       </c>
-      <c r="F135" s="22" t="inlineStr">
+      <c r="F135" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G135" s="22" t="inlineStr">
+      <c r="G135" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H135" s="22" t="inlineStr">
+      <c r="H135" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I135" s="22" t="inlineStr">
+      <c r="I135" s="20" t="inlineStr">
         <is>
           <t>06/09/2024</t>
         </is>
       </c>
-      <c r="J135" s="22" t="inlineStr">
+      <c r="J135" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K135" s="22" t="inlineStr">
+      <c r="K135" s="20" t="inlineStr">
         <is>
           <t>34 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L135" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M135" s="22" t="inlineStr">
+      <c r="L135" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M135" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N135" s="22" t="inlineStr">
+      <c r="N135" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O135" s="22" t="inlineStr"/>
-      <c r="P135" s="22" t="inlineStr"/>
-      <c r="Q135" s="22" t="inlineStr"/>
-      <c r="R135" s="23" t="inlineStr"/>
-      <c r="S135" s="22" t="inlineStr"/>
-      <c r="T135" s="22" t="inlineStr">
+      <c r="O135" s="20" t="inlineStr"/>
+      <c r="P135" s="20" t="inlineStr"/>
+      <c r="Q135" s="20" t="inlineStr"/>
+      <c r="R135" s="21" t="inlineStr"/>
+      <c r="S135" s="20" t="inlineStr"/>
+      <c r="T135" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U135" s="22" t="inlineStr">
+      <c r="U135" s="20" t="inlineStr">
         <is>
           <t>MUNKA</t>
         </is>
       </c>
-      <c r="V135" s="22" t="inlineStr">
+      <c r="V135" s="20" t="inlineStr">
         <is>
           <t>Elise, Adeline, Marie</t>
         </is>
       </c>
-      <c r="W135" s="22" t="inlineStr">
+      <c r="W135" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X135" s="22" t="inlineStr">
+      <c r="X135" s="20" t="inlineStr">
         <is>
           <t>18, rue de bouteiller</t>
         </is>
       </c>
-      <c r="Y135" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z135" s="22" t="inlineStr">
+      <c r="Y135" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z135" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="22" t="inlineStr">
+      <c r="A136" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B136" s="23" t="inlineStr">
+      <c r="B136" s="21" t="inlineStr">
         <is>
           <t>400782892</t>
         </is>
       </c>
-      <c r="C136" s="23" t="inlineStr">
+      <c r="C136" s="21" t="inlineStr">
         <is>
           <t>40078289200048</t>
         </is>
       </c>
-      <c r="D136" s="22" t="inlineStr">
+      <c r="D136" s="20" t="inlineStr">
         <is>
           <t>DU PALAIS</t>
         </is>
       </c>
-      <c r="E136" s="22" t="inlineStr">
+      <c r="E136" s="20" t="inlineStr">
         <is>
           <t>DU PALAIS</t>
         </is>
       </c>
-      <c r="F136" s="22" t="inlineStr">
+      <c r="F136" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G136" s="22" t="inlineStr">
+      <c r="G136" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H136" s="22" t="inlineStr">
+      <c r="H136" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I136" s="22" t="inlineStr">
+      <c r="I136" s="20" t="inlineStr">
         <is>
           <t>01/05/1995</t>
         </is>
       </c>
-      <c r="J136" s="22" t="inlineStr">
+      <c r="J136" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="K136" s="22" t="inlineStr">
+      <c r="K136" s="20" t="inlineStr">
         <is>
           <t>24 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L136" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M136" s="22" t="inlineStr">
+      <c r="L136" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M136" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N136" s="22" t="inlineStr">
+      <c r="N136" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O136" s="22" t="n">
-        <v>822074</v>
-      </c>
-      <c r="P136" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q136" s="22" t="inlineStr"/>
-      <c r="R136" s="23" t="inlineStr"/>
-      <c r="S136" s="22" t="inlineStr"/>
-      <c r="T136" s="22" t="inlineStr">
+      <c r="O136" s="20" t="inlineStr">
+        <is>
+          <t>822074</t>
+        </is>
+      </c>
+      <c r="P136" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q136" s="20" t="inlineStr"/>
+      <c r="R136" s="21" t="inlineStr"/>
+      <c r="S136" s="20" t="inlineStr"/>
+      <c r="T136" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U136" s="22" t="inlineStr">
+      <c r="U136" s="20" t="inlineStr">
         <is>
           <t>PJEVCEVIC</t>
         </is>
       </c>
-      <c r="V136" s="22" t="inlineStr">
+      <c r="V136" s="20" t="inlineStr">
         <is>
           <t>Pierre</t>
         </is>
       </c>
-      <c r="W136" s="22" t="inlineStr">
+      <c r="W136" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X136" s="22" t="inlineStr">
+      <c r="X136" s="20" t="inlineStr">
         <is>
           <t>5 place du général de gaulle</t>
         </is>
       </c>
-      <c r="Y136" s="23" t="inlineStr">
+      <c r="Y136" s="21" t="inlineStr">
         <is>
           <t>57155</t>
         </is>
       </c>
-      <c r="Z136" s="22" t="inlineStr">
+      <c r="Z136" s="20" t="inlineStr">
         <is>
           <t>Marly</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="22" t="inlineStr">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B137" s="23" t="inlineStr">
+      <c r="B137" s="21" t="inlineStr">
         <is>
           <t>981166085</t>
         </is>
       </c>
-      <c r="C137" s="23" t="inlineStr">
+      <c r="C137" s="21" t="inlineStr">
         <is>
           <t>98116608500010</t>
         </is>
       </c>
-      <c r="D137" s="22" t="inlineStr">
+      <c r="D137" s="20" t="inlineStr">
         <is>
           <t>RED BARREL</t>
         </is>
       </c>
-      <c r="E137" s="22" t="inlineStr">
+      <c r="E137" s="20" t="inlineStr">
         <is>
           <t>RED BARREL</t>
         </is>
       </c>
-      <c r="F137" s="22" t="inlineStr">
+      <c r="F137" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G137" s="22" t="inlineStr">
+      <c r="G137" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H137" s="22" t="inlineStr">
+      <c r="H137" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I137" s="22" t="inlineStr">
+      <c r="I137" s="20" t="inlineStr">
         <is>
           <t>31/08/2023</t>
         </is>
       </c>
-      <c r="J137" s="22" t="inlineStr">
+      <c r="J137" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K137" s="22" t="inlineStr">
+      <c r="K137" s="20" t="inlineStr">
         <is>
           <t>19 AVENUE ROBERT SCHUMAN</t>
         </is>
       </c>
-      <c r="L137" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M137" s="22" t="inlineStr">
+      <c r="L137" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M137" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N137" s="22" t="inlineStr">
+      <c r="N137" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O137" s="22" t="inlineStr"/>
-      <c r="P137" s="22" t="inlineStr"/>
-      <c r="Q137" s="22" t="inlineStr"/>
-      <c r="R137" s="23" t="inlineStr"/>
-      <c r="S137" s="22" t="inlineStr"/>
-      <c r="T137" s="22" t="inlineStr">
+      <c r="O137" s="20" t="inlineStr"/>
+      <c r="P137" s="20" t="inlineStr"/>
+      <c r="Q137" s="20" t="inlineStr"/>
+      <c r="R137" s="21" t="inlineStr"/>
+      <c r="S137" s="20" t="inlineStr"/>
+      <c r="T137" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U137" s="22" t="inlineStr">
+      <c r="U137" s="20" t="inlineStr">
         <is>
           <t>BAUDE</t>
         </is>
       </c>
-      <c r="V137" s="22" t="inlineStr">
+      <c r="V137" s="20" t="inlineStr">
         <is>
           <t>Jérémy, Marc, Georges</t>
         </is>
       </c>
-      <c r="W137" s="22" t="inlineStr">
+      <c r="W137" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X137" s="22" t="inlineStr">
+      <c r="X137" s="20" t="inlineStr">
         <is>
           <t>4 rue du maitre échevin</t>
         </is>
       </c>
-      <c r="Y137" s="23" t="inlineStr">
+      <c r="Y137" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z137" s="22" t="inlineStr">
+      <c r="Z137" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="22" t="inlineStr">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B138" s="23" t="inlineStr">
+      <c r="B138" s="21" t="inlineStr">
         <is>
           <t>881776280</t>
         </is>
       </c>
-      <c r="C138" s="23" t="inlineStr">
+      <c r="C138" s="21" t="inlineStr">
         <is>
           <t>88177628000011</t>
         </is>
       </c>
-      <c r="D138" s="22" t="inlineStr">
+      <c r="D138" s="20" t="inlineStr">
         <is>
           <t>MUPI</t>
         </is>
       </c>
-      <c r="E138" s="22" t="inlineStr">
+      <c r="E138" s="20" t="inlineStr">
         <is>
           <t>MUPI</t>
         </is>
       </c>
-      <c r="F138" s="22" t="inlineStr">
+      <c r="F138" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G138" s="22" t="inlineStr">
+      <c r="G138" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H138" s="22" t="inlineStr">
+      <c r="H138" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I138" s="22" t="inlineStr">
+      <c r="I138" s="20" t="inlineStr">
         <is>
           <t>19/02/2020</t>
         </is>
       </c>
-      <c r="J138" s="22" t="inlineStr">
+      <c r="J138" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K138" s="22" t="inlineStr">
+      <c r="K138" s="20" t="inlineStr">
         <is>
           <t>53 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L138" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M138" s="22" t="inlineStr">
+      <c r="L138" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M138" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N138" s="22" t="inlineStr">
+      <c r="N138" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O138" s="22" t="inlineStr"/>
-      <c r="P138" s="22" t="inlineStr"/>
-      <c r="Q138" s="22" t="inlineStr"/>
-      <c r="R138" s="23" t="inlineStr"/>
-      <c r="S138" s="22" t="inlineStr"/>
-      <c r="T138" s="22" t="inlineStr">
+      <c r="O138" s="20" t="inlineStr"/>
+      <c r="P138" s="20" t="inlineStr"/>
+      <c r="Q138" s="20" t="inlineStr"/>
+      <c r="R138" s="21" t="inlineStr"/>
+      <c r="S138" s="20" t="inlineStr"/>
+      <c r="T138" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U138" s="22" t="inlineStr">
+      <c r="U138" s="20" t="inlineStr">
         <is>
           <t>MULLER</t>
         </is>
       </c>
-      <c r="V138" s="22" t="inlineStr">
+      <c r="V138" s="20" t="inlineStr">
         <is>
           <t>Stéphane</t>
         </is>
       </c>
-      <c r="W138" s="22" t="inlineStr">
+      <c r="W138" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X138" s="22" t="inlineStr">
+      <c r="X138" s="20" t="inlineStr">
         <is>
           <t>13 rue des Huiliers</t>
         </is>
       </c>
-      <c r="Y138" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z138" s="22" t="inlineStr">
+      <c r="Y138" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z138" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="22" t="inlineStr">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B139" s="23" t="inlineStr">
+      <c r="B139" s="21" t="inlineStr">
         <is>
           <t>800477713</t>
         </is>
       </c>
-      <c r="C139" s="23" t="inlineStr">
+      <c r="C139" s="21" t="inlineStr">
         <is>
           <t>80047771300013</t>
         </is>
       </c>
-      <c r="D139" s="22" t="inlineStr">
+      <c r="D139" s="20" t="inlineStr">
         <is>
           <t>LE PETIT BISTROT</t>
         </is>
       </c>
-      <c r="E139" s="22" t="inlineStr">
+      <c r="E139" s="20" t="inlineStr">
         <is>
           <t>LE PETIT BISTROT</t>
         </is>
       </c>
-      <c r="F139" s="22" t="inlineStr">
+      <c r="F139" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G139" s="22" t="inlineStr">
+      <c r="G139" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H139" s="22" t="inlineStr">
+      <c r="H139" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I139" s="22" t="inlineStr">
+      <c r="I139" s="20" t="inlineStr">
         <is>
           <t>15/02/2014</t>
         </is>
       </c>
-      <c r="J139" s="22" t="inlineStr">
+      <c r="J139" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K139" s="22" t="inlineStr">
+      <c r="K139" s="20" t="inlineStr">
         <is>
           <t>22 BOULEVARD ANDRE MAGINOT</t>
         </is>
       </c>
-      <c r="L139" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M139" s="22" t="inlineStr">
+      <c r="L139" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M139" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N139" s="22" t="inlineStr">
+      <c r="N139" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O139" s="22" t="inlineStr"/>
-      <c r="P139" s="22" t="inlineStr"/>
-      <c r="Q139" s="22" t="inlineStr"/>
-      <c r="R139" s="23" t="inlineStr"/>
-      <c r="S139" s="22" t="inlineStr"/>
-      <c r="T139" s="22" t="inlineStr">
+      <c r="O139" s="20" t="inlineStr"/>
+      <c r="P139" s="20" t="inlineStr"/>
+      <c r="Q139" s="20" t="inlineStr"/>
+      <c r="R139" s="21" t="inlineStr"/>
+      <c r="S139" s="20" t="inlineStr"/>
+      <c r="T139" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U139" s="22" t="inlineStr">
+      <c r="U139" s="20" t="inlineStr">
         <is>
           <t>ALLALI</t>
         </is>
       </c>
-      <c r="V139" s="22" t="inlineStr">
+      <c r="V139" s="20" t="inlineStr">
         <is>
           <t>Ahmed</t>
         </is>
       </c>
-      <c r="W139" s="22" t="inlineStr">
+      <c r="W139" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X139" s="22" t="inlineStr">
+      <c r="X139" s="20" t="inlineStr">
         <is>
           <t>10 rue Dupont des Loges</t>
         </is>
       </c>
-      <c r="Y139" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z139" s="22" t="inlineStr">
+      <c r="Y139" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z139" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="22" t="inlineStr">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B140" s="23" t="inlineStr">
+      <c r="B140" s="21" t="inlineStr">
         <is>
           <t>979036894</t>
         </is>
       </c>
-      <c r="C140" s="23" t="inlineStr">
+      <c r="C140" s="21" t="inlineStr">
         <is>
           <t>97903689400017</t>
         </is>
       </c>
-      <c r="D140" s="22" t="inlineStr">
+      <c r="D140" s="20" t="inlineStr">
         <is>
           <t>THE PARTING GLASS</t>
         </is>
       </c>
-      <c r="E140" s="22" t="inlineStr">
+      <c r="E140" s="20" t="inlineStr">
         <is>
           <t>THE PARTING GLASS</t>
         </is>
       </c>
-      <c r="F140" s="22" t="inlineStr">
+      <c r="F140" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G140" s="22" t="inlineStr">
+      <c r="G140" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H140" s="22" t="inlineStr">
+      <c r="H140" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I140" s="22" t="inlineStr">
+      <c r="I140" s="20" t="inlineStr">
         <is>
           <t>31/08/2023</t>
         </is>
       </c>
-      <c r="J140" s="22" t="inlineStr">
+      <c r="J140" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K140" s="22" t="inlineStr">
+      <c r="K140" s="20" t="inlineStr">
         <is>
           <t>27 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L140" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M140" s="22" t="inlineStr">
+      <c r="L140" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M140" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N140" s="22" t="inlineStr">
+      <c r="N140" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O140" s="22" t="inlineStr"/>
-      <c r="P140" s="22" t="inlineStr"/>
-      <c r="Q140" s="22" t="inlineStr"/>
-      <c r="R140" s="23" t="inlineStr"/>
-      <c r="S140" s="22" t="inlineStr"/>
-      <c r="T140" s="22" t="inlineStr">
+      <c r="O140" s="20" t="inlineStr"/>
+      <c r="P140" s="20" t="inlineStr"/>
+      <c r="Q140" s="20" t="inlineStr"/>
+      <c r="R140" s="21" t="inlineStr"/>
+      <c r="S140" s="20" t="inlineStr"/>
+      <c r="T140" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U140" s="22" t="inlineStr">
+      <c r="U140" s="20" t="inlineStr">
         <is>
           <t>LANG</t>
         </is>
       </c>
-      <c r="V140" s="22" t="inlineStr">
+      <c r="V140" s="20" t="inlineStr">
         <is>
           <t>Nicolas, Ewen, Guillaume</t>
         </is>
       </c>
-      <c r="W140" s="22" t="inlineStr">
+      <c r="W140" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X140" s="22" t="inlineStr"/>
-      <c r="Y140" s="23" t="inlineStr"/>
-      <c r="Z140" s="22" t="inlineStr"/>
+      <c r="X140" s="20" t="inlineStr"/>
+      <c r="Y140" s="21" t="inlineStr"/>
+      <c r="Z140" s="20" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="22" t="inlineStr">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B141" s="23" t="inlineStr">
+      <c r="B141" s="21" t="inlineStr">
         <is>
           <t>431215516</t>
         </is>
       </c>
-      <c r="C141" s="23" t="inlineStr">
+      <c r="C141" s="21" t="inlineStr">
         <is>
           <t>43121551600011</t>
         </is>
       </c>
-      <c r="D141" s="22" t="inlineStr">
+      <c r="D141" s="20" t="inlineStr">
         <is>
           <t>LA VILLE DE CASA</t>
         </is>
       </c>
-      <c r="E141" s="22" t="inlineStr">
+      <c r="E141" s="20" t="inlineStr">
         <is>
           <t>LA VILLE DE CASA</t>
         </is>
       </c>
-      <c r="F141" s="22" t="inlineStr">
+      <c r="F141" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G141" s="22" t="inlineStr">
+      <c r="G141" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H141" s="22" t="inlineStr">
+      <c r="H141" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I141" s="22" t="inlineStr">
+      <c r="I141" s="20" t="inlineStr">
         <is>
           <t>06/04/2000</t>
         </is>
       </c>
-      <c r="J141" s="22" t="inlineStr">
+      <c r="J141" s="20" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="K141" s="22" t="inlineStr">
+      <c r="K141" s="20" t="inlineStr">
         <is>
           <t>16 RUE MAZELLE</t>
         </is>
       </c>
-      <c r="L141" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M141" s="22" t="inlineStr">
+      <c r="L141" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M141" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N141" s="22" t="inlineStr">
+      <c r="N141" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O141" s="22" t="inlineStr"/>
-      <c r="P141" s="22" t="inlineStr"/>
-      <c r="Q141" s="22" t="inlineStr"/>
-      <c r="R141" s="23" t="inlineStr"/>
-      <c r="S141" s="22" t="inlineStr"/>
-      <c r="T141" s="22" t="inlineStr">
+      <c r="O141" s="20" t="inlineStr"/>
+      <c r="P141" s="20" t="inlineStr"/>
+      <c r="Q141" s="20" t="inlineStr"/>
+      <c r="R141" s="21" t="inlineStr"/>
+      <c r="S141" s="20" t="inlineStr"/>
+      <c r="T141" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U141" s="22" t="inlineStr">
+      <c r="U141" s="20" t="inlineStr">
         <is>
           <t>EL AMRI</t>
         </is>
       </c>
-      <c r="V141" s="22" t="inlineStr">
+      <c r="V141" s="20" t="inlineStr">
         <is>
           <t>Abdallah</t>
         </is>
       </c>
-      <c r="W141" s="22" t="inlineStr">
+      <c r="W141" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X141" s="22" t="inlineStr">
+      <c r="X141" s="20" t="inlineStr">
         <is>
           <t>8 boulevard Serot</t>
         </is>
       </c>
-      <c r="Y141" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z141" s="22" t="inlineStr">
+      <c r="Y141" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z141" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="22" t="inlineStr">
+      <c r="A142" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B142" s="23" t="inlineStr">
+      <c r="B142" s="21" t="inlineStr">
         <is>
           <t>944744200</t>
         </is>
       </c>
-      <c r="C142" s="23" t="inlineStr">
+      <c r="C142" s="21" t="inlineStr">
         <is>
           <t>94474420000014</t>
         </is>
       </c>
-      <c r="D142" s="22" t="inlineStr">
+      <c r="D142" s="20" t="inlineStr">
         <is>
           <t>METZZARELLA</t>
         </is>
       </c>
-      <c r="E142" s="22" t="inlineStr">
+      <c r="E142" s="20" t="inlineStr">
         <is>
           <t>METZZARELLA</t>
         </is>
       </c>
-      <c r="F142" s="22" t="inlineStr">
+      <c r="F142" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G142" s="22" t="inlineStr">
+      <c r="G142" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H142" s="22" t="inlineStr">
+      <c r="H142" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I142" s="22" t="inlineStr">
+      <c r="I142" s="20" t="inlineStr">
         <is>
           <t>02/05/2025</t>
         </is>
       </c>
-      <c r="J142" s="22" t="inlineStr">
+      <c r="J142" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K142" s="22" t="inlineStr">
+      <c r="K142" s="20" t="inlineStr">
         <is>
           <t>41 RUE DES ALLEMANDS</t>
         </is>
       </c>
-      <c r="L142" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M142" s="22" t="inlineStr">
+      <c r="L142" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M142" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N142" s="22" t="inlineStr">
+      <c r="N142" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O142" s="22" t="inlineStr"/>
-      <c r="P142" s="22" t="inlineStr"/>
-      <c r="Q142" s="22" t="inlineStr"/>
-      <c r="R142" s="23" t="inlineStr"/>
-      <c r="S142" s="22" t="inlineStr"/>
-      <c r="T142" s="22" t="inlineStr">
+      <c r="O142" s="20" t="inlineStr"/>
+      <c r="P142" s="20" t="inlineStr"/>
+      <c r="Q142" s="20" t="inlineStr"/>
+      <c r="R142" s="21" t="inlineStr"/>
+      <c r="S142" s="20" t="inlineStr"/>
+      <c r="T142" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U142" s="22" t="inlineStr">
+      <c r="U142" s="20" t="inlineStr">
         <is>
           <t>LHIOUI</t>
         </is>
       </c>
-      <c r="V142" s="22" t="inlineStr">
+      <c r="V142" s="20" t="inlineStr">
         <is>
           <t>Ramzi</t>
         </is>
       </c>
-      <c r="W142" s="22" t="inlineStr">
+      <c r="W142" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X142" s="22" t="inlineStr">
+      <c r="X142" s="20" t="inlineStr">
         <is>
           <t>02 rue du wad billy</t>
         </is>
       </c>
-      <c r="Y142" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z142" s="22" t="inlineStr">
+      <c r="Y142" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z142" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="22" t="inlineStr">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B143" s="23" t="inlineStr">
+      <c r="B143" s="21" t="inlineStr">
         <is>
           <t>351052949</t>
         </is>
       </c>
-      <c r="C143" s="23" t="inlineStr">
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>35105294900010</t>
         </is>
       </c>
-      <c r="D143" s="22" t="inlineStr">
+      <c r="D143" s="20" t="inlineStr">
         <is>
           <t>ITALREST</t>
         </is>
       </c>
-      <c r="E143" s="22" t="inlineStr">
+      <c r="E143" s="20" t="inlineStr">
         <is>
           <t>ITALREST</t>
         </is>
       </c>
-      <c r="F143" s="22" t="inlineStr">
+      <c r="F143" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G143" s="22" t="inlineStr">
+      <c r="G143" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H143" s="22" t="inlineStr">
+      <c r="H143" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I143" s="22" t="inlineStr">
+      <c r="I143" s="20" t="inlineStr">
         <is>
           <t>30/05/1989</t>
         </is>
       </c>
-      <c r="J143" s="22" t="inlineStr">
+      <c r="J143" s="20" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="K143" s="22" t="inlineStr">
+      <c r="K143" s="20" t="inlineStr">
         <is>
           <t>18 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="L143" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M143" s="22" t="inlineStr">
+      <c r="L143" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M143" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N143" s="22" t="inlineStr">
+      <c r="N143" s="20" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="O143" s="22" t="n">
-        <v>1704665</v>
-      </c>
-      <c r="P143" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q143" s="22" t="inlineStr"/>
-      <c r="R143" s="23" t="inlineStr"/>
-      <c r="S143" s="22" t="inlineStr"/>
-      <c r="T143" s="22" t="inlineStr">
+      <c r="O143" s="20" t="inlineStr">
+        <is>
+          <t>1704665</t>
+        </is>
+      </c>
+      <c r="P143" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q143" s="20" t="inlineStr"/>
+      <c r="R143" s="21" t="inlineStr"/>
+      <c r="S143" s="20" t="inlineStr"/>
+      <c r="T143" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U143" s="22" t="inlineStr">
+      <c r="U143" s="20" t="inlineStr">
         <is>
           <t>SCIGLIANO</t>
         </is>
       </c>
-      <c r="V143" s="22" t="inlineStr">
+      <c r="V143" s="20" t="inlineStr">
         <is>
           <t>Marcello</t>
         </is>
       </c>
-      <c r="W143" s="22" t="inlineStr">
+      <c r="W143" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X143" s="22" t="inlineStr">
+      <c r="X143" s="20" t="inlineStr">
         <is>
           <t>38 rue Dupont des Loges</t>
         </is>
       </c>
-      <c r="Y143" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z143" s="22" t="inlineStr">
+      <c r="Y143" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z143" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="22" t="inlineStr">
+      <c r="A144" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B144" s="23" t="inlineStr">
+      <c r="B144" s="21" t="inlineStr">
         <is>
           <t>930385398</t>
         </is>
       </c>
-      <c r="C144" s="23" t="inlineStr">
+      <c r="C144" s="21" t="inlineStr">
         <is>
           <t>93038539800019</t>
         </is>
       </c>
-      <c r="D144" s="22" t="inlineStr">
+      <c r="D144" s="20" t="inlineStr">
         <is>
           <t>L'HEDONISTE</t>
         </is>
       </c>
-      <c r="E144" s="22" t="inlineStr">
+      <c r="E144" s="20" t="inlineStr">
         <is>
           <t>L'HEDONISTE</t>
         </is>
       </c>
-      <c r="F144" s="22" t="inlineStr">
+      <c r="F144" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G144" s="22" t="inlineStr">
+      <c r="G144" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H144" s="22" t="inlineStr">
+      <c r="H144" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I144" s="22" t="inlineStr">
+      <c r="I144" s="20" t="inlineStr">
         <is>
           <t>14/06/2024</t>
         </is>
       </c>
-      <c r="J144" s="22" t="inlineStr">
+      <c r="J144" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K144" s="22" t="inlineStr">
+      <c r="K144" s="20" t="inlineStr">
         <is>
           <t>23 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L144" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M144" s="22" t="inlineStr">
+      <c r="L144" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M144" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N144" s="22" t="inlineStr">
+      <c r="N144" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O144" s="22" t="inlineStr"/>
-      <c r="P144" s="22" t="inlineStr"/>
-      <c r="Q144" s="22" t="inlineStr"/>
-      <c r="R144" s="23" t="inlineStr"/>
-      <c r="S144" s="22" t="inlineStr"/>
-      <c r="T144" s="22" t="inlineStr">
+      <c r="O144" s="20" t="inlineStr"/>
+      <c r="P144" s="20" t="inlineStr"/>
+      <c r="Q144" s="20" t="inlineStr"/>
+      <c r="R144" s="21" t="inlineStr"/>
+      <c r="S144" s="20" t="inlineStr"/>
+      <c r="T144" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U144" s="22" t="inlineStr">
+      <c r="U144" s="20" t="inlineStr">
         <is>
           <t>SIMON</t>
         </is>
       </c>
-      <c r="V144" s="22" t="inlineStr">
+      <c r="V144" s="20" t="inlineStr">
         <is>
           <t>Bastien, Cris, Ian</t>
         </is>
       </c>
-      <c r="W144" s="22" t="inlineStr">
+      <c r="W144" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X144" s="22" t="inlineStr">
+      <c r="X144" s="20" t="inlineStr">
         <is>
           <t>43, rue Maurice Ravel</t>
         </is>
       </c>
-      <c r="Y144" s="23" t="inlineStr">
+      <c r="Y144" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z144" s="22" t="inlineStr">
+      <c r="Z144" s="20" t="inlineStr">
         <is>
           <t>Woippy</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="22" t="inlineStr">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B145" s="23" t="inlineStr">
+      <c r="B145" s="21" t="inlineStr">
         <is>
           <t>979422748</t>
         </is>
       </c>
-      <c r="C145" s="23" t="inlineStr">
+      <c r="C145" s="21" t="inlineStr">
         <is>
           <t>97942274800025</t>
         </is>
       </c>
-      <c r="D145" s="22" t="inlineStr">
+      <c r="D145" s="20" t="inlineStr">
         <is>
           <t>Petit bamboo</t>
         </is>
       </c>
-      <c r="E145" s="22" t="inlineStr">
+      <c r="E145" s="20" t="inlineStr">
         <is>
           <t>Petit bamboo</t>
         </is>
       </c>
-      <c r="F145" s="22" t="inlineStr">
+      <c r="F145" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G145" s="22" t="inlineStr">
+      <c r="G145" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H145" s="22" t="inlineStr">
+      <c r="H145" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I145" s="22" t="inlineStr">
+      <c r="I145" s="20" t="inlineStr">
         <is>
           <t>25/08/2023</t>
         </is>
       </c>
-      <c r="J145" s="22" t="inlineStr">
+      <c r="J145" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K145" s="22" t="inlineStr">
+      <c r="K145" s="20" t="inlineStr">
         <is>
           <t>11 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L145" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M145" s="22" t="inlineStr">
+      <c r="L145" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M145" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N145" s="22" t="inlineStr">
+      <c r="N145" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O145" s="22" t="inlineStr"/>
-      <c r="P145" s="22" t="inlineStr"/>
-      <c r="Q145" s="22" t="inlineStr"/>
-      <c r="R145" s="23" t="inlineStr"/>
-      <c r="S145" s="22" t="inlineStr"/>
-      <c r="T145" s="22" t="inlineStr">
+      <c r="O145" s="20" t="inlineStr"/>
+      <c r="P145" s="20" t="inlineStr"/>
+      <c r="Q145" s="20" t="inlineStr"/>
+      <c r="R145" s="21" t="inlineStr"/>
+      <c r="S145" s="20" t="inlineStr"/>
+      <c r="T145" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U145" s="22" t="inlineStr">
+      <c r="U145" s="20" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="V145" s="22" t="inlineStr">
+      <c r="V145" s="20" t="inlineStr">
         <is>
           <t>Yang</t>
         </is>
       </c>
-      <c r="W145" s="22" t="inlineStr">
+      <c r="W145" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X145" s="22" t="inlineStr">
+      <c r="X145" s="20" t="inlineStr">
         <is>
           <t>72 cours de la libération et du général de gaulle</t>
         </is>
       </c>
-      <c r="Y145" s="23" t="inlineStr">
+      <c r="Y145" s="21" t="inlineStr">
         <is>
           <t>38100</t>
         </is>
       </c>
-      <c r="Z145" s="22" t="inlineStr">
+      <c r="Z145" s="20" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="22" t="inlineStr">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B146" s="23" t="inlineStr">
+      <c r="B146" s="21" t="inlineStr">
         <is>
           <t>810501825</t>
         </is>
       </c>
-      <c r="C146" s="23" t="inlineStr">
+      <c r="C146" s="21" t="inlineStr">
         <is>
           <t>81050182500022</t>
         </is>
       </c>
-      <c r="D146" s="22" t="inlineStr">
+      <c r="D146" s="20" t="inlineStr">
         <is>
           <t>JDC 33 QFX</t>
         </is>
       </c>
-      <c r="E146" s="22" t="inlineStr">
+      <c r="E146" s="20" t="inlineStr">
         <is>
           <t>JDC 33 QFX</t>
         </is>
       </c>
-      <c r="F146" s="22" t="inlineStr">
+      <c r="F146" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G146" s="22" t="inlineStr">
+      <c r="G146" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H146" s="22" t="inlineStr">
+      <c r="H146" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I146" s="22" t="inlineStr">
+      <c r="I146" s="20" t="inlineStr">
         <is>
           <t>27/03/2015</t>
         </is>
       </c>
-      <c r="J146" s="22" t="inlineStr">
+      <c r="J146" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K146" s="22" t="inlineStr">
+      <c r="K146" s="20" t="inlineStr">
         <is>
           <t>33 QUAI FELIX MARECHAL</t>
         </is>
       </c>
-      <c r="L146" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M146" s="22" t="inlineStr">
+      <c r="L146" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M146" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N146" s="22" t="inlineStr">
+      <c r="N146" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O146" s="22" t="inlineStr"/>
-      <c r="P146" s="22" t="inlineStr"/>
-      <c r="Q146" s="22" t="inlineStr"/>
-      <c r="R146" s="23" t="inlineStr"/>
-      <c r="S146" s="22" t="inlineStr"/>
-      <c r="T146" s="22" t="inlineStr">
+      <c r="O146" s="20" t="inlineStr"/>
+      <c r="P146" s="20" t="inlineStr"/>
+      <c r="Q146" s="20" t="inlineStr"/>
+      <c r="R146" s="21" t="inlineStr"/>
+      <c r="S146" s="20" t="inlineStr"/>
+      <c r="T146" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U146" s="22" t="inlineStr">
+      <c r="U146" s="20" t="inlineStr">
         <is>
           <t>NEVEU</t>
         </is>
       </c>
-      <c r="V146" s="22" t="inlineStr">
+      <c r="V146" s="20" t="inlineStr">
         <is>
           <t>Alexandre, Hervé, Fabien</t>
         </is>
       </c>
-      <c r="W146" s="22" t="inlineStr">
+      <c r="W146" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X146" s="22" t="inlineStr">
+      <c r="X146" s="20" t="inlineStr">
         <is>
           <t>8 rue Amiral Varney</t>
         </is>
       </c>
-      <c r="Y146" s="23" t="inlineStr">
+      <c r="Y146" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z146" s="22" t="inlineStr">
+      <c r="Z146" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="22" t="inlineStr">
+      <c r="A147" s="20" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B147" s="23" t="inlineStr">
+      <c r="B147" s="21" t="inlineStr">
         <is>
           <t>431503341</t>
         </is>
       </c>
-      <c r="C147" s="23" t="inlineStr">
+      <c r="C147" s="21" t="inlineStr">
         <is>
           <t>43150334100015</t>
         </is>
       </c>
-      <c r="D147" s="22" t="inlineStr">
+      <c r="D147" s="20" t="inlineStr">
         <is>
           <t>MAHAL</t>
         </is>
       </c>
-      <c r="E147" s="22" t="inlineStr">
+      <c r="E147" s="20" t="inlineStr">
         <is>
           <t>MAHAL</t>
         </is>
       </c>
-      <c r="F147" s="22" t="inlineStr">
+      <c r="F147" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G147" s="22" t="inlineStr">
+      <c r="G147" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H147" s="22" t="inlineStr">
+      <c r="H147" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I147" s="22" t="inlineStr">
+      <c r="I147" s="20" t="inlineStr">
         <is>
           <t>30/04/2000</t>
         </is>
       </c>
-      <c r="J147" s="22" t="inlineStr">
+      <c r="J147" s="20" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="K147" s="22" t="inlineStr">
+      <c r="K147" s="20" t="inlineStr">
         <is>
           <t>16 RUE DES JARDINS</t>
         </is>
       </c>
-      <c r="L147" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M147" s="22" t="inlineStr">
+      <c r="L147" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M147" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N147" s="22" t="inlineStr">
+      <c r="N147" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O147" s="22" t="inlineStr"/>
-      <c r="P147" s="22" t="inlineStr"/>
-      <c r="Q147" s="22" t="inlineStr"/>
-      <c r="R147" s="23" t="inlineStr"/>
-      <c r="S147" s="22" t="inlineStr"/>
-      <c r="T147" s="22" t="inlineStr">
+      <c r="O147" s="20" t="inlineStr"/>
+      <c r="P147" s="20" t="inlineStr"/>
+      <c r="Q147" s="20" t="inlineStr"/>
+      <c r="R147" s="21" t="inlineStr"/>
+      <c r="S147" s="20" t="inlineStr"/>
+      <c r="T147" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U147" s="22" t="inlineStr">
+      <c r="U147" s="20" t="inlineStr">
         <is>
           <t>RAVIKUMAR</t>
         </is>
       </c>
-      <c r="V147" s="22" t="inlineStr">
+      <c r="V147" s="20" t="inlineStr">
         <is>
           <t>Kanapathipillah</t>
         </is>
       </c>
-      <c r="W147" s="22" t="inlineStr">
+      <c r="W147" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X147" s="22" t="inlineStr">
+      <c r="X147" s="20" t="inlineStr">
         <is>
           <t>60 rue Madame Carre de Malberg</t>
         </is>
       </c>
-      <c r="Y147" s="23" t="inlineStr">
+      <c r="Y147" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z147" s="22" t="inlineStr">
+      <c r="Z147" s="20" t="inlineStr">
         <is>
           <t>Lorry-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B148" s="23" t="inlineStr">
+        <is>
+          <t>852241488</t>
+        </is>
+      </c>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>85224148800018</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="inlineStr">
+        <is>
+          <t>CUREL</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="inlineStr">
+        <is>
+          <t>CUREL</t>
+        </is>
+      </c>
+      <c r="F148" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G148" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H148" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I148" s="22" t="inlineStr">
+        <is>
+          <t>24/05/2019</t>
+        </is>
+      </c>
+      <c r="J148" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K148" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE FRANCOIS DE CUREL</t>
+        </is>
+      </c>
+      <c r="L148" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M148" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N148" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O148" s="22" t="inlineStr"/>
+      <c r="P148" s="22" t="inlineStr"/>
+      <c r="Q148" s="22" t="inlineStr"/>
+      <c r="R148" s="23" t="inlineStr"/>
+      <c r="S148" s="22" t="inlineStr"/>
+      <c r="T148" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U148" s="22" t="inlineStr">
+        <is>
+          <t>BILGEN</t>
+        </is>
+      </c>
+      <c r="V148" s="22" t="inlineStr">
+        <is>
+          <t>Engin</t>
+        </is>
+      </c>
+      <c r="W148" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X148" s="22" t="inlineStr">
+        <is>
+          <t>32 Rue du Grand Pré</t>
+        </is>
+      </c>
+      <c r="Y148" s="23" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="Z148" s="22" t="inlineStr">
+        <is>
+          <t>Marsilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B149" s="23" t="inlineStr">
+        <is>
+          <t>911478162</t>
+        </is>
+      </c>
+      <c r="C149" s="23" t="inlineStr">
+        <is>
+          <t>91147816200017</t>
+        </is>
+      </c>
+      <c r="D149" s="22" t="inlineStr">
+        <is>
+          <t>TDC BAGEL</t>
+        </is>
+      </c>
+      <c r="E149" s="22" t="inlineStr">
+        <is>
+          <t>TDC BAGEL</t>
+        </is>
+      </c>
+      <c r="F149" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G149" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H149" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I149" s="22" t="inlineStr">
+        <is>
+          <t>15/03/2022</t>
+        </is>
+      </c>
+      <c r="J149" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K149" s="22" t="inlineStr">
+        <is>
+          <t>25 PLACE SAINT-JACQUES</t>
+        </is>
+      </c>
+      <c r="L149" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M149" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N149" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O149" s="22" t="inlineStr"/>
+      <c r="P149" s="22" t="inlineStr"/>
+      <c r="Q149" s="22" t="inlineStr"/>
+      <c r="R149" s="23" t="inlineStr"/>
+      <c r="S149" s="22" t="inlineStr"/>
+      <c r="T149" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U149" s="22" t="inlineStr">
+        <is>
+          <t>DARSCH</t>
+        </is>
+      </c>
+      <c r="V149" s="22" t="inlineStr">
+        <is>
+          <t>Audrey, Mélanie</t>
+        </is>
+      </c>
+      <c r="W149" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X149" s="22" t="inlineStr">
+        <is>
+          <t>16 Rue des Frères Lacretelle Appart 49</t>
+        </is>
+      </c>
+      <c r="Y149" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z149" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B150" s="23" t="inlineStr">
+        <is>
+          <t>831699053</t>
+        </is>
+      </c>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t>83169905300011</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="inlineStr">
+        <is>
+          <t>VERY GOOD</t>
+        </is>
+      </c>
+      <c r="E150" s="22" t="inlineStr">
+        <is>
+          <t>VERY GOOD</t>
+        </is>
+      </c>
+      <c r="F150" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G150" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H150" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I150" s="22" t="inlineStr">
+        <is>
+          <t>25/09/2017</t>
+        </is>
+      </c>
+      <c r="J150" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K150" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DES PARMENTIERS</t>
+        </is>
+      </c>
+      <c r="L150" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M150" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N150" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O150" s="22" t="inlineStr"/>
+      <c r="P150" s="22" t="inlineStr"/>
+      <c r="Q150" s="22" t="inlineStr"/>
+      <c r="R150" s="23" t="inlineStr"/>
+      <c r="S150" s="22" t="inlineStr"/>
+      <c r="T150" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U150" s="22" t="inlineStr">
+        <is>
+          <t>MINET</t>
+        </is>
+      </c>
+      <c r="V150" s="22" t="inlineStr">
+        <is>
+          <t>Stéphanie, Cécile</t>
+        </is>
+      </c>
+      <c r="W150" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X150" s="22" t="inlineStr">
+        <is>
+          <t>16 allée du Fort</t>
+        </is>
+      </c>
+      <c r="Y150" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z150" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Julien-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="inlineStr">
+        <is>
+          <t>951330232</t>
+        </is>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t>95133023200012</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="inlineStr">
+        <is>
+          <t>AK DENIZZ KEBAB</t>
+        </is>
+      </c>
+      <c r="E151" s="22" t="inlineStr">
+        <is>
+          <t>AK DENIZZ KEBAB</t>
+        </is>
+      </c>
+      <c r="F151" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G151" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I151" s="22" t="inlineStr">
+        <is>
+          <t>30/03/2023</t>
+        </is>
+      </c>
+      <c r="J151" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K151" s="22" t="inlineStr">
+        <is>
+          <t>228 AVENUE ANDRE MALRAUX</t>
+        </is>
+      </c>
+      <c r="L151" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M151" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N151" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O151" s="22" t="inlineStr"/>
+      <c r="P151" s="22" t="inlineStr"/>
+      <c r="Q151" s="22" t="inlineStr"/>
+      <c r="R151" s="23" t="inlineStr"/>
+      <c r="S151" s="22" t="inlineStr"/>
+      <c r="T151" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U151" s="22" t="inlineStr">
+        <is>
+          <t>GUL</t>
+        </is>
+      </c>
+      <c r="V151" s="22" t="inlineStr">
+        <is>
+          <t>Mustafa</t>
+        </is>
+      </c>
+      <c r="W151" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X151" s="22" t="inlineStr">
+        <is>
+          <t>226 Avenue André Malraux</t>
+        </is>
+      </c>
+      <c r="Y151" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z151" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B152" s="23" t="inlineStr">
+        <is>
+          <t>840500375</t>
+        </is>
+      </c>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t>84050037500018</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="inlineStr">
+        <is>
+          <t>F-MOZ</t>
+        </is>
+      </c>
+      <c r="E152" s="22" t="inlineStr">
+        <is>
+          <t>F-MOZ</t>
+        </is>
+      </c>
+      <c r="F152" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H152" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I152" s="22" t="inlineStr">
+        <is>
+          <t>20/06/2018</t>
+        </is>
+      </c>
+      <c r="J152" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K152" s="22" t="inlineStr">
+        <is>
+          <t>8 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L152" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M152" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N152" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O152" s="22" t="inlineStr"/>
+      <c r="P152" s="22" t="inlineStr"/>
+      <c r="Q152" s="22" t="inlineStr"/>
+      <c r="R152" s="23" t="inlineStr"/>
+      <c r="S152" s="22" t="inlineStr"/>
+      <c r="T152" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U152" s="22" t="inlineStr">
+        <is>
+          <t>EL BARNOUSSI</t>
+        </is>
+      </c>
+      <c r="V152" s="22" t="inlineStr">
+        <is>
+          <t>Zouhaïr</t>
+        </is>
+      </c>
+      <c r="W152" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X152" s="22" t="inlineStr">
+        <is>
+          <t>12 Boulevard de Provence</t>
+        </is>
+      </c>
+      <c r="Y152" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z152" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B153" s="23" t="inlineStr">
+        <is>
+          <t>811177609</t>
+        </is>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t>81117760900021</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="inlineStr">
+        <is>
+          <t>PIZZA &amp; CO</t>
+        </is>
+      </c>
+      <c r="E153" s="22" t="inlineStr">
+        <is>
+          <t>PIZZA &amp; CO</t>
+        </is>
+      </c>
+      <c r="F153" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G153" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H153" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I153" s="22" t="inlineStr">
+        <is>
+          <t>01/04/2015</t>
+        </is>
+      </c>
+      <c r="J153" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K153" s="22" t="inlineStr">
+        <is>
+          <t>30 RUE SAINT-JEAN</t>
+        </is>
+      </c>
+      <c r="L153" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M153" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N153" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O153" s="22" t="inlineStr"/>
+      <c r="P153" s="22" t="inlineStr"/>
+      <c r="Q153" s="22" t="inlineStr"/>
+      <c r="R153" s="23" t="inlineStr"/>
+      <c r="S153" s="22" t="inlineStr"/>
+      <c r="T153" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U153" s="22" t="inlineStr">
+        <is>
+          <t>KOCH</t>
+        </is>
+      </c>
+      <c r="V153" s="22" t="inlineStr">
+        <is>
+          <t>Jean-pierre</t>
+        </is>
+      </c>
+      <c r="W153" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X153" s="22" t="inlineStr">
+        <is>
+          <t>20 route de Briey</t>
+        </is>
+      </c>
+      <c r="Y153" s="23" t="inlineStr">
+        <is>
+          <t>57160</t>
+        </is>
+      </c>
+      <c r="Z153" s="22" t="inlineStr">
+        <is>
+          <t>Châtel-Saint-Germain</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B154" s="23" t="inlineStr">
+        <is>
+          <t>983329558</t>
+        </is>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>98332955800016</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>THIEBAUD PATRICK</t>
+        </is>
+      </c>
+      <c r="E154" s="22" t="inlineStr">
+        <is>
+          <t>THIEBAUD PATRICK</t>
+        </is>
+      </c>
+      <c r="F154" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G154" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H154" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I154" s="22" t="inlineStr">
+        <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="J154" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K154" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DE TOUL</t>
+        </is>
+      </c>
+      <c r="L154" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M154" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N154" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O154" s="22" t="inlineStr"/>
+      <c r="P154" s="22" t="inlineStr"/>
+      <c r="Q154" s="22" t="inlineStr"/>
+      <c r="R154" s="23" t="inlineStr"/>
+      <c r="S154" s="22" t="inlineStr"/>
+      <c r="T154" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U154" s="22" t="inlineStr">
+        <is>
+          <t>THIEBAUD</t>
+        </is>
+      </c>
+      <c r="V154" s="22" t="inlineStr">
+        <is>
+          <t>Patrick, Pierre</t>
+        </is>
+      </c>
+      <c r="W154" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X154" s="22" t="inlineStr"/>
+      <c r="Y154" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z154" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B155" s="23" t="inlineStr">
+        <is>
+          <t>994221810</t>
+        </is>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>99422181000017</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ SAM</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ SAM</t>
+        </is>
+      </c>
+      <c r="F155" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G155" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H155" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I155" s="22" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="J155" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K155" s="22" t="inlineStr">
+        <is>
+          <t>37 RUE DE LA CHAPELLE</t>
+        </is>
+      </c>
+      <c r="L155" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M155" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N155" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O155" s="22" t="inlineStr"/>
+      <c r="P155" s="22" t="inlineStr"/>
+      <c r="Q155" s="22" t="inlineStr"/>
+      <c r="R155" s="23" t="inlineStr"/>
+      <c r="S155" s="22" t="inlineStr"/>
+      <c r="T155" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U155" s="22" t="inlineStr">
+        <is>
+          <t>AHMAIDI</t>
+        </is>
+      </c>
+      <c r="V155" s="22" t="inlineStr">
+        <is>
+          <t>Amer</t>
+        </is>
+      </c>
+      <c r="W155" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X155" s="22" t="inlineStr"/>
+      <c r="Y155" s="23" t="inlineStr">
+        <is>
+          <t>57185</t>
+        </is>
+      </c>
+      <c r="Z155" s="22" t="inlineStr">
+        <is>
+          <t>Clouange</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B156" s="23" t="inlineStr">
+        <is>
+          <t>832238687</t>
+        </is>
+      </c>
+      <c r="C156" s="23" t="inlineStr">
+        <is>
+          <t>83223868700020</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="inlineStr">
+        <is>
+          <t>STLI</t>
+        </is>
+      </c>
+      <c r="E156" s="22" t="inlineStr">
+        <is>
+          <t>STLI</t>
+        </is>
+      </c>
+      <c r="F156" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G156" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H156" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="inlineStr">
+        <is>
+          <t>26/09/2017</t>
+        </is>
+      </c>
+      <c r="J156" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K156" s="22" t="inlineStr">
+        <is>
+          <t>9 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L156" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M156" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N156" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O156" s="22" t="inlineStr"/>
+      <c r="P156" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q156" s="22" t="inlineStr"/>
+      <c r="R156" s="23" t="inlineStr"/>
+      <c r="S156" s="22" t="inlineStr"/>
+      <c r="T156" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U156" s="22" t="inlineStr">
+        <is>
+          <t>TEITEN</t>
+        </is>
+      </c>
+      <c r="V156" s="22" t="inlineStr">
+        <is>
+          <t>Jean, Pierre</t>
+        </is>
+      </c>
+      <c r="W156" s="22" t="inlineStr">
+        <is>
+          <t>Directeur général</t>
+        </is>
+      </c>
+      <c r="X156" s="22" t="inlineStr">
+        <is>
+          <t>2 rue d'Asfeld</t>
+        </is>
+      </c>
+      <c r="Y156" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z156" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B157" s="23" t="inlineStr">
+        <is>
+          <t>449357169</t>
+        </is>
+      </c>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t>44935716900019</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="E157" s="22" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="F157" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G157" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H157" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I157" s="22" t="inlineStr">
+        <is>
+          <t>10/07/2003</t>
+        </is>
+      </c>
+      <c r="J157" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K157" s="22" t="inlineStr">
+        <is>
+          <t>20 RUE AUX OURS</t>
+        </is>
+      </c>
+      <c r="L157" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M157" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N157" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O157" s="22" t="inlineStr"/>
+      <c r="P157" s="22" t="inlineStr"/>
+      <c r="Q157" s="22" t="inlineStr"/>
+      <c r="R157" s="23" t="inlineStr"/>
+      <c r="S157" s="22" t="inlineStr"/>
+      <c r="T157" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U157" s="22" t="inlineStr">
+        <is>
+          <t>FAAS</t>
+        </is>
+      </c>
+      <c r="V157" s="22" t="inlineStr">
+        <is>
+          <t>Jocelyne, Annie</t>
+        </is>
+      </c>
+      <c r="W157" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X157" s="22" t="inlineStr">
+        <is>
+          <t>10 Allée du Haut des Chênes</t>
+        </is>
+      </c>
+      <c r="Y157" s="23" t="inlineStr">
+        <is>
+          <t>54210</t>
+        </is>
+      </c>
+      <c r="Z157" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Nicolas-de-Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B158" s="23" t="inlineStr">
+        <is>
+          <t>933343451</t>
+        </is>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>93334345100011</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="inlineStr">
+        <is>
+          <t>SAS A.N.</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="inlineStr">
+        <is>
+          <t>SAS A.N.</t>
+        </is>
+      </c>
+      <c r="F158" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G158" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H158" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I158" s="22" t="inlineStr">
+        <is>
+          <t>12/09/2024</t>
+        </is>
+      </c>
+      <c r="J158" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K158" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L158" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M158" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N158" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O158" s="22" t="inlineStr"/>
+      <c r="P158" s="22" t="inlineStr"/>
+      <c r="Q158" s="22" t="inlineStr"/>
+      <c r="R158" s="23" t="inlineStr"/>
+      <c r="S158" s="22" t="inlineStr"/>
+      <c r="T158" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U158" s="22" t="inlineStr">
+        <is>
+          <t>NICOLAS</t>
+        </is>
+      </c>
+      <c r="V158" s="22" t="inlineStr">
+        <is>
+          <t>Arnaud, Marie</t>
+        </is>
+      </c>
+      <c r="W158" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X158" s="22" t="inlineStr">
+        <is>
+          <t>25 chemin des grandes vignes</t>
+        </is>
+      </c>
+      <c r="Y158" s="23" t="inlineStr">
+        <is>
+          <t>57160</t>
+        </is>
+      </c>
+      <c r="Z158" s="22" t="inlineStr">
+        <is>
+          <t>Scy-Chazelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B159" s="23" t="inlineStr">
+        <is>
+          <t>880075791</t>
+        </is>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>88007579100017</t>
+        </is>
+      </c>
+      <c r="D159" s="22" t="inlineStr">
+        <is>
+          <t>VIVIAN'S PUB FAIRY</t>
+        </is>
+      </c>
+      <c r="E159" s="22" t="inlineStr">
+        <is>
+          <t>VIVIAN'S PUB FAIRY</t>
+        </is>
+      </c>
+      <c r="F159" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G159" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H159" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I159" s="22" t="inlineStr">
+        <is>
+          <t>21/11/2019</t>
+        </is>
+      </c>
+      <c r="J159" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K159" s="22" t="inlineStr">
+        <is>
+          <t>15 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L159" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M159" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N159" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O159" s="22" t="inlineStr"/>
+      <c r="P159" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q159" s="22" t="inlineStr"/>
+      <c r="R159" s="23" t="inlineStr"/>
+      <c r="S159" s="22" t="inlineStr"/>
+      <c r="T159" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U159" s="22" t="inlineStr">
+        <is>
+          <t>OLGA</t>
+        </is>
+      </c>
+      <c r="V159" s="22" t="inlineStr"/>
+      <c r="W159" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X159" s="22" t="inlineStr">
+        <is>
+          <t>15 place Saint-Louis</t>
+        </is>
+      </c>
+      <c r="Y159" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z159" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B160" s="23" t="inlineStr">
+        <is>
+          <t>437791270</t>
+        </is>
+      </c>
+      <c r="C160" s="23" t="inlineStr">
+        <is>
+          <t>43779127000022</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="inlineStr">
+        <is>
+          <t>KARAPOLAT</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="inlineStr">
+        <is>
+          <t>KARAPOLAT</t>
+        </is>
+      </c>
+      <c r="F160" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G160" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H160" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I160" s="22" t="inlineStr">
+        <is>
+          <t>02/05/2001</t>
+        </is>
+      </c>
+      <c r="J160" s="22" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="K160" s="22" t="inlineStr">
+        <is>
+          <t>18 AVENUE ROBERT SCHUMAN</t>
+        </is>
+      </c>
+      <c r="L160" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M160" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N160" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O160" s="22" t="n">
+        <v>260027</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q160" s="22" t="inlineStr"/>
+      <c r="R160" s="23" t="inlineStr"/>
+      <c r="S160" s="22" t="inlineStr"/>
+      <c r="T160" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U160" s="22" t="inlineStr">
+        <is>
+          <t>KARAPOLAT</t>
+        </is>
+      </c>
+      <c r="V160" s="22" t="inlineStr">
+        <is>
+          <t>Murat</t>
+        </is>
+      </c>
+      <c r="W160" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X160" s="22" t="inlineStr">
+        <is>
+          <t>209 avenue André Malraux</t>
+        </is>
+      </c>
+      <c r="Y160" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z160" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B161" s="23" t="inlineStr">
+        <is>
+          <t>991397373</t>
+        </is>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>99139737300010</t>
+        </is>
+      </c>
+      <c r="D161" s="22" t="inlineStr">
+        <is>
+          <t>RDJ</t>
+        </is>
+      </c>
+      <c r="E161" s="22" t="inlineStr">
+        <is>
+          <t>RDJ</t>
+        </is>
+      </c>
+      <c r="F161" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G161" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H161" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I161" s="22" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="J161" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K161" s="22" t="inlineStr">
+        <is>
+          <t>35 QUAI FELIX MARECHAL</t>
+        </is>
+      </c>
+      <c r="L161" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M161" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N161" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O161" s="22" t="inlineStr"/>
+      <c r="P161" s="22" t="inlineStr"/>
+      <c r="Q161" s="22" t="inlineStr"/>
+      <c r="R161" s="23" t="inlineStr"/>
+      <c r="S161" s="22" t="inlineStr"/>
+      <c r="T161" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U161" s="22" t="inlineStr">
+        <is>
+          <t>AHMED</t>
+        </is>
+      </c>
+      <c r="V161" s="22" t="inlineStr">
+        <is>
+          <t>Amer</t>
+        </is>
+      </c>
+      <c r="W161" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X161" s="22" t="inlineStr"/>
+      <c r="Y161" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="Z161" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B162" s="23" t="inlineStr">
+        <is>
+          <t>899724975</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>89972497500011</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="inlineStr">
+        <is>
+          <t>FUKUOKA</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="inlineStr">
+        <is>
+          <t>FUKUOKA</t>
+        </is>
+      </c>
+      <c r="F162" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G162" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H162" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I162" s="22" t="inlineStr">
+        <is>
+          <t>01/06/2021</t>
+        </is>
+      </c>
+      <c r="J162" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K162" s="22" t="inlineStr">
+        <is>
+          <t>11 RUE PASTEUR</t>
+        </is>
+      </c>
+      <c r="L162" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M162" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N162" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O162" s="22" t="inlineStr"/>
+      <c r="P162" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q162" s="22" t="inlineStr"/>
+      <c r="R162" s="23" t="inlineStr"/>
+      <c r="S162" s="22" t="inlineStr"/>
+      <c r="T162" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U162" s="22" t="inlineStr">
+        <is>
+          <t>ZHOU</t>
+        </is>
+      </c>
+      <c r="V162" s="22" t="inlineStr">
+        <is>
+          <t>Tirong</t>
+        </is>
+      </c>
+      <c r="W162" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X162" s="22" t="inlineStr">
+        <is>
+          <t>4 Allée Arthur Honegger</t>
+        </is>
+      </c>
+      <c r="Y162" s="23" t="inlineStr">
+        <is>
+          <t>93110</t>
+        </is>
+      </c>
+      <c r="Z162" s="22" t="inlineStr">
+        <is>
+          <t>Rosny-sous-Bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>880935937</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>88093593700024</t>
+        </is>
+      </c>
+      <c r="D163" s="22" t="inlineStr">
+        <is>
+          <t>MRC</t>
+        </is>
+      </c>
+      <c r="E163" s="22" t="inlineStr">
+        <is>
+          <t>MRC</t>
+        </is>
+      </c>
+      <c r="F163" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G163" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H163" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I163" s="22" t="inlineStr">
+        <is>
+          <t>20/01/2020</t>
+        </is>
+      </c>
+      <c r="J163" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K163" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L163" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M163" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N163" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O163" s="22" t="inlineStr"/>
+      <c r="P163" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q163" s="22" t="inlineStr"/>
+      <c r="R163" s="23" t="inlineStr"/>
+      <c r="S163" s="22" t="inlineStr"/>
+      <c r="T163" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U163" s="22" t="inlineStr">
+        <is>
+          <t>LUDWIG</t>
+        </is>
+      </c>
+      <c r="V163" s="22" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="W163" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X163" s="22" t="inlineStr">
+        <is>
+          <t>1A Rue Jeanne d'Arc</t>
+        </is>
+      </c>
+      <c r="Y163" s="23" t="inlineStr">
+        <is>
+          <t>57280</t>
+        </is>
+      </c>
+      <c r="Z163" s="22" t="inlineStr">
+        <is>
+          <t>Semécourt</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B164" s="23" t="inlineStr">
+        <is>
+          <t>933386880</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>93338688000027</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="inlineStr">
+        <is>
+          <t>SPICE ODYSSEY</t>
+        </is>
+      </c>
+      <c r="E164" s="22" t="inlineStr">
+        <is>
+          <t>SPICE ODYSSEY</t>
+        </is>
+      </c>
+      <c r="F164" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G164" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H164" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I164" s="22" t="inlineStr">
+        <is>
+          <t>19/09/2024</t>
+        </is>
+      </c>
+      <c r="J164" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K164" s="22" t="inlineStr">
+        <is>
+          <t>24 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L164" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M164" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N164" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O164" s="22" t="inlineStr"/>
+      <c r="P164" s="22" t="inlineStr"/>
+      <c r="Q164" s="22" t="inlineStr"/>
+      <c r="R164" s="23" t="inlineStr"/>
+      <c r="S164" s="22" t="inlineStr"/>
+      <c r="T164" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U164" s="22" t="inlineStr">
+        <is>
+          <t>KUHN</t>
+        </is>
+      </c>
+      <c r="V164" s="22" t="inlineStr">
+        <is>
+          <t>Tom, Louis</t>
+        </is>
+      </c>
+      <c r="W164" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X164" s="22" t="inlineStr"/>
+      <c r="Y164" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z164" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B165" s="23" t="inlineStr">
+        <is>
+          <t>922684048</t>
+        </is>
+      </c>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>92268404800015</t>
+        </is>
+      </c>
+      <c r="D165" s="22" t="inlineStr">
+        <is>
+          <t>LE BROOK</t>
+        </is>
+      </c>
+      <c r="E165" s="22" t="inlineStr">
+        <is>
+          <t>LE BROOK</t>
+        </is>
+      </c>
+      <c r="F165" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G165" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H165" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I165" s="22" t="inlineStr">
+        <is>
+          <t>03/01/2023</t>
+        </is>
+      </c>
+      <c r="J165" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K165" s="22" t="inlineStr">
+        <is>
+          <t>25 RUE DES ROCHES</t>
+        </is>
+      </c>
+      <c r="L165" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M165" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N165" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O165" s="22" t="inlineStr"/>
+      <c r="P165" s="22" t="inlineStr"/>
+      <c r="Q165" s="22" t="inlineStr"/>
+      <c r="R165" s="23" t="inlineStr"/>
+      <c r="S165" s="22" t="inlineStr"/>
+      <c r="T165" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U165" s="22" t="inlineStr">
+        <is>
+          <t>DI CARLO</t>
+        </is>
+      </c>
+      <c r="V165" s="22" t="inlineStr">
+        <is>
+          <t>Olivier, Claude</t>
+        </is>
+      </c>
+      <c r="W165" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X165" s="22" t="inlineStr">
+        <is>
+          <t>10 Rue Principale</t>
+        </is>
+      </c>
+      <c r="Y165" s="23" t="inlineStr">
+        <is>
+          <t>57640</t>
+        </is>
+      </c>
+      <c r="Z165" s="22" t="inlineStr">
+        <is>
+          <t>Servigny-lès-Sainte-Barbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B166" s="23" t="inlineStr">
+        <is>
+          <t>879957595</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>87995759500017</t>
+        </is>
+      </c>
+      <c r="D166" s="22" t="inlineStr">
+        <is>
+          <t>KYODAI RAMEN</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="inlineStr">
+        <is>
+          <t>KYODAI RAMEN</t>
+        </is>
+      </c>
+      <c r="F166" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G166" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H166" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I166" s="22" t="inlineStr">
+        <is>
+          <t>19/12/2019</t>
+        </is>
+      </c>
+      <c r="J166" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K166" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L166" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M166" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N166" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O166" s="22" t="inlineStr"/>
+      <c r="P166" s="22" t="inlineStr"/>
+      <c r="Q166" s="22" t="inlineStr"/>
+      <c r="R166" s="23" t="inlineStr"/>
+      <c r="S166" s="22" t="inlineStr"/>
+      <c r="T166" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U166" s="22" t="inlineStr">
+        <is>
+          <t>SUK</t>
+        </is>
+      </c>
+      <c r="V166" s="22" t="inlineStr">
+        <is>
+          <t>Laurent</t>
+        </is>
+      </c>
+      <c r="W166" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X166" s="22" t="inlineStr">
+        <is>
+          <t>7 Haute Rue</t>
+        </is>
+      </c>
+      <c r="Y166" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z166" s="22" t="inlineStr">
+        <is>
+          <t>Norroy-le-Veneur</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>817590185</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>81759018500010</t>
+        </is>
+      </c>
+      <c r="D167" s="22" t="inlineStr">
+        <is>
+          <t>BURGER KEBAB</t>
+        </is>
+      </c>
+      <c r="E167" s="22" t="inlineStr">
+        <is>
+          <t>BURGER KEBAB</t>
+        </is>
+      </c>
+      <c r="F167" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G167" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H167" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I167" s="22" t="inlineStr">
+        <is>
+          <t>27/11/2015</t>
+        </is>
+      </c>
+      <c r="J167" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K167" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L167" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M167" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N167" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O167" s="22" t="inlineStr"/>
+      <c r="P167" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q167" s="22" t="inlineStr"/>
+      <c r="R167" s="23" t="inlineStr"/>
+      <c r="S167" s="22" t="inlineStr"/>
+      <c r="T167" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U167" s="22" t="inlineStr">
+        <is>
+          <t>BILGEN</t>
+        </is>
+      </c>
+      <c r="V167" s="22" t="inlineStr">
+        <is>
+          <t>Engin</t>
+        </is>
+      </c>
+      <c r="W167" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X167" s="22" t="inlineStr">
+        <is>
+          <t>32 Rue du Grand Pré</t>
+        </is>
+      </c>
+      <c r="Y167" s="23" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="Z167" s="22" t="inlineStr">
+        <is>
+          <t>Marsilly</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z147"/>
+  <autoFilter ref="A2:Z167"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z167"/>
+  <dimension ref="A1:Z187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16994,2241 +16994,4493 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="22" t="inlineStr">
+      <c r="A148" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B148" s="23" t="inlineStr">
+      <c r="B148" s="21" t="inlineStr">
         <is>
           <t>852241488</t>
         </is>
       </c>
-      <c r="C148" s="23" t="inlineStr">
+      <c r="C148" s="21" t="inlineStr">
         <is>
           <t>85224148800018</t>
         </is>
       </c>
-      <c r="D148" s="22" t="inlineStr">
+      <c r="D148" s="20" t="inlineStr">
         <is>
           <t>CUREL</t>
         </is>
       </c>
-      <c r="E148" s="22" t="inlineStr">
+      <c r="E148" s="20" t="inlineStr">
         <is>
           <t>CUREL</t>
         </is>
       </c>
-      <c r="F148" s="22" t="inlineStr">
+      <c r="F148" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G148" s="22" t="inlineStr">
+      <c r="G148" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H148" s="22" t="inlineStr">
+      <c r="H148" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I148" s="22" t="inlineStr">
+      <c r="I148" s="20" t="inlineStr">
         <is>
           <t>24/05/2019</t>
         </is>
       </c>
-      <c r="J148" s="22" t="inlineStr">
+      <c r="J148" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K148" s="22" t="inlineStr">
+      <c r="K148" s="20" t="inlineStr">
         <is>
           <t>10 RUE FRANCOIS DE CUREL</t>
         </is>
       </c>
-      <c r="L148" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M148" s="22" t="inlineStr">
+      <c r="L148" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M148" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N148" s="22" t="inlineStr">
+      <c r="N148" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O148" s="22" t="inlineStr"/>
-      <c r="P148" s="22" t="inlineStr"/>
-      <c r="Q148" s="22" t="inlineStr"/>
-      <c r="R148" s="23" t="inlineStr"/>
-      <c r="S148" s="22" t="inlineStr"/>
-      <c r="T148" s="22" t="inlineStr">
+      <c r="O148" s="20" t="inlineStr"/>
+      <c r="P148" s="20" t="inlineStr"/>
+      <c r="Q148" s="20" t="inlineStr"/>
+      <c r="R148" s="21" t="inlineStr"/>
+      <c r="S148" s="20" t="inlineStr"/>
+      <c r="T148" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U148" s="22" t="inlineStr">
+      <c r="U148" s="20" t="inlineStr">
         <is>
           <t>BILGEN</t>
         </is>
       </c>
-      <c r="V148" s="22" t="inlineStr">
+      <c r="V148" s="20" t="inlineStr">
         <is>
           <t>Engin</t>
         </is>
       </c>
-      <c r="W148" s="22" t="inlineStr">
+      <c r="W148" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X148" s="22" t="inlineStr">
+      <c r="X148" s="20" t="inlineStr">
         <is>
           <t>32 Rue du Grand Pré</t>
         </is>
       </c>
-      <c r="Y148" s="23" t="inlineStr">
+      <c r="Y148" s="21" t="inlineStr">
         <is>
           <t>57530</t>
         </is>
       </c>
-      <c r="Z148" s="22" t="inlineStr">
+      <c r="Z148" s="20" t="inlineStr">
         <is>
           <t>Marsilly</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="22" t="inlineStr">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B149" s="23" t="inlineStr">
+      <c r="B149" s="21" t="inlineStr">
         <is>
           <t>911478162</t>
         </is>
       </c>
-      <c r="C149" s="23" t="inlineStr">
+      <c r="C149" s="21" t="inlineStr">
         <is>
           <t>91147816200017</t>
         </is>
       </c>
-      <c r="D149" s="22" t="inlineStr">
+      <c r="D149" s="20" t="inlineStr">
         <is>
           <t>TDC BAGEL</t>
         </is>
       </c>
-      <c r="E149" s="22" t="inlineStr">
+      <c r="E149" s="20" t="inlineStr">
         <is>
           <t>TDC BAGEL</t>
         </is>
       </c>
-      <c r="F149" s="22" t="inlineStr">
+      <c r="F149" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G149" s="22" t="inlineStr">
+      <c r="G149" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H149" s="22" t="inlineStr">
+      <c r="H149" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I149" s="22" t="inlineStr">
+      <c r="I149" s="20" t="inlineStr">
         <is>
           <t>15/03/2022</t>
         </is>
       </c>
-      <c r="J149" s="22" t="inlineStr">
+      <c r="J149" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K149" s="22" t="inlineStr">
+      <c r="K149" s="20" t="inlineStr">
         <is>
           <t>25 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="L149" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M149" s="22" t="inlineStr">
+      <c r="L149" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M149" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N149" s="22" t="inlineStr">
+      <c r="N149" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O149" s="22" t="inlineStr"/>
-      <c r="P149" s="22" t="inlineStr"/>
-      <c r="Q149" s="22" t="inlineStr"/>
-      <c r="R149" s="23" t="inlineStr"/>
-      <c r="S149" s="22" t="inlineStr"/>
-      <c r="T149" s="22" t="inlineStr">
+      <c r="O149" s="20" t="inlineStr"/>
+      <c r="P149" s="20" t="inlineStr"/>
+      <c r="Q149" s="20" t="inlineStr"/>
+      <c r="R149" s="21" t="inlineStr"/>
+      <c r="S149" s="20" t="inlineStr"/>
+      <c r="T149" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U149" s="22" t="inlineStr">
+      <c r="U149" s="20" t="inlineStr">
         <is>
           <t>DARSCH</t>
         </is>
       </c>
-      <c r="V149" s="22" t="inlineStr">
+      <c r="V149" s="20" t="inlineStr">
         <is>
           <t>Audrey, Mélanie</t>
         </is>
       </c>
-      <c r="W149" s="22" t="inlineStr">
+      <c r="W149" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X149" s="22" t="inlineStr">
+      <c r="X149" s="20" t="inlineStr">
         <is>
           <t>16 Rue des Frères Lacretelle Appart 49</t>
         </is>
       </c>
-      <c r="Y149" s="23" t="inlineStr">
+      <c r="Y149" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z149" s="22" t="inlineStr">
+      <c r="Z149" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="22" t="inlineStr">
+      <c r="A150" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B150" s="23" t="inlineStr">
+      <c r="B150" s="21" t="inlineStr">
         <is>
           <t>831699053</t>
         </is>
       </c>
-      <c r="C150" s="23" t="inlineStr">
+      <c r="C150" s="21" t="inlineStr">
         <is>
           <t>83169905300011</t>
         </is>
       </c>
-      <c r="D150" s="22" t="inlineStr">
+      <c r="D150" s="20" t="inlineStr">
         <is>
           <t>VERY GOOD</t>
         </is>
       </c>
-      <c r="E150" s="22" t="inlineStr">
+      <c r="E150" s="20" t="inlineStr">
         <is>
           <t>VERY GOOD</t>
         </is>
       </c>
-      <c r="F150" s="22" t="inlineStr">
+      <c r="F150" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G150" s="22" t="inlineStr">
+      <c r="G150" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H150" s="22" t="inlineStr">
+      <c r="H150" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I150" s="22" t="inlineStr">
+      <c r="I150" s="20" t="inlineStr">
         <is>
           <t>25/09/2017</t>
         </is>
       </c>
-      <c r="J150" s="22" t="inlineStr">
+      <c r="J150" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K150" s="22" t="inlineStr">
+      <c r="K150" s="20" t="inlineStr">
         <is>
           <t>1 RUE DES PARMENTIERS</t>
         </is>
       </c>
-      <c r="L150" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M150" s="22" t="inlineStr">
+      <c r="L150" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M150" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N150" s="22" t="inlineStr">
+      <c r="N150" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O150" s="22" t="inlineStr"/>
-      <c r="P150" s="22" t="inlineStr"/>
-      <c r="Q150" s="22" t="inlineStr"/>
-      <c r="R150" s="23" t="inlineStr"/>
-      <c r="S150" s="22" t="inlineStr"/>
-      <c r="T150" s="22" t="inlineStr">
+      <c r="O150" s="20" t="inlineStr"/>
+      <c r="P150" s="20" t="inlineStr"/>
+      <c r="Q150" s="20" t="inlineStr"/>
+      <c r="R150" s="21" t="inlineStr"/>
+      <c r="S150" s="20" t="inlineStr"/>
+      <c r="T150" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U150" s="22" t="inlineStr">
+      <c r="U150" s="20" t="inlineStr">
         <is>
           <t>MINET</t>
         </is>
       </c>
-      <c r="V150" s="22" t="inlineStr">
+      <c r="V150" s="20" t="inlineStr">
         <is>
           <t>Stéphanie, Cécile</t>
         </is>
       </c>
-      <c r="W150" s="22" t="inlineStr">
+      <c r="W150" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X150" s="22" t="inlineStr">
+      <c r="X150" s="20" t="inlineStr">
         <is>
           <t>16 allée du Fort</t>
         </is>
       </c>
-      <c r="Y150" s="23" t="inlineStr">
+      <c r="Y150" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z150" s="22" t="inlineStr">
+      <c r="Z150" s="20" t="inlineStr">
         <is>
           <t>Saint-Julien-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="22" t="inlineStr">
+      <c r="A151" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B151" s="23" t="inlineStr">
+      <c r="B151" s="21" t="inlineStr">
         <is>
           <t>951330232</t>
         </is>
       </c>
-      <c r="C151" s="23" t="inlineStr">
+      <c r="C151" s="21" t="inlineStr">
         <is>
           <t>95133023200012</t>
         </is>
       </c>
-      <c r="D151" s="22" t="inlineStr">
+      <c r="D151" s="20" t="inlineStr">
         <is>
           <t>AK DENIZZ KEBAB</t>
         </is>
       </c>
-      <c r="E151" s="22" t="inlineStr">
+      <c r="E151" s="20" t="inlineStr">
         <is>
           <t>AK DENIZZ KEBAB</t>
         </is>
       </c>
-      <c r="F151" s="22" t="inlineStr">
+      <c r="F151" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G151" s="22" t="inlineStr">
+      <c r="G151" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H151" s="22" t="inlineStr">
+      <c r="H151" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I151" s="22" t="inlineStr">
+      <c r="I151" s="20" t="inlineStr">
         <is>
           <t>30/03/2023</t>
         </is>
       </c>
-      <c r="J151" s="22" t="inlineStr">
+      <c r="J151" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K151" s="22" t="inlineStr">
+      <c r="K151" s="20" t="inlineStr">
         <is>
           <t>228 AVENUE ANDRE MALRAUX</t>
         </is>
       </c>
-      <c r="L151" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M151" s="22" t="inlineStr">
+      <c r="L151" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M151" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N151" s="22" t="inlineStr">
+      <c r="N151" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O151" s="22" t="inlineStr"/>
-      <c r="P151" s="22" t="inlineStr"/>
-      <c r="Q151" s="22" t="inlineStr"/>
-      <c r="R151" s="23" t="inlineStr"/>
-      <c r="S151" s="22" t="inlineStr"/>
-      <c r="T151" s="22" t="inlineStr">
+      <c r="O151" s="20" t="inlineStr"/>
+      <c r="P151" s="20" t="inlineStr"/>
+      <c r="Q151" s="20" t="inlineStr"/>
+      <c r="R151" s="21" t="inlineStr"/>
+      <c r="S151" s="20" t="inlineStr"/>
+      <c r="T151" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U151" s="22" t="inlineStr">
+      <c r="U151" s="20" t="inlineStr">
         <is>
           <t>GUL</t>
         </is>
       </c>
-      <c r="V151" s="22" t="inlineStr">
+      <c r="V151" s="20" t="inlineStr">
         <is>
           <t>Mustafa</t>
         </is>
       </c>
-      <c r="W151" s="22" t="inlineStr">
+      <c r="W151" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X151" s="22" t="inlineStr">
+      <c r="X151" s="20" t="inlineStr">
         <is>
           <t>226 Avenue André Malraux</t>
         </is>
       </c>
-      <c r="Y151" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z151" s="22" t="inlineStr">
+      <c r="Y151" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z151" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="22" t="inlineStr">
+      <c r="A152" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B152" s="23" t="inlineStr">
+      <c r="B152" s="21" t="inlineStr">
         <is>
           <t>840500375</t>
         </is>
       </c>
-      <c r="C152" s="23" t="inlineStr">
+      <c r="C152" s="21" t="inlineStr">
         <is>
           <t>84050037500018</t>
         </is>
       </c>
-      <c r="D152" s="22" t="inlineStr">
+      <c r="D152" s="20" t="inlineStr">
         <is>
           <t>F-MOZ</t>
         </is>
       </c>
-      <c r="E152" s="22" t="inlineStr">
+      <c r="E152" s="20" t="inlineStr">
         <is>
           <t>F-MOZ</t>
         </is>
       </c>
-      <c r="F152" s="22" t="inlineStr">
+      <c r="F152" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G152" s="22" t="inlineStr">
+      <c r="G152" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H152" s="22" t="inlineStr">
+      <c r="H152" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I152" s="22" t="inlineStr">
+      <c r="I152" s="20" t="inlineStr">
         <is>
           <t>20/06/2018</t>
         </is>
       </c>
-      <c r="J152" s="22" t="inlineStr">
+      <c r="J152" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K152" s="22" t="inlineStr">
+      <c r="K152" s="20" t="inlineStr">
         <is>
           <t>8 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L152" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M152" s="22" t="inlineStr">
+      <c r="L152" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M152" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N152" s="22" t="inlineStr">
+      <c r="N152" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O152" s="22" t="inlineStr"/>
-      <c r="P152" s="22" t="inlineStr"/>
-      <c r="Q152" s="22" t="inlineStr"/>
-      <c r="R152" s="23" t="inlineStr"/>
-      <c r="S152" s="22" t="inlineStr"/>
-      <c r="T152" s="22" t="inlineStr">
+      <c r="O152" s="20" t="inlineStr"/>
+      <c r="P152" s="20" t="inlineStr"/>
+      <c r="Q152" s="20" t="inlineStr"/>
+      <c r="R152" s="21" t="inlineStr"/>
+      <c r="S152" s="20" t="inlineStr"/>
+      <c r="T152" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U152" s="22" t="inlineStr">
+      <c r="U152" s="20" t="inlineStr">
         <is>
           <t>EL BARNOUSSI</t>
         </is>
       </c>
-      <c r="V152" s="22" t="inlineStr">
+      <c r="V152" s="20" t="inlineStr">
         <is>
           <t>Zouhaïr</t>
         </is>
       </c>
-      <c r="W152" s="22" t="inlineStr">
+      <c r="W152" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X152" s="22" t="inlineStr">
+      <c r="X152" s="20" t="inlineStr">
         <is>
           <t>12 Boulevard de Provence</t>
         </is>
       </c>
-      <c r="Y152" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z152" s="22" t="inlineStr">
+      <c r="Y152" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z152" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="22" t="inlineStr">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B153" s="23" t="inlineStr">
+      <c r="B153" s="21" t="inlineStr">
         <is>
           <t>811177609</t>
         </is>
       </c>
-      <c r="C153" s="23" t="inlineStr">
+      <c r="C153" s="21" t="inlineStr">
         <is>
           <t>81117760900021</t>
         </is>
       </c>
-      <c r="D153" s="22" t="inlineStr">
+      <c r="D153" s="20" t="inlineStr">
         <is>
           <t>PIZZA &amp; CO</t>
         </is>
       </c>
-      <c r="E153" s="22" t="inlineStr">
+      <c r="E153" s="20" t="inlineStr">
         <is>
           <t>PIZZA &amp; CO</t>
         </is>
       </c>
-      <c r="F153" s="22" t="inlineStr">
+      <c r="F153" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G153" s="22" t="inlineStr">
+      <c r="G153" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H153" s="22" t="inlineStr">
+      <c r="H153" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I153" s="22" t="inlineStr">
+      <c r="I153" s="20" t="inlineStr">
         <is>
           <t>01/04/2015</t>
         </is>
       </c>
-      <c r="J153" s="22" t="inlineStr">
+      <c r="J153" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K153" s="22" t="inlineStr">
+      <c r="K153" s="20" t="inlineStr">
         <is>
           <t>30 RUE SAINT-JEAN</t>
         </is>
       </c>
-      <c r="L153" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M153" s="22" t="inlineStr">
+      <c r="L153" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M153" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N153" s="22" t="inlineStr">
+      <c r="N153" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O153" s="22" t="inlineStr"/>
-      <c r="P153" s="22" t="inlineStr"/>
-      <c r="Q153" s="22" t="inlineStr"/>
-      <c r="R153" s="23" t="inlineStr"/>
-      <c r="S153" s="22" t="inlineStr"/>
-      <c r="T153" s="22" t="inlineStr">
+      <c r="O153" s="20" t="inlineStr"/>
+      <c r="P153" s="20" t="inlineStr"/>
+      <c r="Q153" s="20" t="inlineStr"/>
+      <c r="R153" s="21" t="inlineStr"/>
+      <c r="S153" s="20" t="inlineStr"/>
+      <c r="T153" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U153" s="22" t="inlineStr">
+      <c r="U153" s="20" t="inlineStr">
         <is>
           <t>KOCH</t>
         </is>
       </c>
-      <c r="V153" s="22" t="inlineStr">
+      <c r="V153" s="20" t="inlineStr">
         <is>
           <t>Jean-pierre</t>
         </is>
       </c>
-      <c r="W153" s="22" t="inlineStr">
+      <c r="W153" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X153" s="22" t="inlineStr">
+      <c r="X153" s="20" t="inlineStr">
         <is>
           <t>20 route de Briey</t>
         </is>
       </c>
-      <c r="Y153" s="23" t="inlineStr">
+      <c r="Y153" s="21" t="inlineStr">
         <is>
           <t>57160</t>
         </is>
       </c>
-      <c r="Z153" s="22" t="inlineStr">
+      <c r="Z153" s="20" t="inlineStr">
         <is>
           <t>Châtel-Saint-Germain</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="22" t="inlineStr">
+      <c r="A154" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B154" s="23" t="inlineStr">
+      <c r="B154" s="21" t="inlineStr">
         <is>
           <t>983329558</t>
         </is>
       </c>
-      <c r="C154" s="23" t="inlineStr">
+      <c r="C154" s="21" t="inlineStr">
         <is>
           <t>98332955800016</t>
         </is>
       </c>
-      <c r="D154" s="22" t="inlineStr">
+      <c r="D154" s="20" t="inlineStr">
         <is>
           <t>THIEBAUD PATRICK</t>
         </is>
       </c>
-      <c r="E154" s="22" t="inlineStr">
+      <c r="E154" s="20" t="inlineStr">
         <is>
           <t>THIEBAUD PATRICK</t>
         </is>
       </c>
-      <c r="F154" s="22" t="inlineStr">
+      <c r="F154" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G154" s="22" t="inlineStr">
+      <c r="G154" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H154" s="22" t="inlineStr">
+      <c r="H154" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I154" s="22" t="inlineStr">
+      <c r="I154" s="20" t="inlineStr">
         <is>
           <t>10/01/2024</t>
         </is>
       </c>
-      <c r="J154" s="22" t="inlineStr">
+      <c r="J154" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K154" s="22" t="inlineStr">
+      <c r="K154" s="20" t="inlineStr">
         <is>
           <t>2 RUE DE TOUL</t>
         </is>
       </c>
-      <c r="L154" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M154" s="22" t="inlineStr">
+      <c r="L154" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M154" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N154" s="22" t="inlineStr">
+      <c r="N154" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O154" s="22" t="inlineStr"/>
-      <c r="P154" s="22" t="inlineStr"/>
-      <c r="Q154" s="22" t="inlineStr"/>
-      <c r="R154" s="23" t="inlineStr"/>
-      <c r="S154" s="22" t="inlineStr"/>
-      <c r="T154" s="22" t="inlineStr">
+      <c r="O154" s="20" t="inlineStr"/>
+      <c r="P154" s="20" t="inlineStr"/>
+      <c r="Q154" s="20" t="inlineStr"/>
+      <c r="R154" s="21" t="inlineStr"/>
+      <c r="S154" s="20" t="inlineStr"/>
+      <c r="T154" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U154" s="22" t="inlineStr">
+      <c r="U154" s="20" t="inlineStr">
         <is>
           <t>THIEBAUD</t>
         </is>
       </c>
-      <c r="V154" s="22" t="inlineStr">
+      <c r="V154" s="20" t="inlineStr">
         <is>
           <t>Patrick, Pierre</t>
         </is>
       </c>
-      <c r="W154" s="22" t="inlineStr">
+      <c r="W154" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X154" s="22" t="inlineStr"/>
-      <c r="Y154" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z154" s="22" t="inlineStr">
+      <c r="X154" s="20" t="inlineStr"/>
+      <c r="Y154" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z154" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="22" t="inlineStr">
+      <c r="A155" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B155" s="23" t="inlineStr">
+      <c r="B155" s="21" t="inlineStr">
         <is>
           <t>994221810</t>
         </is>
       </c>
-      <c r="C155" s="23" t="inlineStr">
+      <c r="C155" s="21" t="inlineStr">
         <is>
           <t>99422181000017</t>
         </is>
       </c>
-      <c r="D155" s="22" t="inlineStr">
+      <c r="D155" s="20" t="inlineStr">
         <is>
           <t>CHEZ SAM</t>
         </is>
       </c>
-      <c r="E155" s="22" t="inlineStr">
+      <c r="E155" s="20" t="inlineStr">
         <is>
           <t>CHEZ SAM</t>
         </is>
       </c>
-      <c r="F155" s="22" t="inlineStr">
+      <c r="F155" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G155" s="22" t="inlineStr">
+      <c r="G155" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H155" s="22" t="inlineStr">
+      <c r="H155" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I155" s="22" t="inlineStr">
+      <c r="I155" s="20" t="inlineStr">
         <is>
           <t>24/09/2025</t>
         </is>
       </c>
-      <c r="J155" s="22" t="inlineStr">
+      <c r="J155" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K155" s="22" t="inlineStr">
+      <c r="K155" s="20" t="inlineStr">
         <is>
           <t>37 RUE DE LA CHAPELLE</t>
         </is>
       </c>
-      <c r="L155" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M155" s="22" t="inlineStr">
+      <c r="L155" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M155" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N155" s="22" t="inlineStr">
+      <c r="N155" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O155" s="22" t="inlineStr"/>
-      <c r="P155" s="22" t="inlineStr"/>
-      <c r="Q155" s="22" t="inlineStr"/>
-      <c r="R155" s="23" t="inlineStr"/>
-      <c r="S155" s="22" t="inlineStr"/>
-      <c r="T155" s="22" t="inlineStr">
+      <c r="O155" s="20" t="inlineStr"/>
+      <c r="P155" s="20" t="inlineStr"/>
+      <c r="Q155" s="20" t="inlineStr"/>
+      <c r="R155" s="21" t="inlineStr"/>
+      <c r="S155" s="20" t="inlineStr"/>
+      <c r="T155" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U155" s="22" t="inlineStr">
+      <c r="U155" s="20" t="inlineStr">
         <is>
           <t>AHMAIDI</t>
         </is>
       </c>
-      <c r="V155" s="22" t="inlineStr">
+      <c r="V155" s="20" t="inlineStr">
         <is>
           <t>Amer</t>
         </is>
       </c>
-      <c r="W155" s="22" t="inlineStr">
+      <c r="W155" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X155" s="22" t="inlineStr"/>
-      <c r="Y155" s="23" t="inlineStr">
+      <c r="X155" s="20" t="inlineStr"/>
+      <c r="Y155" s="21" t="inlineStr">
         <is>
           <t>57185</t>
         </is>
       </c>
-      <c r="Z155" s="22" t="inlineStr">
+      <c r="Z155" s="20" t="inlineStr">
         <is>
           <t>Clouange</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="22" t="inlineStr">
+      <c r="A156" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B156" s="23" t="inlineStr">
+      <c r="B156" s="21" t="inlineStr">
         <is>
           <t>832238687</t>
         </is>
       </c>
-      <c r="C156" s="23" t="inlineStr">
+      <c r="C156" s="21" t="inlineStr">
         <is>
           <t>83223868700020</t>
         </is>
       </c>
-      <c r="D156" s="22" t="inlineStr">
+      <c r="D156" s="20" t="inlineStr">
         <is>
           <t>STLI</t>
         </is>
       </c>
-      <c r="E156" s="22" t="inlineStr">
+      <c r="E156" s="20" t="inlineStr">
         <is>
           <t>STLI</t>
         </is>
       </c>
-      <c r="F156" s="22" t="inlineStr">
+      <c r="F156" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G156" s="22" t="inlineStr">
+      <c r="G156" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H156" s="22" t="inlineStr">
+      <c r="H156" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I156" s="22" t="inlineStr">
+      <c r="I156" s="20" t="inlineStr">
         <is>
           <t>26/09/2017</t>
         </is>
       </c>
-      <c r="J156" s="22" t="inlineStr">
+      <c r="J156" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K156" s="22" t="inlineStr">
+      <c r="K156" s="20" t="inlineStr">
         <is>
           <t>9 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L156" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M156" s="22" t="inlineStr">
+      <c r="L156" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M156" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N156" s="22" t="inlineStr">
+      <c r="N156" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O156" s="22" t="inlineStr"/>
-      <c r="P156" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q156" s="22" t="inlineStr"/>
-      <c r="R156" s="23" t="inlineStr"/>
-      <c r="S156" s="22" t="inlineStr"/>
-      <c r="T156" s="22" t="inlineStr">
+      <c r="O156" s="20" t="inlineStr"/>
+      <c r="P156" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q156" s="20" t="inlineStr"/>
+      <c r="R156" s="21" t="inlineStr"/>
+      <c r="S156" s="20" t="inlineStr"/>
+      <c r="T156" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U156" s="22" t="inlineStr">
+      <c r="U156" s="20" t="inlineStr">
         <is>
           <t>TEITEN</t>
         </is>
       </c>
-      <c r="V156" s="22" t="inlineStr">
+      <c r="V156" s="20" t="inlineStr">
         <is>
           <t>Jean, Pierre</t>
         </is>
       </c>
-      <c r="W156" s="22" t="inlineStr">
+      <c r="W156" s="20" t="inlineStr">
         <is>
           <t>Directeur général</t>
         </is>
       </c>
-      <c r="X156" s="22" t="inlineStr">
+      <c r="X156" s="20" t="inlineStr">
         <is>
           <t>2 rue d'Asfeld</t>
         </is>
       </c>
-      <c r="Y156" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z156" s="22" t="inlineStr">
+      <c r="Y156" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z156" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="22" t="inlineStr">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B157" s="23" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>449357169</t>
         </is>
       </c>
-      <c r="C157" s="23" t="inlineStr">
+      <c r="C157" s="21" t="inlineStr">
         <is>
           <t>44935716900019</t>
         </is>
       </c>
-      <c r="D157" s="22" t="inlineStr">
+      <c r="D157" s="20" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="E157" s="22" t="inlineStr">
+      <c r="E157" s="20" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="F157" s="22" t="inlineStr">
+      <c r="F157" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G157" s="22" t="inlineStr">
+      <c r="G157" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H157" s="22" t="inlineStr">
+      <c r="H157" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I157" s="22" t="inlineStr">
+      <c r="I157" s="20" t="inlineStr">
         <is>
           <t>10/07/2003</t>
         </is>
       </c>
-      <c r="J157" s="22" t="inlineStr">
+      <c r="J157" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K157" s="22" t="inlineStr">
+      <c r="K157" s="20" t="inlineStr">
         <is>
           <t>20 RUE AUX OURS</t>
         </is>
       </c>
-      <c r="L157" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M157" s="22" t="inlineStr">
+      <c r="L157" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M157" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N157" s="22" t="inlineStr">
+      <c r="N157" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O157" s="22" t="inlineStr"/>
-      <c r="P157" s="22" t="inlineStr"/>
-      <c r="Q157" s="22" t="inlineStr"/>
-      <c r="R157" s="23" t="inlineStr"/>
-      <c r="S157" s="22" t="inlineStr"/>
-      <c r="T157" s="22" t="inlineStr">
+      <c r="O157" s="20" t="inlineStr"/>
+      <c r="P157" s="20" t="inlineStr"/>
+      <c r="Q157" s="20" t="inlineStr"/>
+      <c r="R157" s="21" t="inlineStr"/>
+      <c r="S157" s="20" t="inlineStr"/>
+      <c r="T157" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U157" s="22" t="inlineStr">
+      <c r="U157" s="20" t="inlineStr">
         <is>
           <t>FAAS</t>
         </is>
       </c>
-      <c r="V157" s="22" t="inlineStr">
+      <c r="V157" s="20" t="inlineStr">
         <is>
           <t>Jocelyne, Annie</t>
         </is>
       </c>
-      <c r="W157" s="22" t="inlineStr">
+      <c r="W157" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X157" s="22" t="inlineStr">
+      <c r="X157" s="20" t="inlineStr">
         <is>
           <t>10 Allée du Haut des Chênes</t>
         </is>
       </c>
-      <c r="Y157" s="23" t="inlineStr">
+      <c r="Y157" s="21" t="inlineStr">
         <is>
           <t>54210</t>
         </is>
       </c>
-      <c r="Z157" s="22" t="inlineStr">
+      <c r="Z157" s="20" t="inlineStr">
         <is>
           <t>Saint-Nicolas-de-Port</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="22" t="inlineStr">
+      <c r="A158" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B158" s="23" t="inlineStr">
+      <c r="B158" s="21" t="inlineStr">
         <is>
           <t>933343451</t>
         </is>
       </c>
-      <c r="C158" s="23" t="inlineStr">
+      <c r="C158" s="21" t="inlineStr">
         <is>
           <t>93334345100011</t>
         </is>
       </c>
-      <c r="D158" s="22" t="inlineStr">
+      <c r="D158" s="20" t="inlineStr">
         <is>
           <t>SAS A.N.</t>
         </is>
       </c>
-      <c r="E158" s="22" t="inlineStr">
+      <c r="E158" s="20" t="inlineStr">
         <is>
           <t>SAS A.N.</t>
         </is>
       </c>
-      <c r="F158" s="22" t="inlineStr">
+      <c r="F158" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G158" s="22" t="inlineStr">
+      <c r="G158" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H158" s="22" t="inlineStr">
+      <c r="H158" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I158" s="22" t="inlineStr">
+      <c r="I158" s="20" t="inlineStr">
         <is>
           <t>12/09/2024</t>
         </is>
       </c>
-      <c r="J158" s="22" t="inlineStr">
+      <c r="J158" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K158" s="22" t="inlineStr">
+      <c r="K158" s="20" t="inlineStr">
         <is>
           <t>1 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L158" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M158" s="22" t="inlineStr">
+      <c r="L158" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M158" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N158" s="22" t="inlineStr">
+      <c r="N158" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O158" s="22" t="inlineStr"/>
-      <c r="P158" s="22" t="inlineStr"/>
-      <c r="Q158" s="22" t="inlineStr"/>
-      <c r="R158" s="23" t="inlineStr"/>
-      <c r="S158" s="22" t="inlineStr"/>
-      <c r="T158" s="22" t="inlineStr">
+      <c r="O158" s="20" t="inlineStr"/>
+      <c r="P158" s="20" t="inlineStr"/>
+      <c r="Q158" s="20" t="inlineStr"/>
+      <c r="R158" s="21" t="inlineStr"/>
+      <c r="S158" s="20" t="inlineStr"/>
+      <c r="T158" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U158" s="22" t="inlineStr">
+      <c r="U158" s="20" t="inlineStr">
         <is>
           <t>NICOLAS</t>
         </is>
       </c>
-      <c r="V158" s="22" t="inlineStr">
+      <c r="V158" s="20" t="inlineStr">
         <is>
           <t>Arnaud, Marie</t>
         </is>
       </c>
-      <c r="W158" s="22" t="inlineStr">
+      <c r="W158" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X158" s="22" t="inlineStr">
+      <c r="X158" s="20" t="inlineStr">
         <is>
           <t>25 chemin des grandes vignes</t>
         </is>
       </c>
-      <c r="Y158" s="23" t="inlineStr">
+      <c r="Y158" s="21" t="inlineStr">
         <is>
           <t>57160</t>
         </is>
       </c>
-      <c r="Z158" s="22" t="inlineStr">
+      <c r="Z158" s="20" t="inlineStr">
         <is>
           <t>Scy-Chazelles</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="22" t="inlineStr">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B159" s="23" t="inlineStr">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>880075791</t>
         </is>
       </c>
-      <c r="C159" s="23" t="inlineStr">
+      <c r="C159" s="21" t="inlineStr">
         <is>
           <t>88007579100017</t>
         </is>
       </c>
-      <c r="D159" s="22" t="inlineStr">
+      <c r="D159" s="20" t="inlineStr">
         <is>
           <t>VIVIAN'S PUB FAIRY</t>
         </is>
       </c>
-      <c r="E159" s="22" t="inlineStr">
+      <c r="E159" s="20" t="inlineStr">
         <is>
           <t>VIVIAN'S PUB FAIRY</t>
         </is>
       </c>
-      <c r="F159" s="22" t="inlineStr">
+      <c r="F159" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G159" s="22" t="inlineStr">
+      <c r="G159" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H159" s="22" t="inlineStr">
+      <c r="H159" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I159" s="22" t="inlineStr">
+      <c r="I159" s="20" t="inlineStr">
         <is>
           <t>21/11/2019</t>
         </is>
       </c>
-      <c r="J159" s="22" t="inlineStr">
+      <c r="J159" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K159" s="22" t="inlineStr">
+      <c r="K159" s="20" t="inlineStr">
         <is>
           <t>15 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L159" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M159" s="22" t="inlineStr">
+      <c r="L159" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M159" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N159" s="22" t="inlineStr">
+      <c r="N159" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O159" s="22" t="inlineStr"/>
-      <c r="P159" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q159" s="22" t="inlineStr"/>
-      <c r="R159" s="23" t="inlineStr"/>
-      <c r="S159" s="22" t="inlineStr"/>
-      <c r="T159" s="22" t="inlineStr">
+      <c r="O159" s="20" t="inlineStr"/>
+      <c r="P159" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q159" s="20" t="inlineStr"/>
+      <c r="R159" s="21" t="inlineStr"/>
+      <c r="S159" s="20" t="inlineStr"/>
+      <c r="T159" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U159" s="22" t="inlineStr">
+      <c r="U159" s="20" t="inlineStr">
         <is>
           <t>OLGA</t>
         </is>
       </c>
-      <c r="V159" s="22" t="inlineStr"/>
-      <c r="W159" s="22" t="inlineStr">
+      <c r="V159" s="20" t="inlineStr"/>
+      <c r="W159" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X159" s="22" t="inlineStr">
+      <c r="X159" s="20" t="inlineStr">
         <is>
           <t>15 place Saint-Louis</t>
         </is>
       </c>
-      <c r="Y159" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z159" s="22" t="inlineStr">
+      <c r="Y159" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z159" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="22" t="inlineStr">
+      <c r="A160" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B160" s="23" t="inlineStr">
+      <c r="B160" s="21" t="inlineStr">
         <is>
           <t>437791270</t>
         </is>
       </c>
-      <c r="C160" s="23" t="inlineStr">
+      <c r="C160" s="21" t="inlineStr">
         <is>
           <t>43779127000022</t>
         </is>
       </c>
-      <c r="D160" s="22" t="inlineStr">
+      <c r="D160" s="20" t="inlineStr">
         <is>
           <t>KARAPOLAT</t>
         </is>
       </c>
-      <c r="E160" s="22" t="inlineStr">
+      <c r="E160" s="20" t="inlineStr">
         <is>
           <t>KARAPOLAT</t>
         </is>
       </c>
-      <c r="F160" s="22" t="inlineStr">
+      <c r="F160" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G160" s="22" t="inlineStr">
+      <c r="G160" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H160" s="22" t="inlineStr">
+      <c r="H160" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I160" s="22" t="inlineStr">
+      <c r="I160" s="20" t="inlineStr">
         <is>
           <t>02/05/2001</t>
         </is>
       </c>
-      <c r="J160" s="22" t="inlineStr">
+      <c r="J160" s="20" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="K160" s="22" t="inlineStr">
+      <c r="K160" s="20" t="inlineStr">
         <is>
           <t>18 AVENUE ROBERT SCHUMAN</t>
         </is>
       </c>
-      <c r="L160" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M160" s="22" t="inlineStr">
+      <c r="L160" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M160" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N160" s="22" t="inlineStr">
+      <c r="N160" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O160" s="22" t="n">
-        <v>260027</v>
-      </c>
-      <c r="P160" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q160" s="22" t="inlineStr"/>
-      <c r="R160" s="23" t="inlineStr"/>
-      <c r="S160" s="22" t="inlineStr"/>
-      <c r="T160" s="22" t="inlineStr">
+      <c r="O160" s="20" t="inlineStr">
+        <is>
+          <t>260027</t>
+        </is>
+      </c>
+      <c r="P160" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q160" s="20" t="inlineStr"/>
+      <c r="R160" s="21" t="inlineStr"/>
+      <c r="S160" s="20" t="inlineStr"/>
+      <c r="T160" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U160" s="22" t="inlineStr">
+      <c r="U160" s="20" t="inlineStr">
         <is>
           <t>KARAPOLAT</t>
         </is>
       </c>
-      <c r="V160" s="22" t="inlineStr">
+      <c r="V160" s="20" t="inlineStr">
         <is>
           <t>Murat</t>
         </is>
       </c>
-      <c r="W160" s="22" t="inlineStr">
+      <c r="W160" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X160" s="22" t="inlineStr">
+      <c r="X160" s="20" t="inlineStr">
         <is>
           <t>209 avenue André Malraux</t>
         </is>
       </c>
-      <c r="Y160" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z160" s="22" t="inlineStr">
+      <c r="Y160" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z160" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="22" t="inlineStr">
+      <c r="A161" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B161" s="23" t="inlineStr">
+      <c r="B161" s="21" t="inlineStr">
         <is>
           <t>991397373</t>
         </is>
       </c>
-      <c r="C161" s="23" t="inlineStr">
+      <c r="C161" s="21" t="inlineStr">
         <is>
           <t>99139737300010</t>
         </is>
       </c>
-      <c r="D161" s="22" t="inlineStr">
+      <c r="D161" s="20" t="inlineStr">
         <is>
           <t>RDJ</t>
         </is>
       </c>
-      <c r="E161" s="22" t="inlineStr">
+      <c r="E161" s="20" t="inlineStr">
         <is>
           <t>RDJ</t>
         </is>
       </c>
-      <c r="F161" s="22" t="inlineStr">
+      <c r="F161" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G161" s="22" t="inlineStr">
+      <c r="G161" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H161" s="22" t="inlineStr">
+      <c r="H161" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I161" s="22" t="inlineStr">
+      <c r="I161" s="20" t="inlineStr">
         <is>
           <t>11/07/2025</t>
         </is>
       </c>
-      <c r="J161" s="22" t="inlineStr">
+      <c r="J161" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K161" s="22" t="inlineStr">
+      <c r="K161" s="20" t="inlineStr">
         <is>
           <t>35 QUAI FELIX MARECHAL</t>
         </is>
       </c>
-      <c r="L161" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M161" s="22" t="inlineStr">
+      <c r="L161" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M161" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N161" s="22" t="inlineStr">
+      <c r="N161" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O161" s="22" t="inlineStr"/>
-      <c r="P161" s="22" t="inlineStr"/>
-      <c r="Q161" s="22" t="inlineStr"/>
-      <c r="R161" s="23" t="inlineStr"/>
-      <c r="S161" s="22" t="inlineStr"/>
-      <c r="T161" s="22" t="inlineStr">
+      <c r="O161" s="20" t="inlineStr"/>
+      <c r="P161" s="20" t="inlineStr"/>
+      <c r="Q161" s="20" t="inlineStr"/>
+      <c r="R161" s="21" t="inlineStr"/>
+      <c r="S161" s="20" t="inlineStr"/>
+      <c r="T161" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U161" s="22" t="inlineStr">
+      <c r="U161" s="20" t="inlineStr">
         <is>
           <t>AHMED</t>
         </is>
       </c>
-      <c r="V161" s="22" t="inlineStr">
+      <c r="V161" s="20" t="inlineStr">
         <is>
           <t>Amer</t>
         </is>
       </c>
-      <c r="W161" s="22" t="inlineStr">
+      <c r="W161" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X161" s="22" t="inlineStr"/>
-      <c r="Y161" s="23" t="inlineStr">
+      <c r="X161" s="20" t="inlineStr"/>
+      <c r="Y161" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="Z161" s="22" t="inlineStr">
+      <c r="Z161" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="22" t="inlineStr">
+      <c r="A162" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B162" s="23" t="inlineStr">
+      <c r="B162" s="21" t="inlineStr">
         <is>
           <t>899724975</t>
         </is>
       </c>
-      <c r="C162" s="23" t="inlineStr">
+      <c r="C162" s="21" t="inlineStr">
         <is>
           <t>89972497500011</t>
         </is>
       </c>
-      <c r="D162" s="22" t="inlineStr">
+      <c r="D162" s="20" t="inlineStr">
         <is>
           <t>FUKUOKA</t>
         </is>
       </c>
-      <c r="E162" s="22" t="inlineStr">
+      <c r="E162" s="20" t="inlineStr">
         <is>
           <t>FUKUOKA</t>
         </is>
       </c>
-      <c r="F162" s="22" t="inlineStr">
+      <c r="F162" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G162" s="22" t="inlineStr">
+      <c r="G162" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H162" s="22" t="inlineStr">
+      <c r="H162" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I162" s="22" t="inlineStr">
+      <c r="I162" s="20" t="inlineStr">
         <is>
           <t>01/06/2021</t>
         </is>
       </c>
-      <c r="J162" s="22" t="inlineStr">
+      <c r="J162" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K162" s="22" t="inlineStr">
+      <c r="K162" s="20" t="inlineStr">
         <is>
           <t>11 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="L162" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M162" s="22" t="inlineStr">
+      <c r="L162" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M162" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N162" s="22" t="inlineStr">
+      <c r="N162" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O162" s="22" t="inlineStr"/>
-      <c r="P162" s="22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q162" s="22" t="inlineStr"/>
-      <c r="R162" s="23" t="inlineStr"/>
-      <c r="S162" s="22" t="inlineStr"/>
-      <c r="T162" s="22" t="inlineStr">
+      <c r="O162" s="20" t="inlineStr"/>
+      <c r="P162" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q162" s="20" t="inlineStr"/>
+      <c r="R162" s="21" t="inlineStr"/>
+      <c r="S162" s="20" t="inlineStr"/>
+      <c r="T162" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U162" s="22" t="inlineStr">
+      <c r="U162" s="20" t="inlineStr">
         <is>
           <t>ZHOU</t>
         </is>
       </c>
-      <c r="V162" s="22" t="inlineStr">
+      <c r="V162" s="20" t="inlineStr">
         <is>
           <t>Tirong</t>
         </is>
       </c>
-      <c r="W162" s="22" t="inlineStr">
+      <c r="W162" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X162" s="22" t="inlineStr">
+      <c r="X162" s="20" t="inlineStr">
         <is>
           <t>4 Allée Arthur Honegger</t>
         </is>
       </c>
-      <c r="Y162" s="23" t="inlineStr">
+      <c r="Y162" s="21" t="inlineStr">
         <is>
           <t>93110</t>
         </is>
       </c>
-      <c r="Z162" s="22" t="inlineStr">
+      <c r="Z162" s="20" t="inlineStr">
         <is>
           <t>Rosny-sous-Bois</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="22" t="inlineStr">
+      <c r="A163" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B163" s="23" t="inlineStr">
+      <c r="B163" s="21" t="inlineStr">
         <is>
           <t>880935937</t>
         </is>
       </c>
-      <c r="C163" s="23" t="inlineStr">
+      <c r="C163" s="21" t="inlineStr">
         <is>
           <t>88093593700024</t>
         </is>
       </c>
-      <c r="D163" s="22" t="inlineStr">
+      <c r="D163" s="20" t="inlineStr">
         <is>
           <t>MRC</t>
         </is>
       </c>
-      <c r="E163" s="22" t="inlineStr">
+      <c r="E163" s="20" t="inlineStr">
         <is>
           <t>MRC</t>
         </is>
       </c>
-      <c r="F163" s="22" t="inlineStr">
+      <c r="F163" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G163" s="22" t="inlineStr">
+      <c r="G163" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H163" s="22" t="inlineStr">
+      <c r="H163" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I163" s="22" t="inlineStr">
+      <c r="I163" s="20" t="inlineStr">
         <is>
           <t>20/01/2020</t>
         </is>
       </c>
-      <c r="J163" s="22" t="inlineStr">
+      <c r="J163" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K163" s="22" t="inlineStr">
+      <c r="K163" s="20" t="inlineStr">
         <is>
           <t>10 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L163" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M163" s="22" t="inlineStr">
+      <c r="L163" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M163" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N163" s="22" t="inlineStr">
+      <c r="N163" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O163" s="22" t="inlineStr"/>
-      <c r="P163" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q163" s="22" t="inlineStr"/>
-      <c r="R163" s="23" t="inlineStr"/>
-      <c r="S163" s="22" t="inlineStr"/>
-      <c r="T163" s="22" t="inlineStr">
+      <c r="O163" s="20" t="inlineStr"/>
+      <c r="P163" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q163" s="20" t="inlineStr"/>
+      <c r="R163" s="21" t="inlineStr"/>
+      <c r="S163" s="20" t="inlineStr"/>
+      <c r="T163" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U163" s="22" t="inlineStr">
+      <c r="U163" s="20" t="inlineStr">
         <is>
           <t>LUDWIG</t>
         </is>
       </c>
-      <c r="V163" s="22" t="inlineStr">
+      <c r="V163" s="20" t="inlineStr">
         <is>
           <t>Marine</t>
         </is>
       </c>
-      <c r="W163" s="22" t="inlineStr">
+      <c r="W163" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X163" s="22" t="inlineStr">
+      <c r="X163" s="20" t="inlineStr">
         <is>
           <t>1A Rue Jeanne d'Arc</t>
         </is>
       </c>
-      <c r="Y163" s="23" t="inlineStr">
+      <c r="Y163" s="21" t="inlineStr">
         <is>
           <t>57280</t>
         </is>
       </c>
-      <c r="Z163" s="22" t="inlineStr">
+      <c r="Z163" s="20" t="inlineStr">
         <is>
           <t>Semécourt</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="22" t="inlineStr">
+      <c r="A164" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B164" s="23" t="inlineStr">
+      <c r="B164" s="21" t="inlineStr">
         <is>
           <t>933386880</t>
         </is>
       </c>
-      <c r="C164" s="23" t="inlineStr">
+      <c r="C164" s="21" t="inlineStr">
         <is>
           <t>93338688000027</t>
         </is>
       </c>
-      <c r="D164" s="22" t="inlineStr">
+      <c r="D164" s="20" t="inlineStr">
         <is>
           <t>SPICE ODYSSEY</t>
         </is>
       </c>
-      <c r="E164" s="22" t="inlineStr">
+      <c r="E164" s="20" t="inlineStr">
         <is>
           <t>SPICE ODYSSEY</t>
         </is>
       </c>
-      <c r="F164" s="22" t="inlineStr">
+      <c r="F164" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G164" s="22" t="inlineStr">
+      <c r="G164" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H164" s="22" t="inlineStr">
+      <c r="H164" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I164" s="22" t="inlineStr">
+      <c r="I164" s="20" t="inlineStr">
         <is>
           <t>19/09/2024</t>
         </is>
       </c>
-      <c r="J164" s="22" t="inlineStr">
+      <c r="J164" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K164" s="22" t="inlineStr">
+      <c r="K164" s="20" t="inlineStr">
         <is>
           <t>24 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L164" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M164" s="22" t="inlineStr">
+      <c r="L164" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M164" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N164" s="22" t="inlineStr">
+      <c r="N164" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O164" s="22" t="inlineStr"/>
-      <c r="P164" s="22" t="inlineStr"/>
-      <c r="Q164" s="22" t="inlineStr"/>
-      <c r="R164" s="23" t="inlineStr"/>
-      <c r="S164" s="22" t="inlineStr"/>
-      <c r="T164" s="22" t="inlineStr">
+      <c r="O164" s="20" t="inlineStr"/>
+      <c r="P164" s="20" t="inlineStr"/>
+      <c r="Q164" s="20" t="inlineStr"/>
+      <c r="R164" s="21" t="inlineStr"/>
+      <c r="S164" s="20" t="inlineStr"/>
+      <c r="T164" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U164" s="22" t="inlineStr">
+      <c r="U164" s="20" t="inlineStr">
         <is>
           <t>KUHN</t>
         </is>
       </c>
-      <c r="V164" s="22" t="inlineStr">
+      <c r="V164" s="20" t="inlineStr">
         <is>
           <t>Tom, Louis</t>
         </is>
       </c>
-      <c r="W164" s="22" t="inlineStr">
+      <c r="W164" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X164" s="22" t="inlineStr"/>
-      <c r="Y164" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z164" s="22" t="inlineStr">
+      <c r="X164" s="20" t="inlineStr"/>
+      <c r="Y164" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z164" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="22" t="inlineStr">
+      <c r="A165" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B165" s="23" t="inlineStr">
+      <c r="B165" s="21" t="inlineStr">
         <is>
           <t>922684048</t>
         </is>
       </c>
-      <c r="C165" s="23" t="inlineStr">
+      <c r="C165" s="21" t="inlineStr">
         <is>
           <t>92268404800015</t>
         </is>
       </c>
-      <c r="D165" s="22" t="inlineStr">
+      <c r="D165" s="20" t="inlineStr">
         <is>
           <t>LE BROOK</t>
         </is>
       </c>
-      <c r="E165" s="22" t="inlineStr">
+      <c r="E165" s="20" t="inlineStr">
         <is>
           <t>LE BROOK</t>
         </is>
       </c>
-      <c r="F165" s="22" t="inlineStr">
+      <c r="F165" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G165" s="22" t="inlineStr">
+      <c r="G165" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H165" s="22" t="inlineStr">
+      <c r="H165" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I165" s="22" t="inlineStr">
+      <c r="I165" s="20" t="inlineStr">
         <is>
           <t>03/01/2023</t>
         </is>
       </c>
-      <c r="J165" s="22" t="inlineStr">
+      <c r="J165" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K165" s="22" t="inlineStr">
+      <c r="K165" s="20" t="inlineStr">
         <is>
           <t>25 RUE DES ROCHES</t>
         </is>
       </c>
-      <c r="L165" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M165" s="22" t="inlineStr">
+      <c r="L165" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M165" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N165" s="22" t="inlineStr">
+      <c r="N165" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O165" s="22" t="inlineStr"/>
-      <c r="P165" s="22" t="inlineStr"/>
-      <c r="Q165" s="22" t="inlineStr"/>
-      <c r="R165" s="23" t="inlineStr"/>
-      <c r="S165" s="22" t="inlineStr"/>
-      <c r="T165" s="22" t="inlineStr">
+      <c r="O165" s="20" t="inlineStr"/>
+      <c r="P165" s="20" t="inlineStr"/>
+      <c r="Q165" s="20" t="inlineStr"/>
+      <c r="R165" s="21" t="inlineStr"/>
+      <c r="S165" s="20" t="inlineStr"/>
+      <c r="T165" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U165" s="22" t="inlineStr">
+      <c r="U165" s="20" t="inlineStr">
         <is>
           <t>DI CARLO</t>
         </is>
       </c>
-      <c r="V165" s="22" t="inlineStr">
+      <c r="V165" s="20" t="inlineStr">
         <is>
           <t>Olivier, Claude</t>
         </is>
       </c>
-      <c r="W165" s="22" t="inlineStr">
+      <c r="W165" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X165" s="22" t="inlineStr">
+      <c r="X165" s="20" t="inlineStr">
         <is>
           <t>10 Rue Principale</t>
         </is>
       </c>
-      <c r="Y165" s="23" t="inlineStr">
+      <c r="Y165" s="21" t="inlineStr">
         <is>
           <t>57640</t>
         </is>
       </c>
-      <c r="Z165" s="22" t="inlineStr">
+      <c r="Z165" s="20" t="inlineStr">
         <is>
           <t>Servigny-lès-Sainte-Barbe</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="22" t="inlineStr">
+      <c r="A166" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B166" s="23" t="inlineStr">
+      <c r="B166" s="21" t="inlineStr">
         <is>
           <t>879957595</t>
         </is>
       </c>
-      <c r="C166" s="23" t="inlineStr">
+      <c r="C166" s="21" t="inlineStr">
         <is>
           <t>87995759500017</t>
         </is>
       </c>
-      <c r="D166" s="22" t="inlineStr">
+      <c r="D166" s="20" t="inlineStr">
         <is>
           <t>KYODAI RAMEN</t>
         </is>
       </c>
-      <c r="E166" s="22" t="inlineStr">
+      <c r="E166" s="20" t="inlineStr">
         <is>
           <t>KYODAI RAMEN</t>
         </is>
       </c>
-      <c r="F166" s="22" t="inlineStr">
+      <c r="F166" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G166" s="22" t="inlineStr">
+      <c r="G166" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H166" s="22" t="inlineStr">
+      <c r="H166" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I166" s="22" t="inlineStr">
+      <c r="I166" s="20" t="inlineStr">
         <is>
           <t>19/12/2019</t>
         </is>
       </c>
-      <c r="J166" s="22" t="inlineStr">
+      <c r="J166" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K166" s="22" t="inlineStr">
+      <c r="K166" s="20" t="inlineStr">
         <is>
           <t>9 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L166" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M166" s="22" t="inlineStr">
+      <c r="L166" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M166" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N166" s="22" t="inlineStr">
+      <c r="N166" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O166" s="22" t="inlineStr"/>
-      <c r="P166" s="22" t="inlineStr"/>
-      <c r="Q166" s="22" t="inlineStr"/>
-      <c r="R166" s="23" t="inlineStr"/>
-      <c r="S166" s="22" t="inlineStr"/>
-      <c r="T166" s="22" t="inlineStr">
+      <c r="O166" s="20" t="inlineStr"/>
+      <c r="P166" s="20" t="inlineStr"/>
+      <c r="Q166" s="20" t="inlineStr"/>
+      <c r="R166" s="21" t="inlineStr"/>
+      <c r="S166" s="20" t="inlineStr"/>
+      <c r="T166" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U166" s="22" t="inlineStr">
+      <c r="U166" s="20" t="inlineStr">
         <is>
           <t>SUK</t>
         </is>
       </c>
-      <c r="V166" s="22" t="inlineStr">
+      <c r="V166" s="20" t="inlineStr">
         <is>
           <t>Laurent</t>
         </is>
       </c>
-      <c r="W166" s="22" t="inlineStr">
+      <c r="W166" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X166" s="22" t="inlineStr">
+      <c r="X166" s="20" t="inlineStr">
         <is>
           <t>7 Haute Rue</t>
         </is>
       </c>
-      <c r="Y166" s="23" t="inlineStr">
+      <c r="Y166" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z166" s="22" t="inlineStr">
+      <c r="Z166" s="20" t="inlineStr">
         <is>
           <t>Norroy-le-Veneur</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="22" t="inlineStr">
+      <c r="A167" s="20" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B167" s="23" t="inlineStr">
+      <c r="B167" s="21" t="inlineStr">
         <is>
           <t>817590185</t>
         </is>
       </c>
-      <c r="C167" s="23" t="inlineStr">
+      <c r="C167" s="21" t="inlineStr">
         <is>
           <t>81759018500010</t>
         </is>
       </c>
-      <c r="D167" s="22" t="inlineStr">
+      <c r="D167" s="20" t="inlineStr">
         <is>
           <t>BURGER KEBAB</t>
         </is>
       </c>
-      <c r="E167" s="22" t="inlineStr">
+      <c r="E167" s="20" t="inlineStr">
         <is>
           <t>BURGER KEBAB</t>
         </is>
       </c>
-      <c r="F167" s="22" t="inlineStr">
+      <c r="F167" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G167" s="22" t="inlineStr">
+      <c r="G167" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H167" s="22" t="inlineStr">
+      <c r="H167" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I167" s="22" t="inlineStr">
+      <c r="I167" s="20" t="inlineStr">
         <is>
           <t>27/11/2015</t>
         </is>
       </c>
-      <c r="J167" s="22" t="inlineStr">
+      <c r="J167" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K167" s="22" t="inlineStr">
+      <c r="K167" s="20" t="inlineStr">
         <is>
           <t>5 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L167" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M167" s="22" t="inlineStr">
+      <c r="L167" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M167" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N167" s="22" t="inlineStr">
+      <c r="N167" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O167" s="22" t="inlineStr"/>
-      <c r="P167" s="22" t="n">
+      <c r="O167" s="20" t="inlineStr"/>
+      <c r="P167" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q167" s="20" t="inlineStr"/>
+      <c r="R167" s="21" t="inlineStr"/>
+      <c r="S167" s="20" t="inlineStr"/>
+      <c r="T167" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U167" s="20" t="inlineStr">
+        <is>
+          <t>BILGEN</t>
+        </is>
+      </c>
+      <c r="V167" s="20" t="inlineStr">
+        <is>
+          <t>Engin</t>
+        </is>
+      </c>
+      <c r="W167" s="20" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X167" s="20" t="inlineStr">
+        <is>
+          <t>32 Rue du Grand Pré</t>
+        </is>
+      </c>
+      <c r="Y167" s="21" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="Z167" s="20" t="inlineStr">
+        <is>
+          <t>Marsilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B168" s="23" t="inlineStr">
+        <is>
+          <t>884397282</t>
+        </is>
+      </c>
+      <c r="C168" s="23" t="inlineStr">
+        <is>
+          <t>88439728200010</t>
+        </is>
+      </c>
+      <c r="D168" s="22" t="inlineStr">
+        <is>
+          <t>B&amp;D FOOD</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="inlineStr">
+        <is>
+          <t>B&amp;D FOOD</t>
+        </is>
+      </c>
+      <c r="F168" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G168" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H168" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I168" s="22" t="inlineStr">
+        <is>
+          <t>01/06/2020</t>
+        </is>
+      </c>
+      <c r="J168" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K168" s="22" t="inlineStr">
+        <is>
+          <t>20 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L168" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M168" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N168" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O168" s="22" t="inlineStr"/>
+      <c r="P168" s="22" t="inlineStr"/>
+      <c r="Q168" s="22" t="inlineStr"/>
+      <c r="R168" s="23" t="inlineStr"/>
+      <c r="S168" s="22" t="inlineStr"/>
+      <c r="T168" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U168" s="22" t="inlineStr">
+        <is>
+          <t>SAYEH</t>
+        </is>
+      </c>
+      <c r="V168" s="22" t="inlineStr">
+        <is>
+          <t>Issam</t>
+        </is>
+      </c>
+      <c r="W168" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X168" s="22" t="inlineStr">
+        <is>
+          <t>38 Rue de Verdun</t>
+        </is>
+      </c>
+      <c r="Y168" s="23" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="Z168" s="22" t="inlineStr">
+        <is>
+          <t>Thionville</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>912319654</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>91231965400014</t>
+        </is>
+      </c>
+      <c r="D169" s="22" t="inlineStr">
+        <is>
+          <t>PIZZA PALMA SAS</t>
+        </is>
+      </c>
+      <c r="E169" s="22" t="inlineStr">
+        <is>
+          <t>PIZZA PALMA SAS</t>
+        </is>
+      </c>
+      <c r="F169" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G169" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H169" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I169" s="22" t="inlineStr">
+        <is>
+          <t>11/04/2022</t>
+        </is>
+      </c>
+      <c r="J169" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K169" s="22" t="inlineStr">
+        <is>
+          <t>33 BOULEVARD PAIXHANS</t>
+        </is>
+      </c>
+      <c r="L169" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M169" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N169" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O169" s="22" t="inlineStr"/>
+      <c r="P169" s="22" t="inlineStr"/>
+      <c r="Q169" s="22" t="inlineStr"/>
+      <c r="R169" s="23" t="inlineStr"/>
+      <c r="S169" s="22" t="inlineStr"/>
+      <c r="T169" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U169" s="22" t="inlineStr">
+        <is>
+          <t>AIT KHOUYA</t>
+        </is>
+      </c>
+      <c r="V169" s="22" t="inlineStr">
+        <is>
+          <t>Ammar</t>
+        </is>
+      </c>
+      <c r="W169" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X169" s="22" t="inlineStr">
+        <is>
+          <t>9 Rue Henri Bergson</t>
+        </is>
+      </c>
+      <c r="Y169" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z169" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B170" s="23" t="inlineStr">
+        <is>
+          <t>979176484</t>
+        </is>
+      </c>
+      <c r="C170" s="23" t="inlineStr">
+        <is>
+          <t>97917648400017</t>
+        </is>
+      </c>
+      <c r="D170" s="22" t="inlineStr">
+        <is>
+          <t>O&amp;J BURGER</t>
+        </is>
+      </c>
+      <c r="E170" s="22" t="inlineStr">
+        <is>
+          <t>O&amp;J BURGER</t>
+        </is>
+      </c>
+      <c r="F170" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G170" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H170" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I170" s="22" t="inlineStr">
+        <is>
+          <t>05/08/2023</t>
+        </is>
+      </c>
+      <c r="J170" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K170" s="22" t="inlineStr">
+        <is>
+          <t>7 EN FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="L170" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M170" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N170" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O170" s="22" t="inlineStr"/>
+      <c r="P170" s="22" t="inlineStr"/>
+      <c r="Q170" s="22" t="inlineStr"/>
+      <c r="R170" s="23" t="inlineStr"/>
+      <c r="S170" s="22" t="inlineStr"/>
+      <c r="T170" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U170" s="22" t="inlineStr">
+        <is>
+          <t>CHENH</t>
+        </is>
+      </c>
+      <c r="V170" s="22" t="inlineStr">
+        <is>
+          <t>Jason, Ji, Kin</t>
+        </is>
+      </c>
+      <c r="W170" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X170" s="22" t="inlineStr"/>
+      <c r="Y170" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z170" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B171" s="23" t="inlineStr">
+        <is>
+          <t>817735848</t>
+        </is>
+      </c>
+      <c r="C171" s="23" t="inlineStr">
+        <is>
+          <t>81773584800019</t>
+        </is>
+      </c>
+      <c r="D171" s="22" t="inlineStr">
+        <is>
+          <t>SASU UMUT</t>
+        </is>
+      </c>
+      <c r="E171" s="22" t="inlineStr">
+        <is>
+          <t>SASU UMUT</t>
+        </is>
+      </c>
+      <c r="F171" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H171" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I171" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2015</t>
+        </is>
+      </c>
+      <c r="J171" s="22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K171" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L171" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M171" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N171" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O171" s="22" t="inlineStr"/>
+      <c r="P171" s="22" t="inlineStr"/>
+      <c r="Q171" s="22" t="inlineStr"/>
+      <c r="R171" s="23" t="inlineStr"/>
+      <c r="S171" s="22" t="inlineStr"/>
+      <c r="T171" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U171" s="22" t="inlineStr">
+        <is>
+          <t>DUGENCI</t>
+        </is>
+      </c>
+      <c r="V171" s="22" t="inlineStr">
+        <is>
+          <t>Suleyman</t>
+        </is>
+      </c>
+      <c r="W171" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X171" s="22" t="inlineStr">
+        <is>
+          <t>2 rue Jean-Adolf Lasaulce</t>
+        </is>
+      </c>
+      <c r="Y171" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z171" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B172" s="23" t="inlineStr">
+        <is>
+          <t>990733776</t>
+        </is>
+      </c>
+      <c r="C172" s="23" t="inlineStr">
+        <is>
+          <t>99073377600027</t>
+        </is>
+      </c>
+      <c r="D172" s="22" t="inlineStr">
+        <is>
+          <t>SAS AUX DELICES CAPRICIEUX</t>
+        </is>
+      </c>
+      <c r="E172" s="22" t="inlineStr">
+        <is>
+          <t>SAS AUX DELICES CAPRICIEUX</t>
+        </is>
+      </c>
+      <c r="F172" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G172" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H172" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I172" s="22" t="inlineStr">
+        <is>
+          <t>16/07/2025</t>
+        </is>
+      </c>
+      <c r="J172" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K172" s="22" t="inlineStr">
+        <is>
+          <t>26 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L172" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M172" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N172" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O172" s="22" t="inlineStr"/>
+      <c r="P172" s="22" t="inlineStr"/>
+      <c r="Q172" s="22" t="inlineStr"/>
+      <c r="R172" s="23" t="inlineStr"/>
+      <c r="S172" s="22" t="inlineStr"/>
+      <c r="T172" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U172" s="22" t="inlineStr">
+        <is>
+          <t>DEMUTH</t>
+        </is>
+      </c>
+      <c r="V172" s="22" t="inlineStr">
+        <is>
+          <t>Jean-marc</t>
+        </is>
+      </c>
+      <c r="W172" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X172" s="22" t="inlineStr">
+        <is>
+          <t>156 rue d'edling</t>
+        </is>
+      </c>
+      <c r="Y172" s="23" t="inlineStr">
+        <is>
+          <t>57320</t>
+        </is>
+      </c>
+      <c r="Z172" s="22" t="inlineStr">
+        <is>
+          <t>Anzeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B173" s="23" t="inlineStr">
+        <is>
+          <t>922700430</t>
+        </is>
+      </c>
+      <c r="C173" s="23" t="inlineStr">
+        <is>
+          <t>92270043000015</t>
+        </is>
+      </c>
+      <c r="D173" s="22" t="inlineStr">
+        <is>
+          <t>MEET TEA</t>
+        </is>
+      </c>
+      <c r="E173" s="22" t="inlineStr">
+        <is>
+          <t>MEET TEA</t>
+        </is>
+      </c>
+      <c r="F173" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G173" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H173" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I173" s="22" t="inlineStr">
+        <is>
+          <t>14/11/2022</t>
+        </is>
+      </c>
+      <c r="J173" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K173" s="22" t="inlineStr">
+        <is>
+          <t>40 EN CHAPLERUE</t>
+        </is>
+      </c>
+      <c r="L173" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M173" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N173" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O173" s="22" t="inlineStr"/>
+      <c r="P173" s="22" t="inlineStr"/>
+      <c r="Q173" s="22" t="inlineStr"/>
+      <c r="R173" s="23" t="inlineStr"/>
+      <c r="S173" s="22" t="inlineStr"/>
+      <c r="T173" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U173" s="22" t="inlineStr">
+        <is>
+          <t>ZHANG</t>
+        </is>
+      </c>
+      <c r="V173" s="22" t="inlineStr">
+        <is>
+          <t>Qing</t>
+        </is>
+      </c>
+      <c r="W173" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X173" s="22" t="inlineStr">
+        <is>
+          <t>162 Grande rue</t>
+        </is>
+      </c>
+      <c r="Y173" s="23" t="inlineStr">
+        <is>
+          <t>93000</t>
+        </is>
+      </c>
+      <c r="Z173" s="22" t="inlineStr">
+        <is>
+          <t>Bobigny</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B174" s="23" t="inlineStr">
+        <is>
+          <t>508607488</t>
+        </is>
+      </c>
+      <c r="C174" s="23" t="inlineStr">
+        <is>
+          <t>50860748800022</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>BMT FINANCES</t>
+        </is>
+      </c>
+      <c r="E174" s="22" t="inlineStr">
+        <is>
+          <t>BMT FINANCES</t>
+        </is>
+      </c>
+      <c r="F174" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G174" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H174" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I174" s="22" t="inlineStr">
+        <is>
+          <t>17/10/2008</t>
+        </is>
+      </c>
+      <c r="J174" s="22" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K174" s="22" t="inlineStr">
+        <is>
+          <t>24 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L174" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M174" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N174" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O174" s="22" t="inlineStr"/>
+      <c r="P174" s="22" t="inlineStr"/>
+      <c r="Q174" s="22" t="inlineStr"/>
+      <c r="R174" s="23" t="inlineStr"/>
+      <c r="S174" s="22" t="inlineStr"/>
+      <c r="T174" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U174" s="22" t="inlineStr">
+        <is>
+          <t>TAFFNER</t>
+        </is>
+      </c>
+      <c r="V174" s="22" t="inlineStr">
+        <is>
+          <t>Blaise</t>
+        </is>
+      </c>
+      <c r="W174" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X174" s="22" t="inlineStr">
+        <is>
+          <t>4 rue Georges Robinson</t>
+        </is>
+      </c>
+      <c r="Y174" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z174" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B175" s="23" t="inlineStr">
+        <is>
+          <t>934099813</t>
+        </is>
+      </c>
+      <c r="C175" s="23" t="inlineStr">
+        <is>
+          <t>93409981300016</t>
+        </is>
+      </c>
+      <c r="D175" s="22" t="inlineStr">
+        <is>
+          <t>KABUL 2</t>
+        </is>
+      </c>
+      <c r="E175" s="22" t="inlineStr">
+        <is>
+          <t>KABUL 2</t>
+        </is>
+      </c>
+      <c r="F175" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G175" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H175" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I175" s="22" t="inlineStr">
+        <is>
+          <t>07/10/2024</t>
+        </is>
+      </c>
+      <c r="J175" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K175" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE DU NEUFBOURG</t>
+        </is>
+      </c>
+      <c r="L175" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M175" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N175" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O175" s="22" t="inlineStr"/>
+      <c r="P175" s="22" t="inlineStr"/>
+      <c r="Q175" s="22" t="inlineStr"/>
+      <c r="R175" s="23" t="inlineStr"/>
+      <c r="S175" s="22" t="inlineStr"/>
+      <c r="T175" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U175" s="22" t="inlineStr">
+        <is>
+          <t>ALOKOZAY</t>
+        </is>
+      </c>
+      <c r="V175" s="22" t="inlineStr">
+        <is>
+          <t>Sawab</t>
+        </is>
+      </c>
+      <c r="W175" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X175" s="22" t="inlineStr">
+        <is>
+          <t>8 d rue pépin le bref</t>
+        </is>
+      </c>
+      <c r="Y175" s="23" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="Z175" s="22" t="inlineStr">
+        <is>
+          <t>Thionville</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B176" s="23" t="inlineStr">
+        <is>
+          <t>919654962</t>
+        </is>
+      </c>
+      <c r="C176" s="23" t="inlineStr">
+        <is>
+          <t>91965496200019</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>ANNA</t>
+        </is>
+      </c>
+      <c r="E176" s="22" t="inlineStr">
+        <is>
+          <t>ANNA</t>
+        </is>
+      </c>
+      <c r="F176" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G176" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H176" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I176" s="22" t="inlineStr">
+        <is>
+          <t>30/09/2022</t>
+        </is>
+      </c>
+      <c r="J176" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K176" s="22" t="inlineStr">
+        <is>
+          <t>61 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L176" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M176" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N176" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O176" s="22" t="inlineStr"/>
+      <c r="P176" s="22" t="inlineStr"/>
+      <c r="Q176" s="22" t="inlineStr"/>
+      <c r="R176" s="23" t="inlineStr"/>
+      <c r="S176" s="22" t="inlineStr"/>
+      <c r="T176" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U176" s="22" t="inlineStr">
+        <is>
+          <t>REZAOUI</t>
+        </is>
+      </c>
+      <c r="V176" s="22" t="inlineStr">
+        <is>
+          <t>Tarik</t>
+        </is>
+      </c>
+      <c r="W176" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X176" s="22" t="inlineStr">
+        <is>
+          <t>23 rue de la Marne</t>
+        </is>
+      </c>
+      <c r="Y176" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z176" s="22" t="inlineStr">
+        <is>
+          <t>Le Ban-Saint-Martin</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B177" s="23" t="inlineStr">
+        <is>
+          <t>925068710</t>
+        </is>
+      </c>
+      <c r="C177" s="23" t="inlineStr">
+        <is>
+          <t>92506871000019</t>
+        </is>
+      </c>
+      <c r="D177" s="22" t="inlineStr">
+        <is>
+          <t>SFV</t>
+        </is>
+      </c>
+      <c r="E177" s="22" t="inlineStr">
+        <is>
+          <t>SFV</t>
+        </is>
+      </c>
+      <c r="F177" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G177" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H177" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I177" s="22" t="inlineStr">
+        <is>
+          <t>28/03/2024</t>
+        </is>
+      </c>
+      <c r="J177" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K177" s="22" t="inlineStr">
+        <is>
+          <t>7 B RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L177" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M177" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N177" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O177" s="22" t="inlineStr"/>
+      <c r="P177" s="22" t="inlineStr"/>
+      <c r="Q177" s="22" t="inlineStr"/>
+      <c r="R177" s="23" t="inlineStr"/>
+      <c r="S177" s="22" t="inlineStr"/>
+      <c r="T177" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U177" s="22" t="inlineStr">
+        <is>
+          <t>FREYERMUTH</t>
+        </is>
+      </c>
+      <c r="V177" s="22" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="W177" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X177" s="22" t="inlineStr"/>
+      <c r="Y177" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z177" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B178" s="23" t="inlineStr">
+        <is>
+          <t>850625724</t>
+        </is>
+      </c>
+      <c r="C178" s="23" t="inlineStr">
+        <is>
+          <t>85062572400024</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>GRAMOPHONE</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="inlineStr">
+        <is>
+          <t>GRAMOPHONE</t>
+        </is>
+      </c>
+      <c r="F178" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G178" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H178" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I178" s="22" t="inlineStr">
+        <is>
+          <t>09/05/2019</t>
+        </is>
+      </c>
+      <c r="J178" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K178" s="22" t="inlineStr">
+        <is>
+          <t>35 PLACE SAINT-JACQUES</t>
+        </is>
+      </c>
+      <c r="L178" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M178" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N178" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O178" s="22" t="inlineStr"/>
+      <c r="P178" s="22" t="inlineStr"/>
+      <c r="Q178" s="22" t="inlineStr"/>
+      <c r="R178" s="23" t="inlineStr"/>
+      <c r="S178" s="22" t="inlineStr"/>
+      <c r="T178" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U178" s="22" t="inlineStr">
+        <is>
+          <t>LENNINGER</t>
+        </is>
+      </c>
+      <c r="V178" s="22" t="inlineStr">
+        <is>
+          <t>Sébastien</t>
+        </is>
+      </c>
+      <c r="W178" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X178" s="22" t="inlineStr">
+        <is>
+          <t>20 Rue Jean Mermoz</t>
+        </is>
+      </c>
+      <c r="Y178" s="23" t="inlineStr">
+        <is>
+          <t>57970</t>
+        </is>
+      </c>
+      <c r="Z178" s="22" t="inlineStr">
+        <is>
+          <t>Yutz</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B179" s="23" t="inlineStr">
+        <is>
+          <t>524992765</t>
+        </is>
+      </c>
+      <c r="C179" s="23" t="inlineStr">
+        <is>
+          <t>52499276500023</t>
+        </is>
+      </c>
+      <c r="D179" s="22" t="inlineStr">
+        <is>
+          <t>I LOVE</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="inlineStr">
+        <is>
+          <t>I LOVE</t>
+        </is>
+      </c>
+      <c r="F179" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H179" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I179" s="22" t="inlineStr">
+        <is>
+          <t>20/09/2010</t>
+        </is>
+      </c>
+      <c r="J179" s="22" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K179" s="22" t="inlineStr">
+        <is>
+          <t>4 PLACE PHILIPPE DE VIGNEULLES</t>
+        </is>
+      </c>
+      <c r="L179" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M179" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N179" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O179" s="22" t="inlineStr"/>
+      <c r="P179" s="22" t="inlineStr"/>
+      <c r="Q179" s="22" t="inlineStr"/>
+      <c r="R179" s="23" t="inlineStr"/>
+      <c r="S179" s="22" t="inlineStr"/>
+      <c r="T179" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U179" s="22" t="inlineStr">
+        <is>
+          <t>LONGHI</t>
+        </is>
+      </c>
+      <c r="V179" s="22" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="W179" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X179" s="22" t="inlineStr">
+        <is>
+          <t>4 place Philippe de Vigneulles</t>
+        </is>
+      </c>
+      <c r="Y179" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z179" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B180" s="23" t="inlineStr">
+        <is>
+          <t>425078383</t>
+        </is>
+      </c>
+      <c r="C180" s="23" t="inlineStr">
+        <is>
+          <t>42507838300030</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="inlineStr">
+        <is>
+          <t>SARL L'HYPPODROME</t>
+        </is>
+      </c>
+      <c r="E180" s="22" t="inlineStr">
+        <is>
+          <t>SARL L'HYPPODROME</t>
+        </is>
+      </c>
+      <c r="F180" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G180" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H180" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I180" s="22" t="inlineStr">
+        <is>
+          <t>21/10/1999</t>
+        </is>
+      </c>
+      <c r="J180" s="22" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="K180" s="22" t="inlineStr">
+        <is>
+          <t>31 PLACE DU QUARTEAU</t>
+        </is>
+      </c>
+      <c r="L180" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M180" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N180" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O180" s="22" t="n">
+        <v>116768</v>
+      </c>
+      <c r="P180" s="22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="Q180" s="22" t="inlineStr"/>
+      <c r="R180" s="23" t="inlineStr"/>
+      <c r="S180" s="22" t="inlineStr"/>
+      <c r="T180" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U180" s="22" t="inlineStr">
+        <is>
+          <t>BONK</t>
+        </is>
+      </c>
+      <c r="V180" s="22" t="inlineStr">
+        <is>
+          <t>Pierre, Edmond</t>
+        </is>
+      </c>
+      <c r="W180" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X180" s="22" t="inlineStr">
+        <is>
+          <t>1 Rue Saint-Livier</t>
+        </is>
+      </c>
+      <c r="Y180" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z180" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B181" s="23" t="inlineStr">
+        <is>
+          <t>807447941</t>
+        </is>
+      </c>
+      <c r="C181" s="23" t="inlineStr">
+        <is>
+          <t>80744794100012</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="inlineStr">
+        <is>
+          <t>Aux Paraiges</t>
+        </is>
+      </c>
+      <c r="E181" s="22" t="inlineStr">
+        <is>
+          <t>Aux Paraiges</t>
+        </is>
+      </c>
+      <c r="F181" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G181" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H181" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I181" s="22" t="inlineStr">
+        <is>
+          <t>15/11/2014</t>
+        </is>
+      </c>
+      <c r="J181" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K181" s="22" t="inlineStr">
+        <is>
+          <t>27 RUE DU CHANGE</t>
+        </is>
+      </c>
+      <c r="L181" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M181" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N181" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O181" s="22" t="inlineStr"/>
+      <c r="P181" s="22" t="n">
         <v>2023</v>
       </c>
-      <c r="Q167" s="22" t="inlineStr"/>
-      <c r="R167" s="23" t="inlineStr"/>
-      <c r="S167" s="22" t="inlineStr"/>
-      <c r="T167" s="22" t="inlineStr">
+      <c r="Q181" s="22" t="inlineStr"/>
+      <c r="R181" s="23" t="inlineStr"/>
+      <c r="S181" s="22" t="inlineStr"/>
+      <c r="T181" s="22" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U167" s="22" t="inlineStr">
-        <is>
-          <t>BILGEN</t>
-        </is>
-      </c>
-      <c r="V167" s="22" t="inlineStr">
-        <is>
-          <t>Engin</t>
-        </is>
-      </c>
-      <c r="W167" s="22" t="inlineStr">
+      <c r="U181" s="22" t="inlineStr">
+        <is>
+          <t>TRABAND</t>
+        </is>
+      </c>
+      <c r="V181" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas, Gerard, Charles, Andre</t>
+        </is>
+      </c>
+      <c r="W181" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X181" s="22" t="inlineStr">
+        <is>
+          <t>56 rue Haute Seille</t>
+        </is>
+      </c>
+      <c r="Y181" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z181" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B182" s="23" t="inlineStr">
+        <is>
+          <t>950773291</t>
+        </is>
+      </c>
+      <c r="C182" s="23" t="inlineStr">
+        <is>
+          <t>95077329100030</t>
+        </is>
+      </c>
+      <c r="D182" s="22" t="inlineStr">
+        <is>
+          <t>LOCKY</t>
+        </is>
+      </c>
+      <c r="E182" s="22" t="inlineStr">
+        <is>
+          <t>LOCKY</t>
+        </is>
+      </c>
+      <c r="F182" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G182" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H182" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I182" s="22" t="inlineStr">
+        <is>
+          <t>21/03/2023</t>
+        </is>
+      </c>
+      <c r="J182" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K182" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE DUPONT DES LOGES</t>
+        </is>
+      </c>
+      <c r="L182" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M182" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N182" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O182" s="22" t="inlineStr"/>
+      <c r="P182" s="22" t="inlineStr"/>
+      <c r="Q182" s="22" t="inlineStr"/>
+      <c r="R182" s="23" t="inlineStr"/>
+      <c r="S182" s="22" t="inlineStr"/>
+      <c r="T182" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U182" s="22" t="inlineStr">
+        <is>
+          <t>PFORTNER</t>
+        </is>
+      </c>
+      <c r="V182" s="22" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="W182" s="22" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X167" s="22" t="inlineStr">
-        <is>
-          <t>32 Rue du Grand Pré</t>
-        </is>
-      </c>
-      <c r="Y167" s="23" t="inlineStr">
-        <is>
-          <t>57530</t>
-        </is>
-      </c>
-      <c r="Z167" s="22" t="inlineStr">
-        <is>
-          <t>Marsilly</t>
+      <c r="X182" s="22" t="inlineStr">
+        <is>
+          <t>5 de l'Horticulture</t>
+        </is>
+      </c>
+      <c r="Y182" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z182" s="22" t="inlineStr">
+        <is>
+          <t>Longeville-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B183" s="23" t="inlineStr">
+        <is>
+          <t>914827779</t>
+        </is>
+      </c>
+      <c r="C183" s="23" t="inlineStr">
+        <is>
+          <t>91482777900010</t>
+        </is>
+      </c>
+      <c r="D183" s="22" t="inlineStr">
+        <is>
+          <t>FONTAINE</t>
+        </is>
+      </c>
+      <c r="E183" s="22" t="inlineStr">
+        <is>
+          <t>FONTAINE</t>
+        </is>
+      </c>
+      <c r="F183" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G183" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H183" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I183" s="22" t="inlineStr">
+        <is>
+          <t>21/06/2022</t>
+        </is>
+      </c>
+      <c r="J183" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K183" s="22" t="inlineStr">
+        <is>
+          <t>31 RUE TAISON</t>
+        </is>
+      </c>
+      <c r="L183" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M183" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N183" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O183" s="22" t="inlineStr"/>
+      <c r="P183" s="22" t="inlineStr"/>
+      <c r="Q183" s="22" t="inlineStr"/>
+      <c r="R183" s="23" t="inlineStr"/>
+      <c r="S183" s="22" t="inlineStr"/>
+      <c r="T183" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U183" s="22" t="inlineStr">
+        <is>
+          <t>MARCUS</t>
+        </is>
+      </c>
+      <c r="V183" s="22" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="W183" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X183" s="22" t="inlineStr">
+        <is>
+          <t>6 Rue du Chevremont</t>
+        </is>
+      </c>
+      <c r="Y183" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z183" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B184" s="23" t="inlineStr">
+        <is>
+          <t>539786228</t>
+        </is>
+      </c>
+      <c r="C184" s="23" t="inlineStr">
+        <is>
+          <t>53978622800012</t>
+        </is>
+      </c>
+      <c r="D184" s="22" t="inlineStr">
+        <is>
+          <t>MONGUI</t>
+        </is>
+      </c>
+      <c r="E184" s="22" t="inlineStr">
+        <is>
+          <t>MONGUI</t>
+        </is>
+      </c>
+      <c r="F184" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H184" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I184" s="22" t="inlineStr">
+        <is>
+          <t>08/02/2012</t>
+        </is>
+      </c>
+      <c r="J184" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K184" s="22" t="inlineStr">
+        <is>
+          <t>34 RUE TAISON</t>
+        </is>
+      </c>
+      <c r="L184" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M184" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N184" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O184" s="22" t="inlineStr"/>
+      <c r="P184" s="22" t="inlineStr"/>
+      <c r="Q184" s="22" t="inlineStr"/>
+      <c r="R184" s="23" t="inlineStr"/>
+      <c r="S184" s="22" t="inlineStr"/>
+      <c r="T184" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U184" s="22" t="inlineStr">
+        <is>
+          <t>GUILLERAND</t>
+        </is>
+      </c>
+      <c r="V184" s="22" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="W184" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X184" s="22" t="inlineStr">
+        <is>
+          <t>25 rue des Martyrs de la Résistance</t>
+        </is>
+      </c>
+      <c r="Y184" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="Z184" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B185" s="23" t="inlineStr">
+        <is>
+          <t>803425701</t>
+        </is>
+      </c>
+      <c r="C185" s="23" t="inlineStr">
+        <is>
+          <t>80342570100015</t>
+        </is>
+      </c>
+      <c r="D185" s="22" t="inlineStr">
+        <is>
+          <t>LA QUILLE METZ</t>
+        </is>
+      </c>
+      <c r="E185" s="22" t="inlineStr">
+        <is>
+          <t>LA QUILLE METZ</t>
+        </is>
+      </c>
+      <c r="F185" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G185" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H185" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I185" s="22" t="inlineStr">
+        <is>
+          <t>07/07/2014</t>
+        </is>
+      </c>
+      <c r="J185" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K185" s="22" t="inlineStr">
+        <is>
+          <t>27 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L185" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M185" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N185" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O185" s="22" t="inlineStr"/>
+      <c r="P185" s="22" t="inlineStr"/>
+      <c r="Q185" s="22" t="inlineStr"/>
+      <c r="R185" s="23" t="inlineStr"/>
+      <c r="S185" s="22" t="inlineStr"/>
+      <c r="T185" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U185" s="22" t="inlineStr">
+        <is>
+          <t>JEANGEORGE</t>
+        </is>
+      </c>
+      <c r="V185" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="W185" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X185" s="22" t="inlineStr">
+        <is>
+          <t>27 rue du Général de Gaulle</t>
+        </is>
+      </c>
+      <c r="Y185" s="23" t="inlineStr">
+        <is>
+          <t>68990</t>
+        </is>
+      </c>
+      <c r="Z185" s="22" t="inlineStr">
+        <is>
+          <t>Heimsbrunn</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B186" s="23" t="inlineStr">
+        <is>
+          <t>820553329</t>
+        </is>
+      </c>
+      <c r="C186" s="23" t="inlineStr">
+        <is>
+          <t>82055332900021</t>
+        </is>
+      </c>
+      <c r="D186" s="22" t="inlineStr">
+        <is>
+          <t>LA PROMENADE</t>
+        </is>
+      </c>
+      <c r="E186" s="22" t="inlineStr">
+        <is>
+          <t>LA PROMENADE</t>
+        </is>
+      </c>
+      <c r="F186" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G186" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H186" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I186" s="22" t="inlineStr">
+        <is>
+          <t>26/05/2016</t>
+        </is>
+      </c>
+      <c r="J186" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K186" s="22" t="inlineStr">
+        <is>
+          <t>3 AVENUE LECLERC DE HAUTECLOCQUE</t>
+        </is>
+      </c>
+      <c r="L186" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M186" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N186" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O186" s="22" t="n">
+        <v>121375</v>
+      </c>
+      <c r="P186" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q186" s="22" t="inlineStr"/>
+      <c r="R186" s="23" t="inlineStr"/>
+      <c r="S186" s="22" t="inlineStr"/>
+      <c r="T186" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U186" s="22" t="inlineStr">
+        <is>
+          <t>MILOSEVIC</t>
+        </is>
+      </c>
+      <c r="V186" s="22" t="inlineStr">
+        <is>
+          <t>Olivera</t>
+        </is>
+      </c>
+      <c r="W186" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X186" s="22" t="inlineStr">
+        <is>
+          <t>10 rue du Petit Clou</t>
+        </is>
+      </c>
+      <c r="Y186" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z186" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B187" s="23" t="inlineStr">
+        <is>
+          <t>331334367</t>
+        </is>
+      </c>
+      <c r="C187" s="23" t="inlineStr">
+        <is>
+          <t>33133436700025</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>BERGER Gilbert</t>
+        </is>
+      </c>
+      <c r="E187" s="22" t="inlineStr">
+        <is>
+          <t>BERGER Gilbert</t>
+        </is>
+      </c>
+      <c r="F187" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H187" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I187" s="22" t="inlineStr">
+        <is>
+          <t>10/10/1984</t>
+        </is>
+      </c>
+      <c r="J187" s="22" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="K187" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE DU CHANGE</t>
+        </is>
+      </c>
+      <c r="L187" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M187" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N187" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O187" s="22" t="inlineStr"/>
+      <c r="P187" s="22" t="inlineStr"/>
+      <c r="Q187" s="22" t="inlineStr"/>
+      <c r="R187" s="23" t="inlineStr"/>
+      <c r="S187" s="22" t="inlineStr"/>
+      <c r="T187" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U187" s="22" t="inlineStr">
+        <is>
+          <t>BERGER</t>
+        </is>
+      </c>
+      <c r="V187" s="22" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="W187" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X187" s="22" t="inlineStr"/>
+      <c r="Y187" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z187" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z167"/>
+  <autoFilter ref="A2:Z187"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z187"/>
+  <dimension ref="A1:Z207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19242,2245 +19242,4465 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="22" t="inlineStr">
+      <c r="A168" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B168" s="23" t="inlineStr">
+      <c r="B168" s="21" t="inlineStr">
         <is>
           <t>884397282</t>
         </is>
       </c>
-      <c r="C168" s="23" t="inlineStr">
+      <c r="C168" s="21" t="inlineStr">
         <is>
           <t>88439728200010</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr">
+      <c r="D168" s="20" t="inlineStr">
         <is>
           <t>B&amp;D FOOD</t>
         </is>
       </c>
-      <c r="E168" s="22" t="inlineStr">
+      <c r="E168" s="20" t="inlineStr">
         <is>
           <t>B&amp;D FOOD</t>
         </is>
       </c>
-      <c r="F168" s="22" t="inlineStr">
+      <c r="F168" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G168" s="22" t="inlineStr">
+      <c r="G168" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H168" s="22" t="inlineStr">
+      <c r="H168" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I168" s="22" t="inlineStr">
+      <c r="I168" s="20" t="inlineStr">
         <is>
           <t>01/06/2020</t>
         </is>
       </c>
-      <c r="J168" s="22" t="inlineStr">
+      <c r="J168" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K168" s="22" t="inlineStr">
+      <c r="K168" s="20" t="inlineStr">
         <is>
           <t>20 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L168" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M168" s="22" t="inlineStr">
+      <c r="L168" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M168" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N168" s="22" t="inlineStr">
+      <c r="N168" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O168" s="22" t="inlineStr"/>
-      <c r="P168" s="22" t="inlineStr"/>
-      <c r="Q168" s="22" t="inlineStr"/>
-      <c r="R168" s="23" t="inlineStr"/>
-      <c r="S168" s="22" t="inlineStr"/>
-      <c r="T168" s="22" t="inlineStr">
+      <c r="O168" s="20" t="inlineStr"/>
+      <c r="P168" s="20" t="inlineStr"/>
+      <c r="Q168" s="20" t="inlineStr"/>
+      <c r="R168" s="21" t="inlineStr"/>
+      <c r="S168" s="20" t="inlineStr"/>
+      <c r="T168" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U168" s="22" t="inlineStr">
+      <c r="U168" s="20" t="inlineStr">
         <is>
           <t>SAYEH</t>
         </is>
       </c>
-      <c r="V168" s="22" t="inlineStr">
+      <c r="V168" s="20" t="inlineStr">
         <is>
           <t>Issam</t>
         </is>
       </c>
-      <c r="W168" s="22" t="inlineStr">
+      <c r="W168" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X168" s="22" t="inlineStr">
+      <c r="X168" s="20" t="inlineStr">
         <is>
           <t>38 Rue de Verdun</t>
         </is>
       </c>
-      <c r="Y168" s="23" t="inlineStr">
+      <c r="Y168" s="21" t="inlineStr">
         <is>
           <t>57100</t>
         </is>
       </c>
-      <c r="Z168" s="22" t="inlineStr">
+      <c r="Z168" s="20" t="inlineStr">
         <is>
           <t>Thionville</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="22" t="inlineStr">
+      <c r="A169" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B169" s="23" t="inlineStr">
+      <c r="B169" s="21" t="inlineStr">
         <is>
           <t>912319654</t>
         </is>
       </c>
-      <c r="C169" s="23" t="inlineStr">
+      <c r="C169" s="21" t="inlineStr">
         <is>
           <t>91231965400014</t>
         </is>
       </c>
-      <c r="D169" s="22" t="inlineStr">
+      <c r="D169" s="20" t="inlineStr">
         <is>
           <t>PIZZA PALMA SAS</t>
         </is>
       </c>
-      <c r="E169" s="22" t="inlineStr">
+      <c r="E169" s="20" t="inlineStr">
         <is>
           <t>PIZZA PALMA SAS</t>
         </is>
       </c>
-      <c r="F169" s="22" t="inlineStr">
+      <c r="F169" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G169" s="22" t="inlineStr">
+      <c r="G169" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H169" s="22" t="inlineStr">
+      <c r="H169" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I169" s="22" t="inlineStr">
+      <c r="I169" s="20" t="inlineStr">
         <is>
           <t>11/04/2022</t>
         </is>
       </c>
-      <c r="J169" s="22" t="inlineStr">
+      <c r="J169" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K169" s="22" t="inlineStr">
+      <c r="K169" s="20" t="inlineStr">
         <is>
           <t>33 BOULEVARD PAIXHANS</t>
         </is>
       </c>
-      <c r="L169" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M169" s="22" t="inlineStr">
+      <c r="L169" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M169" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N169" s="22" t="inlineStr">
+      <c r="N169" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O169" s="22" t="inlineStr"/>
-      <c r="P169" s="22" t="inlineStr"/>
-      <c r="Q169" s="22" t="inlineStr"/>
-      <c r="R169" s="23" t="inlineStr"/>
-      <c r="S169" s="22" t="inlineStr"/>
-      <c r="T169" s="22" t="inlineStr">
+      <c r="O169" s="20" t="inlineStr"/>
+      <c r="P169" s="20" t="inlineStr"/>
+      <c r="Q169" s="20" t="inlineStr"/>
+      <c r="R169" s="21" t="inlineStr"/>
+      <c r="S169" s="20" t="inlineStr"/>
+      <c r="T169" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U169" s="22" t="inlineStr">
+      <c r="U169" s="20" t="inlineStr">
         <is>
           <t>AIT KHOUYA</t>
         </is>
       </c>
-      <c r="V169" s="22" t="inlineStr">
+      <c r="V169" s="20" t="inlineStr">
         <is>
           <t>Ammar</t>
         </is>
       </c>
-      <c r="W169" s="22" t="inlineStr">
+      <c r="W169" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X169" s="22" t="inlineStr">
+      <c r="X169" s="20" t="inlineStr">
         <is>
           <t>9 Rue Henri Bergson</t>
         </is>
       </c>
-      <c r="Y169" s="23" t="inlineStr">
+      <c r="Y169" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z169" s="22" t="inlineStr">
+      <c r="Z169" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="22" t="inlineStr">
+      <c r="A170" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B170" s="23" t="inlineStr">
+      <c r="B170" s="21" t="inlineStr">
         <is>
           <t>979176484</t>
         </is>
       </c>
-      <c r="C170" s="23" t="inlineStr">
+      <c r="C170" s="21" t="inlineStr">
         <is>
           <t>97917648400017</t>
         </is>
       </c>
-      <c r="D170" s="22" t="inlineStr">
+      <c r="D170" s="20" t="inlineStr">
         <is>
           <t>O&amp;J BURGER</t>
         </is>
       </c>
-      <c r="E170" s="22" t="inlineStr">
+      <c r="E170" s="20" t="inlineStr">
         <is>
           <t>O&amp;J BURGER</t>
         </is>
       </c>
-      <c r="F170" s="22" t="inlineStr">
+      <c r="F170" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G170" s="22" t="inlineStr">
+      <c r="G170" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H170" s="22" t="inlineStr">
+      <c r="H170" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I170" s="22" t="inlineStr">
+      <c r="I170" s="20" t="inlineStr">
         <is>
           <t>05/08/2023</t>
         </is>
       </c>
-      <c r="J170" s="22" t="inlineStr">
+      <c r="J170" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K170" s="22" t="inlineStr">
+      <c r="K170" s="20" t="inlineStr">
         <is>
           <t>7 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L170" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M170" s="22" t="inlineStr">
+      <c r="L170" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M170" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N170" s="22" t="inlineStr">
+      <c r="N170" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O170" s="22" t="inlineStr"/>
-      <c r="P170" s="22" t="inlineStr"/>
-      <c r="Q170" s="22" t="inlineStr"/>
-      <c r="R170" s="23" t="inlineStr"/>
-      <c r="S170" s="22" t="inlineStr"/>
-      <c r="T170" s="22" t="inlineStr">
+      <c r="O170" s="20" t="inlineStr"/>
+      <c r="P170" s="20" t="inlineStr"/>
+      <c r="Q170" s="20" t="inlineStr"/>
+      <c r="R170" s="21" t="inlineStr"/>
+      <c r="S170" s="20" t="inlineStr"/>
+      <c r="T170" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U170" s="22" t="inlineStr">
+      <c r="U170" s="20" t="inlineStr">
         <is>
           <t>CHENH</t>
         </is>
       </c>
-      <c r="V170" s="22" t="inlineStr">
+      <c r="V170" s="20" t="inlineStr">
         <is>
           <t>Jason, Ji, Kin</t>
         </is>
       </c>
-      <c r="W170" s="22" t="inlineStr">
+      <c r="W170" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X170" s="22" t="inlineStr"/>
-      <c r="Y170" s="23" t="inlineStr">
+      <c r="X170" s="20" t="inlineStr"/>
+      <c r="Y170" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z170" s="22" t="inlineStr">
+      <c r="Z170" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="22" t="inlineStr">
+      <c r="A171" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B171" s="23" t="inlineStr">
+      <c r="B171" s="21" t="inlineStr">
         <is>
           <t>817735848</t>
         </is>
       </c>
-      <c r="C171" s="23" t="inlineStr">
+      <c r="C171" s="21" t="inlineStr">
         <is>
           <t>81773584800019</t>
         </is>
       </c>
-      <c r="D171" s="22" t="inlineStr">
+      <c r="D171" s="20" t="inlineStr">
         <is>
           <t>SASU UMUT</t>
         </is>
       </c>
-      <c r="E171" s="22" t="inlineStr">
+      <c r="E171" s="20" t="inlineStr">
         <is>
           <t>SASU UMUT</t>
         </is>
       </c>
-      <c r="F171" s="22" t="inlineStr">
+      <c r="F171" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G171" s="22" t="inlineStr">
+      <c r="G171" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H171" s="22" t="inlineStr">
+      <c r="H171" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I171" s="22" t="inlineStr">
+      <c r="I171" s="20" t="inlineStr">
         <is>
           <t>01/12/2015</t>
         </is>
       </c>
-      <c r="J171" s="22" t="inlineStr">
+      <c r="J171" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K171" s="22" t="inlineStr">
+      <c r="K171" s="20" t="inlineStr">
         <is>
           <t>18 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L171" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M171" s="22" t="inlineStr">
+      <c r="L171" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M171" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N171" s="22" t="inlineStr">
+      <c r="N171" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O171" s="22" t="inlineStr"/>
-      <c r="P171" s="22" t="inlineStr"/>
-      <c r="Q171" s="22" t="inlineStr"/>
-      <c r="R171" s="23" t="inlineStr"/>
-      <c r="S171" s="22" t="inlineStr"/>
-      <c r="T171" s="22" t="inlineStr">
+      <c r="O171" s="20" t="inlineStr"/>
+      <c r="P171" s="20" t="inlineStr"/>
+      <c r="Q171" s="20" t="inlineStr"/>
+      <c r="R171" s="21" t="inlineStr"/>
+      <c r="S171" s="20" t="inlineStr"/>
+      <c r="T171" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U171" s="22" t="inlineStr">
+      <c r="U171" s="20" t="inlineStr">
         <is>
           <t>DUGENCI</t>
         </is>
       </c>
-      <c r="V171" s="22" t="inlineStr">
+      <c r="V171" s="20" t="inlineStr">
         <is>
           <t>Suleyman</t>
         </is>
       </c>
-      <c r="W171" s="22" t="inlineStr">
+      <c r="W171" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X171" s="22" t="inlineStr">
+      <c r="X171" s="20" t="inlineStr">
         <is>
           <t>2 rue Jean-Adolf Lasaulce</t>
         </is>
       </c>
-      <c r="Y171" s="23" t="inlineStr">
+      <c r="Y171" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z171" s="22" t="inlineStr">
+      <c r="Z171" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="22" t="inlineStr">
+      <c r="A172" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B172" s="23" t="inlineStr">
+      <c r="B172" s="21" t="inlineStr">
         <is>
           <t>990733776</t>
         </is>
       </c>
-      <c r="C172" s="23" t="inlineStr">
+      <c r="C172" s="21" t="inlineStr">
         <is>
           <t>99073377600027</t>
         </is>
       </c>
-      <c r="D172" s="22" t="inlineStr">
+      <c r="D172" s="20" t="inlineStr">
         <is>
           <t>SAS AUX DELICES CAPRICIEUX</t>
         </is>
       </c>
-      <c r="E172" s="22" t="inlineStr">
+      <c r="E172" s="20" t="inlineStr">
         <is>
           <t>SAS AUX DELICES CAPRICIEUX</t>
         </is>
       </c>
-      <c r="F172" s="22" t="inlineStr">
+      <c r="F172" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G172" s="22" t="inlineStr">
+      <c r="G172" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H172" s="22" t="inlineStr">
+      <c r="H172" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I172" s="22" t="inlineStr">
+      <c r="I172" s="20" t="inlineStr">
         <is>
           <t>16/07/2025</t>
         </is>
       </c>
-      <c r="J172" s="22" t="inlineStr">
+      <c r="J172" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K172" s="22" t="inlineStr">
+      <c r="K172" s="20" t="inlineStr">
         <is>
           <t>26 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L172" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M172" s="22" t="inlineStr">
+      <c r="L172" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M172" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N172" s="22" t="inlineStr">
+      <c r="N172" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O172" s="22" t="inlineStr"/>
-      <c r="P172" s="22" t="inlineStr"/>
-      <c r="Q172" s="22" t="inlineStr"/>
-      <c r="R172" s="23" t="inlineStr"/>
-      <c r="S172" s="22" t="inlineStr"/>
-      <c r="T172" s="22" t="inlineStr">
+      <c r="O172" s="20" t="inlineStr"/>
+      <c r="P172" s="20" t="inlineStr"/>
+      <c r="Q172" s="20" t="inlineStr"/>
+      <c r="R172" s="21" t="inlineStr"/>
+      <c r="S172" s="20" t="inlineStr"/>
+      <c r="T172" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U172" s="22" t="inlineStr">
+      <c r="U172" s="20" t="inlineStr">
         <is>
           <t>DEMUTH</t>
         </is>
       </c>
-      <c r="V172" s="22" t="inlineStr">
+      <c r="V172" s="20" t="inlineStr">
         <is>
           <t>Jean-marc</t>
         </is>
       </c>
-      <c r="W172" s="22" t="inlineStr">
+      <c r="W172" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X172" s="22" t="inlineStr">
+      <c r="X172" s="20" t="inlineStr">
         <is>
           <t>156 rue d'edling</t>
         </is>
       </c>
-      <c r="Y172" s="23" t="inlineStr">
+      <c r="Y172" s="21" t="inlineStr">
         <is>
           <t>57320</t>
         </is>
       </c>
-      <c r="Z172" s="22" t="inlineStr">
+      <c r="Z172" s="20" t="inlineStr">
         <is>
           <t>Anzeling</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="22" t="inlineStr">
+      <c r="A173" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B173" s="23" t="inlineStr">
+      <c r="B173" s="21" t="inlineStr">
         <is>
           <t>922700430</t>
         </is>
       </c>
-      <c r="C173" s="23" t="inlineStr">
+      <c r="C173" s="21" t="inlineStr">
         <is>
           <t>92270043000015</t>
         </is>
       </c>
-      <c r="D173" s="22" t="inlineStr">
+      <c r="D173" s="20" t="inlineStr">
         <is>
           <t>MEET TEA</t>
         </is>
       </c>
-      <c r="E173" s="22" t="inlineStr">
+      <c r="E173" s="20" t="inlineStr">
         <is>
           <t>MEET TEA</t>
         </is>
       </c>
-      <c r="F173" s="22" t="inlineStr">
+      <c r="F173" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G173" s="22" t="inlineStr">
+      <c r="G173" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H173" s="22" t="inlineStr">
+      <c r="H173" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I173" s="22" t="inlineStr">
+      <c r="I173" s="20" t="inlineStr">
         <is>
           <t>14/11/2022</t>
         </is>
       </c>
-      <c r="J173" s="22" t="inlineStr">
+      <c r="J173" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K173" s="22" t="inlineStr">
+      <c r="K173" s="20" t="inlineStr">
         <is>
           <t>40 EN CHAPLERUE</t>
         </is>
       </c>
-      <c r="L173" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M173" s="22" t="inlineStr">
+      <c r="L173" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M173" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N173" s="22" t="inlineStr">
+      <c r="N173" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O173" s="22" t="inlineStr"/>
-      <c r="P173" s="22" t="inlineStr"/>
-      <c r="Q173" s="22" t="inlineStr"/>
-      <c r="R173" s="23" t="inlineStr"/>
-      <c r="S173" s="22" t="inlineStr"/>
-      <c r="T173" s="22" t="inlineStr">
+      <c r="O173" s="20" t="inlineStr"/>
+      <c r="P173" s="20" t="inlineStr"/>
+      <c r="Q173" s="20" t="inlineStr"/>
+      <c r="R173" s="21" t="inlineStr"/>
+      <c r="S173" s="20" t="inlineStr"/>
+      <c r="T173" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U173" s="22" t="inlineStr">
+      <c r="U173" s="20" t="inlineStr">
         <is>
           <t>ZHANG</t>
         </is>
       </c>
-      <c r="V173" s="22" t="inlineStr">
+      <c r="V173" s="20" t="inlineStr">
         <is>
           <t>Qing</t>
         </is>
       </c>
-      <c r="W173" s="22" t="inlineStr">
+      <c r="W173" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X173" s="22" t="inlineStr">
+      <c r="X173" s="20" t="inlineStr">
         <is>
           <t>162 Grande rue</t>
         </is>
       </c>
-      <c r="Y173" s="23" t="inlineStr">
+      <c r="Y173" s="21" t="inlineStr">
         <is>
           <t>93000</t>
         </is>
       </c>
-      <c r="Z173" s="22" t="inlineStr">
+      <c r="Z173" s="20" t="inlineStr">
         <is>
           <t>Bobigny</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="22" t="inlineStr">
+      <c r="A174" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B174" s="23" t="inlineStr">
+      <c r="B174" s="21" t="inlineStr">
         <is>
           <t>508607488</t>
         </is>
       </c>
-      <c r="C174" s="23" t="inlineStr">
+      <c r="C174" s="21" t="inlineStr">
         <is>
           <t>50860748800022</t>
         </is>
       </c>
-      <c r="D174" s="22" t="inlineStr">
+      <c r="D174" s="20" t="inlineStr">
         <is>
           <t>BMT FINANCES</t>
         </is>
       </c>
-      <c r="E174" s="22" t="inlineStr">
+      <c r="E174" s="20" t="inlineStr">
         <is>
           <t>BMT FINANCES</t>
         </is>
       </c>
-      <c r="F174" s="22" t="inlineStr">
+      <c r="F174" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G174" s="22" t="inlineStr">
+      <c r="G174" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H174" s="22" t="inlineStr">
+      <c r="H174" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I174" s="22" t="inlineStr">
+      <c r="I174" s="20" t="inlineStr">
         <is>
           <t>17/10/2008</t>
         </is>
       </c>
-      <c r="J174" s="22" t="inlineStr">
+      <c r="J174" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K174" s="22" t="inlineStr">
+      <c r="K174" s="20" t="inlineStr">
         <is>
           <t>24 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L174" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M174" s="22" t="inlineStr">
+      <c r="L174" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M174" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N174" s="22" t="inlineStr">
+      <c r="N174" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O174" s="22" t="inlineStr"/>
-      <c r="P174" s="22" t="inlineStr"/>
-      <c r="Q174" s="22" t="inlineStr"/>
-      <c r="R174" s="23" t="inlineStr"/>
-      <c r="S174" s="22" t="inlineStr"/>
-      <c r="T174" s="22" t="inlineStr">
+      <c r="O174" s="20" t="inlineStr"/>
+      <c r="P174" s="20" t="inlineStr"/>
+      <c r="Q174" s="20" t="inlineStr"/>
+      <c r="R174" s="21" t="inlineStr"/>
+      <c r="S174" s="20" t="inlineStr"/>
+      <c r="T174" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U174" s="22" t="inlineStr">
+      <c r="U174" s="20" t="inlineStr">
         <is>
           <t>TAFFNER</t>
         </is>
       </c>
-      <c r="V174" s="22" t="inlineStr">
+      <c r="V174" s="20" t="inlineStr">
         <is>
           <t>Blaise</t>
         </is>
       </c>
-      <c r="W174" s="22" t="inlineStr">
+      <c r="W174" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X174" s="22" t="inlineStr">
+      <c r="X174" s="20" t="inlineStr">
         <is>
           <t>4 rue Georges Robinson</t>
         </is>
       </c>
-      <c r="Y174" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z174" s="22" t="inlineStr">
+      <c r="Y174" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z174" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="22" t="inlineStr">
+      <c r="A175" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B175" s="23" t="inlineStr">
+      <c r="B175" s="21" t="inlineStr">
         <is>
           <t>934099813</t>
         </is>
       </c>
-      <c r="C175" s="23" t="inlineStr">
+      <c r="C175" s="21" t="inlineStr">
         <is>
           <t>93409981300016</t>
         </is>
       </c>
-      <c r="D175" s="22" t="inlineStr">
+      <c r="D175" s="20" t="inlineStr">
         <is>
           <t>KABUL 2</t>
         </is>
       </c>
-      <c r="E175" s="22" t="inlineStr">
+      <c r="E175" s="20" t="inlineStr">
         <is>
           <t>KABUL 2</t>
         </is>
       </c>
-      <c r="F175" s="22" t="inlineStr">
+      <c r="F175" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G175" s="22" t="inlineStr">
+      <c r="G175" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H175" s="22" t="inlineStr">
+      <c r="H175" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I175" s="22" t="inlineStr">
+      <c r="I175" s="20" t="inlineStr">
         <is>
           <t>07/10/2024</t>
         </is>
       </c>
-      <c r="J175" s="22" t="inlineStr">
+      <c r="J175" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K175" s="22" t="inlineStr">
+      <c r="K175" s="20" t="inlineStr">
         <is>
           <t>9 RUE DU NEUFBOURG</t>
         </is>
       </c>
-      <c r="L175" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M175" s="22" t="inlineStr">
+      <c r="L175" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M175" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N175" s="22" t="inlineStr">
+      <c r="N175" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O175" s="22" t="inlineStr"/>
-      <c r="P175" s="22" t="inlineStr"/>
-      <c r="Q175" s="22" t="inlineStr"/>
-      <c r="R175" s="23" t="inlineStr"/>
-      <c r="S175" s="22" t="inlineStr"/>
-      <c r="T175" s="22" t="inlineStr">
+      <c r="O175" s="20" t="inlineStr"/>
+      <c r="P175" s="20" t="inlineStr"/>
+      <c r="Q175" s="20" t="inlineStr"/>
+      <c r="R175" s="21" t="inlineStr"/>
+      <c r="S175" s="20" t="inlineStr"/>
+      <c r="T175" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U175" s="22" t="inlineStr">
+      <c r="U175" s="20" t="inlineStr">
         <is>
           <t>ALOKOZAY</t>
         </is>
       </c>
-      <c r="V175" s="22" t="inlineStr">
+      <c r="V175" s="20" t="inlineStr">
         <is>
           <t>Sawab</t>
         </is>
       </c>
-      <c r="W175" s="22" t="inlineStr">
+      <c r="W175" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X175" s="22" t="inlineStr">
+      <c r="X175" s="20" t="inlineStr">
         <is>
           <t>8 d rue pépin le bref</t>
         </is>
       </c>
-      <c r="Y175" s="23" t="inlineStr">
+      <c r="Y175" s="21" t="inlineStr">
         <is>
           <t>57100</t>
         </is>
       </c>
-      <c r="Z175" s="22" t="inlineStr">
+      <c r="Z175" s="20" t="inlineStr">
         <is>
           <t>Thionville</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="22" t="inlineStr">
+      <c r="A176" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B176" s="23" t="inlineStr">
+      <c r="B176" s="21" t="inlineStr">
         <is>
           <t>919654962</t>
         </is>
       </c>
-      <c r="C176" s="23" t="inlineStr">
+      <c r="C176" s="21" t="inlineStr">
         <is>
           <t>91965496200019</t>
         </is>
       </c>
-      <c r="D176" s="22" t="inlineStr">
+      <c r="D176" s="20" t="inlineStr">
         <is>
           <t>ANNA</t>
         </is>
       </c>
-      <c r="E176" s="22" t="inlineStr">
+      <c r="E176" s="20" t="inlineStr">
         <is>
           <t>ANNA</t>
         </is>
       </c>
-      <c r="F176" s="22" t="inlineStr">
+      <c r="F176" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G176" s="22" t="inlineStr">
+      <c r="G176" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H176" s="22" t="inlineStr">
+      <c r="H176" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I176" s="22" t="inlineStr">
+      <c r="I176" s="20" t="inlineStr">
         <is>
           <t>30/09/2022</t>
         </is>
       </c>
-      <c r="J176" s="22" t="inlineStr">
+      <c r="J176" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K176" s="22" t="inlineStr">
+      <c r="K176" s="20" t="inlineStr">
         <is>
           <t>61 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L176" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M176" s="22" t="inlineStr">
+      <c r="L176" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M176" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N176" s="22" t="inlineStr">
+      <c r="N176" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O176" s="22" t="inlineStr"/>
-      <c r="P176" s="22" t="inlineStr"/>
-      <c r="Q176" s="22" t="inlineStr"/>
-      <c r="R176" s="23" t="inlineStr"/>
-      <c r="S176" s="22" t="inlineStr"/>
-      <c r="T176" s="22" t="inlineStr">
+      <c r="O176" s="20" t="inlineStr"/>
+      <c r="P176" s="20" t="inlineStr"/>
+      <c r="Q176" s="20" t="inlineStr"/>
+      <c r="R176" s="21" t="inlineStr"/>
+      <c r="S176" s="20" t="inlineStr"/>
+      <c r="T176" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U176" s="22" t="inlineStr">
+      <c r="U176" s="20" t="inlineStr">
         <is>
           <t>REZAOUI</t>
         </is>
       </c>
-      <c r="V176" s="22" t="inlineStr">
+      <c r="V176" s="20" t="inlineStr">
         <is>
           <t>Tarik</t>
         </is>
       </c>
-      <c r="W176" s="22" t="inlineStr">
+      <c r="W176" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X176" s="22" t="inlineStr">
+      <c r="X176" s="20" t="inlineStr">
         <is>
           <t>23 rue de la Marne</t>
         </is>
       </c>
-      <c r="Y176" s="23" t="inlineStr">
+      <c r="Y176" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z176" s="22" t="inlineStr">
+      <c r="Z176" s="20" t="inlineStr">
         <is>
           <t>Le Ban-Saint-Martin</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="22" t="inlineStr">
+      <c r="A177" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B177" s="23" t="inlineStr">
+      <c r="B177" s="21" t="inlineStr">
         <is>
           <t>925068710</t>
         </is>
       </c>
-      <c r="C177" s="23" t="inlineStr">
+      <c r="C177" s="21" t="inlineStr">
         <is>
           <t>92506871000019</t>
         </is>
       </c>
-      <c r="D177" s="22" t="inlineStr">
+      <c r="D177" s="20" t="inlineStr">
         <is>
           <t>SFV</t>
         </is>
       </c>
-      <c r="E177" s="22" t="inlineStr">
+      <c r="E177" s="20" t="inlineStr">
         <is>
           <t>SFV</t>
         </is>
       </c>
-      <c r="F177" s="22" t="inlineStr">
+      <c r="F177" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G177" s="22" t="inlineStr">
+      <c r="G177" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H177" s="22" t="inlineStr">
+      <c r="H177" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I177" s="22" t="inlineStr">
+      <c r="I177" s="20" t="inlineStr">
         <is>
           <t>28/03/2024</t>
         </is>
       </c>
-      <c r="J177" s="22" t="inlineStr">
+      <c r="J177" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K177" s="22" t="inlineStr">
+      <c r="K177" s="20" t="inlineStr">
         <is>
           <t>7 B RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L177" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M177" s="22" t="inlineStr">
+      <c r="L177" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M177" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N177" s="22" t="inlineStr">
+      <c r="N177" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O177" s="22" t="inlineStr"/>
-      <c r="P177" s="22" t="inlineStr"/>
-      <c r="Q177" s="22" t="inlineStr"/>
-      <c r="R177" s="23" t="inlineStr"/>
-      <c r="S177" s="22" t="inlineStr"/>
-      <c r="T177" s="22" t="inlineStr">
+      <c r="O177" s="20" t="inlineStr"/>
+      <c r="P177" s="20" t="inlineStr"/>
+      <c r="Q177" s="20" t="inlineStr"/>
+      <c r="R177" s="21" t="inlineStr"/>
+      <c r="S177" s="20" t="inlineStr"/>
+      <c r="T177" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U177" s="22" t="inlineStr">
+      <c r="U177" s="20" t="inlineStr">
         <is>
           <t>FREYERMUTH</t>
         </is>
       </c>
-      <c r="V177" s="22" t="inlineStr">
+      <c r="V177" s="20" t="inlineStr">
         <is>
           <t>Julien</t>
         </is>
       </c>
-      <c r="W177" s="22" t="inlineStr">
+      <c r="W177" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X177" s="22" t="inlineStr"/>
-      <c r="Y177" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z177" s="22" t="inlineStr">
+      <c r="X177" s="20" t="inlineStr"/>
+      <c r="Y177" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z177" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="22" t="inlineStr">
+      <c r="A178" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B178" s="23" t="inlineStr">
+      <c r="B178" s="21" t="inlineStr">
         <is>
           <t>850625724</t>
         </is>
       </c>
-      <c r="C178" s="23" t="inlineStr">
+      <c r="C178" s="21" t="inlineStr">
         <is>
           <t>85062572400024</t>
         </is>
       </c>
-      <c r="D178" s="22" t="inlineStr">
+      <c r="D178" s="20" t="inlineStr">
         <is>
           <t>GRAMOPHONE</t>
         </is>
       </c>
-      <c r="E178" s="22" t="inlineStr">
+      <c r="E178" s="20" t="inlineStr">
         <is>
           <t>GRAMOPHONE</t>
         </is>
       </c>
-      <c r="F178" s="22" t="inlineStr">
+      <c r="F178" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G178" s="22" t="inlineStr">
+      <c r="G178" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H178" s="22" t="inlineStr">
+      <c r="H178" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I178" s="22" t="inlineStr">
+      <c r="I178" s="20" t="inlineStr">
         <is>
           <t>09/05/2019</t>
         </is>
       </c>
-      <c r="J178" s="22" t="inlineStr">
+      <c r="J178" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K178" s="22" t="inlineStr">
+      <c r="K178" s="20" t="inlineStr">
         <is>
           <t>35 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="L178" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M178" s="22" t="inlineStr">
+      <c r="L178" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M178" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N178" s="22" t="inlineStr">
+      <c r="N178" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O178" s="22" t="inlineStr"/>
-      <c r="P178" s="22" t="inlineStr"/>
-      <c r="Q178" s="22" t="inlineStr"/>
-      <c r="R178" s="23" t="inlineStr"/>
-      <c r="S178" s="22" t="inlineStr"/>
-      <c r="T178" s="22" t="inlineStr">
+      <c r="O178" s="20" t="inlineStr"/>
+      <c r="P178" s="20" t="inlineStr"/>
+      <c r="Q178" s="20" t="inlineStr"/>
+      <c r="R178" s="21" t="inlineStr"/>
+      <c r="S178" s="20" t="inlineStr"/>
+      <c r="T178" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U178" s="22" t="inlineStr">
+      <c r="U178" s="20" t="inlineStr">
         <is>
           <t>LENNINGER</t>
         </is>
       </c>
-      <c r="V178" s="22" t="inlineStr">
+      <c r="V178" s="20" t="inlineStr">
         <is>
           <t>Sébastien</t>
         </is>
       </c>
-      <c r="W178" s="22" t="inlineStr">
+      <c r="W178" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X178" s="22" t="inlineStr">
+      <c r="X178" s="20" t="inlineStr">
         <is>
           <t>20 Rue Jean Mermoz</t>
         </is>
       </c>
-      <c r="Y178" s="23" t="inlineStr">
+      <c r="Y178" s="21" t="inlineStr">
         <is>
           <t>57970</t>
         </is>
       </c>
-      <c r="Z178" s="22" t="inlineStr">
+      <c r="Z178" s="20" t="inlineStr">
         <is>
           <t>Yutz</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="22" t="inlineStr">
+      <c r="A179" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B179" s="23" t="inlineStr">
+      <c r="B179" s="21" t="inlineStr">
         <is>
           <t>524992765</t>
         </is>
       </c>
-      <c r="C179" s="23" t="inlineStr">
+      <c r="C179" s="21" t="inlineStr">
         <is>
           <t>52499276500023</t>
         </is>
       </c>
-      <c r="D179" s="22" t="inlineStr">
+      <c r="D179" s="20" t="inlineStr">
         <is>
           <t>I LOVE</t>
         </is>
       </c>
-      <c r="E179" s="22" t="inlineStr">
+      <c r="E179" s="20" t="inlineStr">
         <is>
           <t>I LOVE</t>
         </is>
       </c>
-      <c r="F179" s="22" t="inlineStr">
+      <c r="F179" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G179" s="22" t="inlineStr">
+      <c r="G179" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H179" s="22" t="inlineStr">
+      <c r="H179" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I179" s="22" t="inlineStr">
+      <c r="I179" s="20" t="inlineStr">
         <is>
           <t>20/09/2010</t>
         </is>
       </c>
-      <c r="J179" s="22" t="inlineStr">
+      <c r="J179" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K179" s="22" t="inlineStr">
+      <c r="K179" s="20" t="inlineStr">
         <is>
           <t>4 PLACE PHILIPPE DE VIGNEULLES</t>
         </is>
       </c>
-      <c r="L179" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M179" s="22" t="inlineStr">
+      <c r="L179" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M179" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N179" s="22" t="inlineStr">
+      <c r="N179" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O179" s="22" t="inlineStr"/>
-      <c r="P179" s="22" t="inlineStr"/>
-      <c r="Q179" s="22" t="inlineStr"/>
-      <c r="R179" s="23" t="inlineStr"/>
-      <c r="S179" s="22" t="inlineStr"/>
-      <c r="T179" s="22" t="inlineStr">
+      <c r="O179" s="20" t="inlineStr"/>
+      <c r="P179" s="20" t="inlineStr"/>
+      <c r="Q179" s="20" t="inlineStr"/>
+      <c r="R179" s="21" t="inlineStr"/>
+      <c r="S179" s="20" t="inlineStr"/>
+      <c r="T179" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U179" s="22" t="inlineStr">
+      <c r="U179" s="20" t="inlineStr">
         <is>
           <t>LONGHI</t>
         </is>
       </c>
-      <c r="V179" s="22" t="inlineStr">
+      <c r="V179" s="20" t="inlineStr">
         <is>
           <t>Julien</t>
         </is>
       </c>
-      <c r="W179" s="22" t="inlineStr">
+      <c r="W179" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X179" s="22" t="inlineStr">
+      <c r="X179" s="20" t="inlineStr">
         <is>
           <t>4 place Philippe de Vigneulles</t>
         </is>
       </c>
-      <c r="Y179" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z179" s="22" t="inlineStr">
+      <c r="Y179" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z179" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="22" t="inlineStr">
+      <c r="A180" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B180" s="23" t="inlineStr">
+      <c r="B180" s="21" t="inlineStr">
         <is>
           <t>425078383</t>
         </is>
       </c>
-      <c r="C180" s="23" t="inlineStr">
+      <c r="C180" s="21" t="inlineStr">
         <is>
           <t>42507838300030</t>
         </is>
       </c>
-      <c r="D180" s="22" t="inlineStr">
+      <c r="D180" s="20" t="inlineStr">
         <is>
           <t>SARL L'HYPPODROME</t>
         </is>
       </c>
-      <c r="E180" s="22" t="inlineStr">
+      <c r="E180" s="20" t="inlineStr">
         <is>
           <t>SARL L'HYPPODROME</t>
         </is>
       </c>
-      <c r="F180" s="22" t="inlineStr">
+      <c r="F180" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G180" s="22" t="inlineStr">
+      <c r="G180" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H180" s="22" t="inlineStr">
+      <c r="H180" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I180" s="22" t="inlineStr">
+      <c r="I180" s="20" t="inlineStr">
         <is>
           <t>21/10/1999</t>
         </is>
       </c>
-      <c r="J180" s="22" t="inlineStr">
+      <c r="J180" s="20" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="K180" s="22" t="inlineStr">
+      <c r="K180" s="20" t="inlineStr">
         <is>
           <t>31 PLACE DU QUARTEAU</t>
         </is>
       </c>
-      <c r="L180" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M180" s="22" t="inlineStr">
+      <c r="L180" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M180" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N180" s="22" t="inlineStr">
+      <c r="N180" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O180" s="22" t="n">
-        <v>116768</v>
-      </c>
-      <c r="P180" s="22" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Q180" s="22" t="inlineStr"/>
-      <c r="R180" s="23" t="inlineStr"/>
-      <c r="S180" s="22" t="inlineStr"/>
-      <c r="T180" s="22" t="inlineStr">
+      <c r="O180" s="20" t="inlineStr">
+        <is>
+          <t>116768</t>
+        </is>
+      </c>
+      <c r="P180" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q180" s="20" t="inlineStr"/>
+      <c r="R180" s="21" t="inlineStr"/>
+      <c r="S180" s="20" t="inlineStr"/>
+      <c r="T180" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U180" s="22" t="inlineStr">
+      <c r="U180" s="20" t="inlineStr">
         <is>
           <t>BONK</t>
         </is>
       </c>
-      <c r="V180" s="22" t="inlineStr">
+      <c r="V180" s="20" t="inlineStr">
         <is>
           <t>Pierre, Edmond</t>
         </is>
       </c>
-      <c r="W180" s="22" t="inlineStr">
+      <c r="W180" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X180" s="22" t="inlineStr">
+      <c r="X180" s="20" t="inlineStr">
         <is>
           <t>1 Rue Saint-Livier</t>
         </is>
       </c>
-      <c r="Y180" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z180" s="22" t="inlineStr">
+      <c r="Y180" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z180" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="22" t="inlineStr">
+      <c r="A181" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B181" s="23" t="inlineStr">
+      <c r="B181" s="21" t="inlineStr">
         <is>
           <t>807447941</t>
         </is>
       </c>
-      <c r="C181" s="23" t="inlineStr">
+      <c r="C181" s="21" t="inlineStr">
         <is>
           <t>80744794100012</t>
         </is>
       </c>
-      <c r="D181" s="22" t="inlineStr">
+      <c r="D181" s="20" t="inlineStr">
         <is>
           <t>Aux Paraiges</t>
         </is>
       </c>
-      <c r="E181" s="22" t="inlineStr">
+      <c r="E181" s="20" t="inlineStr">
         <is>
           <t>Aux Paraiges</t>
         </is>
       </c>
-      <c r="F181" s="22" t="inlineStr">
+      <c r="F181" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G181" s="22" t="inlineStr">
+      <c r="G181" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H181" s="22" t="inlineStr">
+      <c r="H181" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I181" s="22" t="inlineStr">
+      <c r="I181" s="20" t="inlineStr">
         <is>
           <t>15/11/2014</t>
         </is>
       </c>
-      <c r="J181" s="22" t="inlineStr">
+      <c r="J181" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K181" s="22" t="inlineStr">
+      <c r="K181" s="20" t="inlineStr">
         <is>
           <t>27 RUE DU CHANGE</t>
         </is>
       </c>
-      <c r="L181" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M181" s="22" t="inlineStr">
+      <c r="L181" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M181" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N181" s="22" t="inlineStr">
+      <c r="N181" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O181" s="22" t="inlineStr"/>
-      <c r="P181" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q181" s="22" t="inlineStr"/>
-      <c r="R181" s="23" t="inlineStr"/>
-      <c r="S181" s="22" t="inlineStr"/>
-      <c r="T181" s="22" t="inlineStr">
+      <c r="O181" s="20" t="inlineStr"/>
+      <c r="P181" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q181" s="20" t="inlineStr"/>
+      <c r="R181" s="21" t="inlineStr"/>
+      <c r="S181" s="20" t="inlineStr"/>
+      <c r="T181" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U181" s="22" t="inlineStr">
+      <c r="U181" s="20" t="inlineStr">
         <is>
           <t>TRABAND</t>
         </is>
       </c>
-      <c r="V181" s="22" t="inlineStr">
+      <c r="V181" s="20" t="inlineStr">
         <is>
           <t>Nicolas, Gerard, Charles, Andre</t>
         </is>
       </c>
-      <c r="W181" s="22" t="inlineStr">
+      <c r="W181" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X181" s="22" t="inlineStr">
+      <c r="X181" s="20" t="inlineStr">
         <is>
           <t>56 rue Haute Seille</t>
         </is>
       </c>
-      <c r="Y181" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z181" s="22" t="inlineStr">
+      <c r="Y181" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z181" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="22" t="inlineStr">
+      <c r="A182" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B182" s="23" t="inlineStr">
+      <c r="B182" s="21" t="inlineStr">
         <is>
           <t>950773291</t>
         </is>
       </c>
-      <c r="C182" s="23" t="inlineStr">
+      <c r="C182" s="21" t="inlineStr">
         <is>
           <t>95077329100030</t>
         </is>
       </c>
-      <c r="D182" s="22" t="inlineStr">
+      <c r="D182" s="20" t="inlineStr">
         <is>
           <t>LOCKY</t>
         </is>
       </c>
-      <c r="E182" s="22" t="inlineStr">
+      <c r="E182" s="20" t="inlineStr">
         <is>
           <t>LOCKY</t>
         </is>
       </c>
-      <c r="F182" s="22" t="inlineStr">
+      <c r="F182" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G182" s="22" t="inlineStr">
+      <c r="G182" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H182" s="22" t="inlineStr">
+      <c r="H182" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I182" s="22" t="inlineStr">
+      <c r="I182" s="20" t="inlineStr">
         <is>
           <t>21/03/2023</t>
         </is>
       </c>
-      <c r="J182" s="22" t="inlineStr">
+      <c r="J182" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K182" s="22" t="inlineStr">
+      <c r="K182" s="20" t="inlineStr">
         <is>
           <t>4 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="L182" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M182" s="22" t="inlineStr">
+      <c r="L182" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M182" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N182" s="22" t="inlineStr">
+      <c r="N182" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O182" s="22" t="inlineStr"/>
-      <c r="P182" s="22" t="inlineStr"/>
-      <c r="Q182" s="22" t="inlineStr"/>
-      <c r="R182" s="23" t="inlineStr"/>
-      <c r="S182" s="22" t="inlineStr"/>
-      <c r="T182" s="22" t="inlineStr">
+      <c r="O182" s="20" t="inlineStr"/>
+      <c r="P182" s="20" t="inlineStr"/>
+      <c r="Q182" s="20" t="inlineStr"/>
+      <c r="R182" s="21" t="inlineStr"/>
+      <c r="S182" s="20" t="inlineStr"/>
+      <c r="T182" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U182" s="22" t="inlineStr">
+      <c r="U182" s="20" t="inlineStr">
         <is>
           <t>PFORTNER</t>
         </is>
       </c>
-      <c r="V182" s="22" t="inlineStr">
+      <c r="V182" s="20" t="inlineStr">
         <is>
           <t>Tom</t>
         </is>
       </c>
-      <c r="W182" s="22" t="inlineStr">
+      <c r="W182" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X182" s="22" t="inlineStr">
+      <c r="X182" s="20" t="inlineStr">
         <is>
           <t>5 de l'Horticulture</t>
         </is>
       </c>
-      <c r="Y182" s="23" t="inlineStr">
+      <c r="Y182" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z182" s="22" t="inlineStr">
+      <c r="Z182" s="20" t="inlineStr">
         <is>
           <t>Longeville-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="22" t="inlineStr">
+      <c r="A183" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B183" s="23" t="inlineStr">
+      <c r="B183" s="21" t="inlineStr">
         <is>
           <t>914827779</t>
         </is>
       </c>
-      <c r="C183" s="23" t="inlineStr">
+      <c r="C183" s="21" t="inlineStr">
         <is>
           <t>91482777900010</t>
         </is>
       </c>
-      <c r="D183" s="22" t="inlineStr">
+      <c r="D183" s="20" t="inlineStr">
         <is>
           <t>FONTAINE</t>
         </is>
       </c>
-      <c r="E183" s="22" t="inlineStr">
+      <c r="E183" s="20" t="inlineStr">
         <is>
           <t>FONTAINE</t>
         </is>
       </c>
-      <c r="F183" s="22" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G183" s="22" t="inlineStr">
+      <c r="G183" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H183" s="22" t="inlineStr">
+      <c r="H183" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I183" s="22" t="inlineStr">
+      <c r="I183" s="20" t="inlineStr">
         <is>
           <t>21/06/2022</t>
         </is>
       </c>
-      <c r="J183" s="22" t="inlineStr">
+      <c r="J183" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K183" s="22" t="inlineStr">
+      <c r="K183" s="20" t="inlineStr">
         <is>
           <t>31 RUE TAISON</t>
         </is>
       </c>
-      <c r="L183" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M183" s="22" t="inlineStr">
+      <c r="L183" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M183" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N183" s="22" t="inlineStr">
+      <c r="N183" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O183" s="22" t="inlineStr"/>
-      <c r="P183" s="22" t="inlineStr"/>
-      <c r="Q183" s="22" t="inlineStr"/>
-      <c r="R183" s="23" t="inlineStr"/>
-      <c r="S183" s="22" t="inlineStr"/>
-      <c r="T183" s="22" t="inlineStr">
+      <c r="O183" s="20" t="inlineStr"/>
+      <c r="P183" s="20" t="inlineStr"/>
+      <c r="Q183" s="20" t="inlineStr"/>
+      <c r="R183" s="21" t="inlineStr"/>
+      <c r="S183" s="20" t="inlineStr"/>
+      <c r="T183" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U183" s="22" t="inlineStr">
+      <c r="U183" s="20" t="inlineStr">
         <is>
           <t>MARCUS</t>
         </is>
       </c>
-      <c r="V183" s="22" t="inlineStr">
+      <c r="V183" s="20" t="inlineStr">
         <is>
           <t>Rémi</t>
         </is>
       </c>
-      <c r="W183" s="22" t="inlineStr">
+      <c r="W183" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X183" s="22" t="inlineStr">
+      <c r="X183" s="20" t="inlineStr">
         <is>
           <t>6 Rue du Chevremont</t>
         </is>
       </c>
-      <c r="Y183" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z183" s="22" t="inlineStr">
+      <c r="Y183" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z183" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="22" t="inlineStr">
+      <c r="A184" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B184" s="23" t="inlineStr">
+      <c r="B184" s="21" t="inlineStr">
         <is>
           <t>539786228</t>
         </is>
       </c>
-      <c r="C184" s="23" t="inlineStr">
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>53978622800012</t>
         </is>
       </c>
-      <c r="D184" s="22" t="inlineStr">
+      <c r="D184" s="20" t="inlineStr">
         <is>
           <t>MONGUI</t>
         </is>
       </c>
-      <c r="E184" s="22" t="inlineStr">
+      <c r="E184" s="20" t="inlineStr">
         <is>
           <t>MONGUI</t>
         </is>
       </c>
-      <c r="F184" s="22" t="inlineStr">
+      <c r="F184" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G184" s="22" t="inlineStr">
+      <c r="G184" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H184" s="22" t="inlineStr">
+      <c r="H184" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I184" s="22" t="inlineStr">
+      <c r="I184" s="20" t="inlineStr">
         <is>
           <t>08/02/2012</t>
         </is>
       </c>
-      <c r="J184" s="22" t="inlineStr">
+      <c r="J184" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K184" s="22" t="inlineStr">
+      <c r="K184" s="20" t="inlineStr">
         <is>
           <t>34 RUE TAISON</t>
         </is>
       </c>
-      <c r="L184" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M184" s="22" t="inlineStr">
+      <c r="L184" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M184" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N184" s="22" t="inlineStr">
+      <c r="N184" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O184" s="22" t="inlineStr"/>
-      <c r="P184" s="22" t="inlineStr"/>
-      <c r="Q184" s="22" t="inlineStr"/>
-      <c r="R184" s="23" t="inlineStr"/>
-      <c r="S184" s="22" t="inlineStr"/>
-      <c r="T184" s="22" t="inlineStr">
+      <c r="O184" s="20" t="inlineStr"/>
+      <c r="P184" s="20" t="inlineStr"/>
+      <c r="Q184" s="20" t="inlineStr"/>
+      <c r="R184" s="21" t="inlineStr"/>
+      <c r="S184" s="20" t="inlineStr"/>
+      <c r="T184" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U184" s="22" t="inlineStr">
+      <c r="U184" s="20" t="inlineStr">
         <is>
           <t>GUILLERAND</t>
         </is>
       </c>
-      <c r="V184" s="22" t="inlineStr">
+      <c r="V184" s="20" t="inlineStr">
         <is>
           <t>Patrick</t>
         </is>
       </c>
-      <c r="W184" s="22" t="inlineStr">
+      <c r="W184" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X184" s="22" t="inlineStr">
+      <c r="X184" s="20" t="inlineStr">
         <is>
           <t>25 rue des Martyrs de la Résistance</t>
         </is>
       </c>
-      <c r="Y184" s="23" t="inlineStr">
+      <c r="Y184" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="Z184" s="22" t="inlineStr">
+      <c r="Z184" s="20" t="inlineStr">
         <is>
           <t>Montigny-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="22" t="inlineStr">
+      <c r="A185" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B185" s="23" t="inlineStr">
+      <c r="B185" s="21" t="inlineStr">
         <is>
           <t>803425701</t>
         </is>
       </c>
-      <c r="C185" s="23" t="inlineStr">
+      <c r="C185" s="21" t="inlineStr">
         <is>
           <t>80342570100015</t>
         </is>
       </c>
-      <c r="D185" s="22" t="inlineStr">
+      <c r="D185" s="20" t="inlineStr">
         <is>
           <t>LA QUILLE METZ</t>
         </is>
       </c>
-      <c r="E185" s="22" t="inlineStr">
+      <c r="E185" s="20" t="inlineStr">
         <is>
           <t>LA QUILLE METZ</t>
         </is>
       </c>
-      <c r="F185" s="22" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G185" s="22" t="inlineStr">
+      <c r="G185" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H185" s="22" t="inlineStr">
+      <c r="H185" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I185" s="22" t="inlineStr">
+      <c r="I185" s="20" t="inlineStr">
         <is>
           <t>07/07/2014</t>
         </is>
       </c>
-      <c r="J185" s="22" t="inlineStr">
+      <c r="J185" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K185" s="22" t="inlineStr">
+      <c r="K185" s="20" t="inlineStr">
         <is>
           <t>27 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L185" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M185" s="22" t="inlineStr">
+      <c r="L185" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M185" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N185" s="22" t="inlineStr">
+      <c r="N185" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O185" s="22" t="inlineStr"/>
-      <c r="P185" s="22" t="inlineStr"/>
-      <c r="Q185" s="22" t="inlineStr"/>
-      <c r="R185" s="23" t="inlineStr"/>
-      <c r="S185" s="22" t="inlineStr"/>
-      <c r="T185" s="22" t="inlineStr">
+      <c r="O185" s="20" t="inlineStr"/>
+      <c r="P185" s="20" t="inlineStr"/>
+      <c r="Q185" s="20" t="inlineStr"/>
+      <c r="R185" s="21" t="inlineStr"/>
+      <c r="S185" s="20" t="inlineStr"/>
+      <c r="T185" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U185" s="22" t="inlineStr">
+      <c r="U185" s="20" t="inlineStr">
         <is>
           <t>JEANGEORGE</t>
         </is>
       </c>
-      <c r="V185" s="22" t="inlineStr">
+      <c r="V185" s="20" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="W185" s="22" t="inlineStr">
+      <c r="W185" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X185" s="22" t="inlineStr">
+      <c r="X185" s="20" t="inlineStr">
         <is>
           <t>27 rue du Général de Gaulle</t>
         </is>
       </c>
-      <c r="Y185" s="23" t="inlineStr">
+      <c r="Y185" s="21" t="inlineStr">
         <is>
           <t>68990</t>
         </is>
       </c>
-      <c r="Z185" s="22" t="inlineStr">
+      <c r="Z185" s="20" t="inlineStr">
         <is>
           <t>Heimsbrunn</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="22" t="inlineStr">
+      <c r="A186" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B186" s="23" t="inlineStr">
+      <c r="B186" s="21" t="inlineStr">
         <is>
           <t>820553329</t>
         </is>
       </c>
-      <c r="C186" s="23" t="inlineStr">
+      <c r="C186" s="21" t="inlineStr">
         <is>
           <t>82055332900021</t>
         </is>
       </c>
-      <c r="D186" s="22" t="inlineStr">
+      <c r="D186" s="20" t="inlineStr">
         <is>
           <t>LA PROMENADE</t>
         </is>
       </c>
-      <c r="E186" s="22" t="inlineStr">
+      <c r="E186" s="20" t="inlineStr">
         <is>
           <t>LA PROMENADE</t>
         </is>
       </c>
-      <c r="F186" s="22" t="inlineStr">
+      <c r="F186" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G186" s="22" t="inlineStr">
+      <c r="G186" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H186" s="22" t="inlineStr">
+      <c r="H186" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I186" s="22" t="inlineStr">
+      <c r="I186" s="20" t="inlineStr">
         <is>
           <t>26/05/2016</t>
         </is>
       </c>
-      <c r="J186" s="22" t="inlineStr">
+      <c r="J186" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K186" s="22" t="inlineStr">
+      <c r="K186" s="20" t="inlineStr">
         <is>
           <t>3 AVENUE LECLERC DE HAUTECLOCQUE</t>
         </is>
       </c>
-      <c r="L186" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M186" s="22" t="inlineStr">
+      <c r="L186" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M186" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N186" s="22" t="inlineStr">
+      <c r="N186" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O186" s="22" t="n">
-        <v>121375</v>
-      </c>
-      <c r="P186" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q186" s="22" t="inlineStr"/>
-      <c r="R186" s="23" t="inlineStr"/>
-      <c r="S186" s="22" t="inlineStr"/>
-      <c r="T186" s="22" t="inlineStr">
+      <c r="O186" s="20" t="inlineStr">
+        <is>
+          <t>121375</t>
+        </is>
+      </c>
+      <c r="P186" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q186" s="20" t="inlineStr"/>
+      <c r="R186" s="21" t="inlineStr"/>
+      <c r="S186" s="20" t="inlineStr"/>
+      <c r="T186" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U186" s="22" t="inlineStr">
+      <c r="U186" s="20" t="inlineStr">
         <is>
           <t>MILOSEVIC</t>
         </is>
       </c>
-      <c r="V186" s="22" t="inlineStr">
+      <c r="V186" s="20" t="inlineStr">
         <is>
           <t>Olivera</t>
         </is>
       </c>
-      <c r="W186" s="22" t="inlineStr">
+      <c r="W186" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X186" s="22" t="inlineStr">
+      <c r="X186" s="20" t="inlineStr">
         <is>
           <t>10 rue du Petit Clou</t>
         </is>
       </c>
-      <c r="Y186" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z186" s="22" t="inlineStr">
+      <c r="Y186" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z186" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="22" t="inlineStr">
+      <c r="A187" s="20" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B187" s="23" t="inlineStr">
+      <c r="B187" s="21" t="inlineStr">
         <is>
           <t>331334367</t>
         </is>
       </c>
-      <c r="C187" s="23" t="inlineStr">
+      <c r="C187" s="21" t="inlineStr">
         <is>
           <t>33133436700025</t>
         </is>
       </c>
-      <c r="D187" s="22" t="inlineStr">
+      <c r="D187" s="20" t="inlineStr">
         <is>
           <t>BERGER Gilbert</t>
         </is>
       </c>
-      <c r="E187" s="22" t="inlineStr">
+      <c r="E187" s="20" t="inlineStr">
         <is>
           <t>BERGER Gilbert</t>
         </is>
       </c>
-      <c r="F187" s="22" t="inlineStr">
+      <c r="F187" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G187" s="22" t="inlineStr">
+      <c r="G187" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H187" s="22" t="inlineStr">
+      <c r="H187" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I187" s="22" t="inlineStr">
+      <c r="I187" s="20" t="inlineStr">
         <is>
           <t>10/10/1984</t>
         </is>
       </c>
-      <c r="J187" s="22" t="inlineStr">
+      <c r="J187" s="20" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="K187" s="22" t="inlineStr">
+      <c r="K187" s="20" t="inlineStr">
         <is>
           <t>4 RUE DU CHANGE</t>
         </is>
       </c>
-      <c r="L187" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M187" s="22" t="inlineStr">
+      <c r="L187" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M187" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N187" s="22" t="inlineStr">
+      <c r="N187" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O187" s="22" t="inlineStr"/>
-      <c r="P187" s="22" t="inlineStr"/>
-      <c r="Q187" s="22" t="inlineStr"/>
-      <c r="R187" s="23" t="inlineStr"/>
-      <c r="S187" s="22" t="inlineStr"/>
-      <c r="T187" s="22" t="inlineStr">
+      <c r="O187" s="20" t="inlineStr"/>
+      <c r="P187" s="20" t="inlineStr"/>
+      <c r="Q187" s="20" t="inlineStr"/>
+      <c r="R187" s="21" t="inlineStr"/>
+      <c r="S187" s="20" t="inlineStr"/>
+      <c r="T187" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U187" s="22" t="inlineStr">
+      <c r="U187" s="20" t="inlineStr">
         <is>
           <t>BERGER</t>
         </is>
       </c>
-      <c r="V187" s="22" t="inlineStr">
+      <c r="V187" s="20" t="inlineStr">
         <is>
           <t>Gilbert</t>
         </is>
       </c>
-      <c r="W187" s="22" t="inlineStr">
+      <c r="W187" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X187" s="22" t="inlineStr"/>
-      <c r="Y187" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z187" s="22" t="inlineStr">
+      <c r="X187" s="20" t="inlineStr"/>
+      <c r="Y187" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z187" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B188" s="23" t="inlineStr">
+        <is>
+          <t>521477844</t>
+        </is>
+      </c>
+      <c r="C188" s="23" t="inlineStr">
+        <is>
+          <t>52147784400026</t>
+        </is>
+      </c>
+      <c r="D188" s="22" t="inlineStr">
+        <is>
+          <t>SARL VONG</t>
+        </is>
+      </c>
+      <c r="E188" s="22" t="inlineStr">
+        <is>
+          <t>SARL VONG</t>
+        </is>
+      </c>
+      <c r="F188" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G188" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H188" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I188" s="22" t="inlineStr">
+        <is>
+          <t>31/03/2010</t>
+        </is>
+      </c>
+      <c r="J188" s="22" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K188" s="22" t="inlineStr">
+        <is>
+          <t>44 PLACE MAZELLE</t>
+        </is>
+      </c>
+      <c r="L188" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M188" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N188" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O188" s="22" t="inlineStr"/>
+      <c r="P188" s="22" t="inlineStr"/>
+      <c r="Q188" s="22" t="inlineStr"/>
+      <c r="R188" s="23" t="inlineStr"/>
+      <c r="S188" s="22" t="inlineStr"/>
+      <c r="T188" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U188" s="22" t="inlineStr">
+        <is>
+          <t>NOANG</t>
+        </is>
+      </c>
+      <c r="V188" s="22" t="inlineStr">
+        <is>
+          <t>Sylvie</t>
+        </is>
+      </c>
+      <c r="W188" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X188" s="22" t="inlineStr">
+        <is>
+          <t>6 rue du Bugey</t>
+        </is>
+      </c>
+      <c r="Y188" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z188" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B189" s="23" t="inlineStr">
+        <is>
+          <t>984246629</t>
+        </is>
+      </c>
+      <c r="C189" s="23" t="inlineStr">
+        <is>
+          <t>98424662900013</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ MARIETTE</t>
+        </is>
+      </c>
+      <c r="E189" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ MARIETTE</t>
+        </is>
+      </c>
+      <c r="F189" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H189" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I189" s="22" t="inlineStr">
+        <is>
+          <t>12/01/2024</t>
+        </is>
+      </c>
+      <c r="J189" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K189" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L189" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M189" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N189" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O189" s="22" t="inlineStr"/>
+      <c r="P189" s="22" t="inlineStr"/>
+      <c r="Q189" s="22" t="inlineStr"/>
+      <c r="R189" s="23" t="inlineStr"/>
+      <c r="S189" s="22" t="inlineStr"/>
+      <c r="T189" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U189" s="22" t="inlineStr">
+        <is>
+          <t>EISENBERG</t>
+        </is>
+      </c>
+      <c r="V189" s="22" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="W189" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X189" s="22" t="inlineStr">
+        <is>
+          <t>43 rue saint andre</t>
+        </is>
+      </c>
+      <c r="Y189" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z189" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B190" s="23" t="inlineStr">
+        <is>
+          <t>950787556</t>
+        </is>
+      </c>
+      <c r="C190" s="23" t="inlineStr">
+        <is>
+          <t>95078755600014</t>
+        </is>
+      </c>
+      <c r="D190" s="22" t="inlineStr">
+        <is>
+          <t>SZ AVA SARL</t>
+        </is>
+      </c>
+      <c r="E190" s="22" t="inlineStr">
+        <is>
+          <t>SZ AVA SARL</t>
+        </is>
+      </c>
+      <c r="F190" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H190" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I190" s="22" t="inlineStr">
+        <is>
+          <t>21/03/2023</t>
+        </is>
+      </c>
+      <c r="J190" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K190" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DU PONT DES ROCHES</t>
+        </is>
+      </c>
+      <c r="L190" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M190" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N190" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O190" s="22" t="inlineStr"/>
+      <c r="P190" s="22" t="inlineStr"/>
+      <c r="Q190" s="22" t="inlineStr"/>
+      <c r="R190" s="23" t="inlineStr"/>
+      <c r="S190" s="22" t="inlineStr"/>
+      <c r="T190" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U190" s="22" t="inlineStr">
+        <is>
+          <t>MULLER</t>
+        </is>
+      </c>
+      <c r="V190" s="22" t="inlineStr">
+        <is>
+          <t>Stéphane</t>
+        </is>
+      </c>
+      <c r="W190" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X190" s="22" t="inlineStr">
+        <is>
+          <t>18 Rue de la Haye</t>
+        </is>
+      </c>
+      <c r="Y190" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z190" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B191" s="23" t="inlineStr">
+        <is>
+          <t>853606333</t>
+        </is>
+      </c>
+      <c r="C191" s="23" t="inlineStr">
+        <is>
+          <t>85360633300013</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="inlineStr">
+        <is>
+          <t>DE MELLO Richard</t>
+        </is>
+      </c>
+      <c r="E191" s="22" t="inlineStr">
+        <is>
+          <t>DE MELLO Richard</t>
+        </is>
+      </c>
+      <c r="F191" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H191" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I191" s="22" t="inlineStr">
+        <is>
+          <t>13/09/2019</t>
+        </is>
+      </c>
+      <c r="J191" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K191" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE DU PARADIS</t>
+        </is>
+      </c>
+      <c r="L191" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M191" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N191" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O191" s="22" t="inlineStr"/>
+      <c r="P191" s="22" t="inlineStr"/>
+      <c r="Q191" s="22" t="inlineStr"/>
+      <c r="R191" s="23" t="inlineStr"/>
+      <c r="S191" s="22" t="inlineStr"/>
+      <c r="T191" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U191" s="22" t="inlineStr">
+        <is>
+          <t>DE MELLO</t>
+        </is>
+      </c>
+      <c r="V191" s="22" t="inlineStr">
+        <is>
+          <t>Richard, Denis, Maurice</t>
+        </is>
+      </c>
+      <c r="W191" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X191" s="22" t="inlineStr"/>
+      <c r="Y191" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z191" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B192" s="23" t="inlineStr">
+        <is>
+          <t>945208700</t>
+        </is>
+      </c>
+      <c r="C192" s="23" t="inlineStr">
+        <is>
+          <t>94520870000019</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="inlineStr">
+        <is>
+          <t>CASA RAMEN</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="inlineStr">
+        <is>
+          <t>CASA RAMEN</t>
+        </is>
+      </c>
+      <c r="F192" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G192" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H192" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I192" s="22" t="inlineStr">
+        <is>
+          <t>21/05/2025</t>
+        </is>
+      </c>
+      <c r="J192" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K192" s="22" t="inlineStr">
+        <is>
+          <t>22 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L192" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M192" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N192" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O192" s="22" t="inlineStr"/>
+      <c r="P192" s="22" t="inlineStr"/>
+      <c r="Q192" s="22" t="inlineStr"/>
+      <c r="R192" s="23" t="inlineStr"/>
+      <c r="S192" s="22" t="inlineStr"/>
+      <c r="T192" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U192" s="22" t="inlineStr">
+        <is>
+          <t>SUK</t>
+        </is>
+      </c>
+      <c r="V192" s="22" t="inlineStr">
+        <is>
+          <t>Laurent, Sébastien</t>
+        </is>
+      </c>
+      <c r="W192" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X192" s="22" t="inlineStr"/>
+      <c r="Y192" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z192" s="22" t="inlineStr">
+        <is>
+          <t>Norroy-le-Veneur</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B193" s="23" t="inlineStr">
+        <is>
+          <t>404529984</t>
+        </is>
+      </c>
+      <c r="C193" s="23" t="inlineStr">
+        <is>
+          <t>40452998400019</t>
+        </is>
+      </c>
+      <c r="D193" s="22" t="inlineStr">
+        <is>
+          <t>BAZ ANGEL ALONSO MANUEL</t>
+        </is>
+      </c>
+      <c r="E193" s="22" t="inlineStr">
+        <is>
+          <t>BAZ ANGEL ALONSO MANUEL</t>
+        </is>
+      </c>
+      <c r="F193" s="22" t="inlineStr">
+        <is>
+          <t>Société créée de fait entre personnes physiques</t>
+        </is>
+      </c>
+      <c r="G193" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H193" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I193" s="22" t="inlineStr">
+        <is>
+          <t>11/08/1995</t>
+        </is>
+      </c>
+      <c r="J193" s="22" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="K193" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DU CHAMPE</t>
+        </is>
+      </c>
+      <c r="L193" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M193" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N193" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O193" s="22" t="inlineStr"/>
+      <c r="P193" s="22" t="inlineStr"/>
+      <c r="Q193" s="22" t="inlineStr"/>
+      <c r="R193" s="23" t="inlineStr"/>
+      <c r="S193" s="22" t="inlineStr"/>
+      <c r="T193" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U193" s="22" t="inlineStr"/>
+      <c r="V193" s="22" t="inlineStr"/>
+      <c r="W193" s="22" t="inlineStr"/>
+      <c r="X193" s="22" t="inlineStr"/>
+      <c r="Y193" s="23" t="inlineStr"/>
+      <c r="Z193" s="22" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B194" s="23" t="inlineStr">
+        <is>
+          <t>102628740</t>
+        </is>
+      </c>
+      <c r="C194" s="23" t="inlineStr">
+        <is>
+          <t>10262874000015</t>
+        </is>
+      </c>
+      <c r="D194" s="22" t="inlineStr">
+        <is>
+          <t>BARAMEYS SAS</t>
+        </is>
+      </c>
+      <c r="E194" s="22" t="inlineStr">
+        <is>
+          <t>BARAMEYS SAS</t>
+        </is>
+      </c>
+      <c r="F194" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G194" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H194" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I194" s="22" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="J194" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K194" s="22" t="inlineStr">
+        <is>
+          <t>11 RUE SAINT-VINCENT</t>
+        </is>
+      </c>
+      <c r="L194" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M194" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N194" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O194" s="22" t="inlineStr"/>
+      <c r="P194" s="22" t="inlineStr"/>
+      <c r="Q194" s="22" t="inlineStr"/>
+      <c r="R194" s="23" t="inlineStr"/>
+      <c r="S194" s="22" t="inlineStr"/>
+      <c r="T194" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U194" s="22" t="inlineStr">
+        <is>
+          <t>CHHIN</t>
+        </is>
+      </c>
+      <c r="V194" s="22" t="inlineStr">
+        <is>
+          <t>Sinoch</t>
+        </is>
+      </c>
+      <c r="W194" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X194" s="22" t="inlineStr">
+        <is>
+          <t>ll,rue soint vincent</t>
+        </is>
+      </c>
+      <c r="Y194" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z194" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B195" s="23" t="inlineStr">
+        <is>
+          <t>921835187</t>
+        </is>
+      </c>
+      <c r="C195" s="23" t="inlineStr">
+        <is>
+          <t>92183518700011</t>
+        </is>
+      </c>
+      <c r="D195" s="22" t="inlineStr">
+        <is>
+          <t>HOTH</t>
+        </is>
+      </c>
+      <c r="E195" s="22" t="inlineStr">
+        <is>
+          <t>HOTH</t>
+        </is>
+      </c>
+      <c r="F195" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G195" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H195" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I195" s="22" t="inlineStr">
+        <is>
+          <t>01/12/2022</t>
+        </is>
+      </c>
+      <c r="J195" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K195" s="22" t="inlineStr">
+        <is>
+          <t>20 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L195" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M195" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N195" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O195" s="22" t="inlineStr"/>
+      <c r="P195" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q195" s="22" t="inlineStr"/>
+      <c r="R195" s="23" t="inlineStr"/>
+      <c r="S195" s="22" t="inlineStr"/>
+      <c r="T195" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U195" s="22" t="inlineStr">
+        <is>
+          <t>GUYON</t>
+        </is>
+      </c>
+      <c r="V195" s="22" t="inlineStr">
+        <is>
+          <t>Arnaud, Joseph, Marcel, Marie</t>
+        </is>
+      </c>
+      <c r="W195" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X195" s="22" t="inlineStr"/>
+      <c r="Y195" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z195" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B196" s="23" t="inlineStr">
+        <is>
+          <t>845249119</t>
+        </is>
+      </c>
+      <c r="C196" s="23" t="inlineStr">
+        <is>
+          <t>84524911900015</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="inlineStr">
+        <is>
+          <t>DI ZHENG</t>
+        </is>
+      </c>
+      <c r="E196" s="22" t="inlineStr">
+        <is>
+          <t>DI ZHENG</t>
+        </is>
+      </c>
+      <c r="F196" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G196" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H196" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I196" s="22" t="inlineStr">
+        <is>
+          <t>14/01/2019</t>
+        </is>
+      </c>
+      <c r="J196" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K196" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L196" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M196" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N196" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O196" s="22" t="inlineStr"/>
+      <c r="P196" s="22" t="inlineStr"/>
+      <c r="Q196" s="22" t="inlineStr"/>
+      <c r="R196" s="23" t="inlineStr"/>
+      <c r="S196" s="22" t="inlineStr"/>
+      <c r="T196" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U196" s="22" t="inlineStr">
+        <is>
+          <t>ZHENG</t>
+        </is>
+      </c>
+      <c r="V196" s="22" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="W196" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X196" s="22" t="inlineStr">
+        <is>
+          <t>26 avenue Anatole France</t>
+        </is>
+      </c>
+      <c r="Y196" s="23" t="inlineStr">
+        <is>
+          <t>93500</t>
+        </is>
+      </c>
+      <c r="Z196" s="22" t="inlineStr">
+        <is>
+          <t>Pantin</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B197" s="23" t="inlineStr">
+        <is>
+          <t>918159047</t>
+        </is>
+      </c>
+      <c r="C197" s="23" t="inlineStr">
+        <is>
+          <t>91815904700078</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="inlineStr">
+        <is>
+          <t>HJMN</t>
+        </is>
+      </c>
+      <c r="E197" s="22" t="inlineStr">
+        <is>
+          <t>HJMN</t>
+        </is>
+      </c>
+      <c r="F197" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H197" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I197" s="22" t="inlineStr">
+        <is>
+          <t>19/10/2022</t>
+        </is>
+      </c>
+      <c r="J197" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K197" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE SERPENOISE</t>
+        </is>
+      </c>
+      <c r="L197" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M197" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N197" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O197" s="22" t="inlineStr"/>
+      <c r="P197" s="22" t="inlineStr"/>
+      <c r="Q197" s="22" t="inlineStr"/>
+      <c r="R197" s="23" t="inlineStr"/>
+      <c r="S197" s="22" t="inlineStr"/>
+      <c r="T197" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U197" s="22" t="inlineStr">
+        <is>
+          <t>BUDAIOVA</t>
+        </is>
+      </c>
+      <c r="V197" s="22" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="W197" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X197" s="22" t="inlineStr"/>
+      <c r="Y197" s="23" t="inlineStr">
+        <is>
+          <t>93200</t>
+        </is>
+      </c>
+      <c r="Z197" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B198" s="23" t="inlineStr">
+        <is>
+          <t>403469174</t>
+        </is>
+      </c>
+      <c r="C198" s="23" t="inlineStr">
+        <is>
+          <t>40346917400011</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="inlineStr">
+        <is>
+          <t>AMPIRE</t>
+        </is>
+      </c>
+      <c r="E198" s="22" t="inlineStr">
+        <is>
+          <t>AMPIRE</t>
+        </is>
+      </c>
+      <c r="F198" s="22" t="inlineStr">
+        <is>
+          <t>SA à conseil d'administration (s.a.i.)</t>
+        </is>
+      </c>
+      <c r="G198" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H198" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I198" s="22" t="inlineStr">
+        <is>
+          <t>01/11/1995</t>
+        </is>
+      </c>
+      <c r="J198" s="22" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="K198" s="22" t="inlineStr">
+        <is>
+          <t>MARCHE DE LA CHEVRE</t>
+        </is>
+      </c>
+      <c r="L198" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M198" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N198" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O198" s="22" t="inlineStr"/>
+      <c r="P198" s="22" t="inlineStr"/>
+      <c r="Q198" s="22" t="inlineStr"/>
+      <c r="R198" s="23" t="inlineStr"/>
+      <c r="S198" s="22" t="inlineStr"/>
+      <c r="T198" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U198" s="22" t="inlineStr">
+        <is>
+          <t>ARNOULD</t>
+        </is>
+      </c>
+      <c r="V198" s="22" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="W198" s="22" t="inlineStr">
+        <is>
+          <t>Président du conseil d'administration, Directeur général</t>
+        </is>
+      </c>
+      <c r="X198" s="22" t="inlineStr">
+        <is>
+          <t>20 place Carnot</t>
+        </is>
+      </c>
+      <c r="Y198" s="23" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="Z198" s="22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B199" s="23" t="inlineStr">
+        <is>
+          <t>505123745</t>
+        </is>
+      </c>
+      <c r="C199" s="23" t="inlineStr">
+        <is>
+          <t>50512374500018</t>
+        </is>
+      </c>
+      <c r="D199" s="22" t="inlineStr">
+        <is>
+          <t>C.D.F.P.</t>
+        </is>
+      </c>
+      <c r="E199" s="22" t="inlineStr">
+        <is>
+          <t>C.D.F.P.</t>
+        </is>
+      </c>
+      <c r="F199" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G199" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H199" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I199" s="22" t="inlineStr">
+        <is>
+          <t>07/07/2008</t>
+        </is>
+      </c>
+      <c r="J199" s="22" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K199" s="22" t="inlineStr">
+        <is>
+          <t>29 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L199" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M199" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N199" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O199" s="22" t="inlineStr"/>
+      <c r="P199" s="22" t="inlineStr"/>
+      <c r="Q199" s="22" t="inlineStr"/>
+      <c r="R199" s="23" t="inlineStr"/>
+      <c r="S199" s="22" t="inlineStr"/>
+      <c r="T199" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U199" s="22" t="inlineStr">
+        <is>
+          <t>BASTIEN</t>
+        </is>
+      </c>
+      <c r="V199" s="22" t="inlineStr">
+        <is>
+          <t>Christophe, Pierre, Michel</t>
+        </is>
+      </c>
+      <c r="W199" s="22" t="inlineStr">
+        <is>
+          <t>Gérant, Associé indéfiniment responsable</t>
+        </is>
+      </c>
+      <c r="X199" s="22" t="inlineStr">
+        <is>
+          <t>10 rue aux Ours</t>
+        </is>
+      </c>
+      <c r="Y199" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z199" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B200" s="23" t="inlineStr">
+        <is>
+          <t>878094952</t>
+        </is>
+      </c>
+      <c r="C200" s="23" t="inlineStr">
+        <is>
+          <t>87809495200016</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="inlineStr">
+        <is>
+          <t>BIERSTUB</t>
+        </is>
+      </c>
+      <c r="E200" s="22" t="inlineStr">
+        <is>
+          <t>BIERSTUB</t>
+        </is>
+      </c>
+      <c r="F200" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G200" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H200" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I200" s="22" t="inlineStr">
+        <is>
+          <t>11/10/2019</t>
+        </is>
+      </c>
+      <c r="J200" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K200" s="22" t="inlineStr">
+        <is>
+          <t>44 EN FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="L200" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M200" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N200" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O200" s="22" t="inlineStr"/>
+      <c r="P200" s="22" t="inlineStr"/>
+      <c r="Q200" s="22" t="inlineStr"/>
+      <c r="R200" s="23" t="inlineStr"/>
+      <c r="S200" s="22" t="inlineStr"/>
+      <c r="T200" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U200" s="22" t="inlineStr">
+        <is>
+          <t>FERREIRA</t>
+        </is>
+      </c>
+      <c r="V200" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="W200" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X200" s="22" t="inlineStr">
+        <is>
+          <t>8 rue des Chardonnerets</t>
+        </is>
+      </c>
+      <c r="Y200" s="23" t="inlineStr">
+        <is>
+          <t>57365</t>
+        </is>
+      </c>
+      <c r="Z200" s="22" t="inlineStr">
+        <is>
+          <t>Ennery</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B201" s="23" t="inlineStr">
+        <is>
+          <t>832347397</t>
+        </is>
+      </c>
+      <c r="C201" s="23" t="inlineStr">
+        <is>
+          <t>83234739700016</t>
+        </is>
+      </c>
+      <c r="D201" s="22" t="inlineStr">
+        <is>
+          <t>NANGARHAR</t>
+        </is>
+      </c>
+      <c r="E201" s="22" t="inlineStr">
+        <is>
+          <t>NANGARHAR</t>
+        </is>
+      </c>
+      <c r="F201" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G201" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H201" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I201" s="22" t="inlineStr">
+        <is>
+          <t>15/10/2017</t>
+        </is>
+      </c>
+      <c r="J201" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K201" s="22" t="inlineStr">
+        <is>
+          <t>17 RUE DU CHANGE</t>
+        </is>
+      </c>
+      <c r="L201" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M201" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N201" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O201" s="22" t="inlineStr"/>
+      <c r="P201" s="22" t="inlineStr"/>
+      <c r="Q201" s="22" t="inlineStr"/>
+      <c r="R201" s="23" t="inlineStr"/>
+      <c r="S201" s="22" t="inlineStr"/>
+      <c r="T201" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U201" s="22" t="inlineStr">
+        <is>
+          <t>AHMADZAI</t>
+        </is>
+      </c>
+      <c r="V201" s="22" t="inlineStr">
+        <is>
+          <t>Jacques</t>
+        </is>
+      </c>
+      <c r="W201" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X201" s="22" t="inlineStr">
+        <is>
+          <t>6 square Henri Dunant</t>
+        </is>
+      </c>
+      <c r="Y201" s="23" t="inlineStr">
+        <is>
+          <t>93260</t>
+        </is>
+      </c>
+      <c r="Z201" s="22" t="inlineStr">
+        <is>
+          <t>Les lilas</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B202" s="23" t="inlineStr">
+        <is>
+          <t>934539925</t>
+        </is>
+      </c>
+      <c r="C202" s="23" t="inlineStr">
+        <is>
+          <t>93453992500016</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="inlineStr">
+        <is>
+          <t>SAVEURS DU TIBET</t>
+        </is>
+      </c>
+      <c r="E202" s="22" t="inlineStr">
+        <is>
+          <t>SAVEURS DU TIBET</t>
+        </is>
+      </c>
+      <c r="F202" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G202" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H202" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I202" s="22" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="J202" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K202" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE DU CHAMPE</t>
+        </is>
+      </c>
+      <c r="L202" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M202" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N202" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O202" s="22" t="inlineStr"/>
+      <c r="P202" s="22" t="inlineStr"/>
+      <c r="Q202" s="22" t="inlineStr"/>
+      <c r="R202" s="23" t="inlineStr"/>
+      <c r="S202" s="22" t="inlineStr"/>
+      <c r="T202" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U202" s="22" t="inlineStr">
+        <is>
+          <t>TSANG</t>
+        </is>
+      </c>
+      <c r="V202" s="22" t="inlineStr">
+        <is>
+          <t>Nurbu, Tsering</t>
+        </is>
+      </c>
+      <c r="W202" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X202" s="22" t="inlineStr">
+        <is>
+          <t>69 bis avenue du général de gaulle</t>
+        </is>
+      </c>
+      <c r="Y202" s="23" t="inlineStr">
+        <is>
+          <t>92800</t>
+        </is>
+      </c>
+      <c r="Z202" s="22" t="inlineStr">
+        <is>
+          <t>Puteaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B203" s="23" t="inlineStr">
+        <is>
+          <t>911630168</t>
+        </is>
+      </c>
+      <c r="C203" s="23" t="inlineStr">
+        <is>
+          <t>91163016800019</t>
+        </is>
+      </c>
+      <c r="D203" s="22" t="inlineStr">
+        <is>
+          <t>LE CAFE DU PORT</t>
+        </is>
+      </c>
+      <c r="E203" s="22" t="inlineStr">
+        <is>
+          <t>LE CAFE DU PORT</t>
+        </is>
+      </c>
+      <c r="F203" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G203" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H203" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I203" s="22" t="inlineStr">
+        <is>
+          <t>22/03/2022</t>
+        </is>
+      </c>
+      <c r="J203" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K203" s="22" t="inlineStr">
+        <is>
+          <t>32 PLACE SAINT-THIEBAULT</t>
+        </is>
+      </c>
+      <c r="L203" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M203" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N203" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O203" s="22" t="inlineStr"/>
+      <c r="P203" s="22" t="inlineStr"/>
+      <c r="Q203" s="22" t="inlineStr"/>
+      <c r="R203" s="23" t="inlineStr"/>
+      <c r="S203" s="22" t="inlineStr"/>
+      <c r="T203" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U203" s="22" t="inlineStr">
+        <is>
+          <t>PERIAT</t>
+        </is>
+      </c>
+      <c r="V203" s="22" t="inlineStr">
+        <is>
+          <t>Anaïs, Eva, Louise</t>
+        </is>
+      </c>
+      <c r="W203" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X203" s="22" t="inlineStr">
+        <is>
+          <t>26 Rue Saint-Paul</t>
+        </is>
+      </c>
+      <c r="Y203" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="Z203" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B204" s="23" t="inlineStr">
+        <is>
+          <t>909107831</t>
+        </is>
+      </c>
+      <c r="C204" s="23" t="inlineStr">
+        <is>
+          <t>90910783100010</t>
+        </is>
+      </c>
+      <c r="D204" s="22" t="inlineStr">
+        <is>
+          <t>BOQUITA</t>
+        </is>
+      </c>
+      <c r="E204" s="22" t="inlineStr">
+        <is>
+          <t>BOQUITA</t>
+        </is>
+      </c>
+      <c r="F204" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G204" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H204" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I204" s="22" t="inlineStr">
+        <is>
+          <t>06/01/2022</t>
+        </is>
+      </c>
+      <c r="J204" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K204" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L204" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M204" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N204" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O204" s="22" t="inlineStr"/>
+      <c r="P204" s="22" t="inlineStr"/>
+      <c r="Q204" s="22" t="inlineStr"/>
+      <c r="R204" s="23" t="inlineStr"/>
+      <c r="S204" s="22" t="inlineStr"/>
+      <c r="T204" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U204" s="22" t="inlineStr">
+        <is>
+          <t>VAISSE</t>
+        </is>
+      </c>
+      <c r="V204" s="22" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="W204" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X204" s="22" t="inlineStr">
+        <is>
+          <t>12 Rue Léon Jouhaux</t>
+        </is>
+      </c>
+      <c r="Y204" s="23" t="inlineStr">
+        <is>
+          <t>75010</t>
+        </is>
+      </c>
+      <c r="Z204" s="22" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B205" s="23" t="inlineStr">
+        <is>
+          <t>852872480</t>
+        </is>
+      </c>
+      <c r="C205" s="23" t="inlineStr">
+        <is>
+          <t>85287248000011</t>
+        </is>
+      </c>
+      <c r="D205" s="22" t="inlineStr">
+        <is>
+          <t>MONDO PIZZA</t>
+        </is>
+      </c>
+      <c r="E205" s="22" t="inlineStr">
+        <is>
+          <t>MONDO PIZZA</t>
+        </is>
+      </c>
+      <c r="F205" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G205" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H205" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I205" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2019</t>
+        </is>
+      </c>
+      <c r="J205" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K205" s="22" t="inlineStr">
+        <is>
+          <t>20 RUE SAINT-PIERRE</t>
+        </is>
+      </c>
+      <c r="L205" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M205" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N205" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O205" s="22" t="n">
+        <v>20833</v>
+      </c>
+      <c r="P205" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q205" s="22" t="inlineStr"/>
+      <c r="R205" s="23" t="inlineStr"/>
+      <c r="S205" s="22" t="inlineStr"/>
+      <c r="T205" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U205" s="22" t="inlineStr">
+        <is>
+          <t>CHOUIKHA</t>
+        </is>
+      </c>
+      <c r="V205" s="22" t="inlineStr">
+        <is>
+          <t>Mohamed, Ali</t>
+        </is>
+      </c>
+      <c r="W205" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X205" s="22" t="inlineStr">
+        <is>
+          <t>1 Rue Général de Gaulle</t>
+        </is>
+      </c>
+      <c r="Y205" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z205" s="22" t="inlineStr">
+        <is>
+          <t>Longeville-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B206" s="23" t="inlineStr">
+        <is>
+          <t>912274776</t>
+        </is>
+      </c>
+      <c r="C206" s="23" t="inlineStr">
+        <is>
+          <t>91227477600018</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="inlineStr">
+        <is>
+          <t>ANGKOR WAT BUBBLE TEA</t>
+        </is>
+      </c>
+      <c r="E206" s="22" t="inlineStr">
+        <is>
+          <t>ANGKOR WAT BUBBLE TEA</t>
+        </is>
+      </c>
+      <c r="F206" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G206" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H206" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I206" s="22" t="inlineStr">
+        <is>
+          <t>14/03/2022</t>
+        </is>
+      </c>
+      <c r="J206" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K206" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE GOUSSAUD</t>
+        </is>
+      </c>
+      <c r="L206" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M206" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N206" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O206" s="22" t="inlineStr"/>
+      <c r="P206" s="22" t="inlineStr"/>
+      <c r="Q206" s="22" t="inlineStr"/>
+      <c r="R206" s="23" t="inlineStr"/>
+      <c r="S206" s="22" t="inlineStr"/>
+      <c r="T206" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U206" s="22" t="inlineStr">
+        <is>
+          <t>CHHIN</t>
+        </is>
+      </c>
+      <c r="V206" s="22" t="inlineStr">
+        <is>
+          <t>Sinoch</t>
+        </is>
+      </c>
+      <c r="W206" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X206" s="22" t="inlineStr">
+        <is>
+          <t>11 rue saint vincent</t>
+        </is>
+      </c>
+      <c r="Y206" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z206" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B207" s="23" t="inlineStr">
+        <is>
+          <t>839969888</t>
+        </is>
+      </c>
+      <c r="C207" s="23" t="inlineStr">
+        <is>
+          <t>83996988800016</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="inlineStr">
+        <is>
+          <t>SAS  SRA</t>
+        </is>
+      </c>
+      <c r="E207" s="22" t="inlineStr">
+        <is>
+          <t>SAS  SRA</t>
+        </is>
+      </c>
+      <c r="F207" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G207" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H207" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I207" s="22" t="inlineStr">
+        <is>
+          <t>29/05/2018</t>
+        </is>
+      </c>
+      <c r="J207" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K207" s="22" t="inlineStr">
+        <is>
+          <t>16 PLACE DES CHARRONS</t>
+        </is>
+      </c>
+      <c r="L207" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M207" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N207" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O207" s="22" t="n">
+        <v>166565</v>
+      </c>
+      <c r="P207" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q207" s="22" t="inlineStr"/>
+      <c r="R207" s="23" t="inlineStr"/>
+      <c r="S207" s="22" t="inlineStr"/>
+      <c r="T207" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U207" s="22" t="inlineStr">
+        <is>
+          <t>TAIRACH</t>
+        </is>
+      </c>
+      <c r="V207" s="22" t="inlineStr">
+        <is>
+          <t>Brahim</t>
+        </is>
+      </c>
+      <c r="W207" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X207" s="22" t="inlineStr">
+        <is>
+          <t>26 rue de la Reole</t>
+        </is>
+      </c>
+      <c r="Y207" s="23" t="inlineStr">
+        <is>
+          <t>54350</t>
+        </is>
+      </c>
+      <c r="Z207" s="22" t="inlineStr">
+        <is>
+          <t>Mont-Saint-Martin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z187"/>
+  <autoFilter ref="A2:Z207"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z207"/>
+  <dimension ref="A1:Z227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21490,2217 +21490,4439 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="22" t="inlineStr">
+      <c r="A188" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B188" s="23" t="inlineStr">
+      <c r="B188" s="21" t="inlineStr">
         <is>
           <t>521477844</t>
         </is>
       </c>
-      <c r="C188" s="23" t="inlineStr">
+      <c r="C188" s="21" t="inlineStr">
         <is>
           <t>52147784400026</t>
         </is>
       </c>
-      <c r="D188" s="22" t="inlineStr">
+      <c r="D188" s="20" t="inlineStr">
         <is>
           <t>SARL VONG</t>
         </is>
       </c>
-      <c r="E188" s="22" t="inlineStr">
+      <c r="E188" s="20" t="inlineStr">
         <is>
           <t>SARL VONG</t>
         </is>
       </c>
-      <c r="F188" s="22" t="inlineStr">
+      <c r="F188" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G188" s="22" t="inlineStr">
+      <c r="G188" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H188" s="22" t="inlineStr">
+      <c r="H188" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I188" s="22" t="inlineStr">
+      <c r="I188" s="20" t="inlineStr">
         <is>
           <t>31/03/2010</t>
         </is>
       </c>
-      <c r="J188" s="22" t="inlineStr">
+      <c r="J188" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K188" s="22" t="inlineStr">
+      <c r="K188" s="20" t="inlineStr">
         <is>
           <t>44 PLACE MAZELLE</t>
         </is>
       </c>
-      <c r="L188" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M188" s="22" t="inlineStr">
+      <c r="L188" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M188" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N188" s="22" t="inlineStr">
+      <c r="N188" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O188" s="22" t="inlineStr"/>
-      <c r="P188" s="22" t="inlineStr"/>
-      <c r="Q188" s="22" t="inlineStr"/>
-      <c r="R188" s="23" t="inlineStr"/>
-      <c r="S188" s="22" t="inlineStr"/>
-      <c r="T188" s="22" t="inlineStr">
+      <c r="O188" s="20" t="inlineStr"/>
+      <c r="P188" s="20" t="inlineStr"/>
+      <c r="Q188" s="20" t="inlineStr"/>
+      <c r="R188" s="21" t="inlineStr"/>
+      <c r="S188" s="20" t="inlineStr"/>
+      <c r="T188" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U188" s="22" t="inlineStr">
+      <c r="U188" s="20" t="inlineStr">
         <is>
           <t>NOANG</t>
         </is>
       </c>
-      <c r="V188" s="22" t="inlineStr">
+      <c r="V188" s="20" t="inlineStr">
         <is>
           <t>Sylvie</t>
         </is>
       </c>
-      <c r="W188" s="22" t="inlineStr">
+      <c r="W188" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X188" s="22" t="inlineStr">
+      <c r="X188" s="20" t="inlineStr">
         <is>
           <t>6 rue du Bugey</t>
         </is>
       </c>
-      <c r="Y188" s="23" t="inlineStr">
+      <c r="Y188" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z188" s="22" t="inlineStr">
+      <c r="Z188" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="22" t="inlineStr">
+      <c r="A189" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B189" s="23" t="inlineStr">
+      <c r="B189" s="21" t="inlineStr">
         <is>
           <t>984246629</t>
         </is>
       </c>
-      <c r="C189" s="23" t="inlineStr">
+      <c r="C189" s="21" t="inlineStr">
         <is>
           <t>98424662900013</t>
         </is>
       </c>
-      <c r="D189" s="22" t="inlineStr">
+      <c r="D189" s="20" t="inlineStr">
         <is>
           <t>CHEZ MARIETTE</t>
         </is>
       </c>
-      <c r="E189" s="22" t="inlineStr">
+      <c r="E189" s="20" t="inlineStr">
         <is>
           <t>CHEZ MARIETTE</t>
         </is>
       </c>
-      <c r="F189" s="22" t="inlineStr">
+      <c r="F189" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G189" s="22" t="inlineStr">
+      <c r="G189" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H189" s="22" t="inlineStr">
+      <c r="H189" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I189" s="22" t="inlineStr">
+      <c r="I189" s="20" t="inlineStr">
         <is>
           <t>12/01/2024</t>
         </is>
       </c>
-      <c r="J189" s="22" t="inlineStr">
+      <c r="J189" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K189" s="22" t="inlineStr">
+      <c r="K189" s="20" t="inlineStr">
         <is>
           <t>16 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L189" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M189" s="22" t="inlineStr">
+      <c r="L189" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M189" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N189" s="22" t="inlineStr">
+      <c r="N189" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O189" s="22" t="inlineStr"/>
-      <c r="P189" s="22" t="inlineStr"/>
-      <c r="Q189" s="22" t="inlineStr"/>
-      <c r="R189" s="23" t="inlineStr"/>
-      <c r="S189" s="22" t="inlineStr"/>
-      <c r="T189" s="22" t="inlineStr">
+      <c r="O189" s="20" t="inlineStr"/>
+      <c r="P189" s="20" t="inlineStr"/>
+      <c r="Q189" s="20" t="inlineStr"/>
+      <c r="R189" s="21" t="inlineStr"/>
+      <c r="S189" s="20" t="inlineStr"/>
+      <c r="T189" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U189" s="22" t="inlineStr">
+      <c r="U189" s="20" t="inlineStr">
         <is>
           <t>EISENBERG</t>
         </is>
       </c>
-      <c r="V189" s="22" t="inlineStr">
+      <c r="V189" s="20" t="inlineStr">
         <is>
           <t>Laura</t>
         </is>
       </c>
-      <c r="W189" s="22" t="inlineStr">
+      <c r="W189" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X189" s="22" t="inlineStr">
+      <c r="X189" s="20" t="inlineStr">
         <is>
           <t>43 rue saint andre</t>
         </is>
       </c>
-      <c r="Y189" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z189" s="22" t="inlineStr">
+      <c r="Y189" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z189" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="22" t="inlineStr">
+      <c r="A190" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B190" s="23" t="inlineStr">
+      <c r="B190" s="21" t="inlineStr">
         <is>
           <t>950787556</t>
         </is>
       </c>
-      <c r="C190" s="23" t="inlineStr">
+      <c r="C190" s="21" t="inlineStr">
         <is>
           <t>95078755600014</t>
         </is>
       </c>
-      <c r="D190" s="22" t="inlineStr">
+      <c r="D190" s="20" t="inlineStr">
         <is>
           <t>SZ AVA SARL</t>
         </is>
       </c>
-      <c r="E190" s="22" t="inlineStr">
+      <c r="E190" s="20" t="inlineStr">
         <is>
           <t>SZ AVA SARL</t>
         </is>
       </c>
-      <c r="F190" s="22" t="inlineStr">
+      <c r="F190" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G190" s="22" t="inlineStr">
+      <c r="G190" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H190" s="22" t="inlineStr">
+      <c r="H190" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I190" s="22" t="inlineStr">
+      <c r="I190" s="20" t="inlineStr">
         <is>
           <t>21/03/2023</t>
         </is>
       </c>
-      <c r="J190" s="22" t="inlineStr">
+      <c r="J190" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K190" s="22" t="inlineStr">
+      <c r="K190" s="20" t="inlineStr">
         <is>
           <t>1 RUE DU PONT DES ROCHES</t>
         </is>
       </c>
-      <c r="L190" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M190" s="22" t="inlineStr">
+      <c r="L190" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M190" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N190" s="22" t="inlineStr">
+      <c r="N190" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O190" s="22" t="inlineStr"/>
-      <c r="P190" s="22" t="inlineStr"/>
-      <c r="Q190" s="22" t="inlineStr"/>
-      <c r="R190" s="23" t="inlineStr"/>
-      <c r="S190" s="22" t="inlineStr"/>
-      <c r="T190" s="22" t="inlineStr">
+      <c r="O190" s="20" t="inlineStr"/>
+      <c r="P190" s="20" t="inlineStr"/>
+      <c r="Q190" s="20" t="inlineStr"/>
+      <c r="R190" s="21" t="inlineStr"/>
+      <c r="S190" s="20" t="inlineStr"/>
+      <c r="T190" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U190" s="22" t="inlineStr">
+      <c r="U190" s="20" t="inlineStr">
         <is>
           <t>MULLER</t>
         </is>
       </c>
-      <c r="V190" s="22" t="inlineStr">
+      <c r="V190" s="20" t="inlineStr">
         <is>
           <t>Stéphane</t>
         </is>
       </c>
-      <c r="W190" s="22" t="inlineStr">
+      <c r="W190" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X190" s="22" t="inlineStr">
+      <c r="X190" s="20" t="inlineStr">
         <is>
           <t>18 Rue de la Haye</t>
         </is>
       </c>
-      <c r="Y190" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z190" s="22" t="inlineStr">
+      <c r="Y190" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z190" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="22" t="inlineStr">
+      <c r="A191" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B191" s="23" t="inlineStr">
+      <c r="B191" s="21" t="inlineStr">
         <is>
           <t>853606333</t>
         </is>
       </c>
-      <c r="C191" s="23" t="inlineStr">
+      <c r="C191" s="21" t="inlineStr">
         <is>
           <t>85360633300013</t>
         </is>
       </c>
-      <c r="D191" s="22" t="inlineStr">
+      <c r="D191" s="20" t="inlineStr">
         <is>
           <t>DE MELLO Richard</t>
         </is>
       </c>
-      <c r="E191" s="22" t="inlineStr">
+      <c r="E191" s="20" t="inlineStr">
         <is>
           <t>DE MELLO Richard</t>
         </is>
       </c>
-      <c r="F191" s="22" t="inlineStr">
+      <c r="F191" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G191" s="22" t="inlineStr">
+      <c r="G191" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H191" s="22" t="inlineStr">
+      <c r="H191" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I191" s="22" t="inlineStr">
+      <c r="I191" s="20" t="inlineStr">
         <is>
           <t>13/09/2019</t>
         </is>
       </c>
-      <c r="J191" s="22" t="inlineStr">
+      <c r="J191" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K191" s="22" t="inlineStr">
+      <c r="K191" s="20" t="inlineStr">
         <is>
           <t>3 RUE DU PARADIS</t>
         </is>
       </c>
-      <c r="L191" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M191" s="22" t="inlineStr">
+      <c r="L191" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M191" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N191" s="22" t="inlineStr">
+      <c r="N191" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O191" s="22" t="inlineStr"/>
-      <c r="P191" s="22" t="inlineStr"/>
-      <c r="Q191" s="22" t="inlineStr"/>
-      <c r="R191" s="23" t="inlineStr"/>
-      <c r="S191" s="22" t="inlineStr"/>
-      <c r="T191" s="22" t="inlineStr">
+      <c r="O191" s="20" t="inlineStr"/>
+      <c r="P191" s="20" t="inlineStr"/>
+      <c r="Q191" s="20" t="inlineStr"/>
+      <c r="R191" s="21" t="inlineStr"/>
+      <c r="S191" s="20" t="inlineStr"/>
+      <c r="T191" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U191" s="22" t="inlineStr">
+      <c r="U191" s="20" t="inlineStr">
         <is>
           <t>DE MELLO</t>
         </is>
       </c>
-      <c r="V191" s="22" t="inlineStr">
+      <c r="V191" s="20" t="inlineStr">
         <is>
           <t>Richard, Denis, Maurice</t>
         </is>
       </c>
-      <c r="W191" s="22" t="inlineStr">
+      <c r="W191" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X191" s="22" t="inlineStr"/>
-      <c r="Y191" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z191" s="22" t="inlineStr">
+      <c r="X191" s="20" t="inlineStr"/>
+      <c r="Y191" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z191" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="22" t="inlineStr">
+      <c r="A192" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B192" s="23" t="inlineStr">
+      <c r="B192" s="21" t="inlineStr">
         <is>
           <t>945208700</t>
         </is>
       </c>
-      <c r="C192" s="23" t="inlineStr">
+      <c r="C192" s="21" t="inlineStr">
         <is>
           <t>94520870000019</t>
         </is>
       </c>
-      <c r="D192" s="22" t="inlineStr">
+      <c r="D192" s="20" t="inlineStr">
         <is>
           <t>CASA RAMEN</t>
         </is>
       </c>
-      <c r="E192" s="22" t="inlineStr">
+      <c r="E192" s="20" t="inlineStr">
         <is>
           <t>CASA RAMEN</t>
         </is>
       </c>
-      <c r="F192" s="22" t="inlineStr">
+      <c r="F192" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G192" s="22" t="inlineStr">
+      <c r="G192" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H192" s="22" t="inlineStr">
+      <c r="H192" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I192" s="22" t="inlineStr">
+      <c r="I192" s="20" t="inlineStr">
         <is>
           <t>21/05/2025</t>
         </is>
       </c>
-      <c r="J192" s="22" t="inlineStr">
+      <c r="J192" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K192" s="22" t="inlineStr">
+      <c r="K192" s="20" t="inlineStr">
         <is>
           <t>22 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L192" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M192" s="22" t="inlineStr">
+      <c r="L192" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M192" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N192" s="22" t="inlineStr">
+      <c r="N192" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O192" s="22" t="inlineStr"/>
-      <c r="P192" s="22" t="inlineStr"/>
-      <c r="Q192" s="22" t="inlineStr"/>
-      <c r="R192" s="23" t="inlineStr"/>
-      <c r="S192" s="22" t="inlineStr"/>
-      <c r="T192" s="22" t="inlineStr">
+      <c r="O192" s="20" t="inlineStr"/>
+      <c r="P192" s="20" t="inlineStr"/>
+      <c r="Q192" s="20" t="inlineStr"/>
+      <c r="R192" s="21" t="inlineStr"/>
+      <c r="S192" s="20" t="inlineStr"/>
+      <c r="T192" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U192" s="22" t="inlineStr">
+      <c r="U192" s="20" t="inlineStr">
         <is>
           <t>SUK</t>
         </is>
       </c>
-      <c r="V192" s="22" t="inlineStr">
+      <c r="V192" s="20" t="inlineStr">
         <is>
           <t>Laurent, Sébastien</t>
         </is>
       </c>
-      <c r="W192" s="22" t="inlineStr">
+      <c r="W192" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X192" s="22" t="inlineStr"/>
-      <c r="Y192" s="23" t="inlineStr">
+      <c r="X192" s="20" t="inlineStr"/>
+      <c r="Y192" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z192" s="22" t="inlineStr">
+      <c r="Z192" s="20" t="inlineStr">
         <is>
           <t>Norroy-le-Veneur</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="22" t="inlineStr">
+      <c r="A193" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B193" s="23" t="inlineStr">
+      <c r="B193" s="21" t="inlineStr">
         <is>
           <t>404529984</t>
         </is>
       </c>
-      <c r="C193" s="23" t="inlineStr">
+      <c r="C193" s="21" t="inlineStr">
         <is>
           <t>40452998400019</t>
         </is>
       </c>
-      <c r="D193" s="22" t="inlineStr">
+      <c r="D193" s="20" t="inlineStr">
         <is>
           <t>BAZ ANGEL ALONSO MANUEL</t>
         </is>
       </c>
-      <c r="E193" s="22" t="inlineStr">
+      <c r="E193" s="20" t="inlineStr">
         <is>
           <t>BAZ ANGEL ALONSO MANUEL</t>
         </is>
       </c>
-      <c r="F193" s="22" t="inlineStr">
+      <c r="F193" s="20" t="inlineStr">
         <is>
           <t>Société créée de fait entre personnes physiques</t>
         </is>
       </c>
-      <c r="G193" s="22" t="inlineStr">
+      <c r="G193" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H193" s="22" t="inlineStr">
+      <c r="H193" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I193" s="22" t="inlineStr">
+      <c r="I193" s="20" t="inlineStr">
         <is>
           <t>11/08/1995</t>
         </is>
       </c>
-      <c r="J193" s="22" t="inlineStr">
+      <c r="J193" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="K193" s="22" t="inlineStr">
+      <c r="K193" s="20" t="inlineStr">
         <is>
           <t>1 RUE DU CHAMPE</t>
         </is>
       </c>
-      <c r="L193" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M193" s="22" t="inlineStr">
+      <c r="L193" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M193" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N193" s="22" t="inlineStr">
+      <c r="N193" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O193" s="22" t="inlineStr"/>
-      <c r="P193" s="22" t="inlineStr"/>
-      <c r="Q193" s="22" t="inlineStr"/>
-      <c r="R193" s="23" t="inlineStr"/>
-      <c r="S193" s="22" t="inlineStr"/>
-      <c r="T193" s="22" t="inlineStr">
+      <c r="O193" s="20" t="inlineStr"/>
+      <c r="P193" s="20" t="inlineStr"/>
+      <c r="Q193" s="20" t="inlineStr"/>
+      <c r="R193" s="21" t="inlineStr"/>
+      <c r="S193" s="20" t="inlineStr"/>
+      <c r="T193" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U193" s="22" t="inlineStr"/>
-      <c r="V193" s="22" t="inlineStr"/>
-      <c r="W193" s="22" t="inlineStr"/>
-      <c r="X193" s="22" t="inlineStr"/>
-      <c r="Y193" s="23" t="inlineStr"/>
-      <c r="Z193" s="22" t="inlineStr"/>
+      <c r="U193" s="20" t="inlineStr"/>
+      <c r="V193" s="20" t="inlineStr"/>
+      <c r="W193" s="20" t="inlineStr"/>
+      <c r="X193" s="20" t="inlineStr"/>
+      <c r="Y193" s="21" t="inlineStr"/>
+      <c r="Z193" s="20" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="22" t="inlineStr">
+      <c r="A194" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B194" s="23" t="inlineStr">
+      <c r="B194" s="21" t="inlineStr">
         <is>
           <t>102628740</t>
         </is>
       </c>
-      <c r="C194" s="23" t="inlineStr">
+      <c r="C194" s="21" t="inlineStr">
         <is>
           <t>10262874000015</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="D194" s="20" t="inlineStr">
         <is>
           <t>BARAMEYS SAS</t>
         </is>
       </c>
-      <c r="E194" s="22" t="inlineStr">
+      <c r="E194" s="20" t="inlineStr">
         <is>
           <t>BARAMEYS SAS</t>
         </is>
       </c>
-      <c r="F194" s="22" t="inlineStr">
+      <c r="F194" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G194" s="22" t="inlineStr">
+      <c r="G194" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H194" s="22" t="inlineStr">
+      <c r="H194" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I194" s="22" t="inlineStr">
+      <c r="I194" s="20" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="J194" s="22" t="inlineStr">
+      <c r="J194" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K194" s="22" t="inlineStr">
+      <c r="K194" s="20" t="inlineStr">
         <is>
           <t>11 RUE SAINT-VINCENT</t>
         </is>
       </c>
-      <c r="L194" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M194" s="22" t="inlineStr">
+      <c r="L194" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M194" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N194" s="22" t="inlineStr">
+      <c r="N194" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O194" s="22" t="inlineStr"/>
-      <c r="P194" s="22" t="inlineStr"/>
-      <c r="Q194" s="22" t="inlineStr"/>
-      <c r="R194" s="23" t="inlineStr"/>
-      <c r="S194" s="22" t="inlineStr"/>
-      <c r="T194" s="22" t="inlineStr">
+      <c r="O194" s="20" t="inlineStr"/>
+      <c r="P194" s="20" t="inlineStr"/>
+      <c r="Q194" s="20" t="inlineStr"/>
+      <c r="R194" s="21" t="inlineStr"/>
+      <c r="S194" s="20" t="inlineStr"/>
+      <c r="T194" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U194" s="22" t="inlineStr">
+      <c r="U194" s="20" t="inlineStr">
         <is>
           <t>CHHIN</t>
         </is>
       </c>
-      <c r="V194" s="22" t="inlineStr">
+      <c r="V194" s="20" t="inlineStr">
         <is>
           <t>Sinoch</t>
         </is>
       </c>
-      <c r="W194" s="22" t="inlineStr">
+      <c r="W194" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X194" s="22" t="inlineStr">
+      <c r="X194" s="20" t="inlineStr">
         <is>
           <t>ll,rue soint vincent</t>
         </is>
       </c>
-      <c r="Y194" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z194" s="22" t="inlineStr">
+      <c r="Y194" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z194" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="22" t="inlineStr">
+      <c r="A195" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B195" s="23" t="inlineStr">
+      <c r="B195" s="21" t="inlineStr">
         <is>
           <t>921835187</t>
         </is>
       </c>
-      <c r="C195" s="23" t="inlineStr">
+      <c r="C195" s="21" t="inlineStr">
         <is>
           <t>92183518700011</t>
         </is>
       </c>
-      <c r="D195" s="22" t="inlineStr">
+      <c r="D195" s="20" t="inlineStr">
         <is>
           <t>HOTH</t>
         </is>
       </c>
-      <c r="E195" s="22" t="inlineStr">
+      <c r="E195" s="20" t="inlineStr">
         <is>
           <t>HOTH</t>
         </is>
       </c>
-      <c r="F195" s="22" t="inlineStr">
+      <c r="F195" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G195" s="22" t="inlineStr">
+      <c r="G195" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H195" s="22" t="inlineStr">
+      <c r="H195" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I195" s="22" t="inlineStr">
+      <c r="I195" s="20" t="inlineStr">
         <is>
           <t>01/12/2022</t>
         </is>
       </c>
-      <c r="J195" s="22" t="inlineStr">
+      <c r="J195" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K195" s="22" t="inlineStr">
+      <c r="K195" s="20" t="inlineStr">
         <is>
           <t>20 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L195" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M195" s="22" t="inlineStr">
+      <c r="L195" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M195" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N195" s="22" t="inlineStr">
+      <c r="N195" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O195" s="22" t="inlineStr"/>
-      <c r="P195" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q195" s="22" t="inlineStr"/>
-      <c r="R195" s="23" t="inlineStr"/>
-      <c r="S195" s="22" t="inlineStr"/>
-      <c r="T195" s="22" t="inlineStr">
+      <c r="O195" s="20" t="inlineStr"/>
+      <c r="P195" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q195" s="20" t="inlineStr"/>
+      <c r="R195" s="21" t="inlineStr"/>
+      <c r="S195" s="20" t="inlineStr"/>
+      <c r="T195" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U195" s="22" t="inlineStr">
+      <c r="U195" s="20" t="inlineStr">
         <is>
           <t>GUYON</t>
         </is>
       </c>
-      <c r="V195" s="22" t="inlineStr">
+      <c r="V195" s="20" t="inlineStr">
         <is>
           <t>Arnaud, Joseph, Marcel, Marie</t>
         </is>
       </c>
-      <c r="W195" s="22" t="inlineStr">
+      <c r="W195" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X195" s="22" t="inlineStr"/>
-      <c r="Y195" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z195" s="22" t="inlineStr">
+      <c r="X195" s="20" t="inlineStr"/>
+      <c r="Y195" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z195" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="22" t="inlineStr">
+      <c r="A196" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B196" s="23" t="inlineStr">
+      <c r="B196" s="21" t="inlineStr">
         <is>
           <t>845249119</t>
         </is>
       </c>
-      <c r="C196" s="23" t="inlineStr">
+      <c r="C196" s="21" t="inlineStr">
         <is>
           <t>84524911900015</t>
         </is>
       </c>
-      <c r="D196" s="22" t="inlineStr">
+      <c r="D196" s="20" t="inlineStr">
         <is>
           <t>DI ZHENG</t>
         </is>
       </c>
-      <c r="E196" s="22" t="inlineStr">
+      <c r="E196" s="20" t="inlineStr">
         <is>
           <t>DI ZHENG</t>
         </is>
       </c>
-      <c r="F196" s="22" t="inlineStr">
+      <c r="F196" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G196" s="22" t="inlineStr">
+      <c r="G196" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H196" s="22" t="inlineStr">
+      <c r="H196" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I196" s="22" t="inlineStr">
+      <c r="I196" s="20" t="inlineStr">
         <is>
           <t>14/01/2019</t>
         </is>
       </c>
-      <c r="J196" s="22" t="inlineStr">
+      <c r="J196" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K196" s="22" t="inlineStr">
+      <c r="K196" s="20" t="inlineStr">
         <is>
           <t>5 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L196" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M196" s="22" t="inlineStr">
+      <c r="L196" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M196" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N196" s="22" t="inlineStr">
+      <c r="N196" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O196" s="22" t="inlineStr"/>
-      <c r="P196" s="22" t="inlineStr"/>
-      <c r="Q196" s="22" t="inlineStr"/>
-      <c r="R196" s="23" t="inlineStr"/>
-      <c r="S196" s="22" t="inlineStr"/>
-      <c r="T196" s="22" t="inlineStr">
+      <c r="O196" s="20" t="inlineStr"/>
+      <c r="P196" s="20" t="inlineStr"/>
+      <c r="Q196" s="20" t="inlineStr"/>
+      <c r="R196" s="21" t="inlineStr"/>
+      <c r="S196" s="20" t="inlineStr"/>
+      <c r="T196" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U196" s="22" t="inlineStr">
+      <c r="U196" s="20" t="inlineStr">
         <is>
           <t>ZHENG</t>
         </is>
       </c>
-      <c r="V196" s="22" t="inlineStr">
+      <c r="V196" s="20" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="W196" s="22" t="inlineStr">
+      <c r="W196" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X196" s="22" t="inlineStr">
+      <c r="X196" s="20" t="inlineStr">
         <is>
           <t>26 avenue Anatole France</t>
         </is>
       </c>
-      <c r="Y196" s="23" t="inlineStr">
+      <c r="Y196" s="21" t="inlineStr">
         <is>
           <t>93500</t>
         </is>
       </c>
-      <c r="Z196" s="22" t="inlineStr">
+      <c r="Z196" s="20" t="inlineStr">
         <is>
           <t>Pantin</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="22" t="inlineStr">
+      <c r="A197" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B197" s="23" t="inlineStr">
+      <c r="B197" s="21" t="inlineStr">
         <is>
           <t>918159047</t>
         </is>
       </c>
-      <c r="C197" s="23" t="inlineStr">
+      <c r="C197" s="21" t="inlineStr">
         <is>
           <t>91815904700078</t>
         </is>
       </c>
-      <c r="D197" s="22" t="inlineStr">
+      <c r="D197" s="20" t="inlineStr">
         <is>
           <t>HJMN</t>
         </is>
       </c>
-      <c r="E197" s="22" t="inlineStr">
+      <c r="E197" s="20" t="inlineStr">
         <is>
           <t>HJMN</t>
         </is>
       </c>
-      <c r="F197" s="22" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G197" s="22" t="inlineStr">
+      <c r="G197" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H197" s="22" t="inlineStr">
+      <c r="H197" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I197" s="22" t="inlineStr">
+      <c r="I197" s="20" t="inlineStr">
         <is>
           <t>19/10/2022</t>
         </is>
       </c>
-      <c r="J197" s="22" t="inlineStr">
+      <c r="J197" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K197" s="22" t="inlineStr">
+      <c r="K197" s="20" t="inlineStr">
         <is>
           <t>4 RUE SERPENOISE</t>
         </is>
       </c>
-      <c r="L197" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M197" s="22" t="inlineStr">
+      <c r="L197" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M197" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N197" s="22" t="inlineStr">
+      <c r="N197" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O197" s="22" t="inlineStr"/>
-      <c r="P197" s="22" t="inlineStr"/>
-      <c r="Q197" s="22" t="inlineStr"/>
-      <c r="R197" s="23" t="inlineStr"/>
-      <c r="S197" s="22" t="inlineStr"/>
-      <c r="T197" s="22" t="inlineStr">
+      <c r="O197" s="20" t="inlineStr"/>
+      <c r="P197" s="20" t="inlineStr"/>
+      <c r="Q197" s="20" t="inlineStr"/>
+      <c r="R197" s="21" t="inlineStr"/>
+      <c r="S197" s="20" t="inlineStr"/>
+      <c r="T197" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U197" s="22" t="inlineStr">
+      <c r="U197" s="20" t="inlineStr">
         <is>
           <t>BUDAIOVA</t>
         </is>
       </c>
-      <c r="V197" s="22" t="inlineStr">
+      <c r="V197" s="20" t="inlineStr">
         <is>
           <t>Sara</t>
         </is>
       </c>
-      <c r="W197" s="22" t="inlineStr">
+      <c r="W197" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X197" s="22" t="inlineStr"/>
-      <c r="Y197" s="23" t="inlineStr">
+      <c r="X197" s="20" t="inlineStr"/>
+      <c r="Y197" s="21" t="inlineStr">
         <is>
           <t>93200</t>
         </is>
       </c>
-      <c r="Z197" s="22" t="inlineStr">
+      <c r="Z197" s="20" t="inlineStr">
         <is>
           <t>Saint-Denis</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="22" t="inlineStr">
+      <c r="A198" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B198" s="23" t="inlineStr">
+      <c r="B198" s="21" t="inlineStr">
         <is>
           <t>403469174</t>
         </is>
       </c>
-      <c r="C198" s="23" t="inlineStr">
+      <c r="C198" s="21" t="inlineStr">
         <is>
           <t>40346917400011</t>
         </is>
       </c>
-      <c r="D198" s="22" t="inlineStr">
+      <c r="D198" s="20" t="inlineStr">
         <is>
           <t>AMPIRE</t>
         </is>
       </c>
-      <c r="E198" s="22" t="inlineStr">
+      <c r="E198" s="20" t="inlineStr">
         <is>
           <t>AMPIRE</t>
         </is>
       </c>
-      <c r="F198" s="22" t="inlineStr">
+      <c r="F198" s="20" t="inlineStr">
         <is>
           <t>SA à conseil d'administration (s.a.i.)</t>
         </is>
       </c>
-      <c r="G198" s="22" t="inlineStr">
+      <c r="G198" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H198" s="22" t="inlineStr">
+      <c r="H198" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I198" s="22" t="inlineStr">
+      <c r="I198" s="20" t="inlineStr">
         <is>
           <t>01/11/1995</t>
         </is>
       </c>
-      <c r="J198" s="22" t="inlineStr">
+      <c r="J198" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="K198" s="22" t="inlineStr">
+      <c r="K198" s="20" t="inlineStr">
         <is>
           <t>MARCHE DE LA CHEVRE</t>
         </is>
       </c>
-      <c r="L198" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M198" s="22" t="inlineStr">
+      <c r="L198" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M198" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N198" s="22" t="inlineStr">
+      <c r="N198" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O198" s="22" t="inlineStr"/>
-      <c r="P198" s="22" t="inlineStr"/>
-      <c r="Q198" s="22" t="inlineStr"/>
-      <c r="R198" s="23" t="inlineStr"/>
-      <c r="S198" s="22" t="inlineStr"/>
-      <c r="T198" s="22" t="inlineStr">
+      <c r="O198" s="20" t="inlineStr"/>
+      <c r="P198" s="20" t="inlineStr"/>
+      <c r="Q198" s="20" t="inlineStr"/>
+      <c r="R198" s="21" t="inlineStr"/>
+      <c r="S198" s="20" t="inlineStr"/>
+      <c r="T198" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U198" s="22" t="inlineStr">
+      <c r="U198" s="20" t="inlineStr">
         <is>
           <t>ARNOULD</t>
         </is>
       </c>
-      <c r="V198" s="22" t="inlineStr">
+      <c r="V198" s="20" t="inlineStr">
         <is>
           <t>Michel</t>
         </is>
       </c>
-      <c r="W198" s="22" t="inlineStr">
+      <c r="W198" s="20" t="inlineStr">
         <is>
           <t>Président du conseil d'administration, Directeur général</t>
         </is>
       </c>
-      <c r="X198" s="22" t="inlineStr">
+      <c r="X198" s="20" t="inlineStr">
         <is>
           <t>20 place Carnot</t>
         </is>
       </c>
-      <c r="Y198" s="23" t="inlineStr">
+      <c r="Y198" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="Z198" s="22" t="inlineStr">
+      <c r="Z198" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="22" t="inlineStr">
+      <c r="A199" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B199" s="23" t="inlineStr">
+      <c r="B199" s="21" t="inlineStr">
         <is>
           <t>505123745</t>
         </is>
       </c>
-      <c r="C199" s="23" t="inlineStr">
+      <c r="C199" s="21" t="inlineStr">
         <is>
           <t>50512374500018</t>
         </is>
       </c>
-      <c r="D199" s="22" t="inlineStr">
+      <c r="D199" s="20" t="inlineStr">
         <is>
           <t>C.D.F.P.</t>
         </is>
       </c>
-      <c r="E199" s="22" t="inlineStr">
+      <c r="E199" s="20" t="inlineStr">
         <is>
           <t>C.D.F.P.</t>
         </is>
       </c>
-      <c r="F199" s="22" t="inlineStr">
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G199" s="22" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H199" s="22" t="inlineStr">
+      <c r="H199" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I199" s="22" t="inlineStr">
+      <c r="I199" s="20" t="inlineStr">
         <is>
           <t>07/07/2008</t>
         </is>
       </c>
-      <c r="J199" s="22" t="inlineStr">
+      <c r="J199" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K199" s="22" t="inlineStr">
+      <c r="K199" s="20" t="inlineStr">
         <is>
           <t>29 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L199" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M199" s="22" t="inlineStr">
+      <c r="L199" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M199" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N199" s="22" t="inlineStr">
+      <c r="N199" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O199" s="22" t="inlineStr"/>
-      <c r="P199" s="22" t="inlineStr"/>
-      <c r="Q199" s="22" t="inlineStr"/>
-      <c r="R199" s="23" t="inlineStr"/>
-      <c r="S199" s="22" t="inlineStr"/>
-      <c r="T199" s="22" t="inlineStr">
+      <c r="O199" s="20" t="inlineStr"/>
+      <c r="P199" s="20" t="inlineStr"/>
+      <c r="Q199" s="20" t="inlineStr"/>
+      <c r="R199" s="21" t="inlineStr"/>
+      <c r="S199" s="20" t="inlineStr"/>
+      <c r="T199" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U199" s="22" t="inlineStr">
+      <c r="U199" s="20" t="inlineStr">
         <is>
           <t>BASTIEN</t>
         </is>
       </c>
-      <c r="V199" s="22" t="inlineStr">
+      <c r="V199" s="20" t="inlineStr">
         <is>
           <t>Christophe, Pierre, Michel</t>
         </is>
       </c>
-      <c r="W199" s="22" t="inlineStr">
+      <c r="W199" s="20" t="inlineStr">
         <is>
           <t>Gérant, Associé indéfiniment responsable</t>
         </is>
       </c>
-      <c r="X199" s="22" t="inlineStr">
+      <c r="X199" s="20" t="inlineStr">
         <is>
           <t>10 rue aux Ours</t>
         </is>
       </c>
-      <c r="Y199" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z199" s="22" t="inlineStr">
+      <c r="Y199" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z199" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="22" t="inlineStr">
+      <c r="A200" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B200" s="23" t="inlineStr">
+      <c r="B200" s="21" t="inlineStr">
         <is>
           <t>878094952</t>
         </is>
       </c>
-      <c r="C200" s="23" t="inlineStr">
+      <c r="C200" s="21" t="inlineStr">
         <is>
           <t>87809495200016</t>
         </is>
       </c>
-      <c r="D200" s="22" t="inlineStr">
+      <c r="D200" s="20" t="inlineStr">
         <is>
           <t>BIERSTUB</t>
         </is>
       </c>
-      <c r="E200" s="22" t="inlineStr">
+      <c r="E200" s="20" t="inlineStr">
         <is>
           <t>BIERSTUB</t>
         </is>
       </c>
-      <c r="F200" s="22" t="inlineStr">
+      <c r="F200" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G200" s="22" t="inlineStr">
+      <c r="G200" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H200" s="22" t="inlineStr">
+      <c r="H200" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I200" s="22" t="inlineStr">
+      <c r="I200" s="20" t="inlineStr">
         <is>
           <t>11/10/2019</t>
         </is>
       </c>
-      <c r="J200" s="22" t="inlineStr">
+      <c r="J200" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K200" s="22" t="inlineStr">
+      <c r="K200" s="20" t="inlineStr">
         <is>
           <t>44 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L200" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M200" s="22" t="inlineStr">
+      <c r="L200" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M200" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N200" s="22" t="inlineStr">
+      <c r="N200" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O200" s="22" t="inlineStr"/>
-      <c r="P200" s="22" t="inlineStr"/>
-      <c r="Q200" s="22" t="inlineStr"/>
-      <c r="R200" s="23" t="inlineStr"/>
-      <c r="S200" s="22" t="inlineStr"/>
-      <c r="T200" s="22" t="inlineStr">
+      <c r="O200" s="20" t="inlineStr"/>
+      <c r="P200" s="20" t="inlineStr"/>
+      <c r="Q200" s="20" t="inlineStr"/>
+      <c r="R200" s="21" t="inlineStr"/>
+      <c r="S200" s="20" t="inlineStr"/>
+      <c r="T200" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U200" s="22" t="inlineStr">
+      <c r="U200" s="20" t="inlineStr">
         <is>
           <t>FERREIRA</t>
         </is>
       </c>
-      <c r="V200" s="22" t="inlineStr">
+      <c r="V200" s="20" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="W200" s="22" t="inlineStr">
+      <c r="W200" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X200" s="22" t="inlineStr">
+      <c r="X200" s="20" t="inlineStr">
         <is>
           <t>8 rue des Chardonnerets</t>
         </is>
       </c>
-      <c r="Y200" s="23" t="inlineStr">
+      <c r="Y200" s="21" t="inlineStr">
         <is>
           <t>57365</t>
         </is>
       </c>
-      <c r="Z200" s="22" t="inlineStr">
+      <c r="Z200" s="20" t="inlineStr">
         <is>
           <t>Ennery</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="22" t="inlineStr">
+      <c r="A201" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B201" s="23" t="inlineStr">
+      <c r="B201" s="21" t="inlineStr">
         <is>
           <t>832347397</t>
         </is>
       </c>
-      <c r="C201" s="23" t="inlineStr">
+      <c r="C201" s="21" t="inlineStr">
         <is>
           <t>83234739700016</t>
         </is>
       </c>
-      <c r="D201" s="22" t="inlineStr">
+      <c r="D201" s="20" t="inlineStr">
         <is>
           <t>NANGARHAR</t>
         </is>
       </c>
-      <c r="E201" s="22" t="inlineStr">
+      <c r="E201" s="20" t="inlineStr">
         <is>
           <t>NANGARHAR</t>
         </is>
       </c>
-      <c r="F201" s="22" t="inlineStr">
+      <c r="F201" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G201" s="22" t="inlineStr">
+      <c r="G201" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H201" s="22" t="inlineStr">
+      <c r="H201" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I201" s="22" t="inlineStr">
+      <c r="I201" s="20" t="inlineStr">
         <is>
           <t>15/10/2017</t>
         </is>
       </c>
-      <c r="J201" s="22" t="inlineStr">
+      <c r="J201" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K201" s="22" t="inlineStr">
+      <c r="K201" s="20" t="inlineStr">
         <is>
           <t>17 RUE DU CHANGE</t>
         </is>
       </c>
-      <c r="L201" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M201" s="22" t="inlineStr">
+      <c r="L201" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M201" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N201" s="22" t="inlineStr">
+      <c r="N201" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O201" s="22" t="inlineStr"/>
-      <c r="P201" s="22" t="inlineStr"/>
-      <c r="Q201" s="22" t="inlineStr"/>
-      <c r="R201" s="23" t="inlineStr"/>
-      <c r="S201" s="22" t="inlineStr"/>
-      <c r="T201" s="22" t="inlineStr">
+      <c r="O201" s="20" t="inlineStr"/>
+      <c r="P201" s="20" t="inlineStr"/>
+      <c r="Q201" s="20" t="inlineStr"/>
+      <c r="R201" s="21" t="inlineStr"/>
+      <c r="S201" s="20" t="inlineStr"/>
+      <c r="T201" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U201" s="22" t="inlineStr">
+      <c r="U201" s="20" t="inlineStr">
         <is>
           <t>AHMADZAI</t>
         </is>
       </c>
-      <c r="V201" s="22" t="inlineStr">
+      <c r="V201" s="20" t="inlineStr">
         <is>
           <t>Jacques</t>
         </is>
       </c>
-      <c r="W201" s="22" t="inlineStr">
+      <c r="W201" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X201" s="22" t="inlineStr">
+      <c r="X201" s="20" t="inlineStr">
         <is>
           <t>6 square Henri Dunant</t>
         </is>
       </c>
-      <c r="Y201" s="23" t="inlineStr">
+      <c r="Y201" s="21" t="inlineStr">
         <is>
           <t>93260</t>
         </is>
       </c>
-      <c r="Z201" s="22" t="inlineStr">
+      <c r="Z201" s="20" t="inlineStr">
         <is>
           <t>Les lilas</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="22" t="inlineStr">
+      <c r="A202" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B202" s="23" t="inlineStr">
+      <c r="B202" s="21" t="inlineStr">
         <is>
           <t>934539925</t>
         </is>
       </c>
-      <c r="C202" s="23" t="inlineStr">
+      <c r="C202" s="21" t="inlineStr">
         <is>
           <t>93453992500016</t>
         </is>
       </c>
-      <c r="D202" s="22" t="inlineStr">
+      <c r="D202" s="20" t="inlineStr">
         <is>
           <t>SAVEURS DU TIBET</t>
         </is>
       </c>
-      <c r="E202" s="22" t="inlineStr">
+      <c r="E202" s="20" t="inlineStr">
         <is>
           <t>SAVEURS DU TIBET</t>
         </is>
       </c>
-      <c r="F202" s="22" t="inlineStr">
+      <c r="F202" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G202" s="22" t="inlineStr">
+      <c r="G202" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H202" s="22" t="inlineStr">
+      <c r="H202" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I202" s="22" t="inlineStr">
+      <c r="I202" s="20" t="inlineStr">
         <is>
           <t>15/10/2024</t>
         </is>
       </c>
-      <c r="J202" s="22" t="inlineStr">
+      <c r="J202" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K202" s="22" t="inlineStr">
+      <c r="K202" s="20" t="inlineStr">
         <is>
           <t>3 RUE DU CHAMPE</t>
         </is>
       </c>
-      <c r="L202" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M202" s="22" t="inlineStr">
+      <c r="L202" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M202" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N202" s="22" t="inlineStr">
+      <c r="N202" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O202" s="22" t="inlineStr"/>
-      <c r="P202" s="22" t="inlineStr"/>
-      <c r="Q202" s="22" t="inlineStr"/>
-      <c r="R202" s="23" t="inlineStr"/>
-      <c r="S202" s="22" t="inlineStr"/>
-      <c r="T202" s="22" t="inlineStr">
+      <c r="O202" s="20" t="inlineStr"/>
+      <c r="P202" s="20" t="inlineStr"/>
+      <c r="Q202" s="20" t="inlineStr"/>
+      <c r="R202" s="21" t="inlineStr"/>
+      <c r="S202" s="20" t="inlineStr"/>
+      <c r="T202" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U202" s="22" t="inlineStr">
+      <c r="U202" s="20" t="inlineStr">
         <is>
           <t>TSANG</t>
         </is>
       </c>
-      <c r="V202" s="22" t="inlineStr">
+      <c r="V202" s="20" t="inlineStr">
         <is>
           <t>Nurbu, Tsering</t>
         </is>
       </c>
-      <c r="W202" s="22" t="inlineStr">
+      <c r="W202" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X202" s="22" t="inlineStr">
+      <c r="X202" s="20" t="inlineStr">
         <is>
           <t>69 bis avenue du général de gaulle</t>
         </is>
       </c>
-      <c r="Y202" s="23" t="inlineStr">
+      <c r="Y202" s="21" t="inlineStr">
         <is>
           <t>92800</t>
         </is>
       </c>
-      <c r="Z202" s="22" t="inlineStr">
+      <c r="Z202" s="20" t="inlineStr">
         <is>
           <t>Puteaux</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="22" t="inlineStr">
+      <c r="A203" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B203" s="23" t="inlineStr">
+      <c r="B203" s="21" t="inlineStr">
         <is>
           <t>911630168</t>
         </is>
       </c>
-      <c r="C203" s="23" t="inlineStr">
+      <c r="C203" s="21" t="inlineStr">
         <is>
           <t>91163016800019</t>
         </is>
       </c>
-      <c r="D203" s="22" t="inlineStr">
+      <c r="D203" s="20" t="inlineStr">
         <is>
           <t>LE CAFE DU PORT</t>
         </is>
       </c>
-      <c r="E203" s="22" t="inlineStr">
+      <c r="E203" s="20" t="inlineStr">
         <is>
           <t>LE CAFE DU PORT</t>
         </is>
       </c>
-      <c r="F203" s="22" t="inlineStr">
+      <c r="F203" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G203" s="22" t="inlineStr">
+      <c r="G203" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H203" s="22" t="inlineStr">
+      <c r="H203" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I203" s="22" t="inlineStr">
+      <c r="I203" s="20" t="inlineStr">
         <is>
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="J203" s="22" t="inlineStr">
+      <c r="J203" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K203" s="22" t="inlineStr">
+      <c r="K203" s="20" t="inlineStr">
         <is>
           <t>32 PLACE SAINT-THIEBAULT</t>
         </is>
       </c>
-      <c r="L203" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M203" s="22" t="inlineStr">
+      <c r="L203" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M203" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N203" s="22" t="inlineStr">
+      <c r="N203" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O203" s="22" t="inlineStr"/>
-      <c r="P203" s="22" t="inlineStr"/>
-      <c r="Q203" s="22" t="inlineStr"/>
-      <c r="R203" s="23" t="inlineStr"/>
-      <c r="S203" s="22" t="inlineStr"/>
-      <c r="T203" s="22" t="inlineStr">
+      <c r="O203" s="20" t="inlineStr"/>
+      <c r="P203" s="20" t="inlineStr"/>
+      <c r="Q203" s="20" t="inlineStr"/>
+      <c r="R203" s="21" t="inlineStr"/>
+      <c r="S203" s="20" t="inlineStr"/>
+      <c r="T203" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U203" s="22" t="inlineStr">
+      <c r="U203" s="20" t="inlineStr">
         <is>
           <t>PERIAT</t>
         </is>
       </c>
-      <c r="V203" s="22" t="inlineStr">
+      <c r="V203" s="20" t="inlineStr">
         <is>
           <t>Anaïs, Eva, Louise</t>
         </is>
       </c>
-      <c r="W203" s="22" t="inlineStr">
+      <c r="W203" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X203" s="22" t="inlineStr">
+      <c r="X203" s="20" t="inlineStr">
         <is>
           <t>26 Rue Saint-Paul</t>
         </is>
       </c>
-      <c r="Y203" s="23" t="inlineStr">
+      <c r="Y203" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="Z203" s="22" t="inlineStr">
+      <c r="Z203" s="20" t="inlineStr">
         <is>
           <t>Montigny-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="22" t="inlineStr">
+      <c r="A204" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B204" s="23" t="inlineStr">
+      <c r="B204" s="21" t="inlineStr">
         <is>
           <t>909107831</t>
         </is>
       </c>
-      <c r="C204" s="23" t="inlineStr">
+      <c r="C204" s="21" t="inlineStr">
         <is>
           <t>90910783100010</t>
         </is>
       </c>
-      <c r="D204" s="22" t="inlineStr">
+      <c r="D204" s="20" t="inlineStr">
         <is>
           <t>BOQUITA</t>
         </is>
       </c>
-      <c r="E204" s="22" t="inlineStr">
+      <c r="E204" s="20" t="inlineStr">
         <is>
           <t>BOQUITA</t>
         </is>
       </c>
-      <c r="F204" s="22" t="inlineStr">
+      <c r="F204" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G204" s="22" t="inlineStr">
+      <c r="G204" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H204" s="22" t="inlineStr">
+      <c r="H204" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I204" s="22" t="inlineStr">
+      <c r="I204" s="20" t="inlineStr">
         <is>
           <t>06/01/2022</t>
         </is>
       </c>
-      <c r="J204" s="22" t="inlineStr">
+      <c r="J204" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K204" s="22" t="inlineStr">
+      <c r="K204" s="20" t="inlineStr">
         <is>
           <t>4 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L204" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M204" s="22" t="inlineStr">
+      <c r="L204" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M204" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N204" s="22" t="inlineStr">
+      <c r="N204" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O204" s="22" t="inlineStr"/>
-      <c r="P204" s="22" t="inlineStr"/>
-      <c r="Q204" s="22" t="inlineStr"/>
-      <c r="R204" s="23" t="inlineStr"/>
-      <c r="S204" s="22" t="inlineStr"/>
-      <c r="T204" s="22" t="inlineStr">
+      <c r="O204" s="20" t="inlineStr"/>
+      <c r="P204" s="20" t="inlineStr"/>
+      <c r="Q204" s="20" t="inlineStr"/>
+      <c r="R204" s="21" t="inlineStr"/>
+      <c r="S204" s="20" t="inlineStr"/>
+      <c r="T204" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U204" s="22" t="inlineStr">
+      <c r="U204" s="20" t="inlineStr">
         <is>
           <t>VAISSE</t>
         </is>
       </c>
-      <c r="V204" s="22" t="inlineStr">
+      <c r="V204" s="20" t="inlineStr">
         <is>
           <t>Camille</t>
         </is>
       </c>
-      <c r="W204" s="22" t="inlineStr">
+      <c r="W204" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X204" s="22" t="inlineStr">
+      <c r="X204" s="20" t="inlineStr">
         <is>
           <t>12 Rue Léon Jouhaux</t>
         </is>
       </c>
-      <c r="Y204" s="23" t="inlineStr">
+      <c r="Y204" s="21" t="inlineStr">
         <is>
           <t>75010</t>
         </is>
       </c>
-      <c r="Z204" s="22" t="inlineStr">
+      <c r="Z204" s="20" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="22" t="inlineStr">
+      <c r="A205" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B205" s="23" t="inlineStr">
+      <c r="B205" s="21" t="inlineStr">
         <is>
           <t>852872480</t>
         </is>
       </c>
-      <c r="C205" s="23" t="inlineStr">
+      <c r="C205" s="21" t="inlineStr">
         <is>
           <t>85287248000011</t>
         </is>
       </c>
-      <c r="D205" s="22" t="inlineStr">
+      <c r="D205" s="20" t="inlineStr">
         <is>
           <t>MONDO PIZZA</t>
         </is>
       </c>
-      <c r="E205" s="22" t="inlineStr">
+      <c r="E205" s="20" t="inlineStr">
         <is>
           <t>MONDO PIZZA</t>
         </is>
       </c>
-      <c r="F205" s="22" t="inlineStr">
+      <c r="F205" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G205" s="22" t="inlineStr">
+      <c r="G205" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H205" s="22" t="inlineStr">
+      <c r="H205" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I205" s="22" t="inlineStr">
+      <c r="I205" s="20" t="inlineStr">
         <is>
           <t>01/09/2019</t>
         </is>
       </c>
-      <c r="J205" s="22" t="inlineStr">
+      <c r="J205" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K205" s="22" t="inlineStr">
+      <c r="K205" s="20" t="inlineStr">
         <is>
           <t>20 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="L205" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M205" s="22" t="inlineStr">
+      <c r="L205" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M205" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N205" s="22" t="inlineStr">
+      <c r="N205" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O205" s="22" t="n">
-        <v>20833</v>
-      </c>
-      <c r="P205" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q205" s="22" t="inlineStr"/>
-      <c r="R205" s="23" t="inlineStr"/>
-      <c r="S205" s="22" t="inlineStr"/>
-      <c r="T205" s="22" t="inlineStr">
+      <c r="O205" s="20" t="inlineStr">
+        <is>
+          <t>20833</t>
+        </is>
+      </c>
+      <c r="P205" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q205" s="20" t="inlineStr"/>
+      <c r="R205" s="21" t="inlineStr"/>
+      <c r="S205" s="20" t="inlineStr"/>
+      <c r="T205" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U205" s="22" t="inlineStr">
+      <c r="U205" s="20" t="inlineStr">
         <is>
           <t>CHOUIKHA</t>
         </is>
       </c>
-      <c r="V205" s="22" t="inlineStr">
+      <c r="V205" s="20" t="inlineStr">
         <is>
           <t>Mohamed, Ali</t>
         </is>
       </c>
-      <c r="W205" s="22" t="inlineStr">
+      <c r="W205" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X205" s="22" t="inlineStr">
+      <c r="X205" s="20" t="inlineStr">
         <is>
           <t>1 Rue Général de Gaulle</t>
         </is>
       </c>
-      <c r="Y205" s="23" t="inlineStr">
+      <c r="Y205" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z205" s="22" t="inlineStr">
+      <c r="Z205" s="20" t="inlineStr">
         <is>
           <t>Longeville-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="22" t="inlineStr">
+      <c r="A206" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B206" s="23" t="inlineStr">
+      <c r="B206" s="21" t="inlineStr">
         <is>
           <t>912274776</t>
         </is>
       </c>
-      <c r="C206" s="23" t="inlineStr">
+      <c r="C206" s="21" t="inlineStr">
         <is>
           <t>91227477600018</t>
         </is>
       </c>
-      <c r="D206" s="22" t="inlineStr">
+      <c r="D206" s="20" t="inlineStr">
         <is>
           <t>ANGKOR WAT BUBBLE TEA</t>
         </is>
       </c>
-      <c r="E206" s="22" t="inlineStr">
+      <c r="E206" s="20" t="inlineStr">
         <is>
           <t>ANGKOR WAT BUBBLE TEA</t>
         </is>
       </c>
-      <c r="F206" s="22" t="inlineStr">
+      <c r="F206" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G206" s="22" t="inlineStr">
+      <c r="G206" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H206" s="22" t="inlineStr">
+      <c r="H206" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I206" s="22" t="inlineStr">
+      <c r="I206" s="20" t="inlineStr">
         <is>
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="J206" s="22" t="inlineStr">
+      <c r="J206" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K206" s="22" t="inlineStr">
+      <c r="K206" s="20" t="inlineStr">
         <is>
           <t>12 RUE GOUSSAUD</t>
         </is>
       </c>
-      <c r="L206" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M206" s="22" t="inlineStr">
+      <c r="L206" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M206" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N206" s="22" t="inlineStr">
+      <c r="N206" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O206" s="22" t="inlineStr"/>
-      <c r="P206" s="22" t="inlineStr"/>
-      <c r="Q206" s="22" t="inlineStr"/>
-      <c r="R206" s="23" t="inlineStr"/>
-      <c r="S206" s="22" t="inlineStr"/>
-      <c r="T206" s="22" t="inlineStr">
+      <c r="O206" s="20" t="inlineStr"/>
+      <c r="P206" s="20" t="inlineStr"/>
+      <c r="Q206" s="20" t="inlineStr"/>
+      <c r="R206" s="21" t="inlineStr"/>
+      <c r="S206" s="20" t="inlineStr"/>
+      <c r="T206" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U206" s="22" t="inlineStr">
+      <c r="U206" s="20" t="inlineStr">
         <is>
           <t>CHHIN</t>
         </is>
       </c>
-      <c r="V206" s="22" t="inlineStr">
+      <c r="V206" s="20" t="inlineStr">
         <is>
           <t>Sinoch</t>
         </is>
       </c>
-      <c r="W206" s="22" t="inlineStr">
+      <c r="W206" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X206" s="22" t="inlineStr">
+      <c r="X206" s="20" t="inlineStr">
         <is>
           <t>11 rue saint vincent</t>
         </is>
       </c>
-      <c r="Y206" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z206" s="22" t="inlineStr">
+      <c r="Y206" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z206" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="22" t="inlineStr">
+      <c r="A207" s="20" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B207" s="23" t="inlineStr">
+      <c r="B207" s="21" t="inlineStr">
         <is>
           <t>839969888</t>
         </is>
       </c>
-      <c r="C207" s="23" t="inlineStr">
+      <c r="C207" s="21" t="inlineStr">
         <is>
           <t>83996988800016</t>
         </is>
       </c>
-      <c r="D207" s="22" t="inlineStr">
+      <c r="D207" s="20" t="inlineStr">
         <is>
           <t>SAS  SRA</t>
         </is>
       </c>
-      <c r="E207" s="22" t="inlineStr">
+      <c r="E207" s="20" t="inlineStr">
         <is>
           <t>SAS  SRA</t>
         </is>
       </c>
-      <c r="F207" s="22" t="inlineStr">
+      <c r="F207" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G207" s="22" t="inlineStr">
+      <c r="G207" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H207" s="22" t="inlineStr">
+      <c r="H207" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I207" s="22" t="inlineStr">
+      <c r="I207" s="20" t="inlineStr">
         <is>
           <t>29/05/2018</t>
         </is>
       </c>
-      <c r="J207" s="22" t="inlineStr">
+      <c r="J207" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K207" s="22" t="inlineStr">
+      <c r="K207" s="20" t="inlineStr">
         <is>
           <t>16 PLACE DES CHARRONS</t>
         </is>
       </c>
-      <c r="L207" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M207" s="22" t="inlineStr">
+      <c r="L207" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M207" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N207" s="22" t="inlineStr">
+      <c r="N207" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O207" s="22" t="n">
-        <v>166565</v>
-      </c>
-      <c r="P207" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q207" s="22" t="inlineStr"/>
-      <c r="R207" s="23" t="inlineStr"/>
-      <c r="S207" s="22" t="inlineStr"/>
-      <c r="T207" s="22" t="inlineStr">
+      <c r="O207" s="20" t="inlineStr">
+        <is>
+          <t>166565</t>
+        </is>
+      </c>
+      <c r="P207" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q207" s="20" t="inlineStr"/>
+      <c r="R207" s="21" t="inlineStr"/>
+      <c r="S207" s="20" t="inlineStr"/>
+      <c r="T207" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U207" s="22" t="inlineStr">
+      <c r="U207" s="20" t="inlineStr">
         <is>
           <t>TAIRACH</t>
         </is>
       </c>
-      <c r="V207" s="22" t="inlineStr">
+      <c r="V207" s="20" t="inlineStr">
         <is>
           <t>Brahim</t>
         </is>
       </c>
-      <c r="W207" s="22" t="inlineStr">
+      <c r="W207" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X207" s="22" t="inlineStr">
+      <c r="X207" s="20" t="inlineStr">
         <is>
           <t>26 rue de la Reole</t>
         </is>
       </c>
-      <c r="Y207" s="23" t="inlineStr">
+      <c r="Y207" s="21" t="inlineStr">
         <is>
           <t>54350</t>
         </is>
       </c>
-      <c r="Z207" s="22" t="inlineStr">
+      <c r="Z207" s="20" t="inlineStr">
         <is>
           <t>Mont-Saint-Martin</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B208" s="23" t="inlineStr">
+        <is>
+          <t>792027021</t>
+        </is>
+      </c>
+      <c r="C208" s="23" t="inlineStr">
+        <is>
+          <t>79202702100023</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="inlineStr">
+        <is>
+          <t>PORTANOVA</t>
+        </is>
+      </c>
+      <c r="E208" s="22" t="inlineStr">
+        <is>
+          <t>PORTANOVA</t>
+        </is>
+      </c>
+      <c r="F208" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G208" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H208" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I208" s="22" t="inlineStr">
+        <is>
+          <t>01/03/2013</t>
+        </is>
+      </c>
+      <c r="J208" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K208" s="22" t="inlineStr">
+        <is>
+          <t>6 RUE HARELLE</t>
+        </is>
+      </c>
+      <c r="L208" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M208" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N208" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O208" s="22" t="n">
+        <v>51761</v>
+      </c>
+      <c r="P208" s="22" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q208" s="22" t="inlineStr"/>
+      <c r="R208" s="23" t="inlineStr"/>
+      <c r="S208" s="22" t="inlineStr"/>
+      <c r="T208" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U208" s="22" t="inlineStr">
+        <is>
+          <t>KHENISSI</t>
+        </is>
+      </c>
+      <c r="V208" s="22" t="inlineStr">
+        <is>
+          <t>Mourad</t>
+        </is>
+      </c>
+      <c r="W208" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X208" s="22" t="inlineStr">
+        <is>
+          <t>35 rue Henri Billotte</t>
+        </is>
+      </c>
+      <c r="Y208" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z208" s="22" t="inlineStr">
+        <is>
+          <t>Saint-Julien-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B209" s="23" t="inlineStr">
+        <is>
+          <t>100105311</t>
+        </is>
+      </c>
+      <c r="C209" s="23" t="inlineStr">
+        <is>
+          <t>10010531100011</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="inlineStr">
+        <is>
+          <t>CROQ'MINUTE</t>
+        </is>
+      </c>
+      <c r="E209" s="22" t="inlineStr">
+        <is>
+          <t>CROQ'MINUTE</t>
+        </is>
+      </c>
+      <c r="F209" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G209" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H209" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I209" s="22" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="J209" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K209" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE HOLANDRE PIQUEMAL</t>
+        </is>
+      </c>
+      <c r="L209" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M209" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N209" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O209" s="22" t="inlineStr"/>
+      <c r="P209" s="22" t="inlineStr"/>
+      <c r="Q209" s="22" t="inlineStr"/>
+      <c r="R209" s="23" t="inlineStr"/>
+      <c r="S209" s="22" t="inlineStr"/>
+      <c r="T209" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U209" s="22" t="inlineStr">
+        <is>
+          <t>UGHI</t>
+        </is>
+      </c>
+      <c r="V209" s="22" t="inlineStr">
+        <is>
+          <t>Gabrielle, Jean-baptiste</t>
+        </is>
+      </c>
+      <c r="W209" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X209" s="22" t="inlineStr">
+        <is>
+          <t>4 rue Germaine Tillion</t>
+        </is>
+      </c>
+      <c r="Y209" s="23" t="inlineStr">
+        <is>
+          <t>57190</t>
+        </is>
+      </c>
+      <c r="Z209" s="22" t="inlineStr">
+        <is>
+          <t>Florange</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B210" s="23" t="inlineStr">
+        <is>
+          <t>324484518</t>
+        </is>
+      </c>
+      <c r="C210" s="23" t="inlineStr">
+        <is>
+          <t>32448451800018</t>
+        </is>
+      </c>
+      <c r="D210" s="22" t="inlineStr">
+        <is>
+          <t>ROSSI Anne-Marie</t>
+        </is>
+      </c>
+      <c r="E210" s="22" t="inlineStr">
+        <is>
+          <t>ROSSI Anne-Marie</t>
+        </is>
+      </c>
+      <c r="F210" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G210" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H210" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I210" s="22" t="inlineStr">
+        <is>
+          <t>01/04/1982</t>
+        </is>
+      </c>
+      <c r="J210" s="22" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="K210" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE PASTEUR</t>
+        </is>
+      </c>
+      <c r="L210" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M210" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N210" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O210" s="22" t="inlineStr"/>
+      <c r="P210" s="22" t="inlineStr"/>
+      <c r="Q210" s="22" t="inlineStr"/>
+      <c r="R210" s="23" t="inlineStr"/>
+      <c r="S210" s="22" t="inlineStr"/>
+      <c r="T210" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U210" s="22" t="inlineStr">
+        <is>
+          <t>FILONI</t>
+        </is>
+      </c>
+      <c r="V210" s="22" t="inlineStr">
+        <is>
+          <t>Anne, Marie</t>
+        </is>
+      </c>
+      <c r="W210" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X210" s="22" t="inlineStr"/>
+      <c r="Y210" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z210" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B211" s="23" t="inlineStr">
+        <is>
+          <t>529111346</t>
+        </is>
+      </c>
+      <c r="C211" s="23" t="inlineStr">
+        <is>
+          <t>52911134600027</t>
+        </is>
+      </c>
+      <c r="D211" s="22" t="inlineStr">
+        <is>
+          <t>THEATRIS BAR</t>
+        </is>
+      </c>
+      <c r="E211" s="22" t="inlineStr">
+        <is>
+          <t>THEATRIS BAR</t>
+        </is>
+      </c>
+      <c r="F211" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G211" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H211" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I211" s="22" t="inlineStr">
+        <is>
+          <t>01/11/2010</t>
+        </is>
+      </c>
+      <c r="J211" s="22" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K211" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DE LA PISCINE</t>
+        </is>
+      </c>
+      <c r="L211" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M211" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N211" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O211" s="22" t="inlineStr"/>
+      <c r="P211" s="22" t="inlineStr"/>
+      <c r="Q211" s="22" t="inlineStr"/>
+      <c r="R211" s="23" t="inlineStr"/>
+      <c r="S211" s="22" t="inlineStr"/>
+      <c r="T211" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U211" s="22" t="inlineStr">
+        <is>
+          <t>ARBIA</t>
+        </is>
+      </c>
+      <c r="V211" s="22" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="W211" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X211" s="22" t="inlineStr">
+        <is>
+          <t>128 avenue André Malraux</t>
+        </is>
+      </c>
+      <c r="Y211" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z211" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B212" s="23" t="inlineStr">
+        <is>
+          <t>477586556</t>
+        </is>
+      </c>
+      <c r="C212" s="23" t="inlineStr">
+        <is>
+          <t>47758655600011</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="inlineStr">
+        <is>
+          <t>QUICK BAR (SOCIETE EN LIQUIDATON)</t>
+        </is>
+      </c>
+      <c r="E212" s="22" t="inlineStr">
+        <is>
+          <t>QUICK BAR (SOCIETE EN LIQUIDATON)</t>
+        </is>
+      </c>
+      <c r="F212" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G212" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H212" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I212" s="22" t="inlineStr">
+        <is>
+          <t>14/05/2004</t>
+        </is>
+      </c>
+      <c r="J212" s="22" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="K212" s="22" t="inlineStr">
+        <is>
+          <t>31 PLACE DU QUARTEAU</t>
+        </is>
+      </c>
+      <c r="L212" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M212" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N212" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O212" s="22" t="inlineStr"/>
+      <c r="P212" s="22" t="inlineStr"/>
+      <c r="Q212" s="22" t="inlineStr"/>
+      <c r="R212" s="23" t="inlineStr"/>
+      <c r="S212" s="22" t="inlineStr"/>
+      <c r="T212" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U212" s="22" t="inlineStr">
+        <is>
+          <t>GREINER</t>
+        </is>
+      </c>
+      <c r="V212" s="22" t="inlineStr">
+        <is>
+          <t>Georges</t>
+        </is>
+      </c>
+      <c r="W212" s="22" t="inlineStr">
+        <is>
+          <t>Liquidateur</t>
+        </is>
+      </c>
+      <c r="X212" s="22" t="inlineStr">
+        <is>
+          <t>11 GRIMONAUX</t>
+        </is>
+      </c>
+      <c r="Y212" s="23" t="inlineStr">
+        <is>
+          <t>57255</t>
+        </is>
+      </c>
+      <c r="Z212" s="22" t="inlineStr">
+        <is>
+          <t>STE MARIE AUX CHENES</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B213" s="23" t="inlineStr">
+        <is>
+          <t>831403951</t>
+        </is>
+      </c>
+      <c r="C213" s="23" t="inlineStr">
+        <is>
+          <t>83140395100021</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="inlineStr">
+        <is>
+          <t>LE BLEU</t>
+        </is>
+      </c>
+      <c r="E213" s="22" t="inlineStr">
+        <is>
+          <t>LE BLEU</t>
+        </is>
+      </c>
+      <c r="F213" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G213" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H213" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I213" s="22" t="inlineStr">
+        <is>
+          <t>09/08/2017</t>
+        </is>
+      </c>
+      <c r="J213" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K213" s="22" t="inlineStr">
+        <is>
+          <t>6 RUE WINSTON CHURCHILL</t>
+        </is>
+      </c>
+      <c r="L213" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M213" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N213" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O213" s="22" t="inlineStr"/>
+      <c r="P213" s="22" t="inlineStr"/>
+      <c r="Q213" s="22" t="inlineStr"/>
+      <c r="R213" s="23" t="inlineStr"/>
+      <c r="S213" s="22" t="inlineStr"/>
+      <c r="T213" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U213" s="22" t="inlineStr">
+        <is>
+          <t>WALLERICH</t>
+        </is>
+      </c>
+      <c r="V213" s="22" t="inlineStr">
+        <is>
+          <t>Michel, Ernest</t>
+        </is>
+      </c>
+      <c r="W213" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X213" s="22" t="inlineStr">
+        <is>
+          <t>40 rue Saint-Gengoulf</t>
+        </is>
+      </c>
+      <c r="Y213" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z213" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B214" s="23" t="inlineStr">
+        <is>
+          <t>824141410</t>
+        </is>
+      </c>
+      <c r="C214" s="23" t="inlineStr">
+        <is>
+          <t>82414141000012</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="inlineStr">
+        <is>
+          <t>NEWCO</t>
+        </is>
+      </c>
+      <c r="E214" s="22" t="inlineStr">
+        <is>
+          <t>NEWCO</t>
+        </is>
+      </c>
+      <c r="F214" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G214" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H214" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I214" s="22" t="inlineStr">
+        <is>
+          <t>06/12/2016</t>
+        </is>
+      </c>
+      <c r="J214" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K214" s="22" t="inlineStr">
+        <is>
+          <t>8 RUE DE LADOUCETTE</t>
+        </is>
+      </c>
+      <c r="L214" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M214" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N214" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O214" s="22" t="inlineStr"/>
+      <c r="P214" s="22" t="inlineStr"/>
+      <c r="Q214" s="22" t="inlineStr"/>
+      <c r="R214" s="23" t="inlineStr"/>
+      <c r="S214" s="22" t="inlineStr"/>
+      <c r="T214" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U214" s="22" t="inlineStr">
+        <is>
+          <t>PRZYBYLSKI</t>
+        </is>
+      </c>
+      <c r="V214" s="22" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="W214" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X214" s="22" t="inlineStr">
+        <is>
+          <t>13 rue Georges de la Tour</t>
+        </is>
+      </c>
+      <c r="Y214" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z214" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B215" s="23" t="inlineStr">
+        <is>
+          <t>401623301</t>
+        </is>
+      </c>
+      <c r="C215" s="23" t="inlineStr">
+        <is>
+          <t>40162330100025</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="inlineStr">
+        <is>
+          <t>ASS LES AMIS DE SAINT LOUIS</t>
+        </is>
+      </c>
+      <c r="E215" s="22" t="inlineStr">
+        <is>
+          <t>ASS LES AMIS DE SAINT LOUIS</t>
+        </is>
+      </c>
+      <c r="F215" s="22" t="inlineStr">
+        <is>
+          <t>Association de droit local (Bas-Rhin, Haut-Rhin et Moselle)</t>
+        </is>
+      </c>
+      <c r="G215" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H215" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I215" s="22" t="inlineStr">
+        <is>
+          <t>31/03/1995</t>
+        </is>
+      </c>
+      <c r="J215" s="22" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="K215" s="22" t="inlineStr">
+        <is>
+          <t>4 AV JEAN 23</t>
+        </is>
+      </c>
+      <c r="L215" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M215" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N215" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O215" s="22" t="inlineStr"/>
+      <c r="P215" s="22" t="inlineStr"/>
+      <c r="Q215" s="22" t="inlineStr"/>
+      <c r="R215" s="23" t="inlineStr"/>
+      <c r="S215" s="22" t="inlineStr"/>
+      <c r="T215" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U215" s="22" t="inlineStr"/>
+      <c r="V215" s="22" t="inlineStr"/>
+      <c r="W215" s="22" t="inlineStr"/>
+      <c r="X215" s="22" t="inlineStr"/>
+      <c r="Y215" s="23" t="inlineStr"/>
+      <c r="Z215" s="22" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B216" s="23" t="inlineStr">
+        <is>
+          <t>928015064</t>
+        </is>
+      </c>
+      <c r="C216" s="23" t="inlineStr">
+        <is>
+          <t>92801506400019</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>BRUDEAU</t>
+        </is>
+      </c>
+      <c r="E216" s="22" t="inlineStr">
+        <is>
+          <t>BRUDEAU</t>
+        </is>
+      </c>
+      <c r="F216" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G216" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H216" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I216" s="22" t="inlineStr">
+        <is>
+          <t>29/04/2024</t>
+        </is>
+      </c>
+      <c r="J216" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K216" s="22" t="inlineStr">
+        <is>
+          <t>15 RUE MARCHANT</t>
+        </is>
+      </c>
+      <c r="L216" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M216" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N216" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O216" s="22" t="inlineStr"/>
+      <c r="P216" s="22" t="inlineStr"/>
+      <c r="Q216" s="22" t="inlineStr"/>
+      <c r="R216" s="23" t="inlineStr"/>
+      <c r="S216" s="22" t="inlineStr"/>
+      <c r="T216" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U216" s="22" t="inlineStr">
+        <is>
+          <t>Brutto</t>
+        </is>
+      </c>
+      <c r="V216" s="22" t="inlineStr">
+        <is>
+          <t>Philippe</t>
+        </is>
+      </c>
+      <c r="W216" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X216" s="22" t="inlineStr"/>
+      <c r="Y216" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z216" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B217" s="23" t="inlineStr">
+        <is>
+          <t>507864940</t>
+        </is>
+      </c>
+      <c r="C217" s="23" t="inlineStr">
+        <is>
+          <t>50786494000014</t>
+        </is>
+      </c>
+      <c r="D217" s="22" t="inlineStr">
+        <is>
+          <t>SARL CHANDARA</t>
+        </is>
+      </c>
+      <c r="E217" s="22" t="inlineStr">
+        <is>
+          <t>SARL CHANDARA</t>
+        </is>
+      </c>
+      <c r="F217" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G217" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H217" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I217" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2008</t>
+        </is>
+      </c>
+      <c r="J217" s="22" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K217" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DU PONT DES ROCHES</t>
+        </is>
+      </c>
+      <c r="L217" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M217" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N217" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O217" s="22" t="n">
+        <v>252174</v>
+      </c>
+      <c r="P217" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Q217" s="22" t="inlineStr"/>
+      <c r="R217" s="23" t="inlineStr"/>
+      <c r="S217" s="22" t="inlineStr"/>
+      <c r="T217" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U217" s="22" t="inlineStr">
+        <is>
+          <t>CHAN DARA</t>
+        </is>
+      </c>
+      <c r="V217" s="22" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="W217" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X217" s="22" t="inlineStr">
+        <is>
+          <t>9 rue Robert Schuman</t>
+        </is>
+      </c>
+      <c r="Y217" s="23" t="inlineStr">
+        <is>
+          <t>57580</t>
+        </is>
+      </c>
+      <c r="Z217" s="22" t="inlineStr">
+        <is>
+          <t>Rémilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B218" s="23" t="inlineStr">
+        <is>
+          <t>525353934</t>
+        </is>
+      </c>
+      <c r="C218" s="23" t="inlineStr">
+        <is>
+          <t>52535393400017</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="inlineStr">
+        <is>
+          <t>KYOU</t>
+        </is>
+      </c>
+      <c r="E218" s="22" t="inlineStr">
+        <is>
+          <t>KYOU</t>
+        </is>
+      </c>
+      <c r="F218" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G218" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H218" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I218" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2010</t>
+        </is>
+      </c>
+      <c r="J218" s="22" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K218" s="22" t="inlineStr">
+        <is>
+          <t>6 RUE DU MOYEN PONT</t>
+        </is>
+      </c>
+      <c r="L218" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M218" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N218" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O218" s="22" t="inlineStr"/>
+      <c r="P218" s="22" t="inlineStr"/>
+      <c r="Q218" s="22" t="inlineStr"/>
+      <c r="R218" s="23" t="inlineStr"/>
+      <c r="S218" s="22" t="inlineStr"/>
+      <c r="T218" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U218" s="22" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="V218" s="22" t="inlineStr">
+        <is>
+          <t>Xiaoyan</t>
+        </is>
+      </c>
+      <c r="W218" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X218" s="22" t="inlineStr">
+        <is>
+          <t>15 rue de la Chapelle</t>
+        </is>
+      </c>
+      <c r="Y218" s="23" t="inlineStr">
+        <is>
+          <t>75018</t>
+        </is>
+      </c>
+      <c r="Z218" s="22" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B219" s="23" t="inlineStr">
+        <is>
+          <t>802425421</t>
+        </is>
+      </c>
+      <c r="C219" s="23" t="inlineStr">
+        <is>
+          <t>80242542100012</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="inlineStr">
+        <is>
+          <t>LA GRILLADE METZ</t>
+        </is>
+      </c>
+      <c r="E219" s="22" t="inlineStr">
+        <is>
+          <t>LA GRILLADE METZ</t>
+        </is>
+      </c>
+      <c r="F219" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G219" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H219" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I219" s="22" t="inlineStr">
+        <is>
+          <t>21/05/2014</t>
+        </is>
+      </c>
+      <c r="J219" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K219" s="22" t="inlineStr">
+        <is>
+          <t>24 PLACE SAINT-SIMPLICE</t>
+        </is>
+      </c>
+      <c r="L219" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M219" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N219" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O219" s="22" t="n">
+        <v>110764</v>
+      </c>
+      <c r="P219" s="22" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q219" s="22" t="inlineStr"/>
+      <c r="R219" s="23" t="inlineStr"/>
+      <c r="S219" s="22" t="inlineStr"/>
+      <c r="T219" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U219" s="22" t="inlineStr">
+        <is>
+          <t>BOUTEMEUR</t>
+        </is>
+      </c>
+      <c r="V219" s="22" t="inlineStr">
+        <is>
+          <t>Michaël, Norbert, Antar</t>
+        </is>
+      </c>
+      <c r="W219" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X219" s="22" t="inlineStr">
+        <is>
+          <t>10 rue du Maréchal Juin</t>
+        </is>
+      </c>
+      <c r="Y219" s="23" t="inlineStr">
+        <is>
+          <t>57950</t>
+        </is>
+      </c>
+      <c r="Z219" s="22" t="inlineStr">
+        <is>
+          <t>Montigny-les-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B220" s="23" t="inlineStr">
+        <is>
+          <t>828871509</t>
+        </is>
+      </c>
+      <c r="C220" s="23" t="inlineStr">
+        <is>
+          <t>82887150900018</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="inlineStr">
+        <is>
+          <t>SARL M.C</t>
+        </is>
+      </c>
+      <c r="E220" s="22" t="inlineStr">
+        <is>
+          <t>SARL M.C</t>
+        </is>
+      </c>
+      <c r="F220" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G220" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H220" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I220" s="22" t="inlineStr">
+        <is>
+          <t>09/03/2017</t>
+        </is>
+      </c>
+      <c r="J220" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K220" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L220" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M220" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N220" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O220" s="22" t="inlineStr"/>
+      <c r="P220" s="22" t="inlineStr"/>
+      <c r="Q220" s="22" t="inlineStr"/>
+      <c r="R220" s="23" t="inlineStr"/>
+      <c r="S220" s="22" t="inlineStr"/>
+      <c r="T220" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U220" s="22" t="inlineStr">
+        <is>
+          <t>MENIRI</t>
+        </is>
+      </c>
+      <c r="V220" s="22" t="inlineStr">
+        <is>
+          <t>Mehdi</t>
+        </is>
+      </c>
+      <c r="W220" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X220" s="22" t="inlineStr">
+        <is>
+          <t>34 rue du Chazeau</t>
+        </is>
+      </c>
+      <c r="Y220" s="23" t="inlineStr">
+        <is>
+          <t>54220</t>
+        </is>
+      </c>
+      <c r="Z220" s="22" t="inlineStr">
+        <is>
+          <t>Malzéville</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B221" s="23" t="inlineStr">
+        <is>
+          <t>107909459</t>
+        </is>
+      </c>
+      <c r="C221" s="23" t="inlineStr">
+        <is>
+          <t>10790945900011</t>
+        </is>
+      </c>
+      <c r="D221" s="22" t="inlineStr">
+        <is>
+          <t>NOTRE CUISINE</t>
+        </is>
+      </c>
+      <c r="E221" s="22" t="inlineStr">
+        <is>
+          <t>NOTRE CUISINE</t>
+        </is>
+      </c>
+      <c r="F221" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G221" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H221" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I221" s="22" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J221" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K221" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE COISLIN</t>
+        </is>
+      </c>
+      <c r="L221" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M221" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N221" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O221" s="22" t="inlineStr"/>
+      <c r="P221" s="22" t="inlineStr"/>
+      <c r="Q221" s="22" t="inlineStr"/>
+      <c r="R221" s="23" t="inlineStr"/>
+      <c r="S221" s="22" t="inlineStr"/>
+      <c r="T221" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U221" s="22" t="inlineStr">
+        <is>
+          <t>HOSSAIN</t>
+        </is>
+      </c>
+      <c r="V221" s="22" t="inlineStr">
+        <is>
+          <t>Masud</t>
+        </is>
+      </c>
+      <c r="W221" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X221" s="22" t="inlineStr"/>
+      <c r="Y221" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z221" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B222" s="23" t="inlineStr">
+        <is>
+          <t>108962721</t>
+        </is>
+      </c>
+      <c r="C222" s="23" t="inlineStr">
+        <is>
+          <t>10896272100016</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="inlineStr">
+        <is>
+          <t>LE CORNER 57</t>
+        </is>
+      </c>
+      <c r="E222" s="22" t="inlineStr">
+        <is>
+          <t>LE CORNER 57</t>
+        </is>
+      </c>
+      <c r="F222" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G222" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H222" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I222" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="J222" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K222" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE COISLIN</t>
+        </is>
+      </c>
+      <c r="L222" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M222" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N222" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O222" s="22" t="inlineStr"/>
+      <c r="P222" s="22" t="inlineStr"/>
+      <c r="Q222" s="22" t="inlineStr"/>
+      <c r="R222" s="23" t="inlineStr"/>
+      <c r="S222" s="22" t="inlineStr"/>
+      <c r="T222" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U222" s="22" t="inlineStr">
+        <is>
+          <t>JAKARIYA</t>
+        </is>
+      </c>
+      <c r="V222" s="22" t="inlineStr">
+        <is>
+          <t>Mohammad</t>
+        </is>
+      </c>
+      <c r="W222" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X222" s="22" t="inlineStr"/>
+      <c r="Y222" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z222" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B223" s="23" t="inlineStr">
+        <is>
+          <t>537967713</t>
+        </is>
+      </c>
+      <c r="C223" s="23" t="inlineStr">
+        <is>
+          <t>53796771300026</t>
+        </is>
+      </c>
+      <c r="D223" s="22" t="inlineStr">
+        <is>
+          <t>DIDAU</t>
+        </is>
+      </c>
+      <c r="E223" s="22" t="inlineStr">
+        <is>
+          <t>DIDAU</t>
+        </is>
+      </c>
+      <c r="F223" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G223" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H223" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I223" s="22" t="inlineStr">
+        <is>
+          <t>17/11/2011</t>
+        </is>
+      </c>
+      <c r="J223" s="22" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="K223" s="22" t="inlineStr">
+        <is>
+          <t>5 PLACE JEAN SPINGA</t>
+        </is>
+      </c>
+      <c r="L223" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M223" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N223" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O223" s="22" t="inlineStr"/>
+      <c r="P223" s="22" t="inlineStr"/>
+      <c r="Q223" s="22" t="inlineStr"/>
+      <c r="R223" s="23" t="inlineStr"/>
+      <c r="S223" s="22" t="inlineStr"/>
+      <c r="T223" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U223" s="22" t="inlineStr">
+        <is>
+          <t>DI CANDIA</t>
+        </is>
+      </c>
+      <c r="V223" s="22" t="inlineStr">
+        <is>
+          <t>Pascal</t>
+        </is>
+      </c>
+      <c r="W223" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X223" s="22" t="inlineStr">
+        <is>
+          <t>22/24 rue du Wad Billy</t>
+        </is>
+      </c>
+      <c r="Y223" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z223" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B224" s="23" t="inlineStr">
+        <is>
+          <t>438601411</t>
+        </is>
+      </c>
+      <c r="C224" s="23" t="inlineStr">
+        <is>
+          <t>43860141100020</t>
+        </is>
+      </c>
+      <c r="D224" s="22" t="inlineStr">
+        <is>
+          <t>LAHYDINA</t>
+        </is>
+      </c>
+      <c r="E224" s="22" t="inlineStr">
+        <is>
+          <t>LAHYDINA</t>
+        </is>
+      </c>
+      <c r="F224" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G224" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H224" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I224" s="22" t="inlineStr">
+        <is>
+          <t>11/07/2001</t>
+        </is>
+      </c>
+      <c r="J224" s="22" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="K224" s="22" t="inlineStr">
+        <is>
+          <t>70 RUE DU XXEME CORPS AMERICAIN</t>
+        </is>
+      </c>
+      <c r="L224" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M224" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N224" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O224" s="22" t="n">
+        <v>88857</v>
+      </c>
+      <c r="P224" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Q224" s="22" t="inlineStr"/>
+      <c r="R224" s="23" t="inlineStr"/>
+      <c r="S224" s="22" t="inlineStr"/>
+      <c r="T224" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U224" s="22" t="inlineStr">
+        <is>
+          <t>BOUYAKHRICHAN</t>
+        </is>
+      </c>
+      <c r="V224" s="22" t="inlineStr">
+        <is>
+          <t>Saïd</t>
+        </is>
+      </c>
+      <c r="W224" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X224" s="22" t="inlineStr">
+        <is>
+          <t>33 rue du Général Metman</t>
+        </is>
+      </c>
+      <c r="Y224" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z224" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B225" s="23" t="inlineStr">
+        <is>
+          <t>341853075</t>
+        </is>
+      </c>
+      <c r="C225" s="23" t="inlineStr">
+        <is>
+          <t>34185307500016</t>
+        </is>
+      </c>
+      <c r="D225" s="22" t="inlineStr">
+        <is>
+          <t>HEWAL</t>
+        </is>
+      </c>
+      <c r="E225" s="22" t="inlineStr">
+        <is>
+          <t>HEWAL</t>
+        </is>
+      </c>
+      <c r="F225" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G225" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H225" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I225" s="22" t="inlineStr">
+        <is>
+          <t>01/08/1987</t>
+        </is>
+      </c>
+      <c r="J225" s="22" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="K225" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L225" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M225" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N225" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O225" s="22" t="inlineStr"/>
+      <c r="P225" s="22" t="inlineStr"/>
+      <c r="Q225" s="22" t="inlineStr"/>
+      <c r="R225" s="23" t="inlineStr"/>
+      <c r="S225" s="22" t="inlineStr"/>
+      <c r="T225" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U225" s="22" t="inlineStr">
+        <is>
+          <t>ARSLAN</t>
+        </is>
+      </c>
+      <c r="V225" s="22" t="inlineStr">
+        <is>
+          <t>Mehmet</t>
+        </is>
+      </c>
+      <c r="W225" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X225" s="22" t="inlineStr">
+        <is>
+          <t>1-157 rue du Barrois</t>
+        </is>
+      </c>
+      <c r="Y225" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z225" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B226" s="23" t="inlineStr">
+        <is>
+          <t>853893436</t>
+        </is>
+      </c>
+      <c r="C226" s="23" t="inlineStr">
+        <is>
+          <t>85389343600024</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="inlineStr">
+        <is>
+          <t>CAMARA HAWA</t>
+        </is>
+      </c>
+      <c r="E226" s="22" t="inlineStr">
+        <is>
+          <t>CAMARA HAWA</t>
+        </is>
+      </c>
+      <c r="F226" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G226" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H226" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I226" s="22" t="inlineStr">
+        <is>
+          <t>13/09/2019</t>
+        </is>
+      </c>
+      <c r="J226" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K226" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE SIMONE VEIL</t>
+        </is>
+      </c>
+      <c r="L226" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M226" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N226" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O226" s="22" t="inlineStr"/>
+      <c r="P226" s="22" t="inlineStr"/>
+      <c r="Q226" s="22" t="inlineStr"/>
+      <c r="R226" s="23" t="inlineStr"/>
+      <c r="S226" s="22" t="inlineStr"/>
+      <c r="T226" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U226" s="22" t="inlineStr">
+        <is>
+          <t>CAMARA</t>
+        </is>
+      </c>
+      <c r="V226" s="22" t="inlineStr">
+        <is>
+          <t>Hawa, Amy</t>
+        </is>
+      </c>
+      <c r="W226" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X226" s="22" t="inlineStr"/>
+      <c r="Y226" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z226" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B227" s="23" t="inlineStr">
+        <is>
+          <t>848518296</t>
+        </is>
+      </c>
+      <c r="C227" s="23" t="inlineStr">
+        <is>
+          <t>84851829600019</t>
+        </is>
+      </c>
+      <c r="D227" s="22" t="inlineStr">
+        <is>
+          <t>CAFE D'LA GARE</t>
+        </is>
+      </c>
+      <c r="E227" s="22" t="inlineStr">
+        <is>
+          <t>CAFE D'LA GARE</t>
+        </is>
+      </c>
+      <c r="F227" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G227" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H227" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I227" s="22" t="inlineStr">
+        <is>
+          <t>21/02/2019</t>
+        </is>
+      </c>
+      <c r="J227" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K227" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L227" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M227" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N227" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O227" s="22" t="inlineStr"/>
+      <c r="P227" s="22" t="inlineStr"/>
+      <c r="Q227" s="22" t="inlineStr"/>
+      <c r="R227" s="23" t="inlineStr"/>
+      <c r="S227" s="22" t="inlineStr"/>
+      <c r="T227" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U227" s="22" t="inlineStr">
+        <is>
+          <t>KAYA</t>
+        </is>
+      </c>
+      <c r="V227" s="22" t="inlineStr">
+        <is>
+          <t>Kadir</t>
+        </is>
+      </c>
+      <c r="W227" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X227" s="22" t="inlineStr">
+        <is>
+          <t>9 rue des Pins</t>
+        </is>
+      </c>
+      <c r="Y227" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z227" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z207"/>
+  <autoFilter ref="A2:Z227"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z227"/>
+  <dimension ref="A1:Z247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23710,2219 +23710,4481 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="22" t="inlineStr">
+      <c r="A208" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B208" s="23" t="inlineStr">
+      <c r="B208" s="21" t="inlineStr">
         <is>
           <t>792027021</t>
         </is>
       </c>
-      <c r="C208" s="23" t="inlineStr">
+      <c r="C208" s="21" t="inlineStr">
         <is>
           <t>79202702100023</t>
         </is>
       </c>
-      <c r="D208" s="22" t="inlineStr">
+      <c r="D208" s="20" t="inlineStr">
         <is>
           <t>PORTANOVA</t>
         </is>
       </c>
-      <c r="E208" s="22" t="inlineStr">
+      <c r="E208" s="20" t="inlineStr">
         <is>
           <t>PORTANOVA</t>
         </is>
       </c>
-      <c r="F208" s="22" t="inlineStr">
+      <c r="F208" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G208" s="22" t="inlineStr">
+      <c r="G208" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H208" s="22" t="inlineStr">
+      <c r="H208" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I208" s="22" t="inlineStr">
+      <c r="I208" s="20" t="inlineStr">
         <is>
           <t>01/03/2013</t>
         </is>
       </c>
-      <c r="J208" s="22" t="inlineStr">
+      <c r="J208" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K208" s="22" t="inlineStr">
+      <c r="K208" s="20" t="inlineStr">
         <is>
           <t>6 RUE HARELLE</t>
         </is>
       </c>
-      <c r="L208" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M208" s="22" t="inlineStr">
+      <c r="L208" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M208" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N208" s="22" t="inlineStr">
+      <c r="N208" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O208" s="22" t="n">
-        <v>51761</v>
-      </c>
-      <c r="P208" s="22" t="n">
-        <v>2015</v>
-      </c>
-      <c r="Q208" s="22" t="inlineStr"/>
-      <c r="R208" s="23" t="inlineStr"/>
-      <c r="S208" s="22" t="inlineStr"/>
-      <c r="T208" s="22" t="inlineStr">
+      <c r="O208" s="20" t="inlineStr">
+        <is>
+          <t>51761</t>
+        </is>
+      </c>
+      <c r="P208" s="20" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q208" s="20" t="inlineStr"/>
+      <c r="R208" s="21" t="inlineStr"/>
+      <c r="S208" s="20" t="inlineStr"/>
+      <c r="T208" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U208" s="22" t="inlineStr">
+      <c r="U208" s="20" t="inlineStr">
         <is>
           <t>KHENISSI</t>
         </is>
       </c>
-      <c r="V208" s="22" t="inlineStr">
+      <c r="V208" s="20" t="inlineStr">
         <is>
           <t>Mourad</t>
         </is>
       </c>
-      <c r="W208" s="22" t="inlineStr">
+      <c r="W208" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X208" s="22" t="inlineStr">
+      <c r="X208" s="20" t="inlineStr">
         <is>
           <t>35 rue Henri Billotte</t>
         </is>
       </c>
-      <c r="Y208" s="23" t="inlineStr">
+      <c r="Y208" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z208" s="22" t="inlineStr">
+      <c r="Z208" s="20" t="inlineStr">
         <is>
           <t>Saint-Julien-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="22" t="inlineStr">
+      <c r="A209" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B209" s="23" t="inlineStr">
+      <c r="B209" s="21" t="inlineStr">
         <is>
           <t>100105311</t>
         </is>
       </c>
-      <c r="C209" s="23" t="inlineStr">
+      <c r="C209" s="21" t="inlineStr">
         <is>
           <t>10010531100011</t>
         </is>
       </c>
-      <c r="D209" s="22" t="inlineStr">
+      <c r="D209" s="20" t="inlineStr">
         <is>
           <t>CROQ'MINUTE</t>
         </is>
       </c>
-      <c r="E209" s="22" t="inlineStr">
+      <c r="E209" s="20" t="inlineStr">
         <is>
           <t>CROQ'MINUTE</t>
         </is>
       </c>
-      <c r="F209" s="22" t="inlineStr">
+      <c r="F209" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G209" s="22" t="inlineStr">
+      <c r="G209" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H209" s="22" t="inlineStr">
+      <c r="H209" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I209" s="22" t="inlineStr">
+      <c r="I209" s="20" t="inlineStr">
         <is>
           <t>17/01/2026</t>
         </is>
       </c>
-      <c r="J209" s="22" t="inlineStr">
+      <c r="J209" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K209" s="22" t="inlineStr">
+      <c r="K209" s="20" t="inlineStr">
         <is>
           <t>4 RUE HOLANDRE PIQUEMAL</t>
         </is>
       </c>
-      <c r="L209" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M209" s="22" t="inlineStr">
+      <c r="L209" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M209" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N209" s="22" t="inlineStr">
+      <c r="N209" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O209" s="22" t="inlineStr"/>
-      <c r="P209" s="22" t="inlineStr"/>
-      <c r="Q209" s="22" t="inlineStr"/>
-      <c r="R209" s="23" t="inlineStr"/>
-      <c r="S209" s="22" t="inlineStr"/>
-      <c r="T209" s="22" t="inlineStr">
+      <c r="O209" s="20" t="inlineStr"/>
+      <c r="P209" s="20" t="inlineStr"/>
+      <c r="Q209" s="20" t="inlineStr"/>
+      <c r="R209" s="21" t="inlineStr"/>
+      <c r="S209" s="20" t="inlineStr"/>
+      <c r="T209" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U209" s="22" t="inlineStr">
+      <c r="U209" s="20" t="inlineStr">
         <is>
           <t>UGHI</t>
         </is>
       </c>
-      <c r="V209" s="22" t="inlineStr">
+      <c r="V209" s="20" t="inlineStr">
         <is>
           <t>Gabrielle, Jean-baptiste</t>
         </is>
       </c>
-      <c r="W209" s="22" t="inlineStr">
+      <c r="W209" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X209" s="22" t="inlineStr">
+      <c r="X209" s="20" t="inlineStr">
         <is>
           <t>4 rue Germaine Tillion</t>
         </is>
       </c>
-      <c r="Y209" s="23" t="inlineStr">
+      <c r="Y209" s="21" t="inlineStr">
         <is>
           <t>57190</t>
         </is>
       </c>
-      <c r="Z209" s="22" t="inlineStr">
+      <c r="Z209" s="20" t="inlineStr">
         <is>
           <t>Florange</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="22" t="inlineStr">
+      <c r="A210" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B210" s="23" t="inlineStr">
+      <c r="B210" s="21" t="inlineStr">
         <is>
           <t>324484518</t>
         </is>
       </c>
-      <c r="C210" s="23" t="inlineStr">
+      <c r="C210" s="21" t="inlineStr">
         <is>
           <t>32448451800018</t>
         </is>
       </c>
-      <c r="D210" s="22" t="inlineStr">
+      <c r="D210" s="20" t="inlineStr">
         <is>
           <t>ROSSI Anne-Marie</t>
         </is>
       </c>
-      <c r="E210" s="22" t="inlineStr">
+      <c r="E210" s="20" t="inlineStr">
         <is>
           <t>ROSSI Anne-Marie</t>
         </is>
       </c>
-      <c r="F210" s="22" t="inlineStr">
+      <c r="F210" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G210" s="22" t="inlineStr">
+      <c r="G210" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H210" s="22" t="inlineStr">
+      <c r="H210" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I210" s="22" t="inlineStr">
+      <c r="I210" s="20" t="inlineStr">
         <is>
           <t>01/04/1982</t>
         </is>
       </c>
-      <c r="J210" s="22" t="inlineStr">
+      <c r="J210" s="20" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="K210" s="22" t="inlineStr">
+      <c r="K210" s="20" t="inlineStr">
         <is>
           <t>10 RUE PASTEUR</t>
         </is>
       </c>
-      <c r="L210" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M210" s="22" t="inlineStr">
+      <c r="L210" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M210" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N210" s="22" t="inlineStr">
+      <c r="N210" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O210" s="22" t="inlineStr"/>
-      <c r="P210" s="22" t="inlineStr"/>
-      <c r="Q210" s="22" t="inlineStr"/>
-      <c r="R210" s="23" t="inlineStr"/>
-      <c r="S210" s="22" t="inlineStr"/>
-      <c r="T210" s="22" t="inlineStr">
+      <c r="O210" s="20" t="inlineStr"/>
+      <c r="P210" s="20" t="inlineStr"/>
+      <c r="Q210" s="20" t="inlineStr"/>
+      <c r="R210" s="21" t="inlineStr"/>
+      <c r="S210" s="20" t="inlineStr"/>
+      <c r="T210" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U210" s="22" t="inlineStr">
+      <c r="U210" s="20" t="inlineStr">
         <is>
           <t>FILONI</t>
         </is>
       </c>
-      <c r="V210" s="22" t="inlineStr">
+      <c r="V210" s="20" t="inlineStr">
         <is>
           <t>Anne, Marie</t>
         </is>
       </c>
-      <c r="W210" s="22" t="inlineStr">
+      <c r="W210" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X210" s="22" t="inlineStr"/>
-      <c r="Y210" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z210" s="22" t="inlineStr">
+      <c r="X210" s="20" t="inlineStr"/>
+      <c r="Y210" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z210" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="22" t="inlineStr">
+      <c r="A211" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B211" s="23" t="inlineStr">
+      <c r="B211" s="21" t="inlineStr">
         <is>
           <t>529111346</t>
         </is>
       </c>
-      <c r="C211" s="23" t="inlineStr">
+      <c r="C211" s="21" t="inlineStr">
         <is>
           <t>52911134600027</t>
         </is>
       </c>
-      <c r="D211" s="22" t="inlineStr">
+      <c r="D211" s="20" t="inlineStr">
         <is>
           <t>THEATRIS BAR</t>
         </is>
       </c>
-      <c r="E211" s="22" t="inlineStr">
+      <c r="E211" s="20" t="inlineStr">
         <is>
           <t>THEATRIS BAR</t>
         </is>
       </c>
-      <c r="F211" s="22" t="inlineStr">
+      <c r="F211" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G211" s="22" t="inlineStr">
+      <c r="G211" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H211" s="22" t="inlineStr">
+      <c r="H211" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I211" s="22" t="inlineStr">
+      <c r="I211" s="20" t="inlineStr">
         <is>
           <t>01/11/2010</t>
         </is>
       </c>
-      <c r="J211" s="22" t="inlineStr">
+      <c r="J211" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K211" s="22" t="inlineStr">
+      <c r="K211" s="20" t="inlineStr">
         <is>
           <t>1 RUE DE LA PISCINE</t>
         </is>
       </c>
-      <c r="L211" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M211" s="22" t="inlineStr">
+      <c r="L211" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M211" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N211" s="22" t="inlineStr">
+      <c r="N211" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O211" s="22" t="inlineStr"/>
-      <c r="P211" s="22" t="inlineStr"/>
-      <c r="Q211" s="22" t="inlineStr"/>
-      <c r="R211" s="23" t="inlineStr"/>
-      <c r="S211" s="22" t="inlineStr"/>
-      <c r="T211" s="22" t="inlineStr">
+      <c r="O211" s="20" t="inlineStr"/>
+      <c r="P211" s="20" t="inlineStr"/>
+      <c r="Q211" s="20" t="inlineStr"/>
+      <c r="R211" s="21" t="inlineStr"/>
+      <c r="S211" s="20" t="inlineStr"/>
+      <c r="T211" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U211" s="22" t="inlineStr">
+      <c r="U211" s="20" t="inlineStr">
         <is>
           <t>ARBIA</t>
         </is>
       </c>
-      <c r="V211" s="22" t="inlineStr">
+      <c r="V211" s="20" t="inlineStr">
         <is>
           <t>Mohamed</t>
         </is>
       </c>
-      <c r="W211" s="22" t="inlineStr">
+      <c r="W211" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X211" s="22" t="inlineStr">
+      <c r="X211" s="20" t="inlineStr">
         <is>
           <t>128 avenue André Malraux</t>
         </is>
       </c>
-      <c r="Y211" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z211" s="22" t="inlineStr">
+      <c r="Y211" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z211" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="22" t="inlineStr">
+      <c r="A212" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B212" s="23" t="inlineStr">
+      <c r="B212" s="21" t="inlineStr">
         <is>
           <t>477586556</t>
         </is>
       </c>
-      <c r="C212" s="23" t="inlineStr">
+      <c r="C212" s="21" t="inlineStr">
         <is>
           <t>47758655600011</t>
         </is>
       </c>
-      <c r="D212" s="22" t="inlineStr">
+      <c r="D212" s="20" t="inlineStr">
         <is>
           <t>QUICK BAR (SOCIETE EN LIQUIDATON)</t>
         </is>
       </c>
-      <c r="E212" s="22" t="inlineStr">
+      <c r="E212" s="20" t="inlineStr">
         <is>
           <t>QUICK BAR (SOCIETE EN LIQUIDATON)</t>
         </is>
       </c>
-      <c r="F212" s="22" t="inlineStr">
+      <c r="F212" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G212" s="22" t="inlineStr">
+      <c r="G212" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H212" s="22" t="inlineStr">
+      <c r="H212" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I212" s="22" t="inlineStr">
+      <c r="I212" s="20" t="inlineStr">
         <is>
           <t>14/05/2004</t>
         </is>
       </c>
-      <c r="J212" s="22" t="inlineStr">
+      <c r="J212" s="20" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="K212" s="22" t="inlineStr">
+      <c r="K212" s="20" t="inlineStr">
         <is>
           <t>31 PLACE DU QUARTEAU</t>
         </is>
       </c>
-      <c r="L212" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M212" s="22" t="inlineStr">
+      <c r="L212" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M212" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N212" s="22" t="inlineStr">
+      <c r="N212" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O212" s="22" t="inlineStr"/>
-      <c r="P212" s="22" t="inlineStr"/>
-      <c r="Q212" s="22" t="inlineStr"/>
-      <c r="R212" s="23" t="inlineStr"/>
-      <c r="S212" s="22" t="inlineStr"/>
-      <c r="T212" s="22" t="inlineStr">
+      <c r="O212" s="20" t="inlineStr"/>
+      <c r="P212" s="20" t="inlineStr"/>
+      <c r="Q212" s="20" t="inlineStr"/>
+      <c r="R212" s="21" t="inlineStr"/>
+      <c r="S212" s="20" t="inlineStr"/>
+      <c r="T212" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U212" s="22" t="inlineStr">
+      <c r="U212" s="20" t="inlineStr">
         <is>
           <t>GREINER</t>
         </is>
       </c>
-      <c r="V212" s="22" t="inlineStr">
+      <c r="V212" s="20" t="inlineStr">
         <is>
           <t>Georges</t>
         </is>
       </c>
-      <c r="W212" s="22" t="inlineStr">
+      <c r="W212" s="20" t="inlineStr">
         <is>
           <t>Liquidateur</t>
         </is>
       </c>
-      <c r="X212" s="22" t="inlineStr">
+      <c r="X212" s="20" t="inlineStr">
         <is>
           <t>11 GRIMONAUX</t>
         </is>
       </c>
-      <c r="Y212" s="23" t="inlineStr">
+      <c r="Y212" s="21" t="inlineStr">
         <is>
           <t>57255</t>
         </is>
       </c>
-      <c r="Z212" s="22" t="inlineStr">
+      <c r="Z212" s="20" t="inlineStr">
         <is>
           <t>STE MARIE AUX CHENES</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="22" t="inlineStr">
+      <c r="A213" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B213" s="23" t="inlineStr">
+      <c r="B213" s="21" t="inlineStr">
         <is>
           <t>831403951</t>
         </is>
       </c>
-      <c r="C213" s="23" t="inlineStr">
+      <c r="C213" s="21" t="inlineStr">
         <is>
           <t>83140395100021</t>
         </is>
       </c>
-      <c r="D213" s="22" t="inlineStr">
+      <c r="D213" s="20" t="inlineStr">
         <is>
           <t>LE BLEU</t>
         </is>
       </c>
-      <c r="E213" s="22" t="inlineStr">
+      <c r="E213" s="20" t="inlineStr">
         <is>
           <t>LE BLEU</t>
         </is>
       </c>
-      <c r="F213" s="22" t="inlineStr">
+      <c r="F213" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G213" s="22" t="inlineStr">
+      <c r="G213" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H213" s="22" t="inlineStr">
+      <c r="H213" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I213" s="22" t="inlineStr">
+      <c r="I213" s="20" t="inlineStr">
         <is>
           <t>09/08/2017</t>
         </is>
       </c>
-      <c r="J213" s="22" t="inlineStr">
+      <c r="J213" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K213" s="22" t="inlineStr">
+      <c r="K213" s="20" t="inlineStr">
         <is>
           <t>6 RUE WINSTON CHURCHILL</t>
         </is>
       </c>
-      <c r="L213" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M213" s="22" t="inlineStr">
+      <c r="L213" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M213" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N213" s="22" t="inlineStr">
+      <c r="N213" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O213" s="22" t="inlineStr"/>
-      <c r="P213" s="22" t="inlineStr"/>
-      <c r="Q213" s="22" t="inlineStr"/>
-      <c r="R213" s="23" t="inlineStr"/>
-      <c r="S213" s="22" t="inlineStr"/>
-      <c r="T213" s="22" t="inlineStr">
+      <c r="O213" s="20" t="inlineStr"/>
+      <c r="P213" s="20" t="inlineStr"/>
+      <c r="Q213" s="20" t="inlineStr"/>
+      <c r="R213" s="21" t="inlineStr"/>
+      <c r="S213" s="20" t="inlineStr"/>
+      <c r="T213" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U213" s="22" t="inlineStr">
+      <c r="U213" s="20" t="inlineStr">
         <is>
           <t>WALLERICH</t>
         </is>
       </c>
-      <c r="V213" s="22" t="inlineStr">
+      <c r="V213" s="20" t="inlineStr">
         <is>
           <t>Michel, Ernest</t>
         </is>
       </c>
-      <c r="W213" s="22" t="inlineStr">
+      <c r="W213" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X213" s="22" t="inlineStr">
+      <c r="X213" s="20" t="inlineStr">
         <is>
           <t>40 rue Saint-Gengoulf</t>
         </is>
       </c>
-      <c r="Y213" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z213" s="22" t="inlineStr">
+      <c r="Y213" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z213" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="22" t="inlineStr">
+      <c r="A214" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B214" s="23" t="inlineStr">
+      <c r="B214" s="21" t="inlineStr">
         <is>
           <t>824141410</t>
         </is>
       </c>
-      <c r="C214" s="23" t="inlineStr">
+      <c r="C214" s="21" t="inlineStr">
         <is>
           <t>82414141000012</t>
         </is>
       </c>
-      <c r="D214" s="22" t="inlineStr">
+      <c r="D214" s="20" t="inlineStr">
         <is>
           <t>NEWCO</t>
         </is>
       </c>
-      <c r="E214" s="22" t="inlineStr">
+      <c r="E214" s="20" t="inlineStr">
         <is>
           <t>NEWCO</t>
         </is>
       </c>
-      <c r="F214" s="22" t="inlineStr">
+      <c r="F214" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G214" s="22" t="inlineStr">
+      <c r="G214" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H214" s="22" t="inlineStr">
+      <c r="H214" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I214" s="22" t="inlineStr">
+      <c r="I214" s="20" t="inlineStr">
         <is>
           <t>06/12/2016</t>
         </is>
       </c>
-      <c r="J214" s="22" t="inlineStr">
+      <c r="J214" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K214" s="22" t="inlineStr">
+      <c r="K214" s="20" t="inlineStr">
         <is>
           <t>8 RUE DE LADOUCETTE</t>
         </is>
       </c>
-      <c r="L214" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M214" s="22" t="inlineStr">
+      <c r="L214" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M214" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N214" s="22" t="inlineStr">
+      <c r="N214" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O214" s="22" t="inlineStr"/>
-      <c r="P214" s="22" t="inlineStr"/>
-      <c r="Q214" s="22" t="inlineStr"/>
-      <c r="R214" s="23" t="inlineStr"/>
-      <c r="S214" s="22" t="inlineStr"/>
-      <c r="T214" s="22" t="inlineStr">
+      <c r="O214" s="20" t="inlineStr"/>
+      <c r="P214" s="20" t="inlineStr"/>
+      <c r="Q214" s="20" t="inlineStr"/>
+      <c r="R214" s="21" t="inlineStr"/>
+      <c r="S214" s="20" t="inlineStr"/>
+      <c r="T214" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U214" s="22" t="inlineStr">
+      <c r="U214" s="20" t="inlineStr">
         <is>
           <t>PRZYBYLSKI</t>
         </is>
       </c>
-      <c r="V214" s="22" t="inlineStr">
+      <c r="V214" s="20" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="W214" s="22" t="inlineStr">
+      <c r="W214" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X214" s="22" t="inlineStr">
+      <c r="X214" s="20" t="inlineStr">
         <is>
           <t>13 rue Georges de la Tour</t>
         </is>
       </c>
-      <c r="Y214" s="23" t="inlineStr">
+      <c r="Y214" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z214" s="22" t="inlineStr">
+      <c r="Z214" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="22" t="inlineStr">
+      <c r="A215" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B215" s="23" t="inlineStr">
+      <c r="B215" s="21" t="inlineStr">
         <is>
           <t>401623301</t>
         </is>
       </c>
-      <c r="C215" s="23" t="inlineStr">
+      <c r="C215" s="21" t="inlineStr">
         <is>
           <t>40162330100025</t>
         </is>
       </c>
-      <c r="D215" s="22" t="inlineStr">
+      <c r="D215" s="20" t="inlineStr">
         <is>
           <t>ASS LES AMIS DE SAINT LOUIS</t>
         </is>
       </c>
-      <c r="E215" s="22" t="inlineStr">
+      <c r="E215" s="20" t="inlineStr">
         <is>
           <t>ASS LES AMIS DE SAINT LOUIS</t>
         </is>
       </c>
-      <c r="F215" s="22" t="inlineStr">
+      <c r="F215" s="20" t="inlineStr">
         <is>
           <t>Association de droit local (Bas-Rhin, Haut-Rhin et Moselle)</t>
         </is>
       </c>
-      <c r="G215" s="22" t="inlineStr">
+      <c r="G215" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H215" s="22" t="inlineStr">
+      <c r="H215" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I215" s="22" t="inlineStr">
+      <c r="I215" s="20" t="inlineStr">
         <is>
           <t>31/03/1995</t>
         </is>
       </c>
-      <c r="J215" s="22" t="inlineStr">
+      <c r="J215" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="K215" s="22" t="inlineStr">
+      <c r="K215" s="20" t="inlineStr">
         <is>
           <t>4 AV JEAN 23</t>
         </is>
       </c>
-      <c r="L215" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M215" s="22" t="inlineStr">
+      <c r="L215" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M215" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N215" s="22" t="inlineStr">
+      <c r="N215" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O215" s="22" t="inlineStr"/>
-      <c r="P215" s="22" t="inlineStr"/>
-      <c r="Q215" s="22" t="inlineStr"/>
-      <c r="R215" s="23" t="inlineStr"/>
-      <c r="S215" s="22" t="inlineStr"/>
-      <c r="T215" s="22" t="inlineStr">
+      <c r="O215" s="20" t="inlineStr"/>
+      <c r="P215" s="20" t="inlineStr"/>
+      <c r="Q215" s="20" t="inlineStr"/>
+      <c r="R215" s="21" t="inlineStr"/>
+      <c r="S215" s="20" t="inlineStr"/>
+      <c r="T215" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U215" s="22" t="inlineStr"/>
-      <c r="V215" s="22" t="inlineStr"/>
-      <c r="W215" s="22" t="inlineStr"/>
-      <c r="X215" s="22" t="inlineStr"/>
-      <c r="Y215" s="23" t="inlineStr"/>
-      <c r="Z215" s="22" t="inlineStr"/>
+      <c r="U215" s="20" t="inlineStr"/>
+      <c r="V215" s="20" t="inlineStr"/>
+      <c r="W215" s="20" t="inlineStr"/>
+      <c r="X215" s="20" t="inlineStr"/>
+      <c r="Y215" s="21" t="inlineStr"/>
+      <c r="Z215" s="20" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="22" t="inlineStr">
+      <c r="A216" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B216" s="23" t="inlineStr">
+      <c r="B216" s="21" t="inlineStr">
         <is>
           <t>928015064</t>
         </is>
       </c>
-      <c r="C216" s="23" t="inlineStr">
+      <c r="C216" s="21" t="inlineStr">
         <is>
           <t>92801506400019</t>
         </is>
       </c>
-      <c r="D216" s="22" t="inlineStr">
+      <c r="D216" s="20" t="inlineStr">
         <is>
           <t>BRUDEAU</t>
         </is>
       </c>
-      <c r="E216" s="22" t="inlineStr">
+      <c r="E216" s="20" t="inlineStr">
         <is>
           <t>BRUDEAU</t>
         </is>
       </c>
-      <c r="F216" s="22" t="inlineStr">
+      <c r="F216" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G216" s="22" t="inlineStr">
+      <c r="G216" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H216" s="22" t="inlineStr">
+      <c r="H216" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I216" s="22" t="inlineStr">
+      <c r="I216" s="20" t="inlineStr">
         <is>
           <t>29/04/2024</t>
         </is>
       </c>
-      <c r="J216" s="22" t="inlineStr">
+      <c r="J216" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K216" s="22" t="inlineStr">
+      <c r="K216" s="20" t="inlineStr">
         <is>
           <t>15 RUE MARCHANT</t>
         </is>
       </c>
-      <c r="L216" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M216" s="22" t="inlineStr">
+      <c r="L216" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M216" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N216" s="22" t="inlineStr">
+      <c r="N216" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O216" s="22" t="inlineStr"/>
-      <c r="P216" s="22" t="inlineStr"/>
-      <c r="Q216" s="22" t="inlineStr"/>
-      <c r="R216" s="23" t="inlineStr"/>
-      <c r="S216" s="22" t="inlineStr"/>
-      <c r="T216" s="22" t="inlineStr">
+      <c r="O216" s="20" t="inlineStr"/>
+      <c r="P216" s="20" t="inlineStr"/>
+      <c r="Q216" s="20" t="inlineStr"/>
+      <c r="R216" s="21" t="inlineStr"/>
+      <c r="S216" s="20" t="inlineStr"/>
+      <c r="T216" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U216" s="22" t="inlineStr">
+      <c r="U216" s="20" t="inlineStr">
         <is>
           <t>Brutto</t>
         </is>
       </c>
-      <c r="V216" s="22" t="inlineStr">
+      <c r="V216" s="20" t="inlineStr">
         <is>
           <t>Philippe</t>
         </is>
       </c>
-      <c r="W216" s="22" t="inlineStr">
+      <c r="W216" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X216" s="22" t="inlineStr"/>
-      <c r="Y216" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z216" s="22" t="inlineStr">
+      <c r="X216" s="20" t="inlineStr"/>
+      <c r="Y216" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z216" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="22" t="inlineStr">
+      <c r="A217" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B217" s="23" t="inlineStr">
+      <c r="B217" s="21" t="inlineStr">
         <is>
           <t>507864940</t>
         </is>
       </c>
-      <c r="C217" s="23" t="inlineStr">
+      <c r="C217" s="21" t="inlineStr">
         <is>
           <t>50786494000014</t>
         </is>
       </c>
-      <c r="D217" s="22" t="inlineStr">
+      <c r="D217" s="20" t="inlineStr">
         <is>
           <t>SARL CHANDARA</t>
         </is>
       </c>
-      <c r="E217" s="22" t="inlineStr">
+      <c r="E217" s="20" t="inlineStr">
         <is>
           <t>SARL CHANDARA</t>
         </is>
       </c>
-      <c r="F217" s="22" t="inlineStr">
+      <c r="F217" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G217" s="22" t="inlineStr">
+      <c r="G217" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H217" s="22" t="inlineStr">
+      <c r="H217" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I217" s="22" t="inlineStr">
+      <c r="I217" s="20" t="inlineStr">
         <is>
           <t>01/09/2008</t>
         </is>
       </c>
-      <c r="J217" s="22" t="inlineStr">
+      <c r="J217" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K217" s="22" t="inlineStr">
+      <c r="K217" s="20" t="inlineStr">
         <is>
           <t>2 RUE DU PONT DES ROCHES</t>
         </is>
       </c>
-      <c r="L217" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M217" s="22" t="inlineStr">
+      <c r="L217" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M217" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N217" s="22" t="inlineStr">
+      <c r="N217" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O217" s="22" t="n">
-        <v>252174</v>
-      </c>
-      <c r="P217" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q217" s="22" t="inlineStr"/>
-      <c r="R217" s="23" t="inlineStr"/>
-      <c r="S217" s="22" t="inlineStr"/>
-      <c r="T217" s="22" t="inlineStr">
+      <c r="O217" s="20" t="inlineStr">
+        <is>
+          <t>252174</t>
+        </is>
+      </c>
+      <c r="P217" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q217" s="20" t="inlineStr"/>
+      <c r="R217" s="21" t="inlineStr"/>
+      <c r="S217" s="20" t="inlineStr"/>
+      <c r="T217" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U217" s="22" t="inlineStr">
+      <c r="U217" s="20" t="inlineStr">
         <is>
           <t>CHAN DARA</t>
         </is>
       </c>
-      <c r="V217" s="22" t="inlineStr">
+      <c r="V217" s="20" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="W217" s="22" t="inlineStr">
+      <c r="W217" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X217" s="22" t="inlineStr">
+      <c r="X217" s="20" t="inlineStr">
         <is>
           <t>9 rue Robert Schuman</t>
         </is>
       </c>
-      <c r="Y217" s="23" t="inlineStr">
+      <c r="Y217" s="21" t="inlineStr">
         <is>
           <t>57580</t>
         </is>
       </c>
-      <c r="Z217" s="22" t="inlineStr">
+      <c r="Z217" s="20" t="inlineStr">
         <is>
           <t>Rémilly</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="22" t="inlineStr">
+      <c r="A218" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B218" s="23" t="inlineStr">
+      <c r="B218" s="21" t="inlineStr">
         <is>
           <t>525353934</t>
         </is>
       </c>
-      <c r="C218" s="23" t="inlineStr">
+      <c r="C218" s="21" t="inlineStr">
         <is>
           <t>52535393400017</t>
         </is>
       </c>
-      <c r="D218" s="22" t="inlineStr">
+      <c r="D218" s="20" t="inlineStr">
         <is>
           <t>KYOU</t>
         </is>
       </c>
-      <c r="E218" s="22" t="inlineStr">
+      <c r="E218" s="20" t="inlineStr">
         <is>
           <t>KYOU</t>
         </is>
       </c>
-      <c r="F218" s="22" t="inlineStr">
+      <c r="F218" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G218" s="22" t="inlineStr">
+      <c r="G218" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H218" s="22" t="inlineStr">
+      <c r="H218" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I218" s="22" t="inlineStr">
+      <c r="I218" s="20" t="inlineStr">
         <is>
           <t>01/10/2010</t>
         </is>
       </c>
-      <c r="J218" s="22" t="inlineStr">
+      <c r="J218" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="K218" s="22" t="inlineStr">
+      <c r="K218" s="20" t="inlineStr">
         <is>
           <t>6 RUE DU MOYEN PONT</t>
         </is>
       </c>
-      <c r="L218" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M218" s="22" t="inlineStr">
+      <c r="L218" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M218" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N218" s="22" t="inlineStr">
+      <c r="N218" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O218" s="22" t="inlineStr"/>
-      <c r="P218" s="22" t="inlineStr"/>
-      <c r="Q218" s="22" t="inlineStr"/>
-      <c r="R218" s="23" t="inlineStr"/>
-      <c r="S218" s="22" t="inlineStr"/>
-      <c r="T218" s="22" t="inlineStr">
+      <c r="O218" s="20" t="inlineStr"/>
+      <c r="P218" s="20" t="inlineStr"/>
+      <c r="Q218" s="20" t="inlineStr"/>
+      <c r="R218" s="21" t="inlineStr"/>
+      <c r="S218" s="20" t="inlineStr"/>
+      <c r="T218" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U218" s="22" t="inlineStr">
+      <c r="U218" s="20" t="inlineStr">
         <is>
           <t>LIN</t>
         </is>
       </c>
-      <c r="V218" s="22" t="inlineStr">
+      <c r="V218" s="20" t="inlineStr">
         <is>
           <t>Xiaoyan</t>
         </is>
       </c>
-      <c r="W218" s="22" t="inlineStr">
+      <c r="W218" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X218" s="22" t="inlineStr">
+      <c r="X218" s="20" t="inlineStr">
         <is>
           <t>15 rue de la Chapelle</t>
         </is>
       </c>
-      <c r="Y218" s="23" t="inlineStr">
+      <c r="Y218" s="21" t="inlineStr">
         <is>
           <t>75018</t>
         </is>
       </c>
-      <c r="Z218" s="22" t="inlineStr">
+      <c r="Z218" s="20" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="22" t="inlineStr">
+      <c r="A219" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B219" s="23" t="inlineStr">
+      <c r="B219" s="21" t="inlineStr">
         <is>
           <t>802425421</t>
         </is>
       </c>
-      <c r="C219" s="23" t="inlineStr">
+      <c r="C219" s="21" t="inlineStr">
         <is>
           <t>80242542100012</t>
         </is>
       </c>
-      <c r="D219" s="22" t="inlineStr">
+      <c r="D219" s="20" t="inlineStr">
         <is>
           <t>LA GRILLADE METZ</t>
         </is>
       </c>
-      <c r="E219" s="22" t="inlineStr">
+      <c r="E219" s="20" t="inlineStr">
         <is>
           <t>LA GRILLADE METZ</t>
         </is>
       </c>
-      <c r="F219" s="22" t="inlineStr">
+      <c r="F219" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G219" s="22" t="inlineStr">
+      <c r="G219" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H219" s="22" t="inlineStr">
+      <c r="H219" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I219" s="22" t="inlineStr">
+      <c r="I219" s="20" t="inlineStr">
         <is>
           <t>21/05/2014</t>
         </is>
       </c>
-      <c r="J219" s="22" t="inlineStr">
+      <c r="J219" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K219" s="22" t="inlineStr">
+      <c r="K219" s="20" t="inlineStr">
         <is>
           <t>24 PLACE SAINT-SIMPLICE</t>
         </is>
       </c>
-      <c r="L219" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M219" s="22" t="inlineStr">
+      <c r="L219" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M219" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N219" s="22" t="inlineStr">
+      <c r="N219" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O219" s="22" t="n">
-        <v>110764</v>
-      </c>
-      <c r="P219" s="22" t="n">
-        <v>2015</v>
-      </c>
-      <c r="Q219" s="22" t="inlineStr"/>
-      <c r="R219" s="23" t="inlineStr"/>
-      <c r="S219" s="22" t="inlineStr"/>
-      <c r="T219" s="22" t="inlineStr">
+      <c r="O219" s="20" t="inlineStr">
+        <is>
+          <t>110764</t>
+        </is>
+      </c>
+      <c r="P219" s="20" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q219" s="20" t="inlineStr"/>
+      <c r="R219" s="21" t="inlineStr"/>
+      <c r="S219" s="20" t="inlineStr"/>
+      <c r="T219" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U219" s="22" t="inlineStr">
+      <c r="U219" s="20" t="inlineStr">
         <is>
           <t>BOUTEMEUR</t>
         </is>
       </c>
-      <c r="V219" s="22" t="inlineStr">
+      <c r="V219" s="20" t="inlineStr">
         <is>
           <t>Michaël, Norbert, Antar</t>
         </is>
       </c>
-      <c r="W219" s="22" t="inlineStr">
+      <c r="W219" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X219" s="22" t="inlineStr">
+      <c r="X219" s="20" t="inlineStr">
         <is>
           <t>10 rue du Maréchal Juin</t>
         </is>
       </c>
-      <c r="Y219" s="23" t="inlineStr">
+      <c r="Y219" s="21" t="inlineStr">
         <is>
           <t>57950</t>
         </is>
       </c>
-      <c r="Z219" s="22" t="inlineStr">
+      <c r="Z219" s="20" t="inlineStr">
         <is>
           <t>Montigny-les-Metz</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="22" t="inlineStr">
+      <c r="A220" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B220" s="23" t="inlineStr">
+      <c r="B220" s="21" t="inlineStr">
         <is>
           <t>828871509</t>
         </is>
       </c>
-      <c r="C220" s="23" t="inlineStr">
+      <c r="C220" s="21" t="inlineStr">
         <is>
           <t>82887150900018</t>
         </is>
       </c>
-      <c r="D220" s="22" t="inlineStr">
+      <c r="D220" s="20" t="inlineStr">
         <is>
           <t>SARL M.C</t>
         </is>
       </c>
-      <c r="E220" s="22" t="inlineStr">
+      <c r="E220" s="20" t="inlineStr">
         <is>
           <t>SARL M.C</t>
         </is>
       </c>
-      <c r="F220" s="22" t="inlineStr">
+      <c r="F220" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G220" s="22" t="inlineStr">
+      <c r="G220" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H220" s="22" t="inlineStr">
+      <c r="H220" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I220" s="22" t="inlineStr">
+      <c r="I220" s="20" t="inlineStr">
         <is>
           <t>09/03/2017</t>
         </is>
       </c>
-      <c r="J220" s="22" t="inlineStr">
+      <c r="J220" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K220" s="22" t="inlineStr">
+      <c r="K220" s="20" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L220" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M220" s="22" t="inlineStr">
+      <c r="L220" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M220" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N220" s="22" t="inlineStr">
+      <c r="N220" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O220" s="22" t="inlineStr"/>
-      <c r="P220" s="22" t="inlineStr"/>
-      <c r="Q220" s="22" t="inlineStr"/>
-      <c r="R220" s="23" t="inlineStr"/>
-      <c r="S220" s="22" t="inlineStr"/>
-      <c r="T220" s="22" t="inlineStr">
+      <c r="O220" s="20" t="inlineStr"/>
+      <c r="P220" s="20" t="inlineStr"/>
+      <c r="Q220" s="20" t="inlineStr"/>
+      <c r="R220" s="21" t="inlineStr"/>
+      <c r="S220" s="20" t="inlineStr"/>
+      <c r="T220" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U220" s="22" t="inlineStr">
+      <c r="U220" s="20" t="inlineStr">
         <is>
           <t>MENIRI</t>
         </is>
       </c>
-      <c r="V220" s="22" t="inlineStr">
+      <c r="V220" s="20" t="inlineStr">
         <is>
           <t>Mehdi</t>
         </is>
       </c>
-      <c r="W220" s="22" t="inlineStr">
+      <c r="W220" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X220" s="22" t="inlineStr">
+      <c r="X220" s="20" t="inlineStr">
         <is>
           <t>34 rue du Chazeau</t>
         </is>
       </c>
-      <c r="Y220" s="23" t="inlineStr">
+      <c r="Y220" s="21" t="inlineStr">
         <is>
           <t>54220</t>
         </is>
       </c>
-      <c r="Z220" s="22" t="inlineStr">
+      <c r="Z220" s="20" t="inlineStr">
         <is>
           <t>Malzéville</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="22" t="inlineStr">
+      <c r="A221" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B221" s="23" t="inlineStr">
+      <c r="B221" s="21" t="inlineStr">
         <is>
           <t>107909459</t>
         </is>
       </c>
-      <c r="C221" s="23" t="inlineStr">
+      <c r="C221" s="21" t="inlineStr">
         <is>
           <t>10790945900011</t>
         </is>
       </c>
-      <c r="D221" s="22" t="inlineStr">
+      <c r="D221" s="20" t="inlineStr">
         <is>
           <t>NOTRE CUISINE</t>
         </is>
       </c>
-      <c r="E221" s="22" t="inlineStr">
+      <c r="E221" s="20" t="inlineStr">
         <is>
           <t>NOTRE CUISINE</t>
         </is>
       </c>
-      <c r="F221" s="22" t="inlineStr">
+      <c r="F221" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G221" s="22" t="inlineStr">
+      <c r="G221" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H221" s="22" t="inlineStr">
+      <c r="H221" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I221" s="22" t="inlineStr">
+      <c r="I221" s="20" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="J221" s="22" t="inlineStr">
+      <c r="J221" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K221" s="22" t="inlineStr">
+      <c r="K221" s="20" t="inlineStr">
         <is>
           <t>16 RUE COISLIN</t>
         </is>
       </c>
-      <c r="L221" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M221" s="22" t="inlineStr">
+      <c r="L221" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M221" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N221" s="22" t="inlineStr">
+      <c r="N221" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O221" s="22" t="inlineStr"/>
-      <c r="P221" s="22" t="inlineStr"/>
-      <c r="Q221" s="22" t="inlineStr"/>
-      <c r="R221" s="23" t="inlineStr"/>
-      <c r="S221" s="22" t="inlineStr"/>
-      <c r="T221" s="22" t="inlineStr">
+      <c r="O221" s="20" t="inlineStr"/>
+      <c r="P221" s="20" t="inlineStr"/>
+      <c r="Q221" s="20" t="inlineStr"/>
+      <c r="R221" s="21" t="inlineStr"/>
+      <c r="S221" s="20" t="inlineStr"/>
+      <c r="T221" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U221" s="22" t="inlineStr">
+      <c r="U221" s="20" t="inlineStr">
         <is>
           <t>HOSSAIN</t>
         </is>
       </c>
-      <c r="V221" s="22" t="inlineStr">
+      <c r="V221" s="20" t="inlineStr">
         <is>
           <t>Masud</t>
         </is>
       </c>
-      <c r="W221" s="22" t="inlineStr">
+      <c r="W221" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X221" s="22" t="inlineStr"/>
-      <c r="Y221" s="23" t="inlineStr">
+      <c r="X221" s="20" t="inlineStr"/>
+      <c r="Y221" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z221" s="22" t="inlineStr">
+      <c r="Z221" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="22" t="inlineStr">
+      <c r="A222" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B222" s="23" t="inlineStr">
+      <c r="B222" s="21" t="inlineStr">
         <is>
           <t>108962721</t>
         </is>
       </c>
-      <c r="C222" s="23" t="inlineStr">
+      <c r="C222" s="21" t="inlineStr">
         <is>
           <t>10896272100016</t>
         </is>
       </c>
-      <c r="D222" s="22" t="inlineStr">
+      <c r="D222" s="20" t="inlineStr">
         <is>
           <t>LE CORNER 57</t>
         </is>
       </c>
-      <c r="E222" s="22" t="inlineStr">
+      <c r="E222" s="20" t="inlineStr">
         <is>
           <t>LE CORNER 57</t>
         </is>
       </c>
-      <c r="F222" s="22" t="inlineStr">
+      <c r="F222" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G222" s="22" t="inlineStr">
+      <c r="G222" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H222" s="22" t="inlineStr">
+      <c r="H222" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I222" s="22" t="inlineStr">
+      <c r="I222" s="20" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="J222" s="22" t="inlineStr">
+      <c r="J222" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K222" s="22" t="inlineStr">
+      <c r="K222" s="20" t="inlineStr">
         <is>
           <t>5 RUE COISLIN</t>
         </is>
       </c>
-      <c r="L222" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M222" s="22" t="inlineStr">
+      <c r="L222" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M222" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N222" s="22" t="inlineStr">
+      <c r="N222" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O222" s="22" t="inlineStr"/>
-      <c r="P222" s="22" t="inlineStr"/>
-      <c r="Q222" s="22" t="inlineStr"/>
-      <c r="R222" s="23" t="inlineStr"/>
-      <c r="S222" s="22" t="inlineStr"/>
-      <c r="T222" s="22" t="inlineStr">
+      <c r="O222" s="20" t="inlineStr"/>
+      <c r="P222" s="20" t="inlineStr"/>
+      <c r="Q222" s="20" t="inlineStr"/>
+      <c r="R222" s="21" t="inlineStr"/>
+      <c r="S222" s="20" t="inlineStr"/>
+      <c r="T222" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U222" s="22" t="inlineStr">
+      <c r="U222" s="20" t="inlineStr">
         <is>
           <t>JAKARIYA</t>
         </is>
       </c>
-      <c r="V222" s="22" t="inlineStr">
+      <c r="V222" s="20" t="inlineStr">
         <is>
           <t>Mohammad</t>
         </is>
       </c>
-      <c r="W222" s="22" t="inlineStr">
+      <c r="W222" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X222" s="22" t="inlineStr"/>
-      <c r="Y222" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z222" s="22" t="inlineStr">
+      <c r="X222" s="20" t="inlineStr"/>
+      <c r="Y222" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z222" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="22" t="inlineStr">
+      <c r="A223" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B223" s="23" t="inlineStr">
+      <c r="B223" s="21" t="inlineStr">
         <is>
           <t>537967713</t>
         </is>
       </c>
-      <c r="C223" s="23" t="inlineStr">
+      <c r="C223" s="21" t="inlineStr">
         <is>
           <t>53796771300026</t>
         </is>
       </c>
-      <c r="D223" s="22" t="inlineStr">
+      <c r="D223" s="20" t="inlineStr">
         <is>
           <t>DIDAU</t>
         </is>
       </c>
-      <c r="E223" s="22" t="inlineStr">
+      <c r="E223" s="20" t="inlineStr">
         <is>
           <t>DIDAU</t>
         </is>
       </c>
-      <c r="F223" s="22" t="inlineStr">
+      <c r="F223" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G223" s="22" t="inlineStr">
+      <c r="G223" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H223" s="22" t="inlineStr">
+      <c r="H223" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I223" s="22" t="inlineStr">
+      <c r="I223" s="20" t="inlineStr">
         <is>
           <t>17/11/2011</t>
         </is>
       </c>
-      <c r="J223" s="22" t="inlineStr">
+      <c r="J223" s="20" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="K223" s="22" t="inlineStr">
+      <c r="K223" s="20" t="inlineStr">
         <is>
           <t>5 PLACE JEAN SPINGA</t>
         </is>
       </c>
-      <c r="L223" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M223" s="22" t="inlineStr">
+      <c r="L223" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M223" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N223" s="22" t="inlineStr">
+      <c r="N223" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O223" s="22" t="inlineStr"/>
-      <c r="P223" s="22" t="inlineStr"/>
-      <c r="Q223" s="22" t="inlineStr"/>
-      <c r="R223" s="23" t="inlineStr"/>
-      <c r="S223" s="22" t="inlineStr"/>
-      <c r="T223" s="22" t="inlineStr">
+      <c r="O223" s="20" t="inlineStr"/>
+      <c r="P223" s="20" t="inlineStr"/>
+      <c r="Q223" s="20" t="inlineStr"/>
+      <c r="R223" s="21" t="inlineStr"/>
+      <c r="S223" s="20" t="inlineStr"/>
+      <c r="T223" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U223" s="22" t="inlineStr">
+      <c r="U223" s="20" t="inlineStr">
         <is>
           <t>DI CANDIA</t>
         </is>
       </c>
-      <c r="V223" s="22" t="inlineStr">
+      <c r="V223" s="20" t="inlineStr">
         <is>
           <t>Pascal</t>
         </is>
       </c>
-      <c r="W223" s="22" t="inlineStr">
+      <c r="W223" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X223" s="22" t="inlineStr">
+      <c r="X223" s="20" t="inlineStr">
         <is>
           <t>22/24 rue du Wad Billy</t>
         </is>
       </c>
-      <c r="Y223" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z223" s="22" t="inlineStr">
+      <c r="Y223" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z223" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="22" t="inlineStr">
+      <c r="A224" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B224" s="23" t="inlineStr">
+      <c r="B224" s="21" t="inlineStr">
         <is>
           <t>438601411</t>
         </is>
       </c>
-      <c r="C224" s="23" t="inlineStr">
+      <c r="C224" s="21" t="inlineStr">
         <is>
           <t>43860141100020</t>
         </is>
       </c>
-      <c r="D224" s="22" t="inlineStr">
+      <c r="D224" s="20" t="inlineStr">
         <is>
           <t>LAHYDINA</t>
         </is>
       </c>
-      <c r="E224" s="22" t="inlineStr">
+      <c r="E224" s="20" t="inlineStr">
         <is>
           <t>LAHYDINA</t>
         </is>
       </c>
-      <c r="F224" s="22" t="inlineStr">
+      <c r="F224" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G224" s="22" t="inlineStr">
+      <c r="G224" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H224" s="22" t="inlineStr">
+      <c r="H224" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I224" s="22" t="inlineStr">
+      <c r="I224" s="20" t="inlineStr">
         <is>
           <t>11/07/2001</t>
         </is>
       </c>
-      <c r="J224" s="22" t="inlineStr">
+      <c r="J224" s="20" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="K224" s="22" t="inlineStr">
+      <c r="K224" s="20" t="inlineStr">
         <is>
           <t>70 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="L224" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M224" s="22" t="inlineStr">
+      <c r="L224" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M224" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N224" s="22" t="inlineStr">
+      <c r="N224" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O224" s="22" t="n">
-        <v>88857</v>
-      </c>
-      <c r="P224" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q224" s="22" t="inlineStr"/>
-      <c r="R224" s="23" t="inlineStr"/>
-      <c r="S224" s="22" t="inlineStr"/>
-      <c r="T224" s="22" t="inlineStr">
+      <c r="O224" s="20" t="inlineStr">
+        <is>
+          <t>88857</t>
+        </is>
+      </c>
+      <c r="P224" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q224" s="20" t="inlineStr"/>
+      <c r="R224" s="21" t="inlineStr"/>
+      <c r="S224" s="20" t="inlineStr"/>
+      <c r="T224" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U224" s="22" t="inlineStr">
+      <c r="U224" s="20" t="inlineStr">
         <is>
           <t>BOUYAKHRICHAN</t>
         </is>
       </c>
-      <c r="V224" s="22" t="inlineStr">
+      <c r="V224" s="20" t="inlineStr">
         <is>
           <t>Saïd</t>
         </is>
       </c>
-      <c r="W224" s="22" t="inlineStr">
+      <c r="W224" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X224" s="22" t="inlineStr">
+      <c r="X224" s="20" t="inlineStr">
         <is>
           <t>33 rue du Général Metman</t>
         </is>
       </c>
-      <c r="Y224" s="23" t="inlineStr">
+      <c r="Y224" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z224" s="22" t="inlineStr">
+      <c r="Z224" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="22" t="inlineStr">
+      <c r="A225" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B225" s="23" t="inlineStr">
+      <c r="B225" s="21" t="inlineStr">
         <is>
           <t>341853075</t>
         </is>
       </c>
-      <c r="C225" s="23" t="inlineStr">
+      <c r="C225" s="21" t="inlineStr">
         <is>
           <t>34185307500016</t>
         </is>
       </c>
-      <c r="D225" s="22" t="inlineStr">
+      <c r="D225" s="20" t="inlineStr">
         <is>
           <t>HEWAL</t>
         </is>
       </c>
-      <c r="E225" s="22" t="inlineStr">
+      <c r="E225" s="20" t="inlineStr">
         <is>
           <t>HEWAL</t>
         </is>
       </c>
-      <c r="F225" s="22" t="inlineStr">
+      <c r="F225" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G225" s="22" t="inlineStr">
+      <c r="G225" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H225" s="22" t="inlineStr">
+      <c r="H225" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I225" s="22" t="inlineStr">
+      <c r="I225" s="20" t="inlineStr">
         <is>
           <t>01/08/1987</t>
         </is>
       </c>
-      <c r="J225" s="22" t="inlineStr">
+      <c r="J225" s="20" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="K225" s="22" t="inlineStr">
+      <c r="K225" s="20" t="inlineStr">
         <is>
           <t>5 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L225" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M225" s="22" t="inlineStr">
+      <c r="L225" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M225" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N225" s="22" t="inlineStr">
+      <c r="N225" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O225" s="22" t="inlineStr"/>
-      <c r="P225" s="22" t="inlineStr"/>
-      <c r="Q225" s="22" t="inlineStr"/>
-      <c r="R225" s="23" t="inlineStr"/>
-      <c r="S225" s="22" t="inlineStr"/>
-      <c r="T225" s="22" t="inlineStr">
+      <c r="O225" s="20" t="inlineStr"/>
+      <c r="P225" s="20" t="inlineStr"/>
+      <c r="Q225" s="20" t="inlineStr"/>
+      <c r="R225" s="21" t="inlineStr"/>
+      <c r="S225" s="20" t="inlineStr"/>
+      <c r="T225" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U225" s="22" t="inlineStr">
+      <c r="U225" s="20" t="inlineStr">
         <is>
           <t>ARSLAN</t>
         </is>
       </c>
-      <c r="V225" s="22" t="inlineStr">
+      <c r="V225" s="20" t="inlineStr">
         <is>
           <t>Mehmet</t>
         </is>
       </c>
-      <c r="W225" s="22" t="inlineStr">
+      <c r="W225" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X225" s="22" t="inlineStr">
+      <c r="X225" s="20" t="inlineStr">
         <is>
           <t>1-157 rue du Barrois</t>
         </is>
       </c>
-      <c r="Y225" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z225" s="22" t="inlineStr">
+      <c r="Y225" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z225" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="22" t="inlineStr">
+      <c r="A226" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B226" s="23" t="inlineStr">
+      <c r="B226" s="21" t="inlineStr">
         <is>
           <t>853893436</t>
         </is>
       </c>
-      <c r="C226" s="23" t="inlineStr">
+      <c r="C226" s="21" t="inlineStr">
         <is>
           <t>85389343600024</t>
         </is>
       </c>
-      <c r="D226" s="22" t="inlineStr">
+      <c r="D226" s="20" t="inlineStr">
         <is>
           <t>CAMARA HAWA</t>
         </is>
       </c>
-      <c r="E226" s="22" t="inlineStr">
+      <c r="E226" s="20" t="inlineStr">
         <is>
           <t>CAMARA HAWA</t>
         </is>
       </c>
-      <c r="F226" s="22" t="inlineStr">
+      <c r="F226" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G226" s="22" t="inlineStr">
+      <c r="G226" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H226" s="22" t="inlineStr">
+      <c r="H226" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I226" s="22" t="inlineStr">
+      <c r="I226" s="20" t="inlineStr">
         <is>
           <t>13/09/2019</t>
         </is>
       </c>
-      <c r="J226" s="22" t="inlineStr">
+      <c r="J226" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K226" s="22" t="inlineStr">
+      <c r="K226" s="20" t="inlineStr">
         <is>
           <t>3 RUE SIMONE VEIL</t>
         </is>
       </c>
-      <c r="L226" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M226" s="22" t="inlineStr">
+      <c r="L226" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M226" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N226" s="22" t="inlineStr">
+      <c r="N226" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O226" s="22" t="inlineStr"/>
-      <c r="P226" s="22" t="inlineStr"/>
-      <c r="Q226" s="22" t="inlineStr"/>
-      <c r="R226" s="23" t="inlineStr"/>
-      <c r="S226" s="22" t="inlineStr"/>
-      <c r="T226" s="22" t="inlineStr">
+      <c r="O226" s="20" t="inlineStr"/>
+      <c r="P226" s="20" t="inlineStr"/>
+      <c r="Q226" s="20" t="inlineStr"/>
+      <c r="R226" s="21" t="inlineStr"/>
+      <c r="S226" s="20" t="inlineStr"/>
+      <c r="T226" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U226" s="22" t="inlineStr">
+      <c r="U226" s="20" t="inlineStr">
         <is>
           <t>CAMARA</t>
         </is>
       </c>
-      <c r="V226" s="22" t="inlineStr">
+      <c r="V226" s="20" t="inlineStr">
         <is>
           <t>Hawa, Amy</t>
         </is>
       </c>
-      <c r="W226" s="22" t="inlineStr">
+      <c r="W226" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X226" s="22" t="inlineStr"/>
-      <c r="Y226" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z226" s="22" t="inlineStr">
+      <c r="X226" s="20" t="inlineStr"/>
+      <c r="Y226" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z226" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="22" t="inlineStr">
+      <c r="A227" s="20" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B227" s="23" t="inlineStr">
+      <c r="B227" s="21" t="inlineStr">
         <is>
           <t>848518296</t>
         </is>
       </c>
-      <c r="C227" s="23" t="inlineStr">
+      <c r="C227" s="21" t="inlineStr">
         <is>
           <t>84851829600019</t>
         </is>
       </c>
-      <c r="D227" s="22" t="inlineStr">
+      <c r="D227" s="20" t="inlineStr">
         <is>
           <t>CAFE D'LA GARE</t>
         </is>
       </c>
-      <c r="E227" s="22" t="inlineStr">
+      <c r="E227" s="20" t="inlineStr">
         <is>
           <t>CAFE D'LA GARE</t>
         </is>
       </c>
-      <c r="F227" s="22" t="inlineStr">
+      <c r="F227" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G227" s="22" t="inlineStr">
+      <c r="G227" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H227" s="22" t="inlineStr">
+      <c r="H227" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I227" s="22" t="inlineStr">
+      <c r="I227" s="20" t="inlineStr">
         <is>
           <t>21/02/2019</t>
         </is>
       </c>
-      <c r="J227" s="22" t="inlineStr">
+      <c r="J227" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K227" s="22" t="inlineStr">
+      <c r="K227" s="20" t="inlineStr">
         <is>
           <t>18 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L227" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M227" s="22" t="inlineStr">
+      <c r="L227" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M227" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N227" s="22" t="inlineStr">
+      <c r="N227" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O227" s="22" t="inlineStr"/>
-      <c r="P227" s="22" t="inlineStr"/>
-      <c r="Q227" s="22" t="inlineStr"/>
-      <c r="R227" s="23" t="inlineStr"/>
-      <c r="S227" s="22" t="inlineStr"/>
-      <c r="T227" s="22" t="inlineStr">
+      <c r="O227" s="20" t="inlineStr"/>
+      <c r="P227" s="20" t="inlineStr"/>
+      <c r="Q227" s="20" t="inlineStr"/>
+      <c r="R227" s="21" t="inlineStr"/>
+      <c r="S227" s="20" t="inlineStr"/>
+      <c r="T227" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U227" s="22" t="inlineStr">
+      <c r="U227" s="20" t="inlineStr">
         <is>
           <t>KAYA</t>
         </is>
       </c>
-      <c r="V227" s="22" t="inlineStr">
+      <c r="V227" s="20" t="inlineStr">
         <is>
           <t>Kadir</t>
         </is>
       </c>
-      <c r="W227" s="22" t="inlineStr">
+      <c r="W227" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X227" s="22" t="inlineStr">
+      <c r="X227" s="20" t="inlineStr">
         <is>
           <t>9 rue des Pins</t>
         </is>
       </c>
-      <c r="Y227" s="23" t="inlineStr">
+      <c r="Y227" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z227" s="22" t="inlineStr">
+      <c r="Z227" s="20" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B228" s="23" t="inlineStr">
+        <is>
+          <t>831063144</t>
+        </is>
+      </c>
+      <c r="C228" s="23" t="inlineStr">
+        <is>
+          <t>83106314400016</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="inlineStr">
+        <is>
+          <t>BAUDIER'S COFFY</t>
+        </is>
+      </c>
+      <c r="E228" s="22" t="inlineStr">
+        <is>
+          <t>BAUDIER'S COFFY</t>
+        </is>
+      </c>
+      <c r="F228" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G228" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H228" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I228" s="22" t="inlineStr">
+        <is>
+          <t>24/07/2017</t>
+        </is>
+      </c>
+      <c r="J228" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K228" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE MAZELLE</t>
+        </is>
+      </c>
+      <c r="L228" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M228" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N228" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O228" s="22" t="inlineStr"/>
+      <c r="P228" s="22" t="inlineStr"/>
+      <c r="Q228" s="22" t="inlineStr"/>
+      <c r="R228" s="23" t="inlineStr"/>
+      <c r="S228" s="22" t="inlineStr"/>
+      <c r="T228" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U228" s="22" t="inlineStr">
+        <is>
+          <t>BAUDIER</t>
+        </is>
+      </c>
+      <c r="V228" s="22" t="inlineStr">
+        <is>
+          <t>Philippe, Claude</t>
+        </is>
+      </c>
+      <c r="W228" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X228" s="22" t="inlineStr">
+        <is>
+          <t>9 sentier de la Butte</t>
+        </is>
+      </c>
+      <c r="Y228" s="23" t="inlineStr">
+        <is>
+          <t>57050</t>
+        </is>
+      </c>
+      <c r="Z228" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B229" s="23" t="inlineStr">
+        <is>
+          <t>939687174</t>
+        </is>
+      </c>
+      <c r="C229" s="23" t="inlineStr">
+        <is>
+          <t>93968717400028</t>
+        </is>
+      </c>
+      <c r="D229" s="22" t="inlineStr">
+        <is>
+          <t>ALBICA</t>
+        </is>
+      </c>
+      <c r="E229" s="22" t="inlineStr">
+        <is>
+          <t>ALBICA</t>
+        </is>
+      </c>
+      <c r="F229" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G229" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H229" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I229" s="22" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="J229" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K229" s="22" t="inlineStr">
+        <is>
+          <t>4 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L229" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M229" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N229" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O229" s="22" t="inlineStr"/>
+      <c r="P229" s="22" t="inlineStr"/>
+      <c r="Q229" s="22" t="inlineStr"/>
+      <c r="R229" s="23" t="inlineStr"/>
+      <c r="S229" s="22" t="inlineStr"/>
+      <c r="T229" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U229" s="22" t="inlineStr">
+        <is>
+          <t>B.B.H.</t>
+        </is>
+      </c>
+      <c r="V229" s="22" t="inlineStr"/>
+      <c r="W229" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X229" s="22" t="inlineStr">
+        <is>
+          <t>38 En Fournirue</t>
+        </is>
+      </c>
+      <c r="Y229" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z229" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B230" s="23" t="inlineStr">
+        <is>
+          <t>447521428</t>
+        </is>
+      </c>
+      <c r="C230" s="23" t="inlineStr">
+        <is>
+          <t>44752142800014</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="inlineStr">
+        <is>
+          <t>DRIMI</t>
+        </is>
+      </c>
+      <c r="E230" s="22" t="inlineStr">
+        <is>
+          <t>DRIMI</t>
+        </is>
+      </c>
+      <c r="F230" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G230" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H230" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I230" s="22" t="inlineStr">
+        <is>
+          <t>20/01/2003</t>
+        </is>
+      </c>
+      <c r="J230" s="22" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K230" s="22" t="inlineStr">
+        <is>
+          <t>7 RUE PONCELET</t>
+        </is>
+      </c>
+      <c r="L230" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M230" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N230" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O230" s="22" t="n">
+        <v>363640</v>
+      </c>
+      <c r="P230" s="22" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q230" s="22" t="inlineStr"/>
+      <c r="R230" s="23" t="inlineStr"/>
+      <c r="S230" s="22" t="inlineStr"/>
+      <c r="T230" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U230" s="22" t="inlineStr">
+        <is>
+          <t>MUSTAPHA</t>
+        </is>
+      </c>
+      <c r="V230" s="22" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="W230" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X230" s="22" t="inlineStr">
+        <is>
+          <t>7 Ruelle du Haut Village</t>
+        </is>
+      </c>
+      <c r="Y230" s="23" t="inlineStr">
+        <is>
+          <t>54710</t>
+        </is>
+      </c>
+      <c r="Z230" s="22" t="inlineStr">
+        <is>
+          <t>Fléville-devant-Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B231" s="23" t="inlineStr">
+        <is>
+          <t>453139826</t>
+        </is>
+      </c>
+      <c r="C231" s="23" t="inlineStr">
+        <is>
+          <t>45313982600011</t>
+        </is>
+      </c>
+      <c r="D231" s="22" t="inlineStr">
+        <is>
+          <t>RUBIS</t>
+        </is>
+      </c>
+      <c r="E231" s="22" t="inlineStr">
+        <is>
+          <t>RUBIS</t>
+        </is>
+      </c>
+      <c r="F231" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G231" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H231" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I231" s="22" t="inlineStr">
+        <is>
+          <t>15/04/2004</t>
+        </is>
+      </c>
+      <c r="J231" s="22" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="K231" s="22" t="inlineStr">
+        <is>
+          <t>25 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L231" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M231" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N231" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O231" s="22" t="n">
+        <v>603095</v>
+      </c>
+      <c r="P231" s="22" t="n">
+        <v>2018</v>
+      </c>
+      <c r="Q231" s="22" t="inlineStr"/>
+      <c r="R231" s="23" t="inlineStr"/>
+      <c r="S231" s="22" t="inlineStr"/>
+      <c r="T231" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U231" s="22" t="inlineStr">
+        <is>
+          <t>PANZA</t>
+        </is>
+      </c>
+      <c r="V231" s="22" t="inlineStr">
+        <is>
+          <t>Jean, Pierre</t>
+        </is>
+      </c>
+      <c r="W231" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X231" s="22" t="inlineStr">
+        <is>
+          <t>137B RUE DE METZ</t>
+        </is>
+      </c>
+      <c r="Y231" s="23" t="inlineStr">
+        <is>
+          <t>57525</t>
+        </is>
+      </c>
+      <c r="Z231" s="22" t="inlineStr">
+        <is>
+          <t>TALANGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B232" s="23" t="inlineStr">
+        <is>
+          <t>510743925</t>
+        </is>
+      </c>
+      <c r="C232" s="23" t="inlineStr">
+        <is>
+          <t>51074392500016</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="inlineStr">
+        <is>
+          <t>LA CANTINA</t>
+        </is>
+      </c>
+      <c r="E232" s="22" t="inlineStr">
+        <is>
+          <t>LA CANTINA</t>
+        </is>
+      </c>
+      <c r="F232" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G232" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H232" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I232" s="22" t="inlineStr">
+        <is>
+          <t>25/02/2009</t>
+        </is>
+      </c>
+      <c r="J232" s="22" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="K232" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DU PONT DES ROCHES</t>
+        </is>
+      </c>
+      <c r="L232" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M232" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N232" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O232" s="22" t="n">
+        <v>563903</v>
+      </c>
+      <c r="P232" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q232" s="22" t="inlineStr"/>
+      <c r="R232" s="23" t="inlineStr"/>
+      <c r="S232" s="22" t="inlineStr"/>
+      <c r="T232" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U232" s="22" t="inlineStr">
+        <is>
+          <t>GUYON</t>
+        </is>
+      </c>
+      <c r="V232" s="22" t="inlineStr">
+        <is>
+          <t>Arnaud, Joseph, Marcel, Marie</t>
+        </is>
+      </c>
+      <c r="W232" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X232" s="22" t="inlineStr"/>
+      <c r="Y232" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z232" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B233" s="23" t="inlineStr">
+        <is>
+          <t>978677367</t>
+        </is>
+      </c>
+      <c r="C233" s="23" t="inlineStr">
+        <is>
+          <t>97867736700010</t>
+        </is>
+      </c>
+      <c r="D233" s="22" t="inlineStr">
+        <is>
+          <t>ROJUPHI</t>
+        </is>
+      </c>
+      <c r="E233" s="22" t="inlineStr">
+        <is>
+          <t>ROJUPHI</t>
+        </is>
+      </c>
+      <c r="F233" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G233" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H233" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I233" s="22" t="inlineStr">
+        <is>
+          <t>17/08/2023</t>
+        </is>
+      </c>
+      <c r="J233" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K233" s="22" t="inlineStr">
+        <is>
+          <t>CTRE COMMERCIAL ST JACQUES</t>
+        </is>
+      </c>
+      <c r="L233" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M233" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N233" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O233" s="22" t="n">
+        <v>62063</v>
+      </c>
+      <c r="P233" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q233" s="22" t="inlineStr"/>
+      <c r="R233" s="23" t="inlineStr"/>
+      <c r="S233" s="22" t="inlineStr"/>
+      <c r="T233" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U233" s="22" t="inlineStr">
+        <is>
+          <t>KNAB</t>
+        </is>
+      </c>
+      <c r="V233" s="22" t="inlineStr">
+        <is>
+          <t>Philippe, Roger</t>
+        </is>
+      </c>
+      <c r="W233" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X233" s="22" t="inlineStr">
+        <is>
+          <t>9 Rue du Four du Cloître</t>
+        </is>
+      </c>
+      <c r="Y233" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z233" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B234" s="23" t="inlineStr">
+        <is>
+          <t>827801085</t>
+        </is>
+      </c>
+      <c r="C234" s="23" t="inlineStr">
+        <is>
+          <t>82780108500016</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="inlineStr">
+        <is>
+          <t>EURL LA CANTINE</t>
+        </is>
+      </c>
+      <c r="E234" s="22" t="inlineStr">
+        <is>
+          <t>EURL LA CANTINE</t>
+        </is>
+      </c>
+      <c r="F234" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G234" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H234" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I234" s="22" t="inlineStr">
+        <is>
+          <t>17/02/2017</t>
+        </is>
+      </c>
+      <c r="J234" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K234" s="22" t="inlineStr">
+        <is>
+          <t>16 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L234" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M234" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N234" s="22" t="inlineStr">
+        <is>
+          <t>Entre 20 et 49 salariés</t>
+        </is>
+      </c>
+      <c r="O234" s="22" t="inlineStr"/>
+      <c r="P234" s="22" t="inlineStr"/>
+      <c r="Q234" s="22" t="inlineStr"/>
+      <c r="R234" s="23" t="inlineStr"/>
+      <c r="S234" s="22" t="inlineStr"/>
+      <c r="T234" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U234" s="22" t="inlineStr">
+        <is>
+          <t>DI BERNARDI</t>
+        </is>
+      </c>
+      <c r="V234" s="22" t="inlineStr">
+        <is>
+          <t>Sandro, Dino, Diego</t>
+        </is>
+      </c>
+      <c r="W234" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X234" s="22" t="inlineStr">
+        <is>
+          <t>27 place de Chambre</t>
+        </is>
+      </c>
+      <c r="Y234" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z234" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B235" s="23" t="inlineStr">
+        <is>
+          <t>982839888</t>
+        </is>
+      </c>
+      <c r="C235" s="23" t="inlineStr">
+        <is>
+          <t>98283988800012</t>
+        </is>
+      </c>
+      <c r="D235" s="22" t="inlineStr">
+        <is>
+          <t>AU ROCHER DU LION</t>
+        </is>
+      </c>
+      <c r="E235" s="22" t="inlineStr">
+        <is>
+          <t>AU ROCHER DU LION</t>
+        </is>
+      </c>
+      <c r="F235" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G235" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H235" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I235" s="22" t="inlineStr">
+        <is>
+          <t>15/12/2023</t>
+        </is>
+      </c>
+      <c r="J235" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K235" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE DU NEUFBOURG</t>
+        </is>
+      </c>
+      <c r="L235" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M235" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N235" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O235" s="22" t="inlineStr"/>
+      <c r="P235" s="22" t="inlineStr"/>
+      <c r="Q235" s="22" t="inlineStr"/>
+      <c r="R235" s="23" t="inlineStr"/>
+      <c r="S235" s="22" t="inlineStr"/>
+      <c r="T235" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U235" s="22" t="inlineStr">
+        <is>
+          <t>ANTONY</t>
+        </is>
+      </c>
+      <c r="V235" s="22" t="inlineStr">
+        <is>
+          <t>Franck</t>
+        </is>
+      </c>
+      <c r="W235" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X235" s="22" t="inlineStr">
+        <is>
+          <t>197 rue de Vallières</t>
+        </is>
+      </c>
+      <c r="Y235" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z235" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B236" s="23" t="inlineStr">
+        <is>
+          <t>938696135</t>
+        </is>
+      </c>
+      <c r="C236" s="23" t="inlineStr">
+        <is>
+          <t>93869613500012</t>
+        </is>
+      </c>
+      <c r="D236" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORKYNETTE </t>
+        </is>
+      </c>
+      <c r="E236" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORKYNETTE </t>
+        </is>
+      </c>
+      <c r="F236" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G236" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H236" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I236" s="22" t="inlineStr">
+        <is>
+          <t>05/11/2024</t>
+        </is>
+      </c>
+      <c r="J236" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K236" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L236" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M236" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N236" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O236" s="22" t="inlineStr"/>
+      <c r="P236" s="22" t="inlineStr"/>
+      <c r="Q236" s="22" t="inlineStr"/>
+      <c r="R236" s="23" t="inlineStr"/>
+      <c r="S236" s="22" t="inlineStr"/>
+      <c r="T236" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U236" s="22" t="inlineStr">
+        <is>
+          <t>MOUGENOT</t>
+        </is>
+      </c>
+      <c r="V236" s="22" t="inlineStr">
+        <is>
+          <t>Adrien, Charles, Emmanuel</t>
+        </is>
+      </c>
+      <c r="W236" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X236" s="22" t="inlineStr">
+        <is>
+          <t>1 rue du pont des morts</t>
+        </is>
+      </c>
+      <c r="Y236" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z236" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B237" s="23" t="inlineStr">
+        <is>
+          <t>799191598</t>
+        </is>
+      </c>
+      <c r="C237" s="23" t="inlineStr">
+        <is>
+          <t>79919159800017</t>
+        </is>
+      </c>
+      <c r="D237" s="22" t="inlineStr">
+        <is>
+          <t>RESTAURANT "LE PARIS"</t>
+        </is>
+      </c>
+      <c r="E237" s="22" t="inlineStr">
+        <is>
+          <t>RESTAURANT "LE PARIS"</t>
+        </is>
+      </c>
+      <c r="F237" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G237" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H237" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I237" s="22" t="inlineStr">
+        <is>
+          <t>13/12/2013</t>
+        </is>
+      </c>
+      <c r="J237" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K237" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DE LA GENDARMERIE</t>
+        </is>
+      </c>
+      <c r="L237" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M237" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N237" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O237" s="22" t="n">
+        <v>441526</v>
+      </c>
+      <c r="P237" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Q237" s="22" t="inlineStr"/>
+      <c r="R237" s="23" t="inlineStr"/>
+      <c r="S237" s="22" t="inlineStr"/>
+      <c r="T237" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U237" s="22" t="inlineStr">
+        <is>
+          <t>MARRUNCHEDDU</t>
+        </is>
+      </c>
+      <c r="V237" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="W237" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X237" s="22" t="inlineStr">
+        <is>
+          <t>91 voie de la Liberté</t>
+        </is>
+      </c>
+      <c r="Y237" s="23" t="inlineStr">
+        <is>
+          <t>57160</t>
+        </is>
+      </c>
+      <c r="Z237" s="22" t="inlineStr">
+        <is>
+          <t>Scy-Chazelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B238" s="23" t="inlineStr">
+        <is>
+          <t>899806657</t>
+        </is>
+      </c>
+      <c r="C238" s="23" t="inlineStr">
+        <is>
+          <t>89980665700016</t>
+        </is>
+      </c>
+      <c r="D238" s="22" t="inlineStr">
+        <is>
+          <t>LE JARDIN SUSPENDU</t>
+        </is>
+      </c>
+      <c r="E238" s="22" t="inlineStr">
+        <is>
+          <t>LE JARDIN SUSPENDU</t>
+        </is>
+      </c>
+      <c r="F238" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G238" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H238" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I238" s="22" t="inlineStr">
+        <is>
+          <t>17/05/2021</t>
+        </is>
+      </c>
+      <c r="J238" s="22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K238" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L238" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M238" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N238" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O238" s="22" t="inlineStr"/>
+      <c r="P238" s="22" t="inlineStr"/>
+      <c r="Q238" s="22" t="inlineStr"/>
+      <c r="R238" s="23" t="inlineStr"/>
+      <c r="S238" s="22" t="inlineStr"/>
+      <c r="T238" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U238" s="22" t="inlineStr">
+        <is>
+          <t>BOPP</t>
+        </is>
+      </c>
+      <c r="V238" s="22" t="inlineStr">
+        <is>
+          <t>Caroline, Jeanne</t>
+        </is>
+      </c>
+      <c r="W238" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X238" s="22" t="inlineStr">
+        <is>
+          <t>5 C Rue de la Fontaine</t>
+        </is>
+      </c>
+      <c r="Y238" s="23" t="inlineStr">
+        <is>
+          <t>57645</t>
+        </is>
+      </c>
+      <c r="Z238" s="22" t="inlineStr">
+        <is>
+          <t>Noisseville</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B239" s="23" t="inlineStr">
+        <is>
+          <t>888717808</t>
+        </is>
+      </c>
+      <c r="C239" s="23" t="inlineStr">
+        <is>
+          <t>88871780800016</t>
+        </is>
+      </c>
+      <c r="D239" s="22" t="inlineStr">
+        <is>
+          <t>NR4 - LE ROMARIN</t>
+        </is>
+      </c>
+      <c r="E239" s="22" t="inlineStr">
+        <is>
+          <t>NR4 - LE ROMARIN</t>
+        </is>
+      </c>
+      <c r="F239" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G239" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H239" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I239" s="22" t="inlineStr">
+        <is>
+          <t>10/08/2020</t>
+        </is>
+      </c>
+      <c r="J239" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K239" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE DES AUGUSTINS</t>
+        </is>
+      </c>
+      <c r="L239" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M239" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N239" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O239" s="22" t="n">
+        <v>949499</v>
+      </c>
+      <c r="P239" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q239" s="22" t="inlineStr"/>
+      <c r="R239" s="23" t="inlineStr"/>
+      <c r="S239" s="22" t="inlineStr"/>
+      <c r="T239" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U239" s="22" t="inlineStr">
+        <is>
+          <t>RAPENNE</t>
+        </is>
+      </c>
+      <c r="V239" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas, Juste, Gilbert</t>
+        </is>
+      </c>
+      <c r="W239" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X239" s="22" t="inlineStr">
+        <is>
+          <t>75 Clos des Acacias</t>
+        </is>
+      </c>
+      <c r="Y239" s="23" t="inlineStr">
+        <is>
+          <t>57157</t>
+        </is>
+      </c>
+      <c r="Z239" s="22" t="inlineStr">
+        <is>
+          <t>Marly</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B240" s="23" t="inlineStr">
+        <is>
+          <t>807525134</t>
+        </is>
+      </c>
+      <c r="C240" s="23" t="inlineStr">
+        <is>
+          <t>80752513400019</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="inlineStr">
+        <is>
+          <t>LE K</t>
+        </is>
+      </c>
+      <c r="E240" s="22" t="inlineStr">
+        <is>
+          <t>LE K</t>
+        </is>
+      </c>
+      <c r="F240" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G240" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H240" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I240" s="22" t="inlineStr">
+        <is>
+          <t>15/10/2014</t>
+        </is>
+      </c>
+      <c r="J240" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K240" s="22" t="inlineStr">
+        <is>
+          <t>11 PLACE DE CHAMBRE</t>
+        </is>
+      </c>
+      <c r="L240" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M240" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N240" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O240" s="22" t="inlineStr"/>
+      <c r="P240" s="22" t="inlineStr"/>
+      <c r="Q240" s="22" t="inlineStr"/>
+      <c r="R240" s="23" t="inlineStr"/>
+      <c r="S240" s="22" t="inlineStr"/>
+      <c r="T240" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U240" s="22" t="inlineStr">
+        <is>
+          <t>ERAYDIN</t>
+        </is>
+      </c>
+      <c r="V240" s="22" t="inlineStr">
+        <is>
+          <t>Kemal</t>
+        </is>
+      </c>
+      <c r="W240" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X240" s="22" t="inlineStr">
+        <is>
+          <t>14 rue Le Goullon</t>
+        </is>
+      </c>
+      <c r="Y240" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z240" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B241" s="23" t="inlineStr">
+        <is>
+          <t>108820531</t>
+        </is>
+      </c>
+      <c r="C241" s="23" t="inlineStr">
+        <is>
+          <t>10882053100011</t>
+        </is>
+      </c>
+      <c r="D241" s="22" t="inlineStr">
+        <is>
+          <t>KAZUKO METZ</t>
+        </is>
+      </c>
+      <c r="E241" s="22" t="inlineStr">
+        <is>
+          <t>KAZUKO METZ</t>
+        </is>
+      </c>
+      <c r="F241" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G241" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H241" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I241" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="J241" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K241" s="22" t="inlineStr">
+        <is>
+          <t>86 EN FOURNIRUE</t>
+        </is>
+      </c>
+      <c r="L241" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M241" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N241" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O241" s="22" t="inlineStr"/>
+      <c r="P241" s="22" t="inlineStr"/>
+      <c r="Q241" s="22" t="inlineStr"/>
+      <c r="R241" s="23" t="inlineStr"/>
+      <c r="S241" s="22" t="inlineStr"/>
+      <c r="T241" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U241" s="22" t="inlineStr">
+        <is>
+          <t>YE</t>
+        </is>
+      </c>
+      <c r="V241" s="22" t="inlineStr">
+        <is>
+          <t>Jacques, Tony</t>
+        </is>
+      </c>
+      <c r="W241" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X241" s="22" t="inlineStr"/>
+      <c r="Y241" s="23" t="inlineStr">
+        <is>
+          <t>95150</t>
+        </is>
+      </c>
+      <c r="Z241" s="22" t="inlineStr">
+        <is>
+          <t>Taverny</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B242" s="23" t="inlineStr">
+        <is>
+          <t>994079499</t>
+        </is>
+      </c>
+      <c r="C242" s="23" t="inlineStr">
+        <is>
+          <t>99407949900012</t>
+        </is>
+      </c>
+      <c r="D242" s="22" t="inlineStr">
+        <is>
+          <t>OPPA EONNI</t>
+        </is>
+      </c>
+      <c r="E242" s="22" t="inlineStr">
+        <is>
+          <t>OPPA EONNI</t>
+        </is>
+      </c>
+      <c r="F242" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G242" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H242" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I242" s="22" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="J242" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K242" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE DUPONT DES LOGES</t>
+        </is>
+      </c>
+      <c r="L242" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M242" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N242" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O242" s="22" t="inlineStr"/>
+      <c r="P242" s="22" t="inlineStr"/>
+      <c r="Q242" s="22" t="inlineStr"/>
+      <c r="R242" s="23" t="inlineStr"/>
+      <c r="S242" s="22" t="inlineStr"/>
+      <c r="T242" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U242" s="22" t="inlineStr">
+        <is>
+          <t>REN</t>
+        </is>
+      </c>
+      <c r="V242" s="22" t="inlineStr">
+        <is>
+          <t>Shengjie</t>
+        </is>
+      </c>
+      <c r="W242" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X242" s="22" t="inlineStr">
+        <is>
+          <t>3, rue de la Commanderie</t>
+        </is>
+      </c>
+      <c r="Y242" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z242" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B243" s="23" t="inlineStr">
+        <is>
+          <t>912810769</t>
+        </is>
+      </c>
+      <c r="C243" s="23" t="inlineStr">
+        <is>
+          <t>91281076900022</t>
+        </is>
+      </c>
+      <c r="D243" s="22" t="inlineStr">
+        <is>
+          <t>AJFM SAINT JACQUES</t>
+        </is>
+      </c>
+      <c r="E243" s="22" t="inlineStr">
+        <is>
+          <t>AJFM SAINT JACQUES</t>
+        </is>
+      </c>
+      <c r="F243" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G243" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H243" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I243" s="22" t="inlineStr">
+        <is>
+          <t>25/04/2022</t>
+        </is>
+      </c>
+      <c r="J243" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K243" s="22" t="inlineStr">
+        <is>
+          <t>16 PLACE SAINT-JACQUES</t>
+        </is>
+      </c>
+      <c r="L243" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M243" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N243" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O243" s="22" t="n">
+        <v>654239</v>
+      </c>
+      <c r="P243" s="22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q243" s="22" t="inlineStr"/>
+      <c r="R243" s="23" t="inlineStr"/>
+      <c r="S243" s="22" t="inlineStr"/>
+      <c r="T243" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U243" s="22" t="inlineStr">
+        <is>
+          <t>CHR INVEST</t>
+        </is>
+      </c>
+      <c r="V243" s="22" t="inlineStr"/>
+      <c r="W243" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X243" s="22" t="inlineStr">
+        <is>
+          <t>41 Place de la Carrière</t>
+        </is>
+      </c>
+      <c r="Y243" s="23" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="Z243" s="22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B244" s="23" t="inlineStr">
+        <is>
+          <t>927730846</t>
+        </is>
+      </c>
+      <c r="C244" s="23" t="inlineStr">
+        <is>
+          <t>92773084600015</t>
+        </is>
+      </c>
+      <c r="D244" s="22" t="inlineStr">
+        <is>
+          <t>C.R.M C.R METZ</t>
+        </is>
+      </c>
+      <c r="E244" s="22" t="inlineStr">
+        <is>
+          <t>C.R METZ</t>
+        </is>
+      </c>
+      <c r="F244" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G244" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H244" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I244" s="22" t="inlineStr">
+        <is>
+          <t>15/04/2024</t>
+        </is>
+      </c>
+      <c r="J244" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K244" s="22" t="inlineStr">
+        <is>
+          <t>1 PARVIS DES DROITS DE L'HOMME</t>
+        </is>
+      </c>
+      <c r="L244" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M244" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N244" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O244" s="22" t="inlineStr"/>
+      <c r="P244" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q244" s="22" t="inlineStr"/>
+      <c r="R244" s="23" t="inlineStr"/>
+      <c r="S244" s="22" t="inlineStr"/>
+      <c r="T244" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U244" s="22" t="inlineStr">
+        <is>
+          <t>C.R. RESTAURANT</t>
+        </is>
+      </c>
+      <c r="V244" s="22" t="inlineStr"/>
+      <c r="W244" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X244" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE Sainte Catherine</t>
+        </is>
+      </c>
+      <c r="Y244" s="23" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="Z244" s="22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B245" s="23" t="inlineStr">
+        <is>
+          <t>789923539</t>
+        </is>
+      </c>
+      <c r="C245" s="23" t="inlineStr">
+        <is>
+          <t>78992353900017</t>
+        </is>
+      </c>
+      <c r="D245" s="22" t="inlineStr">
+        <is>
+          <t>BENAISSA NABILL</t>
+        </is>
+      </c>
+      <c r="E245" s="22" t="inlineStr">
+        <is>
+          <t>BENAISSA NABILL</t>
+        </is>
+      </c>
+      <c r="F245" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G245" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H245" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I245" s="22" t="inlineStr">
+        <is>
+          <t>10/12/2012</t>
+        </is>
+      </c>
+      <c r="J245" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K245" s="22" t="inlineStr">
+        <is>
+          <t>26 RUE DES JARDINS</t>
+        </is>
+      </c>
+      <c r="L245" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M245" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N245" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O245" s="22" t="inlineStr"/>
+      <c r="P245" s="22" t="inlineStr"/>
+      <c r="Q245" s="22" t="inlineStr"/>
+      <c r="R245" s="23" t="inlineStr"/>
+      <c r="S245" s="22" t="inlineStr"/>
+      <c r="T245" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U245" s="22" t="inlineStr">
+        <is>
+          <t>BENAISSA</t>
+        </is>
+      </c>
+      <c r="V245" s="22" t="inlineStr">
+        <is>
+          <t>Nabill</t>
+        </is>
+      </c>
+      <c r="W245" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X245" s="22" t="inlineStr"/>
+      <c r="Y245" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z245" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B246" s="23" t="inlineStr">
+        <is>
+          <t>822300059</t>
+        </is>
+      </c>
+      <c r="C246" s="23" t="inlineStr">
+        <is>
+          <t>82230005900026</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="inlineStr">
+        <is>
+          <t>O'MEZZA</t>
+        </is>
+      </c>
+      <c r="E246" s="22" t="inlineStr">
+        <is>
+          <t>O'MEZZA</t>
+        </is>
+      </c>
+      <c r="F246" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G246" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H246" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I246" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2016</t>
+        </is>
+      </c>
+      <c r="J246" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K246" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE BELLE-ISLE</t>
+        </is>
+      </c>
+      <c r="L246" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M246" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N246" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O246" s="22" t="inlineStr"/>
+      <c r="P246" s="22" t="inlineStr"/>
+      <c r="Q246" s="22" t="inlineStr"/>
+      <c r="R246" s="23" t="inlineStr"/>
+      <c r="S246" s="22" t="inlineStr"/>
+      <c r="T246" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U246" s="22" t="inlineStr">
+        <is>
+          <t>SABRA</t>
+        </is>
+      </c>
+      <c r="V246" s="22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="W246" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X246" s="22" t="inlineStr">
+        <is>
+          <t>7 rue de la Haye</t>
+        </is>
+      </c>
+      <c r="Y246" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z246" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B247" s="23" t="inlineStr">
+        <is>
+          <t>889062568</t>
+        </is>
+      </c>
+      <c r="C247" s="23" t="inlineStr">
+        <is>
+          <t>88906256800015</t>
+        </is>
+      </c>
+      <c r="D247" s="22" t="inlineStr">
+        <is>
+          <t>FAYER &amp; CO</t>
+        </is>
+      </c>
+      <c r="E247" s="22" t="inlineStr">
+        <is>
+          <t>FAYER &amp; CO</t>
+        </is>
+      </c>
+      <c r="F247" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G247" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H247" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I247" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2020</t>
+        </is>
+      </c>
+      <c r="J247" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K247" s="22" t="inlineStr">
+        <is>
+          <t>27 RUE DE LA PRINCERIE</t>
+        </is>
+      </c>
+      <c r="L247" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M247" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N247" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O247" s="22" t="inlineStr"/>
+      <c r="P247" s="22" t="inlineStr"/>
+      <c r="Q247" s="22" t="inlineStr"/>
+      <c r="R247" s="23" t="inlineStr"/>
+      <c r="S247" s="22" t="inlineStr"/>
+      <c r="T247" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U247" s="22" t="inlineStr">
+        <is>
+          <t>FAYER</t>
+        </is>
+      </c>
+      <c r="V247" s="22" t="inlineStr">
+        <is>
+          <t>Emmanuel, Renan</t>
+        </is>
+      </c>
+      <c r="W247" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X247" s="22" t="inlineStr">
+        <is>
+          <t>27 Rue de la Princerie</t>
+        </is>
+      </c>
+      <c r="Y247" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z247" s="22" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z227"/>
+  <autoFilter ref="A2:Z247"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z247"/>
+  <dimension ref="A1:Z267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25938,2253 +25938,4515 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="22" t="inlineStr">
+      <c r="A228" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B228" s="23" t="inlineStr">
+      <c r="B228" s="21" t="inlineStr">
         <is>
           <t>831063144</t>
         </is>
       </c>
-      <c r="C228" s="23" t="inlineStr">
+      <c r="C228" s="21" t="inlineStr">
         <is>
           <t>83106314400016</t>
         </is>
       </c>
-      <c r="D228" s="22" t="inlineStr">
+      <c r="D228" s="20" t="inlineStr">
         <is>
           <t>BAUDIER'S COFFY</t>
         </is>
       </c>
-      <c r="E228" s="22" t="inlineStr">
+      <c r="E228" s="20" t="inlineStr">
         <is>
           <t>BAUDIER'S COFFY</t>
         </is>
       </c>
-      <c r="F228" s="22" t="inlineStr">
+      <c r="F228" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G228" s="22" t="inlineStr">
+      <c r="G228" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H228" s="22" t="inlineStr">
+      <c r="H228" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I228" s="22" t="inlineStr">
+      <c r="I228" s="20" t="inlineStr">
         <is>
           <t>24/07/2017</t>
         </is>
       </c>
-      <c r="J228" s="22" t="inlineStr">
+      <c r="J228" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K228" s="22" t="inlineStr">
+      <c r="K228" s="20" t="inlineStr">
         <is>
           <t>4 RUE MAZELLE</t>
         </is>
       </c>
-      <c r="L228" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M228" s="22" t="inlineStr">
+      <c r="L228" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M228" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N228" s="22" t="inlineStr">
+      <c r="N228" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O228" s="22" t="inlineStr"/>
-      <c r="P228" s="22" t="inlineStr"/>
-      <c r="Q228" s="22" t="inlineStr"/>
-      <c r="R228" s="23" t="inlineStr"/>
-      <c r="S228" s="22" t="inlineStr"/>
-      <c r="T228" s="22" t="inlineStr">
+      <c r="O228" s="20" t="inlineStr"/>
+      <c r="P228" s="20" t="inlineStr"/>
+      <c r="Q228" s="20" t="inlineStr"/>
+      <c r="R228" s="21" t="inlineStr"/>
+      <c r="S228" s="20" t="inlineStr"/>
+      <c r="T228" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U228" s="22" t="inlineStr">
+      <c r="U228" s="20" t="inlineStr">
         <is>
           <t>BAUDIER</t>
         </is>
       </c>
-      <c r="V228" s="22" t="inlineStr">
+      <c r="V228" s="20" t="inlineStr">
         <is>
           <t>Philippe, Claude</t>
         </is>
       </c>
-      <c r="W228" s="22" t="inlineStr">
+      <c r="W228" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X228" s="22" t="inlineStr">
+      <c r="X228" s="20" t="inlineStr">
         <is>
           <t>9 sentier de la Butte</t>
         </is>
       </c>
-      <c r="Y228" s="23" t="inlineStr">
+      <c r="Y228" s="21" t="inlineStr">
         <is>
           <t>57050</t>
         </is>
       </c>
-      <c r="Z228" s="22" t="inlineStr">
+      <c r="Z228" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="22" t="inlineStr">
+      <c r="A229" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B229" s="23" t="inlineStr">
+      <c r="B229" s="21" t="inlineStr">
         <is>
           <t>939687174</t>
         </is>
       </c>
-      <c r="C229" s="23" t="inlineStr">
+      <c r="C229" s="21" t="inlineStr">
         <is>
           <t>93968717400028</t>
         </is>
       </c>
-      <c r="D229" s="22" t="inlineStr">
+      <c r="D229" s="20" t="inlineStr">
         <is>
           <t>ALBICA</t>
         </is>
       </c>
-      <c r="E229" s="22" t="inlineStr">
+      <c r="E229" s="20" t="inlineStr">
         <is>
           <t>ALBICA</t>
         </is>
       </c>
-      <c r="F229" s="22" t="inlineStr">
+      <c r="F229" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G229" s="22" t="inlineStr">
+      <c r="G229" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H229" s="22" t="inlineStr">
+      <c r="H229" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I229" s="22" t="inlineStr">
+      <c r="I229" s="20" t="inlineStr">
         <is>
           <t>01/02/2025</t>
         </is>
       </c>
-      <c r="J229" s="22" t="inlineStr">
+      <c r="J229" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K229" s="22" t="inlineStr">
+      <c r="K229" s="20" t="inlineStr">
         <is>
           <t>4 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L229" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M229" s="22" t="inlineStr">
+      <c r="L229" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M229" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N229" s="22" t="inlineStr">
+      <c r="N229" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O229" s="22" t="inlineStr"/>
-      <c r="P229" s="22" t="inlineStr"/>
-      <c r="Q229" s="22" t="inlineStr"/>
-      <c r="R229" s="23" t="inlineStr"/>
-      <c r="S229" s="22" t="inlineStr"/>
-      <c r="T229" s="22" t="inlineStr">
+      <c r="O229" s="20" t="inlineStr"/>
+      <c r="P229" s="20" t="inlineStr"/>
+      <c r="Q229" s="20" t="inlineStr"/>
+      <c r="R229" s="21" t="inlineStr"/>
+      <c r="S229" s="20" t="inlineStr"/>
+      <c r="T229" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U229" s="22" t="inlineStr">
+      <c r="U229" s="20" t="inlineStr">
         <is>
           <t>B.B.H.</t>
         </is>
       </c>
-      <c r="V229" s="22" t="inlineStr"/>
-      <c r="W229" s="22" t="inlineStr">
+      <c r="V229" s="20" t="inlineStr"/>
+      <c r="W229" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X229" s="22" t="inlineStr">
+      <c r="X229" s="20" t="inlineStr">
         <is>
           <t>38 En Fournirue</t>
         </is>
       </c>
-      <c r="Y229" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z229" s="22" t="inlineStr">
+      <c r="Y229" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z229" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="22" t="inlineStr">
+      <c r="A230" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B230" s="23" t="inlineStr">
+      <c r="B230" s="21" t="inlineStr">
         <is>
           <t>447521428</t>
         </is>
       </c>
-      <c r="C230" s="23" t="inlineStr">
+      <c r="C230" s="21" t="inlineStr">
         <is>
           <t>44752142800014</t>
         </is>
       </c>
-      <c r="D230" s="22" t="inlineStr">
+      <c r="D230" s="20" t="inlineStr">
         <is>
           <t>DRIMI</t>
         </is>
       </c>
-      <c r="E230" s="22" t="inlineStr">
+      <c r="E230" s="20" t="inlineStr">
         <is>
           <t>DRIMI</t>
         </is>
       </c>
-      <c r="F230" s="22" t="inlineStr">
+      <c r="F230" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G230" s="22" t="inlineStr">
+      <c r="G230" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H230" s="22" t="inlineStr">
+      <c r="H230" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I230" s="22" t="inlineStr">
+      <c r="I230" s="20" t="inlineStr">
         <is>
           <t>20/01/2003</t>
         </is>
       </c>
-      <c r="J230" s="22" t="inlineStr">
+      <c r="J230" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="K230" s="22" t="inlineStr">
+      <c r="K230" s="20" t="inlineStr">
         <is>
           <t>7 RUE PONCELET</t>
         </is>
       </c>
-      <c r="L230" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M230" s="22" t="inlineStr">
+      <c r="L230" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M230" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N230" s="22" t="inlineStr">
+      <c r="N230" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O230" s="22" t="n">
-        <v>363640</v>
-      </c>
-      <c r="P230" s="22" t="n">
-        <v>2015</v>
-      </c>
-      <c r="Q230" s="22" t="inlineStr"/>
-      <c r="R230" s="23" t="inlineStr"/>
-      <c r="S230" s="22" t="inlineStr"/>
-      <c r="T230" s="22" t="inlineStr">
+      <c r="O230" s="20" t="inlineStr">
+        <is>
+          <t>363640</t>
+        </is>
+      </c>
+      <c r="P230" s="20" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q230" s="20" t="inlineStr"/>
+      <c r="R230" s="21" t="inlineStr"/>
+      <c r="S230" s="20" t="inlineStr"/>
+      <c r="T230" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U230" s="22" t="inlineStr">
+      <c r="U230" s="20" t="inlineStr">
         <is>
           <t>MUSTAPHA</t>
         </is>
       </c>
-      <c r="V230" s="22" t="inlineStr">
+      <c r="V230" s="20" t="inlineStr">
         <is>
           <t>John</t>
         </is>
       </c>
-      <c r="W230" s="22" t="inlineStr">
+      <c r="W230" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X230" s="22" t="inlineStr">
+      <c r="X230" s="20" t="inlineStr">
         <is>
           <t>7 Ruelle du Haut Village</t>
         </is>
       </c>
-      <c r="Y230" s="23" t="inlineStr">
+      <c r="Y230" s="21" t="inlineStr">
         <is>
           <t>54710</t>
         </is>
       </c>
-      <c r="Z230" s="22" t="inlineStr">
+      <c r="Z230" s="20" t="inlineStr">
         <is>
           <t>Fléville-devant-Nancy</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="22" t="inlineStr">
+      <c r="A231" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B231" s="23" t="inlineStr">
+      <c r="B231" s="21" t="inlineStr">
         <is>
           <t>453139826</t>
         </is>
       </c>
-      <c r="C231" s="23" t="inlineStr">
+      <c r="C231" s="21" t="inlineStr">
         <is>
           <t>45313982600011</t>
         </is>
       </c>
-      <c r="D231" s="22" t="inlineStr">
+      <c r="D231" s="20" t="inlineStr">
         <is>
           <t>RUBIS</t>
         </is>
       </c>
-      <c r="E231" s="22" t="inlineStr">
+      <c r="E231" s="20" t="inlineStr">
         <is>
           <t>RUBIS</t>
         </is>
       </c>
-      <c r="F231" s="22" t="inlineStr">
+      <c r="F231" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G231" s="22" t="inlineStr">
+      <c r="G231" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H231" s="22" t="inlineStr">
+      <c r="H231" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I231" s="22" t="inlineStr">
+      <c r="I231" s="20" t="inlineStr">
         <is>
           <t>15/04/2004</t>
         </is>
       </c>
-      <c r="J231" s="22" t="inlineStr">
+      <c r="J231" s="20" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="K231" s="22" t="inlineStr">
+      <c r="K231" s="20" t="inlineStr">
         <is>
           <t>25 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L231" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M231" s="22" t="inlineStr">
+      <c r="L231" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M231" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N231" s="22" t="inlineStr">
+      <c r="N231" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O231" s="22" t="n">
-        <v>603095</v>
-      </c>
-      <c r="P231" s="22" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Q231" s="22" t="inlineStr"/>
-      <c r="R231" s="23" t="inlineStr"/>
-      <c r="S231" s="22" t="inlineStr"/>
-      <c r="T231" s="22" t="inlineStr">
+      <c r="O231" s="20" t="inlineStr">
+        <is>
+          <t>603095</t>
+        </is>
+      </c>
+      <c r="P231" s="20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q231" s="20" t="inlineStr"/>
+      <c r="R231" s="21" t="inlineStr"/>
+      <c r="S231" s="20" t="inlineStr"/>
+      <c r="T231" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U231" s="22" t="inlineStr">
+      <c r="U231" s="20" t="inlineStr">
         <is>
           <t>PANZA</t>
         </is>
       </c>
-      <c r="V231" s="22" t="inlineStr">
+      <c r="V231" s="20" t="inlineStr">
         <is>
           <t>Jean, Pierre</t>
         </is>
       </c>
-      <c r="W231" s="22" t="inlineStr">
+      <c r="W231" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X231" s="22" t="inlineStr">
+      <c r="X231" s="20" t="inlineStr">
         <is>
           <t>137B RUE DE METZ</t>
         </is>
       </c>
-      <c r="Y231" s="23" t="inlineStr">
+      <c r="Y231" s="21" t="inlineStr">
         <is>
           <t>57525</t>
         </is>
       </c>
-      <c r="Z231" s="22" t="inlineStr">
+      <c r="Z231" s="20" t="inlineStr">
         <is>
           <t>TALANGE</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="22" t="inlineStr">
+      <c r="A232" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B232" s="23" t="inlineStr">
+      <c r="B232" s="21" t="inlineStr">
         <is>
           <t>510743925</t>
         </is>
       </c>
-      <c r="C232" s="23" t="inlineStr">
+      <c r="C232" s="21" t="inlineStr">
         <is>
           <t>51074392500016</t>
         </is>
       </c>
-      <c r="D232" s="22" t="inlineStr">
+      <c r="D232" s="20" t="inlineStr">
         <is>
           <t>LA CANTINA</t>
         </is>
       </c>
-      <c r="E232" s="22" t="inlineStr">
+      <c r="E232" s="20" t="inlineStr">
         <is>
           <t>LA CANTINA</t>
         </is>
       </c>
-      <c r="F232" s="22" t="inlineStr">
+      <c r="F232" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G232" s="22" t="inlineStr">
+      <c r="G232" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H232" s="22" t="inlineStr">
+      <c r="H232" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I232" s="22" t="inlineStr">
+      <c r="I232" s="20" t="inlineStr">
         <is>
           <t>25/02/2009</t>
         </is>
       </c>
-      <c r="J232" s="22" t="inlineStr">
+      <c r="J232" s="20" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="K232" s="22" t="inlineStr">
+      <c r="K232" s="20" t="inlineStr">
         <is>
           <t>2 RUE DU PONT DES ROCHES</t>
         </is>
       </c>
-      <c r="L232" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M232" s="22" t="inlineStr">
+      <c r="L232" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M232" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N232" s="22" t="inlineStr">
+      <c r="N232" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O232" s="22" t="n">
-        <v>563903</v>
-      </c>
-      <c r="P232" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q232" s="22" t="inlineStr"/>
-      <c r="R232" s="23" t="inlineStr"/>
-      <c r="S232" s="22" t="inlineStr"/>
-      <c r="T232" s="22" t="inlineStr">
+      <c r="O232" s="20" t="inlineStr">
+        <is>
+          <t>563903</t>
+        </is>
+      </c>
+      <c r="P232" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q232" s="20" t="inlineStr"/>
+      <c r="R232" s="21" t="inlineStr"/>
+      <c r="S232" s="20" t="inlineStr"/>
+      <c r="T232" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U232" s="22" t="inlineStr">
+      <c r="U232" s="20" t="inlineStr">
         <is>
           <t>GUYON</t>
         </is>
       </c>
-      <c r="V232" s="22" t="inlineStr">
+      <c r="V232" s="20" t="inlineStr">
         <is>
           <t>Arnaud, Joseph, Marcel, Marie</t>
         </is>
       </c>
-      <c r="W232" s="22" t="inlineStr">
+      <c r="W232" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X232" s="22" t="inlineStr"/>
-      <c r="Y232" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z232" s="22" t="inlineStr">
+      <c r="X232" s="20" t="inlineStr"/>
+      <c r="Y232" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z232" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="22" t="inlineStr">
+      <c r="A233" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B233" s="23" t="inlineStr">
+      <c r="B233" s="21" t="inlineStr">
         <is>
           <t>978677367</t>
         </is>
       </c>
-      <c r="C233" s="23" t="inlineStr">
+      <c r="C233" s="21" t="inlineStr">
         <is>
           <t>97867736700010</t>
         </is>
       </c>
-      <c r="D233" s="22" t="inlineStr">
+      <c r="D233" s="20" t="inlineStr">
         <is>
           <t>ROJUPHI</t>
         </is>
       </c>
-      <c r="E233" s="22" t="inlineStr">
+      <c r="E233" s="20" t="inlineStr">
         <is>
           <t>ROJUPHI</t>
         </is>
       </c>
-      <c r="F233" s="22" t="inlineStr">
+      <c r="F233" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G233" s="22" t="inlineStr">
+      <c r="G233" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H233" s="22" t="inlineStr">
+      <c r="H233" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I233" s="22" t="inlineStr">
+      <c r="I233" s="20" t="inlineStr">
         <is>
           <t>17/08/2023</t>
         </is>
       </c>
-      <c r="J233" s="22" t="inlineStr">
+      <c r="J233" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K233" s="22" t="inlineStr">
+      <c r="K233" s="20" t="inlineStr">
         <is>
           <t>CTRE COMMERCIAL ST JACQUES</t>
         </is>
       </c>
-      <c r="L233" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M233" s="22" t="inlineStr">
+      <c r="L233" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M233" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N233" s="22" t="inlineStr">
+      <c r="N233" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O233" s="22" t="n">
-        <v>62063</v>
-      </c>
-      <c r="P233" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q233" s="22" t="inlineStr"/>
-      <c r="R233" s="23" t="inlineStr"/>
-      <c r="S233" s="22" t="inlineStr"/>
-      <c r="T233" s="22" t="inlineStr">
+      <c r="O233" s="20" t="inlineStr">
+        <is>
+          <t>62063</t>
+        </is>
+      </c>
+      <c r="P233" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q233" s="20" t="inlineStr"/>
+      <c r="R233" s="21" t="inlineStr"/>
+      <c r="S233" s="20" t="inlineStr"/>
+      <c r="T233" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U233" s="22" t="inlineStr">
+      <c r="U233" s="20" t="inlineStr">
         <is>
           <t>KNAB</t>
         </is>
       </c>
-      <c r="V233" s="22" t="inlineStr">
+      <c r="V233" s="20" t="inlineStr">
         <is>
           <t>Philippe, Roger</t>
         </is>
       </c>
-      <c r="W233" s="22" t="inlineStr">
+      <c r="W233" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X233" s="22" t="inlineStr">
+      <c r="X233" s="20" t="inlineStr">
         <is>
           <t>9 Rue du Four du Cloître</t>
         </is>
       </c>
-      <c r="Y233" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z233" s="22" t="inlineStr">
+      <c r="Y233" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z233" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="22" t="inlineStr">
+      <c r="A234" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B234" s="23" t="inlineStr">
+      <c r="B234" s="21" t="inlineStr">
         <is>
           <t>827801085</t>
         </is>
       </c>
-      <c r="C234" s="23" t="inlineStr">
+      <c r="C234" s="21" t="inlineStr">
         <is>
           <t>82780108500016</t>
         </is>
       </c>
-      <c r="D234" s="22" t="inlineStr">
+      <c r="D234" s="20" t="inlineStr">
         <is>
           <t>EURL LA CANTINE</t>
         </is>
       </c>
-      <c r="E234" s="22" t="inlineStr">
+      <c r="E234" s="20" t="inlineStr">
         <is>
           <t>EURL LA CANTINE</t>
         </is>
       </c>
-      <c r="F234" s="22" t="inlineStr">
+      <c r="F234" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G234" s="22" t="inlineStr">
+      <c r="G234" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H234" s="22" t="inlineStr">
+      <c r="H234" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I234" s="22" t="inlineStr">
+      <c r="I234" s="20" t="inlineStr">
         <is>
           <t>17/02/2017</t>
         </is>
       </c>
-      <c r="J234" s="22" t="inlineStr">
+      <c r="J234" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K234" s="22" t="inlineStr">
+      <c r="K234" s="20" t="inlineStr">
         <is>
           <t>16 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L234" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M234" s="22" t="inlineStr">
+      <c r="L234" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M234" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N234" s="22" t="inlineStr">
+      <c r="N234" s="20" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="O234" s="22" t="inlineStr"/>
-      <c r="P234" s="22" t="inlineStr"/>
-      <c r="Q234" s="22" t="inlineStr"/>
-      <c r="R234" s="23" t="inlineStr"/>
-      <c r="S234" s="22" t="inlineStr"/>
-      <c r="T234" s="22" t="inlineStr">
+      <c r="O234" s="20" t="inlineStr"/>
+      <c r="P234" s="20" t="inlineStr"/>
+      <c r="Q234" s="20" t="inlineStr"/>
+      <c r="R234" s="21" t="inlineStr"/>
+      <c r="S234" s="20" t="inlineStr"/>
+      <c r="T234" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U234" s="22" t="inlineStr">
+      <c r="U234" s="20" t="inlineStr">
         <is>
           <t>DI BERNARDI</t>
         </is>
       </c>
-      <c r="V234" s="22" t="inlineStr">
+      <c r="V234" s="20" t="inlineStr">
         <is>
           <t>Sandro, Dino, Diego</t>
         </is>
       </c>
-      <c r="W234" s="22" t="inlineStr">
+      <c r="W234" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X234" s="22" t="inlineStr">
+      <c r="X234" s="20" t="inlineStr">
         <is>
           <t>27 place de Chambre</t>
         </is>
       </c>
-      <c r="Y234" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z234" s="22" t="inlineStr">
+      <c r="Y234" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z234" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="22" t="inlineStr">
+      <c r="A235" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B235" s="23" t="inlineStr">
+      <c r="B235" s="21" t="inlineStr">
         <is>
           <t>982839888</t>
         </is>
       </c>
-      <c r="C235" s="23" t="inlineStr">
+      <c r="C235" s="21" t="inlineStr">
         <is>
           <t>98283988800012</t>
         </is>
       </c>
-      <c r="D235" s="22" t="inlineStr">
+      <c r="D235" s="20" t="inlineStr">
         <is>
           <t>AU ROCHER DU LION</t>
         </is>
       </c>
-      <c r="E235" s="22" t="inlineStr">
+      <c r="E235" s="20" t="inlineStr">
         <is>
           <t>AU ROCHER DU LION</t>
         </is>
       </c>
-      <c r="F235" s="22" t="inlineStr">
+      <c r="F235" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G235" s="22" t="inlineStr">
+      <c r="G235" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H235" s="22" t="inlineStr">
+      <c r="H235" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I235" s="22" t="inlineStr">
+      <c r="I235" s="20" t="inlineStr">
         <is>
           <t>15/12/2023</t>
         </is>
       </c>
-      <c r="J235" s="22" t="inlineStr">
+      <c r="J235" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K235" s="22" t="inlineStr">
+      <c r="K235" s="20" t="inlineStr">
         <is>
           <t>12 RUE DU NEUFBOURG</t>
         </is>
       </c>
-      <c r="L235" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M235" s="22" t="inlineStr">
+      <c r="L235" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M235" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N235" s="22" t="inlineStr">
+      <c r="N235" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O235" s="22" t="inlineStr"/>
-      <c r="P235" s="22" t="inlineStr"/>
-      <c r="Q235" s="22" t="inlineStr"/>
-      <c r="R235" s="23" t="inlineStr"/>
-      <c r="S235" s="22" t="inlineStr"/>
-      <c r="T235" s="22" t="inlineStr">
+      <c r="O235" s="20" t="inlineStr"/>
+      <c r="P235" s="20" t="inlineStr"/>
+      <c r="Q235" s="20" t="inlineStr"/>
+      <c r="R235" s="21" t="inlineStr"/>
+      <c r="S235" s="20" t="inlineStr"/>
+      <c r="T235" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U235" s="22" t="inlineStr">
+      <c r="U235" s="20" t="inlineStr">
         <is>
           <t>ANTONY</t>
         </is>
       </c>
-      <c r="V235" s="22" t="inlineStr">
+      <c r="V235" s="20" t="inlineStr">
         <is>
           <t>Franck</t>
         </is>
       </c>
-      <c r="W235" s="22" t="inlineStr">
+      <c r="W235" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X235" s="22" t="inlineStr">
+      <c r="X235" s="20" t="inlineStr">
         <is>
           <t>197 rue de Vallières</t>
         </is>
       </c>
-      <c r="Y235" s="23" t="inlineStr">
+      <c r="Y235" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z235" s="22" t="inlineStr">
+      <c r="Z235" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="22" t="inlineStr">
+      <c r="A236" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B236" s="23" t="inlineStr">
+      <c r="B236" s="21" t="inlineStr">
         <is>
           <t>938696135</t>
         </is>
       </c>
-      <c r="C236" s="23" t="inlineStr">
+      <c r="C236" s="21" t="inlineStr">
         <is>
           <t>93869613500012</t>
         </is>
       </c>
-      <c r="D236" s="22" t="inlineStr">
+      <c r="D236" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">PORKYNETTE </t>
         </is>
       </c>
-      <c r="E236" s="22" t="inlineStr">
+      <c r="E236" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">PORKYNETTE </t>
         </is>
       </c>
-      <c r="F236" s="22" t="inlineStr">
+      <c r="F236" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G236" s="22" t="inlineStr">
+      <c r="G236" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H236" s="22" t="inlineStr">
+      <c r="H236" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I236" s="22" t="inlineStr">
+      <c r="I236" s="20" t="inlineStr">
         <is>
           <t>05/11/2024</t>
         </is>
       </c>
-      <c r="J236" s="22" t="inlineStr">
+      <c r="J236" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K236" s="22" t="inlineStr">
+      <c r="K236" s="20" t="inlineStr">
         <is>
           <t>1 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L236" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M236" s="22" t="inlineStr">
+      <c r="L236" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M236" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N236" s="22" t="inlineStr">
+      <c r="N236" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O236" s="22" t="inlineStr"/>
-      <c r="P236" s="22" t="inlineStr"/>
-      <c r="Q236" s="22" t="inlineStr"/>
-      <c r="R236" s="23" t="inlineStr"/>
-      <c r="S236" s="22" t="inlineStr"/>
-      <c r="T236" s="22" t="inlineStr">
+      <c r="O236" s="20" t="inlineStr"/>
+      <c r="P236" s="20" t="inlineStr"/>
+      <c r="Q236" s="20" t="inlineStr"/>
+      <c r="R236" s="21" t="inlineStr"/>
+      <c r="S236" s="20" t="inlineStr"/>
+      <c r="T236" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U236" s="22" t="inlineStr">
+      <c r="U236" s="20" t="inlineStr">
         <is>
           <t>MOUGENOT</t>
         </is>
       </c>
-      <c r="V236" s="22" t="inlineStr">
+      <c r="V236" s="20" t="inlineStr">
         <is>
           <t>Adrien, Charles, Emmanuel</t>
         </is>
       </c>
-      <c r="W236" s="22" t="inlineStr">
+      <c r="W236" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X236" s="22" t="inlineStr">
+      <c r="X236" s="20" t="inlineStr">
         <is>
           <t>1 rue du pont des morts</t>
         </is>
       </c>
-      <c r="Y236" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z236" s="22" t="inlineStr">
+      <c r="Y236" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z236" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="22" t="inlineStr">
+      <c r="A237" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B237" s="23" t="inlineStr">
+      <c r="B237" s="21" t="inlineStr">
         <is>
           <t>799191598</t>
         </is>
       </c>
-      <c r="C237" s="23" t="inlineStr">
+      <c r="C237" s="21" t="inlineStr">
         <is>
           <t>79919159800017</t>
         </is>
       </c>
-      <c r="D237" s="22" t="inlineStr">
+      <c r="D237" s="20" t="inlineStr">
         <is>
           <t>RESTAURANT "LE PARIS"</t>
         </is>
       </c>
-      <c r="E237" s="22" t="inlineStr">
+      <c r="E237" s="20" t="inlineStr">
         <is>
           <t>RESTAURANT "LE PARIS"</t>
         </is>
       </c>
-      <c r="F237" s="22" t="inlineStr">
+      <c r="F237" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G237" s="22" t="inlineStr">
+      <c r="G237" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H237" s="22" t="inlineStr">
+      <c r="H237" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I237" s="22" t="inlineStr">
+      <c r="I237" s="20" t="inlineStr">
         <is>
           <t>13/12/2013</t>
         </is>
       </c>
-      <c r="J237" s="22" t="inlineStr">
+      <c r="J237" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K237" s="22" t="inlineStr">
+      <c r="K237" s="20" t="inlineStr">
         <is>
           <t>2 RUE DE LA GENDARMERIE</t>
         </is>
       </c>
-      <c r="L237" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M237" s="22" t="inlineStr">
+      <c r="L237" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M237" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N237" s="22" t="inlineStr">
+      <c r="N237" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O237" s="22" t="n">
-        <v>441526</v>
-      </c>
-      <c r="P237" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q237" s="22" t="inlineStr"/>
-      <c r="R237" s="23" t="inlineStr"/>
-      <c r="S237" s="22" t="inlineStr"/>
-      <c r="T237" s="22" t="inlineStr">
+      <c r="O237" s="20" t="inlineStr">
+        <is>
+          <t>441526</t>
+        </is>
+      </c>
+      <c r="P237" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q237" s="20" t="inlineStr"/>
+      <c r="R237" s="21" t="inlineStr"/>
+      <c r="S237" s="20" t="inlineStr"/>
+      <c r="T237" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U237" s="22" t="inlineStr">
+      <c r="U237" s="20" t="inlineStr">
         <is>
           <t>MARRUNCHEDDU</t>
         </is>
       </c>
-      <c r="V237" s="22" t="inlineStr">
+      <c r="V237" s="20" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="W237" s="22" t="inlineStr">
+      <c r="W237" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X237" s="22" t="inlineStr">
+      <c r="X237" s="20" t="inlineStr">
         <is>
           <t>91 voie de la Liberté</t>
         </is>
       </c>
-      <c r="Y237" s="23" t="inlineStr">
+      <c r="Y237" s="21" t="inlineStr">
         <is>
           <t>57160</t>
         </is>
       </c>
-      <c r="Z237" s="22" t="inlineStr">
+      <c r="Z237" s="20" t="inlineStr">
         <is>
           <t>Scy-Chazelles</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="22" t="inlineStr">
+      <c r="A238" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B238" s="23" t="inlineStr">
+      <c r="B238" s="21" t="inlineStr">
         <is>
           <t>899806657</t>
         </is>
       </c>
-      <c r="C238" s="23" t="inlineStr">
+      <c r="C238" s="21" t="inlineStr">
         <is>
           <t>89980665700016</t>
         </is>
       </c>
-      <c r="D238" s="22" t="inlineStr">
+      <c r="D238" s="20" t="inlineStr">
         <is>
           <t>LE JARDIN SUSPENDU</t>
         </is>
       </c>
-      <c r="E238" s="22" t="inlineStr">
+      <c r="E238" s="20" t="inlineStr">
         <is>
           <t>LE JARDIN SUSPENDU</t>
         </is>
       </c>
-      <c r="F238" s="22" t="inlineStr">
+      <c r="F238" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G238" s="22" t="inlineStr">
+      <c r="G238" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H238" s="22" t="inlineStr">
+      <c r="H238" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I238" s="22" t="inlineStr">
+      <c r="I238" s="20" t="inlineStr">
         <is>
           <t>17/05/2021</t>
         </is>
       </c>
-      <c r="J238" s="22" t="inlineStr">
+      <c r="J238" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K238" s="22" t="inlineStr">
+      <c r="K238" s="20" t="inlineStr">
         <is>
           <t>4 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L238" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M238" s="22" t="inlineStr">
+      <c r="L238" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M238" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N238" s="22" t="inlineStr">
+      <c r="N238" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O238" s="22" t="inlineStr"/>
-      <c r="P238" s="22" t="inlineStr"/>
-      <c r="Q238" s="22" t="inlineStr"/>
-      <c r="R238" s="23" t="inlineStr"/>
-      <c r="S238" s="22" t="inlineStr"/>
-      <c r="T238" s="22" t="inlineStr">
+      <c r="O238" s="20" t="inlineStr"/>
+      <c r="P238" s="20" t="inlineStr"/>
+      <c r="Q238" s="20" t="inlineStr"/>
+      <c r="R238" s="21" t="inlineStr"/>
+      <c r="S238" s="20" t="inlineStr"/>
+      <c r="T238" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U238" s="22" t="inlineStr">
+      <c r="U238" s="20" t="inlineStr">
         <is>
           <t>BOPP</t>
         </is>
       </c>
-      <c r="V238" s="22" t="inlineStr">
+      <c r="V238" s="20" t="inlineStr">
         <is>
           <t>Caroline, Jeanne</t>
         </is>
       </c>
-      <c r="W238" s="22" t="inlineStr">
+      <c r="W238" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X238" s="22" t="inlineStr">
+      <c r="X238" s="20" t="inlineStr">
         <is>
           <t>5 C Rue de la Fontaine</t>
         </is>
       </c>
-      <c r="Y238" s="23" t="inlineStr">
+      <c r="Y238" s="21" t="inlineStr">
         <is>
           <t>57645</t>
         </is>
       </c>
-      <c r="Z238" s="22" t="inlineStr">
+      <c r="Z238" s="20" t="inlineStr">
         <is>
           <t>Noisseville</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="22" t="inlineStr">
+      <c r="A239" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B239" s="23" t="inlineStr">
+      <c r="B239" s="21" t="inlineStr">
         <is>
           <t>888717808</t>
         </is>
       </c>
-      <c r="C239" s="23" t="inlineStr">
+      <c r="C239" s="21" t="inlineStr">
         <is>
           <t>88871780800016</t>
         </is>
       </c>
-      <c r="D239" s="22" t="inlineStr">
+      <c r="D239" s="20" t="inlineStr">
         <is>
           <t>NR4 - LE ROMARIN</t>
         </is>
       </c>
-      <c r="E239" s="22" t="inlineStr">
+      <c r="E239" s="20" t="inlineStr">
         <is>
           <t>NR4 - LE ROMARIN</t>
         </is>
       </c>
-      <c r="F239" s="22" t="inlineStr">
+      <c r="F239" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G239" s="22" t="inlineStr">
+      <c r="G239" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H239" s="22" t="inlineStr">
+      <c r="H239" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I239" s="22" t="inlineStr">
+      <c r="I239" s="20" t="inlineStr">
         <is>
           <t>10/08/2020</t>
         </is>
       </c>
-      <c r="J239" s="22" t="inlineStr">
+      <c r="J239" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K239" s="22" t="inlineStr">
+      <c r="K239" s="20" t="inlineStr">
         <is>
           <t>18 RUE DES AUGUSTINS</t>
         </is>
       </c>
-      <c r="L239" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M239" s="22" t="inlineStr">
+      <c r="L239" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M239" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N239" s="22" t="inlineStr">
+      <c r="N239" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O239" s="22" t="n">
-        <v>949499</v>
-      </c>
-      <c r="P239" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q239" s="22" t="inlineStr"/>
-      <c r="R239" s="23" t="inlineStr"/>
-      <c r="S239" s="22" t="inlineStr"/>
-      <c r="T239" s="22" t="inlineStr">
+      <c r="O239" s="20" t="inlineStr">
+        <is>
+          <t>949499</t>
+        </is>
+      </c>
+      <c r="P239" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q239" s="20" t="inlineStr"/>
+      <c r="R239" s="21" t="inlineStr"/>
+      <c r="S239" s="20" t="inlineStr"/>
+      <c r="T239" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U239" s="22" t="inlineStr">
+      <c r="U239" s="20" t="inlineStr">
         <is>
           <t>RAPENNE</t>
         </is>
       </c>
-      <c r="V239" s="22" t="inlineStr">
+      <c r="V239" s="20" t="inlineStr">
         <is>
           <t>Nicolas, Juste, Gilbert</t>
         </is>
       </c>
-      <c r="W239" s="22" t="inlineStr">
+      <c r="W239" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X239" s="22" t="inlineStr">
+      <c r="X239" s="20" t="inlineStr">
         <is>
           <t>75 Clos des Acacias</t>
         </is>
       </c>
-      <c r="Y239" s="23" t="inlineStr">
+      <c r="Y239" s="21" t="inlineStr">
         <is>
           <t>57157</t>
         </is>
       </c>
-      <c r="Z239" s="22" t="inlineStr">
+      <c r="Z239" s="20" t="inlineStr">
         <is>
           <t>Marly</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="22" t="inlineStr">
+      <c r="A240" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B240" s="23" t="inlineStr">
+      <c r="B240" s="21" t="inlineStr">
         <is>
           <t>807525134</t>
         </is>
       </c>
-      <c r="C240" s="23" t="inlineStr">
+      <c r="C240" s="21" t="inlineStr">
         <is>
           <t>80752513400019</t>
         </is>
       </c>
-      <c r="D240" s="22" t="inlineStr">
+      <c r="D240" s="20" t="inlineStr">
         <is>
           <t>LE K</t>
         </is>
       </c>
-      <c r="E240" s="22" t="inlineStr">
+      <c r="E240" s="20" t="inlineStr">
         <is>
           <t>LE K</t>
         </is>
       </c>
-      <c r="F240" s="22" t="inlineStr">
+      <c r="F240" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G240" s="22" t="inlineStr">
+      <c r="G240" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H240" s="22" t="inlineStr">
+      <c r="H240" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I240" s="22" t="inlineStr">
+      <c r="I240" s="20" t="inlineStr">
         <is>
           <t>15/10/2014</t>
         </is>
       </c>
-      <c r="J240" s="22" t="inlineStr">
+      <c r="J240" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K240" s="22" t="inlineStr">
+      <c r="K240" s="20" t="inlineStr">
         <is>
           <t>11 PLACE DE CHAMBRE</t>
         </is>
       </c>
-      <c r="L240" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M240" s="22" t="inlineStr">
+      <c r="L240" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M240" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N240" s="22" t="inlineStr">
+      <c r="N240" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O240" s="22" t="inlineStr"/>
-      <c r="P240" s="22" t="inlineStr"/>
-      <c r="Q240" s="22" t="inlineStr"/>
-      <c r="R240" s="23" t="inlineStr"/>
-      <c r="S240" s="22" t="inlineStr"/>
-      <c r="T240" s="22" t="inlineStr">
+      <c r="O240" s="20" t="inlineStr"/>
+      <c r="P240" s="20" t="inlineStr"/>
+      <c r="Q240" s="20" t="inlineStr"/>
+      <c r="R240" s="21" t="inlineStr"/>
+      <c r="S240" s="20" t="inlineStr"/>
+      <c r="T240" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U240" s="22" t="inlineStr">
+      <c r="U240" s="20" t="inlineStr">
         <is>
           <t>ERAYDIN</t>
         </is>
       </c>
-      <c r="V240" s="22" t="inlineStr">
+      <c r="V240" s="20" t="inlineStr">
         <is>
           <t>Kemal</t>
         </is>
       </c>
-      <c r="W240" s="22" t="inlineStr">
+      <c r="W240" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X240" s="22" t="inlineStr">
+      <c r="X240" s="20" t="inlineStr">
         <is>
           <t>14 rue Le Goullon</t>
         </is>
       </c>
-      <c r="Y240" s="23" t="inlineStr">
+      <c r="Y240" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z240" s="22" t="inlineStr">
+      <c r="Z240" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="22" t="inlineStr">
+      <c r="A241" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B241" s="23" t="inlineStr">
+      <c r="B241" s="21" t="inlineStr">
         <is>
           <t>108820531</t>
         </is>
       </c>
-      <c r="C241" s="23" t="inlineStr">
+      <c r="C241" s="21" t="inlineStr">
         <is>
           <t>10882053100011</t>
         </is>
       </c>
-      <c r="D241" s="22" t="inlineStr">
+      <c r="D241" s="20" t="inlineStr">
         <is>
           <t>KAZUKO METZ</t>
         </is>
       </c>
-      <c r="E241" s="22" t="inlineStr">
+      <c r="E241" s="20" t="inlineStr">
         <is>
           <t>KAZUKO METZ</t>
         </is>
       </c>
-      <c r="F241" s="22" t="inlineStr">
+      <c r="F241" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G241" s="22" t="inlineStr">
+      <c r="G241" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H241" s="22" t="inlineStr">
+      <c r="H241" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I241" s="22" t="inlineStr">
+      <c r="I241" s="20" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="J241" s="22" t="inlineStr">
+      <c r="J241" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K241" s="22" t="inlineStr">
+      <c r="K241" s="20" t="inlineStr">
         <is>
           <t>86 EN FOURNIRUE</t>
         </is>
       </c>
-      <c r="L241" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M241" s="22" t="inlineStr">
+      <c r="L241" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M241" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N241" s="22" t="inlineStr">
+      <c r="N241" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O241" s="22" t="inlineStr"/>
-      <c r="P241" s="22" t="inlineStr"/>
-      <c r="Q241" s="22" t="inlineStr"/>
-      <c r="R241" s="23" t="inlineStr"/>
-      <c r="S241" s="22" t="inlineStr"/>
-      <c r="T241" s="22" t="inlineStr">
+      <c r="O241" s="20" t="inlineStr"/>
+      <c r="P241" s="20" t="inlineStr"/>
+      <c r="Q241" s="20" t="inlineStr"/>
+      <c r="R241" s="21" t="inlineStr"/>
+      <c r="S241" s="20" t="inlineStr"/>
+      <c r="T241" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U241" s="22" t="inlineStr">
+      <c r="U241" s="20" t="inlineStr">
         <is>
           <t>YE</t>
         </is>
       </c>
-      <c r="V241" s="22" t="inlineStr">
+      <c r="V241" s="20" t="inlineStr">
         <is>
           <t>Jacques, Tony</t>
         </is>
       </c>
-      <c r="W241" s="22" t="inlineStr">
+      <c r="W241" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X241" s="22" t="inlineStr"/>
-      <c r="Y241" s="23" t="inlineStr">
+      <c r="X241" s="20" t="inlineStr"/>
+      <c r="Y241" s="21" t="inlineStr">
         <is>
           <t>95150</t>
         </is>
       </c>
-      <c r="Z241" s="22" t="inlineStr">
+      <c r="Z241" s="20" t="inlineStr">
         <is>
           <t>Taverny</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="22" t="inlineStr">
+      <c r="A242" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B242" s="23" t="inlineStr">
+      <c r="B242" s="21" t="inlineStr">
         <is>
           <t>994079499</t>
         </is>
       </c>
-      <c r="C242" s="23" t="inlineStr">
+      <c r="C242" s="21" t="inlineStr">
         <is>
           <t>99407949900012</t>
         </is>
       </c>
-      <c r="D242" s="22" t="inlineStr">
+      <c r="D242" s="20" t="inlineStr">
         <is>
           <t>OPPA EONNI</t>
         </is>
       </c>
-      <c r="E242" s="22" t="inlineStr">
+      <c r="E242" s="20" t="inlineStr">
         <is>
           <t>OPPA EONNI</t>
         </is>
       </c>
-      <c r="F242" s="22" t="inlineStr">
+      <c r="F242" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G242" s="22" t="inlineStr">
+      <c r="G242" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H242" s="22" t="inlineStr">
+      <c r="H242" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I242" s="22" t="inlineStr">
+      <c r="I242" s="20" t="inlineStr">
         <is>
           <t>18/09/2025</t>
         </is>
       </c>
-      <c r="J242" s="22" t="inlineStr">
+      <c r="J242" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K242" s="22" t="inlineStr">
+      <c r="K242" s="20" t="inlineStr">
         <is>
           <t>3 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="L242" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M242" s="22" t="inlineStr">
+      <c r="L242" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M242" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N242" s="22" t="inlineStr">
+      <c r="N242" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O242" s="22" t="inlineStr"/>
-      <c r="P242" s="22" t="inlineStr"/>
-      <c r="Q242" s="22" t="inlineStr"/>
-      <c r="R242" s="23" t="inlineStr"/>
-      <c r="S242" s="22" t="inlineStr"/>
-      <c r="T242" s="22" t="inlineStr">
+      <c r="O242" s="20" t="inlineStr"/>
+      <c r="P242" s="20" t="inlineStr"/>
+      <c r="Q242" s="20" t="inlineStr"/>
+      <c r="R242" s="21" t="inlineStr"/>
+      <c r="S242" s="20" t="inlineStr"/>
+      <c r="T242" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U242" s="22" t="inlineStr">
+      <c r="U242" s="20" t="inlineStr">
         <is>
           <t>REN</t>
         </is>
       </c>
-      <c r="V242" s="22" t="inlineStr">
+      <c r="V242" s="20" t="inlineStr">
         <is>
           <t>Shengjie</t>
         </is>
       </c>
-      <c r="W242" s="22" t="inlineStr">
+      <c r="W242" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X242" s="22" t="inlineStr">
+      <c r="X242" s="20" t="inlineStr">
         <is>
           <t>3, rue de la Commanderie</t>
         </is>
       </c>
-      <c r="Y242" s="23" t="inlineStr">
+      <c r="Y242" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z242" s="22" t="inlineStr">
+      <c r="Z242" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="22" t="inlineStr">
+      <c r="A243" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B243" s="23" t="inlineStr">
+      <c r="B243" s="21" t="inlineStr">
         <is>
           <t>912810769</t>
         </is>
       </c>
-      <c r="C243" s="23" t="inlineStr">
+      <c r="C243" s="21" t="inlineStr">
         <is>
           <t>91281076900022</t>
         </is>
       </c>
-      <c r="D243" s="22" t="inlineStr">
+      <c r="D243" s="20" t="inlineStr">
         <is>
           <t>AJFM SAINT JACQUES</t>
         </is>
       </c>
-      <c r="E243" s="22" t="inlineStr">
+      <c r="E243" s="20" t="inlineStr">
         <is>
           <t>AJFM SAINT JACQUES</t>
         </is>
       </c>
-      <c r="F243" s="22" t="inlineStr">
+      <c r="F243" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G243" s="22" t="inlineStr">
+      <c r="G243" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H243" s="22" t="inlineStr">
+      <c r="H243" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I243" s="22" t="inlineStr">
+      <c r="I243" s="20" t="inlineStr">
         <is>
           <t>25/04/2022</t>
         </is>
       </c>
-      <c r="J243" s="22" t="inlineStr">
+      <c r="J243" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K243" s="22" t="inlineStr">
+      <c r="K243" s="20" t="inlineStr">
         <is>
           <t>16 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="L243" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M243" s="22" t="inlineStr">
+      <c r="L243" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M243" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N243" s="22" t="inlineStr">
+      <c r="N243" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O243" s="22" t="n">
-        <v>654239</v>
-      </c>
-      <c r="P243" s="22" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q243" s="22" t="inlineStr"/>
-      <c r="R243" s="23" t="inlineStr"/>
-      <c r="S243" s="22" t="inlineStr"/>
-      <c r="T243" s="22" t="inlineStr">
+      <c r="O243" s="20" t="inlineStr">
+        <is>
+          <t>654239</t>
+        </is>
+      </c>
+      <c r="P243" s="20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q243" s="20" t="inlineStr"/>
+      <c r="R243" s="21" t="inlineStr"/>
+      <c r="S243" s="20" t="inlineStr"/>
+      <c r="T243" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U243" s="22" t="inlineStr">
+      <c r="U243" s="20" t="inlineStr">
         <is>
           <t>CHR INVEST</t>
         </is>
       </c>
-      <c r="V243" s="22" t="inlineStr"/>
-      <c r="W243" s="22" t="inlineStr">
+      <c r="V243" s="20" t="inlineStr"/>
+      <c r="W243" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X243" s="22" t="inlineStr">
+      <c r="X243" s="20" t="inlineStr">
         <is>
           <t>41 Place de la Carrière</t>
         </is>
       </c>
-      <c r="Y243" s="23" t="inlineStr">
+      <c r="Y243" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="Z243" s="22" t="inlineStr">
+      <c r="Z243" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="22" t="inlineStr">
+      <c r="A244" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B244" s="23" t="inlineStr">
+      <c r="B244" s="21" t="inlineStr">
         <is>
           <t>927730846</t>
         </is>
       </c>
-      <c r="C244" s="23" t="inlineStr">
+      <c r="C244" s="21" t="inlineStr">
         <is>
           <t>92773084600015</t>
         </is>
       </c>
-      <c r="D244" s="22" t="inlineStr">
+      <c r="D244" s="20" t="inlineStr">
         <is>
           <t>C.R.M C.R METZ</t>
         </is>
       </c>
-      <c r="E244" s="22" t="inlineStr">
+      <c r="E244" s="20" t="inlineStr">
         <is>
           <t>C.R METZ</t>
         </is>
       </c>
-      <c r="F244" s="22" t="inlineStr">
+      <c r="F244" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G244" s="22" t="inlineStr">
+      <c r="G244" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H244" s="22" t="inlineStr">
+      <c r="H244" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I244" s="22" t="inlineStr">
+      <c r="I244" s="20" t="inlineStr">
         <is>
           <t>15/04/2024</t>
         </is>
       </c>
-      <c r="J244" s="22" t="inlineStr">
+      <c r="J244" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K244" s="22" t="inlineStr">
+      <c r="K244" s="20" t="inlineStr">
         <is>
           <t>1 PARVIS DES DROITS DE L'HOMME</t>
         </is>
       </c>
-      <c r="L244" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M244" s="22" t="inlineStr">
+      <c r="L244" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M244" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N244" s="22" t="inlineStr">
+      <c r="N244" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O244" s="22" t="inlineStr"/>
-      <c r="P244" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q244" s="22" t="inlineStr"/>
-      <c r="R244" s="23" t="inlineStr"/>
-      <c r="S244" s="22" t="inlineStr"/>
-      <c r="T244" s="22" t="inlineStr">
+      <c r="O244" s="20" t="inlineStr"/>
+      <c r="P244" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q244" s="20" t="inlineStr"/>
+      <c r="R244" s="21" t="inlineStr"/>
+      <c r="S244" s="20" t="inlineStr"/>
+      <c r="T244" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U244" s="22" t="inlineStr">
+      <c r="U244" s="20" t="inlineStr">
         <is>
           <t>C.R. RESTAURANT</t>
         </is>
       </c>
-      <c r="V244" s="22" t="inlineStr"/>
-      <c r="W244" s="22" t="inlineStr">
+      <c r="V244" s="20" t="inlineStr"/>
+      <c r="W244" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X244" s="22" t="inlineStr">
+      <c r="X244" s="20" t="inlineStr">
         <is>
           <t>3 RUE Sainte Catherine</t>
         </is>
       </c>
-      <c r="Y244" s="23" t="inlineStr">
+      <c r="Y244" s="21" t="inlineStr">
         <is>
           <t>54000</t>
         </is>
       </c>
-      <c r="Z244" s="22" t="inlineStr">
+      <c r="Z244" s="20" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="22" t="inlineStr">
+      <c r="A245" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B245" s="23" t="inlineStr">
+      <c r="B245" s="21" t="inlineStr">
         <is>
           <t>789923539</t>
         </is>
       </c>
-      <c r="C245" s="23" t="inlineStr">
+      <c r="C245" s="21" t="inlineStr">
         <is>
           <t>78992353900017</t>
         </is>
       </c>
-      <c r="D245" s="22" t="inlineStr">
+      <c r="D245" s="20" t="inlineStr">
         <is>
           <t>BENAISSA NABILL</t>
         </is>
       </c>
-      <c r="E245" s="22" t="inlineStr">
+      <c r="E245" s="20" t="inlineStr">
         <is>
           <t>BENAISSA NABILL</t>
         </is>
       </c>
-      <c r="F245" s="22" t="inlineStr">
+      <c r="F245" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G245" s="22" t="inlineStr">
+      <c r="G245" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H245" s="22" t="inlineStr">
+      <c r="H245" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I245" s="22" t="inlineStr">
+      <c r="I245" s="20" t="inlineStr">
         <is>
           <t>10/12/2012</t>
         </is>
       </c>
-      <c r="J245" s="22" t="inlineStr">
+      <c r="J245" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K245" s="22" t="inlineStr">
+      <c r="K245" s="20" t="inlineStr">
         <is>
           <t>26 RUE DES JARDINS</t>
         </is>
       </c>
-      <c r="L245" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M245" s="22" t="inlineStr">
+      <c r="L245" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M245" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N245" s="22" t="inlineStr">
+      <c r="N245" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O245" s="22" t="inlineStr"/>
-      <c r="P245" s="22" t="inlineStr"/>
-      <c r="Q245" s="22" t="inlineStr"/>
-      <c r="R245" s="23" t="inlineStr"/>
-      <c r="S245" s="22" t="inlineStr"/>
-      <c r="T245" s="22" t="inlineStr">
+      <c r="O245" s="20" t="inlineStr"/>
+      <c r="P245" s="20" t="inlineStr"/>
+      <c r="Q245" s="20" t="inlineStr"/>
+      <c r="R245" s="21" t="inlineStr"/>
+      <c r="S245" s="20" t="inlineStr"/>
+      <c r="T245" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U245" s="22" t="inlineStr">
+      <c r="U245" s="20" t="inlineStr">
         <is>
           <t>BENAISSA</t>
         </is>
       </c>
-      <c r="V245" s="22" t="inlineStr">
+      <c r="V245" s="20" t="inlineStr">
         <is>
           <t>Nabill</t>
         </is>
       </c>
-      <c r="W245" s="22" t="inlineStr">
+      <c r="W245" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X245" s="22" t="inlineStr"/>
-      <c r="Y245" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z245" s="22" t="inlineStr">
+      <c r="X245" s="20" t="inlineStr"/>
+      <c r="Y245" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z245" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="22" t="inlineStr">
+      <c r="A246" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B246" s="23" t="inlineStr">
+      <c r="B246" s="21" t="inlineStr">
         <is>
           <t>822300059</t>
         </is>
       </c>
-      <c r="C246" s="23" t="inlineStr">
+      <c r="C246" s="21" t="inlineStr">
         <is>
           <t>82230005900026</t>
         </is>
       </c>
-      <c r="D246" s="22" t="inlineStr">
+      <c r="D246" s="20" t="inlineStr">
         <is>
           <t>O'MEZZA</t>
         </is>
       </c>
-      <c r="E246" s="22" t="inlineStr">
+      <c r="E246" s="20" t="inlineStr">
         <is>
           <t>O'MEZZA</t>
         </is>
       </c>
-      <c r="F246" s="22" t="inlineStr">
+      <c r="F246" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G246" s="22" t="inlineStr">
+      <c r="G246" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H246" s="22" t="inlineStr">
+      <c r="H246" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I246" s="22" t="inlineStr">
+      <c r="I246" s="20" t="inlineStr">
         <is>
           <t>01/09/2016</t>
         </is>
       </c>
-      <c r="J246" s="22" t="inlineStr">
+      <c r="J246" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K246" s="22" t="inlineStr">
+      <c r="K246" s="20" t="inlineStr">
         <is>
           <t>1 RUE BELLE-ISLE</t>
         </is>
       </c>
-      <c r="L246" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M246" s="22" t="inlineStr">
+      <c r="L246" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M246" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N246" s="22" t="inlineStr">
+      <c r="N246" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O246" s="22" t="inlineStr"/>
-      <c r="P246" s="22" t="inlineStr"/>
-      <c r="Q246" s="22" t="inlineStr"/>
-      <c r="R246" s="23" t="inlineStr"/>
-      <c r="S246" s="22" t="inlineStr"/>
-      <c r="T246" s="22" t="inlineStr">
+      <c r="O246" s="20" t="inlineStr"/>
+      <c r="P246" s="20" t="inlineStr"/>
+      <c r="Q246" s="20" t="inlineStr"/>
+      <c r="R246" s="21" t="inlineStr"/>
+      <c r="S246" s="20" t="inlineStr"/>
+      <c r="T246" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U246" s="22" t="inlineStr">
+      <c r="U246" s="20" t="inlineStr">
         <is>
           <t>SABRA</t>
         </is>
       </c>
-      <c r="V246" s="22" t="inlineStr">
+      <c r="V246" s="20" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="W246" s="22" t="inlineStr">
+      <c r="W246" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X246" s="22" t="inlineStr">
+      <c r="X246" s="20" t="inlineStr">
         <is>
           <t>7 rue de la Haye</t>
         </is>
       </c>
-      <c r="Y246" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z246" s="22" t="inlineStr">
+      <c r="Y246" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z246" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="22" t="inlineStr">
+      <c r="A247" s="20" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B247" s="23" t="inlineStr">
+      <c r="B247" s="21" t="inlineStr">
         <is>
           <t>889062568</t>
         </is>
       </c>
-      <c r="C247" s="23" t="inlineStr">
+      <c r="C247" s="21" t="inlineStr">
         <is>
           <t>88906256800015</t>
         </is>
       </c>
-      <c r="D247" s="22" t="inlineStr">
+      <c r="D247" s="20" t="inlineStr">
         <is>
           <t>FAYER &amp; CO</t>
         </is>
       </c>
-      <c r="E247" s="22" t="inlineStr">
+      <c r="E247" s="20" t="inlineStr">
         <is>
           <t>FAYER &amp; CO</t>
         </is>
       </c>
-      <c r="F247" s="22" t="inlineStr">
+      <c r="F247" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G247" s="22" t="inlineStr">
+      <c r="G247" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H247" s="22" t="inlineStr">
+      <c r="H247" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I247" s="22" t="inlineStr">
+      <c r="I247" s="20" t="inlineStr">
         <is>
           <t>01/09/2020</t>
         </is>
       </c>
-      <c r="J247" s="22" t="inlineStr">
+      <c r="J247" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K247" s="22" t="inlineStr">
+      <c r="K247" s="20" t="inlineStr">
         <is>
           <t>27 RUE DE LA PRINCERIE</t>
         </is>
       </c>
-      <c r="L247" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M247" s="22" t="inlineStr">
+      <c r="L247" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M247" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N247" s="22" t="inlineStr">
+      <c r="N247" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O247" s="22" t="inlineStr"/>
-      <c r="P247" s="22" t="inlineStr"/>
-      <c r="Q247" s="22" t="inlineStr"/>
-      <c r="R247" s="23" t="inlineStr"/>
-      <c r="S247" s="22" t="inlineStr"/>
-      <c r="T247" s="22" t="inlineStr">
+      <c r="O247" s="20" t="inlineStr"/>
+      <c r="P247" s="20" t="inlineStr"/>
+      <c r="Q247" s="20" t="inlineStr"/>
+      <c r="R247" s="21" t="inlineStr"/>
+      <c r="S247" s="20" t="inlineStr"/>
+      <c r="T247" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U247" s="22" t="inlineStr">
+      <c r="U247" s="20" t="inlineStr">
         <is>
           <t>FAYER</t>
         </is>
       </c>
-      <c r="V247" s="22" t="inlineStr">
+      <c r="V247" s="20" t="inlineStr">
         <is>
           <t>Emmanuel, Renan</t>
         </is>
       </c>
-      <c r="W247" s="22" t="inlineStr">
+      <c r="W247" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X247" s="22" t="inlineStr">
+      <c r="X247" s="20" t="inlineStr">
         <is>
           <t>27 Rue de la Princerie</t>
         </is>
       </c>
-      <c r="Y247" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z247" s="22" t="inlineStr">
+      <c r="Y247" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z247" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B248" s="23" t="inlineStr">
+        <is>
+          <t>993782200</t>
+        </is>
+      </c>
+      <c r="C248" s="23" t="inlineStr">
+        <is>
+          <t>99378220000014</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="inlineStr">
+        <is>
+          <t>SLMUSE</t>
+        </is>
+      </c>
+      <c r="E248" s="22" t="inlineStr">
+        <is>
+          <t>SLMUSE</t>
+        </is>
+      </c>
+      <c r="F248" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G248" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H248" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I248" s="22" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="J248" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K248" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRE COMMERCIAL MUSE </t>
+        </is>
+      </c>
+      <c r="L248" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M248" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N248" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O248" s="22" t="inlineStr"/>
+      <c r="P248" s="22" t="inlineStr"/>
+      <c r="Q248" s="22" t="inlineStr"/>
+      <c r="R248" s="23" t="inlineStr"/>
+      <c r="S248" s="22" t="inlineStr"/>
+      <c r="T248" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U248" s="22" t="inlineStr">
+        <is>
+          <t>SL RESTAURATION</t>
+        </is>
+      </c>
+      <c r="V248" s="22" t="inlineStr"/>
+      <c r="W248" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X248" s="22" t="inlineStr">
+        <is>
+          <t>28 RUE Principale</t>
+        </is>
+      </c>
+      <c r="Y248" s="23" t="inlineStr">
+        <is>
+          <t>57590</t>
+        </is>
+      </c>
+      <c r="Z248" s="22" t="inlineStr">
+        <is>
+          <t>Jallaucourt</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B249" s="23" t="inlineStr">
+        <is>
+          <t>822790689</t>
+        </is>
+      </c>
+      <c r="C249" s="23" t="inlineStr">
+        <is>
+          <t>82279068900019</t>
+        </is>
+      </c>
+      <c r="D249" s="22" t="inlineStr">
+        <is>
+          <t>LA MAISON DU BURGER</t>
+        </is>
+      </c>
+      <c r="E249" s="22" t="inlineStr">
+        <is>
+          <t>LA MAISON DU BURGER</t>
+        </is>
+      </c>
+      <c r="F249" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G249" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H249" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I249" s="22" t="inlineStr">
+        <is>
+          <t>01/10/2016</t>
+        </is>
+      </c>
+      <c r="J249" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K249" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE CLOVIS</t>
+        </is>
+      </c>
+      <c r="L249" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M249" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N249" s="22" t="inlineStr">
+        <is>
+          <t>Entre 1 et 2 salariés</t>
+        </is>
+      </c>
+      <c r="O249" s="22" t="inlineStr"/>
+      <c r="P249" s="22" t="inlineStr"/>
+      <c r="Q249" s="22" t="inlineStr"/>
+      <c r="R249" s="23" t="inlineStr"/>
+      <c r="S249" s="22" t="inlineStr"/>
+      <c r="T249" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U249" s="22" t="inlineStr">
+        <is>
+          <t>JOLIOT</t>
+        </is>
+      </c>
+      <c r="V249" s="22" t="inlineStr">
+        <is>
+          <t>Axel</t>
+        </is>
+      </c>
+      <c r="W249" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X249" s="22" t="inlineStr">
+        <is>
+          <t>68 avenue Alexandre Dreux</t>
+        </is>
+      </c>
+      <c r="Y249" s="23" t="inlineStr">
+        <is>
+          <t>54910</t>
+        </is>
+      </c>
+      <c r="Z249" s="22" t="inlineStr">
+        <is>
+          <t>Valleroy</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B250" s="23" t="inlineStr">
+        <is>
+          <t>930096938</t>
+        </is>
+      </c>
+      <c r="C250" s="23" t="inlineStr">
+        <is>
+          <t>93009693800012</t>
+        </is>
+      </c>
+      <c r="D250" s="22" t="inlineStr">
+        <is>
+          <t>AU FIL DE VOUS</t>
+        </is>
+      </c>
+      <c r="E250" s="22" t="inlineStr">
+        <is>
+          <t>AU FIL DE VOUS</t>
+        </is>
+      </c>
+      <c r="F250" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G250" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H250" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I250" s="22" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="J250" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K250" s="22" t="inlineStr">
+        <is>
+          <t>34 RUE DE PONT-A-MOUSSON</t>
+        </is>
+      </c>
+      <c r="L250" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M250" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N250" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O250" s="22" t="inlineStr"/>
+      <c r="P250" s="22" t="inlineStr"/>
+      <c r="Q250" s="22" t="inlineStr"/>
+      <c r="R250" s="23" t="inlineStr"/>
+      <c r="S250" s="22" t="inlineStr"/>
+      <c r="T250" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U250" s="22" t="inlineStr">
+        <is>
+          <t>THOMAS</t>
+        </is>
+      </c>
+      <c r="V250" s="22" t="inlineStr">
+        <is>
+          <t>Typhaine</t>
+        </is>
+      </c>
+      <c r="W250" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X250" s="22" t="inlineStr">
+        <is>
+          <t>allée saint symphorien péniche octopus</t>
+        </is>
+      </c>
+      <c r="Y250" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z250" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B251" s="23" t="inlineStr">
+        <is>
+          <t>505253534</t>
+        </is>
+      </c>
+      <c r="C251" s="23" t="inlineStr">
+        <is>
+          <t>50525353400018</t>
+        </is>
+      </c>
+      <c r="D251" s="22" t="inlineStr">
+        <is>
+          <t>BOLIFAB</t>
+        </is>
+      </c>
+      <c r="E251" s="22" t="inlineStr">
+        <is>
+          <t>BOLIFAB</t>
+        </is>
+      </c>
+      <c r="F251" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G251" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H251" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I251" s="22" t="inlineStr">
+        <is>
+          <t>21/06/2008</t>
+        </is>
+      </c>
+      <c r="J251" s="22" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K251" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE VICTOR JACOB</t>
+        </is>
+      </c>
+      <c r="L251" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M251" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N251" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O251" s="22" t="inlineStr"/>
+      <c r="P251" s="22" t="inlineStr"/>
+      <c r="Q251" s="22" t="inlineStr"/>
+      <c r="R251" s="23" t="inlineStr"/>
+      <c r="S251" s="22" t="inlineStr"/>
+      <c r="T251" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U251" s="22" t="inlineStr">
+        <is>
+          <t>Fabian</t>
+        </is>
+      </c>
+      <c r="V251" s="22" t="inlineStr">
+        <is>
+          <t>Ludovic</t>
+        </is>
+      </c>
+      <c r="W251" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X251" s="22" t="inlineStr"/>
+      <c r="Y251" s="23" t="inlineStr">
+        <is>
+          <t>57100</t>
+        </is>
+      </c>
+      <c r="Z251" s="22" t="inlineStr">
+        <is>
+          <t>MANOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B252" s="23" t="inlineStr">
+        <is>
+          <t>828631572</t>
+        </is>
+      </c>
+      <c r="C252" s="23" t="inlineStr">
+        <is>
+          <t>82863157200017</t>
+        </is>
+      </c>
+      <c r="D252" s="22" t="inlineStr">
+        <is>
+          <t>SABLE D'OR</t>
+        </is>
+      </c>
+      <c r="E252" s="22" t="inlineStr">
+        <is>
+          <t>SABLE D'OR</t>
+        </is>
+      </c>
+      <c r="F252" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G252" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H252" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I252" s="22" t="inlineStr">
+        <is>
+          <t>23/03/2017</t>
+        </is>
+      </c>
+      <c r="J252" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K252" s="22" t="inlineStr">
+        <is>
+          <t>80 RUE SAINT-PIERRE</t>
+        </is>
+      </c>
+      <c r="L252" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M252" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N252" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O252" s="22" t="inlineStr"/>
+      <c r="P252" s="22" t="inlineStr"/>
+      <c r="Q252" s="22" t="inlineStr"/>
+      <c r="R252" s="23" t="inlineStr"/>
+      <c r="S252" s="22" t="inlineStr"/>
+      <c r="T252" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U252" s="22" t="inlineStr">
+        <is>
+          <t>TENANI</t>
+        </is>
+      </c>
+      <c r="V252" s="22" t="inlineStr">
+        <is>
+          <t>Rachid</t>
+        </is>
+      </c>
+      <c r="W252" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X252" s="22" t="inlineStr">
+        <is>
+          <t>18 rue Gabriel Pierné</t>
+        </is>
+      </c>
+      <c r="Y252" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z252" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B253" s="23" t="inlineStr">
+        <is>
+          <t>882202997</t>
+        </is>
+      </c>
+      <c r="C253" s="23" t="inlineStr">
+        <is>
+          <t>88220299700012</t>
+        </is>
+      </c>
+      <c r="D253" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ FETHI</t>
+        </is>
+      </c>
+      <c r="E253" s="22" t="inlineStr">
+        <is>
+          <t>CHEZ FETHI</t>
+        </is>
+      </c>
+      <c r="F253" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G253" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H253" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I253" s="22" t="inlineStr">
+        <is>
+          <t>02/03/2020</t>
+        </is>
+      </c>
+      <c r="J253" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K253" s="22" t="inlineStr">
+        <is>
+          <t>22 RUE DES ALLEMANDS</t>
+        </is>
+      </c>
+      <c r="L253" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M253" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N253" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O253" s="22" t="inlineStr"/>
+      <c r="P253" s="22" t="inlineStr"/>
+      <c r="Q253" s="22" t="inlineStr"/>
+      <c r="R253" s="23" t="inlineStr"/>
+      <c r="S253" s="22" t="inlineStr"/>
+      <c r="T253" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U253" s="22" t="inlineStr">
+        <is>
+          <t>FARHATI</t>
+        </is>
+      </c>
+      <c r="V253" s="22" t="inlineStr">
+        <is>
+          <t>Ibtissem</t>
+        </is>
+      </c>
+      <c r="W253" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X253" s="22" t="inlineStr">
+        <is>
+          <t>44 rue jules guichard</t>
+        </is>
+      </c>
+      <c r="Y253" s="23" t="inlineStr">
+        <is>
+          <t>51100</t>
+        </is>
+      </c>
+      <c r="Z253" s="22" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B254" s="23" t="inlineStr">
+        <is>
+          <t>791123334</t>
+        </is>
+      </c>
+      <c r="C254" s="23" t="inlineStr">
+        <is>
+          <t>79112333400017</t>
+        </is>
+      </c>
+      <c r="D254" s="22" t="inlineStr">
+        <is>
+          <t>LE TROUBADOUR</t>
+        </is>
+      </c>
+      <c r="E254" s="22" t="inlineStr">
+        <is>
+          <t>LE TROUBADOUR</t>
+        </is>
+      </c>
+      <c r="F254" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G254" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H254" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I254" s="22" t="inlineStr">
+        <is>
+          <t>12/02/2013</t>
+        </is>
+      </c>
+      <c r="J254" s="22" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K254" s="22" t="inlineStr">
+        <is>
+          <t>32 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L254" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M254" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N254" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O254" s="22" t="inlineStr"/>
+      <c r="P254" s="22" t="inlineStr"/>
+      <c r="Q254" s="22" t="inlineStr"/>
+      <c r="R254" s="23" t="inlineStr"/>
+      <c r="S254" s="22" t="inlineStr"/>
+      <c r="T254" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U254" s="22" t="inlineStr">
+        <is>
+          <t>TRABAND</t>
+        </is>
+      </c>
+      <c r="V254" s="22" t="inlineStr">
+        <is>
+          <t>Nicolas, Gerard, Charles, Andre</t>
+        </is>
+      </c>
+      <c r="W254" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X254" s="22" t="inlineStr">
+        <is>
+          <t>56 Rue Haute Seille</t>
+        </is>
+      </c>
+      <c r="Y254" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z254" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B255" s="23" t="inlineStr">
+        <is>
+          <t>348030784</t>
+        </is>
+      </c>
+      <c r="C255" s="23" t="inlineStr">
+        <is>
+          <t>34803078400030</t>
+        </is>
+      </c>
+      <c r="D255" s="22" t="inlineStr">
+        <is>
+          <t>GORLINI Frederic</t>
+        </is>
+      </c>
+      <c r="E255" s="22" t="inlineStr">
+        <is>
+          <t>GORLINI Frederic</t>
+        </is>
+      </c>
+      <c r="F255" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G255" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H255" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I255" s="22" t="inlineStr">
+        <is>
+          <t>01/04/1988</t>
+        </is>
+      </c>
+      <c r="J255" s="22" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="K255" s="22" t="inlineStr">
+        <is>
+          <t>6 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L255" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M255" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N255" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O255" s="22" t="inlineStr"/>
+      <c r="P255" s="22" t="inlineStr"/>
+      <c r="Q255" s="22" t="inlineStr"/>
+      <c r="R255" s="23" t="inlineStr"/>
+      <c r="S255" s="22" t="inlineStr"/>
+      <c r="T255" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U255" s="22" t="inlineStr">
+        <is>
+          <t>GORLINI</t>
+        </is>
+      </c>
+      <c r="V255" s="22" t="inlineStr">
+        <is>
+          <t>Frederic, Jean, Pierre</t>
+        </is>
+      </c>
+      <c r="W255" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X255" s="22" t="inlineStr"/>
+      <c r="Y255" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z255" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B256" s="23" t="inlineStr">
+        <is>
+          <t>913114872</t>
+        </is>
+      </c>
+      <c r="C256" s="23" t="inlineStr">
+        <is>
+          <t>91311487200017</t>
+        </is>
+      </c>
+      <c r="D256" s="22" t="inlineStr">
+        <is>
+          <t>LA HAVANE</t>
+        </is>
+      </c>
+      <c r="E256" s="22" t="inlineStr">
+        <is>
+          <t>LA HAVANE</t>
+        </is>
+      </c>
+      <c r="F256" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G256" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H256" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I256" s="22" t="inlineStr">
+        <is>
+          <t>22/04/2022</t>
+        </is>
+      </c>
+      <c r="J256" s="22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K256" s="22" t="inlineStr">
+        <is>
+          <t>47 PLACE SAINT-LOUIS</t>
+        </is>
+      </c>
+      <c r="L256" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M256" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N256" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O256" s="22" t="inlineStr"/>
+      <c r="P256" s="22" t="inlineStr"/>
+      <c r="Q256" s="22" t="inlineStr"/>
+      <c r="R256" s="23" t="inlineStr"/>
+      <c r="S256" s="22" t="inlineStr"/>
+      <c r="T256" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U256" s="22" t="inlineStr">
+        <is>
+          <t>BUCKEL</t>
+        </is>
+      </c>
+      <c r="V256" s="22" t="inlineStr">
+        <is>
+          <t>Mickaël</t>
+        </is>
+      </c>
+      <c r="W256" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X256" s="22" t="inlineStr">
+        <is>
+          <t>7 Boulevard Robert Sernot</t>
+        </is>
+      </c>
+      <c r="Y256" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z256" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B257" s="23" t="inlineStr">
+        <is>
+          <t>790033898</t>
+        </is>
+      </c>
+      <c r="C257" s="23" t="inlineStr">
+        <is>
+          <t>79003389800012</t>
+        </is>
+      </c>
+      <c r="D257" s="22" t="inlineStr">
+        <is>
+          <t>LE BARATIN</t>
+        </is>
+      </c>
+      <c r="E257" s="22" t="inlineStr">
+        <is>
+          <t>LE BARATIN</t>
+        </is>
+      </c>
+      <c r="F257" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G257" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H257" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I257" s="22" t="inlineStr">
+        <is>
+          <t>29/11/2012</t>
+        </is>
+      </c>
+      <c r="J257" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K257" s="22" t="inlineStr">
+        <is>
+          <t>8 RUE DES PARMENTIERS</t>
+        </is>
+      </c>
+      <c r="L257" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M257" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N257" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O257" s="22" t="inlineStr"/>
+      <c r="P257" s="22" t="inlineStr"/>
+      <c r="Q257" s="22" t="inlineStr"/>
+      <c r="R257" s="23" t="inlineStr"/>
+      <c r="S257" s="22" t="inlineStr"/>
+      <c r="T257" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U257" s="22" t="inlineStr">
+        <is>
+          <t>SCHMALTZ</t>
+        </is>
+      </c>
+      <c r="V257" s="22" t="inlineStr">
+        <is>
+          <t>Cédric</t>
+        </is>
+      </c>
+      <c r="W257" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X257" s="22" t="inlineStr">
+        <is>
+          <t>3 rue Saint-Henry</t>
+        </is>
+      </c>
+      <c r="Y257" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z257" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B258" s="23" t="inlineStr">
+        <is>
+          <t>987739000</t>
+        </is>
+      </c>
+      <c r="C258" s="23" t="inlineStr">
+        <is>
+          <t>98773900000014</t>
+        </is>
+      </c>
+      <c r="D258" s="22" t="inlineStr">
+        <is>
+          <t>LE LABO</t>
+        </is>
+      </c>
+      <c r="E258" s="22" t="inlineStr">
+        <is>
+          <t>LE LABO</t>
+        </is>
+      </c>
+      <c r="F258" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G258" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H258" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I258" s="22" t="inlineStr">
+        <is>
+          <t>15/03/2024</t>
+        </is>
+      </c>
+      <c r="J258" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K258" s="22" t="inlineStr">
+        <is>
+          <t>16 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L258" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M258" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N258" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O258" s="22" t="inlineStr"/>
+      <c r="P258" s="22" t="inlineStr"/>
+      <c r="Q258" s="22" t="inlineStr"/>
+      <c r="R258" s="23" t="inlineStr"/>
+      <c r="S258" s="22" t="inlineStr"/>
+      <c r="T258" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U258" s="22" t="inlineStr">
+        <is>
+          <t>SCHLUCK</t>
+        </is>
+      </c>
+      <c r="V258" s="22" t="inlineStr">
+        <is>
+          <t>Herve</t>
+        </is>
+      </c>
+      <c r="W258" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X258" s="22" t="inlineStr">
+        <is>
+          <t>14 avenue André Malraux</t>
+        </is>
+      </c>
+      <c r="Y258" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z258" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B259" s="23" t="inlineStr">
+        <is>
+          <t>834775033</t>
+        </is>
+      </c>
+      <c r="C259" s="23" t="inlineStr">
+        <is>
+          <t>83477503300014</t>
+        </is>
+      </c>
+      <c r="D259" s="22" t="inlineStr">
+        <is>
+          <t>CAROLANS</t>
+        </is>
+      </c>
+      <c r="E259" s="22" t="inlineStr">
+        <is>
+          <t>CAROLANS</t>
+        </is>
+      </c>
+      <c r="F259" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G259" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H259" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I259" s="22" t="inlineStr">
+        <is>
+          <t>19/01/2018</t>
+        </is>
+      </c>
+      <c r="J259" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K259" s="22" t="inlineStr">
+        <is>
+          <t>20 B AVENUE ROBERT SCHUMAN</t>
+        </is>
+      </c>
+      <c r="L259" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M259" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N259" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O259" s="22" t="inlineStr"/>
+      <c r="P259" s="22" t="inlineStr"/>
+      <c r="Q259" s="22" t="inlineStr"/>
+      <c r="R259" s="23" t="inlineStr"/>
+      <c r="S259" s="22" t="inlineStr"/>
+      <c r="T259" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U259" s="22" t="inlineStr">
+        <is>
+          <t>LENNINGER</t>
+        </is>
+      </c>
+      <c r="V259" s="22" t="inlineStr">
+        <is>
+          <t>Sébastien</t>
+        </is>
+      </c>
+      <c r="W259" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X259" s="22" t="inlineStr">
+        <is>
+          <t>20 rue Jean Mermoz</t>
+        </is>
+      </c>
+      <c r="Y259" s="23" t="inlineStr">
+        <is>
+          <t>57970</t>
+        </is>
+      </c>
+      <c r="Z259" s="22" t="inlineStr">
+        <is>
+          <t>Yutz</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B260" s="23" t="inlineStr">
+        <is>
+          <t>334930047</t>
+        </is>
+      </c>
+      <c r="C260" s="23" t="inlineStr">
+        <is>
+          <t>33493004700033</t>
+        </is>
+      </c>
+      <c r="D260" s="22" t="inlineStr">
+        <is>
+          <t>BOGNER Henri</t>
+        </is>
+      </c>
+      <c r="E260" s="22" t="inlineStr">
+        <is>
+          <t>BOGNER Henri</t>
+        </is>
+      </c>
+      <c r="F260" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G260" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H260" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I260" s="22" t="inlineStr">
+        <is>
+          <t>01/01/1986</t>
+        </is>
+      </c>
+      <c r="J260" s="22" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="K260" s="22" t="inlineStr">
+        <is>
+          <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
+        </is>
+      </c>
+      <c r="L260" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M260" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N260" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O260" s="22" t="inlineStr"/>
+      <c r="P260" s="22" t="inlineStr"/>
+      <c r="Q260" s="22" t="inlineStr"/>
+      <c r="R260" s="23" t="inlineStr"/>
+      <c r="S260" s="22" t="inlineStr"/>
+      <c r="T260" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U260" s="22" t="inlineStr">
+        <is>
+          <t>BOGNER</t>
+        </is>
+      </c>
+      <c r="V260" s="22" t="inlineStr">
+        <is>
+          <t>Henri, Georges, Antoine</t>
+        </is>
+      </c>
+      <c r="W260" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X260" s="22" t="inlineStr"/>
+      <c r="Y260" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z260" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B261" s="23" t="inlineStr">
+        <is>
+          <t>405332453</t>
+        </is>
+      </c>
+      <c r="C261" s="23" t="inlineStr">
+        <is>
+          <t>40533245300019</t>
+        </is>
+      </c>
+      <c r="D261" s="22" t="inlineStr">
+        <is>
+          <t>LE SAINT JACQUES</t>
+        </is>
+      </c>
+      <c r="E261" s="22" t="inlineStr">
+        <is>
+          <t>LE SAINT JACQUES</t>
+        </is>
+      </c>
+      <c r="F261" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G261" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H261" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I261" s="22" t="inlineStr">
+        <is>
+          <t>16/04/1996</t>
+        </is>
+      </c>
+      <c r="J261" s="22" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="K261" s="22" t="inlineStr">
+        <is>
+          <t>10 PLACE SAINT-JACQUES</t>
+        </is>
+      </c>
+      <c r="L261" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M261" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N261" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O261" s="22" t="n">
+        <v>774898</v>
+      </c>
+      <c r="P261" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Q261" s="22" t="inlineStr"/>
+      <c r="R261" s="23" t="inlineStr"/>
+      <c r="S261" s="22" t="inlineStr"/>
+      <c r="T261" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U261" s="22" t="inlineStr">
+        <is>
+          <t>POTIER</t>
+        </is>
+      </c>
+      <c r="V261" s="22" t="inlineStr">
+        <is>
+          <t>Sylvain</t>
+        </is>
+      </c>
+      <c r="W261" s="22" t="inlineStr">
+        <is>
+          <t>Directeur général</t>
+        </is>
+      </c>
+      <c r="X261" s="22" t="inlineStr">
+        <is>
+          <t>13 rue de la louvière</t>
+        </is>
+      </c>
+      <c r="Y261" s="23" t="inlineStr">
+        <is>
+          <t>54330</t>
+        </is>
+      </c>
+      <c r="Z261" s="22" t="inlineStr">
+        <is>
+          <t>Hammeville</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B262" s="23" t="inlineStr">
+        <is>
+          <t>878788272</t>
+        </is>
+      </c>
+      <c r="C262" s="23" t="inlineStr">
+        <is>
+          <t>87878827200010</t>
+        </is>
+      </c>
+      <c r="D262" s="22" t="inlineStr">
+        <is>
+          <t>LA CATHEDRALE EXPLOITATION</t>
+        </is>
+      </c>
+      <c r="E262" s="22" t="inlineStr">
+        <is>
+          <t>LA CATHEDRALE EXPLOITATION</t>
+        </is>
+      </c>
+      <c r="F262" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G262" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H262" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I262" s="22" t="inlineStr">
+        <is>
+          <t>18/10/2019</t>
+        </is>
+      </c>
+      <c r="J262" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K262" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE BLONDEL</t>
+        </is>
+      </c>
+      <c r="L262" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M262" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N262" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O262" s="22" t="inlineStr"/>
+      <c r="P262" s="22" t="inlineStr"/>
+      <c r="Q262" s="22" t="inlineStr"/>
+      <c r="R262" s="23" t="inlineStr"/>
+      <c r="S262" s="22" t="inlineStr"/>
+      <c r="T262" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U262" s="22" t="inlineStr">
+        <is>
+          <t>ZIMMER</t>
+        </is>
+      </c>
+      <c r="V262" s="22" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="W262" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X262" s="22" t="inlineStr">
+        <is>
+          <t>50 rue aux Arènes</t>
+        </is>
+      </c>
+      <c r="Y262" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z262" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B263" s="23" t="inlineStr">
+        <is>
+          <t>879118438</t>
+        </is>
+      </c>
+      <c r="C263" s="23" t="inlineStr">
+        <is>
+          <t>87911843800016</t>
+        </is>
+      </c>
+      <c r="D263" s="22" t="inlineStr">
+        <is>
+          <t>LES BISTROTS DE METZ</t>
+        </is>
+      </c>
+      <c r="E263" s="22" t="inlineStr">
+        <is>
+          <t>LES BISTROTS DE METZ</t>
+        </is>
+      </c>
+      <c r="F263" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G263" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H263" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I263" s="22" t="inlineStr">
+        <is>
+          <t>16/10/2019</t>
+        </is>
+      </c>
+      <c r="J263" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K263" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE DU FAISAN</t>
+        </is>
+      </c>
+      <c r="L263" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M263" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N263" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O263" s="22" t="inlineStr"/>
+      <c r="P263" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q263" s="22" t="inlineStr"/>
+      <c r="R263" s="23" t="inlineStr"/>
+      <c r="S263" s="22" t="inlineStr"/>
+      <c r="T263" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U263" s="22" t="inlineStr">
+        <is>
+          <t>ZIMMER</t>
+        </is>
+      </c>
+      <c r="V263" s="22" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="W263" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X263" s="22" t="inlineStr">
+        <is>
+          <t>50 rue aux Arènes</t>
+        </is>
+      </c>
+      <c r="Y263" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z263" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B264" s="23" t="inlineStr">
+        <is>
+          <t>801372699</t>
+        </is>
+      </c>
+      <c r="C264" s="23" t="inlineStr">
+        <is>
+          <t>80137269900034</t>
+        </is>
+      </c>
+      <c r="D264" s="22" t="inlineStr">
+        <is>
+          <t>ANCY PIZZA EXPRESS</t>
+        </is>
+      </c>
+      <c r="E264" s="22" t="inlineStr">
+        <is>
+          <t>ANCY PIZZA EXPRESS</t>
+        </is>
+      </c>
+      <c r="F264" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G264" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H264" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I264" s="22" t="inlineStr">
+        <is>
+          <t>15/04/2014</t>
+        </is>
+      </c>
+      <c r="J264" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K264" s="22" t="inlineStr">
+        <is>
+          <t>31 RUE SAINT-PIERRE</t>
+        </is>
+      </c>
+      <c r="L264" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M264" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N264" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O264" s="22" t="inlineStr"/>
+      <c r="P264" s="22" t="inlineStr"/>
+      <c r="Q264" s="22" t="inlineStr"/>
+      <c r="R264" s="23" t="inlineStr"/>
+      <c r="S264" s="22" t="inlineStr"/>
+      <c r="T264" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U264" s="22" t="inlineStr">
+        <is>
+          <t>POISSENOT</t>
+        </is>
+      </c>
+      <c r="V264" s="22" t="inlineStr">
+        <is>
+          <t>Sébastien, Bernard</t>
+        </is>
+      </c>
+      <c r="W264" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X264" s="22" t="inlineStr">
+        <is>
+          <t>13 rue de la Barre</t>
+        </is>
+      </c>
+      <c r="Y264" s="23" t="inlineStr">
+        <is>
+          <t>57130</t>
+        </is>
+      </c>
+      <c r="Z264" s="22" t="inlineStr">
+        <is>
+          <t>Ancy-sur-Moselle</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B265" s="23" t="inlineStr">
+        <is>
+          <t>803552546</t>
+        </is>
+      </c>
+      <c r="C265" s="23" t="inlineStr">
+        <is>
+          <t>80355254600019</t>
+        </is>
+      </c>
+      <c r="D265" s="22" t="inlineStr">
+        <is>
+          <t>SAS SUMMUM EXPRESS</t>
+        </is>
+      </c>
+      <c r="E265" s="22" t="inlineStr">
+        <is>
+          <t>SAS SUMMUM EXPRESS</t>
+        </is>
+      </c>
+      <c r="F265" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G265" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H265" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I265" s="22" t="inlineStr">
+        <is>
+          <t>10/07/2014</t>
+        </is>
+      </c>
+      <c r="J265" s="22" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K265" s="22" t="inlineStr">
+        <is>
+          <t>9 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L265" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M265" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N265" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O265" s="22" t="inlineStr"/>
+      <c r="P265" s="22" t="inlineStr"/>
+      <c r="Q265" s="22" t="inlineStr"/>
+      <c r="R265" s="23" t="inlineStr"/>
+      <c r="S265" s="22" t="inlineStr"/>
+      <c r="T265" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U265" s="22" t="inlineStr">
+        <is>
+          <t>EL MOUSSATI</t>
+        </is>
+      </c>
+      <c r="V265" s="22" t="inlineStr">
+        <is>
+          <t>Mohammed</t>
+        </is>
+      </c>
+      <c r="W265" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X265" s="22" t="inlineStr">
+        <is>
+          <t>68 avenue de Thionville</t>
+        </is>
+      </c>
+      <c r="Y265" s="23" t="inlineStr">
+        <is>
+          <t>57140</t>
+        </is>
+      </c>
+      <c r="Z265" s="22" t="inlineStr">
+        <is>
+          <t>Woippy</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B266" s="23" t="inlineStr">
+        <is>
+          <t>993449727</t>
+        </is>
+      </c>
+      <c r="C266" s="23" t="inlineStr">
+        <is>
+          <t>99344972700011</t>
+        </is>
+      </c>
+      <c r="D266" s="22" t="inlineStr">
+        <is>
+          <t>SWEET HOUSE</t>
+        </is>
+      </c>
+      <c r="E266" s="22" t="inlineStr">
+        <is>
+          <t>SWEET HOUSE</t>
+        </is>
+      </c>
+      <c r="F266" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G266" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H266" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I266" s="22" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="J266" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K266" s="22" t="inlineStr">
+        <is>
+          <t>8 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L266" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M266" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N266" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O266" s="22" t="inlineStr"/>
+      <c r="P266" s="22" t="inlineStr"/>
+      <c r="Q266" s="22" t="inlineStr"/>
+      <c r="R266" s="23" t="inlineStr"/>
+      <c r="S266" s="22" t="inlineStr"/>
+      <c r="T266" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U266" s="22" t="inlineStr">
+        <is>
+          <t>CAPO-CHICHI</t>
+        </is>
+      </c>
+      <c r="V266" s="22" t="inlineStr">
+        <is>
+          <t>Julie, Irma</t>
+        </is>
+      </c>
+      <c r="W266" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X266" s="22" t="inlineStr">
+        <is>
+          <t>1 rue de coetlosquet</t>
+        </is>
+      </c>
+      <c r="Y266" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z266" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B267" s="23" t="inlineStr">
+        <is>
+          <t>978313823</t>
+        </is>
+      </c>
+      <c r="C267" s="23" t="inlineStr">
+        <is>
+          <t>97831382300012</t>
+        </is>
+      </c>
+      <c r="D267" s="22" t="inlineStr">
+        <is>
+          <t>LECHA</t>
+        </is>
+      </c>
+      <c r="E267" s="22" t="inlineStr">
+        <is>
+          <t>LECHA</t>
+        </is>
+      </c>
+      <c r="F267" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G267" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H267" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I267" s="22" t="inlineStr">
+        <is>
+          <t>01/08/2023</t>
+        </is>
+      </c>
+      <c r="J267" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K267" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DE LA PAIX</t>
+        </is>
+      </c>
+      <c r="L267" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M267" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N267" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O267" s="22" t="inlineStr"/>
+      <c r="P267" s="22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q267" s="22" t="inlineStr"/>
+      <c r="R267" s="23" t="inlineStr"/>
+      <c r="S267" s="22" t="inlineStr"/>
+      <c r="T267" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U267" s="22" t="inlineStr">
+        <is>
+          <t>YE</t>
+        </is>
+      </c>
+      <c r="V267" s="22" t="inlineStr">
+        <is>
+          <t>Junda</t>
+        </is>
+      </c>
+      <c r="W267" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X267" s="22" t="inlineStr">
+        <is>
+          <t>41 Rue du Potier</t>
+        </is>
+      </c>
+      <c r="Y267" s="23" t="inlineStr">
+        <is>
+          <t>93150</t>
+        </is>
+      </c>
+      <c r="Z267" s="22" t="inlineStr">
+        <is>
+          <t>Le Blanc-Mesnil</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z247"/>
+  <autoFilter ref="A2:Z267"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z267"/>
+  <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28214,2239 +28214,4465 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="22" t="inlineStr">
+      <c r="A248" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B248" s="23" t="inlineStr">
+      <c r="B248" s="21" t="inlineStr">
         <is>
           <t>993782200</t>
         </is>
       </c>
-      <c r="C248" s="23" t="inlineStr">
+      <c r="C248" s="21" t="inlineStr">
         <is>
           <t>99378220000014</t>
         </is>
       </c>
-      <c r="D248" s="22" t="inlineStr">
+      <c r="D248" s="20" t="inlineStr">
         <is>
           <t>SLMUSE</t>
         </is>
       </c>
-      <c r="E248" s="22" t="inlineStr">
+      <c r="E248" s="20" t="inlineStr">
         <is>
           <t>SLMUSE</t>
         </is>
       </c>
-      <c r="F248" s="22" t="inlineStr">
+      <c r="F248" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G248" s="22" t="inlineStr">
+      <c r="G248" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H248" s="22" t="inlineStr">
+      <c r="H248" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I248" s="22" t="inlineStr">
+      <c r="I248" s="20" t="inlineStr">
         <is>
           <t>10/11/2025</t>
         </is>
       </c>
-      <c r="J248" s="22" t="inlineStr">
+      <c r="J248" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K248" s="22" t="inlineStr">
+      <c r="K248" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">CENTRE COMMERCIAL MUSE </t>
         </is>
       </c>
-      <c r="L248" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M248" s="22" t="inlineStr">
+      <c r="L248" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M248" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N248" s="22" t="inlineStr">
+      <c r="N248" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O248" s="22" t="inlineStr"/>
-      <c r="P248" s="22" t="inlineStr"/>
-      <c r="Q248" s="22" t="inlineStr"/>
-      <c r="R248" s="23" t="inlineStr"/>
-      <c r="S248" s="22" t="inlineStr"/>
-      <c r="T248" s="22" t="inlineStr">
+      <c r="O248" s="20" t="inlineStr"/>
+      <c r="P248" s="20" t="inlineStr"/>
+      <c r="Q248" s="20" t="inlineStr"/>
+      <c r="R248" s="21" t="inlineStr"/>
+      <c r="S248" s="20" t="inlineStr"/>
+      <c r="T248" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U248" s="22" t="inlineStr">
+      <c r="U248" s="20" t="inlineStr">
         <is>
           <t>SL RESTAURATION</t>
         </is>
       </c>
-      <c r="V248" s="22" t="inlineStr"/>
-      <c r="W248" s="22" t="inlineStr">
+      <c r="V248" s="20" t="inlineStr"/>
+      <c r="W248" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X248" s="22" t="inlineStr">
+      <c r="X248" s="20" t="inlineStr">
         <is>
           <t>28 RUE Principale</t>
         </is>
       </c>
-      <c r="Y248" s="23" t="inlineStr">
+      <c r="Y248" s="21" t="inlineStr">
         <is>
           <t>57590</t>
         </is>
       </c>
-      <c r="Z248" s="22" t="inlineStr">
+      <c r="Z248" s="20" t="inlineStr">
         <is>
           <t>Jallaucourt</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="22" t="inlineStr">
+      <c r="A249" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B249" s="23" t="inlineStr">
+      <c r="B249" s="21" t="inlineStr">
         <is>
           <t>822790689</t>
         </is>
       </c>
-      <c r="C249" s="23" t="inlineStr">
+      <c r="C249" s="21" t="inlineStr">
         <is>
           <t>82279068900019</t>
         </is>
       </c>
-      <c r="D249" s="22" t="inlineStr">
+      <c r="D249" s="20" t="inlineStr">
         <is>
           <t>LA MAISON DU BURGER</t>
         </is>
       </c>
-      <c r="E249" s="22" t="inlineStr">
+      <c r="E249" s="20" t="inlineStr">
         <is>
           <t>LA MAISON DU BURGER</t>
         </is>
       </c>
-      <c r="F249" s="22" t="inlineStr">
+      <c r="F249" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G249" s="22" t="inlineStr">
+      <c r="G249" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H249" s="22" t="inlineStr">
+      <c r="H249" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I249" s="22" t="inlineStr">
+      <c r="I249" s="20" t="inlineStr">
         <is>
           <t>01/10/2016</t>
         </is>
       </c>
-      <c r="J249" s="22" t="inlineStr">
+      <c r="J249" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K249" s="22" t="inlineStr">
+      <c r="K249" s="20" t="inlineStr">
         <is>
           <t>3 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="L249" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M249" s="22" t="inlineStr">
+      <c r="L249" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M249" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N249" s="22" t="inlineStr">
+      <c r="N249" s="20" t="inlineStr">
         <is>
           <t>Entre 1 et 2 salariés</t>
         </is>
       </c>
-      <c r="O249" s="22" t="inlineStr"/>
-      <c r="P249" s="22" t="inlineStr"/>
-      <c r="Q249" s="22" t="inlineStr"/>
-      <c r="R249" s="23" t="inlineStr"/>
-      <c r="S249" s="22" t="inlineStr"/>
-      <c r="T249" s="22" t="inlineStr">
+      <c r="O249" s="20" t="inlineStr"/>
+      <c r="P249" s="20" t="inlineStr"/>
+      <c r="Q249" s="20" t="inlineStr"/>
+      <c r="R249" s="21" t="inlineStr"/>
+      <c r="S249" s="20" t="inlineStr"/>
+      <c r="T249" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U249" s="22" t="inlineStr">
+      <c r="U249" s="20" t="inlineStr">
         <is>
           <t>JOLIOT</t>
         </is>
       </c>
-      <c r="V249" s="22" t="inlineStr">
+      <c r="V249" s="20" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="W249" s="22" t="inlineStr">
+      <c r="W249" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X249" s="22" t="inlineStr">
+      <c r="X249" s="20" t="inlineStr">
         <is>
           <t>68 avenue Alexandre Dreux</t>
         </is>
       </c>
-      <c r="Y249" s="23" t="inlineStr">
+      <c r="Y249" s="21" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
       </c>
-      <c r="Z249" s="22" t="inlineStr">
+      <c r="Z249" s="20" t="inlineStr">
         <is>
           <t>Valleroy</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="22" t="inlineStr">
+      <c r="A250" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B250" s="23" t="inlineStr">
+      <c r="B250" s="21" t="inlineStr">
         <is>
           <t>930096938</t>
         </is>
       </c>
-      <c r="C250" s="23" t="inlineStr">
+      <c r="C250" s="21" t="inlineStr">
         <is>
           <t>93009693800012</t>
         </is>
       </c>
-      <c r="D250" s="22" t="inlineStr">
+      <c r="D250" s="20" t="inlineStr">
         <is>
           <t>AU FIL DE VOUS</t>
         </is>
       </c>
-      <c r="E250" s="22" t="inlineStr">
+      <c r="E250" s="20" t="inlineStr">
         <is>
           <t>AU FIL DE VOUS</t>
         </is>
       </c>
-      <c r="F250" s="22" t="inlineStr">
+      <c r="F250" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G250" s="22" t="inlineStr">
+      <c r="G250" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H250" s="22" t="inlineStr">
+      <c r="H250" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I250" s="22" t="inlineStr">
+      <c r="I250" s="20" t="inlineStr">
         <is>
           <t>01/07/2024</t>
         </is>
       </c>
-      <c r="J250" s="22" t="inlineStr">
+      <c r="J250" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K250" s="22" t="inlineStr">
+      <c r="K250" s="20" t="inlineStr">
         <is>
           <t>34 RUE DE PONT-A-MOUSSON</t>
         </is>
       </c>
-      <c r="L250" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M250" s="22" t="inlineStr">
+      <c r="L250" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M250" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N250" s="22" t="inlineStr">
+      <c r="N250" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O250" s="22" t="inlineStr"/>
-      <c r="P250" s="22" t="inlineStr"/>
-      <c r="Q250" s="22" t="inlineStr"/>
-      <c r="R250" s="23" t="inlineStr"/>
-      <c r="S250" s="22" t="inlineStr"/>
-      <c r="T250" s="22" t="inlineStr">
+      <c r="O250" s="20" t="inlineStr"/>
+      <c r="P250" s="20" t="inlineStr"/>
+      <c r="Q250" s="20" t="inlineStr"/>
+      <c r="R250" s="21" t="inlineStr"/>
+      <c r="S250" s="20" t="inlineStr"/>
+      <c r="T250" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U250" s="22" t="inlineStr">
+      <c r="U250" s="20" t="inlineStr">
         <is>
           <t>THOMAS</t>
         </is>
       </c>
-      <c r="V250" s="22" t="inlineStr">
+      <c r="V250" s="20" t="inlineStr">
         <is>
           <t>Typhaine</t>
         </is>
       </c>
-      <c r="W250" s="22" t="inlineStr">
+      <c r="W250" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X250" s="22" t="inlineStr">
+      <c r="X250" s="20" t="inlineStr">
         <is>
           <t>allée saint symphorien péniche octopus</t>
         </is>
       </c>
-      <c r="Y250" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z250" s="22" t="inlineStr">
+      <c r="Y250" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z250" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="22" t="inlineStr">
+      <c r="A251" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B251" s="23" t="inlineStr">
+      <c r="B251" s="21" t="inlineStr">
         <is>
           <t>505253534</t>
         </is>
       </c>
-      <c r="C251" s="23" t="inlineStr">
+      <c r="C251" s="21" t="inlineStr">
         <is>
           <t>50525353400018</t>
         </is>
       </c>
-      <c r="D251" s="22" t="inlineStr">
+      <c r="D251" s="20" t="inlineStr">
         <is>
           <t>BOLIFAB</t>
         </is>
       </c>
-      <c r="E251" s="22" t="inlineStr">
+      <c r="E251" s="20" t="inlineStr">
         <is>
           <t>BOLIFAB</t>
         </is>
       </c>
-      <c r="F251" s="22" t="inlineStr">
+      <c r="F251" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G251" s="22" t="inlineStr">
+      <c r="G251" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H251" s="22" t="inlineStr">
+      <c r="H251" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I251" s="22" t="inlineStr">
+      <c r="I251" s="20" t="inlineStr">
         <is>
           <t>21/06/2008</t>
         </is>
       </c>
-      <c r="J251" s="22" t="inlineStr">
+      <c r="J251" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K251" s="22" t="inlineStr">
+      <c r="K251" s="20" t="inlineStr">
         <is>
           <t>1 RUE VICTOR JACOB</t>
         </is>
       </c>
-      <c r="L251" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M251" s="22" t="inlineStr">
+      <c r="L251" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M251" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N251" s="22" t="inlineStr">
+      <c r="N251" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O251" s="22" t="inlineStr"/>
-      <c r="P251" s="22" t="inlineStr"/>
-      <c r="Q251" s="22" t="inlineStr"/>
-      <c r="R251" s="23" t="inlineStr"/>
-      <c r="S251" s="22" t="inlineStr"/>
-      <c r="T251" s="22" t="inlineStr">
+      <c r="O251" s="20" t="inlineStr"/>
+      <c r="P251" s="20" t="inlineStr"/>
+      <c r="Q251" s="20" t="inlineStr"/>
+      <c r="R251" s="21" t="inlineStr"/>
+      <c r="S251" s="20" t="inlineStr"/>
+      <c r="T251" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U251" s="22" t="inlineStr">
+      <c r="U251" s="20" t="inlineStr">
         <is>
           <t>Fabian</t>
         </is>
       </c>
-      <c r="V251" s="22" t="inlineStr">
+      <c r="V251" s="20" t="inlineStr">
         <is>
           <t>Ludovic</t>
         </is>
       </c>
-      <c r="W251" s="22" t="inlineStr">
+      <c r="W251" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X251" s="22" t="inlineStr"/>
-      <c r="Y251" s="23" t="inlineStr">
+      <c r="X251" s="20" t="inlineStr"/>
+      <c r="Y251" s="21" t="inlineStr">
         <is>
           <t>57100</t>
         </is>
       </c>
-      <c r="Z251" s="22" t="inlineStr">
+      <c r="Z251" s="20" t="inlineStr">
         <is>
           <t>MANOM</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="22" t="inlineStr">
+      <c r="A252" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B252" s="23" t="inlineStr">
+      <c r="B252" s="21" t="inlineStr">
         <is>
           <t>828631572</t>
         </is>
       </c>
-      <c r="C252" s="23" t="inlineStr">
+      <c r="C252" s="21" t="inlineStr">
         <is>
           <t>82863157200017</t>
         </is>
       </c>
-      <c r="D252" s="22" t="inlineStr">
+      <c r="D252" s="20" t="inlineStr">
         <is>
           <t>SABLE D'OR</t>
         </is>
       </c>
-      <c r="E252" s="22" t="inlineStr">
+      <c r="E252" s="20" t="inlineStr">
         <is>
           <t>SABLE D'OR</t>
         </is>
       </c>
-      <c r="F252" s="22" t="inlineStr">
+      <c r="F252" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G252" s="22" t="inlineStr">
+      <c r="G252" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H252" s="22" t="inlineStr">
+      <c r="H252" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I252" s="22" t="inlineStr">
+      <c r="I252" s="20" t="inlineStr">
         <is>
           <t>23/03/2017</t>
         </is>
       </c>
-      <c r="J252" s="22" t="inlineStr">
+      <c r="J252" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K252" s="22" t="inlineStr">
+      <c r="K252" s="20" t="inlineStr">
         <is>
           <t>80 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="L252" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M252" s="22" t="inlineStr">
+      <c r="L252" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M252" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N252" s="22" t="inlineStr">
+      <c r="N252" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O252" s="22" t="inlineStr"/>
-      <c r="P252" s="22" t="inlineStr"/>
-      <c r="Q252" s="22" t="inlineStr"/>
-      <c r="R252" s="23" t="inlineStr"/>
-      <c r="S252" s="22" t="inlineStr"/>
-      <c r="T252" s="22" t="inlineStr">
+      <c r="O252" s="20" t="inlineStr"/>
+      <c r="P252" s="20" t="inlineStr"/>
+      <c r="Q252" s="20" t="inlineStr"/>
+      <c r="R252" s="21" t="inlineStr"/>
+      <c r="S252" s="20" t="inlineStr"/>
+      <c r="T252" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U252" s="22" t="inlineStr">
+      <c r="U252" s="20" t="inlineStr">
         <is>
           <t>TENANI</t>
         </is>
       </c>
-      <c r="V252" s="22" t="inlineStr">
+      <c r="V252" s="20" t="inlineStr">
         <is>
           <t>Rachid</t>
         </is>
       </c>
-      <c r="W252" s="22" t="inlineStr">
+      <c r="W252" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X252" s="22" t="inlineStr">
+      <c r="X252" s="20" t="inlineStr">
         <is>
           <t>18 rue Gabriel Pierné</t>
         </is>
       </c>
-      <c r="Y252" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z252" s="22" t="inlineStr">
+      <c r="Y252" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z252" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="22" t="inlineStr">
+      <c r="A253" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B253" s="23" t="inlineStr">
+      <c r="B253" s="21" t="inlineStr">
         <is>
           <t>882202997</t>
         </is>
       </c>
-      <c r="C253" s="23" t="inlineStr">
+      <c r="C253" s="21" t="inlineStr">
         <is>
           <t>88220299700012</t>
         </is>
       </c>
-      <c r="D253" s="22" t="inlineStr">
+      <c r="D253" s="20" t="inlineStr">
         <is>
           <t>CHEZ FETHI</t>
         </is>
       </c>
-      <c r="E253" s="22" t="inlineStr">
+      <c r="E253" s="20" t="inlineStr">
         <is>
           <t>CHEZ FETHI</t>
         </is>
       </c>
-      <c r="F253" s="22" t="inlineStr">
+      <c r="F253" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G253" s="22" t="inlineStr">
+      <c r="G253" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H253" s="22" t="inlineStr">
+      <c r="H253" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I253" s="22" t="inlineStr">
+      <c r="I253" s="20" t="inlineStr">
         <is>
           <t>02/03/2020</t>
         </is>
       </c>
-      <c r="J253" s="22" t="inlineStr">
+      <c r="J253" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K253" s="22" t="inlineStr">
+      <c r="K253" s="20" t="inlineStr">
         <is>
           <t>22 RUE DES ALLEMANDS</t>
         </is>
       </c>
-      <c r="L253" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M253" s="22" t="inlineStr">
+      <c r="L253" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M253" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N253" s="22" t="inlineStr">
+      <c r="N253" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O253" s="22" t="inlineStr"/>
-      <c r="P253" s="22" t="inlineStr"/>
-      <c r="Q253" s="22" t="inlineStr"/>
-      <c r="R253" s="23" t="inlineStr"/>
-      <c r="S253" s="22" t="inlineStr"/>
-      <c r="T253" s="22" t="inlineStr">
+      <c r="O253" s="20" t="inlineStr"/>
+      <c r="P253" s="20" t="inlineStr"/>
+      <c r="Q253" s="20" t="inlineStr"/>
+      <c r="R253" s="21" t="inlineStr"/>
+      <c r="S253" s="20" t="inlineStr"/>
+      <c r="T253" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U253" s="22" t="inlineStr">
+      <c r="U253" s="20" t="inlineStr">
         <is>
           <t>FARHATI</t>
         </is>
       </c>
-      <c r="V253" s="22" t="inlineStr">
+      <c r="V253" s="20" t="inlineStr">
         <is>
           <t>Ibtissem</t>
         </is>
       </c>
-      <c r="W253" s="22" t="inlineStr">
+      <c r="W253" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X253" s="22" t="inlineStr">
+      <c r="X253" s="20" t="inlineStr">
         <is>
           <t>44 rue jules guichard</t>
         </is>
       </c>
-      <c r="Y253" s="23" t="inlineStr">
+      <c r="Y253" s="21" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="Z253" s="22" t="inlineStr">
+      <c r="Z253" s="20" t="inlineStr">
         <is>
           <t>Reims</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="22" t="inlineStr">
+      <c r="A254" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B254" s="23" t="inlineStr">
+      <c r="B254" s="21" t="inlineStr">
         <is>
           <t>791123334</t>
         </is>
       </c>
-      <c r="C254" s="23" t="inlineStr">
+      <c r="C254" s="21" t="inlineStr">
         <is>
           <t>79112333400017</t>
         </is>
       </c>
-      <c r="D254" s="22" t="inlineStr">
+      <c r="D254" s="20" t="inlineStr">
         <is>
           <t>LE TROUBADOUR</t>
         </is>
       </c>
-      <c r="E254" s="22" t="inlineStr">
+      <c r="E254" s="20" t="inlineStr">
         <is>
           <t>LE TROUBADOUR</t>
         </is>
       </c>
-      <c r="F254" s="22" t="inlineStr">
+      <c r="F254" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G254" s="22" t="inlineStr">
+      <c r="G254" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H254" s="22" t="inlineStr">
+      <c r="H254" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I254" s="22" t="inlineStr">
+      <c r="I254" s="20" t="inlineStr">
         <is>
           <t>12/02/2013</t>
         </is>
       </c>
-      <c r="J254" s="22" t="inlineStr">
+      <c r="J254" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K254" s="22" t="inlineStr">
+      <c r="K254" s="20" t="inlineStr">
         <is>
           <t>32 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L254" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M254" s="22" t="inlineStr">
+      <c r="L254" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M254" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N254" s="22" t="inlineStr">
+      <c r="N254" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O254" s="22" t="inlineStr"/>
-      <c r="P254" s="22" t="inlineStr"/>
-      <c r="Q254" s="22" t="inlineStr"/>
-      <c r="R254" s="23" t="inlineStr"/>
-      <c r="S254" s="22" t="inlineStr"/>
-      <c r="T254" s="22" t="inlineStr">
+      <c r="O254" s="20" t="inlineStr"/>
+      <c r="P254" s="20" t="inlineStr"/>
+      <c r="Q254" s="20" t="inlineStr"/>
+      <c r="R254" s="21" t="inlineStr"/>
+      <c r="S254" s="20" t="inlineStr"/>
+      <c r="T254" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U254" s="22" t="inlineStr">
+      <c r="U254" s="20" t="inlineStr">
         <is>
           <t>TRABAND</t>
         </is>
       </c>
-      <c r="V254" s="22" t="inlineStr">
+      <c r="V254" s="20" t="inlineStr">
         <is>
           <t>Nicolas, Gerard, Charles, Andre</t>
         </is>
       </c>
-      <c r="W254" s="22" t="inlineStr">
+      <c r="W254" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X254" s="22" t="inlineStr">
+      <c r="X254" s="20" t="inlineStr">
         <is>
           <t>56 Rue Haute Seille</t>
         </is>
       </c>
-      <c r="Y254" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z254" s="22" t="inlineStr">
+      <c r="Y254" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z254" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="22" t="inlineStr">
+      <c r="A255" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B255" s="23" t="inlineStr">
+      <c r="B255" s="21" t="inlineStr">
         <is>
           <t>348030784</t>
         </is>
       </c>
-      <c r="C255" s="23" t="inlineStr">
+      <c r="C255" s="21" t="inlineStr">
         <is>
           <t>34803078400030</t>
         </is>
       </c>
-      <c r="D255" s="22" t="inlineStr">
+      <c r="D255" s="20" t="inlineStr">
         <is>
           <t>GORLINI Frederic</t>
         </is>
       </c>
-      <c r="E255" s="22" t="inlineStr">
+      <c r="E255" s="20" t="inlineStr">
         <is>
           <t>GORLINI Frederic</t>
         </is>
       </c>
-      <c r="F255" s="22" t="inlineStr">
+      <c r="F255" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G255" s="22" t="inlineStr">
+      <c r="G255" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H255" s="22" t="inlineStr">
+      <c r="H255" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I255" s="22" t="inlineStr">
+      <c r="I255" s="20" t="inlineStr">
         <is>
           <t>01/04/1988</t>
         </is>
       </c>
-      <c r="J255" s="22" t="inlineStr">
+      <c r="J255" s="20" t="inlineStr">
         <is>
           <t>1988</t>
         </is>
       </c>
-      <c r="K255" s="22" t="inlineStr">
+      <c r="K255" s="20" t="inlineStr">
         <is>
           <t>6 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L255" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M255" s="22" t="inlineStr">
+      <c r="L255" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M255" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N255" s="22" t="inlineStr">
+      <c r="N255" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O255" s="22" t="inlineStr"/>
-      <c r="P255" s="22" t="inlineStr"/>
-      <c r="Q255" s="22" t="inlineStr"/>
-      <c r="R255" s="23" t="inlineStr"/>
-      <c r="S255" s="22" t="inlineStr"/>
-      <c r="T255" s="22" t="inlineStr">
+      <c r="O255" s="20" t="inlineStr"/>
+      <c r="P255" s="20" t="inlineStr"/>
+      <c r="Q255" s="20" t="inlineStr"/>
+      <c r="R255" s="21" t="inlineStr"/>
+      <c r="S255" s="20" t="inlineStr"/>
+      <c r="T255" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U255" s="22" t="inlineStr">
+      <c r="U255" s="20" t="inlineStr">
         <is>
           <t>GORLINI</t>
         </is>
       </c>
-      <c r="V255" s="22" t="inlineStr">
+      <c r="V255" s="20" t="inlineStr">
         <is>
           <t>Frederic, Jean, Pierre</t>
         </is>
       </c>
-      <c r="W255" s="22" t="inlineStr">
+      <c r="W255" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X255" s="22" t="inlineStr"/>
-      <c r="Y255" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z255" s="22" t="inlineStr">
+      <c r="X255" s="20" t="inlineStr"/>
+      <c r="Y255" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z255" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="22" t="inlineStr">
+      <c r="A256" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B256" s="23" t="inlineStr">
+      <c r="B256" s="21" t="inlineStr">
         <is>
           <t>913114872</t>
         </is>
       </c>
-      <c r="C256" s="23" t="inlineStr">
+      <c r="C256" s="21" t="inlineStr">
         <is>
           <t>91311487200017</t>
         </is>
       </c>
-      <c r="D256" s="22" t="inlineStr">
+      <c r="D256" s="20" t="inlineStr">
         <is>
           <t>LA HAVANE</t>
         </is>
       </c>
-      <c r="E256" s="22" t="inlineStr">
+      <c r="E256" s="20" t="inlineStr">
         <is>
           <t>LA HAVANE</t>
         </is>
       </c>
-      <c r="F256" s="22" t="inlineStr">
+      <c r="F256" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G256" s="22" t="inlineStr">
+      <c r="G256" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H256" s="22" t="inlineStr">
+      <c r="H256" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I256" s="22" t="inlineStr">
+      <c r="I256" s="20" t="inlineStr">
         <is>
           <t>22/04/2022</t>
         </is>
       </c>
-      <c r="J256" s="22" t="inlineStr">
+      <c r="J256" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K256" s="22" t="inlineStr">
+      <c r="K256" s="20" t="inlineStr">
         <is>
           <t>47 PLACE SAINT-LOUIS</t>
         </is>
       </c>
-      <c r="L256" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M256" s="22" t="inlineStr">
+      <c r="L256" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M256" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N256" s="22" t="inlineStr">
+      <c r="N256" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O256" s="22" t="inlineStr"/>
-      <c r="P256" s="22" t="inlineStr"/>
-      <c r="Q256" s="22" t="inlineStr"/>
-      <c r="R256" s="23" t="inlineStr"/>
-      <c r="S256" s="22" t="inlineStr"/>
-      <c r="T256" s="22" t="inlineStr">
+      <c r="O256" s="20" t="inlineStr"/>
+      <c r="P256" s="20" t="inlineStr"/>
+      <c r="Q256" s="20" t="inlineStr"/>
+      <c r="R256" s="21" t="inlineStr"/>
+      <c r="S256" s="20" t="inlineStr"/>
+      <c r="T256" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U256" s="22" t="inlineStr">
+      <c r="U256" s="20" t="inlineStr">
         <is>
           <t>BUCKEL</t>
         </is>
       </c>
-      <c r="V256" s="22" t="inlineStr">
+      <c r="V256" s="20" t="inlineStr">
         <is>
           <t>Mickaël</t>
         </is>
       </c>
-      <c r="W256" s="22" t="inlineStr">
+      <c r="W256" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X256" s="22" t="inlineStr">
+      <c r="X256" s="20" t="inlineStr">
         <is>
           <t>7 Boulevard Robert Sernot</t>
         </is>
       </c>
-      <c r="Y256" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z256" s="22" t="inlineStr">
+      <c r="Y256" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z256" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="22" t="inlineStr">
+      <c r="A257" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B257" s="23" t="inlineStr">
+      <c r="B257" s="21" t="inlineStr">
         <is>
           <t>790033898</t>
         </is>
       </c>
-      <c r="C257" s="23" t="inlineStr">
+      <c r="C257" s="21" t="inlineStr">
         <is>
           <t>79003389800012</t>
         </is>
       </c>
-      <c r="D257" s="22" t="inlineStr">
+      <c r="D257" s="20" t="inlineStr">
         <is>
           <t>LE BARATIN</t>
         </is>
       </c>
-      <c r="E257" s="22" t="inlineStr">
+      <c r="E257" s="20" t="inlineStr">
         <is>
           <t>LE BARATIN</t>
         </is>
       </c>
-      <c r="F257" s="22" t="inlineStr">
+      <c r="F257" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G257" s="22" t="inlineStr">
+      <c r="G257" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H257" s="22" t="inlineStr">
+      <c r="H257" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I257" s="22" t="inlineStr">
+      <c r="I257" s="20" t="inlineStr">
         <is>
           <t>29/11/2012</t>
         </is>
       </c>
-      <c r="J257" s="22" t="inlineStr">
+      <c r="J257" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K257" s="22" t="inlineStr">
+      <c r="K257" s="20" t="inlineStr">
         <is>
           <t>8 RUE DES PARMENTIERS</t>
         </is>
       </c>
-      <c r="L257" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M257" s="22" t="inlineStr">
+      <c r="L257" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M257" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N257" s="22" t="inlineStr">
+      <c r="N257" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O257" s="22" t="inlineStr"/>
-      <c r="P257" s="22" t="inlineStr"/>
-      <c r="Q257" s="22" t="inlineStr"/>
-      <c r="R257" s="23" t="inlineStr"/>
-      <c r="S257" s="22" t="inlineStr"/>
-      <c r="T257" s="22" t="inlineStr">
+      <c r="O257" s="20" t="inlineStr"/>
+      <c r="P257" s="20" t="inlineStr"/>
+      <c r="Q257" s="20" t="inlineStr"/>
+      <c r="R257" s="21" t="inlineStr"/>
+      <c r="S257" s="20" t="inlineStr"/>
+      <c r="T257" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U257" s="22" t="inlineStr">
+      <c r="U257" s="20" t="inlineStr">
         <is>
           <t>SCHMALTZ</t>
         </is>
       </c>
-      <c r="V257" s="22" t="inlineStr">
+      <c r="V257" s="20" t="inlineStr">
         <is>
           <t>Cédric</t>
         </is>
       </c>
-      <c r="W257" s="22" t="inlineStr">
+      <c r="W257" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X257" s="22" t="inlineStr">
+      <c r="X257" s="20" t="inlineStr">
         <is>
           <t>3 rue Saint-Henry</t>
         </is>
       </c>
-      <c r="Y257" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z257" s="22" t="inlineStr">
+      <c r="Y257" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z257" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="22" t="inlineStr">
+      <c r="A258" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B258" s="23" t="inlineStr">
+      <c r="B258" s="21" t="inlineStr">
         <is>
           <t>987739000</t>
         </is>
       </c>
-      <c r="C258" s="23" t="inlineStr">
+      <c r="C258" s="21" t="inlineStr">
         <is>
           <t>98773900000014</t>
         </is>
       </c>
-      <c r="D258" s="22" t="inlineStr">
+      <c r="D258" s="20" t="inlineStr">
         <is>
           <t>LE LABO</t>
         </is>
       </c>
-      <c r="E258" s="22" t="inlineStr">
+      <c r="E258" s="20" t="inlineStr">
         <is>
           <t>LE LABO</t>
         </is>
       </c>
-      <c r="F258" s="22" t="inlineStr">
+      <c r="F258" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G258" s="22" t="inlineStr">
+      <c r="G258" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H258" s="22" t="inlineStr">
+      <c r="H258" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I258" s="22" t="inlineStr">
+      <c r="I258" s="20" t="inlineStr">
         <is>
           <t>15/03/2024</t>
         </is>
       </c>
-      <c r="J258" s="22" t="inlineStr">
+      <c r="J258" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K258" s="22" t="inlineStr">
+      <c r="K258" s="20" t="inlineStr">
         <is>
           <t>16 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L258" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M258" s="22" t="inlineStr">
+      <c r="L258" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M258" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N258" s="22" t="inlineStr">
+      <c r="N258" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O258" s="22" t="inlineStr"/>
-      <c r="P258" s="22" t="inlineStr"/>
-      <c r="Q258" s="22" t="inlineStr"/>
-      <c r="R258" s="23" t="inlineStr"/>
-      <c r="S258" s="22" t="inlineStr"/>
-      <c r="T258" s="22" t="inlineStr">
+      <c r="O258" s="20" t="inlineStr"/>
+      <c r="P258" s="20" t="inlineStr"/>
+      <c r="Q258" s="20" t="inlineStr"/>
+      <c r="R258" s="21" t="inlineStr"/>
+      <c r="S258" s="20" t="inlineStr"/>
+      <c r="T258" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U258" s="22" t="inlineStr">
+      <c r="U258" s="20" t="inlineStr">
         <is>
           <t>SCHLUCK</t>
         </is>
       </c>
-      <c r="V258" s="22" t="inlineStr">
+      <c r="V258" s="20" t="inlineStr">
         <is>
           <t>Herve</t>
         </is>
       </c>
-      <c r="W258" s="22" t="inlineStr">
+      <c r="W258" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X258" s="22" t="inlineStr">
+      <c r="X258" s="20" t="inlineStr">
         <is>
           <t>14 avenue André Malraux</t>
         </is>
       </c>
-      <c r="Y258" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z258" s="22" t="inlineStr">
+      <c r="Y258" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z258" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="22" t="inlineStr">
+      <c r="A259" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B259" s="23" t="inlineStr">
+      <c r="B259" s="21" t="inlineStr">
         <is>
           <t>834775033</t>
         </is>
       </c>
-      <c r="C259" s="23" t="inlineStr">
+      <c r="C259" s="21" t="inlineStr">
         <is>
           <t>83477503300014</t>
         </is>
       </c>
-      <c r="D259" s="22" t="inlineStr">
+      <c r="D259" s="20" t="inlineStr">
         <is>
           <t>CAROLANS</t>
         </is>
       </c>
-      <c r="E259" s="22" t="inlineStr">
+      <c r="E259" s="20" t="inlineStr">
         <is>
           <t>CAROLANS</t>
         </is>
       </c>
-      <c r="F259" s="22" t="inlineStr">
+      <c r="F259" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G259" s="22" t="inlineStr">
+      <c r="G259" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H259" s="22" t="inlineStr">
+      <c r="H259" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I259" s="22" t="inlineStr">
+      <c r="I259" s="20" t="inlineStr">
         <is>
           <t>19/01/2018</t>
         </is>
       </c>
-      <c r="J259" s="22" t="inlineStr">
+      <c r="J259" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K259" s="22" t="inlineStr">
+      <c r="K259" s="20" t="inlineStr">
         <is>
           <t>20 B AVENUE ROBERT SCHUMAN</t>
         </is>
       </c>
-      <c r="L259" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M259" s="22" t="inlineStr">
+      <c r="L259" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M259" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N259" s="22" t="inlineStr">
+      <c r="N259" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O259" s="22" t="inlineStr"/>
-      <c r="P259" s="22" t="inlineStr"/>
-      <c r="Q259" s="22" t="inlineStr"/>
-      <c r="R259" s="23" t="inlineStr"/>
-      <c r="S259" s="22" t="inlineStr"/>
-      <c r="T259" s="22" t="inlineStr">
+      <c r="O259" s="20" t="inlineStr"/>
+      <c r="P259" s="20" t="inlineStr"/>
+      <c r="Q259" s="20" t="inlineStr"/>
+      <c r="R259" s="21" t="inlineStr"/>
+      <c r="S259" s="20" t="inlineStr"/>
+      <c r="T259" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U259" s="22" t="inlineStr">
+      <c r="U259" s="20" t="inlineStr">
         <is>
           <t>LENNINGER</t>
         </is>
       </c>
-      <c r="V259" s="22" t="inlineStr">
+      <c r="V259" s="20" t="inlineStr">
         <is>
           <t>Sébastien</t>
         </is>
       </c>
-      <c r="W259" s="22" t="inlineStr">
+      <c r="W259" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X259" s="22" t="inlineStr">
+      <c r="X259" s="20" t="inlineStr">
         <is>
           <t>20 rue Jean Mermoz</t>
         </is>
       </c>
-      <c r="Y259" s="23" t="inlineStr">
+      <c r="Y259" s="21" t="inlineStr">
         <is>
           <t>57970</t>
         </is>
       </c>
-      <c r="Z259" s="22" t="inlineStr">
+      <c r="Z259" s="20" t="inlineStr">
         <is>
           <t>Yutz</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="22" t="inlineStr">
+      <c r="A260" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B260" s="23" t="inlineStr">
+      <c r="B260" s="21" t="inlineStr">
         <is>
           <t>334930047</t>
         </is>
       </c>
-      <c r="C260" s="23" t="inlineStr">
+      <c r="C260" s="21" t="inlineStr">
         <is>
           <t>33493004700033</t>
         </is>
       </c>
-      <c r="D260" s="22" t="inlineStr">
+      <c r="D260" s="20" t="inlineStr">
         <is>
           <t>BOGNER Henri</t>
         </is>
       </c>
-      <c r="E260" s="22" t="inlineStr">
+      <c r="E260" s="20" t="inlineStr">
         <is>
           <t>BOGNER Henri</t>
         </is>
       </c>
-      <c r="F260" s="22" t="inlineStr">
+      <c r="F260" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G260" s="22" t="inlineStr">
+      <c r="G260" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H260" s="22" t="inlineStr">
+      <c r="H260" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I260" s="22" t="inlineStr">
+      <c r="I260" s="20" t="inlineStr">
         <is>
           <t>01/01/1986</t>
         </is>
       </c>
-      <c r="J260" s="22" t="inlineStr">
+      <c r="J260" s="20" t="inlineStr">
         <is>
           <t>1986</t>
         </is>
       </c>
-      <c r="K260" s="22" t="inlineStr">
+      <c r="K260" s="20" t="inlineStr">
         <is>
           <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
         </is>
       </c>
-      <c r="L260" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M260" s="22" t="inlineStr">
+      <c r="L260" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M260" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N260" s="22" t="inlineStr">
+      <c r="N260" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O260" s="22" t="inlineStr"/>
-      <c r="P260" s="22" t="inlineStr"/>
-      <c r="Q260" s="22" t="inlineStr"/>
-      <c r="R260" s="23" t="inlineStr"/>
-      <c r="S260" s="22" t="inlineStr"/>
-      <c r="T260" s="22" t="inlineStr">
+      <c r="O260" s="20" t="inlineStr"/>
+      <c r="P260" s="20" t="inlineStr"/>
+      <c r="Q260" s="20" t="inlineStr"/>
+      <c r="R260" s="21" t="inlineStr"/>
+      <c r="S260" s="20" t="inlineStr"/>
+      <c r="T260" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U260" s="22" t="inlineStr">
+      <c r="U260" s="20" t="inlineStr">
         <is>
           <t>BOGNER</t>
         </is>
       </c>
-      <c r="V260" s="22" t="inlineStr">
+      <c r="V260" s="20" t="inlineStr">
         <is>
           <t>Henri, Georges, Antoine</t>
         </is>
       </c>
-      <c r="W260" s="22" t="inlineStr">
+      <c r="W260" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X260" s="22" t="inlineStr"/>
-      <c r="Y260" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z260" s="22" t="inlineStr">
+      <c r="X260" s="20" t="inlineStr"/>
+      <c r="Y260" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z260" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="22" t="inlineStr">
+      <c r="A261" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B261" s="23" t="inlineStr">
+      <c r="B261" s="21" t="inlineStr">
         <is>
           <t>405332453</t>
         </is>
       </c>
-      <c r="C261" s="23" t="inlineStr">
+      <c r="C261" s="21" t="inlineStr">
         <is>
           <t>40533245300019</t>
         </is>
       </c>
-      <c r="D261" s="22" t="inlineStr">
+      <c r="D261" s="20" t="inlineStr">
         <is>
           <t>LE SAINT JACQUES</t>
         </is>
       </c>
-      <c r="E261" s="22" t="inlineStr">
+      <c r="E261" s="20" t="inlineStr">
         <is>
           <t>LE SAINT JACQUES</t>
         </is>
       </c>
-      <c r="F261" s="22" t="inlineStr">
+      <c r="F261" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G261" s="22" t="inlineStr">
+      <c r="G261" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H261" s="22" t="inlineStr">
+      <c r="H261" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I261" s="22" t="inlineStr">
+      <c r="I261" s="20" t="inlineStr">
         <is>
           <t>16/04/1996</t>
         </is>
       </c>
-      <c r="J261" s="22" t="inlineStr">
+      <c r="J261" s="20" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="K261" s="22" t="inlineStr">
+      <c r="K261" s="20" t="inlineStr">
         <is>
           <t>10 PLACE SAINT-JACQUES</t>
         </is>
       </c>
-      <c r="L261" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M261" s="22" t="inlineStr">
+      <c r="L261" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M261" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N261" s="22" t="inlineStr">
+      <c r="N261" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O261" s="22" t="n">
-        <v>774898</v>
-      </c>
-      <c r="P261" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q261" s="22" t="inlineStr"/>
-      <c r="R261" s="23" t="inlineStr"/>
-      <c r="S261" s="22" t="inlineStr"/>
-      <c r="T261" s="22" t="inlineStr">
+      <c r="O261" s="20" t="inlineStr">
+        <is>
+          <t>774898</t>
+        </is>
+      </c>
+      <c r="P261" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q261" s="20" t="inlineStr"/>
+      <c r="R261" s="21" t="inlineStr"/>
+      <c r="S261" s="20" t="inlineStr"/>
+      <c r="T261" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U261" s="22" t="inlineStr">
+      <c r="U261" s="20" t="inlineStr">
         <is>
           <t>POTIER</t>
         </is>
       </c>
-      <c r="V261" s="22" t="inlineStr">
+      <c r="V261" s="20" t="inlineStr">
         <is>
           <t>Sylvain</t>
         </is>
       </c>
-      <c r="W261" s="22" t="inlineStr">
+      <c r="W261" s="20" t="inlineStr">
         <is>
           <t>Directeur général</t>
         </is>
       </c>
-      <c r="X261" s="22" t="inlineStr">
+      <c r="X261" s="20" t="inlineStr">
         <is>
           <t>13 rue de la louvière</t>
         </is>
       </c>
-      <c r="Y261" s="23" t="inlineStr">
+      <c r="Y261" s="21" t="inlineStr">
         <is>
           <t>54330</t>
         </is>
       </c>
-      <c r="Z261" s="22" t="inlineStr">
+      <c r="Z261" s="20" t="inlineStr">
         <is>
           <t>Hammeville</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="22" t="inlineStr">
+      <c r="A262" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B262" s="23" t="inlineStr">
+      <c r="B262" s="21" t="inlineStr">
         <is>
           <t>878788272</t>
         </is>
       </c>
-      <c r="C262" s="23" t="inlineStr">
+      <c r="C262" s="21" t="inlineStr">
         <is>
           <t>87878827200010</t>
         </is>
       </c>
-      <c r="D262" s="22" t="inlineStr">
+      <c r="D262" s="20" t="inlineStr">
         <is>
           <t>LA CATHEDRALE EXPLOITATION</t>
         </is>
       </c>
-      <c r="E262" s="22" t="inlineStr">
+      <c r="E262" s="20" t="inlineStr">
         <is>
           <t>LA CATHEDRALE EXPLOITATION</t>
         </is>
       </c>
-      <c r="F262" s="22" t="inlineStr">
+      <c r="F262" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G262" s="22" t="inlineStr">
+      <c r="G262" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H262" s="22" t="inlineStr">
+      <c r="H262" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I262" s="22" t="inlineStr">
+      <c r="I262" s="20" t="inlineStr">
         <is>
           <t>18/10/2019</t>
         </is>
       </c>
-      <c r="J262" s="22" t="inlineStr">
+      <c r="J262" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K262" s="22" t="inlineStr">
+      <c r="K262" s="20" t="inlineStr">
         <is>
           <t>3 RUE BLONDEL</t>
         </is>
       </c>
-      <c r="L262" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M262" s="22" t="inlineStr">
+      <c r="L262" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M262" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N262" s="22" t="inlineStr">
+      <c r="N262" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O262" s="22" t="inlineStr"/>
-      <c r="P262" s="22" t="inlineStr"/>
-      <c r="Q262" s="22" t="inlineStr"/>
-      <c r="R262" s="23" t="inlineStr"/>
-      <c r="S262" s="22" t="inlineStr"/>
-      <c r="T262" s="22" t="inlineStr">
+      <c r="O262" s="20" t="inlineStr"/>
+      <c r="P262" s="20" t="inlineStr"/>
+      <c r="Q262" s="20" t="inlineStr"/>
+      <c r="R262" s="21" t="inlineStr"/>
+      <c r="S262" s="20" t="inlineStr"/>
+      <c r="T262" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U262" s="22" t="inlineStr">
+      <c r="U262" s="20" t="inlineStr">
         <is>
           <t>ZIMMER</t>
         </is>
       </c>
-      <c r="V262" s="22" t="inlineStr">
+      <c r="V262" s="20" t="inlineStr">
         <is>
           <t>Alexandra</t>
         </is>
       </c>
-      <c r="W262" s="22" t="inlineStr">
+      <c r="W262" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X262" s="22" t="inlineStr">
+      <c r="X262" s="20" t="inlineStr">
         <is>
           <t>50 rue aux Arènes</t>
         </is>
       </c>
-      <c r="Y262" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z262" s="22" t="inlineStr">
+      <c r="Y262" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z262" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="22" t="inlineStr">
+      <c r="A263" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B263" s="23" t="inlineStr">
+      <c r="B263" s="21" t="inlineStr">
         <is>
           <t>879118438</t>
         </is>
       </c>
-      <c r="C263" s="23" t="inlineStr">
+      <c r="C263" s="21" t="inlineStr">
         <is>
           <t>87911843800016</t>
         </is>
       </c>
-      <c r="D263" s="22" t="inlineStr">
+      <c r="D263" s="20" t="inlineStr">
         <is>
           <t>LES BISTROTS DE METZ</t>
         </is>
       </c>
-      <c r="E263" s="22" t="inlineStr">
+      <c r="E263" s="20" t="inlineStr">
         <is>
           <t>LES BISTROTS DE METZ</t>
         </is>
       </c>
-      <c r="F263" s="22" t="inlineStr">
+      <c r="F263" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G263" s="22" t="inlineStr">
+      <c r="G263" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H263" s="22" t="inlineStr">
+      <c r="H263" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I263" s="22" t="inlineStr">
+      <c r="I263" s="20" t="inlineStr">
         <is>
           <t>16/10/2019</t>
         </is>
       </c>
-      <c r="J263" s="22" t="inlineStr">
+      <c r="J263" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K263" s="22" t="inlineStr">
+      <c r="K263" s="20" t="inlineStr">
         <is>
           <t>12 RUE DU FAISAN</t>
         </is>
       </c>
-      <c r="L263" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M263" s="22" t="inlineStr">
+      <c r="L263" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M263" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N263" s="22" t="inlineStr">
+      <c r="N263" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O263" s="22" t="inlineStr"/>
-      <c r="P263" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q263" s="22" t="inlineStr"/>
-      <c r="R263" s="23" t="inlineStr"/>
-      <c r="S263" s="22" t="inlineStr"/>
-      <c r="T263" s="22" t="inlineStr">
+      <c r="O263" s="20" t="inlineStr"/>
+      <c r="P263" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q263" s="20" t="inlineStr"/>
+      <c r="R263" s="21" t="inlineStr"/>
+      <c r="S263" s="20" t="inlineStr"/>
+      <c r="T263" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U263" s="22" t="inlineStr">
+      <c r="U263" s="20" t="inlineStr">
         <is>
           <t>ZIMMER</t>
         </is>
       </c>
-      <c r="V263" s="22" t="inlineStr">
+      <c r="V263" s="20" t="inlineStr">
         <is>
           <t>Alexandra</t>
         </is>
       </c>
-      <c r="W263" s="22" t="inlineStr">
+      <c r="W263" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X263" s="22" t="inlineStr">
+      <c r="X263" s="20" t="inlineStr">
         <is>
           <t>50 rue aux Arènes</t>
         </is>
       </c>
-      <c r="Y263" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z263" s="22" t="inlineStr">
+      <c r="Y263" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z263" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="22" t="inlineStr">
+      <c r="A264" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B264" s="23" t="inlineStr">
+      <c r="B264" s="21" t="inlineStr">
         <is>
           <t>801372699</t>
         </is>
       </c>
-      <c r="C264" s="23" t="inlineStr">
+      <c r="C264" s="21" t="inlineStr">
         <is>
           <t>80137269900034</t>
         </is>
       </c>
-      <c r="D264" s="22" t="inlineStr">
+      <c r="D264" s="20" t="inlineStr">
         <is>
           <t>ANCY PIZZA EXPRESS</t>
         </is>
       </c>
-      <c r="E264" s="22" t="inlineStr">
+      <c r="E264" s="20" t="inlineStr">
         <is>
           <t>ANCY PIZZA EXPRESS</t>
         </is>
       </c>
-      <c r="F264" s="22" t="inlineStr">
+      <c r="F264" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G264" s="22" t="inlineStr">
+      <c r="G264" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H264" s="22" t="inlineStr">
+      <c r="H264" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I264" s="22" t="inlineStr">
+      <c r="I264" s="20" t="inlineStr">
         <is>
           <t>15/04/2014</t>
         </is>
       </c>
-      <c r="J264" s="22" t="inlineStr">
+      <c r="J264" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K264" s="22" t="inlineStr">
+      <c r="K264" s="20" t="inlineStr">
         <is>
           <t>31 RUE SAINT-PIERRE</t>
         </is>
       </c>
-      <c r="L264" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M264" s="22" t="inlineStr">
+      <c r="L264" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M264" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N264" s="22" t="inlineStr">
+      <c r="N264" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O264" s="22" t="inlineStr"/>
-      <c r="P264" s="22" t="inlineStr"/>
-      <c r="Q264" s="22" t="inlineStr"/>
-      <c r="R264" s="23" t="inlineStr"/>
-      <c r="S264" s="22" t="inlineStr"/>
-      <c r="T264" s="22" t="inlineStr">
+      <c r="O264" s="20" t="inlineStr"/>
+      <c r="P264" s="20" t="inlineStr"/>
+      <c r="Q264" s="20" t="inlineStr"/>
+      <c r="R264" s="21" t="inlineStr"/>
+      <c r="S264" s="20" t="inlineStr"/>
+      <c r="T264" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U264" s="22" t="inlineStr">
+      <c r="U264" s="20" t="inlineStr">
         <is>
           <t>POISSENOT</t>
         </is>
       </c>
-      <c r="V264" s="22" t="inlineStr">
+      <c r="V264" s="20" t="inlineStr">
         <is>
           <t>Sébastien, Bernard</t>
         </is>
       </c>
-      <c r="W264" s="22" t="inlineStr">
+      <c r="W264" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X264" s="22" t="inlineStr">
+      <c r="X264" s="20" t="inlineStr">
         <is>
           <t>13 rue de la Barre</t>
         </is>
       </c>
-      <c r="Y264" s="23" t="inlineStr">
+      <c r="Y264" s="21" t="inlineStr">
         <is>
           <t>57130</t>
         </is>
       </c>
-      <c r="Z264" s="22" t="inlineStr">
+      <c r="Z264" s="20" t="inlineStr">
         <is>
           <t>Ancy-sur-Moselle</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="22" t="inlineStr">
+      <c r="A265" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B265" s="23" t="inlineStr">
+      <c r="B265" s="21" t="inlineStr">
         <is>
           <t>803552546</t>
         </is>
       </c>
-      <c r="C265" s="23" t="inlineStr">
+      <c r="C265" s="21" t="inlineStr">
         <is>
           <t>80355254600019</t>
         </is>
       </c>
-      <c r="D265" s="22" t="inlineStr">
+      <c r="D265" s="20" t="inlineStr">
         <is>
           <t>SAS SUMMUM EXPRESS</t>
         </is>
       </c>
-      <c r="E265" s="22" t="inlineStr">
+      <c r="E265" s="20" t="inlineStr">
         <is>
           <t>SAS SUMMUM EXPRESS</t>
         </is>
       </c>
-      <c r="F265" s="22" t="inlineStr">
+      <c r="F265" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G265" s="22" t="inlineStr">
+      <c r="G265" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H265" s="22" t="inlineStr">
+      <c r="H265" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I265" s="22" t="inlineStr">
+      <c r="I265" s="20" t="inlineStr">
         <is>
           <t>10/07/2014</t>
         </is>
       </c>
-      <c r="J265" s="22" t="inlineStr">
+      <c r="J265" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="K265" s="22" t="inlineStr">
+      <c r="K265" s="20" t="inlineStr">
         <is>
           <t>9 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L265" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M265" s="22" t="inlineStr">
+      <c r="L265" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M265" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N265" s="22" t="inlineStr">
+      <c r="N265" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O265" s="22" t="inlineStr"/>
-      <c r="P265" s="22" t="inlineStr"/>
-      <c r="Q265" s="22" t="inlineStr"/>
-      <c r="R265" s="23" t="inlineStr"/>
-      <c r="S265" s="22" t="inlineStr"/>
-      <c r="T265" s="22" t="inlineStr">
+      <c r="O265" s="20" t="inlineStr"/>
+      <c r="P265" s="20" t="inlineStr"/>
+      <c r="Q265" s="20" t="inlineStr"/>
+      <c r="R265" s="21" t="inlineStr"/>
+      <c r="S265" s="20" t="inlineStr"/>
+      <c r="T265" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U265" s="22" t="inlineStr">
+      <c r="U265" s="20" t="inlineStr">
         <is>
           <t>EL MOUSSATI</t>
         </is>
       </c>
-      <c r="V265" s="22" t="inlineStr">
+      <c r="V265" s="20" t="inlineStr">
         <is>
           <t>Mohammed</t>
         </is>
       </c>
-      <c r="W265" s="22" t="inlineStr">
+      <c r="W265" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X265" s="22" t="inlineStr">
+      <c r="X265" s="20" t="inlineStr">
         <is>
           <t>68 avenue de Thionville</t>
         </is>
       </c>
-      <c r="Y265" s="23" t="inlineStr">
+      <c r="Y265" s="21" t="inlineStr">
         <is>
           <t>57140</t>
         </is>
       </c>
-      <c r="Z265" s="22" t="inlineStr">
+      <c r="Z265" s="20" t="inlineStr">
         <is>
           <t>Woippy</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="22" t="inlineStr">
+      <c r="A266" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B266" s="23" t="inlineStr">
+      <c r="B266" s="21" t="inlineStr">
         <is>
           <t>993449727</t>
         </is>
       </c>
-      <c r="C266" s="23" t="inlineStr">
+      <c r="C266" s="21" t="inlineStr">
         <is>
           <t>99344972700011</t>
         </is>
       </c>
-      <c r="D266" s="22" t="inlineStr">
+      <c r="D266" s="20" t="inlineStr">
         <is>
           <t>SWEET HOUSE</t>
         </is>
       </c>
-      <c r="E266" s="22" t="inlineStr">
+      <c r="E266" s="20" t="inlineStr">
         <is>
           <t>SWEET HOUSE</t>
         </is>
       </c>
-      <c r="F266" s="22" t="inlineStr">
+      <c r="F266" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G266" s="22" t="inlineStr">
+      <c r="G266" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H266" s="22" t="inlineStr">
+      <c r="H266" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I266" s="22" t="inlineStr">
+      <c r="I266" s="20" t="inlineStr">
         <is>
           <t>28/10/2025</t>
         </is>
       </c>
-      <c r="J266" s="22" t="inlineStr">
+      <c r="J266" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K266" s="22" t="inlineStr">
+      <c r="K266" s="20" t="inlineStr">
         <is>
           <t>8 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L266" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M266" s="22" t="inlineStr">
+      <c r="L266" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M266" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N266" s="22" t="inlineStr">
+      <c r="N266" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O266" s="22" t="inlineStr"/>
-      <c r="P266" s="22" t="inlineStr"/>
-      <c r="Q266" s="22" t="inlineStr"/>
-      <c r="R266" s="23" t="inlineStr"/>
-      <c r="S266" s="22" t="inlineStr"/>
-      <c r="T266" s="22" t="inlineStr">
+      <c r="O266" s="20" t="inlineStr"/>
+      <c r="P266" s="20" t="inlineStr"/>
+      <c r="Q266" s="20" t="inlineStr"/>
+      <c r="R266" s="21" t="inlineStr"/>
+      <c r="S266" s="20" t="inlineStr"/>
+      <c r="T266" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U266" s="22" t="inlineStr">
+      <c r="U266" s="20" t="inlineStr">
         <is>
           <t>CAPO-CHICHI</t>
         </is>
       </c>
-      <c r="V266" s="22" t="inlineStr">
+      <c r="V266" s="20" t="inlineStr">
         <is>
           <t>Julie, Irma</t>
         </is>
       </c>
-      <c r="W266" s="22" t="inlineStr">
+      <c r="W266" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X266" s="22" t="inlineStr">
+      <c r="X266" s="20" t="inlineStr">
         <is>
           <t>1 rue de coetlosquet</t>
         </is>
       </c>
-      <c r="Y266" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z266" s="22" t="inlineStr">
+      <c r="Y266" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z266" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="22" t="inlineStr">
+      <c r="A267" s="20" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B267" s="23" t="inlineStr">
+      <c r="B267" s="21" t="inlineStr">
         <is>
           <t>978313823</t>
         </is>
       </c>
-      <c r="C267" s="23" t="inlineStr">
+      <c r="C267" s="21" t="inlineStr">
         <is>
           <t>97831382300012</t>
         </is>
       </c>
-      <c r="D267" s="22" t="inlineStr">
+      <c r="D267" s="20" t="inlineStr">
         <is>
           <t>LECHA</t>
         </is>
       </c>
-      <c r="E267" s="22" t="inlineStr">
+      <c r="E267" s="20" t="inlineStr">
         <is>
           <t>LECHA</t>
         </is>
       </c>
-      <c r="F267" s="22" t="inlineStr">
+      <c r="F267" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G267" s="22" t="inlineStr">
+      <c r="G267" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H267" s="22" t="inlineStr">
+      <c r="H267" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I267" s="22" t="inlineStr">
+      <c r="I267" s="20" t="inlineStr">
         <is>
           <t>01/08/2023</t>
         </is>
       </c>
-      <c r="J267" s="22" t="inlineStr">
+      <c r="J267" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K267" s="22" t="inlineStr">
+      <c r="K267" s="20" t="inlineStr">
         <is>
           <t>1 RUE DE LA PAIX</t>
         </is>
       </c>
-      <c r="L267" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M267" s="22" t="inlineStr">
+      <c r="L267" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M267" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N267" s="22" t="inlineStr">
+      <c r="N267" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O267" s="22" t="inlineStr"/>
-      <c r="P267" s="22" t="n">
+      <c r="O267" s="20" t="inlineStr"/>
+      <c r="P267" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q267" s="20" t="inlineStr"/>
+      <c r="R267" s="21" t="inlineStr"/>
+      <c r="S267" s="20" t="inlineStr"/>
+      <c r="T267" s="20" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U267" s="20" t="inlineStr">
+        <is>
+          <t>YE</t>
+        </is>
+      </c>
+      <c r="V267" s="20" t="inlineStr">
+        <is>
+          <t>Junda</t>
+        </is>
+      </c>
+      <c r="W267" s="20" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X267" s="20" t="inlineStr">
+        <is>
+          <t>41 Rue du Potier</t>
+        </is>
+      </c>
+      <c r="Y267" s="21" t="inlineStr">
+        <is>
+          <t>93150</t>
+        </is>
+      </c>
+      <c r="Z267" s="20" t="inlineStr">
+        <is>
+          <t>Le Blanc-Mesnil</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B268" s="23" t="inlineStr">
+        <is>
+          <t>832795587</t>
+        </is>
+      </c>
+      <c r="C268" s="23" t="inlineStr">
+        <is>
+          <t>83279558700019</t>
+        </is>
+      </c>
+      <c r="D268" s="22" t="inlineStr">
+        <is>
+          <t>SITWELL</t>
+        </is>
+      </c>
+      <c r="E268" s="22" t="inlineStr">
+        <is>
+          <t>SITWELL</t>
+        </is>
+      </c>
+      <c r="F268" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G268" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H268" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I268" s="22" t="inlineStr">
+        <is>
+          <t>25/09/2017</t>
+        </is>
+      </c>
+      <c r="J268" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K268" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L268" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M268" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N268" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O268" s="22" t="inlineStr"/>
+      <c r="P268" s="22" t="inlineStr"/>
+      <c r="Q268" s="22" t="inlineStr"/>
+      <c r="R268" s="23" t="inlineStr"/>
+      <c r="S268" s="22" t="inlineStr"/>
+      <c r="T268" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U268" s="22" t="inlineStr">
+        <is>
+          <t>MECHKENE</t>
+        </is>
+      </c>
+      <c r="V268" s="22" t="inlineStr">
+        <is>
+          <t>Raouf</t>
+        </is>
+      </c>
+      <c r="W268" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X268" s="22" t="inlineStr">
+        <is>
+          <t>6 En Froide Ruelle</t>
+        </is>
+      </c>
+      <c r="Y268" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z268" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B269" s="23" t="inlineStr">
+        <is>
+          <t>937636165</t>
+        </is>
+      </c>
+      <c r="C269" s="23" t="inlineStr">
+        <is>
+          <t>93763616500022</t>
+        </is>
+      </c>
+      <c r="D269" s="22" t="inlineStr">
+        <is>
+          <t>B'CHETTES</t>
+        </is>
+      </c>
+      <c r="E269" s="22" t="inlineStr">
+        <is>
+          <t>B'CHETTES</t>
+        </is>
+      </c>
+      <c r="F269" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G269" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H269" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I269" s="22" t="inlineStr">
+        <is>
+          <t>01/11/2024</t>
+        </is>
+      </c>
+      <c r="J269" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K269" s="22" t="inlineStr">
+        <is>
+          <t>81 RUE DU XXEME CORPS AMERICAIN</t>
+        </is>
+      </c>
+      <c r="L269" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M269" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N269" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O269" s="22" t="inlineStr"/>
+      <c r="P269" s="22" t="inlineStr"/>
+      <c r="Q269" s="22" t="inlineStr"/>
+      <c r="R269" s="23" t="inlineStr"/>
+      <c r="S269" s="22" t="inlineStr"/>
+      <c r="T269" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U269" s="22" t="inlineStr">
+        <is>
+          <t>DOUM HOLDING</t>
+        </is>
+      </c>
+      <c r="V269" s="22" t="inlineStr"/>
+      <c r="W269" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X269" s="22" t="inlineStr">
+        <is>
+          <t>10 RUE des Ormes</t>
+        </is>
+      </c>
+      <c r="Y269" s="23" t="inlineStr">
+        <is>
+          <t>57645</t>
+        </is>
+      </c>
+      <c r="Z269" s="22" t="inlineStr">
+        <is>
+          <t>Retonfey</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B270" s="23" t="inlineStr">
+        <is>
+          <t>101043727</t>
+        </is>
+      </c>
+      <c r="C270" s="23" t="inlineStr">
+        <is>
+          <t>10104372700011</t>
+        </is>
+      </c>
+      <c r="D270" s="22" t="inlineStr">
+        <is>
+          <t>TRIPLE M</t>
+        </is>
+      </c>
+      <c r="E270" s="22" t="inlineStr">
+        <is>
+          <t>TRIPLE M</t>
+        </is>
+      </c>
+      <c r="F270" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G270" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H270" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I270" s="22" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="J270" s="22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K270" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DE PARIS</t>
+        </is>
+      </c>
+      <c r="L270" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M270" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N270" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O270" s="22" t="inlineStr"/>
+      <c r="P270" s="22" t="inlineStr"/>
+      <c r="Q270" s="22" t="inlineStr"/>
+      <c r="R270" s="23" t="inlineStr"/>
+      <c r="S270" s="22" t="inlineStr"/>
+      <c r="T270" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U270" s="22" t="inlineStr">
+        <is>
+          <t>BEN OMAR</t>
+        </is>
+      </c>
+      <c r="V270" s="22" t="inlineStr">
+        <is>
+          <t>Ilyess</t>
+        </is>
+      </c>
+      <c r="W270" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X270" s="22" t="inlineStr">
+        <is>
+          <t>9 rue des lisières</t>
+        </is>
+      </c>
+      <c r="Y270" s="23" t="inlineStr">
+        <is>
+          <t>33530</t>
+        </is>
+      </c>
+      <c r="Z270" s="22" t="inlineStr">
+        <is>
+          <t>Bassens</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B271" s="23" t="inlineStr">
+        <is>
+          <t>929593143</t>
+        </is>
+      </c>
+      <c r="C271" s="23" t="inlineStr">
+        <is>
+          <t>92959314300019</t>
+        </is>
+      </c>
+      <c r="D271" s="22" t="inlineStr">
+        <is>
+          <t>SABE FOOD</t>
+        </is>
+      </c>
+      <c r="E271" s="22" t="inlineStr">
+        <is>
+          <t>SABE FOOD</t>
+        </is>
+      </c>
+      <c r="F271" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G271" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H271" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I271" s="22" t="inlineStr">
+        <is>
+          <t>01/06/2024</t>
+        </is>
+      </c>
+      <c r="J271" s="22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K271" s="22" t="inlineStr">
+        <is>
+          <t>3 RUE CLOVIS</t>
+        </is>
+      </c>
+      <c r="L271" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M271" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N271" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O271" s="22" t="inlineStr"/>
+      <c r="P271" s="22" t="inlineStr"/>
+      <c r="Q271" s="22" t="inlineStr"/>
+      <c r="R271" s="23" t="inlineStr"/>
+      <c r="S271" s="22" t="inlineStr"/>
+      <c r="T271" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U271" s="22" t="inlineStr">
+        <is>
+          <t>BATE EBAI</t>
+        </is>
+      </c>
+      <c r="V271" s="22" t="inlineStr">
+        <is>
+          <t>Daniel, Beteck</t>
+        </is>
+      </c>
+      <c r="W271" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X271" s="22" t="inlineStr">
+        <is>
+          <t>7 rue de champagne</t>
+        </is>
+      </c>
+      <c r="Y271" s="23" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="Z271" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B272" s="23" t="inlineStr">
+        <is>
+          <t>941014409</t>
+        </is>
+      </c>
+      <c r="C272" s="23" t="inlineStr">
+        <is>
+          <t>94101440900028</t>
+        </is>
+      </c>
+      <c r="D272" s="22" t="inlineStr">
+        <is>
+          <t>BWMetz</t>
+        </is>
+      </c>
+      <c r="E272" s="22" t="inlineStr">
+        <is>
+          <t>BWMetz</t>
+        </is>
+      </c>
+      <c r="F272" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G272" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H272" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I272" s="22" t="inlineStr">
+        <is>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="J272" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K272" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L272" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M272" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N272" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O272" s="22" t="inlineStr"/>
+      <c r="P272" s="22" t="inlineStr"/>
+      <c r="Q272" s="22" t="inlineStr"/>
+      <c r="R272" s="23" t="inlineStr"/>
+      <c r="S272" s="22" t="inlineStr"/>
+      <c r="T272" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U272" s="22" t="inlineStr">
+        <is>
+          <t>AGMA SERVICES</t>
+        </is>
+      </c>
+      <c r="V272" s="22" t="inlineStr"/>
+      <c r="W272" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X272" s="22" t="inlineStr">
+        <is>
+          <t>64 AV de la Liberté</t>
+        </is>
+      </c>
+      <c r="Y272" s="23" t="inlineStr">
+        <is>
+          <t>L1930</t>
+        </is>
+      </c>
+      <c r="Z272" s="22" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B273" s="23" t="inlineStr">
+        <is>
+          <t>995078458</t>
+        </is>
+      </c>
+      <c r="C273" s="23" t="inlineStr">
+        <is>
+          <t>99507845800016</t>
+        </is>
+      </c>
+      <c r="D273" s="22" t="inlineStr">
+        <is>
+          <t>IL GIGLIO</t>
+        </is>
+      </c>
+      <c r="E273" s="22" t="inlineStr">
+        <is>
+          <t>IL GIGLIO</t>
+        </is>
+      </c>
+      <c r="F273" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G273" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H273" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I273" s="22" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="J273" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K273" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DU CHAMPE</t>
+        </is>
+      </c>
+      <c r="L273" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M273" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N273" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O273" s="22" t="inlineStr"/>
+      <c r="P273" s="22" t="inlineStr"/>
+      <c r="Q273" s="22" t="inlineStr"/>
+      <c r="R273" s="23" t="inlineStr"/>
+      <c r="S273" s="22" t="inlineStr"/>
+      <c r="T273" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U273" s="22" t="inlineStr">
+        <is>
+          <t>STHRUDEL</t>
+        </is>
+      </c>
+      <c r="V273" s="22" t="inlineStr">
+        <is>
+          <t>Marie-claire</t>
+        </is>
+      </c>
+      <c r="W273" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X273" s="22" t="inlineStr">
+        <is>
+          <t>2 b rue maurice barrès</t>
+        </is>
+      </c>
+      <c r="Y273" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z273" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B274" s="23" t="inlineStr">
+        <is>
+          <t>942629916</t>
+        </is>
+      </c>
+      <c r="C274" s="23" t="inlineStr">
+        <is>
+          <t>94262991600019</t>
+        </is>
+      </c>
+      <c r="D274" s="22" t="inlineStr">
+        <is>
+          <t>MEAT HOUSE</t>
+        </is>
+      </c>
+      <c r="E274" s="22" t="inlineStr">
+        <is>
+          <t>MEAT HOUSE</t>
+        </is>
+      </c>
+      <c r="F274" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G274" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H274" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I274" s="22" t="inlineStr">
+        <is>
+          <t>01/04/2025</t>
+        </is>
+      </c>
+      <c r="J274" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K274" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE GAMBETTA</t>
+        </is>
+      </c>
+      <c r="L274" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M274" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N274" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O274" s="22" t="inlineStr"/>
+      <c r="P274" s="22" t="inlineStr"/>
+      <c r="Q274" s="22" t="inlineStr"/>
+      <c r="R274" s="23" t="inlineStr"/>
+      <c r="S274" s="22" t="inlineStr"/>
+      <c r="T274" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U274" s="22" t="inlineStr">
+        <is>
+          <t>ERESLAN</t>
+        </is>
+      </c>
+      <c r="V274" s="22" t="inlineStr">
+        <is>
+          <t>Suleyman</t>
+        </is>
+      </c>
+      <c r="W274" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X274" s="22" t="inlineStr"/>
+      <c r="Y274" s="23" t="inlineStr"/>
+      <c r="Z274" s="22" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B275" s="23" t="inlineStr">
+        <is>
+          <t>483887311</t>
+        </is>
+      </c>
+      <c r="C275" s="23" t="inlineStr">
+        <is>
+          <t>48388731100015</t>
+        </is>
+      </c>
+      <c r="D275" s="22" t="inlineStr">
+        <is>
+          <t>NAMUR FRANCE</t>
+        </is>
+      </c>
+      <c r="E275" s="22" t="inlineStr">
+        <is>
+          <t>NAMUR FRANCE</t>
+        </is>
+      </c>
+      <c r="F275" s="22" t="inlineStr">
+        <is>
+          <t>SAS, société par actions simplifiée</t>
+        </is>
+      </c>
+      <c r="G275" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H275" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I275" s="22" t="inlineStr">
+        <is>
+          <t>01/09/2005</t>
+        </is>
+      </c>
+      <c r="J275" s="22" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K275" s="22" t="inlineStr">
+        <is>
+          <t>7 PLACE DE LA CATHEDRALE</t>
+        </is>
+      </c>
+      <c r="L275" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M275" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N275" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O275" s="22" t="inlineStr"/>
+      <c r="P275" s="22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q275" s="22" t="inlineStr"/>
+      <c r="R275" s="23" t="inlineStr"/>
+      <c r="S275" s="22" t="inlineStr"/>
+      <c r="T275" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U275" s="22" t="inlineStr">
+        <is>
+          <t>NICKELS</t>
+        </is>
+      </c>
+      <c r="V275" s="22" t="inlineStr">
+        <is>
+          <t>Jean, Paul</t>
+        </is>
+      </c>
+      <c r="W275" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X275" s="22" t="inlineStr"/>
+      <c r="Y275" s="23" t="inlineStr">
+        <is>
+          <t>8181</t>
+        </is>
+      </c>
+      <c r="Z275" s="22" t="inlineStr">
+        <is>
+          <t>L 8131 BRIDEL (LUXEMBOURG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B276" s="23" t="inlineStr">
+        <is>
+          <t>381870401</t>
+        </is>
+      </c>
+      <c r="C276" s="23" t="inlineStr">
+        <is>
+          <t>38187040100027</t>
+        </is>
+      </c>
+      <c r="D276" s="22" t="inlineStr">
+        <is>
+          <t>D'ARGENTEAU</t>
+        </is>
+      </c>
+      <c r="E276" s="22" t="inlineStr">
+        <is>
+          <t>D'ARGENTEAU</t>
+        </is>
+      </c>
+      <c r="F276" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G276" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H276" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I276" s="22" t="inlineStr">
+        <is>
+          <t>30/04/1991</t>
+        </is>
+      </c>
+      <c r="J276" s="22" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="K276" s="22" t="inlineStr">
+        <is>
+          <t>1 RUE DU PALAIS</t>
+        </is>
+      </c>
+      <c r="L276" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M276" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N276" s="22" t="inlineStr">
+        <is>
+          <t>Entre 20 et 49 salariés</t>
+        </is>
+      </c>
+      <c r="O276" s="22" t="n">
+        <v>2360012</v>
+      </c>
+      <c r="P276" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q276" s="22" t="inlineStr"/>
+      <c r="R276" s="23" t="inlineStr"/>
+      <c r="S276" s="22" t="inlineStr"/>
+      <c r="T276" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U276" s="22" t="inlineStr">
+        <is>
+          <t>GEHIN</t>
+        </is>
+      </c>
+      <c r="V276" s="22" t="inlineStr">
+        <is>
+          <t>Frédéric, Bernard</t>
+        </is>
+      </c>
+      <c r="W276" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X276" s="22" t="inlineStr">
+        <is>
+          <t>50 rue de Verdun</t>
+        </is>
+      </c>
+      <c r="Y276" s="23" t="inlineStr">
+        <is>
+          <t>57160</t>
+        </is>
+      </c>
+      <c r="Z276" s="22" t="inlineStr">
+        <is>
+          <t>Moulins-lès-Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B277" s="23" t="inlineStr">
+        <is>
+          <t>749887006</t>
+        </is>
+      </c>
+      <c r="C277" s="23" t="inlineStr">
+        <is>
+          <t>74988700600015</t>
+        </is>
+      </c>
+      <c r="D277" s="22" t="inlineStr">
+        <is>
+          <t>LE PALAIS DU SOLEIL (SOCIETE EN LIQUIDATION)</t>
+        </is>
+      </c>
+      <c r="E277" s="22" t="inlineStr">
+        <is>
+          <t>LE PALAIS DU SOLEIL (SOCIETE EN LIQUIDATION)</t>
+        </is>
+      </c>
+      <c r="F277" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G277" s="22" t="inlineStr">
+        <is>
+          <t>56.10C</t>
+        </is>
+      </c>
+      <c r="H277" s="22" t="inlineStr">
+        <is>
+          <t>Restauration de type rapide</t>
+        </is>
+      </c>
+      <c r="I277" s="22" t="inlineStr">
+        <is>
+          <t>01/01/2012</t>
+        </is>
+      </c>
+      <c r="J277" s="22" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K277" s="22" t="inlineStr">
+        <is>
+          <t>23 RUE DU PONT DES MORTS</t>
+        </is>
+      </c>
+      <c r="L277" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M277" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N277" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O277" s="22" t="inlineStr"/>
+      <c r="P277" s="22" t="inlineStr"/>
+      <c r="Q277" s="22" t="inlineStr"/>
+      <c r="R277" s="23" t="inlineStr"/>
+      <c r="S277" s="22" t="inlineStr"/>
+      <c r="T277" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U277" s="22" t="inlineStr">
+        <is>
+          <t>MAHMOOD</t>
+        </is>
+      </c>
+      <c r="V277" s="22" t="inlineStr">
+        <is>
+          <t>Abbas</t>
+        </is>
+      </c>
+      <c r="W277" s="22" t="inlineStr">
+        <is>
+          <t>Liquidateur</t>
+        </is>
+      </c>
+      <c r="X277" s="22" t="inlineStr">
+        <is>
+          <t>23 rue du Pont des Morts</t>
+        </is>
+      </c>
+      <c r="Y277" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z277" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B278" s="23" t="inlineStr">
+        <is>
+          <t>884426107</t>
+        </is>
+      </c>
+      <c r="C278" s="23" t="inlineStr">
+        <is>
+          <t>88442610700014</t>
+        </is>
+      </c>
+      <c r="D278" s="22" t="inlineStr">
+        <is>
+          <t>FRASANABAR</t>
+        </is>
+      </c>
+      <c r="E278" s="22" t="inlineStr">
+        <is>
+          <t>FRASANABAR</t>
+        </is>
+      </c>
+      <c r="F278" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G278" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H278" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I278" s="22" t="inlineStr">
+        <is>
+          <t>19/06/2020</t>
+        </is>
+      </c>
+      <c r="J278" s="22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K278" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE SAINTE MARIE</t>
+        </is>
+      </c>
+      <c r="L278" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M278" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N278" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O278" s="22" t="inlineStr"/>
+      <c r="P278" s="22" t="inlineStr"/>
+      <c r="Q278" s="22" t="inlineStr"/>
+      <c r="R278" s="23" t="inlineStr"/>
+      <c r="S278" s="22" t="inlineStr"/>
+      <c r="T278" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U278" s="22" t="inlineStr">
+        <is>
+          <t>SERURIER</t>
+        </is>
+      </c>
+      <c r="V278" s="22" t="inlineStr">
+        <is>
+          <t>Franck</t>
+        </is>
+      </c>
+      <c r="W278" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X278" s="22" t="inlineStr">
+        <is>
+          <t>45 Grande Rue Grand Rue</t>
+        </is>
+      </c>
+      <c r="Y278" s="23" t="inlineStr">
+        <is>
+          <t>54470</t>
+        </is>
+      </c>
+      <c r="Z278" s="22" t="inlineStr">
+        <is>
+          <t>Limey-Remenauville</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B279" s="23" t="inlineStr">
+        <is>
+          <t>830223871</t>
+        </is>
+      </c>
+      <c r="C279" s="23" t="inlineStr">
+        <is>
+          <t>83022387100013</t>
+        </is>
+      </c>
+      <c r="D279" s="22" t="inlineStr">
+        <is>
+          <t>AVENUE CAFE DE NANCY</t>
+        </is>
+      </c>
+      <c r="E279" s="22" t="inlineStr">
+        <is>
+          <t>AVENUE CAFE DE NANCY</t>
+        </is>
+      </c>
+      <c r="F279" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G279" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H279" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I279" s="22" t="inlineStr">
+        <is>
+          <t>13/06/2017</t>
+        </is>
+      </c>
+      <c r="J279" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K279" s="22" t="inlineStr">
+        <is>
+          <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
+        </is>
+      </c>
+      <c r="L279" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M279" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N279" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O279" s="22" t="inlineStr"/>
+      <c r="P279" s="22" t="inlineStr"/>
+      <c r="Q279" s="22" t="inlineStr"/>
+      <c r="R279" s="23" t="inlineStr"/>
+      <c r="S279" s="22" t="inlineStr"/>
+      <c r="T279" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U279" s="22" t="inlineStr">
+        <is>
+          <t>ALLALI</t>
+        </is>
+      </c>
+      <c r="V279" s="22" t="inlineStr">
+        <is>
+          <t>Nasser</t>
+        </is>
+      </c>
+      <c r="W279" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X279" s="22" t="inlineStr">
+        <is>
+          <t>10 rue Dupont des Loges</t>
+        </is>
+      </c>
+      <c r="Y279" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z279" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B280" s="23" t="inlineStr">
+        <is>
+          <t>981763824</t>
+        </is>
+      </c>
+      <c r="C280" s="23" t="inlineStr">
+        <is>
+          <t>98176382400019</t>
+        </is>
+      </c>
+      <c r="D280" s="22" t="inlineStr">
+        <is>
+          <t>LE BISTROT DES AMIS</t>
+        </is>
+      </c>
+      <c r="E280" s="22" t="inlineStr">
+        <is>
+          <t>LE BISTROT DES AMIS</t>
+        </is>
+      </c>
+      <c r="F280" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G280" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H280" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I280" s="22" t="inlineStr">
+        <is>
+          <t>20/11/2023</t>
+        </is>
+      </c>
+      <c r="J280" s="22" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K280" s="22" t="inlineStr">
+        <is>
+          <t>37 RUE DE LA CHAPELLE</t>
+        </is>
+      </c>
+      <c r="L280" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M280" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N280" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O280" s="22" t="inlineStr"/>
+      <c r="P280" s="22" t="inlineStr"/>
+      <c r="Q280" s="22" t="inlineStr"/>
+      <c r="R280" s="23" t="inlineStr"/>
+      <c r="S280" s="22" t="inlineStr"/>
+      <c r="T280" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U280" s="22" t="inlineStr">
+        <is>
+          <t>YILDIRIM</t>
+        </is>
+      </c>
+      <c r="V280" s="22" t="inlineStr">
+        <is>
+          <t>Ilfer</t>
+        </is>
+      </c>
+      <c r="W280" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X280" s="22" t="inlineStr">
+        <is>
+          <t>134 avenue andre malraux</t>
+        </is>
+      </c>
+      <c r="Y280" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z280" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B281" s="23" t="inlineStr">
+        <is>
+          <t>823430798</t>
+        </is>
+      </c>
+      <c r="C281" s="23" t="inlineStr">
+        <is>
+          <t>82343079800012</t>
+        </is>
+      </c>
+      <c r="D281" s="22" t="inlineStr">
+        <is>
+          <t>LES TROIS MOUSSEQUETAIRES</t>
+        </is>
+      </c>
+      <c r="E281" s="22" t="inlineStr">
+        <is>
+          <t>LES TROIS MOUSSEQUETAIRES</t>
+        </is>
+      </c>
+      <c r="F281" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G281" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H281" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I281" s="22" t="inlineStr">
+        <is>
+          <t>21/10/2016</t>
+        </is>
+      </c>
+      <c r="J281" s="22" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K281" s="22" t="inlineStr">
+        <is>
+          <t>18 RUE TAISON</t>
+        </is>
+      </c>
+      <c r="L281" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M281" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N281" s="22" t="inlineStr">
+        <is>
+          <t>Entre 6 et 9 salariés</t>
+        </is>
+      </c>
+      <c r="O281" s="22" t="inlineStr"/>
+      <c r="P281" s="22" t="inlineStr"/>
+      <c r="Q281" s="22" t="inlineStr"/>
+      <c r="R281" s="23" t="inlineStr"/>
+      <c r="S281" s="22" t="inlineStr"/>
+      <c r="T281" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U281" s="22" t="inlineStr">
+        <is>
+          <t>PILLET</t>
+        </is>
+      </c>
+      <c r="V281" s="22" t="inlineStr">
+        <is>
+          <t>Baptiste, André, Michel</t>
+        </is>
+      </c>
+      <c r="W281" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X281" s="22" t="inlineStr">
+        <is>
+          <t>9 Rue du Pont des Morts</t>
+        </is>
+      </c>
+      <c r="Y281" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z281" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B282" s="23" t="inlineStr">
+        <is>
+          <t>834496119</t>
+        </is>
+      </c>
+      <c r="C282" s="23" t="inlineStr">
+        <is>
+          <t>83449611900019</t>
+        </is>
+      </c>
+      <c r="D282" s="22" t="inlineStr">
+        <is>
+          <t>SAMOX</t>
+        </is>
+      </c>
+      <c r="E282" s="22" t="inlineStr">
+        <is>
+          <t>SAMOX</t>
+        </is>
+      </c>
+      <c r="F282" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G282" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H282" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I282" s="22" t="inlineStr">
+        <is>
+          <t>10/01/2018</t>
+        </is>
+      </c>
+      <c r="J282" s="22" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K282" s="22" t="inlineStr">
+        <is>
+          <t>4 RUE DU CHANGE</t>
+        </is>
+      </c>
+      <c r="L282" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M282" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N282" s="22" t="inlineStr">
+        <is>
+          <t>Entre 3 et 5 salariés</t>
+        </is>
+      </c>
+      <c r="O282" s="22" t="inlineStr"/>
+      <c r="P282" s="22" t="inlineStr"/>
+      <c r="Q282" s="22" t="inlineStr"/>
+      <c r="R282" s="23" t="inlineStr"/>
+      <c r="S282" s="22" t="inlineStr"/>
+      <c r="T282" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U282" s="22" t="inlineStr">
+        <is>
+          <t>DURAL</t>
+        </is>
+      </c>
+      <c r="V282" s="22" t="inlineStr">
+        <is>
+          <t>Mahsum</t>
+        </is>
+      </c>
+      <c r="W282" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X282" s="22" t="inlineStr">
+        <is>
+          <t>11 rue de Pont à Mousson</t>
+        </is>
+      </c>
+      <c r="Y282" s="23" t="inlineStr">
+        <is>
+          <t>57380</t>
+        </is>
+      </c>
+      <c r="Z282" s="22" t="inlineStr">
+        <is>
+          <t>Faulquemont</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B283" s="23" t="inlineStr">
+        <is>
+          <t>500497961</t>
+        </is>
+      </c>
+      <c r="C283" s="23" t="inlineStr">
+        <is>
+          <t>50049796100010</t>
+        </is>
+      </c>
+      <c r="D283" s="22" t="inlineStr">
+        <is>
+          <t>FOETZ Joel</t>
+        </is>
+      </c>
+      <c r="E283" s="22" t="inlineStr">
+        <is>
+          <t>FOETZ Joel</t>
+        </is>
+      </c>
+      <c r="F283" s="22" t="inlineStr">
+        <is>
+          <t>Entrepreneur individuel</t>
+        </is>
+      </c>
+      <c r="G283" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H283" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I283" s="22" t="inlineStr">
+        <is>
+          <t>28/09/2007</t>
+        </is>
+      </c>
+      <c r="J283" s="22" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K283" s="22" t="inlineStr">
+        <is>
+          <t>27 RUE LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="L283" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M283" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N283" s="22" t="inlineStr">
+        <is>
+          <t>0 salarié</t>
+        </is>
+      </c>
+      <c r="O283" s="22" t="inlineStr"/>
+      <c r="P283" s="22" t="inlineStr"/>
+      <c r="Q283" s="22" t="inlineStr"/>
+      <c r="R283" s="23" t="inlineStr"/>
+      <c r="S283" s="22" t="inlineStr"/>
+      <c r="T283" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U283" s="22" t="inlineStr">
+        <is>
+          <t>FOETZ</t>
+        </is>
+      </c>
+      <c r="V283" s="22" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="W283" s="22" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise</t>
+        </is>
+      </c>
+      <c r="X283" s="22" t="inlineStr"/>
+      <c r="Y283" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z283" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B284" s="23" t="inlineStr">
+        <is>
+          <t>992901124</t>
+        </is>
+      </c>
+      <c r="C284" s="23" t="inlineStr">
+        <is>
+          <t>99290112400014</t>
+        </is>
+      </c>
+      <c r="D284" s="22" t="inlineStr">
+        <is>
+          <t>JBCED</t>
+        </is>
+      </c>
+      <c r="E284" s="22" t="inlineStr">
+        <is>
+          <t>JBCED</t>
+        </is>
+      </c>
+      <c r="F284" s="22" t="inlineStr">
+        <is>
+          <t>SARL, société à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G284" s="22" t="inlineStr">
+        <is>
+          <t>56.30Z</t>
+        </is>
+      </c>
+      <c r="H284" s="22" t="inlineStr">
+        <is>
+          <t>Débits de boissons</t>
+        </is>
+      </c>
+      <c r="I284" s="22" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="J284" s="22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K284" s="22" t="inlineStr">
+        <is>
+          <t>5 RUE DE LA FONTAINE</t>
+        </is>
+      </c>
+      <c r="L284" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M284" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N284" s="22" t="inlineStr">
+        <is>
+          <t>Au moins 1 salarié</t>
+        </is>
+      </c>
+      <c r="O284" s="22" t="inlineStr"/>
+      <c r="P284" s="22" t="inlineStr"/>
+      <c r="Q284" s="22" t="inlineStr"/>
+      <c r="R284" s="23" t="inlineStr"/>
+      <c r="S284" s="22" t="inlineStr"/>
+      <c r="T284" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U284" s="22" t="inlineStr">
+        <is>
+          <t>HEITZMANN</t>
+        </is>
+      </c>
+      <c r="V284" s="22" t="inlineStr">
+        <is>
+          <t>Jean-baptiste, Angel, André</t>
+        </is>
+      </c>
+      <c r="W284" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X284" s="22" t="inlineStr">
+        <is>
+          <t>3, rue de la fontaine</t>
+        </is>
+      </c>
+      <c r="Y284" s="23" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z284" s="22" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B285" s="23" t="inlineStr">
+        <is>
+          <t>309444545</t>
+        </is>
+      </c>
+      <c r="C285" s="23" t="inlineStr">
+        <is>
+          <t>30944454500011</t>
+        </is>
+      </c>
+      <c r="D285" s="22" t="inlineStr">
+        <is>
+          <t>LA TOSCANE</t>
+        </is>
+      </c>
+      <c r="E285" s="22" t="inlineStr">
+        <is>
+          <t>LA TOSCANE</t>
+        </is>
+      </c>
+      <c r="F285" s="22" t="inlineStr">
+        <is>
+          <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
+        </is>
+      </c>
+      <c r="G285" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H285" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I285" s="22" t="inlineStr">
+        <is>
+          <t>01/01/1977</t>
+        </is>
+      </c>
+      <c r="J285" s="22" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="K285" s="22" t="inlineStr">
+        <is>
+          <t>12 RUE DUPONT DES LOGES</t>
+        </is>
+      </c>
+      <c r="L285" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M285" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N285" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O285" s="22" t="inlineStr"/>
+      <c r="P285" s="22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q285" s="22" t="inlineStr"/>
+      <c r="R285" s="23" t="inlineStr"/>
+      <c r="S285" s="22" t="inlineStr"/>
+      <c r="T285" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U285" s="22" t="inlineStr">
+        <is>
+          <t>Belkacem</t>
+        </is>
+      </c>
+      <c r="V285" s="22" t="inlineStr">
+        <is>
+          <t>Mohand, -, Larbi</t>
+        </is>
+      </c>
+      <c r="W285" s="22" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="X285" s="22" t="inlineStr"/>
+      <c r="Y285" s="23" t="inlineStr">
+        <is>
+          <t>92200</t>
+        </is>
+      </c>
+      <c r="Z285" s="22" t="inlineStr">
+        <is>
+          <t>Neuilly-sur-Seine</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B286" s="23" t="inlineStr">
+        <is>
+          <t>830776167</t>
+        </is>
+      </c>
+      <c r="C286" s="23" t="inlineStr">
+        <is>
+          <t>83077616700017</t>
+        </is>
+      </c>
+      <c r="D286" s="22" t="inlineStr">
+        <is>
+          <t>AS MUSE</t>
+        </is>
+      </c>
+      <c r="E286" s="22" t="inlineStr">
+        <is>
+          <t>AS MUSE</t>
+        </is>
+      </c>
+      <c r="F286" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G286" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H286" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I286" s="22" t="inlineStr">
+        <is>
+          <t>06/06/2017</t>
+        </is>
+      </c>
+      <c r="J286" s="22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="K286" s="22" t="inlineStr">
+        <is>
+          <t>2 RUE DES MESSAGERIES</t>
+        </is>
+      </c>
+      <c r="L286" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M286" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N286" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O286" s="22" t="inlineStr"/>
+      <c r="P286" s="22" t="n">
         <v>2024</v>
       </c>
-      <c r="Q267" s="22" t="inlineStr"/>
-      <c r="R267" s="23" t="inlineStr"/>
-      <c r="S267" s="22" t="inlineStr"/>
-      <c r="T267" s="22" t="inlineStr">
+      <c r="Q286" s="22" t="inlineStr"/>
+      <c r="R286" s="23" t="inlineStr"/>
+      <c r="S286" s="22" t="inlineStr"/>
+      <c r="T286" s="22" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U267" s="22" t="inlineStr">
-        <is>
-          <t>YE</t>
-        </is>
-      </c>
-      <c r="V267" s="22" t="inlineStr">
-        <is>
-          <t>Junda</t>
-        </is>
-      </c>
-      <c r="W267" s="22" t="inlineStr">
-        <is>
-          <t>Gérant</t>
-        </is>
-      </c>
-      <c r="X267" s="22" t="inlineStr">
-        <is>
-          <t>41 Rue du Potier</t>
-        </is>
-      </c>
-      <c r="Y267" s="23" t="inlineStr">
-        <is>
-          <t>93150</t>
-        </is>
-      </c>
-      <c r="Z267" s="22" t="inlineStr">
-        <is>
-          <t>Le Blanc-Mesnil</t>
+      <c r="U286" s="22" t="inlineStr">
+        <is>
+          <t>SLAKX</t>
+        </is>
+      </c>
+      <c r="V286" s="22" t="inlineStr"/>
+      <c r="W286" s="22" t="inlineStr">
+        <is>
+          <t>Président</t>
+        </is>
+      </c>
+      <c r="X286" s="22" t="inlineStr">
+        <is>
+          <t>19 Rue de la Louvière</t>
+        </is>
+      </c>
+      <c r="Y286" s="23" t="inlineStr">
+        <is>
+          <t>57280</t>
+        </is>
+      </c>
+      <c r="Z286" s="22" t="inlineStr">
+        <is>
+          <t>Semécourt</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B287" s="23" t="inlineStr">
+        <is>
+          <t>850564261</t>
+        </is>
+      </c>
+      <c r="C287" s="23" t="inlineStr">
+        <is>
+          <t>85056426100020</t>
+        </is>
+      </c>
+      <c r="D287" s="22" t="inlineStr">
+        <is>
+          <t>CITY'REST</t>
+        </is>
+      </c>
+      <c r="E287" s="22" t="inlineStr">
+        <is>
+          <t>CITY'REST</t>
+        </is>
+      </c>
+      <c r="F287" s="22" t="inlineStr">
+        <is>
+          <t>SASU, société par actions simplifiée unipersonnelle</t>
+        </is>
+      </c>
+      <c r="G287" s="22" t="inlineStr">
+        <is>
+          <t>56.10A</t>
+        </is>
+      </c>
+      <c r="H287" s="22" t="inlineStr">
+        <is>
+          <t>Restauration traditionnelle</t>
+        </is>
+      </c>
+      <c r="I287" s="22" t="inlineStr">
+        <is>
+          <t>07/05/2019</t>
+        </is>
+      </c>
+      <c r="J287" s="22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K287" s="22" t="inlineStr">
+        <is>
+          <t>14 RUE MARGUERITE PUHL-DEMANGE</t>
+        </is>
+      </c>
+      <c r="L287" s="22" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M287" s="22" t="inlineStr">
+        <is>
+          <t>METZ</t>
+        </is>
+      </c>
+      <c r="N287" s="22" t="inlineStr">
+        <is>
+          <t>Entre 10 et 19 salariés</t>
+        </is>
+      </c>
+      <c r="O287" s="22" t="n">
+        <v>902183</v>
+      </c>
+      <c r="P287" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q287" s="22" t="inlineStr"/>
+      <c r="R287" s="23" t="inlineStr"/>
+      <c r="S287" s="22" t="inlineStr"/>
+      <c r="T287" s="22" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="U287" s="22" t="inlineStr">
+        <is>
+          <t>LOMUSCIO</t>
+        </is>
+      </c>
+      <c r="V287" s="22" t="inlineStr">
+        <is>
+          <t>Riccardo</t>
+        </is>
+      </c>
+      <c r="W287" s="22" t="inlineStr">
+        <is>
+          <t>Directeur général</t>
+        </is>
+      </c>
+      <c r="X287" s="22" t="inlineStr">
+        <is>
+          <t>51 rue paul verlaine</t>
+        </is>
+      </c>
+      <c r="Y287" s="23" t="inlineStr">
+        <is>
+          <t>57310</t>
+        </is>
+      </c>
+      <c r="Z287" s="22" t="inlineStr">
+        <is>
+          <t>Rurange-lès-Thionville</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z267"/>
+  <autoFilter ref="A2:Z287"/>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="U1:Z1"/>

--- a/data/restaurants_metz.xlsx
+++ b/data/restaurants_metz.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Restaurants Metz" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurants Metz'!$A$2:$Z$307</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z287"/>
+  <dimension ref="A1:Z307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30454,2225 +30454,4475 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="22" t="inlineStr">
+      <c r="A268" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B268" s="23" t="inlineStr">
+      <c r="B268" s="21" t="inlineStr">
         <is>
           <t>832795587</t>
         </is>
       </c>
-      <c r="C268" s="23" t="inlineStr">
+      <c r="C268" s="21" t="inlineStr">
         <is>
           <t>83279558700019</t>
         </is>
       </c>
-      <c r="D268" s="22" t="inlineStr">
+      <c r="D268" s="20" t="inlineStr">
         <is>
           <t>SITWELL</t>
         </is>
       </c>
-      <c r="E268" s="22" t="inlineStr">
+      <c r="E268" s="20" t="inlineStr">
         <is>
           <t>SITWELL</t>
         </is>
       </c>
-      <c r="F268" s="22" t="inlineStr">
+      <c r="F268" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G268" s="22" t="inlineStr">
+      <c r="G268" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H268" s="22" t="inlineStr">
+      <c r="H268" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I268" s="22" t="inlineStr">
+      <c r="I268" s="20" t="inlineStr">
         <is>
           <t>25/09/2017</t>
         </is>
       </c>
-      <c r="J268" s="22" t="inlineStr">
+      <c r="J268" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K268" s="22" t="inlineStr">
+      <c r="K268" s="20" t="inlineStr">
         <is>
           <t>12 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L268" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M268" s="22" t="inlineStr">
+      <c r="L268" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M268" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N268" s="22" t="inlineStr">
+      <c r="N268" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O268" s="22" t="inlineStr"/>
-      <c r="P268" s="22" t="inlineStr"/>
-      <c r="Q268" s="22" t="inlineStr"/>
-      <c r="R268" s="23" t="inlineStr"/>
-      <c r="S268" s="22" t="inlineStr"/>
-      <c r="T268" s="22" t="inlineStr">
+      <c r="O268" s="20" t="inlineStr"/>
+      <c r="P268" s="20" t="inlineStr"/>
+      <c r="Q268" s="20" t="inlineStr"/>
+      <c r="R268" s="21" t="inlineStr"/>
+      <c r="S268" s="20" t="inlineStr"/>
+      <c r="T268" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U268" s="22" t="inlineStr">
+      <c r="U268" s="20" t="inlineStr">
         <is>
           <t>MECHKENE</t>
         </is>
       </c>
-      <c r="V268" s="22" t="inlineStr">
+      <c r="V268" s="20" t="inlineStr">
         <is>
           <t>Raouf</t>
         </is>
       </c>
-      <c r="W268" s="22" t="inlineStr">
+      <c r="W268" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X268" s="22" t="inlineStr">
+      <c r="X268" s="20" t="inlineStr">
         <is>
           <t>6 En Froide Ruelle</t>
         </is>
       </c>
-      <c r="Y268" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z268" s="22" t="inlineStr">
+      <c r="Y268" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z268" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="22" t="inlineStr">
+      <c r="A269" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B269" s="23" t="inlineStr">
+      <c r="B269" s="21" t="inlineStr">
         <is>
           <t>937636165</t>
         </is>
       </c>
-      <c r="C269" s="23" t="inlineStr">
+      <c r="C269" s="21" t="inlineStr">
         <is>
           <t>93763616500022</t>
         </is>
       </c>
-      <c r="D269" s="22" t="inlineStr">
+      <c r="D269" s="20" t="inlineStr">
         <is>
           <t>B'CHETTES</t>
         </is>
       </c>
-      <c r="E269" s="22" t="inlineStr">
+      <c r="E269" s="20" t="inlineStr">
         <is>
           <t>B'CHETTES</t>
         </is>
       </c>
-      <c r="F269" s="22" t="inlineStr">
+      <c r="F269" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G269" s="22" t="inlineStr">
+      <c r="G269" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H269" s="22" t="inlineStr">
+      <c r="H269" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I269" s="22" t="inlineStr">
+      <c r="I269" s="20" t="inlineStr">
         <is>
           <t>01/11/2024</t>
         </is>
       </c>
-      <c r="J269" s="22" t="inlineStr">
+      <c r="J269" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K269" s="22" t="inlineStr">
+      <c r="K269" s="20" t="inlineStr">
         <is>
           <t>81 RUE DU XXEME CORPS AMERICAIN</t>
         </is>
       </c>
-      <c r="L269" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M269" s="22" t="inlineStr">
+      <c r="L269" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M269" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N269" s="22" t="inlineStr">
+      <c r="N269" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O269" s="22" t="inlineStr"/>
-      <c r="P269" s="22" t="inlineStr"/>
-      <c r="Q269" s="22" t="inlineStr"/>
-      <c r="R269" s="23" t="inlineStr"/>
-      <c r="S269" s="22" t="inlineStr"/>
-      <c r="T269" s="22" t="inlineStr">
+      <c r="O269" s="20" t="inlineStr"/>
+      <c r="P269" s="20" t="inlineStr"/>
+      <c r="Q269" s="20" t="inlineStr"/>
+      <c r="R269" s="21" t="inlineStr"/>
+      <c r="S269" s="20" t="inlineStr"/>
+      <c r="T269" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U269" s="22" t="inlineStr">
+      <c r="U269" s="20" t="inlineStr">
         <is>
           <t>DOUM HOLDING</t>
         </is>
       </c>
-      <c r="V269" s="22" t="inlineStr"/>
-      <c r="W269" s="22" t="inlineStr">
+      <c r="V269" s="20" t="inlineStr"/>
+      <c r="W269" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X269" s="22" t="inlineStr">
+      <c r="X269" s="20" t="inlineStr">
         <is>
           <t>10 RUE des Ormes</t>
         </is>
       </c>
-      <c r="Y269" s="23" t="inlineStr">
+      <c r="Y269" s="21" t="inlineStr">
         <is>
           <t>57645</t>
         </is>
       </c>
-      <c r="Z269" s="22" t="inlineStr">
+      <c r="Z269" s="20" t="inlineStr">
         <is>
           <t>Retonfey</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="22" t="inlineStr">
+      <c r="A270" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B270" s="23" t="inlineStr">
+      <c r="B270" s="21" t="inlineStr">
         <is>
           <t>101043727</t>
         </is>
       </c>
-      <c r="C270" s="23" t="inlineStr">
+      <c r="C270" s="21" t="inlineStr">
         <is>
           <t>10104372700011</t>
         </is>
       </c>
-      <c r="D270" s="22" t="inlineStr">
+      <c r="D270" s="20" t="inlineStr">
         <is>
           <t>TRIPLE M</t>
         </is>
       </c>
-      <c r="E270" s="22" t="inlineStr">
+      <c r="E270" s="20" t="inlineStr">
         <is>
           <t>TRIPLE M</t>
         </is>
       </c>
-      <c r="F270" s="22" t="inlineStr">
+      <c r="F270" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G270" s="22" t="inlineStr">
+      <c r="G270" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H270" s="22" t="inlineStr">
+      <c r="H270" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I270" s="22" t="inlineStr">
+      <c r="I270" s="20" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="J270" s="22" t="inlineStr">
+      <c r="J270" s="20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K270" s="22" t="inlineStr">
+      <c r="K270" s="20" t="inlineStr">
         <is>
           <t>2 RUE DE PARIS</t>
         </is>
       </c>
-      <c r="L270" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M270" s="22" t="inlineStr">
+      <c r="L270" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M270" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N270" s="22" t="inlineStr">
+      <c r="N270" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O270" s="22" t="inlineStr"/>
-      <c r="P270" s="22" t="inlineStr"/>
-      <c r="Q270" s="22" t="inlineStr"/>
-      <c r="R270" s="23" t="inlineStr"/>
-      <c r="S270" s="22" t="inlineStr"/>
-      <c r="T270" s="22" t="inlineStr">
+      <c r="O270" s="20" t="inlineStr"/>
+      <c r="P270" s="20" t="inlineStr"/>
+      <c r="Q270" s="20" t="inlineStr"/>
+      <c r="R270" s="21" t="inlineStr"/>
+      <c r="S270" s="20" t="inlineStr"/>
+      <c r="T270" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U270" s="22" t="inlineStr">
+      <c r="U270" s="20" t="inlineStr">
         <is>
           <t>BEN OMAR</t>
         </is>
       </c>
-      <c r="V270" s="22" t="inlineStr">
+      <c r="V270" s="20" t="inlineStr">
         <is>
           <t>Ilyess</t>
         </is>
       </c>
-      <c r="W270" s="22" t="inlineStr">
+      <c r="W270" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X270" s="22" t="inlineStr">
+      <c r="X270" s="20" t="inlineStr">
         <is>
           <t>9 rue des lisières</t>
         </is>
       </c>
-      <c r="Y270" s="23" t="inlineStr">
+      <c r="Y270" s="21" t="inlineStr">
         <is>
           <t>33530</t>
         </is>
       </c>
-      <c r="Z270" s="22" t="inlineStr">
+      <c r="Z270" s="20" t="inlineStr">
         <is>
           <t>Bassens</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="22" t="inlineStr">
+      <c r="A271" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B271" s="23" t="inlineStr">
+      <c r="B271" s="21" t="inlineStr">
         <is>
           <t>929593143</t>
         </is>
       </c>
-      <c r="C271" s="23" t="inlineStr">
+      <c r="C271" s="21" t="inlineStr">
         <is>
           <t>92959314300019</t>
         </is>
       </c>
-      <c r="D271" s="22" t="inlineStr">
+      <c r="D271" s="20" t="inlineStr">
         <is>
           <t>SABE FOOD</t>
         </is>
       </c>
-      <c r="E271" s="22" t="inlineStr">
+      <c r="E271" s="20" t="inlineStr">
         <is>
           <t>SABE FOOD</t>
         </is>
       </c>
-      <c r="F271" s="22" t="inlineStr">
+      <c r="F271" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G271" s="22" t="inlineStr">
+      <c r="G271" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H271" s="22" t="inlineStr">
+      <c r="H271" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I271" s="22" t="inlineStr">
+      <c r="I271" s="20" t="inlineStr">
         <is>
           <t>01/06/2024</t>
         </is>
       </c>
-      <c r="J271" s="22" t="inlineStr">
+      <c r="J271" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K271" s="22" t="inlineStr">
+      <c r="K271" s="20" t="inlineStr">
         <is>
           <t>3 RUE CLOVIS</t>
         </is>
       </c>
-      <c r="L271" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M271" s="22" t="inlineStr">
+      <c r="L271" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M271" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N271" s="22" t="inlineStr">
+      <c r="N271" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O271" s="22" t="inlineStr"/>
-      <c r="P271" s="22" t="inlineStr"/>
-      <c r="Q271" s="22" t="inlineStr"/>
-      <c r="R271" s="23" t="inlineStr"/>
-      <c r="S271" s="22" t="inlineStr"/>
-      <c r="T271" s="22" t="inlineStr">
+      <c r="O271" s="20" t="inlineStr"/>
+      <c r="P271" s="20" t="inlineStr"/>
+      <c r="Q271" s="20" t="inlineStr"/>
+      <c r="R271" s="21" t="inlineStr"/>
+      <c r="S271" s="20" t="inlineStr"/>
+      <c r="T271" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U271" s="22" t="inlineStr">
+      <c r="U271" s="20" t="inlineStr">
         <is>
           <t>BATE EBAI</t>
         </is>
       </c>
-      <c r="V271" s="22" t="inlineStr">
+      <c r="V271" s="20" t="inlineStr">
         <is>
           <t>Daniel, Beteck</t>
         </is>
       </c>
-      <c r="W271" s="22" t="inlineStr">
+      <c r="W271" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X271" s="22" t="inlineStr">
+      <c r="X271" s="20" t="inlineStr">
         <is>
           <t>7 rue de champagne</t>
         </is>
       </c>
-      <c r="Y271" s="23" t="inlineStr">
+      <c r="Y271" s="21" t="inlineStr">
         <is>
           <t>57070</t>
         </is>
       </c>
-      <c r="Z271" s="22" t="inlineStr">
+      <c r="Z271" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="22" t="inlineStr">
+      <c r="A272" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B272" s="23" t="inlineStr">
+      <c r="B272" s="21" t="inlineStr">
         <is>
           <t>941014409</t>
         </is>
       </c>
-      <c r="C272" s="23" t="inlineStr">
+      <c r="C272" s="21" t="inlineStr">
         <is>
           <t>94101440900028</t>
         </is>
       </c>
-      <c r="D272" s="22" t="inlineStr">
+      <c r="D272" s="20" t="inlineStr">
         <is>
           <t>BWMetz</t>
         </is>
       </c>
-      <c r="E272" s="22" t="inlineStr">
+      <c r="E272" s="20" t="inlineStr">
         <is>
           <t>BWMetz</t>
         </is>
       </c>
-      <c r="F272" s="22" t="inlineStr">
+      <c r="F272" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G272" s="22" t="inlineStr">
+      <c r="G272" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H272" s="22" t="inlineStr">
+      <c r="H272" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I272" s="22" t="inlineStr">
+      <c r="I272" s="20" t="inlineStr">
         <is>
           <t>10/02/2025</t>
         </is>
       </c>
-      <c r="J272" s="22" t="inlineStr">
+      <c r="J272" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K272" s="22" t="inlineStr">
+      <c r="K272" s="20" t="inlineStr">
         <is>
           <t>2 RUE DES MESSAGERIES</t>
         </is>
       </c>
-      <c r="L272" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M272" s="22" t="inlineStr">
+      <c r="L272" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M272" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N272" s="22" t="inlineStr">
+      <c r="N272" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O272" s="22" t="inlineStr"/>
-      <c r="P272" s="22" t="inlineStr"/>
-      <c r="Q272" s="22" t="inlineStr"/>
-      <c r="R272" s="23" t="inlineStr"/>
-      <c r="S272" s="22" t="inlineStr"/>
-      <c r="T272" s="22" t="inlineStr">
+      <c r="O272" s="20" t="inlineStr"/>
+      <c r="P272" s="20" t="inlineStr"/>
+      <c r="Q272" s="20" t="inlineStr"/>
+      <c r="R272" s="21" t="inlineStr"/>
+      <c r="S272" s="20" t="inlineStr"/>
+      <c r="T272" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U272" s="22" t="inlineStr">
+      <c r="U272" s="20" t="inlineStr">
         <is>
           <t>AGMA SERVICES</t>
         </is>
       </c>
-      <c r="V272" s="22" t="inlineStr"/>
-      <c r="W272" s="22" t="inlineStr">
+      <c r="V272" s="20" t="inlineStr"/>
+      <c r="W272" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X272" s="22" t="inlineStr">
+      <c r="X272" s="20" t="inlineStr">
         <is>
           <t>64 AV de la Liberté</t>
         </is>
       </c>
-      <c r="Y272" s="23" t="inlineStr">
+      <c r="Y272" s="21" t="inlineStr">
         <is>
           <t>L1930</t>
         </is>
       </c>
-      <c r="Z272" s="22" t="inlineStr">
+      <c r="Z272" s="20" t="inlineStr">
         <is>
           <t>LUXEMBOURG</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="22" t="inlineStr">
+      <c r="A273" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B273" s="23" t="inlineStr">
+      <c r="B273" s="21" t="inlineStr">
         <is>
           <t>995078458</t>
         </is>
       </c>
-      <c r="C273" s="23" t="inlineStr">
+      <c r="C273" s="21" t="inlineStr">
         <is>
           <t>99507845800016</t>
         </is>
       </c>
-      <c r="D273" s="22" t="inlineStr">
+      <c r="D273" s="20" t="inlineStr">
         <is>
           <t>IL GIGLIO</t>
         </is>
       </c>
-      <c r="E273" s="22" t="inlineStr">
+      <c r="E273" s="20" t="inlineStr">
         <is>
           <t>IL GIGLIO</t>
         </is>
       </c>
-      <c r="F273" s="22" t="inlineStr">
+      <c r="F273" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G273" s="22" t="inlineStr">
+      <c r="G273" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H273" s="22" t="inlineStr">
+      <c r="H273" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I273" s="22" t="inlineStr">
+      <c r="I273" s="20" t="inlineStr">
         <is>
           <t>25/11/2025</t>
         </is>
       </c>
-      <c r="J273" s="22" t="inlineStr">
+      <c r="J273" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K273" s="22" t="inlineStr">
+      <c r="K273" s="20" t="inlineStr">
         <is>
           <t>5 RUE DU CHAMPE</t>
         </is>
       </c>
-      <c r="L273" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M273" s="22" t="inlineStr">
+      <c r="L273" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M273" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N273" s="22" t="inlineStr">
+      <c r="N273" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O273" s="22" t="inlineStr"/>
-      <c r="P273" s="22" t="inlineStr"/>
-      <c r="Q273" s="22" t="inlineStr"/>
-      <c r="R273" s="23" t="inlineStr"/>
-      <c r="S273" s="22" t="inlineStr"/>
-      <c r="T273" s="22" t="inlineStr">
+      <c r="O273" s="20" t="inlineStr"/>
+      <c r="P273" s="20" t="inlineStr"/>
+      <c r="Q273" s="20" t="inlineStr"/>
+      <c r="R273" s="21" t="inlineStr"/>
+      <c r="S273" s="20" t="inlineStr"/>
+      <c r="T273" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U273" s="22" t="inlineStr">
+      <c r="U273" s="20" t="inlineStr">
         <is>
           <t>STHRUDEL</t>
         </is>
       </c>
-      <c r="V273" s="22" t="inlineStr">
+      <c r="V273" s="20" t="inlineStr">
         <is>
           <t>Marie-claire</t>
         </is>
       </c>
-      <c r="W273" s="22" t="inlineStr">
+      <c r="W273" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X273" s="22" t="inlineStr">
+      <c r="X273" s="20" t="inlineStr">
         <is>
           <t>2 b rue maurice barrès</t>
         </is>
       </c>
-      <c r="Y273" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z273" s="22" t="inlineStr">
+      <c r="Y273" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z273" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="22" t="inlineStr">
+      <c r="A274" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B274" s="23" t="inlineStr">
+      <c r="B274" s="21" t="inlineStr">
         <is>
           <t>942629916</t>
         </is>
       </c>
-      <c r="C274" s="23" t="inlineStr">
+      <c r="C274" s="21" t="inlineStr">
         <is>
           <t>94262991600019</t>
         </is>
       </c>
-      <c r="D274" s="22" t="inlineStr">
+      <c r="D274" s="20" t="inlineStr">
         <is>
           <t>MEAT HOUSE</t>
         </is>
       </c>
-      <c r="E274" s="22" t="inlineStr">
+      <c r="E274" s="20" t="inlineStr">
         <is>
           <t>MEAT HOUSE</t>
         </is>
       </c>
-      <c r="F274" s="22" t="inlineStr">
+      <c r="F274" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G274" s="22" t="inlineStr">
+      <c r="G274" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H274" s="22" t="inlineStr">
+      <c r="H274" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I274" s="22" t="inlineStr">
+      <c r="I274" s="20" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="J274" s="22" t="inlineStr">
+      <c r="J274" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K274" s="22" t="inlineStr">
+      <c r="K274" s="20" t="inlineStr">
         <is>
           <t>18 RUE GAMBETTA</t>
         </is>
       </c>
-      <c r="L274" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M274" s="22" t="inlineStr">
+      <c r="L274" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M274" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N274" s="22" t="inlineStr">
+      <c r="N274" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O274" s="22" t="inlineStr"/>
-      <c r="P274" s="22" t="inlineStr"/>
-      <c r="Q274" s="22" t="inlineStr"/>
-      <c r="R274" s="23" t="inlineStr"/>
-      <c r="S274" s="22" t="inlineStr"/>
-      <c r="T274" s="22" t="inlineStr">
+      <c r="O274" s="20" t="inlineStr"/>
+      <c r="P274" s="20" t="inlineStr"/>
+      <c r="Q274" s="20" t="inlineStr"/>
+      <c r="R274" s="21" t="inlineStr"/>
+      <c r="S274" s="20" t="inlineStr"/>
+      <c r="T274" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U274" s="22" t="inlineStr">
+      <c r="U274" s="20" t="inlineStr">
         <is>
           <t>ERESLAN</t>
         </is>
       </c>
-      <c r="V274" s="22" t="inlineStr">
+      <c r="V274" s="20" t="inlineStr">
         <is>
           <t>Suleyman</t>
         </is>
       </c>
-      <c r="W274" s="22" t="inlineStr">
+      <c r="W274" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X274" s="22" t="inlineStr"/>
-      <c r="Y274" s="23" t="inlineStr"/>
-      <c r="Z274" s="22" t="inlineStr"/>
+      <c r="X274" s="20" t="inlineStr"/>
+      <c r="Y274" s="21" t="inlineStr"/>
+      <c r="Z274" s="20" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="22" t="inlineStr">
+      <c r="A275" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B275" s="23" t="inlineStr">
+      <c r="B275" s="21" t="inlineStr">
         <is>
           <t>483887311</t>
         </is>
       </c>
-      <c r="C275" s="23" t="inlineStr">
+      <c r="C275" s="21" t="inlineStr">
         <is>
           <t>48388731100015</t>
         </is>
       </c>
-      <c r="D275" s="22" t="inlineStr">
+      <c r="D275" s="20" t="inlineStr">
         <is>
           <t>NAMUR FRANCE</t>
         </is>
       </c>
-      <c r="E275" s="22" t="inlineStr">
+      <c r="E275" s="20" t="inlineStr">
         <is>
           <t>NAMUR FRANCE</t>
         </is>
       </c>
-      <c r="F275" s="22" t="inlineStr">
+      <c r="F275" s="20" t="inlineStr">
         <is>
           <t>SAS, société par actions simplifiée</t>
         </is>
       </c>
-      <c r="G275" s="22" t="inlineStr">
+      <c r="G275" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H275" s="22" t="inlineStr">
+      <c r="H275" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I275" s="22" t="inlineStr">
+      <c r="I275" s="20" t="inlineStr">
         <is>
           <t>01/09/2005</t>
         </is>
       </c>
-      <c r="J275" s="22" t="inlineStr">
+      <c r="J275" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="K275" s="22" t="inlineStr">
+      <c r="K275" s="20" t="inlineStr">
         <is>
           <t>7 PLACE DE LA CATHEDRALE</t>
         </is>
       </c>
-      <c r="L275" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M275" s="22" t="inlineStr">
+      <c r="L275" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M275" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N275" s="22" t="inlineStr">
+      <c r="N275" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O275" s="22" t="inlineStr"/>
-      <c r="P275" s="22" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q275" s="22" t="inlineStr"/>
-      <c r="R275" s="23" t="inlineStr"/>
-      <c r="S275" s="22" t="inlineStr"/>
-      <c r="T275" s="22" t="inlineStr">
+      <c r="O275" s="20" t="inlineStr"/>
+      <c r="P275" s="20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q275" s="20" t="inlineStr"/>
+      <c r="R275" s="21" t="inlineStr"/>
+      <c r="S275" s="20" t="inlineStr"/>
+      <c r="T275" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U275" s="22" t="inlineStr">
+      <c r="U275" s="20" t="inlineStr">
         <is>
           <t>NICKELS</t>
         </is>
       </c>
-      <c r="V275" s="22" t="inlineStr">
+      <c r="V275" s="20" t="inlineStr">
         <is>
           <t>Jean, Paul</t>
         </is>
       </c>
-      <c r="W275" s="22" t="inlineStr">
+      <c r="W275" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X275" s="22" t="inlineStr"/>
-      <c r="Y275" s="23" t="inlineStr">
+      <c r="X275" s="20" t="inlineStr"/>
+      <c r="Y275" s="21" t="inlineStr">
         <is>
           <t>8181</t>
         </is>
       </c>
-      <c r="Z275" s="22" t="inlineStr">
+      <c r="Z275" s="20" t="inlineStr">
         <is>
           <t>L 8131 BRIDEL (LUXEMBOURG)</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="22" t="inlineStr">
+      <c r="A276" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B276" s="23" t="inlineStr">
+      <c r="B276" s="21" t="inlineStr">
         <is>
           <t>381870401</t>
         </is>
       </c>
-      <c r="C276" s="23" t="inlineStr">
+      <c r="C276" s="21" t="inlineStr">
         <is>
           <t>38187040100027</t>
         </is>
       </c>
-      <c r="D276" s="22" t="inlineStr">
+      <c r="D276" s="20" t="inlineStr">
         <is>
           <t>D'ARGENTEAU</t>
         </is>
       </c>
-      <c r="E276" s="22" t="inlineStr">
+      <c r="E276" s="20" t="inlineStr">
         <is>
           <t>D'ARGENTEAU</t>
         </is>
       </c>
-      <c r="F276" s="22" t="inlineStr">
+      <c r="F276" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G276" s="22" t="inlineStr">
+      <c r="G276" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H276" s="22" t="inlineStr">
+      <c r="H276" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I276" s="22" t="inlineStr">
+      <c r="I276" s="20" t="inlineStr">
         <is>
           <t>30/04/1991</t>
         </is>
       </c>
-      <c r="J276" s="22" t="inlineStr">
+      <c r="J276" s="20" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="K276" s="22" t="inlineStr">
+      <c r="K276" s="20" t="inlineStr">
         <is>
           <t>1 RUE DU PALAIS</t>
         </is>
       </c>
-      <c r="L276" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M276" s="22" t="inlineStr">
+      <c r="L276" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M276" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N276" s="22" t="inlineStr">
+      <c r="N276" s="20" t="inlineStr">
         <is>
           <t>Entre 20 et 49 salariés</t>
         </is>
       </c>
-      <c r="O276" s="22" t="n">
-        <v>2360012</v>
-      </c>
-      <c r="P276" s="22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q276" s="22" t="inlineStr"/>
-      <c r="R276" s="23" t="inlineStr"/>
-      <c r="S276" s="22" t="inlineStr"/>
-      <c r="T276" s="22" t="inlineStr">
+      <c r="O276" s="20" t="inlineStr">
+        <is>
+          <t>2360012</t>
+        </is>
+      </c>
+      <c r="P276" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q276" s="20" t="inlineStr"/>
+      <c r="R276" s="21" t="inlineStr"/>
+      <c r="S276" s="20" t="inlineStr"/>
+      <c r="T276" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U276" s="22" t="inlineStr">
+      <c r="U276" s="20" t="inlineStr">
         <is>
           <t>GEHIN</t>
         </is>
       </c>
-      <c r="V276" s="22" t="inlineStr">
+      <c r="V276" s="20" t="inlineStr">
         <is>
           <t>Frédéric, Bernard</t>
         </is>
       </c>
-      <c r="W276" s="22" t="inlineStr">
+      <c r="W276" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X276" s="22" t="inlineStr">
+      <c r="X276" s="20" t="inlineStr">
         <is>
           <t>50 rue de Verdun</t>
         </is>
       </c>
-      <c r="Y276" s="23" t="inlineStr">
+      <c r="Y276" s="21" t="inlineStr">
         <is>
           <t>57160</t>
         </is>
       </c>
-      <c r="Z276" s="22" t="inlineStr">
+      <c r="Z276" s="20" t="inlineStr">
         <is>
           <t>Moulins-lès-Metz</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="22" t="inlineStr">
+      <c r="A277" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B277" s="23" t="inlineStr">
+      <c r="B277" s="21" t="inlineStr">
         <is>
           <t>749887006</t>
         </is>
       </c>
-      <c r="C277" s="23" t="inlineStr">
+      <c r="C277" s="21" t="inlineStr">
         <is>
           <t>74988700600015</t>
         </is>
       </c>
-      <c r="D277" s="22" t="inlineStr">
+      <c r="D277" s="20" t="inlineStr">
         <is>
           <t>LE PALAIS DU SOLEIL (SOCIETE EN LIQUIDATION)</t>
         </is>
       </c>
-      <c r="E277" s="22" t="inlineStr">
+      <c r="E277" s="20" t="inlineStr">
         <is>
           <t>LE PALAIS DU SOLEIL (SOCIETE EN LIQUIDATION)</t>
         </is>
       </c>
-      <c r="F277" s="22" t="inlineStr">
+      <c r="F277" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G277" s="22" t="inlineStr">
+      <c r="G277" s="20" t="inlineStr">
         <is>
           <t>56.10C</t>
         </is>
       </c>
-      <c r="H277" s="22" t="inlineStr">
+      <c r="H277" s="20" t="inlineStr">
         <is>
           <t>Restauration de type rapide</t>
         </is>
       </c>
-      <c r="I277" s="22" t="inlineStr">
+      <c r="I277" s="20" t="inlineStr">
         <is>
           <t>01/01/2012</t>
         </is>
       </c>
-      <c r="J277" s="22" t="inlineStr">
+      <c r="J277" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="K277" s="22" t="inlineStr">
+      <c r="K277" s="20" t="inlineStr">
         <is>
           <t>23 RUE DU PONT DES MORTS</t>
         </is>
       </c>
-      <c r="L277" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M277" s="22" t="inlineStr">
+      <c r="L277" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M277" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N277" s="22" t="inlineStr">
+      <c r="N277" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O277" s="22" t="inlineStr"/>
-      <c r="P277" s="22" t="inlineStr"/>
-      <c r="Q277" s="22" t="inlineStr"/>
-      <c r="R277" s="23" t="inlineStr"/>
-      <c r="S277" s="22" t="inlineStr"/>
-      <c r="T277" s="22" t="inlineStr">
+      <c r="O277" s="20" t="inlineStr"/>
+      <c r="P277" s="20" t="inlineStr"/>
+      <c r="Q277" s="20" t="inlineStr"/>
+      <c r="R277" s="21" t="inlineStr"/>
+      <c r="S277" s="20" t="inlineStr"/>
+      <c r="T277" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U277" s="22" t="inlineStr">
+      <c r="U277" s="20" t="inlineStr">
         <is>
           <t>MAHMOOD</t>
         </is>
       </c>
-      <c r="V277" s="22" t="inlineStr">
+      <c r="V277" s="20" t="inlineStr">
         <is>
           <t>Abbas</t>
         </is>
       </c>
-      <c r="W277" s="22" t="inlineStr">
+      <c r="W277" s="20" t="inlineStr">
         <is>
           <t>Liquidateur</t>
         </is>
       </c>
-      <c r="X277" s="22" t="inlineStr">
+      <c r="X277" s="20" t="inlineStr">
         <is>
           <t>23 rue du Pont des Morts</t>
         </is>
       </c>
-      <c r="Y277" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z277" s="22" t="inlineStr">
+      <c r="Y277" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z277" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="22" t="inlineStr">
+      <c r="A278" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B278" s="23" t="inlineStr">
+      <c r="B278" s="21" t="inlineStr">
         <is>
           <t>884426107</t>
         </is>
       </c>
-      <c r="C278" s="23" t="inlineStr">
+      <c r="C278" s="21" t="inlineStr">
         <is>
           <t>88442610700014</t>
         </is>
       </c>
-      <c r="D278" s="22" t="inlineStr">
+      <c r="D278" s="20" t="inlineStr">
         <is>
           <t>FRASANABAR</t>
         </is>
       </c>
-      <c r="E278" s="22" t="inlineStr">
+      <c r="E278" s="20" t="inlineStr">
         <is>
           <t>FRASANABAR</t>
         </is>
       </c>
-      <c r="F278" s="22" t="inlineStr">
+      <c r="F278" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G278" s="22" t="inlineStr">
+      <c r="G278" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H278" s="22" t="inlineStr">
+      <c r="H278" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I278" s="22" t="inlineStr">
+      <c r="I278" s="20" t="inlineStr">
         <is>
           <t>19/06/2020</t>
         </is>
       </c>
-      <c r="J278" s="22" t="inlineStr">
+      <c r="J278" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="K278" s="22" t="inlineStr">
+      <c r="K278" s="20" t="inlineStr">
         <is>
           <t>4 RUE SAINTE MARIE</t>
         </is>
       </c>
-      <c r="L278" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M278" s="22" t="inlineStr">
+      <c r="L278" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M278" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N278" s="22" t="inlineStr">
+      <c r="N278" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O278" s="22" t="inlineStr"/>
-      <c r="P278" s="22" t="inlineStr"/>
-      <c r="Q278" s="22" t="inlineStr"/>
-      <c r="R278" s="23" t="inlineStr"/>
-      <c r="S278" s="22" t="inlineStr"/>
-      <c r="T278" s="22" t="inlineStr">
+      <c r="O278" s="20" t="inlineStr"/>
+      <c r="P278" s="20" t="inlineStr"/>
+      <c r="Q278" s="20" t="inlineStr"/>
+      <c r="R278" s="21" t="inlineStr"/>
+      <c r="S278" s="20" t="inlineStr"/>
+      <c r="T278" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U278" s="22" t="inlineStr">
+      <c r="U278" s="20" t="inlineStr">
         <is>
           <t>SERURIER</t>
         </is>
       </c>
-      <c r="V278" s="22" t="inlineStr">
+      <c r="V278" s="20" t="inlineStr">
         <is>
           <t>Franck</t>
         </is>
       </c>
-      <c r="W278" s="22" t="inlineStr">
+      <c r="W278" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X278" s="22" t="inlineStr">
+      <c r="X278" s="20" t="inlineStr">
         <is>
           <t>45 Grande Rue Grand Rue</t>
         </is>
       </c>
-      <c r="Y278" s="23" t="inlineStr">
+      <c r="Y278" s="21" t="inlineStr">
         <is>
           <t>54470</t>
         </is>
       </c>
-      <c r="Z278" s="22" t="inlineStr">
+      <c r="Z278" s="20" t="inlineStr">
         <is>
           <t>Limey-Remenauville</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="22" t="inlineStr">
+      <c r="A279" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B279" s="23" t="inlineStr">
+      <c r="B279" s="21" t="inlineStr">
         <is>
           <t>830223871</t>
         </is>
       </c>
-      <c r="C279" s="23" t="inlineStr">
+      <c r="C279" s="21" t="inlineStr">
         <is>
           <t>83022387100013</t>
         </is>
       </c>
-      <c r="D279" s="22" t="inlineStr">
+      <c r="D279" s="20" t="inlineStr">
         <is>
           <t>AVENUE CAFE DE NANCY</t>
         </is>
       </c>
-      <c r="E279" s="22" t="inlineStr">
+      <c r="E279" s="20" t="inlineStr">
         <is>
           <t>AVENUE CAFE DE NANCY</t>
         </is>
       </c>
-      <c r="F279" s="22" t="inlineStr">
+      <c r="F279" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G279" s="22" t="inlineStr">
+      <c r="G279" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H279" s="22" t="inlineStr">
+      <c r="H279" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I279" s="22" t="inlineStr">
+      <c r="I279" s="20" t="inlineStr">
         <is>
           <t>13/06/2017</t>
         </is>
       </c>
-      <c r="J279" s="22" t="inlineStr">
+      <c r="J279" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K279" s="22" t="inlineStr">
+      <c r="K279" s="20" t="inlineStr">
         <is>
           <t>1 B AVENUE DE LATTRE DE TASSIGNY</t>
         </is>
       </c>
-      <c r="L279" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M279" s="22" t="inlineStr">
+      <c r="L279" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M279" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N279" s="22" t="inlineStr">
+      <c r="N279" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O279" s="22" t="inlineStr"/>
-      <c r="P279" s="22" t="inlineStr"/>
-      <c r="Q279" s="22" t="inlineStr"/>
-      <c r="R279" s="23" t="inlineStr"/>
-      <c r="S279" s="22" t="inlineStr"/>
-      <c r="T279" s="22" t="inlineStr">
+      <c r="O279" s="20" t="inlineStr"/>
+      <c r="P279" s="20" t="inlineStr"/>
+      <c r="Q279" s="20" t="inlineStr"/>
+      <c r="R279" s="21" t="inlineStr"/>
+      <c r="S279" s="20" t="inlineStr"/>
+      <c r="T279" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U279" s="22" t="inlineStr">
+      <c r="U279" s="20" t="inlineStr">
         <is>
           <t>ALLALI</t>
         </is>
       </c>
-      <c r="V279" s="22" t="inlineStr">
+      <c r="V279" s="20" t="inlineStr">
         <is>
           <t>Nasser</t>
         </is>
       </c>
-      <c r="W279" s="22" t="inlineStr">
+      <c r="W279" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X279" s="22" t="inlineStr">
+      <c r="X279" s="20" t="inlineStr">
         <is>
           <t>10 rue Dupont des Loges</t>
         </is>
       </c>
-      <c r="Y279" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z279" s="22" t="inlineStr">
+      <c r="Y279" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z279" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="22" t="inlineStr">
+      <c r="A280" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B280" s="23" t="inlineStr">
+      <c r="B280" s="21" t="inlineStr">
         <is>
           <t>981763824</t>
         </is>
       </c>
-      <c r="C280" s="23" t="inlineStr">
+      <c r="C280" s="21" t="inlineStr">
         <is>
           <t>98176382400019</t>
         </is>
       </c>
-      <c r="D280" s="22" t="inlineStr">
+      <c r="D280" s="20" t="inlineStr">
         <is>
           <t>LE BISTROT DES AMIS</t>
         </is>
       </c>
-      <c r="E280" s="22" t="inlineStr">
+      <c r="E280" s="20" t="inlineStr">
         <is>
           <t>LE BISTROT DES AMIS</t>
         </is>
       </c>
-      <c r="F280" s="22" t="inlineStr">
+      <c r="F280" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G280" s="22" t="inlineStr">
+      <c r="G280" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H280" s="22" t="inlineStr">
+      <c r="H280" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I280" s="22" t="inlineStr">
+      <c r="I280" s="20" t="inlineStr">
         <is>
           <t>20/11/2023</t>
         </is>
       </c>
-      <c r="J280" s="22" t="inlineStr">
+      <c r="J280" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K280" s="22" t="inlineStr">
+      <c r="K280" s="20" t="inlineStr">
         <is>
           <t>37 RUE DE LA CHAPELLE</t>
         </is>
       </c>
-      <c r="L280" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M280" s="22" t="inlineStr">
+      <c r="L280" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M280" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N280" s="22" t="inlineStr">
+      <c r="N280" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O280" s="22" t="inlineStr"/>
-      <c r="P280" s="22" t="inlineStr"/>
-      <c r="Q280" s="22" t="inlineStr"/>
-      <c r="R280" s="23" t="inlineStr"/>
-      <c r="S280" s="22" t="inlineStr"/>
-      <c r="T280" s="22" t="inlineStr">
+      <c r="O280" s="20" t="inlineStr"/>
+      <c r="P280" s="20" t="inlineStr"/>
+      <c r="Q280" s="20" t="inlineStr"/>
+      <c r="R280" s="21" t="inlineStr"/>
+      <c r="S280" s="20" t="inlineStr"/>
+      <c r="T280" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U280" s="22" t="inlineStr">
+      <c r="U280" s="20" t="inlineStr">
         <is>
           <t>YILDIRIM</t>
         </is>
       </c>
-      <c r="V280" s="22" t="inlineStr">
+      <c r="V280" s="20" t="inlineStr">
         <is>
           <t>Ilfer</t>
         </is>
       </c>
-      <c r="W280" s="22" t="inlineStr">
+      <c r="W280" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X280" s="22" t="inlineStr">
+      <c r="X280" s="20" t="inlineStr">
         <is>
           <t>134 avenue andre malraux</t>
         </is>
       </c>
-      <c r="Y280" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z280" s="22" t="inlineStr">
+      <c r="Y280" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z280" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="22" t="inlineStr">
+      <c r="A281" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B281" s="23" t="inlineStr">
+      <c r="B281" s="21" t="inlineStr">
         <is>
           <t>823430798</t>
         </is>
       </c>
-      <c r="C281" s="23" t="inlineStr">
+      <c r="C281" s="21" t="inlineStr">
         <is>
           <t>82343079800012</t>
         </is>
       </c>
-      <c r="D281" s="22" t="inlineStr">
+      <c r="D281" s="20" t="inlineStr">
         <is>
           <t>LES TROIS MOUSSEQUETAIRES</t>
         </is>
       </c>
-      <c r="E281" s="22" t="inlineStr">
+      <c r="E281" s="20" t="inlineStr">
         <is>
           <t>LES TROIS MOUSSEQUETAIRES</t>
         </is>
       </c>
-      <c r="F281" s="22" t="inlineStr">
+      <c r="F281" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G281" s="22" t="inlineStr">
+      <c r="G281" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H281" s="22" t="inlineStr">
+      <c r="H281" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I281" s="22" t="inlineStr">
+      <c r="I281" s="20" t="inlineStr">
         <is>
           <t>21/10/2016</t>
         </is>
       </c>
-      <c r="J281" s="22" t="inlineStr">
+      <c r="J281" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K281" s="22" t="inlineStr">
+      <c r="K281" s="20" t="inlineStr">
         <is>
           <t>18 RUE TAISON</t>
         </is>
       </c>
-      <c r="L281" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M281" s="22" t="inlineStr">
+      <c r="L281" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M281" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N281" s="22" t="inlineStr">
+      <c r="N281" s="20" t="inlineStr">
         <is>
           <t>Entre 6 et 9 salariés</t>
         </is>
       </c>
-      <c r="O281" s="22" t="inlineStr"/>
-      <c r="P281" s="22" t="inlineStr"/>
-      <c r="Q281" s="22" t="inlineStr"/>
-      <c r="R281" s="23" t="inlineStr"/>
-      <c r="S281" s="22" t="inlineStr"/>
-      <c r="T281" s="22" t="inlineStr">
+      <c r="O281" s="20" t="inlineStr"/>
+      <c r="P281" s="20" t="inlineStr"/>
+      <c r="Q281" s="20" t="inlineStr"/>
+      <c r="R281" s="21" t="inlineStr"/>
+      <c r="S281" s="20" t="inlineStr"/>
+      <c r="T281" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U281" s="22" t="inlineStr">
+      <c r="U281" s="20" t="inlineStr">
         <is>
           <t>PILLET</t>
         </is>
       </c>
-      <c r="V281" s="22" t="inlineStr">
+      <c r="V281" s="20" t="inlineStr">
         <is>
           <t>Baptiste, André, Michel</t>
         </is>
       </c>
-      <c r="W281" s="22" t="inlineStr">
+      <c r="W281" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X281" s="22" t="inlineStr">
+      <c r="X281" s="20" t="inlineStr">
         <is>
           <t>9 Rue du Pont des Morts</t>
         </is>
       </c>
-      <c r="Y281" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z281" s="22" t="inlineStr">
+      <c r="Y281" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z281" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="22" t="inlineStr">
+      <c r="A282" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B282" s="23" t="inlineStr">
+      <c r="B282" s="21" t="inlineStr">
         <is>
           <t>834496119</t>
         </is>
       </c>
-      <c r="C282" s="23" t="inlineStr">
+      <c r="C282" s="21" t="inlineStr">
         <is>
           <t>83449611900019</t>
         </is>
       </c>
-      <c r="D282" s="22" t="inlineStr">
+      <c r="D282" s="20" t="inlineStr">
         <is>
           <t>SAMOX</t>
         </is>
       </c>
-      <c r="E282" s="22" t="inlineStr">
+      <c r="E282" s="20" t="inlineStr">
         <is>
           <t>SAMOX</t>
         </is>
       </c>
-      <c r="F282" s="22" t="inlineStr">
+      <c r="F282" s="20" t="inlineStr">
         <is>
           <t>SASU, société par actions simplifiée unipersonnelle</t>
         </is>
       </c>
-      <c r="G282" s="22" t="inlineStr">
+      <c r="G282" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H282" s="22" t="inlineStr">
+      <c r="H282" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I282" s="22" t="inlineStr">
+      <c r="I282" s="20" t="inlineStr">
         <is>
           <t>10/01/2018</t>
         </is>
       </c>
-      <c r="J282" s="22" t="inlineStr">
+      <c r="J282" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K282" s="22" t="inlineStr">
+      <c r="K282" s="20" t="inlineStr">
         <is>
           <t>4 RUE DU CHANGE</t>
         </is>
       </c>
-      <c r="L282" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M282" s="22" t="inlineStr">
+      <c r="L282" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M282" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N282" s="22" t="inlineStr">
+      <c r="N282" s="20" t="inlineStr">
         <is>
           <t>Entre 3 et 5 salariés</t>
         </is>
       </c>
-      <c r="O282" s="22" t="inlineStr"/>
-      <c r="P282" s="22" t="inlineStr"/>
-      <c r="Q282" s="22" t="inlineStr"/>
-      <c r="R282" s="23" t="inlineStr"/>
-      <c r="S282" s="22" t="inlineStr"/>
-      <c r="T282" s="22" t="inlineStr">
+      <c r="O282" s="20" t="inlineStr"/>
+      <c r="P282" s="20" t="inlineStr"/>
+      <c r="Q282" s="20" t="inlineStr"/>
+      <c r="R282" s="21" t="inlineStr"/>
+      <c r="S282" s="20" t="inlineStr"/>
+      <c r="T282" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U282" s="22" t="inlineStr">
+      <c r="U282" s="20" t="inlineStr">
         <is>
           <t>DURAL</t>
         </is>
       </c>
-      <c r="V282" s="22" t="inlineStr">
+      <c r="V282" s="20" t="inlineStr">
         <is>
           <t>Mahsum</t>
         </is>
       </c>
-      <c r="W282" s="22" t="inlineStr">
+      <c r="W282" s="20" t="inlineStr">
         <is>
           <t>Président</t>
         </is>
       </c>
-      <c r="X282" s="22" t="inlineStr">
+      <c r="X282" s="20" t="inlineStr">
         <is>
           <t>11 rue de Pont à Mousson</t>
         </is>
       </c>
-      <c r="Y282" s="23" t="inlineStr">
+      <c r="Y282" s="21" t="inlineStr">
         <is>
           <t>57380</t>
         </is>
       </c>
-      <c r="Z282" s="22" t="inlineStr">
+      <c r="Z282" s="20" t="inlineStr">
         <is>
           <t>Faulquemont</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="22" t="inlineStr">
+      <c r="A283" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B283" s="23" t="inlineStr">
+      <c r="B283" s="21" t="inlineStr">
         <is>
           <t>500497961</t>
         </is>
       </c>
-      <c r="C283" s="23" t="inlineStr">
+      <c r="C283" s="21" t="inlineStr">
         <is>
           <t>50049796100010</t>
         </is>
       </c>
-      <c r="D283" s="22" t="inlineStr">
+      <c r="D283" s="20" t="inlineStr">
         <is>
           <t>FOETZ Joel</t>
         </is>
       </c>
-      <c r="E283" s="22" t="inlineStr">
+      <c r="E283" s="20" t="inlineStr">
         <is>
           <t>FOETZ Joel</t>
         </is>
       </c>
-      <c r="F283" s="22" t="inlineStr">
+      <c r="F283" s="20" t="inlineStr">
         <is>
           <t>Entrepreneur individuel</t>
         </is>
       </c>
-      <c r="G283" s="22" t="inlineStr">
+      <c r="G283" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H283" s="22" t="inlineStr">
+      <c r="H283" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I283" s="22" t="inlineStr">
+      <c r="I283" s="20" t="inlineStr">
         <is>
           <t>28/09/2007</t>
         </is>
       </c>
-      <c r="J283" s="22" t="inlineStr">
+      <c r="J283" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="K283" s="22" t="inlineStr">
+      <c r="K283" s="20" t="inlineStr">
         <is>
           <t>27 RUE LAFAYETTE</t>
         </is>
       </c>
-      <c r="L283" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M283" s="22" t="inlineStr">
+      <c r="L283" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M283" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N283" s="22" t="inlineStr">
+      <c r="N283" s="20" t="inlineStr">
         <is>
           <t>0 salarié</t>
         </is>
       </c>
-      <c r="O283" s="22" t="inlineStr"/>
-      <c r="P283" s="22" t="inlineStr"/>
-      <c r="Q283" s="22" t="inlineStr"/>
-      <c r="R283" s="23" t="inlineStr"/>
-      <c r="S283" s="22" t="inlineStr"/>
-      <c r="T283" s="22" t="inlineStr">
+      <c r="O283" s="20" t="inlineStr"/>
+      <c r="P283" s="20" t="inlineStr"/>
+      <c r="Q283" s="20" t="inlineStr"/>
+      <c r="R283" s="21" t="inlineStr"/>
+      <c r="S283" s="20" t="inlineStr"/>
+      <c r="T283" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U283" s="22" t="inlineStr">
+      <c r="U283" s="20" t="inlineStr">
         <is>
           <t>FOETZ</t>
         </is>
       </c>
-      <c r="V283" s="22" t="inlineStr">
+      <c r="V283" s="20" t="inlineStr">
         <is>
           <t>Joel</t>
         </is>
       </c>
-      <c r="W283" s="22" t="inlineStr">
+      <c r="W283" s="20" t="inlineStr">
         <is>
           <t>Chef d'entreprise</t>
         </is>
       </c>
-      <c r="X283" s="22" t="inlineStr"/>
-      <c r="Y283" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z283" s="22" t="inlineStr">
+      <c r="X283" s="20" t="inlineStr"/>
+      <c r="Y283" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z283" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="22" t="inlineStr">
+      <c r="A284" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B284" s="23" t="inlineStr">
+      <c r="B284" s="21" t="inlineStr">
         <is>
           <t>992901124</t>
         </is>
       </c>
-      <c r="C284" s="23" t="inlineStr">
+      <c r="C284" s="21" t="inlineStr">
         <is>
           <t>99290112400014</t>
         </is>
       </c>
-      <c r="D284" s="22" t="inlineStr">
+      <c r="D284" s="20" t="inlineStr">
         <is>
           <t>JBCED</t>
         </is>
       </c>
-      <c r="E284" s="22" t="inlineStr">
+      <c r="E284" s="20" t="inlineStr">
         <is>
           <t>JBCED</t>
         </is>
       </c>
-      <c r="F284" s="22" t="inlineStr">
+      <c r="F284" s="20" t="inlineStr">
         <is>
           <t>SARL, société à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G284" s="22" t="inlineStr">
+      <c r="G284" s="20" t="inlineStr">
         <is>
           <t>56.30Z</t>
         </is>
       </c>
-      <c r="H284" s="22" t="inlineStr">
+      <c r="H284" s="20" t="inlineStr">
         <is>
           <t>Débits de boissons</t>
         </is>
       </c>
-      <c r="I284" s="22" t="inlineStr">
+      <c r="I284" s="20" t="inlineStr">
         <is>
           <t>07/10/2025</t>
         </is>
       </c>
-      <c r="J284" s="22" t="inlineStr">
+      <c r="J284" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K284" s="22" t="inlineStr">
+      <c r="K284" s="20" t="inlineStr">
         <is>
           <t>5 RUE DE LA FONTAINE</t>
         </is>
       </c>
-      <c r="L284" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M284" s="22" t="inlineStr">
+      <c r="L284" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M284" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N284" s="22" t="inlineStr">
+      <c r="N284" s="20" t="inlineStr">
         <is>
           <t>Au moins 1 salarié</t>
         </is>
       </c>
-      <c r="O284" s="22" t="inlineStr"/>
-      <c r="P284" s="22" t="inlineStr"/>
-      <c r="Q284" s="22" t="inlineStr"/>
-      <c r="R284" s="23" t="inlineStr"/>
-      <c r="S284" s="22" t="inlineStr"/>
-      <c r="T284" s="22" t="inlineStr">
+      <c r="O284" s="20" t="inlineStr"/>
+      <c r="P284" s="20" t="inlineStr"/>
+      <c r="Q284" s="20" t="inlineStr"/>
+      <c r="R284" s="21" t="inlineStr"/>
+      <c r="S284" s="20" t="inlineStr"/>
+      <c r="T284" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U284" s="22" t="inlineStr">
+      <c r="U284" s="20" t="inlineStr">
         <is>
           <t>HEITZMANN</t>
         </is>
       </c>
-      <c r="V284" s="22" t="inlineStr">
+      <c r="V284" s="20" t="inlineStr">
         <is>
           <t>Jean-baptiste, Angel, André</t>
         </is>
       </c>
-      <c r="W284" s="22" t="inlineStr">
+      <c r="W284" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X284" s="22" t="inlineStr">
+      <c r="X284" s="20" t="inlineStr">
         <is>
           <t>3, rue de la fontaine</t>
         </is>
       </c>
-      <c r="Y284" s="23" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="Z284" s="22" t="inlineStr">
+      <c r="Y284" s="21" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="Z284" s="20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="22" t="inlineStr">
+      <c r="A285" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B285" s="23" t="inlineStr">
+      <c r="B285" s="21" t="inlineStr">
         <is>
           <t>309444545</t>
         </is>
       </c>
-      <c r="C285" s="23" t="inlineStr">
+      <c r="C285" s="21" t="inlineStr">
         <is>
           <t>30944454500011</t>
         </is>
       </c>
-      <c r="D285" s="22" t="inlineStr">
+      <c r="D285" s="20" t="inlineStr">
         <is>
           <t>LA TOSCANE</t>
         </is>
       </c>
-      <c r="E285" s="22" t="inlineStr">
+      <c r="E285" s="20" t="inlineStr">
         <is>
           <t>LA TOSCANE</t>
         </is>
       </c>
-      <c r="F285" s="22" t="inlineStr">
+      <c r="F285" s="20" t="inlineStr">
         <is>
           <t>EURL, entreprise unipersonnelle à responsabilité limitée</t>
         </is>
       </c>
-      <c r="G285" s="22" t="inlineStr">
+      <c r="G285" s="20" t="inlineStr">
         <is>
           <t>56.10A</t>
         </is>
       </c>
-      <c r="H285" s="22" t="inlineStr">
+      <c r="H285" s="20" t="inlineStr">
         <is>
           <t>Restauration traditionnelle</t>
         </is>
       </c>
-      <c r="I285" s="22" t="inlineStr">
+      <c r="I285" s="20" t="inlineStr">
         <is>
           <t>01/01/1977</t>
         </is>
       </c>
-      <c r="J285" s="22" t="inlineStr">
+      <c r="J285" s="20" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="K285" s="22" t="inlineStr">
+      <c r="K285" s="20" t="inlineStr">
         <is>
           <t>12 RUE DUPONT DES LOGES</t>
         </is>
       </c>
-      <c r="L285" s="22" t="inlineStr">
-        <is>
-          <t>57000</t>
-        </is>
-      </c>
-      <c r="M285" s="22" t="inlineStr">
+      <c r="L285" s="20" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+      <c r="M285" s="20" t="inlineStr">
         <is>
           <t>METZ</t>
         </is>
       </c>
-      <c r="N285" s="22" t="inlineStr">
+      <c r="N285" s="20" t="inlineStr">
         <is>
           <t>Entre 10 et 19 salariés</t>
         </is>
       </c>
-      <c r="O285" s="22" t="inlineStr"/>
-      <c r="P285" s="22" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q285" s="22" t="inlineStr"/>
-      <c r="R285" s="23" t="inlineStr"/>
-      <c r="S285" s="22" t="inlineStr"/>
-      <c r="T285" s="22" t="inlineStr">
+      <c r="O285" s="20" t="inlineStr"/>
+      <c r="P285" s="20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q285" s="20" t="inlineStr"/>
+      <c r="R285" s="21" t="inlineStr"/>
+      <c r="S285" s="20" t="inlineStr"/>
+      <c r="T285" s="20" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="U285" s="22" t="inlineStr">
+      <c r="U285" s="20" t="inlineStr">
         <is>
           <t>Belkacem</t>
         </is>
       </c>
-      <c r="V285" s="22" t="inlineStr">
+      <c r="V285" s="20" t="inlineStr">
         <is>
           <t>Mohand, -, Larbi</t>
         </is>
       </c>
-      <c r="W285" s="22" t="inlineStr">
+      <c r="W285" s="20" t="inlineStr">
         <is>
           <t>Gérant</t>
         </is>
       </c>
-      <c r="X285" s="22" t="inlineStr"/>
-      <c r="Y285" s="23" t="inlineStr">
+      <c r="X285" s="20" t="inlineStr"/>
+      <c r="Y285" s="21" t="inlineStr">
         <is>
           <t>92200</t>
         </is>
       </c>
-      <c r="Z285" s="22" t="inlineStr">
+      <c r="Z285" s="20" t="inlineStr">
         <is>
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="22" t="inlineStr">
+      <c r="A286" s="20" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B286" s